--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,20 +424,30 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>Cifrão</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>Preço</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Virgula</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
         <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Imagem</t>
         </is>
@@ -446,729 +456,999 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Smart Tv 43 Philco P43vik Roku Led Dolby Audio Wi-fi Hdmi Hdr Full Hd 110/220v</t>
+          <t>Kindle 11ª Geração 2024 16gb 6 Antirreflexo Wifi B0cp31l73x Preto</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R$1.454</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>41% OFF no Pix</t>
+          <t>30.000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-43-philco-p43vik-roku-led-dolby-audio-wi-fi-hdmi-hdr-full-hd-110220v/p/MLB63040715?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=1&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4367472775&amp;sid=offers</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_697288-MLA100482486016_122025-AB.webp</t>
+          <t>5% OFF</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/kindle-11-geraco-2024-16gb-6-antirreflexo-wifi-b0cp31l73x/p/MLB52876876?pdp_filters=item_id%3AMLB6601488498&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB6601488498&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_663824-MLA99565687760_122025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Smart Tv Profissional 4k 55  LG Uhd 55au801 Processador 7 Ai Ger8 Super Upscaling Google Cast Alexa Integrado Controle Ai Smart Magic Webos 25</t>
+          <t>Seca Salada Centrífuga Secador De Verduras Manual 3l Cor Transparente</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R$2.469</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38% OFF no Pix</t>
+          <t>0</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-profissional-4k-55-lg-uhd-55au801-processador-7-ai-ger8-super-upscaling-google-cast-alexa-integrado-controle-ai-smart-magic-webos-25/p/MLB58587883?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=2&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4233056093&amp;sid=offers</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_997328-MLA101890264991_122025-AB.webp</t>
+          <t>68% OFF</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/seca-salada-centrifuga-secador-de-verduras-manual-3l-cor-transparente/p/MLB50925841?pdp_filters=item_id%3AMLB5418491250&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB5418491250&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_643381-MLA100095729143_122025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Smart Tv 32 Philco P32vik Roku Led Dolby Audio Hdr Wi-fi 110/220v</t>
+          <t>Kit Fran Love Kit Gloss Labial E Lápis Labial By Franciny</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R$928,32</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>38% OFF no Pix</t>
+          <t>767</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-32-philco-p32vik-roku-led-dolby-audio-hdr-wi-fi-110220v/p/MLB63036814?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=3&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4367472233&amp;sid=offers</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_691057-MLA100479527690_122025-AB.webp</t>
+          <t>37% OFF</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/kit-fran-love-kit-gloss-labial-e-lapis-labial-by-franciny/up/MLBU3214981421?pdp_filters=item_id%3AMLB5415887354&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB5415887354&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_666525-MLB85597283317_062025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Smart Tv LG Uhd Ai Ua75 43 Polegadas Hdr10 Pro Processador 7 Ai Ger8 Webos 25</t>
+          <t>Perfect Pro Condor 973373 Carro De Limpeza Multifuncional C/ Saco Coletor Preto</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R$1.671</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>44% OFF no Pix</t>
+          <t>74</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-lg-uhd-ai-ua75-43-polegadas-hdr10-pro-processador-7-ai-ger8-webos-25/p/MLB51227508?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=4&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB5751232640&amp;sid=offers</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_879007-MLA107588019293_022026-AB.webp</t>
+          <t>32% OFF</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/perfect-pro-condor-973373-carro-de-limpeza-multifuncional-c-saco-coletor/p/MLB28201233?pdp_filters=item_id%3AMLB5124129244&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB5124129244&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_636759-MLA96153269857_102025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Smart Tv Aoc 40  40s5045/78g Roku Tv Dled Full Hd</t>
+          <t>Klm Kit Sds Plus Martelete Ponteiro E Talhadeiras Jogo 3 Peças 20mm E 40mm Compatível Com Todas As Marcas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R$1.234</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>38% OFF no Pix</t>
+          <t>29</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-aoc-40-40s504578g-roku-tv-dled-full-hd/p/MLB43554996?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=5&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4330366495&amp;sid=offers</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_828643-MLA99975300399_112025-AB.webp</t>
+          <t>47% OFF</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/klm-kit-sds-plus-martelete-ponteiro-e-talhadeiras-jogo-3-pecas-20mm-e-40mm-compativel-com-todas-as-marcas/p/MLB47892578?pdp_filters=item_id%3AMLB5360733834&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB5360733834&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_694311-MLA109933866197_042026-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Smart Tv Samsung 32 Ls32h5000fgxzd Hd Led Wifi Hdmi 110/220v</t>
+          <t>Kit 2 Refil Para Mop Giratorio Fit Esfregão De Microfibra Rmop5011 Flash Limp</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R$901,18</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>43% OFF no Pix</t>
+          <t>27</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-samsung-32-ls32h5000fgxzd-hd-led-wifi-hdmi-110220v/p/MLB66191173?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=6&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB6444937486&amp;sid=offers</t>
+          <t>06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_899090-MLA107424021398_032026-AB.webp</t>
+          <t>37% OFF</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/kit-2-refil-para-mop-giratorio-fit-esfrego-de-microfibra-rmop5011-flash-limp/p/MLB29509211?pdp_filters=item_id%3AMLB4197810629&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB4197810629&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_996264-MLA99926132931_112025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Smart Tv LG Qned Ai 4k Qned82 75 Polegadas 2025 Cores Dinâmicas Qned Processador 7 Ai Ger 8</t>
+          <t>Espremedor De Limão Aço Inox Manual Forte Resistente Goumert Pratico - Efigen Prateado</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R$6.649</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>39% OFF no Pix</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>https://click1.mercadolivre.com.br/mclics/clicks/external/MLB/count?a=u2sLqwVCwW9VmAuOXXpHOoI5G9ZBNSGDq1vjDw8FGBdU9Ze6iPtRqySiw5XxmlW7m31NdjfzHkByRcWRGqhNvYE7AU7xVL%2Bw66Y%2Ffvu%2B0NQA1vmlnPKSoHZxDMaF5E0oJ9dYj0Rhr8BwSqSK5rfNSsdgbD2blYIprJmxa922NTPReZdIiWTbP%2BJodtxYipHOQMZUJditMRrRCFK0p7TEWSiVSxITJEIIPhLz3IrE7jqb8Y3SZLTQXSwTlncC5zl%2F4QNnmxEdVOklkNMuUgodmH5n5BJKUkCfXlKls2XV6Ioa%2BT3Av%2BC5UUbSGrhRXUojliqezdn12m7fv%2BGe08Mq28gS11n%2F7wzZHuLMOJjGY6vXEKmJVXPFManuwNALcNK8Lh4UklSrQDCFHd0gzZjlwS6%2BQJLSCLu7OsUj52iwkBEg%2B2ir0jVplggEqxHWfw29PP27VJ1%2FA6VEY2eyKVU1W6kZyNzetopMMwJIl0SbpTI44W%2BOOBXITdSXFmnu884bmx6GgsUWRg%2FFUN0%2FI6OUy65CKPKmMAoCcrT%2B5Q%3D%3D&amp;url=https%3A%2F%2Fwww.mercadolivre.com.br%2Fsmart-tv-lg-qned-ai-4k-qned82-75-polegadas-2025-cores-dinmicas-qned-processador-7-ai-ger-8%2Fp%2FMLB53989218%23searchVariation%3DMLB53989218%26position%3D8%26search_layout%3Dgrid%26deal_print_id%3Dfa05e518-8a77-4b48-b133-0ccb2d58a903%26tracking_id%3Db936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;lm=378245477#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;wid=MLB5742683398&amp;position=2&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;sid=offers</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_967711-MLA107589549723_022026-AB.webp</t>
+          <t>10% OFF</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/espremedor-de-limo-aco-inox-manual-forte-resistente-goumert-pratico-efigen/p/MLB57553562?pdp_filters=item_id%3AMLB4534315079&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB4534315079&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_705348-MLA99579919952_122025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Smart Tv LG Uhd Ai Ua75 65 Polegadas Hdr10 Pro Processador 7 Ai Ger8 Webos 25</t>
+          <t>Endoscópio Digital Otoscópio Câmera Ouvido Celular Tablet Medical 3.5v</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R$3.199</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>36% OFF no Pix</t>
+          <t>62</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-lg-uhd-ai-ua75-65-polegadas-hdr10-pro-processador-7-ai-ger8-webos-25/p/MLB53610161?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=7&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4179239349&amp;sid=offers</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_966485-MLA106907952364_022026-AB.webp</t>
+          <t>38% OFF</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/endoscopio-digital-otoscopio-cmera-ouvido-celular-tablet-medical/p/MLB27730279?pdp_filters=item_id%3AMLB3833154469&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB3833154469&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_777019-MLU78153175420_082024-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Smart Tv LG 43 Full Hd, Processador A5 Ger6, Ai, Alexa E Webos 23 - 43lr6700psa</t>
+          <t>Suqueira Transparente P/ Bebidas 4,5 Lt Super Promoção! Transparente</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R$1.443</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>36% OFF no Pix</t>
+          <t>497</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-lg-43full-hd-processador-a5-ger6-ai-alexa-e-webos-23-43lr6700psa/p/MLB39205913?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=8&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4034479517&amp;sid=offers</t>
+          <t>89</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_741946-MLA107875422514_032026-AB.webp</t>
+          <t>59% OFF</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/suqueira-transparente-p-bebidas--45-lt-super-promocao/up/MLBU1153632449?pdp_filters=item_id%3AMLB3822305971&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB3822305971&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_730816-MLB78414996620_082024-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Smart Tv Samsung 43 Ls43f6000fgxzd Full Hd Led 110v/220v</t>
+          <t>Guincho Elétrico 3000lb 1361kg Cabo De Aço Para Quadriciclo Jeep - 8x Tech 12v</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R$1.619</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>39% OFF no Pix</t>
+          <t>48</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-samsung-43-ls43f6000fgxzd-full-hd-led-110v220v/p/MLB63777677?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=9&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4397189571&amp;sid=offers</t>
+          <t>79</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_850374-MLA103344560695_012026-AB.webp</t>
+          <t>39% OFF</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/guincho-eletrico-3000lb-1361kg-cabo-de-aco-para-quadriciclo-jeep-8x-tech/p/MLB56697110?pdp_filters=item_id%3AMLB4213164577&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB4213164577&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_740232-MLA107635997983_022026-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Smart Tv U8600f Crystal Uhd 4k 50 2025 Preto Samsung</t>
+          <t>Par De Pistão Amortecedor A Gás Portas Móveis Armários 80n Força Normal Jomarca Prata</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R$2.250</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>37% OFF no Pix</t>
+          <t>55</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-u8600f-crystal-uhd-4k-50-2025-preto-samsung/p/MLB50114846?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=10&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB5514430304&amp;sid=offers</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_673180-MLA99945056215_112025-AB.webp</t>
+          <t>61% OFF</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/par-de-pisto-amortecedor-a-gas-portas-moveis-armarios-80n-forca-normal-jomarca/p/MLB25249994?pdp_filters=item_id%3AMLB5054601214&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB5054601214&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_942964-MLA100063613989_122025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Smart Tv LG Uhd Ai Ua85 55 Polegadas Hdr10 Pro Processador 7 Ai Ger 8 Webos 25</t>
+          <t>Mini Bateria Infantil Completa Com Banquinho Instrumento 5 Tambores Brinquedo Menino Criança Kizumba Sortido</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R$2.469</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>39% OFF no Pix</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-lg-uhd-ai-ua85-55-polegadas-hdr10-pro-processador-7-ai-ger-8-webos-25/p/MLB51481327?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=11&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB5751351522&amp;sid=offers</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_709546-MLA107588006083_022026-AB.webp</t>
+          <t>58% OFF</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/mini-bateria-infantil-completa-com-banquinho-instrumento-5-tambores-brinquedo-menino-crianca-kizumba/p/MLB62681535?pdp_filters=item_id%3AMLB6011420542&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB6011420542&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_758915-MLA99952945695_112025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Smart Tv 32 Philco Roku Tv Dolby Áudio Hdr10 P32crb</t>
+          <t>Kit 10 Unidades Ratoeira Adesiva Cola Rato Aranha Barata</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R$854,10</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>43% OFF no Pix</t>
+          <t>49</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-32-philco-roku-tv-dolby-audio-hdr10-p32crb/p/MLB66055148?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=12&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB6411200326&amp;sid=offers</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_636675-MLA107807100101_022026-AB.webp</t>
+          <t>50% OFF</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/kit-10-unidades-ratoeira-adesiva-cola-rato-aranha-barata/up/MLBU3007857169?pdp_filters=item_id%3AMLB5284576998&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB5284576998&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_922431-MLB94682949358_102025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Smart Tv Dled 50 4k Multi Roku 4hdmi 2usb Wi-fi</t>
+          <t>Luva Tirar Pelo Pet Roupa Sofá Mágica Luva Reutilizável Removedor De Pelos Pet Preto</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>R$1.804</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>17% OFF no Pix</t>
+          <t>33</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://click1.mercadolivre.com.br/mclics/clicks/external/MLB/count?a=nHMAyfASwSEcN5cLhrR%2FlVFcMEC4B2k0YrmjRMsirqOBRkuXm6LNe%2B5%2BEaIueRmcdAT94ZxsRaAAJiXTZ4X2IJ36StKjLBtSXg0VDv%2FhCrw1aztCZ9o%2BYJVrFXSECvcoMAuR432zniLhzhS04B7WhlIJ1Bcqm%2B5Ytvkid8gCWhWLLXaE8Oa3bDkxxLx4tlKkJpx480jRb87Ha1Cb3Vp2v7xP%2FX%2FMn6s%2F35B2Nw7ek6q%2BSn6ym1Ta6sD42gsrO6ZzuZSvhY8jitiYvUjWR1NgOJjcMOFseX5WEg%2FZ9aY%2ByEGPvJqE1D8bL16QkbZwx%2B2JBNiO6%2B0ipCHkmKCu4YpoVL0NuOREZXsa%2FoSXlOwMIssYiiKK%2F3YYDyZMQeFI88%2B7B51m4xewHMyaJDyesyCLQcivwwciBCmd4fOfN5yeU4Y10vBfnqjcwX6LQ%2F5XwBkORsg6Y64MWqr1gXeW3yyZErJeexOoZ8x%2BBp8o7DWPZUTL%2F01WT0rOZV7%2FQfmooZQA4vv7RQEkr9kebU%2F22nemUWWjuYTvFY%2FR1elRbA%3D%3D&amp;url=https%3A%2F%2Fwww.mercadolivre.com.br%2Fsmart-tv-dled-50-4k-multi-roku-4hdmi-2usb-wi-fi%2Fp%2FMLB53607753%23searchVariation%3DMLB53607753%26position%3D16%26search_layout%3Dgrid%26deal_print_id%3Dfa05e518-8a77-4b48-b133-0ccb2d58a903%26tracking_id%3Db936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;lm=1837505392#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;wid=MLB4160333439&amp;position=4&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;sid=offers</t>
+          <t>70</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_661143-MLA99989764773_112025-AB.webp</t>
+          <t>41% OFF</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/luva-tirar-pelo-pet-roupa-sofa-magica-luva-reutilizavel-removedor-de-pelos-pet-preto/p/MLB66170458?pdp_filters=item_id%3AMLB4574254285&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB4574254285&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_744088-MLA107394051668_032026-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Smart Tv 50 Aoc 4k Dled 50u7045/78g Roku Tv Quad</t>
+          <t>Kit 2 Cortina Led 300 Leds Pisca Natal Decoração Fio Fada</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>R$1.835</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>51% OFF no Pix</t>
+          <t>42</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-50-aoc-4k-dled-50u704578g-roku-tv-quad/p/MLB51202548?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=14&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4119277221&amp;sid=offers</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_648316-MLA99473453820_112025-AB.webp</t>
+          <t>44% OFF</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>https://produto.mercadolivre.com.br/MLB-5389076918-kit-2-cortina-led-300-leds-pisca-natal-decoraco-fio-fada-_JM?extra_comm=true&amp;searchVariation=187954248661#polycard_client=affiliates</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_626777-MLB96109552820_102025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Smart Tv 32'' LG Hd 32lr600bpsa Processador 5 Ger6 Alexa Webos</t>
+          <t>Kit Cartucho De Gás Campgas 12 Unidades - Nautika</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>R$1.019</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>28% OFF no Pix</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-32-lg-hd-32lr600bpsa-processador-5-ger6-alexa-webos/p/MLB37929806?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=15&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB3762709747&amp;sid=offers</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_934018-MLA99576753908_122025-AB.webp</t>
+          <t>45% OFF</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/cartucho-refil-gas-campgas-nautika-ntk-12-unidades-fogareiro/p/MLB2043857624?pdp_filters=item_id%3AMLB1188886162&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB1188886162&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_752720-MLB89432546149_082025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Smart Tv Samsung Led 65 Lh65befh4ggxzd Led Crystal Processor 4k Uhd Tizen 110v/220v</t>
+          <t>Envasadora Manual Para Docerias E Confeitarias Envase Líquidos E Pastosos Rg-a03 - Registron</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>R$3.609</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>37% OFF no Pix</t>
+          <t>280</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-samsung-led-65-lh65befh4ggxzd-led-crystal-processor-4k-uhd-tizen-110v220v/p/MLB58375066?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=16&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB5751972452&amp;sid=offers</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_712967-MLA96969981644_112025-AB.webp</t>
+          <t>23% OFF</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/envasadora-manual-para-docerias-e-confeitarias-envase-liquidos-e-pastosos-rg-a03-registron/p/MLB46071772?pdp_filters=item_id%3AMLB3754614413&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB3754614413&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_821671-MLA100082632757_122025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Smart Tv Profissional LG 43  Full Hd Processador A5 Ger6 Ai Alexa Integrada Webos 23  43lr671c-b</t>
+          <t>Controlador Temperatura Mt-512e 2hp Full Gauge (c/ Sensor) 127/220v</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>R$1.544</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>32% OFF no Pix</t>
+          <t>175</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-profissional-lg-43-full-hd-processador-a5-ger6-ai-alexa-integrada-webos-23-43lr671c-b/p/MLB41106126?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=18&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4034468765&amp;sid=offers</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_929244-MLA104540336039_012026-AB.webp</t>
+          <t>24% OFF</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/controlador-temperatura-mt-512e-2hp-full-gauge-c-sensor/p/MLB34281514?pdp_filters=item_id%3AMLB4746240384&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB4746240384&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_984355-MLA95502023008_102025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Samsung Smart Tv 43 Qled Full Hd Q5f 2025, Xbox Cloud Gaming, Canais Gratuitos, Hdr, Som Em Movimento Virtual</t>
+          <t>Rodo Rodinho Limpa Vidro Cabo Telescópico Janela Sacada 2x1</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>R$1.849</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>33% OFF no Pix</t>
+          <t>46</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/samsung-smart-tv-43-qled-full-hd-q5f-2025-xbox-cloud-gaming-canais-gratuitos-hdr-som-em-movimento-virtual/p/MLB63467528?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=20&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4480436541&amp;sid=offers</t>
+          <t>75</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_612999-MLA102412809695_122025-AB.webp</t>
+          <t>21% OFF</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/rodo-rodinho-limpa-vidro-cabo-telescopico-janela-sacada-2x1/p/MLB25088337?pdp_filters=item_id%3AMLB4161940375&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB4161940375&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_813259-MLA99587329714_122025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Smart Tv 4k 50  LG Nanocell 50nanoa Processador 7 Ai Ger8 4k Super Upscaling Google Cast Alexa Integrado Controle Ai Smart Magic Webos 25</t>
+          <t>Kit 50 Saquinho Saco Organza 10x15 Branco Lembrancinha Joia</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>R$2.339</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>48% OFF no Pix</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-4k-50-lg-nanocell-50nanoa-processador-7-ai-ger8-4k-super-upscaling-google-cast-alexa-integrado-controle-ai-smart-magic-webos-25/p/MLB50054616?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=23&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4300251889&amp;sid=offers</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_632660-MLA106910958160_022026-AB.webp</t>
+          <t>19% OFF</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/kit-50-saquinho-saco-organza-10x15-branco-lembrancinha-joia/up/MLBU1744793325?pdp_filters=item_id%3AMLB4291598994&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB4291598994&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_948064-MLB94890710513_102025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Smart Tv Semp 32 Led Hd Android Tv Wifi Bluetooth 2 Hdmi Google Tv 60hz Hdr10 32s42</t>
+          <t>Kit Spa Dos Pés Amaciante Para Cutículas E Calosidades Repos</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>R$881,42</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>40% OFF no Pix</t>
+          <t>699</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-semp-32-led-hd-android-tv-wifi-bluetooth-2-hdmi-google-tv-60hz-hdr10-32s42/p/MLB54086608?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=25&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB6279310350&amp;sid=offers</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_678540-MLA103737233598_012026-AB.webp</t>
+          <t>22% OFF</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/kit-spa-dos-pes-amaciante-para-cuticulas-e-calosidades-repos/p/MLB27418055?pdp_filters=item_id%3AMLB4290073617&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB4290073617&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_604844-MLU72604885303_102023-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Smart Tv Philco 58 P58vik 4k Uhd Led Roku Dolby Audio Wi-fi Hdr10 110/220v</t>
+          <t>Par Suporte Quebra Sol Palio Economy Siena Strada Original</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>R$2.374</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>40% OFF no Pix</t>
+          <t>426</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-philco-58-p58vik-4k-uhd-led-roku-dolby-audio-wi-fi-hdr10-110220v/p/MLB67275824?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=26&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4571470859&amp;sid=offers</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_668507-MLA108744768802_032026-AB.webp</t>
+          <t>29% OFF</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/par-suporte-quebra-sol-palio-economy-siena-strada-original/up/MLBU1730235137?pdp_filters=item_id%3AMLB1876768129&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB1876768129&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_678436-MLB108744448528_032026-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Smart Tv Profissional 4k 65  LG Uhd 65au801 Processador 7 Ai Ger8 Super Upscaling Google Cast Alexa Integrado Controle Ai Smart Magic Webos 25</t>
+          <t>Massa Restauração Dente Quebrado Tampa Buraco Provisório</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R$3.385</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>24% OFF no Pix</t>
+          <t>41</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-profissional-4k-65-lg-uhd-65au801-processador-7-ai-ger8-super-upscaling-google-cast-alexa-integrado-controle-ai-smart-magic-webos-25/p/MLB60660217?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=28&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB5826304432&amp;sid=offers</t>
+          <t>84</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_655773-MLA101387244452_122025-AB.webp</t>
+          <t>14% OFF</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/massa-restauracao-dente-quebrado-tampa-buraco-provisorio/up/MLBU2778687994?pdp_filters=item_id%3AMLB3909117631&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB3909117631&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_760928-MLB107595402776_032026-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Smart Tv Qled 50 4k Toshiba Google Tv Wi-fi</t>
+          <t>Chave Para Tirar O Braço Axial Da Caixa De Direção</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>R$2.374</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19% OFF no Pix</t>
+          <t>19</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-qled-50-4k-toshiba-google-tv-wi-fi/p/MLB46565354?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=34&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB5307394256&amp;sid=offers</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_925380-MLA99990600433_112025-AB.webp</t>
+          <t>27% OFF</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/chave-para-tirar-o-braco-axial-da-caixa-de-direcao/up/MLBU747499881?pdp_filters=item_id%3AMLB2125942131&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB2125942131&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_816203-MLB108651195412_032026-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Smart Tv 43 LG Full Hd 43lr67 Thinq Ai Wifi Bluetooth Hdr</t>
+          <t>Descanso Pezinho Lateral Bicicleta Com Regulagem Aro 20 A 29 Marca Homeroarte Preto</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>R$1.471</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>21% OFF no Pix</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-43-lg-full-hd-43lr67-thinq-ai-wifi-bluetooth-hdr/up/MLBU597742854?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=43&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB5013900420&amp;sid=offers</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_714361-MLB100072626435_122025-AB.webp</t>
+          <t>9% OFF</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/descanso-pezinho-lateral-bicicleta-com-regulagem-aro-20-a-29-marca-homeroarte/p/MLB65144012?pdp_filters=item_id%3AMLB3902345975&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB3902345975&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_749474-MLA105680422414_012026-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Smart Tv LG Nanocell Ai 4k Nano80 55 Polegadas Cores Puras Processador 7 Ai Ger 8 Webos 25</t>
+          <t>Kit 16 Bonecos Roblox Articulado Brinquedo Personagens</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>R$2.754</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>44% OFF no Pix</t>
+          <t>64</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-lg-nanocell-ai-4k-nano80-55-polegadas-cores-puras-processador-7-ai-ger-8-webos-25/p/MLB53551208?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=45&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB4281202601&amp;sid=offers</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_791676-MLA107589387381_022026-AB.webp</t>
+          <t>34% OFF</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/kit-16-bonecos-roblox-articulado-brinquedo-personagens/up/MLBU3566296448?pdp_filters=item_id%3AMLB5936637532&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB5936637532&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_704985-MLB98376230413_112025-AB.webp</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Smart Tv Led 24  Hd Philco Wi-fi Dolby Audio Roku Tv Black</t>
+          <t>Pressostato Cebolinha 1/4 120160psi Compressor Suspensão Ar</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>R$839,90</t>
+          <t>R$</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>25% OFF no Pix</t>
+          <t>47</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/smart-tv-led-24--hd-philco-wifi-dolby-audio-roku-tv-black/up/MLBU3206242483?pdp_filters=deal%3AMLB779539-1#polycard_client=offers&amp;deal_print_id=fa05e518-8a77-4b48-b133-0ccb2d58a903&amp;position=47&amp;tracking_id=b936f4cf-1fb6-4b98-9c4d-9588bee8c3df&amp;wid=MLB5409904652&amp;sid=offers</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_656233-MLB85400577623_052025-AB.webp</t>
+          <t>19% OFF</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://www.mercadolivre.com.br/pressostato-cebolinha-14-120160psi-compressor-suspensao-ar/up/MLBU3402614222?pdp_filters=item_id%3AMLB5661585416&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB5661585416&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://http2.mlstatic.com/D_Q_NP_2X_624776-MLB91541087399_092025-AB.webp</t>
         </is>
       </c>
     </row>

--- a/Produtos.xlsx
+++ b/Produtos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,12 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Cifrão</t>
+          <t>Preço</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Preço</t>
+          <t>Preço_Anterior</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
@@ -439,15 +439,20 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Virgula_Anterior</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Desconto</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Link</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Imagem</t>
         </is>
@@ -456,165 +461,185 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Kindle 11ª Geração 2024 16gb 6 Antirreflexo Wifi B0cp31l73x Preto</t>
+          <t>Lavadora Lava Jato Portátil Pressão 2 Baterias + Maleta Preto 127/220v 50 Hz X 60 Hz</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>125</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>30.000</t>
+          <t>229</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>5% OFF</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/kindle-11-geraco-2024-16gb-6-antirreflexo-wifi-b0cp31l73x/p/MLB52876876?pdp_filters=item_id%3AMLB6601488498&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB6601488498&amp;sid=affiliates</t>
+          <t>45% OFF</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_663824-MLA99565687760_122025-AB.webp</t>
+          <t>https://www.mercadolivre.com.br/lavadora-lava-jato-portatil-pressao-2-baterias--maleta/up/MLBU605239077?pdp_filters=item_id%3AMLB3621404839&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB3621404839&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>b'RIFF\x14T\x00\x00WEBPVP8 \x08T\x00\x00pN\x01\x9d\x01*\xc0\x01\xc0\x01&gt;m2\x94G\xa4"\xa2!%\xd2k\xd0\x80\r\x89gn\xe1s. \x19\xbc+\xcf\xee\xfb\xa8=g\x94\xfc\x85\xfc\xa0\xf9\xef\xb3\xbfm\xfcG\xf9-\xd2Ts\xba\xe9\xfdw\xe6\xf7\xf7\xafT\x9fx?z\x1e\xe0\x1f\xa7\xbf\xec?\xbb\xff\x87\xfd\x8c\xee\xaf\xf4\xcd\xf0\'\xfa\x17\xf9\xef\xd8\xefv\xff\xf5\xbf\xb3\x9e\xef\xbf\xb6z\x81\xffE\xff\t\xff\xc3\xd7\x0b\xd8\xf7\xf7\x03\xd87\xf6\xdf\xd3c\xf7[\xe1+\xfa\xd7\xfbo\xdc_\x80\xff\xd8\xff\xfa\xfe\xc0\x1f\xff\xfd@?\xff\xf5w\xf5\xb3\xfd\x1f\xe4\x7f\xbc?"?7\xe1\xaf\x97_h\x7f\x07\xfb\x89\xfe+\xdd\xd7-}\xadjM\xf3O\xc5\xdf\xb9\xff\x01\xfb\xc7\xfe\x1f\xe6\xa7\xf6\xbf\xf8\xff\xcf\xf8\xff\xf1\xcf\xfd\x9f\xf3\x9e\xc1\xdf\x95\x7fC\xff7\xfd\xe7\xf7\x7f\xfcw\xee\xa7\'\xce\xf9\xfe\xdf\xfe\xd7\xfaoaOr\xfe\xc5\xfe\xdb\xfcO\xe5?\xc5\xdf\xd5\xff\xe0\xf4\x83\xf8o\xf2\xbf\xf4=\xc1\xff]?\xe2\xf9mx\xa0\xfe+\xfe?\xec\x8f\xc0/\xf3\xcf\xee\xbf\xf6\x7f\xcb\x7f\x9c\xfd\xd7\xfa\x83\xff\x0f\xff\xaf\xfb?I\x7fT\x7f\xec\xffU\xf0\x1f\xfc\xdf\xfb\xb7\xfd\xaf\xf2\x1f\xe8\xbd\xf9\xfd\x98~\xe6\x7f\xff\xf7v\xfd\xc0\xff\xfek\x9e\xe6A\xd4J\xccC\x1d&gt;&amp;}\xcc\x83\xa8\x95\x98\x86:|L\xfb\x99\x07Q+1\x0cj%\xaf\xa8sUU\xaaZys\xed\r\xd3q\x98dMz\xe4\x1dD\xac\xc41\xd3\xe2g\xdc\xaa\xcc^\xb7*\xbf$\x83w\xcb\xe3\x0b\xa1\x90\xbf\x06\xf50\xc1\x16i5\xe6|\x80+u\x00\x18O\x9d\xc3\xbd\x9f\xf3\xdc\xc8:\x89Y\x88c\xa7\xc4\xcf\x1ck\xff\xff\xacNw\x0f\xdc1\x04\x94\x07b\x86\x81\x15\xfb\xcc\xebl\x9b\xf3\r@`/?\xa3\xca\x03\xa2&lt;\xceO,\xc9\xf7\x92u\x1d&gt;&amp;}\xca\xbc\xbb}\xd9\xdf\x8f\xbbB\x0f\x90\x07\xaf\xcd\xd6&lt;\xe6\xaf\xdf\x15\x8c\xae\x9e\x7f\xff\xea\xb7\xb7\xfc\xa1\xde+p\xa6\x90\xff\x11\xfe\xa7M\xfd\x1b\xd0\'&lt;\xc1\xdb\xbe&lt;\xfe=$\xff]\xd0}\r\xa2\xc41\xd3\xe2g\xdc\xbbK\xc4\xdf]\xbd\x82\xa2\xf1\xf6\xfe\xea\xdd\xd6\xcfM\xda\xfa\x1d=^U\xf1\xff\xba\xc4\xd4\xb5\x83tk\x94\x85\x9f\xd1\xc5\xfb-&gt;H8\xf1:\x80\x98C`mM\x8f\xff\xdc\xbcU\xa9\xd8r\x7fzcBx,\xbf\xe6\xd3\x12\xcd\x96R\\\xe9e|3u\xdakG\xd3\x88\xec\xb9=cT\x8b\xea\xf8\xac\xab\\\x83\xa8\x92\x95|\xbe\xac?\xfd\x19\xea\x8b\x93\x97\x94B\xdf\x15\xaeE\xb2\xfc\xfa\x03\x94\xa9\xaey\xf9Y4\x01\xe9 a)\xc9Op\xf3\xae\xe0\\5\xb4\xfaO,\xc3\xb2\xcet\xe1\xb6\x00\x950^\xee\x16\x19M\xbc-{\xb3\xc6\xfe\xed+\xe7}\xeaow*7~|\xb9)\x1a&amp;\x1f\xc1\xb6\xf5\x9d\xcd\x0e\xb0=\xf2u/\x016\x17h\x86:{U\xe5\xd8\x0e;\x91o,\x19\x18\xc2\xac\xec\x84\xedg\xf5OG{\x88Z\xb5V\xff\xd1\xd5\x1b\x82\x8bp:\x18u\xd2\xe5\xcb^\x90\xd9\\\xa5\x0f\x8f\x95\xd7(h\xce\x96\x10\xde\x1c2\x18\xe3\xf1\xb1Gz\x8e",\x00\xc78j\x08\xd8\x18\xbb\xebQ\xa3\nP\xe3,\xa2\x80md\xba|L\x1f\xf1\x11\x83\xd5\xdf"p;\x15{Z\x18\xce\xe3\xff\xb0\xb3\x15\xe2W\xf0X\x16\xbd\x97\xb46\xfb\x03\x8f\xd7q\xd6\xb1Dr\x03~S\xaa\xf5\xf7E\xc4\x87&gt;\xab\xf7N\xe9\xf3\\(\xaa\'\xa3\xb3\x8f20\xcf\x81\xcb&gt;s-\xeb\xe8\x9b\x07\xaa$D\tM\x82\xc2\xa9`\xa5\xf4\xdf\xbd\xbd\xfb\xadFaL\x00:\xa0\xc5_\x9d\xef\x16U\x05\x8f\x89\x88\\V\x8b-\xe7v\xebnK\xb3\xcd\x9c\xc5wY\x05\x92|\x83\x911\xc8\xb6\xfe\x11&gt;F\x7f\x82\xb0]&lt;\x0c\x84\xafl\xf8\x17\xb8\xfa\xbes-\xd2\x96\xae\xb1 \xae\\|\xf3c\xb1t\xb0t\x93KR,\xc5\x89\x0f+\xbd\xc2\xa4a$\x9a\x17\xe2\xe4S\x8e\xc1\xd5\xd6\xaa\xc0\xfe\xaf\xe2W\x98&amp;"Z\x15\x83/\xc1-\xa4\x15\x9d\xe3\x9e\x97$\x05\xed\xd8\xecJ\xbf=U\x81\x8e\xee\xb2)s\xb9w\xf24n|\x9f\xc0L\xff\xcb\x1ah\xfc\x8f\x97\x8b-\xff\xd0\x910\x94\x08\x1a\xf1\xb8\xa0\xc28\xda\xaf\xd2/\x1c2\xbe\xad\xcby*\xbc\xd9\x0c\xefC\xf8&amp;uN\x8bG\xa8\xed\xfeXS\xec\x91\xfc.G[\xf6\xfd0\xd2\xd7\xda\x10\x03\xc9\xe0\xd4\xdc\xe8\xd2\x7ff&gt;\xedR\x10\x14#\xb8\xb2DA5\x1a\xbb\xd2\xc5;\xaf\xa9D1\xd2.]\x9d\x90`-r\xc4\xe9\xdfM\xee%tc\x9a\x913\xc2l\xd1\xabi.\xf1_\xe7\x05^n\xe6\xd1\xca\x91\xe8K\xa9\xab\xc5\xb0h\xdd\xea\t\xef\xb3\xdb\x069\x9eS\xe9o\x83\x17w\xe9\xbdP\x82\xdbn\x11{L\xe61~\x9f\xb4\x02\xb7W\xdb\x02\x8e\x89Iw\xf5Lf{\xc0\xee\x0e\x85\xaf\\S\xb7w\x91\xa6|\xb3\x10\xc7I\xf8\xd7}\xf8\xd7\x089\xb6{I\x06){\xca)\x97]\xfa\xf9m\x8b\x1fP\xa6\rS]g\xa9\x0b\xf0\\\x90\xed^\xcahH\xe8\xa4\xef&gt;\xba\x12^Y\xea\xde\xc2\xaf\x08\x9b\x11\x9a\x10\xdd\xb0\x1c\x025J6\x15m(\xfaR\xddAk\xcb\x87V\xec\x0b=c\xa8\x8e\x1f\x1f\xdf\x18T\xfd\x93\xeed\x18\x13\xee\xbc\xa7\xaf\xb1\x8a\xa7\xce\xd8\xe5\x06\xe18\xcf\xca\x0c\xb2\x15wydQL\xe3\nCS\xa5\xb3\x8d-\xc3E\x0c\xe69\xdem\xf7\x00\xd9\xb2\xd8{{n\xc8M]\x95\x1f\xf1\x80\x87x\x91\x10\xfa\xfb\\\x0f\xdc.\x8f\x8c\x1a\x83\xa5g\x85|\xcb\xc0\xe9\n$X\xd0A\tO\xfcR\xc7OI\x8cU\xf8i\xf4\x83&gt;\x8f\xf7\xc614 s\xdd\xd2\x1f\xeeg\xff\x01\x8c3|\xaa\xe0 \x1d\xdb\x07Rx\x1b4\xb9)\xfb/\x82r\xf4\x03X\xf1\x03\xc6\xe2\xf8\x92q\xf5\xf7\x88\xf7\x00\x05\xd6\xb1\xb5\xfd\x04\x96\xb3M\'=1\xd7\xc4+dk\x9e\x91\xd2\xe7\xa3\x85\xc7\xc5\x8fOK\xf5\xad`\xf8\xd5vE\xed\x9bh\x8b\xa4\x7f\x05\xe5#\x15\xb1\xdb,\x8d\x1f\x9e\xc8\xc6\xac\xcca\xd5i\xf3_\xa3\x83\x172\xbd\x8f\xf9\xa4\xd1\xcdh\x8c\xc7s\xa6!?\xcf\xcc\x8a\xa8Txo\nv\x8c3l\xf1Y\x9eP\x84T-\xbau\xf4F0\xc7J\xc2C\xcd\xc1\xf8\xea\x1eD&amp;y\xc4\xe5\xcd\x17\x0f\x07\x18\xa5Z\xf7t\x98\xa6\x17\xc4&gt;\xa5\xde\xc3\xd5\x8b\x88\xe6\xf7Y\x960\xc3nb}\xeb\xc7\x96\xef\x80o\x87\x1c+\xb1\xb4\x98\x14\xf8V\xcc\xdf\x80VO\xdaF\x18d\x80JC\xac\xa0\xec\xecl0\xa5m\x08\xfd\xe6On\xacU\xd2\xdc\xe2\xa5\xc0\x8dK\x81\xdc\xdb_\xc8\x89\xa4\x92^\x8c\xfa\xf5\xc3\x82u\x1a\xeb\xc5D\xb6R\x7f)\xa0=\x02s\x84;\x1b\x80 \x90x\x1f`c9\x96?v\x953|\\\xed\x83&lt;\x16\xaf\xef\x1a\xbe\x10\t\x82\xad\x8b=\xcfO\x0e9Z4K\xf2SG\xeb\x10\x03k\xe0\xbf\xac\xa0[E\x94&amp;\xfc\x18\xb8\xc5\xbd\x10e}`\xa1\xd0\xca\x02\x05\xb5|\x96R\xdb\x9f\x98\x92S\xecX\x82\xf6\xb7\xf4\xec\xb0\xb8i} VX\xf2at\xc6\xa3\xf81f\x01\xeb3\t\x07=\'v\xaaf\x14\xfa\x89\xff\xaa+\xdaGQ\x03\x9c\xcem;3\x0e\x05\x89\xee\xe2.\xd7 \x1c\xde\xf0\x99\xc4\xfd\x15\xf5\xfe\xf5\xad(\xfb\x1f1c_\x0bS\xac?\xe3\x0c\xcb\x1dx]2\xdeV\xfa\x90\x9a\xad7\x15\x8d]JBQ\xec\xdd\x9a}\xbcN\xbfy\xa6m\x87Y:\x1f\xf8aE\xf5\xd8\xb5)\xb1\x07\xd8K2\xc4c\xed.\x1a\x19\x17\x0e\xb5\x98Yg\xb9Z\xff\x10\xc4q\x8d\x12\x8a\xde\xc0\x89\x00\xa3\x15\x9d\xd6\xe9\xa1k1\xb1\xba\x95\xbev7\x98\xc3X@\xb5\r\x04\x95\xf5x\x04N\xea6\xb0j9@\xb3\xd3\x16\x8c^j\x1d\x96\xbaA\xa8o\xde\xf5|+\x8b\xfdg2\xa5\xf9( d\x8a\x1f\xf2w\xf1&gt;%\xcdU\xc8jj3\x0f\x84U\xee|eq\x9b\xcf;\xcf\xd9\xab\xb9\x96L+ti\x05\x88\x91\xd1\x136t\xe7\x0b\x01\x0c\xe8\xcd\xefP\x02\x80G\xc7}\xda5.\xa0\xc89\xff\'\xdb\xe5\xde+Fr.\xab\x164\x9a\xd1\xa2\xf7\x03\x90\xdd\x87y\x90_\x89\xe0\x9e\\\xc7q\xefa\x92y\xce\xd5ZH\xe4-\x94\x89\x19\xdf\x94\x88\'E\x8a.\xdf\xc0\xdd\x11*\'9D\xe2rzZ\r\xb6\x16c\xdd\xf9\xbd\xdc\x9b\xeez\x8fL\x9f\x8d\x97\x17:(\xc8\xf9\x1c\x1dci\xefm9\xff\x13|\x9f\xc1\xbc\x1fnjJ/\xb5\'\xee}\xfa\x08-(\xc9%\x03\xc0\x16\x964\xdco\x86p\xde\x19V:\x0eW?\xbe\xf8\x88\xe0\xae\xfa\x15j9g\x8b\xaeyM\xdd\x15\xabd\xa7\t{*S\x98\xcc\xdc\xc5\xdf:\x8b\t5Y\xb2)]}bh\xff\xa5\xd7\xee \xbf\x8f\x0f\x98\xdc\xb1\xdd+\x16E\x88\xc2"\x02\x0f\xe0\x93\xcaCA\x15"\xd7\x9b\x13E_#\xfa#\xf9\x13\xf4\x9a\xd3\xb42\x00\xe9\x00\x96\xbd\x9b3\x0b5\xa7!\xde\x9c?^h\xc0]\xdd\xef%\xd3Q\xaf\xe5\xd3\x8e\xe7\xd8XA\x9cMf\xc5S\x05\x15\xac\x81\xc1\xb3\xc6[\x8br%]-X\xda\xb4\x0e\x03\xb2\x97\xbb\xd2\tl\x19\x1e\x1c&lt;\xc86S?wE\x1c"\xd0N(\xc4\x87\xa4]\xd6t\x81\x1c\x80\xfc\x81O\xdbk\x92\xb8\xc2f\xa4\xa8\x8cf^\xe4K\xca\x0c!!\xd5^\xb0\x12\xdb\x02\xc4\x11\xe3&gt;\xe9\xd6\xb9\x15B3\xc6y\xe6\xc0\xdeFLm\x0f\x03\x95c%\xb9$b\xc4C\x01\x15W\xf5\xeb*\xf0\xf3=Jj1\x00\xfc\rO\xb3\xc7\xac\x02R\xcf,:+d\xd3(\x9d\xdc\xcc\xf0\xdc\x8a\xb7Q\x0c\x9f\xd8\x7f\xeb\xed\xf4\xbc\xe7\x87aG=\xdf\xf6\xcb\xb7-\xd7\x13\xa2\x89\xeb\xb87\xf7B\xef\xab\xc1\xbf\xbe\x92\xc8\xda\x98\xa5\xb9\xa6\xd9\xde\xf8!\x03\xbd$\x9b8X7(S*\xb9\xb3\x83u6\x106\x00:\xd5\xf6s\xd9{\'\xcd\x94\xd4\xaa\x88\x9c\xde\xebS\xeb\xae\x13\x8f[\x8ev\xce.\x82e\x9f\xc9\xa6\xf7\xa6\xdd\xf0\xaa\xe1\'\xaatI\x1c\xae\\\x87\xf80\x95\xc9\x94~\x9foF\xfc\xd6\xef\x17\xa8\xdb\x7fx\x89[\xff\x98\xe0\xafgX=`Wa\x15\x1a\x16\x19\xc0\x1a\xc90-\xacC\x1c&amp;\x99f\xbfd\xf4\r`\xf0\xab\xe4\xd5/*Jd\xa0\xe6\xcdY\xd3J\xda\xeb\xce\xdd\xb4\xf9m\xa93l\xc3\xd2\xa3U\xb2!c\x81M\xeb\xf7\x1a\x11\x07\x80x\x12\xc2\xc7t \xf5\x14A\rX\xbd\xc7u\xfev\xf3]\x18\xf9I\xe5"9\xcc\x88\xc4\xc4\xb7^Ll\xf5\x9a\xd7\xd5\x03yhB\xe1\xbd\xbdS 3\xdf\xd6\xaa\xb1j`_\xad\x81\x86\x85b\xc4\x84\xc3\x9c\x1f\xa6C\x9f\xbbe\xb7F\x03\x08Y\x1e&amp;{\x99\x07Q,\x8d\x86\xe7\x98^Pu\x14=\x88c\xa7\x94\x00\x00\xfe\xfah\x00\x00\x00%_\xe9\xd7B\x82\x8f\xdc5\x108\x9c\xd5:\xa7\x15\xa9\x17u\x93\xf8GCr\x98\xd6\xd1\x06\xff\xf4\x7f&gt;\xf0\x91\xd9\x14\xf5\xbd\x84$\xfcV,\x1b\n\x1fjK \xcf\xd7\x01\t\xc1(\xae\xd4\xe3q\x11\xd6\t\x83`z8\xccA\xb1\x9f\x15\xfe\xa4\x8e\xd6r\x95\xafe\x12i\xa4\x89\xdf\x14\xf2\xe9Wb2\xc2\x93\np\xd8\xcd\\ic\xf2h\x18O&amp;\xc7\xfd\xe3(\x8e\x95\x96\x80\xd0\xe3)u\x03\xab\xcb\xf6\xc6FF"\x03\xcd\x8a\'\xd4}\x1f\xb0\xb1\xcb&amp;\xd7qiW\xd9\xfc\x8eD\r|\xed\x92\xc7\x9amw\x9drc\xf0H\xba\xd2M\xb4\x07\xfb\x07\x82([K\xc6\xb9\x92\r\x91\xb9\xcb\xce!\x8bk\xdf\xf0h\xb9\xc0\xe6\x92\x9f\xe0\x1cv\xd5ZNry&lt;\x0b\x19\xc9\x06\x16\xdbGyW\xd8km\xed\xef\xeb\x10\x16\xb8Jj\x97ZV"\xb5\x03\xe4\xceQ\xf1\x13\x0e\x04h\x7f\n(f&lt;\xdc\xea\x86e\xda\xd8\xef\xdd~&gt;\xca\xf2n*\x9b\r\x1b$\xc9%\xc3\xdff!\xde\x8d\x0f\xcb|u\xcf5\x10\xe1@\x96\xcb\xd3\xcb\x92\xc4\xd3\xca\xe9\'!\x03rC\xfd\xe5\x02\xfc\xdf\x8d\xf6C\x02\x15\x06\xf4\x00\xad\xf1\xe58\xe8\xac!\xc9K\xf0\xde\xc2\xc6\x0e\xa9\xc6A\xa5\x88!\x116&lt;\xdbQ\xd0\x7f\xe3\xf3\x04\x8c\x9a\xd1\xce wO\xa3\xb32\x06\x8c\xa1\xb3\xf7\xc1\x9f^\xfc[\xdaa\xc7\xceSH\xc9\xa7\xab\xd4\x18\xa1\t@1/-4\x1e{56\xf24\xd1\xd1\xe5&gt;\xcf\xc6Z\x96WE.Ev\xa1\x1e-H\xbe\'\xe1\x88\xce\xc5\xd1~\xe1\xdaao\x8f=\xc0P\xf1\xea\x02|\x08\x85\xa6yZ\xd3}et\x982\x05\x14\x01S\xd1s4\xab\xf3\x9a24\xbay\x15\xf3\xcc\xeb\x0e\'\xea{i=\xc4v\x15o\xab\x04\xb3&lt;y\xb7I\xe9\xbf\xf5\xfe\xa9\xee\x1d\xf6\xb7\xebc=#\xa7\xeb&amp;\xc2\x0c\x96Ch\xb4\x068j\xc9\xc5\xbf\xbc\x93\x8a\xdb\xbe\x86Z\xd9\xe6\xd9t\xa3\x19v\xae\xdd\xfe\xefyLQv\xcd\xbb\x14\xd4_Y.\x83/4\xdd\xca\x8f\xa5K\xff\xe1\x7f\xf8\x93\xfa\xd3(\xa3\xb6\x8e2\xcae\xb6B\x17w"T\xf1:\xb3x(}\x98\xd9\x15\x8aJ\\S\xc92\xbf\x1d\x1c\xc2\xdd\xf1B\xad\xcac&gt;FF\xd4\x1dG\xda\xb5K\xf77\x81r\x1d\xf8\xb1,\xeb\xb6K\xf2\xb4\x03\xa3\xf4\x15\xe6\xaa\xdd\xde\xfc\x01W\xfa\x1e\xb4/d\xa8sd.\xec\xc8\xe8\xbbZy\xbbYh=\xa0FF\xeb\xee]\xf2\x9f\x1c\xcc\x84\x11iD\x80\xe7\xdd\x1b\xb4tL\xf2\xcc\x8e\xa4\xd5\xe3\xbc\xb0\x07N \x02\xc1\xa1\xbe\x9e\xa5\x14\xd7:r\xdf\xe9\xadp\x8dK\x98.\x14\x163m\xf3\x88aOnd\xa4CX\xde\x02\x1d\x7f*u\xa2\xa3\xce7\xaa\x9f\x02:\xa3\xb8\xd8\xe2\x95V\xe2\x92&gt;\xc3\xeaK\xf8\xbf(+2\\\r\x05\x059\x19\xc2\x90\xed\xd8\xa4\xc0n\x06U\x12ph\x12,\x00w\xc4\xbf\x04\xae:\x84\x07\x1b\xc19\xb4\xc56\x92(m\xb0\xed\x1f\xbf\x14L@$\x11&lt;\x00H\x10\x84\x91\x92\xb4\xa4:s\x91Hi\x82\x14\xb63\xbbN\x81\x1doq3\n\x02\xea\xa6E\xf4 \xe0\xccqV\xb9&amp;\x8d\xb8\xbfN`Zl\xb4\x13\xb40\x87\xd87\x03\x9e\x9b\x91&lt;[\xcb\xb0\x0f\xf4b\xf4\xb7\xf6\x19\xc0K\x19\xa4f\xd4\xf0\xa7\xe8\x1a\xcd\xa4\xd9\xa4y\x14s\x9e6\xb2\xebgj\x12\xe5\xfbW\xc2\xdd\x13\xe6g\x06C\xdd\xdf\xd7\xf5W\xb0kv\xb1\x82\xce\xd4\xe0\xcd\xb0E\xbb\xb3&amp;\x0c\xff\xbe\xbb\xdc&gt;\xc9}\xad\xb4ue"\xc3 \x0b&gt;\x84\xd9"\x00\xeb\x18\x99:E5\xe4\x9e\xcb\xeb\xb5\x86\xdb\xad\xaf\x1f%\xde#\x9d\xca&gt;\xef\x9by\x16\x02\x17\xdfR\x8d\x97u\xab\xf5\x11\x91\xcbcP\x8c\xd4Zq\x1c\xb6\x8c\xed\xb66\xa5i\xca\x8a\x1cO9\x9f\xfe\xac.\xb0\xf2\xe6\xba\x18d\xde\xd1\xec\x18&amp;\x82oy_\xd1@\xf6\xc6\xa5m\xea\xc5)\xe2)\r\x8c"\xc2\xd1\xfb\x92\xeaE\x162\xb4\x05\xa0\xbe\xbd\x1e\xffX)\xa2\xe0k\xb2\x88u\xe2\nX\x90\x1c\x1f\xda\xd5\x0cD\xf3\xec!j\x8d\x89\xed\x12\xdce\xdbz\x0c\xb2U\x8er\x9e\x0f\x05x&lt;\x1e\xd8u\xf1#\x0eJ\xcaI\x07`\x9c\xc1\x1a\x01\xaf\x88\x13\xd7\xad6\xadB\x81\x8a\xc8\x96\xb6\xda\x81\x82B\x1b\xf8o24&gt;\xe5\xdf\xc2\xedL\xc8P\x08k\xfe\xa0\xc4Hi\x83\xa2\x0f\xf2\x93;\x16\x8e\x9b\xc9\xa4[t\xa7\xe2\x99\xbb}/T\xa6b\x85aT\xe4\xfb\xad\x92\xe6\xa6w\x11\x8b(\xaa\xfc\x0f\x08\xa8^\x03\xb9\xb2\x1d\xca\x1e\xb9\xee\xb5\x126Q\x13\xaf\xbb\xebL\xdc\xff\xa9,\xa3\x0e\xdaH0}\xdb{\xb6\xc6\x07A\xb2hlS\x1eS\x13\xaf\xcf\xadB\x9c\xaaE\x1a\x18\x0c\x9c\x90\xfd\xe1\xbb-z\xa1\xac\x83\x83J\xf8B\x93\xa0\x80\x10\x82)\x045\x80gc\xd2zP\xd6\x13\xe7\xe7\xa0.\xde\x02\xbd\xc8V\xc4#2~\x89\x8a\x05\x8e\x86_? \xf0b}&amp;\x9e4\x83\xe1\xd3\x83&gt;\x1db9\x16h\x18M\x99\x0b)wKb\x01\x03\xef\x01\xa0;\xca1h\x81Z\xcf\x9f\x9e\xfb\xe2\x9d\x02\xde\x0b\xd9\xde\xbc\x19\xba}\xfa_&gt;G\x14\xfdy\xfb;)\x15j\xd9\x1a8\x04 \xbc\n\xf6G\xe5:\x94\x8d$\xb2\xbeU\x7f\x8f\xa9\xc2Xt\xe3\xec\xb0M\xfcoP\xc77\xad\x7f&lt;\xb1\xc4me\xd8\x917X*\x0f\x0cI\xe0\x1e\xce&amp;\xe3\xca"-|t(\xf8\x81E\x06S\xe5TjEB\x9b\x1d\xcf/\xb5\x19C1,\xca}\x0f\xfc,\xdf\x95\xcb\xdev;\xc4p?&amp;W(^\x0b\'v\'\x9b\xe9\xa6\x99k\xf8sg\xc8&gt;\xb1\x06\x92Ujc56\x97\x84\x92\xa6!\xdc\xe7J\xf6\xb0\xd4&gt;kg4\xec\x17\xbd\x95RC\xd8\xbc\x81P\xeeL\xb6\x98\xb8/.\xf0\xf0\x95\x94\xd8\x01,ul\xdct\xcb\xd1\xe2e\xb5R\xe3\x85\xdac\xed`xi\xaf\x8c\x9e{Av\xbe\x84\xd6\x9f\xe8=mf5\xa8$\xdb\x10\x8a\xa6I\xf3\x18\xf3\xa2\xe1X\xc2\xeb\xec\x1ei*\xbe\x16\x85;\xc7A3\xe2\xb9\x1b\x98\x1e\xda\xe6\x1dR\x10\xf1\xf4\xb5\xcd95jOo\xc6\x8d\xed5\x91S\x01\xae\xb6n\x91"\xe1\xe5?\xac`\xc09\xe6\xf8a])q\x18\x0f\xdf\x1d\x8a\xbf\x05\xa8F$\xd5A\x90\xc5\x88\xd7d=\xd0\x9c\x86\xcc\xa6\xfdkyv\x14\xa1\x85\x95\xa0WR\xca.pzM\xa8\x07\x83a\xa8O9c\xed9\xf0\xd8\x1b\x18F\x9dJ\x95\xb4\xadW*\x99\xfd_\x86\x1e\xcfa\x81\xe9\xb1\xd6\xe9\x8daR\x9f\xa9jgX\xe8/\xect\xba(\x81l\xe1\xce\xb2\xbd\x19\x8f{\x92\xbc"F\xb2\xa1T\xf3\xbd\xf5\x15+Q\xb3G\xe2\xa6\xfe\n\xc5o\x1b\x1d\xd9\xe2\xa7\xc5\xcc\xf6ED\x18\x80,9\xa0\x80\x00\xd2\x83M\x1c\xc4\xd9\x01\x89\'\x7f=V{`Z6\x90\xf9\xe2^\xa3\x0c\t&lt;\x85\x02\xaa\xe6\x89\xf0T|\xf4+\x1f\x1a\x08}NM\xedv\x1d\xc7\xe0\xd0z\xb4\xc7Hd\xa1\xaej\xadL0\x81\xdc\xe5\xf4\x12\xd4{\x98\xbe\xb8;\x93\x86\xd5R\xac6\x94\xa8\x938\xa8\x90\'\xbd\x18\xa7&amp;\x9ap\x86\xa0\x7f\xdb\xb0\xcf\x80\xc2//~ZVpu\x91\x05r\x0f\x156\xc4C\xb5G\xfd\xcc]\xa4U\xbc\xda;\xa1\r\x17\xf7\x175(;\x87\x13:\xe2E\x9f\x111\xdc\t\xd8&amp;\x84o\xb4\xce\x7f?\x93_\x99\x0b\xe3\x06\xdbn\xcd}s%\xc8\x83k\xc5V(X\x1e\x0ba\xb7\x10\x19\x16\xecj\xfe\xc3\xfa-\xa6\x99\xc8\x0c@\n\xa9\xbdj\x1fY1\x02\xdd&amp;2\xeaW\xac\xa8\x81\x80\xd4\x1708:\x96\x19G\x90q%lcp\xf4eG\xe5\x9d\xeb\xfc\x08#\x06yqk\xf9S\x86\xa5aJ?\xeb^\x18\xef\x19\x10\xce\xb8\xd9\xc3t\n\xfb\xb4\xe5N\x1a\xd3&gt;\x8f\xca\x95\xfe\xba\xc0\xc2\xd2\xfa=LhUXS\x86]\xa9P\xc5\x08\x91\xc9\x1c\x9e%NJ\x9e~2#\xa6&gt;x\x92\x1e\xec\xab\x81\xee\xc5:\xafxh\\\xd8\x84a\xd8^\x8e|\xbb\xca\x97\xe8QigWR\xa4Sf\xac\xc2\xb5b\xb4*\xa4\x8a$\xc4)K\x06\xea\xd8\xa4\xe3\xae\xacjn\xfe@.\x962_ \xaff5\x7fI\x94\xf3\xb8\xdex:\xf0\xcc%W\xd5\x86\xc0;\x03y\xc5\xdd\xe0\xc3\xcc\xcd\xb96\x1a\x0fn\x8a\xda\x9c\xd4\xdc\xc9\x96\x9ark$\xf7\\\xa2\xb3,\xc8\xab\n\x8eCV\xcd\x91-L\x90#\xf8k`l\xf1\x17l\xceZ1\x8a\xc9[\xa6\xad!\xf2\x1f\x91JH\xed\xa1F\x98\xc8:OG\xd1\xde\x90U\x00\x82\x8a\x9d@\xf2J\x94\xf3\x8f\t\x88\x85a\xc0p_\n\xe0\x81\x1e\x0cy}\x92\xa0}\xdc\xc2\xf2\x97\xa5\xe4\xd9\xbdu\x0cn\x1e/\xb4\x1e\xf8B+^\xd5\x80\xedx+\x0c\xd8W\x1f\xe0\xda\xa0\xffT\xb5;f\xf3|0\xae\x94\xb8Cp\x9f\xce+\\&amp;\x18$\x0ex9$\x90\xa5p\xd3\xce|\x07;&gt;FQ\x002\x94~\x1c\xd8\xb6\xdf\xf6\xe8\xb0\xd8\x9f\x16\x8d\x85\xbaDI\x06\xfbp\xef\xa3K1^\xdf\xdd\xc3\x802\xd5\xbc\x8f{9n\xfbs\xe6\xe34+\xc7\xa4\x08\xaa*H\x07d\tN\x8c\x87\xea\xd8\xa7\xc8\x12\xd0\x9cV\xa8\xd34O9fb\xde\x07\xb3\x05\xa0\xd9c\x03\xea\x81\x89\xc4p\x8bZ\xce\x0e\xc2\'\x82\x06\xd9\x8d\x0e3J\xd5\xc2A\xb5\x95\x81&lt;\xa2n\x96\x8b\x92\x91\x03\x1f\x1e=r\xbf\xe2\xd6\xb9\x0bT\xbbV\x8a\x11%\x87q\xf8\xac7\xb5\xa1\xf6*K\xf3N6\x07\xab\xff\xd7\x1a\xbb`\xafK\xee\xf4\xba.Ky[ \x12\x8c\x8e\x1e\xedV\xa7\x98O\x01+\xdf\xf0=\xcb\xa1\xbc\xd0\xa9\xd4\x18\x05\xc0\x93++\xe7$\x045\x90\xfed\x1e-1S\x1b/\x9a\xe8\x07s\x84&gt;\xc2\xd49\x03\x97lP\xac\xbb\x15^\xfdP\x9e\xa4O\xf3\x1a\xb9GU\x7fuj\x7f\xf9#I\xff\xbfT^v\x11\x0e\x04|E\x1f\xca\xe4a\xa7\xbe\xc4O^\x19`Y\x85\xbe\xa4\x85e\xe8\x1dk\x0e\xfb{^\xdc\x15\xfbRw\x8dXS\x03\xd7\x02\xbd\x19|\xad4\x17\xd0\xb8\x97;\xdd\xc5\xc56\x05\xc0\xeaK\xcd|?\xf0\x92\x11\xda\x81&lt;\x7f\x04\x8a\xd1\xbb\xa8WM\xdcf\xa4\xcc\x15Y\xb6\xdfw\xa38Ug\x8c:9y\x8cRr\xd8\x99r\xe4MX\xd1\x02\xa2d=B\xd3\xd8\xa3\xa9G\xbc\xd8\x13%|.A\xc4\x98\xa4\xc1X\xc94\xa7K$5\xc7\xce\xc8=\x873_&gt;K_AHC\x1e\x82\x17\x98\xc7\xdbB\xd0\xbc\xea\xfb\xa5\xf2\xfc5\x0f\x16\x94p\tH\x08\xbey\x0cV\xdd\x8d\xb5\xc7JG\x06\xa7\x01\x9b\xb4\xe1\xebe13\x91\x02\\\x8eo\x12\xd6\xa9\x89\xb5\x04V\xc4I\x03X\x0f\x85Q$\xf7\xabc\xd8\xe0\x1b\x9b\xd1T\xc3\xdf\xcf\xd4\x1f\x8d\xf0\xb4\xa4#\x18h\xfe\xb57\xe2&lt;1(\xb4;X\xf2U\xe0[\xf2\xdf\xc8\x89\x899\xf1\xc8R\x8e\x15\xe8P\xaaX\x19t\xdf\xdb\xc4\xf0\x161\xda\x06W\x16\xb1kG\xc6MV&amp;\x05_[}\xa7n\xb31\xd1p\xad0\xf3=\x84\x8d\x87j@p\xe5\x93\x1b\x83\xb7W\xf5\xc6r33\r\xe4Vu\x19\x8b)G\x9e,6aa?\x83\xae\x91\xde^\x1b\xf2.Y\x08\x08-8j%\xc9;~x\xe2=\x9edO&gt;\xe2\xd0A~\xb3\xa0\x8f\xb5\xa6\xbe"\x8d\x95a\xbf/\x0b\xdd\n\xf4\xaf\x9d\xc6\xa4\xdciH\xfd\xf9\xb7H\xe6b\x18@\xd7:\xb9\xc5\xed\x96#z\xfeM-\xa4\xd8\xb5\x111\x9dX\xed\x85\xbb\t\xcd ^V\xae\x18\xfb\xe0\x8d\x01\xe6\x1ec%\xda\xdd\'\xae;\x95\x05%\xdbK_]f\xa4d\xcbwa\xd0q\x87&amp;\n:\xbb&lt;\xe5U6o\x9fj\x84\x89\x97\xca\xd5 \xb5L\x95S\xd9-\xbb$\n\x8a8%\xba\xd5O\xde\x87\xda*\xae\xb3:^\x81\x12\x00p}\xe6\xdf\x80\x89Nd\x1c\x19$\xd3|\x08\xea\xc6\xfc\xc8AuC\x9a\x049&gt;\xdd%\xbe\x88 \xfc&lt;\xd8\xb2/\xb4\xe3\xb1\xd5\xc1\x0fs7:\x85L\xb8\xa1q+b\x1f\xc05FPU\xc2\xf1\x1d\xd5\xd0\x1d\x0by\xbeMn493\x82N\xa4\x8a\x9a\x04\xe0\x8c\xd1\x83\x0b\x07\xe2\x0e\x10\xca\x1a\x0ct\x9b\x8f!\xaf\xfd\xe35p\xd1\xf2D\x9cW=\x81yp\xcd\xef\xd8(\xd5\x04\xa9\xa5\xfc\x89"\xe5m\xd2\x14\xad\x19h\x19&amp;\t\r\xefh\xffM\x10.\xf5\xe1sP\xc1\x8a\xe0\x92\x05%`\xf9x \xe8\xa0XZ\x81\xd6\x90\xe4\xb5g\xa8Q\xc4%E\x0cP\'\x0f_\xc0\xcf4&amp;\x0ek\x83\x1e\xf0u\xb1\x95v\x000\xec\xfe\xde\x8b\x1a\xaf~G\x1e\xe5\xea\xb2\xdf\x83\x01\x9e\xb5\x1f0[\n\x83dW\xfcC!u4\x10\xf5;t\xabI\x1e\xff%\x9f\x93\xec3\xd8\x1c\xd9\x0fND\xdf\xd4h\xec\xf8k\xe0K\xeb\xd3\x16&amp;@\xca\x96\x1eG\x07\xd8\xe5\xad\n\xa4\xdc\x97\xc0E\x1fC\xe1\xee\x14O\xc9\xe1\x8f\\\xc6M\xacuO\xeb\x84\xfbU,\xcb\xcb\xe8H|-?\xce+\xc1\xfc\xd8O\xe5\x1b\x0eNT\xc9P\xe8V@m\xb8\xe45\xc0\xb4\xe9"n&gt;\xf9\xed\xac\x8d\xfeF\xe1\xba-I\'\xde\xebssC\x91.\x02hJ \xcd\x11\xb5\xcb\x91\x0cU\x0e#\xc6\x1b\xf3\x17K-&lt;I\x84^f\x90\x84\x9e\x9e\x95\x99qQ\xfcU\n\x9f\x13\x99\x854\xb6,\xec\x83\xe3\x03\x05\xe5v\xc6mo\xf6\xff\xbf8GQ1\xfcM\xae\x8c\\\xc1\x13\x88\xfdmb\x95\xbf9^Y\xdfvzC\x81\xfc\x89\x13`dO\x0ez\xdd\xc0\x0f\x89\x13og&amp;w\xe4\xde\xd6N\x7f\xeb\xaaun\xdb\xc3\xb3\x08\x88X\xb7$\xeb\x1c\rx\x06\xf9K+L\xed*7\xca\\\x99,f\xb6\xb3~\xf5@\xd7\x1e\xd2\x96\x8a\x97\t\x9f\xf3\xe0\xcc5\th}q\xbe=\xc9\xd0\xb3"j\xd7\xc6\xc4 \x82\xbf\xc7\x07\xd7#\xa8\x7f]\x89fz\x1a\xe4\x8d\x13\xd7^\xc7@n\x98qL\x99\xdd+O2DG\x05\x9d\x1aN_\x8c\xb1\xb7\x9aX\xb4\xf7h_\x15^\xd2\x81B\xd9\xb3\t\xc1iV*y\xd0\xeb(\xa5\x08&gt;\xdc\xd8\x02\x14\x17\x0c|\x869\x06\xc1\\\x11v\x10\xc7{\xa7\x15\x8d\x13\xe6N\xbc\x97\x16ie&lt;\x0eM\x036\xf28\x95\x1c++"\x9cS\xef\x13Yx@t\xcc\xfe\xfc\x95\xf58ZCT\x13\xc8Ma\xb8Y\x8a7\x07\xee\xa81\\\'R\xbd\x9f\xf9\x07\xa0\xad\x96\xe0\x81\xd2T\xc4H"\x03I\x93\xadw\x9f\x95J\xa2\xce\x01K\xe7Y\xae\x15\xcc\xf8\x90\x03\xcc&gt;\xc6\x83\xd2\x0er\xc7\xfe\xfaz\x95x\x8d|\\$\\\xe0\xe0\xd9\x899a\xf5\x05\x86J\xacmAo\xcc\x8c\x1a\xaczA\x07X\xc4\x80j8\xf7\xf2\xec\xd2\xfb%\x98Q\xa4\x9c\xe5-K\xa6\xcfw\xf6\xd7\xbb^\x8f\x98\x144\x03\xaf\xb3\xb2i\x18\xf6\r\xac\xcdyg\x92p:i\x83\xab,\xa2r\xd3\x1d9k 5\xe7\xf9GCk\x99\x1fwD\xb5\xabKX\xb3\xde\xf1\x86\xfd\x8a\xb8\xba\xcf]\x17\xba\xec\xb2\x86\x9d\xcbh\x0c\x02\xf0\xeet\x80\xef|\xff\xfe\xa1G\x82\xd6\xde\xb7D\xf9\x03\x85C\xa5V\x84J|\xf1\x85\x93p\x93MD\xd5\xd38\xe6\x9a\xc6"B\xf5\x12\xbaV\xc7\x9f\x8e\xf1q\x17\x89V\x1dB\x19_^\x0fy\xa9Q\xc3cU\xd7R\xd3\x9b\x00@\xfb\xd9\xff$\xf0\xc91\xd6\x90\x93\xb0\x8d\xfdz_S\xef)\xa9\x8f\xc1\x146.\xce\t\xa0\xa3\xce\x1cCOd\x13!\xe8\\sH\xecw\xe8x[hT\xb24iE_r\xb3G\xdbx\x95\xba\xc6\xc1\xd6c\xd4\xc5!\xa5COL\xb4\x15&lt;z\x17\x86.1SU\xf5\x13\xe3\xffI\xfa\x99\x11E\xd2\x8aB\xa9\xee\xd6Y\xb7\xe9\xb1~id\xe2\xed\x85\x05\x87\xee\xe2P\x91\xd9\xf2\xba\xfej\xa8\x8fZ\xf8\xe22\x9c\xfc\xa8@@\xdf\x109-A\x92\x99\x076$Y\x17!\xa0\x10\xc7\x93\xca\xa8\x99\xce;\x9e\xfc$n\xdaj\x05\xf3p\x93\x01\x04\xefa\xca\xbfM)&gt;\xe2\xb0\n\xeab\x03\xa1\x1c\xa8\xfa\x11\xadG\x1d\x9a\x08\xce\xa6\xce\xceC\x19\\\xd9\xab\xf5\xcf\xefWu\xafu\xe6\x9c[\xcfr\xbf\xf4EX\xb9\x9f\xb3\xdah\xdcA\xa8\xfb\xb0\x99Y+\xec\xdbR\x1d\xa7\xa5MLJkr\x02\xc7\xdb\xc4[\x8f\x87\x0e\x06\xce\xc4}\x90\x00\xaf\xa7\xbb\x9c\x08n\x8eo\x11$h*5\xf6\x86H\xe0\x8b\x9c\r\x86^D\xf61\xbc\xa5\xca\x1b\xaaY\x95\x93\x9b\xcd\x01L\xf8J\x91oO\xc9Y(z\xee\xe3~\x0c\x0c\xa0\xea~"S\x16}\xed\xaar\xbfg\x8d\xda\x94\xed\x05]\xfd\\?\xedf\x12\x9a\xb5\x86]\xee\x81\xae\x0cW\xb1\x91\x9a\x0b$\x87\xdc\xcf\xb9`-\xbeoX=\xf6UA99\xf2o\x0f\xdcD-w&gt;Z85M\x83O\xb8(`Q_\xa9\xad\xbd\xe9\x88c\x8b\x98N\x7f\xc3r\x18\xa8\xbf\xa6\x9cz\xff#\xb4\x0b\xbb\x86\xcf\x84\n-\xd2\xe3y|\xf5\xe5\x98\xe4i\xeag\x109\x06\xc7\xcf\xeb[u6\x93:i\x17BKp\xe9F\x8c0|\xc2\x1b\xfb\xc2\xfflF\x80w^\xf6\x9b\xfeZ\xd7\xd8\xae\x11\xaabwx\xfaC\x88\x9e?\x13_\xd5\x8f\x90}{\x11\x87M\xe9\x84\xd7\x95\xd3\x92\t\x18\x11m\xd7ik\x00\x9c\x0f\x9d\xb3\x1a\n\x0c\xe8\xcf\xc6;r\xcf\x98\x9124\xfc\xb5\xd0\xa8\xa5\x98\x91\x08\x9e\xc0\xc0M\xcf\xf9\xa4\x937\x04\xe2\x81\xac0\x18\xe7(\x94M\xf3\x13\xf6\xbb#PF_\xaeC\xf8`\x07\x84\xa9\xacJnV&gt;\x8f\x86\xa0c\xce^\xb2H\xfe\x82\x138\xd3\xf4e\xe01yX\x0c\xc9\xe6\xe4\x99\x0fm\xc8\x11\xc7\x8a\xbf&lt;9q\xd2\x0e8\xe9F\xecG\xcd\xe1\xe7\xf3\xbbx\xfd\rF\r\x19\x94\xfe7\x1a\xf5,\xe5nB}\xdc\xebBN\xad\xacXx\xa4\xd2&gt;\xd7\x1cb\xf0\xdf\xbd\xfe\x84\xc8\xa7\xbdi\xc7W\x07?\xdd\x8f\xb1\xb9\xe3(\xfe\x0e\xf0\x9f_\xc8\xf3\xb3\x03xF^\xe0\xaf\xb5\x98\\ \xeb\xa2\xce\xc4\x9e\x1f\xaa\x86\x87\xf8\xb1\x7fN\x0e\xa4\x82.%?\x9f\x18\xb0\x87\xe0s:&lt;v\xf6\x00\x81\xb1\x83bo\xc5\xc1\x0f\xbb\xe7\xcd\xd8\xaf\x8c\x86\x1b\xa2x\xb2\xfd@\xa7@K\xc2\xd2\xe1T\x91Q\xca\xef\x16\xfe\x90\x12i\xc6\xca\x1a\xcc\x1a4\xe3\xc8f\x05C\xdb\x00\'\xd2\xf7\xe97Es-\x86&amp;_\xfc\xfa_\xc3{\xe4(-\x1d\xaf\x14\x1a\xee*\x02\x17B\x8a\x0f\xdaf\x04K\xb4\x19\x99[\x1bd\x88\x1e4\\\x84\x91\xc7\xb7\x0e9\xb3\x0b\xbb\xa9\x97m\xb59\xa3cA\xe0\xec\xde\xae1\xd3f,Q\xdd\xc6\xc3\x95+\x8a\xcd]\x81\xa1\x90\x96\x17\x7f\xcb\xa5\xbf\xda\xf7\xb7\xb7co\xb7\x89r.Z|I\x9e\xed\x07m\x9b\xa3\x1d\xb1`m\xed\xcc\xdd]\xfa\xd0\x00\xd1\xe6\xf0\x0b\x8bD\xcd\xd3\xc2\xee\x0b\xd5\xfdg\x08g\xe9G\xf2V\x8c|\xb5j)\xad4&lt;NK\xc5\xa5\xe3\x04}\xf2D\x8eI\xc3\xef\xac}\x95\xe3\x05V\x9cR t"O\x16\x80\x14&amp;\xe0\xfa\x93\xda\xe7\x83\x83gL\xf6\x86\xca\x18a\x88\xad]\xe3\xec\x11\x11G\xc5\xf0K\xd8\xa8]pj\x9f\xd8\x96\x0f\xa3\x1a\xf3S\xc2\xb6\x13\x97\xb1\x8e"\x8e\xc6\x97\xe9\xe6\x9b\xa1\x95\xe5\xbc{z\xf7\xb5\x16\xd0.\\\xeag\xe7\xcf\x86#:\x15GJ\xc9\x93\x94\xc1%U}\x8dz"g\r\xfd*d\xe8\x95\x9b\x90\x07\x9ce\x1f\xd7|\x81\xbe\x14r1\x9e4\xb0\xf4\xa8v\r~\xee\xf5\x83O\xc5\xeb\x19\xb8\xb2\x9c&lt;\xcfh\xa1\xca\x87P\xf1\x96F}\xb9\xef#K\xc6+\xf0&lt;;\x17j?gB\'\x0c\xb5\xf9\xbbm{Q_\xcdg\xf8\x0f\x1c_k\xc0\x8fy\xf7k\xc0\xd0\x98[\xf69\x15\x15\xf9\x04\xd8Q:\xf6\x16$3$9\xf0\x034\xedl\xf7\x1d%w\xad\xcb\xe4~hv\n,\x94d\xf9\x83\xf7\xaf\x12\xd3NQ\x15)\xa0\x89\xdb\x9a\xc2] \xe6PuD\xc5\xf3\xa3n_\x17\xd5\xd9a\xa5]\xfa\x1b\nk\xc4TD\x05\x9d\xf3CB|\t\xdf\xf2F\x97\xd6\xb0\xb09\xaf\xebv7`\xf3\xc1\xbe\xef\xd5\x08|\xdf\t\x92r\xae\xf9\x93\x99\xa8&amp;\xf5\xc6i@\x1b\xc6\xc74^\xee\x95T%\xff\x92c\xcf\xf2y\x92\x90H\xad\xf1T\xae\xe3\xbex\xc3\xc0\xf0\xc5\xb0\xeb\xb9G\xad\xd5BgB\xd4\xad\xea\xeb\xaf\x08k3a(\x14\xfe\x02\x06\xeeh\xe9\xc5\xee\xc0\xf6\xcfd\x87\x824\xaa\x88\xfa\xc9\x8aA\xa3{\xc1\xb7D\xb5\xf6\x05\xa7\xcd\xb8\xdf\xd0\xc3\xfd&gt;\x84\xad%\xf0\x99\x1e\xbd\xa3\xb6\\~8\xc8\x93\xb7\r\x89\xe8\x90\xb9\x89\xc7\xbf\x01\xe3Z\xf1\xfeW+\x8a\xa6\x9e#f\xd1\xa1P\xf1y\x14\x8c\x90\xa3\xcc?\x81T\x8b\xe2\xfcL\xb26\x13\x11\xb0av./\x98~WxX\xed\xd9\xf8\x18\xa1\xc9\xfaX\xa1\t}\xf2\xb2\x11\x82\xc7L\xf4D\xb7\x8b\xc2\x00\xcf"{\x80\x98\x90\xc9\x1d\x1b\x9b\xd2\xa3 \x13\x0b\xf95s\xc3\xc7\x87\x87a&lt;8\x1d\x82\xc6R\xf8\x97\xe6Y\xd2\xb4\xa588L\xfd\xe76\xea2w\x9c*[, \x84&lt;Y!W\x8e\x9a\xaf}\xc5\x8c\xd5\x10\x97\x92\x93\x92A7\xa3\xf0\xc3\x81\xc1\xa7\x15\x1bD:\xa4T\x98\xcdO\x8c\xcd\x90\x9c\xea\xae\x08E\xd6\xba?\xa1\xd8\xff\xfe\x1a\n\x05\x8dX\x14\xd1\xfe)\x19\x88$S\x04\xb6\x02\xa23\xe1\xe3\x12\xe7\xe2v8n\x12\x12\xe3?\x14\xd8t6\x89Q\xd6\x9c\x9f\x9d\xe1n\x12D\x1e\xe8p\x025\x958\n\xe0m\xe9d\xdb\xd4X\te\t\xf7~\xd8\xf1\xf1\xa5\xad\x93W\xfd\x86\xc5\xec!\xf6\xc9\xd5\xbf\xfc_\x80\xdb#\xce\xd8\xba9\xa2\xf3\x9av\x00\xc7\x90\xac\x19d\xaa7n\xb9K\xb5\xfc/f\xf8R\xfc\xe6\xf8\xf5I\x94`|Q\x99\xcc\xee&gt;\xbc7p\xfaX\x99\x99\x97-\xbcS\x11\xba&gt;\x03\x14\xc0\x04c8\xd7\xd2}\x92b\xf6#\t@\x80p\xf7\xdc2f\x84^\x98\xae!\x8b\xcfi\xeb&gt;B\xec\xdd\xdf\xac\x10\x1c\xf5\xe6\x96B\xb4\xf0\xde:\xe2bc(\xa0\xc3\x97F\x03\xf6B\xdd\x0f\x7f\xf8\x82\xfeG\xfd\xfb\xa3\xb5J\x8e\xe2=\x88\xca\x0e;c"\x9b\xa4#.\xc5x]8c\xc7Oy\xf4\xc5s}\x03\xbb0f\xa9\xea\x1a\xe9\x13\xe3\x92\xeb\x8bg\xb9\xdf.\xc3\x96\x10\xb0\x02\r\x954-\x0b#$6\x19X\xd5\xa9\xa9\xb0\xd8_x|*\xdb\x0e\xa0\xea\xd8\x9bU\xb2k\xfc+:\x8b\xdc\xd9\xf1w7\xb0\xd2\x12{\x96\xd8C\n\xdc\xf5\xde\x87\xb7\xa9\xb5\xe0&lt;\x91\xaf\xd8\x95P\xaa=\x878\xd5!\xe4\x06\xa9\xba\xb8\xa6x9_C]t\x15\xd10\xd5\xc1"(\xf4j&gt;\xd8\xffp\x00}\x17\x15\xa1\xe56f\xd5C\x17\xd4n\x87\xa0_Ao\x8et}Gt\xf4\xa5\x86\xa1\xd7\x9f\xf7z\x1a\xd9\x86}6"\xa7Q\x81I\x8a\x1c6\x92\xfbD\xf4^\xdb\t\x1b\xcb\xa5\xf2g\xebA\x81=\xea`\xa8\x16\xc0M?\x00\x9f\xa9\x9a\x93\xd8\x1a\xe3\xb3.\x1a\xc1\xd7?\xc3\xb8A\xeft1:}\\\x83\xf0\x8f\xa3\x8d62C\x9a\xba\xfd5\xc88\x11a\x03l\xfe\x11\x12\x94t.c\xab|\xbbO\xcf(\x7f\xfb5v\xeb\x00!\xfbW]\xa1qK\x87\xe2_\xb1\x10=\xa5:)\xad2\x84 x\x181\xe3\xb0%\x1b\xde\x07\x84\xde\xfc\t\xfe{h\xe6\x06\x95\xfa\'+\xc5m\x8c`\x8940k@;0\x98\xf8\xd6e\xe1HWr\x08_\x862\xde\xcf\x9b\x1c\xfa\xc4\x93q\x93^\xb9\xbd*57$\x86(Kp\x1eI.\xdc\x8f\x1f\x01l\xf2\xe9\xe76\xdd\rtc\xb5n\r\xaeP\xb57\x84\xff\x81/\x18p0\x01u\x13\r\xd3\xfe\xa6\xf4o\xac\x87M\xf2\xadC\xf5\xa9\xf3\xc8\x16\xbdY;\xaao\xd4\xf2\xd1\xe0\xdfrc5\xaf\xbc\xda\x8c\x044o\xa0\r/\xa3%q\xafF\xa9\xd6)\xb1\xae\xb7\xd5\x95\xa4[]\xb7\x87\xe0\xdc\xff\xe0A\xd3q\x95\xf8\xb5h\xdf+\xebA\xeeRGYT\xd0AB\xe9\xa2}\xad/\x15"\x90Tp\xd3\xa4G\xfd\xeb^0\xab\xfd\xf5\xe1\x8d\x91\x96\xe6\xe6\x91v\xb3\x1eG@D\xe4\xa88\x0f#N\xfea\xd2\xf0&gt;\xf0T\xf2`\xf6\xa4\xe9\xa3I\xf2\x03\x99\xfcM"\xcc\x00\xc5\x0b\x1e\x95\xbcm\xdb#\xbc h\x10\xec(\xdb\x9dR3b\xbb\xe4,\xc9^\x84\xfe\x8c\x94\xa0\'\xdfhc\xb0\xdf|D\t\xa3\x92\xf2\xa7\xbfK\x17\x17\xd4\x0fAO\x9f\xdb&amp;(\xa2\xd5\xc0\xeb6\x0e\xc4\x05f\xca\xe0\xc9\xa1\xbd \x91\xf7\x0e\xb5\xdej\x85&amp;\xab-\xec\xe4\xa7"\x1c\x18\xde\xc2\x8eqdj\xc7\xc4\x88\xa9S\x1am~\x01]z\xf4\\\xf7\x16U\xa5\x16\x1a\x1bz^\xea\x9b5\xb0U\x13\xfd\xd1\xd6\xa2a\xe2\x00\x8b\xe5c=\x83J+\xf1\xed\x82n\x83\xe6\x15\xf4\t\x8buL\xdfm\x83|\xf3\x9cq\xb9\x97TG\xae(,U\xe5\xbc\xb9;w^o-\xd0\x89\xb0\xce2\x82LS\x02E&amp;\x88\xcd\x0fVx\x88\xb2{\x99\xec)\xb7WbZ(\xdf\xe2Q\xea\xed\'\xc9-\x15\xf6i\x00\x81\xb9\xf9T\xae\xd9M\xb1\xcfK\x99\xadn\xa6\x9d\xa7\xd8\x10\x14\xad\x7f\x86\x03\xafE|\x91\xff\x1d\x1e\x8b\xe8Y\xac9\x08y5\x8e\xe0\xc4\xf9\xe5\x8bZt)\x8e=\xb4\xc9\x1b\x88v\xd8\x10i\x12\xdcvm\xc2L\xb6\xe9\xf8fm\xd8\xf2ve\x19S$\xa7\x94Y\xd9\x8d\x165\x0f\xa1\x11\xbf*\x17\x1c\xaa\x04\x9f\xf9\xd8\xf1\xdd\xb3t\xf6\x02o\'\x8c\x18F$P\ng\xaa};3\x12\x19L\xa2\x85.o\x89]\x1dU-\xbf\xb2\xb4l\xeb\xed\x91\xbb\x1dw\xddJJIj\xc0\xf1p\x98\xb1\xf8q\xbb\xfd\xf8{\x83R\xb1\x0b\xcb\xea\xe0\x99\xe7$\xe2m\xbc\r{y\x80AM\xa1\xee"\x1cw\xfa\x14ms\x18\xab\xaa=j\x15\t\xfe\xddAd\xe6\xa81\x96\xf2\taUIY3\x0f\xe8\xa8\xbd\xb2\xb8\xd2c\xc3\xd1\xbc3\xb5\xcd\x8duk\xc5w\xe2\x11\xdc\xda\x01\xef`G\x8e\xdc\xb8`f\x8a]\xe7\x86RL\xa7\xfb%\xc1\xc37\xdd0\xd2\xb2\xb8t\xafH\xee\xb1p\x13\xe3\x06+~#\x0f\x19\xe9\x1e?\xb79n!\xael\x89B\x91\xd6l\xc0\x0c\xa6\x14\xb6k\x94f\x9e\xd7m\x7f\xe3\xbb\xf27\xa5\xf1\xbe\x9d.(\xc6"\x06t\x91\xfc\xa9\xe1\x00 \x99\x08\xd33\xe1\xf9\x0ed\x04\xd8\xd0\xde\xd2\xd0\xfa\xf6\x9a}\xb8\xa1\xfa8\x7f\xbdu4Rc\r\xaf\x12\x19\x04s\xc4\xbb\xe8=k\x99\xc1o]Y3\xbc\x08v+\xba\xce\xf4\xef\xf8x\xc6d]\x08D(\x9f\x03h~\x12\xce\x1b\xf4\xa0\xe9w5\xf0\xce\xda\xb1v\x92\xff\x05}\xd8\xcalu\xb0\nI\xa4\x0c\xf8\x15\x87\x96e&amp;F\xad\xef\xa4\xb6\xf2\xe7"\x1c\xa3\xad\xc8\xec\xb2\xfd\x10\x95\t\xe6\xecg\xa4\xc4\xa0^\x99\xb7\xad\xd8\xf3M\xd8(\x10\xf9\x08\x13\xa1\xda\x122\xde\x8aS\x18t\xa384U\xaa\xe3 )\xf3r\x05\x7f\x93\xd2Ps\x812\xaa_\x9b\x84\x14\xcf\xdf\'\x9e\xa8\xbf\xf5\xa9V%\xeaj\x852\x08\x89\x87\xde\x85\xb2.\x8f8\x91\xc0\x02\xd6\xccn\x8a\x12p\x1e}\xe0\xcb\x9c\xf32#\x89\xff\xed\x17\xc8\xb30\xb0!\xa8\'e*\x15\xb7$\xee\xa9U\x7f\xb8\xcf\xff\x9a\x04\x93\xb0o\x84V\x88\\]\xc6\xdf\x0f^{\x9b\xf6\xf8\x82\x9c\xa0\xb40\xa5\xf3\xca{\xf3\xd5\xa3\x17\x80\xf4|\xef\x01\x01\xfb\\J\x81\xfe\xe0u,\x93\x03\'\xdf36\x9e\xbd\xeeD\x18\xf5\x83\xd8\xd9\xa5a\x14\t|V\x13\\\xde\xd1\xe6\x86\x17\xbd\x1a\xf4\xf7\xa5\rP\x164\xbb9\xa4`\x00#\xf8O\xf6J0\x02\x8es\xf8\x02\xc0$\xb3\xb1-_d\xe6\x14\xed\xd1\xa8qS\xa6y\xce\xa9k\xc6v1\x01\xe0\t\xdc\x85\x80\xe1`\x16c\xb3\xf2\xbbir\xa5\xb4U\xde\xee\xfa\x90p\xae\xc8\xed\x98\xc4\x98\xb7\x9f \x8eO\x1a\x8d\xbb\xbb/\'\x98N\x11\xce\xd7@\xae\xa8\x89\xa4CE\xcf\xe0)\x8f\x1f\x10\xf5CZ\x12\xfb\xf7\x0e\xaf\x8f\xbe\xf5\\\xaf\xe7\xac\x89\x00\xb8={\x84Q\xd5\xba=S\xebM\xf7\x06\xd8\xd8l\n?\x14\xc9c\x94\x99\x11!N\xf5\xae\x1b\x83\x00\x12\xba\x19F\x1fjq7\xb9\xd9\xc8\x06\xd3\x9c\x80Y\xb1W\x85\xee\xb6&amp;\xe6\xd5\xc0\x96\xc0\\\xb4\xdf\xd1@2\xf6\xe1\x94\xb9\x9fY\xa5\xc9G\xb3\xb8\xaf`\x8e\xef\xf3\\\x01\xa0\xb7$\xf8n h\x91B\x19\x8f;\x98\x95\x93rxx\xe6\xc1\x1a\xc6\xf9r0/\xed\xd1f\xd6\xadNI\xfc\x1cn\x1f\xfc\x1a\x07[s\xcb\x811.\x86\xd1\xf2\xbcCA"\xa9U\xec\x02^&gt;\xa8\xbet\xa2\x8b\x9b\xbczz\xe0\xb8\xa2\xf7\xa5\x95\x98\xcb?\xbf\x1c\xe3\x9e\xabfC\x10[\xa2\x0f\xc1x\x932\xf5* @\x85\xdc\xcb\x18\x9d\xd1\xbf\xb7u\x00\xc8}\xaa\xf9mQ\x8afe\xd2h\xbea\xdc\xac\xfb\xb7\xb2\xd3xA\xfa\xe6\xe2\xa8\xe4[\x03\xbcT\xa4\xfaytL56\x19\x87j\xec\xa0\xbaA[\x1d\xa4a\xcb\xe7\x96\x13~\xfcx\x16\xfb\x1a\xe8\x02\x88\x84L\xb7D\xd2\x9e\xe9\xee\xf2\x0b\xc5\xe6i\xee\r8\x11\x8f\xe7\xd6\xbb\xebs\xeb\x812f\xf3\xcd\xd7L&lt;\x03C"\x10\xda\x90\xcb99\r\xb8`\xa6\xa0Y)\x93O\x00\x06E\r4}\xdf\xc83r\xa7\x07F\xe6\x7fJ\xb7F\x0cI\xf7-y\x8aX.\x1fOA\xe3\xb1\x93\x08K\xd2&amp;\xa9\xce\xf9\xfb\x8a\xef\xf3\xb5\x86\xf4W\xe6\xd2\xabW\x1a/k\xe7\xf1\x87\xd2OH/MW\xa5\xf0!\n\xbe\x89&lt;\xc4w)\x9a}\xba\x15?LD=\xd3&amp;\x1e\xd53\xd4\xb9\xa5\xad`\xa9\x0f\x99K22\xfe^\xc7\xc9\x88Ol\xc3\x93h~\xb4\x94\xa2w\xda\x80R\x0f\t;\xa9\x0c\x82&lt;#\xfc\xef\x0e\x9c\xf7\xba\x14,\xf98\x15"\x99a&lt;Bh\x85\xc3\xeblH1\xe4\x02g\xddy;\x07\x02\xbc7,\xe8(C\xcbP\x17\xc2X\x11\x93(Ff\xf5n\xdd\xf0\xc1\xb9\x9a\xb1\xad\xa2\xd2h\xcc\x8a\xec\x9eo\xbf\xc4BSq^\xb4\xb4_\xe7)\xe0\x16\xcb\xcb^\x96\x88\xac&lt;\x13{\xf1\xe3\xf1[oL\xe6v\xf1\xc7n\x1e\xcbt\x93\xba\x1b\xec|\x05\x06\xbbs\xb6\x94Hf|\xfc)@;*\xc3,B\xc1[\x10\xc7\x08M)?\x10\xcc\x0e\x8c\x9e)\xfb\x1f\x1b\xb5\xc0\xd1\x0c\xd4W\x8c\x8cn\xbei\xb1,\\J\xc6K\xc1\xe6\xd5\\\xa85N\xe5T\x01?q|\x0c#T\x7f\x19\xd4\xfc\x0b\xf5\xe1\xea6\x0f\xde\x11\xecL\x0e\xd4\x9c\xd3\xb8\xc0\x80\x0b:\x7f\xef\xcaV\xff`a\xc4\x19\xb7\n6\x81DNPz\xcfg\xb8\x15\x02y\x92-\xad\x87Ck\x13\xd3s\x89\x1a\xfe\xe5Q\xf9\x16\x11\xc0\x17\x83\xc5\x16\xac\x05S\xa5\x9f\x87\xec\xca\xeaV\xc8f\x96\x9f\xd9\xa8\xa1W1\xf8\xa3\x00@\x87\x0c\x81\x16a\xfd\xc8E\xd4\xfcQM6\x84\xf2\xef\xf0/\xc1wE\x03Zw\x7f\x10{\x0f_\xe8\xe3\xe4\xa1\x02\xa1\xf0E~T\xe3pB\xfc\xff_\xa2\x96\x81\xda\x15wD\xdezO\xb7\xbf;\x1aa)pT\xd1V\xb9\xba,8\xcf\xd9\x11g\x18.\x1e\xa2\xaf\xc3\xb5\x80\xa84L3A\x90*\x9c=\xa0\xd1\x85\x03:\x1b^\xd8\xdch\xf5\x99\xb6\xfc\xa6\xac\xa2\xb8\x0c\xacm\xe3\xe1Y\x85bK\xd8\x1c\xd6\xad\xb8\xa2\x19\x14\xdf\x14\x0b\x8d"\x0b}R\xa4\xd8\x12\x90^(9\xed1Ey\x13\xc5\x01\xea\xc9\xb6+\xc8\xd2\x87=,gr)M\xb1\xaf\x11\x16\xc1\x93$\xf6\xd4\xc8\xfb/\xfc\xd9@W\xe6\x96asHNcW[\xc5SN\x00\xc4\xf4\xdf\xfc\xe9|\xae\xe5 J#\x84iVD\xdc\xd7=o\xc49.\x05\xbb\xea\x80\xbf\x022\xba\x9e\xf5\xde\xa3\xcb\r\x8d\xd6\x0c1T\xd2\xcb\x1eA\xd8~\x957\xc8t)r!\x8d{\x04--\xfbq\x7f\xf6p*I3p7v\xb3\xf8\x1c\xbakz\xc4H\xd1\xbbN\x0e\xc9\x13LTs\x0b\xfb`\x141\xe7\xcb\xfa\x1e\xb7\x1e\xef^G&amp;\xc2\xb0Vc\xe6\xb4\x04L\xa75\x18\x9b\x93\x16\xd2\x85~\x0b\xa6\x12\x90\xf6\xa0\xa6O6K\xa0\xa0\xc4\xaa\xcf\xe7\x1e\xf2~J\x1d\xb7\xbf{\x04\x95\xcd\xdd?\xd0,*\xd8G\x88\xe4\x1ck:\xebS\xb1\xf3D5\xf2\xfd\xe7\x8f\x99\xed\x10\x15\xe7P\xbb}\xb5\xa2a\xec\xe48\xd4t?-\xaf\x9f\xd6^\xbb_\x8e\xd2\x98y&gt;m\x81\x94\xc6\x80\x8e\x0f\xb1\xe0\x16\xacT%jv\xfd\x90\xcf\xc9\xf2\xc8E\x90\x1c56\xae\xc7/z\xd7\xb6Z\x981\xe8\x00\xbe}*=z\xdb\x87\x9aS\xeaM\xe8\xb8\xcd|\xb6\xadLk\x96\x8bnq\xaaR\xdd\x17\xdb@\xf0\xc0=\x94\xc9\xa5V*\x8c\x00h\xc8&amp;n\x92\xcf\xa4D\x06Q!\xdc\xf4\x05\x8a\xbd4\xce\x14\xbe/\x14\xfb\xdd\xbay\xd9\x9d\xfd\xcb\x08\xb8\xf8\x91\xc6\x02\xb2r\x9b\xbay\xb3\x0b\xed\xa3K\xa5\xab\xa3\xb2\xe5}\xb1[f\xa9\xff\xb8&lt;\xae+\xcf\x11\x9b\xc2\xc2\xed,\xe9\xdb\x81\x17\x18C\xa8\xe5n\xa7\x08\x93\xc6u\xd66Qb\xd3\xc8\xb99X\xe5\x89\xa6\xbd\xb1&amp;cZ&amp;\xd2\x96\x1e\xc2\x13\xbf\xadX\xcdDt\xa5\x84u\x03@\xd1/\x11%#\x93B\t\xcd0\xf1\x06\xc0\x8f\x0fB\x8d\xf1\xca\xf0\x95\x91k\x9f\x8f\x00)\xcf \xbe.\xf5\x91\x97\xc6m\xd8s\xf4\xb7\x9a\xe7\x14m\xea\'@\x1bhH\xfd\xd8\x99e\xff\xa0\x88\xde\xa45\xb5\xc3O\xadgK\x16-\xc6\xde\xf9\xc4G\xf2P\x81\x95#q\x030\xc0\xaag\t\x11\x11;\\\x9c\x82!\xf0\xcaW\xebt\xdb\x9bcF\xda\xa9\xf4\x98gDR+\xf5c\x900\xf8c\\\xfbC\xc9\x07\x7f\xf9\xad\x926\x99&lt;zt\x8cSoc\xa5n\xc6\xe7\xca,V\x12\xf6J0\xc8\x89/4dMsb\xff\xd8\xed\xe8\xd4\xa50\xfc\x04\xe7l+\x04\xef_\xfe\x99\x98\x86\xf1\x93h\xe1\x97\x9e\xee\xe3\xb7{\x97y\xdc\xbe\x17\x13f\xea)\x9d\x13&amp;\x91PK\xfb\xf4\xce\xc5^\xc7\x9d\xad\xb9=w\x10(T\xd9\xc7\xca\xd7r\x82B&gt;\x9em#\xcd\xa3nH\xb0\xb6\xe6\x82\x86\xdc/a{i\x96\xb5GkY3\x91\x90\xcd\xca\xd5\xe8m5r\xb9Y\xfe\xa1\xb1\xe0\xc7T\x8e\x93\xdd\x8a%\xf3\xeb\xebZ.=y\x1aVT\x90\xf6\x0c_\x0f\xe7\x0e\xef\xaf\x9a$\xd9\xf7\xe2xt\x85\x96w\xd0\xad\x0e\xbfx\xa6\x9c1\xd6\x15A\xfc\xd3\x12\x93\xe4,\xa8\xbe\xa3\x03v\xb2u\xc3\x08\x8e3\xa3\xf9\xc5\xdd\xbfS\xed\x84\x12\x05\xc4\xe0\xffIw\x80\xff\xd4\x12M\x19\xdc\xea\xfdC\x9b\xbd\x9a\xf7\xb7Y\xcf\x1doq\x99\x14M\n\x8dv\x0c\xc1\xc5&gt;\xcb\xbc,je2\xf1Q:\x12l#\xd4\xcb\xae\n\xb6\xe1\x</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Seca Salada Centrífuga Secador De Verduras Manual 3l Cor Transparente</t>
+          <t>Carregador Compativel Com iPhone 8 X Xr 11 12 13 14 Pro Max Turbo Fonte Tipo C Boyu Cell Branco</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>39</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>68% OFF</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/seca-salada-centrifuga-secador-de-verduras-manual-3l-cor-transparente/p/MLB50925841?pdp_filters=item_id%3AMLB5418491250&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB5418491250&amp;sid=affiliates</t>
+          <t>28% OFF</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_643381-MLA100095729143_122025-AB.webp</t>
+          <t>https://www.mercadolivre.com.br/carregador-compativel-com-iphone-8-x-xr-11-12-13-14-pro-max-turbo-fonte-tipo-c-boyu-cell/p/MLB43351618?pdp_filters=item_id%3AMLB4136027339&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB4136027339&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>b'RIFF\x02(\x00\x00WEBPVP8 \xf6\'\x00\x00P\xd8\x00\x9d\x01*\xc0\x01\xc0\x01&gt;m4\x95I$"\xae"#\x16\xda!\xc0\r\x89gn\xd4\xf6\x16\xdb\x822\xf7,8TG\x84\xf6\xcf\x10\x80Gn\xf2\xf5\x1eR\x1c\x93\xd5\x8f\xae\xfe\xdb\xc5s]yCs\x97\xfc\xffY?\xe8\x7f\xea\x7fx\xf7O\xf9\xef\xfe\xff\xb8\'\xeb\x1f\xfc/\xee\x9f\xda\xbd\xb2=V~\xe4\xfa\x8d\xfd\x8b\xff\xaf\xfeG\xdd\xdf\xfeW\xec\xe7\xbaO\xef?\x90\x1f\x01\x1f\xd8\xff\xcbu\xa7~\xec{\x05ym\xfe\xf3|1\x7fb\xff\x99\xfbQ\xf0-\xfb[\xff\xe7Y\x93{\xfe?\xf5o\xe6\x7fb\xbf\xe4\xfcna\xdf\xb2\x1dK&gt;o\xf8\x8b\xf8\x1e\xb5\xbf\xc0\xf0\xc7\xe4^\xa0\xbe\xc8\xffe\xc1v\x02\xbf2\xfe\xb5\xe6\xc3\xf4\x9ek\xfd\x8d\xff\x97\xee\x03\xfd\x0f\xfb/\xfb_a\xbf\xdf\xf8\xae\xfd\xcf\xfd\x97\xeb\x8f\xc0\x1f\xf3\x0f\xed\xff\xf6?\xcf\xfec|\x9e\x7f\xeb\xfe\xeb\xd1W\xd3\xff\xfc\xff\xd3|\x07\x7f&lt;\xfe\xe5\xfb\x1d\xed\xb9\xec\xbb\xf7s\xda?\xf7\x10|\x8dUUUUUUUUUUUUW\xb6\xb5\x16\xa7z;Qo\'\x99\xcf\x9d\xbe\x14\x99\xac+\x1f\xe2\xfd!\xc8\xce\xfa\x1e\xf2\xb5\xadkZ\xd6\xb5\xadkR\xdbkT\xd3o\x1d\xb7\x82\\\xc1\xfdNGdDDDDE\xae\xbc\xca\x1ay\xe4\xabl\xb1U&lt;\x9dP\xc3\xb5\xe4\xe5\'4\x1a\x8d?\x18\xcf\xe4\x97\xeb\x99\x99\x9a~4\x19\xa2\x15]QD\xd8\xda\x834Z\x8c\xd9\xd4\t\x0c5UB\xfa/,\xcc\xc6N\x9d\xa4C\x12o\x17\x17\xa3\xdf\x17\x13Im\xb5\xb3&amp;\xbff\xd0p\xa6\x874\x05(9\xa0\x1b\xda\xf5\xd8{\xac&lt;f\x0e\xcbk.2i\x95\x99\x9d!P9\xa5#\xb4f\x94\xf0\r\xc8=\x8fEN\x8ah\xfd\xed\x02\xbe*\x8d\x1f\xe5\xf70\x9d\x8e_`\xb8K\xfd\x1c\x1c?\x02\xf7\x87\xe3\xe8\xd66\xb0 \x95\x88\xed&lt;\xee\'\x0b\xd2\x81\xacH\x95\x9e\xb0\xc8\xce!\'G8\xcd\x0f\xa4k\x81\xef\x87\x8f\xc7\xfcy\x87v\xef\x18\xb8\x90tJ\xaf\xa2!z\\X\xd3\x0c\xfd)\xdd\x8a\xd3\xde(\x0c\xb3\x1dx\xc2!p3\xa1\xb0i)|,"\x07\xb7\xb6S|\x95\x8fQ&gt;c\xc5\xbf\t\xd25\x8b\xd4\x88v^\x91m\xec\'7?\xe4\xc7\xd1\xef\xfb\x1f\xe9Bx\xb7[\xcc\xaa\xb5\x14\xf8\xfd\xde\xf2\xc7\x05\x04\xdcW\x1a\xf7\xa3[d\xc6C;\x0cHP\x8b\x8b*\x81\xa2\x9d^\x94\xb2n\x7fr\xb5\xb1*8}\xfe\xacz\xe3^::m4\xe4\xebClF%\x00\xd6\xa1\xf9K\x0f\xa3\x7f\xc7\x11\x15\xc6\xb2|\x93\xa7W\x0e*L:\x8a\xdf\xf7%\x7fF\xac\xd9\xa5"\xab\x99\xfaLwJk9\xaf\x83\x95T\x8d\xd6P\xf6\xe5\xa2\x93\xec\xc6n\xca\xf7\x07\xb639\x04\xd0\xc9\x93\xbd^\x85 \x92W94R\xe9\x88\x10}\x8d# P\x83XV\x94\xd8\x96U\xb9\x1b\x07iv\xf2\xe0E\x03\xf7\x06\xc1\xea[\x0b\x80HMm\x0bds&gt;\r\xac\x14\xc4\xe0\xc2\xb7\xf5\xef\xa5$\xe8\x07\xea\xf3\x0cMDi\x01\x9a\'\xb2\x01\xc4\x14I\x1c\xea\x9e\xe4\xc2\xba}R)\xb4\x8c@\xe7\x94\xff\xd8\xf6)\x84\xda\xda\\\x0c\x19\xd2\xffo\xe0!;\x13Q\x1c\xa4\x02c\xd1 \xc4\x98\x0e\x1fe\xd7\xbd\xc9\x1f\nMk\x0bf\x0f\xff\x18\xca?\xc1o\xa5v&lt;\xe8SQ87b\xcej\x13VF\xd2j\xbb\xb0\r\xb4\xf3\xe2\xac\xc5;\x1c\x99(\xb8u\xff+,\x9b\xf5a+\x80\xe8\'c\x8f\x0f8N1\xea\xd7\x94d\xe7-\x88\x81j\x0f\x10\xc6d\x8b\x8aM\x8d\x89\x18\xa1\xce)Jv\x0c\xb4\xf0\x9c\xcd*\xd8\xef\xdd.\xa8T\x06\xd0Mxq\x02\x91\x8a\x1c\xda\xd141\xc8e\xf2\xe5\xde\x89\xe7\x15\xff\xcc\xaa\xa1\xb7\x9d\xb2\x859\xde\x15\xb8|\x00(P\xf3\x02i1\x08\x99-\xba\x1f\xc9\x84kU\x83V\xa7\xd3\xf9Btr\xee\xf5Du\x11o\xf3\xb9GCh#\xa2\\\xd9\xca~\n\xe2\xd3\'g\xe2\x83\x94/\xfa\xf3V\x0e\xf7\xc74\xdd\x92%\x14a\xe0\xdeS\xc7\xe3\xeb\x97MO\xc6\xaaJ\xc6\xf0q\x1eX\x0e\xe6\'~\x1e\xd1\xf7\x1c\xb9\xccZD\t\x1a8T\x96\xa8.\xed5\x07\x9f\xa1\xc8\xf0\xf5_\xdf\xf6\x0c}\x9e\x1b\x90E\xd7\xc02\xd3\xca\xff&amp;M\xf9\xa8\xd4nd&gt;3\xb9!\x97\x81\x8c\xe3\xfe\xca\xc8\xd7\x95W2\xff\xee\xfe.z\xcf\xcb\xb2\xb9\xf6K\xfd\n|\xdf-\xe2\xbf`\xd0\x19{\xd4\x86O-J\x8e\x18\x0e\xc6\xe1\xbd\x19\x9c"N\xdd3Rd\x03\xa6\\\xb6\xd1\xa0\x08J\xee\x0f\xe9\xbc\x14\x0el\x9bl\x9c@\x0f\xe7\xc0\x06\x15%\xbbB\x85\xb6\xfa9\xedm\x87i\x03:\x03\xdf\xae\xf1\xd5m/\xec\x9e/*\xf1\n\xfb\xf4\x19\xa1cl\xd8\xc4\x94\xfb\x1f\xc7G#\xf0\x90\xef\xad\xcfu(\x1f\xb3\xae\x0fu\xd0K\xe7F\x89\x85\xc8\xf8\xea\xf3!K\x07W&amp;\xc2Dr\xa7}\xe2\xae\xf4\x10\xb2\x06\x82\x19]p\xe2\xf9rW\x1f\xf3a\x14\x86\x02\xd1\xba@\x07\xe0\x98\xa9\x11\xf3r\x8aQ\xc2\xc7\x02\xbb\xce\x0b\xd5\x80\xf8Jla\xcf\xcd\x16\x8e:2(\xfc"\xab\xf7[\xabB\xf08\xb4\r\xd8\x04\x10v=\xcb\xc3\xf2\xa5\x87V\xebF%IM|\xe5!\xa9\x94\xae\xaf\x12\x86!\xc6\xef\x05\'y\x18(\xf97d\x1f\x82k-mN\x9a \r7X\x0c\x1bf\xf27H\x08\x89\xdb\x06b\xe97\x0ePU6\xe9#(S\x02\xb2\xe2\xfa\x86\x86d\xa0\xed\xdf\xa1J\x0c\\ak\x15\x04\x9aV\xf5c\x99\xc2\'\xf7\xceY\xa6\x93\xaf\xf1\xf6\xb6\x9aD\xbf$\x8e\xbd6\xa1\xe9f\xda\x9a\x88M_\x98;\xed\t\xcaX\xc9l\xfb\xe1\xa2\x7f\xefOiH\xafTU\x0f$c\xc2\x84\x85B;\xed\x13\x94\xf5\xd7\x89\xeb\xb8\xe3\xde\xcd\x16\x9c\xdc\xb8\xb67M\x00\x1ah\xea\r\x87\x04\xae\x95\xc3\xac\x91\x1dx\xb2x\x10\x1e1\xc1|\xdf\xda\xbf\x97\xcad\x9d\xd7&lt;\r\x8a=0\xd6%T\xf6\xe3\xbe\xee\x1f1L\n\x94\xc1\r\xd6\xbc\xd0\xf1\xd9w\xbd\xa2\x84\x18\xd4bMX4\xc0\x9a!\x0f=\xfd\xed\xb5\xef\xc1\x97\xe0\xcf\xa4\x7fj\xa8\x9a\x04\xd6\xea\xe1o\xb2P\xeb\xd5\x8c\xa2\x0c\x85\xf9\x0b\xa7=\xbaW{\x99\xab\xc3\xd8w\xa8\x14/\xd8\xf3$[\x1f+"\x8f\xa4\x95\x8d\xd3ug\xf57\xbdl\xbf\x83\x9e\xc9\xf4k=\x02"F:\x93\x8e\xd1t\xa8GMe\xd3q\xcb\x8e\x0bM\x92UU|\xb3\x12\xd7\x82\x01\xb3{K8c\x04\x7f\xf5\x99\xbbfk\x9a\x8d\xb1E\xbc\x81\xf8n\x9b\x98\xe18\xa6Z\x06\x06\x11\xd4}\x89)*\x98!\xba?\xc7\x1a\xc9\x8b/\xb8C\x8c\xaao{\x9f1}\x01\x9eA\x87\xec\x0b\x91\xa4\x15U;\xc6\xc8\xc5T\x84/\xb2\x93\x1d\xf4\xf6\x00R\xb4`\x7f\xec\x98\x85#\x96\xcbA\x1a\xbdvI\x14V\x94=\xef`\x96\xf0\x06I\xbfk\xdf\xc9\xdb\x08\xee\x04\x1d\xd5&amp;333\xf8:\x8b\xd0:\x17\xb7*\xb2uUB\x00\x00\xfe\xfeT\x00\x00\x04\xe0b\x04\x90\xdc\xdcq\xa9\xb0\xefoT`m\xceq\xd0\xcc2y2\xa9\x1e\xbf\xd7b\xb1H\xf1\xe5:\xa1\x91`D\x9f\x93p\xd1`}\xcbx\x8f\x97\xa6\xc0\xb8(\x90\x99\xe6 \x9d\x0b\xe2\xab\xea\xf5\x8d\x85R|\r\x1a\x1er\xafd\xce\x14 \xb2\xf0HF\xe0\x9bl\x0b\xfc\x98\xb9\x98\xe6\xb4L\nz)\xdf\xb21\xeb\xb80\x86\x05\xf9\xb6\xfb\x8b2\x91\xa7~m\x87\xff\x03\x19\xc0\x13\xa8\xa9\xea\x8a\xac/s\x0f\xfc\x11\x8f\xb5\x91\x9b_\xbb\xde\xf5\xd5\xdd\x8d\xcdj\x7f\x14_\x028\x0f\xdc\xe7\x10h"\x08\x02\xa32N\xd7\xb9u\xeb,\x1d\x17\xf8\xb0\x0fa\x8fbn\xb4Q`Uw\xb8\xe6\x06[\x1d\xf7\xa3\xdc:Y\xc6v \xb2\xe6|\x8a=\xa2\xd8\x08\x05\xd7\x12\xd06,Q\xcf\x00]\x7fh\x08\xd0\xe45ykSD;Z&lt;\xc6/\xf2c\x04\xad\x98\xb3\x982\xe1o\x97a\x9a\x01UhN\xadh\xd8rW\xabd\xd0\xca\x99\x1c\x11*\xc9\x04W,\xd3v\xd91\xc0\x0b\x0f\rQ\x85cp{\xb4\xf4\xbf\x08%\xe4N\xc0\x88\x0cDe\x12\x8f\x0b_\xc97\xffz\xb9\xad\xd90/\x0b\xd4\x98\xd6\xa3\xac\x82\x04\xcf\x1b\x9d\xdaF\x80?/\xab&lt;\x0cl\xa62\xcd\x1dh\x02\x00&gt;\xd2\x01\x1a\xc5\x98\xbe\xb8\x11\xe8\xc4\x88Az\xa3\xf9\xa09\x8d\x8d\xc5c\xa9\x04\xffw\xb3\x0fK%x#\x8f\xdd\xa0\x98*2\xdb\xc1\xdf5\x85\xcf\x0b\xf7\xcd\x8f\x0c\xaa\x9a\x8b\xbc+\xafz\xd0m\x8b\x84\xe79\x8e\xd5\x06=\xb5\xac]\x05\x05Nf\xfa\x86\xbf*\x83\xcbz\xc4\xf8\x04)euZ[\x90\xb8\xb7\x00\x15\'\xd9\xf9\xbb\x1az\x81\x1e\xf3[9f\x8c\x8eU\xcb\xb2\xe7D\xc7q\xe4\xb1\x9e\xb3\xbd;C\xdd\xa0\xe4\xa8$\xc2\x9d\x92\xc5\xc9\xae\x92_^^\xf3(\x8c\x0e\xe4`~\t\x87\xc5\xa3\xa8\x17\xec\x08\x90\x17:\xb44fd\x95\xe5C\x07\x00"\x10\x87XQ\xed\x8a&lt;\x8f&amp;\ny\x04\'H7\xd6\xb9\x1a\\\xacZe\x07\xc1\xb9\xa4\x9b@\x16\x8cQ\xef\x8eY\x7f(\xb5  \xb9F\x93Oe\xd9\x97$\xf2$Z\xb6x"W\x7f$/\xc6\xdd\x9b\xdb\xf3\x82\xc8!b\x1a6\xf1n\xf4\x97\t\xe3\xd5\r\x13u\x14\x9b\x9d\xd5\xaf+|x\xc0\xa1\x87[\xd0\x8d\xcc_\x1aV\x9c\xfe\x19\xc3\xb2\x14\x15Tj\xde,\xff%\x02\x0cm\xbf\xb2\xfd+\x8f\x897T\xf4\x8a\xf4\x9a\x11E2\x14-cl#F]\xed\xba\xbe\rv7\x97\xcc\xc2Z\xfb\xef_\x8eR\xcb BI\x1ew\xcazm?@\xc5E6@\xfd\x93\xa4\xb6\x04\xa9\x86\xa4\xf7\x05\xc8Ac\xfa\x8dD\xe8]yd\n\xca\xf7\x1cD\xf4\xb9\xa8\x7f\xb03\x94\x07Q&lt;\x92\x03 \x0c\x10\x8c\xa8\xc1G\x03UUX\x05\xd8\x87O\xb89\x0c\x7f\xb2@\xe8\x81#\xc9Gj\xf7\xa2}\xefzpCNK\xfd\xba\xf1H\x93:\x9at\x8c&gt;K\xaa\xdf\x968\x90\x860\xc5M\x8b\xe7\x8e\xdf\xbf\x97\x8f\r\xae&amp;\t*\xba\x84\xf7\x07\x03m\x93\x0b:\x00\x92\x97\xfb\x10\xc0\xbc\xc8\xd5\xef\x89\x8c\x99\x07\xf8\xe6;-\xf3\xb0\x0e\xf8\x93\xa6\xb8\xf1I\xd3\x04\xfd\x0e\xfbZ\x03y\xe4\x89 \xc0\'\xd2\xbb5G\x8d\xd2\xb2p\xfb\xbe\xf3\xd3J\x18\xae\xd3\xec\xc0\xc5s\xc5x\x82\x1c6\xc6UO\x84-(\x1f\x92\\R7\xeb\xado&lt;\xac\xaf/Z\x037++\xcb\xd6MP\xd6\xc1\xb2\\g\xce\xe9X\xb3\x14\xaf\xcc\xa4\x92\xccb\x9b\x1b\xd1wmD\x8b\x05}\xc4\xa5eM\xc2\xb8\xcb\x93\xd8\xbe3K\xfe \x06\x9b\xcd\xbb\x92\xc3\xf4\x9b\xa8\'\x1cC\xb0\xb0\x1e\x0b!\x8ef8\xaa\x16\x9a{\x0fZ\x892\xaa\'\xa7\xffO\xb4\x85w\x0c\xddY_\xe2\xee\xdax\xf1\xe5\xc9\xdb\x89\xde\x06\xa0Ic2\xa0\xee\x0e\x9d\x04\xed\xb7r\x0bd\x8b\xb4Yl(\x1dJ\xe9\xb5\xea\xa5\xa1\xb4Wt\xadm\x86\xcc^\x9a\xe7\x8d\xca\x90E\xce\xe6\x1ecW\rb\xc3\x13Z\xf1GO\xff\xa9p\x19\x03\xe2*\x9d\xbaL;_\x89\xd6\xa7\x94wQ\xe9\'\xf9\xe2U\xac\xfbx\xa2\x0c{\x87\x98\xbeO\xcd.\xd8\x1f3M\xcd\xdc\x1a\xa5I\xff+\xc6B\xady\x0e]\x96wj\x8d\xde~ \x8f@$l\xa42\x97&lt;&amp;P\xf2C\xceS\x0f\x1c\x95\xcc\x9bL*\xe5\xf9\xbf\r9\x9fh9G\x10j\xa5\xaf!3\x8e\x8b6\x9e[\\\xfd-\xe3\xb1\x86\xe3\xff,g@9\x9e\xf1C\xc61)\xea\xa3\xda\xd5nm\xd7j\x0en\xa9VH\xc9{\xd2\xcaB\xa0\xfe\x1fW\xd7\x85\xbbX\xc9\xa1\xa2\x8al\x1c9\x12\xfb\x15f\xebx\x87\xb5\xfdn\x80\x86\xd2s\xa1\t\xb75Ctoz\x87\xfc@\x19\xd2\xfa\n\xbc\xb4\x92\x14\x18mL\xa9!\xae\xbaR/\x1d\x0cl\xd8&amp;\xd6$\xaf\x89s\xb77^\xcf\x9f3\xd4L\xf5\xa8\xddK\xed1\x94\xbc{\xb7\xc4\xb6\xbd&amp;\xf1q~]\xfd\xb9\x08\x90\xbcn\xc9\xfecm\xd9]\xe9\x86\xe8\x0e\xf6&lt;\xd1\xb8\xa3cUv+\xf4v\x16\xee\xe2%\xd9\xde\x86\xa6!\x91\xd9\xe6\x16\xbe\x1a\r|\xa8i\xccp\x17\xb8-\x15\xb1\x08g8*\xbbf\xdb\x1d\x91\x11q\xdd\xd4\x98\x9e@\xae\x93\xe3\xb4\xc6\x86\xdd\xf8\xc3V*\xff]\xb9\x18L\x9boa\xcb\x06P\x0f\x1bzy\xb3\tFaX\x15\xc8\x8f\xf1jY\xdf\xc5\xf6\xfd\xb2\x82\x90t\xab\xaeN\x04\xf3\xa4eV\xaa\xe3\xaaW"\xd7\x9e&lt;Y\xc8\x97\x1bg\xcbh\x19\x8e\xa6\x97\xa5\xc2\xa0\x87#U\xa7B\xa8\xbd\xd1\x87v,\xfc\x83\x0fV\xff\x02\xf4\xff\x14\x19\x8b\x88+\xc5\x8e&amp;\x0b!\x9b\xf1\x03\xe4&lt;\xcc_u\t\x8d)\xdb\x00\x0b\xbc\x90\xfap\x175\xe1p\x03\xeax$\xba\xdb\x1e[\xf1M\xf1\x087?\xf7(\xe7\x0666H\x9fF8r\x90\xd8\xe4]\xfc.\x9c\x94\xeb9\xfdh\x12}\x15Z\xf684A\x81\xbb\x0cm\xc6T\xc6\xe8wz_A\xc1\xcc\x85\xac\x80G\x85?ITT"MU\x8eF\xcd\x8f\n\xa9G\xf4&lt;\x8c\x95\xeal\xfc3\xcaTZ ,\xf3\xe0\xcb&amp;4\x83\x9aN/\xe6G\x1b\xd7\x1c/\xdf\x1d\xc9\xbd\xa7v\xf0e"\xf3ol\xb3e\x15\'\xf7\x83t\xca\xc6\xf6YO|\xa2\xb8n\x8c\xc0\xf6@c?\x04TW\xd9\\Z\xc9\x95\xbe\xe7B\xdb\x96py\xc4\xe6\x9d\xfaU8wy\xb8\x16i\x97\xc7f\xe0\xf7\x95t\x0e\x8aZ\x9c\xcd\xccV\xf1K\xd7T\x7f\xf4\t\xa6&amp;\xe6R1ke|\x89t\xde\xf3\xe1dx6\x859\xd2\xea\xde\xa1\x15\x0c\xe2w\x96\xde\xb5\xbb\xe7\to\xa2\xb1\xfc\xe7\x12\xd9Ch\'a\x05\x921\xc9Mx\x1b\x85@W\xe54Q\xe4\xeayc\x16g\x08M\xbf\x8c\x90Ma\xb8\x9aP\xfad&amp;\xca\xd6p\xe1\xa1v\xa11l\x98m\xf1\x0c\x1f\xef\xc5\x9cWI\x18N\xef}\xe01\xdcNH\n\x00\xa6\xf1c5W\xf0\x88\xee\xc0&gt;.\x93|\xfe\xf90*\xf7hZ*\x97\xed\xf6\x11\xecG\xa8\xb2\x10!\x04w\x85\x1e\xeb\x94\x86\x16\x8e\xc3\xc0h\xe6\xa2\x87\x15\xa7\xe1S\xb1B\xd2\xee\x03\xbd\xff#Z\x02\xf3\xac]&lt;\x11\x84\x9e\x0b\x99\xfdG\x19)\xc5pJ\x1c\xd1\xa3\x8f\x00\xcc\xe6\x96\xc6\xe5\x91\x97T}N\xd8\x9f;\xb9GO[x\x18\x05\xe2&gt;+4\xe2\xad\xe9\xf2b\x0cM\xc2;\xf8\xebG\x0f\xd3\x99\nqn$\xd7\xbc\xee\t\x95\x89:\xde\xef#\x92M\xa8\x83m_rWx\x8dj\x92U\x16\xc7\xc1\xb0\x7f\xca\xf1\x80\xd7\xb5\x92\xbc\xfd\x96\xaa(sB~\xd6\xcb`n\x04=\xb6\x18\x08C\xf4\n\xbe]c\xfcH\xbd\x0cB\xf8E?\xc5\xc2W\x00B\x80\xc62\x7f":\xb7j\x19\xb8S*\r\xf3\x8e\xa4\x08b\xffw?\n\xee\x8eA\xf4\xcd(\x02\xc1\xee\x83\xeb\xd7\xfb1i9\xed\x18b\xbc\xea\x92\x03|&gt;\xdd\xc3\xdcz\x08\xab\xbe(\xe6\'\xb9\xb1\x9b\xf4A\xc9\x07\\\xa8TA\xf3\x83\xf1i\x9a\xf9\x98\xb4\xc7\xe1P\xb4\xd2\x9dN\x07\x8d\x86\x91PD\x86\x9dGp\xa7}eZ\x87\xaco\x01\xc6q\x97\xdfMU\xfel\xe6\x16\xacKdN\x0c|\xef0\x06d5\xd2~\xbb\xa5\x8f;\xfb[t4=F\x1f\x18y\x90\xe6\x17qU\x86\x0e\xeb_9s\x84W:\xab\xf7sH\x01\xf0\xaf\xd5\x1a\r\xde%\xad7B\xbe\xf24\x84\xfa\xb4\xf6\x1ex\xaa\xae\xdd\x98h\x97\xe2\x9b\xd8$\x84\xc5\x8c\xe2a\xd5\xdb\x1ev$\xea\xb9\x93\x98\x9e\x8a2\x01\xf7\xc2\xe5\xa5\x86\xffH\xba\xc7\x85\n4\xee0\xf3M\x18\xb0\xda\x88\x98|-UfK\x92\x8f\xad\xa9\xb7 \x12\xe2)\xbfr&gt;\'\xcb\x83kj\xf3\x16\x08\x03\x16\xa8\x8f\xba\xc5\x0bb\x13\xec\x98\xe5V5N\xc1\xc3!lI\x8a\x10\xc1\xa8o\xd7Z~\x97\x05\xb8\xb7\xb3PC\x8c\xfeVN\x8c\xca\x99\x15\x9d|!\x8a\x86\x9e\xd56\xe1\xa2\x0e\x893!(\xe8\xa1nV\xb6\xdb\xda\xb1\xf8&lt;0\xa7\xc7\xd5\xff\xf80z\xde\xfb\xe2\x8dp\xc6\xe9\xae\x9f\x1c\x89P\xea\xf7\xc1J\x89o\x1f\x92-\x06L\xb5\xe7\xf2\xe5\xca\xb1\xb3\x83\xff\x002\xcf\xf1z\xee\xaf\xb7\xd0\xc2\xb0?\x1bk\xa6j\x85\th\xab*`\xce\xb5\xbf\xcd\xb6\xd6\xcd\xf7\x10\xe3R\xc8\xfa\x86\x87\xba\xfd\xe1c\x85F\n\xf5@}\xa0\x0e\xbfs\xd5z\x8e\x87\xb7\xdc\xdbV\xee\x89\xf6\x13\x91\xde\t\x00\x17}\xc8\xb9\x88\xf3v=\xadKR\xb2\xc3\xf2m\x88\x196dk\xc9Eh&amp;3\xfe\x1bA6\x10\xdd\xb5\xbbeh\x86\x13d\x81\xf8\x90J\xd6\xdc\xf9i\xd8&gt;xo\x08\xe4\xce,\x86\x08\x8b\xf6o\'\xedv\x91k\xb9\xbf\xb7\xd4\x03"\xf8^\xcc\x0f\xa1k"\x84^J\xacl%H3\xee\x0b/\x15[\x03P\x06t\xa7d$\xa0\x95\xfc8\x01\xff\xb3\xcd\x8c\xb1\xf1&lt;\xbc\x03\xb3\xd7\xa6\xa4\xeaF#\xc49\xbf&lt;\xe4\x7f\xbe\xe9&lt;AZ\xac\xc9\xb5\x0f\xf1F\x10\x9f\x0b\xc0\xba\xc3,\x81L\x066$\xe8\x10g\x17\x9f\xb0\xaa\x035\xd1\x15\xf8/\xc0\xdf\xb4\x85~\xd5\xeb\xa3\x16&amp;&amp;_0$;&lt;\x95#wu\x1dO\x19\xbc\x06;\x84fv\xf5*\xba\xfa\xd9O\xa4\xf5g\x90dP\xaa\xfb&amp;\xb4\x8b\xe8gT2j\xebf\x0fbF\x9b\x1f=\x87\xeb\xc7\xa9\xd8\x03P\xe6f\xdd}R\xa3\xc2q\xe3b\x93\xbc\xbb\xc1Xi\xcc|G\xdf\x12\t\xc5Q\xc0O#\xeaS\xff\xfc\x92\xf0\x96D\xa2\x8eo\x07j\xec\xc6\xc2\xe9]\xc5es\x9d1\x80\xe1\xe3\xb3\xff\xc5s\xa5&amp;\xa5,r^I\x86M\xa7\xad\x84\ry\x0b5A\xd4\xc2a\xde\xb4T\xa8?`[I\xdcHl\x08\xc4\xb0\x8e`\x03]|UC5 l\xc1\x9d\xa5&lt;pr=\xd7\xe6\xa3\xf5\x98\x1e\xc1\xe4\x13\xdc\xb5\xb6\xdd\xe6\xc0Z\x9f\xea$\x87\xd6\x82`\xaa^\xe5\t\xea\xbb\xd9\xa5EN\x17K\x9413\x87@\xdf\x99t\xaf\xa8s\xba\xf4f\xdd\xb4\x0c\xff\xe6\x8fcM\xfdU\x95E\xccp\xba\x81\x83dl\x03\x04\x10\xc9=\x1a\x14\x11ik\xc8\xd6\x9f$\xfc5\xc8\x19\x89P\xd1#\x8bc\xc9\xda:\xb02;\xeeH\xbd\r\xf94\x1c\xe4\x9e\x1b1\xe5\xec\x9e!\x1e9 \xf8\xd2\xd7\x06\x16g\xab\xe7RD\x99\\\x9f\x8e\xd8\xc6\xdc\x98\xb6\xb3dy\xdeYV\x99\x0b\xad\x96!b%\xac\x8c^S\x18\xc2l\x96D\xc1\x89\xb0-\x9c\xbb\x97L\xb2v\n\n\\\xa9\xe2\'\xf7\xe6\t\xcc\x89|\xe5iP\xc9g\xff\xd7\x08\x9er\xb1\xba\xad\x8f\xf4\x85\x15.\xec\x18a\x883V.\xbe\xc3\xc4\xc6\xf6\x8c\x82\x02\x81V\x94\xd0G\x0c\xbc\x05\x87\xf0\x0f\x8c\xb1s\x086\x80\xed\xe8V\xe2\t\xdd\x82]\xd3\xe2\xaf}\x81\xc2\xe2{E\xab\x07\xe9rT\x10\x97\xe4\xebd[\xd5\xb2\xf1&amp;&lt;\xb8\x14D:\x92\x88!`\x1c~\xee}\x84\xdbM\xa1\x82\xdf\x04\xa10r\xeb\x1b\xdb\xe9\xca\xba\xc3pol\xaf\xcd\xa7&gt;&amp;\xdcu\x1e\xf5"\xc4P\xce\xd1\xafS\xb7D4pa-5\xe5P\xaf\xc99\xb7\xe1Ca4\xcfs ~S\xba\x9f\x83_\x84\xb9]\x0eUw\x90\x8d\xa5\xed\x18\x0b.\xbb\xd6\xc6w\x07#S\xd0\xc49F\xbe\x884W\xd5\xfc\xb1\xaf\xcf\xc1\x8e\n\x9a9\xacz\xc5\x00\xd4\xfb\x8e\xe5\xe0\x1e\xcb*\xcb\xb8\x846\x0e\xbd\x03\xfc1b\xf8\xfa\x03i1\xfd\x0e\x1c\'t\x01|9\xfc\x1b\xa2S\x7f\xfc_\x851t\xb4\xb5\xe5\x02\xca\xd8r\xf1\xce\x87\x88\x19\x1f\xbc\x8d")#\x9f\xc5Y\xb9\xbe\xe1\xa4\x88\xd8\xfe\xc2d6\xdb,\x1f\xa6\xaaC\xc0K1P\xc7\r\x82\x1b\xb0\xb5\xff\xfca\x01\xd3\x9f\xef\xb9\xd3\xb1\xcc\xe0\xff\xef$\xbfw\xc4\xdb\xf0\xea]\xe7e\xd5\xccW\xe2\xd8\xbb\xff\x1e\x83\x1a\xe5\xc4\xb0\x07\x81\xa3\xf5\x02\x1foD\x8a=\xc3\xb8e_\x1d\xcaf\xe4\xcf\xd3\xa1\x9f\x82X\x15g\xcc\xb3~\xe0\xa4=\x06(Ro$::\xf3Z\xb4h\x7f\xff\x13\x19$\xf3\xc2`\xe4\xf5S~\xcbI\x8c\xa7Gyc\xad\x96`\x81(\xfc8\xd5P\xf6&gt;\x9b\x1b\xec\xe6\x93&gt;\xf7\xb0;\xa0\xcb\x99\xc8\xa3\x0c\x1f\xfc\x14WYE}\xa2\x0fK\xfeLN\xa5\xda\xe0=v\xd9\x87s\xbbgocq\x078|\x99o\x88\xf10\x85[\x9bO\x8d8\xe5j\xfe\x9e|\x15\x0b\xf5f\x87\xf3\xf8-[\xe7\x00\x16\xf1\x83\xa3\x0c\x137\x14*\x809\xb7\xe85\xd1\x7f=\x13\xff\xe2Q\x1f\x84\xe8\x19\xeb]G\x9cz1\x05\x9flu\xfd\x1fZ\xf3/\xa4_\xa3\xa0\xd8\xb0\xc8\x1a\xc9\xf2Q\\\xaa\x85}6\xba\xf7\xcb&lt;M\xde\xd5\x88\xa7\x87w\xf006\xaf\x0b\x1a\x84\xd1\xea\xa6\xc2`\x90\xdf\xe6\x8b\xa7&lt;\x11\x7f9\xc0r\x14\xd4sb\xf1R\x1a\x81\x00K\xab\\\xae\xbfBu\xda\x0en\x0c\xadJ\x8c\x03$\x82\x0cd&gt;S\xf0c\x1a\xa1b\x10\xc9\xe8\xf9D\xd9\xe0\x11\xfb\xee\xcfj|\xeb4e\x0f\xdb\x01\xb7.0\'\x7f\xc8&lt;\xda\x83=\x96\xf5;\x8c?\xcb\x0f\x0c\xc0d\x16.\x8b\xfe\xc5\xcb\x9eX5_\xb4\x96\x8b\xee\x18\x15\xd5H\xd9s\xbd\x1b\x03\x01Zi[\xe5\xbf\xbe\x8b\xf7.s5\xa6&gt;n\xde\x80_\x91 \xd2\xafOL\xfb\x8e\xa4\xd7\xfb\x90\xe2M\xe9\x01\xaehr\xa5\x1f\x0cY,Al\xa5\x9c \\\xdft\t\xec\x01P\\6\\\x13\x83\x08)\xd3X\xb9\x98\xfa\xda^\x1bI0\x90\xf8\xa2BH\x84\xb3H\xcet\xfd\xb6\xc5^\xd4H\x9b\x9c\xe9lj\xa2te(\x8a!\xb8\xea\x04\xb8!\xcc\xe1\'W\xe3\xbf\x937!v\xbd\xcf\x0e\xf6\xcc\xc4\xacF\xaf:v\xee\xe2\xe5H\x16\x86VP\xd4g,qu|\xe7\xa2\x07\xe4\xe8@\'\xf06W \xf1\x88\xe3\xf0\n\x1c#b\xc8G?\xec\xdd5|+}\xfb\xb7\xdc\xa4u+\xbc/Y\x8e\xde\xc0\xf8\x00\x19#\xef\xdc\x1f)LO\x8e\x1e\xf5\x11[\x8feT\xbbDIA\xceGT\x99bp\xe8\\\x9dJu&amp;\xa1Tx\xe9\x9e \xd9k|k\xe33\x1fT\xed\x16`\xa1\xdf\xa2\x16\xb1\xc8S*\x94A\x94\xba+\x8a\xefL\x10W\xca\xa2\xf1\x7f,$\xb2\x15\xb8\xa0l\x1a\x00\xe7@\xce"\xfb\xeb\xdek\xbd\x15\x12e\xbcH\x99\xb7\x10\xd9\xd4\x17#\xfb\xea1\xbcS\xff\xf2\xf9(\'s\x10\xba\xf76"\x0c\x82\xab\xd9$\x95\x0c\xb9?b\xfc1\xd9L\x9d\xde\x97\x06\xcf\x073X_\x96\x07_\xc3\xe6\xb02\xb2\x8bt*Za+\xc1\x18q\x08\xa4\xb6!\x9b\x9e\xa5d]\xc6d\r\xb7Cu\x1e/\xa2\xe6\xa2\xe9\x1d\x89\xaag?8X,&amp;;\xd0\x96e]\xc4\x1d\xfc)\xe6=N\xce\xb5\xc0\xaa\xac\x1a\xd94\xd4;\xaf\xe7\x07\xfc/\'\x0e\x19\xc8%\x14m\xfc7\xa3D/\x88!\xf4\xa2\x0eN\xf8\x07\x036w@\xf1\x05\\\xd7\x8aT4\xaa\x1a\xe8\xb3N\xc3{Q[\xd8;\x17\xa7L\xa0\xa7\xbe\xb2v\x8b\xb8\xc3A\xca\x1bE\x03\xb9\x92\x9dK\x08\x86kIW8\xc4\\0U\x8b\xf6\xbem&amp;G\xad\xcb\t\xa2\xda7\x16\xf9A\xefp\xa87\x94S\x10\xf8)\xda\xdbl\xed\r\xa9\x07w\xdc"\xa6p\x14\xd3b\xef~\xe0\xbe\xb8\n\xc9k\xa9\x07\xbb\xde\x8b)\x87\xf9#\x11\x83\xcc~\xd615}G:\x86\x84\x98U\xfb\r\xf9\x9f`h\xfc\xe9\x01\x98\x02f\x16\xa9\x88^\xc1HQ\xf6\xfee\x19\xfd\xb5LF\xbf\xef\xc8\xa1v\xea\x06\xa4\xde\x8968\xd7|}GL\x8a\xaf\xc5{-\xddKN\x8bL\xaa\x9a\xa2\xf2\x05\x05\xd1*\xf8TXC\xd6v\x8dh\x11\x0c\xc0\xe7=\xda\xb5,\xc04T\xa7\x1e\x89Ko\xe0\xbdV\xdf\xe2A\xe3\x81\x17\xad\xfe\x19\xd6\x9e\xf0&gt;q\x02{\x14_\xd7\xcc\xd2\x7f\xdc5\xc9\xa9\x8b\xf8\xa1\x9aj\xabhW\xc9\xac\x83\xc7\x04\xed\xb7\xb3\xb7\x07\xc0[\xcd\xdf6\x17\x10?h\x93\xferpP;\xb3\x96z\xe7j\xa3\xbbz\x88\x9f\xe3\x89K8\xd0\xa2\xf6i \xf5C\x05\x06\xd4\x0b\x8dr\xc1uU\x1e\xfc\xdf\x81z\xb8\xfb\xcfma\x9d\xf2\xe6\x03\x96\xa6\x9f\xd3\xe9\xbcR\x81\xe5\x82\xf1\xd2N\xdc?\x1c$A\x00\xea\xa6q\xcd\xcb\xfd\x19\\\x0bD\xe6`\x89\x91\xfc=;tWu,\xd0\xf9\xcf&gt;_I\x01\x8d\xc4\xbep\x19&gt;\x87\x07\xc1\x8bPr3\xbbq6\xc2n,\xd4T\xd3\x89m\x8ep\xc4\x80\x19w\xcd51)\x01Y\x02;\x0c\x1d\xc5\xc54\r\x92\xa0\xa4c_\xe0hH\xbakIC\xc4\x88U\xee9\xd9\x89\x9a\xebV/\x7fZ\xf3\xdda\x07"\xcb\xbd2(\x94o\x1f\x1f\x18\xa5\xc7g\x97&gt;G\xcf\t\x16\x85\no\x1a!\x02-^"\x9b\x053\xa1\xbc\xeaY\xae\x06\xd9H\x9e[\xe6\xe7\n\xcf^%\xb6\xe87\xcf\xc2\x9a\xb6C\xe0\xba\xafq/V\x1d\xe3P\xea\x194\xddJ\xd2\x03\x91\xc3\xda\xe9C\n\xc4\xa5\x13\x08\xd4j\xc9,\x95\xceCh\xa2n\xedZ\xbc.\xae3L\x0e\xeb)\xea\xd5\x13\x14n\xfb\xd5\xb9\x8d\xdc\x86\xa4\xa7\xb5\xcb$\xa3N\xc8\xec\xca@0n\x82\x87X\x1d\xe3\xc4\x9d\x9a"\x8a\xbc\x1f\xf6\xdf\xf9\xff;C\xc8\xd7\xeb\xac\xde\x19\x02\xdf\xa6;8\xc3\xec\xfa\xf0\xaa\x93\xe5\x031\x9d\xa8\xed\'\xdb\xd2\xba\x18\xd9\x90\xaf\x92~5\xf2\x11\x8b_CF\xf1@]\xc9!\xdf\xf8\xbd\xb3c.q\x97.\xb8\xb5e#\x1e\x9e/\xa0\xf7@\x97\xda\xa6qCp\xdfB^\xf2J\xf5\x0f\xaa\x95z[\x9d\xe7\n\xde\xff&lt;~\xfd\xfa=\xdbh]\xea]\xb2&lt;d\xe7m\x80\x9b\xea\xa6\xd7\x83;\x16\xc7\xcf\xfc]\x87Ly\xee\xe7\'\xed\xb9^B#\x1a*\xd4_H\xa2~\xee\x15\xb24\xe1\x7f\x06\xdfW\x15\x0c\x8b\xda\xa7\x82\xfd\x80cbv\x8f\xaat\xcfm\\\xbb8\xe0\xd0\xb3.\xe7SRG\xcb\xf3\\\xfa\xe5\xaem\xfcnG\xf1&amp;\x1e\xfc\xb3)\x86\xffW\x8e\x98\xcb\xdb+\x88\xed\xe4eJo\x9a\x124\xe1\xbe\xe7\x8d\xeac\x93\x9e\x06\xb4\tO\x13][\x85\xf1\x9fYP\xd7\x82\xebm\x00\xd5\xb1)\xdb\x07.\xe3\xe1$\xd7\xed\x13\xda\xc5L\x9b\xba\x0c\xaf\x80~\xf0i\xb6h\x05\x97\xd0\xb6s\r\xd9\xba}tb\xfaJ\xd0\x06{E\xb5\xe4D#\xb3\xc5\xc9\x9e\xc9\x17N\n#[d\xac\xe4\xfd\xec_\xc4.\xc8\x00)+\xb0\x86/\xd1sjJ[R\x8a\xc1P\xbdjN\xd3^``\xaa,S0\x02\xb8l\xb7\xe8\xe0\x8dow\x109c\xac\xcat\x1b\xdd\x03\xa4\xae\xab\x1e\xaf\xf7G\xc3e\xc0\xd9\x997\xb3\xe3`o3\xc8\xb6\x10\xd8?\xe8\xee_\xfb\xcd5\xaf\xf4#\x02V"\x06%1\xd8\x91\xd4\x8cg\xb2v.\x036\x89\xef\x82\xab\xdf8\xeb\x00\x131&amp;\x17`o\xe5\'\xba3\x06\xd9\x1b\x1esA\x83\xa2e\xbf\xd3\x01\xee\x84\r\xac\xc0\xe0\xfd&gt;Q\x15\xff\xb2\xeapu\xe5\xc8\xcb/&gt;#\xa9\xced6(\xdfa\x8d~\x92\xee\xf9\x10\xc7s\xf1\xdc\x1f`\xf1[\xcf\x94\xb8\x8eM\x14\xbf\xebam\xe6iT-\x17?\x8d`\xc9f\x9ed\x9cgU\x1f/N\xf7\x04&gt;\xedcd\xfc\xd6\xd8\xd3j\x7f\xacp\xb1\x13\x10v\xff\xea\xfc\xd4[6\x96\x8fI{-!\x1aW,\xea&lt;{\xde\xcc\xdc\'\x9a\xc8\x04Z\xcf\x8e\x8e\xa6h\xaaJ6H\xf0\x93\xd3\x95dQ\x11\xda&gt;\x92\xde\xcd\xe2\xfb!\x979\x02q\xc1\x97\xe5\x0c\xd4\xab^P\x85@\xaa\x12XK\xb6\xdf&amp;\xd8\xa3Y\x03\x14c\xdek\xe9Z\xd6B\x03\x05$\xe2\x9a&gt;_o&lt;d\xd7:\xa8eu\xaa8\xc6?n\xffc\xd8\x88I\xbb\xc7\xfa\x7fc\x18\x9b\xaa\xd1q\x00q\xf8\xffGR\xd8,\xc6b\xb5\xb8\xa3b\xc3\x9b\xf0\x94\xda\xc8?\xa4V+IS\xd4\x15\xdf\x8f\xc8\x90\xf9\xbe7\x08\x00Q[~U\x98L\x1bfT\x8e\x97\xb4\xeb\x02\xd4\xaf\xd5\x8f\x80}t\x88A\x1e]\x08\x16\x07+\xfa_\xb4\xfa\xd7\xc8\xd8\x86\xa7\xa3\xcfmu\xde\xad]\x1fN^\x08BG\xbcq\xea\x0c\xd5\x89!&amp;!3\xa2\xc6\xf7U\xb5\xa7s\xe4]Q\x19\x01\x8a3/5\x7f\x9c\x8f\x9b\x10F#\xa6\xa2\x8a\x0f\xe83\xbd[\xdb\x02\xf6[\x1c\xb9\xe4\x17?t\xaf\xf8&lt;d\x9d2\xce\xf0^Q=nr\xf3M\x919\x1c?j\xc4\xd3c\x11\xfd\xac\x90x\x95)F.\xea\x99\x017j^\xb8J\x82\xf1\xba\x9dgC\x94\xf7Ti\xe4\x9a\xb1/\xab7\x0e\xa2u\x83\x82\xe9pM\xfe*\xb7f\xc1\x84\xfew\xba\xcf\xda\x08V]Q\xdc\x9f\xa9trM\xe3\xa2U\xe3\xdf\x12\xcb\xe3\x1f\x94\x84g\xa1\x8c\x0eY\xc17\x1d\x91\xf2o\xdf\xea\xd7\x99\xf7\xd8h\xcc\xc4\x82\xdf\x0b\xeb\xe6_\xd7\x1f?\xc5\x95`D?b\xe6\xfb\xc8\xf2\x19\xa1\x1f`d\x03I\xad8\xe5\xa9E\x00\xda\xaa\x03]\xa3Y\x89\x05\x97\xa31\xcf\x90\xedU\x00\xe2\x80\xb6\xc1\xbfm~\xc1i\xea\xf5)9.\xd8\xaf\x0ezN\xca\xd2\x93\xc6\x81&lt;\x16\x12m\xae\x85\xd8\xd96\xbajz\xb1\xe0\r:\x86\xe1\xb1\x83I\x91J/\xbe\xdb\x90\xc3\x8d(\xa6\xcbu\xf3D\xb6\x89\x0e\x80=\x11d\xf15I=\tc\x11\xa8#\xf5\xa8\xa7\x8d=\xbb\xa0"b\xa1\xce\xdb\x163\x069\xdc4\xf4b[\xbd\xd9D\xc4z\xe1\x831J\xca\x12\xc7\xe6\x8fF\x00\xaa\xb7\x8b7\xc6Z\x07NAFr\x08/N\xf2\xb1&amp;\x88?\x03\x1b\xe2\x01\xf65o\nAh\xbe\xedu\xd3b\x89\xf6\xf5\x1d\xd6\xeb?_\xeb\xfa\x11\xe8\xb9K\xe3\xbfb\xdd{\xb8\x06D\xf2\xad&lt;\xa4\xb5\xa5\xb0\xc8[\xef\xd3B_\xac\xc8\xa3`\x90\x8f\x04Y\xe5B:k;f\xe4\x97Gq$y-\t\xc4bV\x0f\x8b\x9ci5N \xaf\x83\xe4\x87+F\xb8\xfa\x81\x94\xbc\xfaxhe9=\xed\x9e\xbdo\xd1\xc8&gt;o\x1e\x9cG\x82\xa0JF}\x127,\x0c\x83\xfbiH\x8f\x10H&amp;B\xeb7\xc5\xe6\xa3\xbb\x83\xb8\xc9~\x88Y\x08\xbf\xd9X\xd6h\x9b\xf8:\x1e\x95\x80\xc4\\\xa4\xd4\xbe#\xcc\x9cN\xc8\x1c\xf1\xf4f\xbe\xfdr\xdc\x11\x86\xfb"\xca+\xb5\x10\x16j\xef\x0f\xdf\x7f\x9cU6\x01\xd7m\xd66E\xde\x1a\xe3=\xbb\xa6\x86f\xd6\xe2\x069\xac\xdeGg\xbd\x8ac\xcf\xac\x85\xa2\x0f(\x8f^\x0b\xaf\xa0c\xb8\xe9\x8b\xafj\x90\x7f\xfe\xc2E\x138\xae\xc8S\xf3\x7ff\xa9t3\xb3\x18\xdfG0\x8f\xf5\xbe\xf3\xd6\xc5\x17\x1d\xcf\'\x9b\x00phh\xf6\xdd\x0e\x13_\xc2\xa48\xf3P~\xa6\xaa\x94\x8c&gt;\xbf\xfa\xb8\xc6X!c\n\x94\xbcEJ\xbc//\x0c\xc2\x1b\x0f\xd9\xfc\xaa6\xb6&gt;\x85tq[w\x8a(&lt;&gt;9\x04w\xdfIM\xc7\xdc\xe3\xf1jlL\xf6\xdfy\x01\xb1v$R\xce\xd2\xea\x13\xe4Rv\xfft&amp;\x01a\x12\xb4\x9d\xd3\xa6Ev\xc9\xb5\xe9\xbe\xe1\x84\x08\xd3\x87\xd6\xc6\x00\xb7\x92\xa2\xb9F\x05\xc2\xd3_\xfb\xd4\x0f\xef\xc5&amp;\xf4\x08\xc3\x1b`,I\xa0\x8d\x82)\xf8\xa6\xce\x93\x8c\xf4\xb0\xa1\xa3%\x03f)\x97\x12z\x88\xdd\x94@i\xbai\xd0{\x00\xe0Y\xba\xe9/rz\xca\x94\xf4\xe4\x83Zw\xde\xad%K\xed\x0b]\x83\t\xfe\x17\x9c\xf4\x87\x1e\x97\x81\xd0\xe3j\xd4\xc1\xd7\x13F\x05C!_\xc36\xf4\xb1$\x83\xb4e\xa5\xf7\x12\x8a\xb4\xa0\xa5\x18\xb4\xef\xaf\x07_\xc8\x0b\x8e\x1b&gt;\x8f\'\x03&amp;S\xeaY\xad\xf5\xc9\xf6\xd1\xf6\x93;\x1d\xbc\xda\xf0\xfa\xba\xfe\xed\x0cx\xddk \xc0m\x03\xfb\xd4\xb42\x81\xaa3\xc1 \x07b&amp;JqB\xa9\xe9{\xe5j\x83\xd85\x07\xe3\xb8,\\\xb8O\xe7\x82T\x82*R\xb1\x7f(\x81?Y\xaa\xff\xe4\x13\x18\xfc\x02\x0c\x7f[K\xe2\x11\xc4\xae\xd1\xeev\xdd\xeajo\xa4\x89&gt;\x8f\x84\xba\xdd\xfc\xb0\xe8^8\x88W\xcf4\x07g\xdb\x1d}\xd6\xb1\xd8`\xbb\x8b\xd0(\xee\xd2\x11\x9d\xb4\xbb\xaf\x00\xa7\x8d\xdf$\x04,\xcds\x90/\xeb\x12\xa4\xa8 95\xc37\xbfI\x14\xf1\x8d\xe8V\xf6\x00=\x93\xb7\xd8[Z\x13&lt;\xfb\xd0"\xc3\xe8\x8a\xe7\xee\x87\xb1\xfc\x18\xeal{\xc0\xabm\xbc\\f\x8d\xd6\x90\xd24\xa5\xf1\xc0\xdb\x0ed\x9a\x14\x1c\x02\xcc\xbe\x0e\xc8\xbc\xd5\'\xdb\xec\xe2\x83\xfbw\xb2\xa7i\xf2Y\x83V*\xde\x9cH\xf9\x0c\xae/\x1fK\x84\x86.$Y\x84[\xed\xd7\xac[\x10\x88\x1emk\xa3L\x04|7\xddA\xaa\xd1\xbcw/W\xd2\xae\xa0\n\x9a\x1dgh\xa7\x96~\xe0\x9aI#\xc6\xf9s\xec\x1a1t\x9f\xe7\xdd\xcf*=\xd2\xd9#\xb9\xcb\x9a]\xa8\xdc;b\x17"\x94\xaf\x1b\x1d\xfe+\xe5\xac\xe9\x88V\x81)\x00\n\x87(\xb0\x05\xe47\xfe9\x989\x90\n\xc4T\xa0wR&amp;\xb2$X\xf7d\x0cf\x19:\x91V&amp;\xd1.\x9c{%j\xecW\xa4\r\x1f\xba\x1d\xa6h\xad(F\xbb\\E\x00\x1c\xd0\x85v\x02\xb5\xe1\xf1\xbfK\x95\xb7Z\x03w-m\x0e\xcejM\xce\x80:9\x1d\x9a|\xb0\xa2jw\xe2\xa7\x9c\'\xb9\xc4\x01\x05\x1bqNo\x91\xd4\x16\xb9\xcd\x06\xf0\\\x10\x01\xbd0A-|N\xe9\xee\xd0\xd3\xf3\x96\x8d|\x13\xd2D_\xc3\x93U\xb4!\xd4\xfd R\xdcpFd\xe0}?\xe5\x0b\x05e\xa6\xbe\x01?\x06\xc1:\xf1\x01\x99\tV\xbf\x91\xde\x08.\xac\xf4D\xa1q\x14\x05\xa0\xa7\x1f\xc6f\x08\xa9\xb3\x1cVA0\xa49IL\xd2\xa3^G\x94#\x113\xe2\xd3yS\x9e\xdc\x90\xe7\x11\x13Y!^\xac(\xbb\xb8\xe3\xf6\x16\x10\x92\x111\xbb\xc8F\xbb\xb6\x95\x0c`&gt;\x9b]2\xdai\x90\xe8F\x8b\x96`\x9f\x98K\x99\x82~\x0cs\xde\x1e\xeb\xe5D\x0b\xbe\x8b\x88\x1cc\xdf\x0f[\xc0S\xb7\xc3\xfaK\xf2h\xc7\xac\xc9\x06\xb5\x02bW9$\xce\x03\xd2\x99O\x810f\x16.\x8f\xf8\x7f\x05\x8fUs\xe2\x1eJ* \n\xd7Z\xe3\xf1\x11E7\xd9(\xe3h\x96"\x97\xfd\xe5\xe4\x0eX%\xc4\x899In\xb7$\t\xf9@O\\\x9b\x0e:Qz\x13]\xad@W\xdc\xa7n\x9d1,\xd7\xc7&gt;r\xc4\x8e\'F\xb3\xc2)}\xcb\xde%\xa3\xbacd\xc6\x02O\xc3\xc0r\x0e\x93\xfe\xf2\xcc\x19\xf9\x87\x83\x01o\xa3\xc9e\x84\xf7\x86\xf2\xe5;\xcf}\xb4\xedI\r\x8f\xf80F\xde\xaf\x94 \xc5;\xf8\xe9\x83\xf5;\xfc\xf0\x06\xb5\xd64\xf2\x1f\x8a+\xbd\x8e\x15\xe7]\x07\xc1\xd8J\x18[\x0cc\xb1\x8c\xdb\x05\xf4\xad\xc5K\x1e\xb4\x8f\xbc\xca \xfas\x1d-\xd8\xd1\x8b&gt;V4\x97f\x18\t\xdf0,\x7f\x99\x15d\xcb:\xaa\xe7\x08\xf5\x89+\xf1}\x99o\x95\xc8KUM\xe9\x8d\x1c\xd7\x02\xa6\x96\xe6N\x81\x8f\x8f\x8f\xcd\xa7\xd9\xb8\xc0\xdbr\xe7\x9b?\x81u\xc3&amp;\xf4\xd0\x8d\x81\xfc\x85\x88\t1xP\xad\xbe`\xee\xb1\n\x18$\xa9$\xe1\xb1\xcc\x03\x81MA\x08\xc9&lt;\xfb)\xccp\xe9n\xf2\x80\xb5\xbe\x8c\xfd\xfcw\xbb\x05\xb1\xea_\xed\xa5\xc7c\x854\xff\x19g=\x9ev&lt;+\x13\xe6i\xb2\xe8B\xc5\x82\x81TE\x1a\xecg\x02Oj&gt;\xa6nL)\xf5\xbd\xc4\xdcU5qvy\xa3\x8cM\xd9\xbcn\xbd\x07b\xb2\xd0\r_\x8f\xa9@jO\x80\xc3wbh\xd3\xd3\xfdMr[\xe9[\xea#\xb8.\xa0\xf1\x08F\xb5L\xd9\xef\xd4\xbb\xfc\xc7]\x8a)3Ab`\x9e\xb9\xc8&gt;\xa0E\x0eWf\x14o\xdey]ZMC\xe5f\xb4\x8d;\xe7p\xbd\x9b\xdeK\x9f\xba\x03,\x17\xd5;\xf4\xdd\xd5\x19W&lt;\x16\t\xdfo&amp;9\x93K\xa6!\xf6\xc4a\xa7\xc9\x054\x120\xa0\x16\xd5\x9a\xb6\x00Qe\xf6J\xb6v\x98A\x1e}\x86\xe1\xef\xf8\xa7\x17\xc2\xef\xbf\xa4\'\xc2\x13]\xba\xb6gx\x9e~)l@ow\xba\xdf\xa5o1p\x1d\xa5\x88\x86\xed\xf4h\xacB\x93\x1b\x01 .\x07H\xf1\xf4Rv\xdb\x8f\xa3\x04G\xe3e\x1cL\xf1\xa9\x01m_\xb8RMa_\xb7\xe1W\x16\x85T\x0f\xec5#\xf40\xbd\xb0\xa2\xdby\xf2\xa3\x81!\x955\x1b\x8epH\xb3|\xdb\xf8A\xb2n\x15\xc8\x04\xf6\x9f\r\x9a\xba\xfd#\xf2P\xd0&amp;*\x08\x9f\x89\xd9\x7f1H\xb0\x01s\x95\xb6\x96\x0c\xf9\x8d\xd6\x98\x91u\xb8u\x97\x138\xa7!;R4\xec\xd6p\x8b\xd2\xe5\xc8u\x1a\xe92L\x90\xf0K\x97Q\x15jG\xd8\x06\x17[\xbb\x82\rPE\x9f\x8fb\x102\x84\x81.\xd5\xb8\xcf\x04\xa3\t:J\xf0\xf3\xc5=\xdd8\x85 \x8cx\xd1\xbf\x02d\x18\xc6\xb3\x05\xc5n\xc2a\xf3\xb4\xa24\x03\t\xe8\x9f\x17\x07%\xeb\xda\xd5\xba5\xffO\xe5\xf0\xca\xa2@\x1d\xda\xe5\xd72Y\x86\xab=\xfe%t\xa7\x97z\xe5\xfa\xe3"\x84\ryN\x1c\xc2+\xf3uhm#\xfc\xc2\xd7\x80j|\x9d$?r\xe3\xee\x1e\xdaN\x9f:\xb6\xb7\x0e\xc1\xeb\xef\x82\x8f;\xadL\'5~j%\xce\x19\xea\xae\x9b\xb2_\xdb0;q\xddj\x86\x90\x88\x81\x19\xe3\x8aS\xe7\xcc\xbe\xbc\x19\xb4QR\n\xee\xb3\x1f9\x95\xf9\xb9uxZ\xb9\xb8\x99\x15F\x01*\xa8\xb0\xff^\xd0+i\x00Q\x05\x8f\xaf\x05Ni\xfc\x90\x0c\'\xef\xc7\xda\x87\x06\x80\xdc\xb0\xec\xba\xeb1j}\xef\xa5\xf4f,\xbfzl\xa8\xec\'O\xfc\xa1\xaf\xc2R2\x18\xa1\x9b7\x7f:\xc9?^\xd2Jpp\xe5A\xd6\xe2\x82\xa4\xaf\xef\xf4\x87q\xb7\xaaj\xafE\rp\x1383l\x85\x95\xe4\x14rN\xab0\xd6J\x9d\xf2\x125\x1f\xaa+\x0e -\x00\x90Pl0\x89g\xce\x92\xec\t\x10\x8b\x9b`1\xc0\xaf\xe5\x9b\xb7\x1a\xf5\xc9uQF\xbe8\xcf\xaa\xcf\xd0\xcf\xef\xa2\xc1\x94\x8aW\xf06W\xbb\xaa\xd5\xb9V,\xc0N\xc1\xb4:!I\xb7\xc7\x07\xa94\x92|\xa9\x8c7p\x16O\x98\x0c\x03D\x13\xb8\xe0\x1c\xf6\xb8\x1a\nSH\x8d\xc3e\xadvLGv]D\x91\x9a\x82&amp;\x99\xa05\xbdD\x15\xb6`\x9a-\xe2~\x8d\xb9d\xdc\x02&lt;\x83\xc7\xeaBd\x00\'\xe1a$0\xa3\xfa\x88^\x01\xcd\xd6\xb6\xd2j\xaa\xdbC\xdb\x91S\x0c\x15Dn\xa7\t\x12q!\xcf\n\xe4\x0e\x86\x10\xa4\x8bo\xa7\x15\xca\xd6s\xe6H\xb10\x99&gt;2\xcd\x16\x17&amp;\xbe\x1e\xfa\xe9t[\x01\xec\xb0do\x93\x87\x8d\x00\x92\xb6 \x82~\xb7\rl\xc0\xbf\xe7\x9eb\xd9\x11\xe0\x0cz\xe1\xa9\xb6\x909am\xed\xfe\xb4Q\xd3\n\xd8\xd6\x1d\x1c\x97\xe9u\x98\xba7;v\xdc\xf6\x07\x8f9\xefD\x8b\x99\xa5\x94#\xfb\xcdIZY1C5\xac\xa8\xf6+i\xd9\xea\xf9%\xbe\x13p\xe0\xcf!\n\xaf-\x1f;Wr&amp;L\xcc\x9f\xb7\x99&gt;(\x03E\xd6\xbe\xf3o\xc7e\x88\xab\x9aU\x0b\xbe]\xbd\xf6\t]\xe0\xcc\xbc\x9c\x87\xf4B\xc7\xdef\xb3^\x1cy\xe4\xd2w\xd9c\xec\x88\xeb\x82\x9ffT\xddlfIu\xce\xad\xdc\xc3\xab\xb3\x8dA\x9e\x862\xdd\tS\xaa\xe9\xc9\x8b\xd1\x95\x02\x936Z\xd6\xb7\x1c\x925\x0b\x80g\xcd\xa6\xd7\x83`j\x01\x1aL\x14\xa1\xa8V\xf5\x84\x86\x16\xcb:\x19\ti\xcf\xa7R7\xbcS.\x1d\xe5\x83[\x02\xb7c\x08\xb7\xcb\xe1\xa4?E\x8b\x19p\xb6C\xe0\xee\x91\x84\xacX\xc2\x97\x11$8\x12\xdbm\xc4\x833\xf2IW\xc0\xe1\x90\x9aw\x0c\t*:\x8c\xeb\nq\x8ch\xcd\x0e\x9a\xc0\xb1\x959t\x08\xb3\x87\xc9!\xd5a\xcf\x9aW\xd0n\xee\xf0\xd77:v\xc0\x01,\x14\xd8Bd)z\xf0_\xb3D\x93\x1cQ\xe6\xcb\xf3\xb8UgV\r\xa2\x12/2\x0b\x95\x97_\x83\x8cnK\xb7uM(\xaf\xc2v\xa8\xbf\xbf\xed\xe6\xa1\xd1\x89\x17\x8a\\\xfb\x85|\x8d\xbb\xa5\x88d\xd0\xec&lt;]\x03T\x03\xeb\x87\x98T\xcf\x7f\xa0}fm\xbb\xf0\x9f}\x07\xb0\xc9J\xce\xb6\xa1a\x02c=\xe1\xe0\xcf\x1c_\xfe\xea\x0e\xb37M\xe2"&gt;\xfc\x1b\x8a\x8f4J\x97\x86\x9e\xc0\xd3\x15\x00GX\r\xdfL_\x1b\x83\n\xfe`\x15\xd1~$\x9d66\xe3\xeco\x82\x95,\xab\xc3kP\xc9\xc1\'\x9b97\x01\x8cm\xf9\x1f\xfeZ\xad\xd37\x0f\x80\xfb%3\xfa\xf4\'\x98\xd0H\xd4\xd8vs\x92 I\xa0\xec\xf4]\xe6,\t\xd2~h\xc5MJ\xbbp\xd3\xc4\xaf\xc4\xc6\x9d+\x86\x10\x88\xe2\xc0\xc1\xb2\xdc\x83:R|\x18\x05?VT*\xe9}-*k\xdf\x9eE\x9d\xfa@3\x03&amp;\xc4\xe43=N\xc5\x16\x7f\x04\x86.\xd7g"\x83\xb2aY\xf1\xae\'\xf62\xa4\x16&amp;|+\xc5i\xe5X\x1d\xfc\xe3\r`\xfc\t\xf2M\xa2\xbf\x19\x8f\xe0\x08\x13\x12/\xdf\x9cI\xe3O}\xb5M\x1e\xfe\x91I\x99Z\x86\x1b\x001\xad\xe9Zf\xfa\xa7+\x98w8\xba\x93\xba+\x997\xc5\x8e\x15\x0e\x00o\xda\x9b\x81\x04\xf9\xf3#\xc2!\x8b\x16l\x89J\xaf\xac\xa4|N\xdb]YF\\\xb1\x08L\x952-|\'%BrDD\xae\xe2&amp;\xde\x8f\xe3\xe6:\xeeL\xbf\x90\xad\x03\x9a\x01\xca\x90\xbaS_\xb3U\x01\x17\x16\xaeT VD\xd9\xed\xff\xb3\xd3Ue\xa2jg\xfaF\rDs\x83\xb7\xaa\xa6\x13\xd4\xf7\xbbk\xeb\x90\x8c\x8f\x14f\xd4\x05\x181\x96\xb7L\xdf\xea!T\x04\xf5\xcept\xc1aK\x040\x84\xbd\x1aQ\xdb\xb2\x82N\x08Z\xa8$H\xf0\x00\x00\x00\x00\x00\x00\x00\x00'</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Kit Fran Love Kit Gloss Labial E Lápis Labial By Franciny</t>
+          <t>Torneira Dazie Metais Com Filtro Cozinha Para Parede Flexível Móvel Em Abs Cromado Filtro Carbon Block Purificador De Agua Com 2 Velas Extras Brilhante</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>74</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>767</t>
+          <t>119</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>37% OFF</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/kit-fran-love-kit-gloss-labial-e-lapis-labial-by-franciny/up/MLBU3214981421?pdp_filters=item_id%3AMLB5415887354&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB5415887354&amp;sid=affiliates</t>
+          <t>38% OFF</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_666525-MLB85597283317_062025-AB.webp</t>
+          <t>https://www.mercadolivre.com.br/torneira-dazie-metais-com-filtro-cozinha-para-parede-flexivel-movel-em-abs-cromado-filtro-carbon-block-purificador-de-agua-com-2-velas-extras/p/MLB25869456?pdp_filters=item_id%3AMLB3834227763&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB3834227763&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>b'RIFF\xd05\x00\x00WEBPVP8 \xc45\x00\x00\x90\xe8\x00\x9d\x01*\xc0\x01\xc0\x01&gt;m2\x95H\xa4"\xa4\xa1$\xd3j8\x90\r\x89gn\xf2{\xd1\xcd\xce\x92\x9b\xdb\x19\xd8\x00\xff)\xd1\x92\xcd%\xe5\xfc\xa6@lY\xf6\xbf\xc9\xce\x90n\x91\xf1\x17Q\xf9\x83\xed\'\xf7\x7f\xdb?0\xfe\x0f\xff\xb7\xfe\xab\xee\xd3\xf3\xbf\xfa\xafp\x0f\xd5\x9f\xd6\xce\xba\x1f\xd8\xbd\x02\xff0\xfe\xdf\xfbK\xefI\xfe\xbb\xd4\xaf\xf6\x9fP\x0f\xea\xbf\xee\xba\xcc\xfd\x04|\xb5\xbfq&gt;\x1a\xff\xb1\x7f\xd0\xfd\xb9\xf6\xaa\xff\xff\xac\xd9\xea\xaf;\x1f&gt;\xfe\x1b\xfe\x17\x86?\x91\xfd\x0f\xf9\x7f\xef?\xb9?\xe1y\x9b\xf6\x1f\x99\xdf\xcd?\x1e\xfe\xaf\xfcg\xb6O\xeb\xbc\x05\xf8\xbd\xfe\xbf\xf8\xff`\x8fh\xff\xa9\xf1g\xfe\xf7\xba\xb3g\xffk\xffS\xfd\x1f\xb0\x8f\xb4\x9fb\xff\x9b\xfec\xf2_\xe0o\xea\xff\xefz!\xf6#\xfe\x87\xf7\xff\x80\x1f\xe8\x1f\xd2\xbf\xdf\x7fx\xf6\xdb\xfe\x0f\x8b\x97\xd6?\xe4\xfb\x03\x7f%\xfe\xdf\xffC\xfc\'\xe6\x7f\xd4\x07\xf7\xbf\xfb?\xd7\xfa3\xfa\x8b\xffW\xfa\xcf\x80\xff\xe7\xdf\xdd\xff\xed\xff\x8c\xf6\xdb\xff\xff\xeeG\xf7;\xff\xc7\xba\x9f\xedO\xff\xf1\xf5\x03\x95\xde\xdc\x91\x01\xc1"OO \xa3\x1aHy*\x08Q\xca*P\xae-Q;\x97{r\xe4\xcb\xbd\xb9m\xc5\xba\tt\xd0\x0cd)\xebJm=\xee\x19\x17\x03\xcb\x04\xec\xd5\x8a*+&lt;\x98\xe3\xcd\xe7R\xfby\xd4\x85ay\x1b\x1c\x99w\xb7.L\xbb\xdb\x97&amp;8\xdc\x0fT\xcdx!\xb8$\x92o\xef\'\xa5\xd8\xbb\xdc\xdfv\xe8O\x9a\xab8\xba\xb8\xc7\xceYxe[\x93.\xf6\xe5\xc9\x97{r\xe4\x88\xfa\x86p\xe8\xa1\xab.^\xb2\x0b\xcc\\A\xafd\xdf\x93\xac\xa7\xdf\x8a\xbb \xcb\x12\xc1\x8dxd\xee&gt;\x14M\xa9\xe2\xa3*\xf1\xb3\x0bo\xc2S\xa8\x7f\x0e;F&lt;\x0b/\x8d\xe0z\xffg\r\xd1r\xa8\x84\xed\xf5\xc5\x16\xb9\x07X9hW\xf6\xd8\xcc_;\xdb\x93\xf9\xdb\xdd\x1e\xfc\xbf\xe9r{\x113\x0e\x1b\xbcH\xd96\xc9O\xd6\xd9\x9fq\xe0|V\xb0}\x8cc\x1f\xea\x1d\xc5\x8d\x00\xd6\xb144\x9d\xac[\xf9\xef\x925Oi\x02XL\x07\x7f\x82b\xc7\xa9\x9b\xdc\xa7\x11\xd8\x1e@tA\xf0\xb9]\xd4]r \xbb5s\x7f*e\xc54&lt;eb\x16\x02\xf6\x07-r\x0b\xa7B\x96\xea_l\xce\x85\xf1k\xe5\x96Vm\x1f\xc1\xee\x94Q\x86\x82I\x0bD\xf2\x1f\xf7\x14\xfb\x07\x9f?(\x12\xd36\xcc\xf1.\'\x9d\x83\x90K=\x9a=\x86O\x95\x8a|2O\xd6\xc22\xf3\xb4\xcb#\x82G\x13h\xe7\x98Nt\x15\xff\xacZt\x96_fbota\x19=\xd2/\x14\xfb$\x85L3\x05(\xeeN\xa4\x80f"2\xb5\x9f\x0e\xcb\xf1]\x1e\xb7A\x1b\xd6\xc7p).A&lt;\x15\x8f5\x81\x8b\xe0\x11\xbb\xdc\x15k\x1e\xcd\x865=|\xab~=\xfc\xa4\xf6\x8b/\xac\xfb\xf1\xe0\x8f4\x1b\x03\xee8f\x9c\x00\xc5/m\xa5,\x94`Lm\xac\x91w\xba\xe0W\x17\xba\xd5w\x863\xda\xc8\xb6\xf2{\xd1o\x83\x99\xa5\xa2\xaf\x16:\'yi\x07\xdc\xc4\x92\xd7\xad:\x8af\xb3\xc7+\xcd_;\xd0\x83\xbb\xf2\x91"\xd5x\xa8\xf0\xa9\xad\x7fA\xe3,\xe1\xa4\xd0\xe0\'F\xed\xc3\xfd\x84:\x04\x85\xeawYw\xabp\x87Zy\xc4\x918\xb9\xe5:\xb7\x87\xb3\x01)\xbb\xe8c\x8eJDh\xfd\x8b\x878\x88\xb5?\x9cK\x1db,+)\xce\xfa\xd1\x80\xae\x0c"+_?\xc2\xd4M\xc0\xb6\xc6tB(\x85\xe7\x96\x94\x17m\x8a\x89}\xc3\r\\\xe3\xf7!\x0bN\x12\xbbF\x0b\xce\xaf\xban\xf32+\x95y\xf3\x17\xc2\xea\x9f"lj\x8a\x10$\xf8\x86\xc6\xbeH\xd8\xc5+\xeeW!\xadU6\x9d\x86h\xab\x88a\x04\x94\x7f\xf6\x04L\x9etMy\xe6\xa5\xb5gNr\xbf\xb4\xb0",\xc5g8\xb7\xd9G\xab\xf8\xad\x0cVC\xbbz$\x0f\x82o\x03!%q\xc1\xd3\x088m7\xfdsx\xcf\xb3\x19\x96\xbf?\x9cb\x99\xd8\xdcR\xc8p\x96s\r3\x06%\xb4W\xf4\x15\x18\xc9\xe0\x99a\xc5\x97\xea(\xeb?\x01\x8c\x15^o\xeb\xa8\x95j\xf2"~\x1b\xcbR\xc9\xd2A\xa3^\x89\x0e4[\xf5\x8a\x92\x8f\x89n[x\x0fP=c\xee\rS\xde\xcf\xef\x05\x10\x8e\xc9\xcb\xb4\x96TX\x0e\xdd\xf9n\x9fA\x8e\xbc\x1b&gt;z\xf9%\x93\x93L\xf6\x8c}\x10|\xe4\x9d{$\x9bL\x07(\x02\xb4\xe8\xc4\x1289\xc0\xceUnU\x00i\x99[:\xe7`C\xad\x1d\xc2\xf4\x15oQ\xb7\xbeB\xac\xa0\xcc\x02\xe6X\x931I\x05\x07\xdcoz\x98*\xce\xd6\x83\xa2;Z\xc24S\x0e\xe5\xde\xdb\xa6\xdb#\x13/\xaeY\xbb\xed\x86\x7f\x95\x86\x17\xf8q\xc1JHu\xb6\x1a\x8d/\x7f\xc5\x99\xf3C\x83\xb7\xe6&gt;v\xf4v)\x8c0\'\xa3@\x05\xf5@\x7f\x00\xa6\x1d\xcb\xbd\x85-\x91\xd1\n$\x8a68\x13\xe4^{\xb3u\xa2 \x99r\xf3\x8c!n|\xb0\xea\xa4\x10\xc0\xb0y\xd4\x10\x95\xd0\x05b\x97\xdb\x0cH\x07\xe9\x93\x990\x10\na\x96\x19\x85`\x85"\xa9}\x04\xe4W\x8a\\v\x8c\xe6/\xfc\xff\xede\xdd\xdf\x85Wt\xabr\xe4\xcb\xbd\xb7O\xc7yhaj\xe5*\xf5\xfb\xb7\x1b\x82$\xae&lt;\xca\x862yC\xa1\xa2\xe5i\xffJv\x96\x9et\xee\x93.\xf6\xe5\xc9\x96\xffS\x92\x0c\xd6g\xd2\xe3\x04\x1bP\xe3h\x1f=\x8e\xa5\x92\x9a\x95\x1a\xf4\xd8_\x80T\xb7\t\xae\'J\x19)\x0b\x8f\xfd\xd9\x11\xab\xa0n\xaf\x89v\xf6\x98\xc6\xd8\xbc\xf4c\xe8\x84\x02\x86\xe6C:^\xd4B5\xb6\xfd\xe8\x8e(Hf-7\xb1&lt;\xef\x04Z\xb4}\xdfDE\x91\x10\xc9\xdc\xbb\xdbt\xdbd`\xf8\xab\x1e\xd1\xcc\xfa\x94a\xee\x86\xe3\x9f\x9e\xe3\x87f\x10\xa8l~\xd5\xc0\xfa!\x00A\x85\x92\x17I\x07\xe8=\xeb\xcd\xcf\x1f\xd7!\x1e\xef\xc8\xac\xbcU E\x1b\x1f8I\xe57!0\xc4\x0c\'\x97\xb1\xdd\x8b7\x16\xcbl\xfb\xb9\xe3\x06\xdagC7n\x9br\xe4\xc8\n(\xcf\xa1LT~\xaa\xc2\x89\xa6\x0c2@\xbe\xc60/\xc5\x8a\x00\x1c\xa5\xce\x9e\xe5\x91D\xeaY\xdebQ\xa9}\xcf\xdf\nd;_\xe2\xee\x88\xf2B\xd9\xf2\xfb\xb8\xb2\xa7\xafE\xf5^\x19;\x97\x14\xb2\x9c\xb1b\x04\xf1\n.\xb7-\x8d/\x86\x08\xcb3!\xd8\x1e\xf6\xb8\xb8\x95n\xbc@\x91\'\x00v$\xcf\x99@\x9b8\x93\xb1PBCD)\xbb\xb0\xac T&gt;\xdc\xb92\xefb\xff\xdf:\xab\xe3~2\xb7\xfd&amp;A@TE\xe9)\xfc\xf9\x89\x85\xc7x\x10\x00\xb5\x9bg\xd0P[H%\xdf\xa1\xfe\x86\xb4&amp;\x8c\xe8bv\xc6m\x03\xa1\x11\x01l\xb4\xe8\xce\x1f\x90V\x0c\xc7\x0c\xcf\x87r\xefn\\\x12\x07"S\x99\x8f\xd0V\xb6\xabKL\xfd\xb7\xf2\xadc[jOPX\xc2?\xe6\n\xce_\x01\xe2p$v\xe8\xdf\xa7V#q&gt;\x18\x95\xce\x96\xdbz \n?\x90\xeb:\x85/\xee\xd1?\xfc\xd2\t\x99t\x81\xf7$5\x12\xd9\xe2P%x\xfd\xad"\x98w.\xf6\xe5\x85\xc70[\x06`\x7fZ\xd2l?LWY\x07\x13\xbd\x1e~\xd8\x12\xc7-\x00G\x1f\xf6\xde!N\xee\xa5\xfbB\xaa\xe7\xb9\x13YL\xeeW\x85\xa9B\xec8Y\xd3\x90\x87RY\xc9\xd1\x8d\x96\xdd\xc6@\xba\xc2\t\xb4\xf5\xb4"\x05\xac6\x02\x01L&amp;f$\xfa\x18\xbe\xfd\xb8\xddf\xeaGkkwr\x029\x9c:f\xd0e\'\x82\'\x0c\x9d\xc9\x18\x00\x00\xfe\xfe\xe6?\xa2\x14\xd4^\xcb\xe2\xe0\x8e\xbc2e\xa9\x00\xa6\x1cY\xa7\xeb\xb5Axw\x8aH`X\xb4\xa5B\xc8\xe1!\xa7\x06\x8b\xa8\x8a\x1d\xf0\x1c@\xd9m\x9b0\xb6\xd4[\xbfV[y\x1a\x00\xc6q$\xcc\xb5$\x07+\x89\x9e\xf7\xaf=\r+O\xc0\xecn\xee\xf9\xeb\xd6\x1b\\Z\xaa\x91x\x0f\xd1\xd2\x1d\xa0Yb\xdc1\xff\xfa\xa5\xb3{\xee\x89\xcc&lt;\xc2\xe6\'(\x12\x9bwm\xdb\x05\n~\xf8\x87%\xdcg\xf0\xe8\xf9\xcf\xe6[\x9e{\xff\xf8\xa9\xd4\x00\x00\x8a\x98h\x1b\x11\xd1\xdb\xd1\xf9\x1e\xe6\x8e\xc1EJi\x93\xd5\xa6\x86\x9d\x82\x9f\xb6\xca\xcb4~\x17\xd3L\xc6\xfe\x11\xa9\x82\xefJ~v|\xe7\x0c\xce\xado^\x89\x1b\x00\x1d+[k/\xb6[q;&amp;\x8b\xa3 \xdb-\xb4\x13\xcb\xca\xfb#{\xf5\x88\x88\x93\xcfK^\x02\x83U-\xb9\xe9\xbb\x11\x89?1\xc6\xa6J\xd3\x86OQ\xd3{\xd0Y\x13\x9d\x84\xa4\x1e\x0e\xc8\xb2h\xe0\xd1\x85\x08\xd3\x98!\x941\x91~\x1d\xe1\xa16\x906\x98\x1f\xa2\xf4HQ\xb9\x045\x86,\xfd;\x15\x11Z\x94\xf3!\x05D{S\xf7)\xe7LW\x94\x18\xd6Jy:\xd5\xc0\x8a\xb3{\xa5\xa7\xfa\t\xb2\x17\xd1G1_\xca\x85-\xea\xb6\xee\xad5\xd9D\xef;\xc0A\xa0\xbb5n\xdc\x1c\xb3\xe9\x9dq\xd1\x1b\xca\x01&gt;\xdd\x0e\x9e\x95i\xe7t\x9d\x91s\xc2\x11\x16\xd6\xaf:\x868\xc7^\xa6\x1fr[\x95m7/V\xcbbs\x9f\x7f\xab{\xa94\x13\xe3\xde\x11\xa3\xbag\x06=t\xd6\xe0\xa3\x00\xbb\xa0h\xcb\x81\xddm\x8d\x91\\\xd4\\\xb5\xa5\x0f\xc6\xc3\xe3\xd9\x18a\xcbj\xc8k\x11\x9d\x07l\xd1\xef\xec\x83k&gt;\xa4\xa6\xee\xc9\xb9\xa9B\xd1\x1cF\xa3\xe4\xb6..\xd5\xaeo5\xd3A{x\xc5\xfbv\xbc\xaf\x9ej\x06]\x98\xba\xd2\x0f\xf2\xdb\xa6;)\x10o\x98rBs\x88n\xdf;\x80\x9b*\xa1\xa7\tI&lt;\xcc0\xa9?fA\xf3\xa6\x0b\xf7=]t\x06\x97\xf6\x8d\xf96\x8e\xb4P\xd2\xc6X\xd0!\xab\xe7)\xae\xaaT\x99D\x98\x06\x88\x17\xf5i\tU\xb7\xda+I\x86\xce\xde\xcf\xe0%\x91\xe0\xb2\xa6\xb6\xe1\t\t\xf5/eQ#\xbb$b\xb0x3S\tvf\xe7F\xa8\xa0s8\xb9:\x9f\xde\xd6\xcf\xfcyb\xd6\x9f\xb0\xf7\\\x1d\xd5\xc0\xc4\xac\xfb\xdc\x00\x00\x0c\xed\x8cN\xac\xe5\xae\xb1\x82\x9b\xb7\x939\x9b\xe3\x94tO\xf5\xbcS\x8d\xff\xa0\xd0\xe1[\xdc\xf26 \xf5\x07\x0ct\x81#4i\xafX\x9d\xd2p\xf1\xf0\xf2\x17\x96\xcf)\r-\xfc\xc7G\xca\xd8\x06\x80+~&amp;\xdb\xca&amp;\xae\x1a1p\x86# q39\xf1(sH/g\x82\xba\x0c\x10cR\x94t\xcat\x0f\x00\xed@\xe7{\xfe2y\x80\xb2\xf5\n\x08&lt;\x92nxn\xdf\xa1\xce\xcf\x9d[i\x1f\xea\xbe\xda\x04c\xb6Y\x18\x9c\xfan(\xdd{\x91pC\xb2\x15\xd5\n\xcdV\x18j\x12\x90\x0bi\xd6\to*\xadS}\xd2\x7f\xc7A\x8c\xd8\xf9\xb9#/:g\xf6E\xcfe83Sm\xcb\xa3YO2\x82\x97y\xe0\x93\xafV\x95\xdac\xdc\xbe\xcf\xb6\x81\x7fv\x7f3\xffH\xe9Mf\xcff\xfdgq\xedX\x95\x83o\xcbR\xba\x91\xf7\x1a\xee7\xae\x9c/EB\t\xb9\xf8\xde\xe7\xe4[G\x05/\xd0u@\xd829k\xf0\xee/)f;\x9cB\x0b}\x9a\xa0\xf2a\xd9ac\xa7\x98\xf9+\x12\xf6\xd6\xab\r\xd2`\xa4\xce\x18(\xa5\xacp\xb9k\x9bGC\xf2\xa5\xb5\x04i\'\xff\x13{\x82\x1e\xb6\x9c\x87\xddG\xa3W\xfa\x011o\x7f\x93"\xeeM\x96\xf4J\xe1\xca\xf5\x1cd=\xfe\x11aV\x8d\xfd\x95MU\xa9\t$\x18\x00usf\xa6\xa5\xa9\n\xcf*\xc2\xbf\x1c\xcb\xfbt\xc8\'\xad\xd5\x95b\x82yC,\xf6\x95\xab\xe4\xe3\xeb*K$\xbf\x18\xa9B\x8f\x8d\x8aS\x8a\xe4\x1c%\x8d:1\x03&lt;V\xb0x\xbcb6Uh\xdao\xdf\x96\x07\x16\x8c/1\x8c\xc4\xd8j\xe8\x92-6\x97\xaed\x18\xe9\x12\xa74\xc5\xbb\xc3\xcb\xe22&gt;;\x80\x18?\x8c\x90\x82\xdes\xaf\x145A\xa5\xf7t\x82&lt;f\xad\x0f\xad\xdd\x80\x1c\xf5zg=\xdc\x853p\x82\xc7\x18\x8eH\\\xca1\xdc\xbb\x96\xe3\x08\x7f\x9e\xba"\x19c\xa1\x96n\x19\xa1BZ\xa15C\xd5}\xd7\xaa\xe9\x9f\xe5\x0c\xe0\xcc\x8e\x9cV\x8b\xdc\xff\xb9\x04U\xc0V9\xf1|O\xc3\x9cj\xef\x91\xed\xe2\xa8\x95\xba\xb0\xfaA\xc2[\x11\x8e\x11J\xf7\xd8\x86\xb0\xb23\x08\xf2\xb1\xe8c\xc3\x08\x8f\xd6b=\x827\xf93\x18\x8d\x06\x8dm\xe5\x1c*%`^\x8fV}\xf0\xb3\xa3V\xedB*\x97\xb1*-\xd6\x83\xd6\xfd\xab\xb7\'\xbe\xd2\xa7\xb6 \xa2\xa9wA\xa2\xf5;%\t\x13\xf9\x0e}\xeb\x90k&gt;\x14\xac\x00V\xfd\xe4T\xad\x9f#\x0e\xff\xee\xd1\xb0\x04\x11\xdfJ6:P\xc2\x88\x91=\x9d\n\xb4*\x04\x1a\xf4(t~s\x15\xcbZ\xc2\x95\xa39\xcb\xa1\xed\xd0/\xeb\xadYF\xc5\x99\xda;\x10\xfd`\xbe[~\x90\xce\xc3\x16\xf7\x8f,\xce\xea\xf0\xff\x0e\xb9\x149k\xdb\x00cl&gt;\xa1\x15\x92\xdbQ\r\x1c\x17\xfeC\xdf\xfa^q\xe0\xaf\xacIv\xe4\x19\xca\x90d\x0es\x04!\xa9P\x17F\x9f\x11\xd2\xe0\xdd\xc6Y6\x953e\xd5P\xec\xb8\xe87\xd5\xdc;[\xe2\xf4##O|\x92WG\x92\xc1=\x95\\\xab6&gt;\\+\x05C\xa8\xff\xf0iQ\xd5\x8b\x9dy\x9f\xe9\x91\xc4;)\x0c\x04\xbcq\xd6\x84\xf5\x1er9\xa9.\xd5\xb9\xe2?\xe6\xa1\xce&amp;\x93\xa9\xcf\xd1/\xc8\x19\x9dx\xda\x90\x9a\xe4[\x94~\x7fU\xa3\x01\xe8;\xf3\xd4\nv\x12!f\xf6\x81!\xc09-/\xb1N:\x9d\xd6\xee\x1d\xf7\xbcvi\x0c&gt;\x04\xf7\xdc\xads\x81~9X\x17\xdc\x93n\xccbi\xc4sa\xc0\x9eR)/3\x85\xacB\xf8^\xc9q\x1d\xb4\\\x04\xec\xb0\xa8!j\xad\x10\xdc/\x13\x05R\x11\xc7\xf9`%d\xab\xac&lt;\x93`\xa0&lt;~O\xfd4\xa2&amp;\xcc\xbc\xdeWW\x19:\xec\xf8\xbe\x000\xae\x8d--\x14\xbdZ\'\x10\xe9F\xbf2\xbf\xa7\x08*(d[\xe6\xdd\xeb\'\x16\xb5\xa0c\xce\xc9\xdd\xc0\xe8\x83:\x16\xbcgLI\x90\xa6\xd7\xb6U\xee.w\xad\xb8V\x9c\xe0^\xc25\\\xc4%\x15o5C\x9c\xf6\xd7\xe9\xb6F\xb4\x9b\x80_\xa0\xaf&gt;\xc8\xc2.\x90\x9b\x1f{\x1c\x11\x90o\xc3\xa9\x98\x1a\xf0\xd8v\x1d\xef\xe6gt\xf3\x9d\xc5\xd6\xe2\xc2\xe5;Wgh\x0cAl\x82\xb51\xe8[\xc5\x17\xa8d\xb5\xa3X\xc2\xfa\x14A\xc9\x0e\x0f\x9d\\9t\x81\xed\xdfpZ\xab\xa6\xb0\xeb\xc7\x98q\xbb\xef\xa9\x95\xbd\x83\x18]\x80.\xd7\x0cvk\x10x\xf6\x071a\xb4\xf8~\xcd\xba\xaar\xf1\x8c\xa0\xe8WDp\xc5\xa7`n\xbe\x9fm3\x0f.j\x19\x92\xf2\xc1\xad\x8f\xde\xb4s\xe6`\x82\xd7\xd1\x94\xf1.\xb8\x7f\xab\xca\x00\xfa|5I\xb4\x07\xae\xbc\x10\xa52@\xe9\xf6(\xc9U\xb3]\x8a\xdd/\xd7=\\\xc5\x98\'6\xcc-\\\xa8\x8d \x18b\xaa\x89\x97D\x04\r5\xac\xab\xdc\x18\x16i\x9f\xf1i\x96\x02\xfd\xb8\xc29\xdeo\tR{\xde\xff1\x17\xad\xd2\x0f\xc4\x9ca\x82\x98$\xed\xfb\xcd\xc8\xec\xda\xab\x1b\x9f\x93\nP\x05\xef\xd59u\xcfe\x1d#\x00\xfa\x1d!x\xd2\x83\x9b\x17\x8eAX\x93\x0c\xd3\x83\xfd\xb6~\xb7\xa7\xd3\x04\xcb\xf8"\xa3u\x02\xc9l\xb8\x03\xd5\n\xf8\x8dg\x82\xcf\xf2\xff\xc7T\xbde\xf0\x0b~K\x87\xfb\x1b2\x96J\xbb\x12c\x1a;\xab\x07g\xd9L\xcag{6\xb3\xf2\x8b\xd3\x99\xf2L\x98\xac\x1f\xe0\xb8\xc7\xd8B\xf2\x08\x89\x12\xf3CA\x97\xef\x0f\x9bp\x1e\x18\xfd\xe4b\x0fH\t\\\xdf\x1f\xd4\x8f\x9f\xf7M\xfd\xa0\xa30\xcf%^j\xfdK\xb5\xfd\x95\xe5\xf0\x07$\x18i\xd4\xfb\xa0\xdf\x8c[5\x93\x1c\x8f\xf8m\x8b\x07R\xc5\xe1\x81U\xf7\x95\xfd\xe6\xe7\xd3\xc0\xe2\\\xc2\x94\x86\xacX\xe3\ns&gt;\xe3vN+*\x12\x16\x96V?\x9a\x13*\x1dN\x19D\xe3\x9d|\xdewy\xb7o\x14\xa7\x96\x8c\xd4\xdd\x84,\xb04\xa3&gt;P\x05\xa3\xe6\xc3T\xe5\x98\x99:\x00\x95\x1e\x0f\xc8\x94\x14z\xaa\x1d&gt;\x8aY\xd6h\x987\xdd\x0fs\x83B\x85@\xbe&lt;`\xe6\xd3pA[\x9a`\xcb\x17\xd2\x08\x06I\xcdw\xe0\xc00\xc8*\xe7\xbez\xce:\xdd\x024\x96@\x974\xe2[\xc2\xab\xd3\xfb\x81\r\x93\t9\xfaE\x9f\xe0#,\x893\xc7!\x14\xb0\xd5hY\x98\xf8\xefh\xd9\xb6\xe1\x11\x92g\xca\x143\xaf\xdb\xfe&amp;Z\x00\x1d\xef\x81\rlH\xeb\xb4\x1bx\xf1\xb8\x03\x00A(hnx\x1d\xa91\xd3\x9b\xdd\xd3\xac4b\xac\xfd@6\x8b9\xfc1\xee&gt;^\t\xc3\x90\xcf\x1a\x98:X\xde\x10=\xde\xb2\t5L\xc2\x1a\xd2m\xc7\xa5\x91\xd7\x8b`p\xdd\x7f\x17\xf2\x8c\x9cA\xbf0\xa1\x8f\xe8\xc1\xa6\'"P\xeeg\xe3\xb8$\xa3\xb8\x8foT\x0eP\xfb\xf9 \xca\xc5\x9d:\xdf\xb0"\x8f\x08\\,jo\xa12\xea\x145\x84\xeb\x8b\xa9\xd5\xc7\x1b\x99f\x99F\xf8\xbe\xa1\x01\xc2l\x0b\xad)\xf0S\xdc\r\xfc\x9d\x8b\xdfaF\x1er4R\xf1\xa7\xab\xf7\xfa0f\x8e\x84\xbc\xba(\xed&gt;\xda\xba;\xd8#\xfe\xee\x0c\xad\xefT\xc4\'\x19B\xc1\xf4\x969\xc4\xe2\x00-\xbe\x8b\xf3\xe1\xb0\xd1\x93n\xfb\x94\x1e\x01N\x1c\x0c6\xcc\xc7\x8a\x9e8\'3j+\xe5\x02h\xbd\x14\xd2\x18\xc9\x99\xd8\x96\x98\x99\x84/\xc4\x12\xb67\xffrS\x98\xf2}\xa2G\xb6g\xf2U\xb5z\xcd\x96r7"\xbf\xa3\x8c\xb2j\xd9\t\xb6\x08e\xca\xd9\x1d\xd3\xc3\xcd\xfd\xb6Y\x80\x0e\xe0\xdaQE\x0eM\xa0\x81\x14\xeb\xd5\xdeo%\x9c\xef\x80A\xf5\x02\x8fX\xb23\x04\x8c\xb0\xf3\x977\xc7\xf2\x90N\xc3\xfd\x89\xcc\xcf\x83(\t\x82m\xf5\x14O\xaf\x02\xb3\xf4F\xc2\xc9f\x9c;\xcb\xdc\x18\x13\xba1\xad\x132\x98M!\x1a\xb2#\x06*C\x10\xf9o\x0f\x8d#\x88?\xd7\xcb%\xac\x9agu\xa5\xa5\xe3x\x01\x17\xf5\xc3\x1c\xc49\x07\tSf\x19t!\xba\xbf\x1f\x9aC\x92\x93O\xb5K\xe7\xa3\xbd.\x92l\xe2\xaa\xf3\xd9\xab\xaaEB\xde=\xa4nD\xc8\xb7\xcf\x97\xa9O\x06\xd7`G\x90\xfe\x92_.\x1cg\xd3!\xdf\x00\xcf=\x98Z\xb4)\xca\x8dPv\x98n\x9b=\x1f"\x14\xd95\xde\xf0\x16\xd6\x19\x17$|\xfb\x11\xe3\xd4\xb8\xb5\xdb\xdb\xc6\xda\xbd\xe6\x89Do\xaeJ\xe3D\xc4\x9a\x95\xc78\xec\xaf\x96\xe0\xed2\xf1nP\xa3\xaaO\xd3\x883\xd1\xfe._&amp;\xbe\xc3\xfer\x89w\x12\xf9w3\xf0\xe4\xa8&lt;\x85\xcbQ!T\xb9\xca1\x9f\xc2\xb7\x89\x91\x18Z\xca8\xfb\x8c\xf1~\xe3\xb8\x05\xa2\xe5\xfc\xfd\xa64v`\xdc\x8f\xa0\xef\n\x8d\xde\xc3\x94\xf5\xb9\xb1\x80\x1a\x87\x84"K\xbab\xb4I\x18\xea\x9eo\x8c\xb1\x9d\xad\x84\x15\xe2\x1b\x8c\xc4M\x8e\x9b\xbcwg\xa2-\x08Z\xf6%\xa4b\xf2P$g\x84^\xddW]b\xcc\x14%V\x80!VUN\t\xdd\xcb\xa4\xccH\xd4T2:\x8f\x8c\x8f!\xe9D,\x1b\xaf%\x8a\x8b\xd7T\xf9*\xfb\xf13`\xe0\x1b\xd3\x87\xf8\x15Q9&amp; \xdbc\x1e\xad\x1c\xf8\x1a\xbf9\x9f\xcai\xa4\xe5\x17\xfe^\x93N\xfb^\xa3\x8f\xe9\xef\x01\x8a\\\x16\x12\xaad\xffW\x18\x1c\xc0M\xfdY\xb2m#\xce\xb8\xc0r&amp;\x0f\xbc\xf1\x99\x9a\x81\xd7\xe8\xf5AQ\xef\xb4(H\xa4\x95C\xd8\x8c\xea\xcf\xbbU,zb\x15\x85\xc3\xd9\x0f\x1c\xe4\xd8a\xd1\x1a\xe3h\x91\x82\x0eS\xf7nU0\xb1i`F5,\xb0N1J\xc50 \xddk\xcaf\xa8\xd3\x83Z\xf3@&gt;\xf0S\xa2VLi#\xde\xf3~\x08\x98\x02\x0bL\xe1\xe2u\xe8Z\x06\x16sH\xf7\x0b\x1d\x05\xd5\x1a\'\x9a\xbb\xed\x989o\x8e\x1c\x0c\xdc\x82\x12+\x92B\x83\x1d\xa2y\xb7\xda.\xff{D\x98\x80ca^\\0\xd8)H,y\x1d\xfax\xed\x8d\x01\x9f{o\xd4\x902\x13r6\x88s\xd3\x85\x03\x98\x96\xac\xa6;\x9c\x8e\x07\xe8n\xff\xca\xad\xb6\xad\x0bb\xf1)\x03\x0b;\xa6\x1bK\xec!\xa2V\xd7\x0f%!\xc1\xcac\xd9\x03\xe8\x18\x16&gt;\xa4\xe5\x851\xd4\xba3f?`\xed\xc2\xab\xe9\xb6\xc7\xb6\xae\x04\x0ez\xca\xd58\x9du\xbc\x98\xb5\xb2\xb7\x92x?\x0b:\xa8\x91l\xb8Q\xaa\xa6\x9a\xacn;X\x87\x9b\xf6\xc3\x1b\xc85\xb7\xcb\x8c\xa6\xd9y\xfbw\xf61X\xddi\x0b%\xa9G/wC\x08\xa4\x86\x88\xaa!\x03\xb5%|\xcb\x13\xdc\x8f7\x9cs@K\x00\x05\xef\xf2\xfb-\xcf\x89\xc8q\xad\x0e\xd9\x1f\x83\xc7\xf5\xa25F\x03Y\xe2\xac\xd6\x84eS\xa7\x99\xd7t\x93\'\xbd\x97K/O-Zy\n\xf8\x170@\xd6(\x00\x18\xe3\xbe[\xe8X7F\xc7\xfd\x8b\xda\xce\xc1\xabRp\xb9L\xcd\xc4\xf4\x1bk\x15\x0fp\xfb\xf9\xe5J\xdb3\xbcJ\xc6B\xd8M\xcc\x9c\xb5\'\x04\xf3\x8doI&gt;\xab\x88\\L\x1e\xb8\x8e\x7f\x0f\x19\x91\xce\x0e\x97\x10\xae\xef\xfd\xdfe\xe3:\x90\x8b\x81\xe8F\xd05\xbd\xbc\x06\xdb\xab\x90\xfbU3\xb4B\xe1\x9e\xb1\xa2\xa1\x83\xb0y\xa3\xb8\xc9\xfb\x0c\x14\x05F\x96\x8a\x00c\xbfE\x92`S\xb1GD\xec\x1e\xf1\x9f\x93w\x82h S\xcc\x13\xb5qG\xff\x1ec\xd1[E.\x07\x9aF\xff\xc1\x05\xdb\xdao-\xa7\x95\x08\x94\x16\xbf:j\x98~\x1e\xed\x90\x1fx\xcb=m\x89\xf9\x11@\xdb\x1a8`\xb3?+|\x03\xdd\x1a\x91sq\x11\x9e\x8e\rW\xd4qY@\xd4\t[*\x98\x87\xd3-*\xd33\xd7K\x97\xb9\x97\xf2Dw\xc1V.\xda\xaafL4\xab\xc7\x00(\xa1`S\x94!\xf1A\xcc\x0c31\xcd\xe7\xca\xd4\x89\xa3\x8d\xed\xe8Ob\xe6\xa1\x81\xbcO\x7f\x92\xcb\xb0\x92t\x9fH\xd2\xad\xfb\x8aV?IF\x85\x14\x8d\xb5f\xb6\xd70\xa3\x86\x81E\xfd\x85\xd60\xef\xfa\xe1\xffx^\xd0\x0b\x9b\xcew\xf6u\xb1!\x0b\xd3\x89\xccM\xc6AH\xe0L\xdb\xcd\x95\xe7f\x1e\xcb\xdc\xe4T\xa7\xec\x108\x1f\xd4\x11\xfa\xcc\x96\xc17c\x89b\xe2s\x07\x07\xdcV\xd6.\x1eo\xe1G\xc7\x14\xd4\xc5n\xb9p\xa5$\x95\'r\x00%\xa2\xf3\xb0\xe4\x89\xc7\x82\xd1\x8f\x16\xe9\x80t\x06ua\xaf\x98\x1c+\xd0\x18\xcd\x16\x0b4\xa5\xac\x91\xb8\x7f\x14\xed\x8b\xa9\xbex\x7fx\xe7\xc5SN#\xb0\x1a\x82\xeb\xd9#\xfcHf\x06=\xbb\xc6\xfb\x92\xd68/y\xf1a\x8cC\xafP\xef\xc2\x87\x16\xbcw\xbfy\xc4fs\xfdAs\x18\xb2\xc9\xf7X\x13\'J\xdb7q\xab\x11\xfb\x0b\x15\x95W\x1f\xde\xdf\xde\xe0V\xcd\xd0\x198jk\\\xcb\xf6Kl\x8fCS\x8dJ\xc0s]\xe6\xfb_\x83\xaa\x1e\x02\xf3\xfbc\x01\x17\x95`\xa9\xa5u\x11S\xdd\x9c\x9e\xa8\xee4n\xb4\xf9@\xcf\xf3etLcB/\x1aD\xa6\x0eg}\x9bR\x1f\x8a\xe9~\t\xc4\x92V\x9e\x9c\xad"J\xa0\x93\xb1*62_\xaa\xa2\xd2 o4\x00v\xf9\xa9\x16\x80\xcbQ(\xf2\xc8\x89\x15\xeb\xf9?\x07\x0e \x97{\xa5\xd1i\xca\xc7\xecm\xfb\x81\x1d\xa6]\xc1\x15WE9\xfeI\xbd\x86\xd4\xe3Ppi\x8b{\x9aw&lt;1S\x93f\x83t!~\x14\x02\xcc}\xad\xd1o|\x86nQ\x1c\x19\xde\xa8\x91\x80\xd2\xc2\xc1$g\xc2\xb7\x98W,\x93\x1f\xb4N\xa5\x86\xe9\x9e%\x81\xd2\x13n\x8c\xef\xd3C~\x1f\xff\xc2\x9ek\x84\x1a\xc1\x82\xac\xed\x9by[\xd7\x85,&gt;\xb9\xab\xe0\x17Y\x91\xdf=y~\xe3\x98Z\xf5\xa2M\xa4\xee\xd2\x0e\xf9\xf7r\xffg\x0c\xb3\xb1\xfa\x00\x1bm\xcf\xe6\x87\xa2m\x1d\x0c\xe9+\xc05@\xc4\x87\xea\xe1\xdfG\xdb\xf9tf)K\x88\xef?\xdd-\r\xbf/\xbe\x01wfP&lt;\xfa\xce\x1e\xf0+\xac\xa3\x81\xfb\xae\x8d\xff\x0f\xf0\x9fS\x1c\x92\xfb6\x98\x11\\\xc3\xd3t{\xaa\xd9\x00\x85\x8a\xac\xd1\x95\x1c\xa5v\xf7\x84t\x1b\xe5\xfeI3\xc8\xe8W\x17\xefva\xca\xf8z\xf3\xd6\xdf7\xac\x85\x0f\xa0us\xff\xf3\xb8v\x92\xf21\xa9/\xe1\x7f,\x1d\xfer\x86\x81\xbc\xd2Fi\xd0\xd9t\x8a\xbe\x82\x82:\x14\x88\xf1\'\x1dKL\x946\x81\xd3_\xe9\xe4\x95X#\xff\x94\xa0\xc5\x9eU((P\x1f\x01P\x93\x1b\x16\xdb\xa0\xd5\x1e\xbdJD\xc7\xf6\x85|\xa0dy\xc2KY\x1f\x98\xb7\x00l\xc4\xaeP\'g\x9e\xef\x8b9\xb2\xfc;\x7f\xfeL\xd9\xccV\xab\xa7\x9aN\xdb\x02\x867M\xdf@\xf5g\x98\x87\xce\x1c\xfd\xd29&lt;\xa2\x9d13X\xe2#\x7f=\xa7np@}G\x9e\xed\x90\x10\xad\xeb\xaeU%\xb1\x00\x8a\xb2\x8a\x90\x9f\xd7\'\x9b;\x92\xf3Bmq\xe7"[=\x8a\x84\xc3\xce}\xea\xc0\x00Y%\x0cm\xb6\x16\xc2@\xc3\xea\x8fz:\xd3\xce7A\\\x83+\xa8\xc1\xbb\xf8\xf2\xfay\x89l\x08nKH7\xddB\xe9\xe1\xc3\x8b\xdf\xf4\xaaY}\r\x91B\x18\xa1\x9e\xa8qG\x94\x93P\xdc5\xa9\x91\xb2E"\xb1\x8b\x9a\xe4\xcc\xaf7B\x1dL\xbc\x9c\x97c \xfc_\xb4\x01\xa3\x1cc\x1d\xbb&lt;\xfb\xc5\xe0\r\xc5\xa01ou\xd8w\xd3\xd9\xfd\xbb\xfa\x03\xb3\xaeW\x11\xfbR\xb8\x1e\x92]\'-\x93\xef$\xe0\x08\xd9h:&amp;\xa7\xa9\x05:}&gt;\t\xe3n\xcd\x8f\x91\xa2\xc0K\xe5\xb0H\xf7a\xa2f\x8bM~\xdeu\x91k\x8cZ\xb7ffJCV\x00\xfa\xe3\xeff|A\xdbxv\xa2\x17\x1ec\xc5/\x8c\xe1&gt;ME\xb3\xd1_:\xbd\xfa\xb6\xb1\xf0\xf0\xf3\x17\xd6\xf6d\xc93\xc6\xff\xdcN7xI\x7f\xa6WE\xb5\xe7.\xa3\x88\xd2\x01\xcb\x11&gt;oL\xc7\x0e-\x9fl}:\xb8\xb4\xdc~\xbf\x1c\x9ec\xb6u\x81\x164\\\xbb\x07P\x85PX\xea\x98\x00k\x92\xc3|4p\x84T\x87\x0ca\x85yl\xfa\x80\xc0\x96o\xacz\xdcG\r\xbc\x02\x93:\xb8\x8e\xe4,}&amp;\\8o\x9a\xfe\x1a\xb0\x01\x17.%p+\x0b\xe8~^\xd7\xdbU\xcd\xe1\xb33\xf8\xbe\xdeDKEu-\xab\xb1\x9b\xd8K\xa7s\xb2\x82\xc3ZU\xd3-:\xf6\x0ec|r\xa9\x85\x91#\xd90\x97Jc\xea1\xfe\x14\x1fx\x98IQ`&lt;\xcd]W\xe5\x07zI\x00HvG\xcc\xf2`I\x947*\xfa\xadAg\xfa\x83\xfb\xf7\xd9\xd7\x03w\xc6\x98\x91\x84\xcf\xac\xc5\x1a%\x13.\'\x05\xc3\xc2\xff\x13\xbb\x1c\x81\xc6\x19\xc1\xe7\xf7\x9d\x88c\xfa\xe0\xeeC\x14\x06\x18\xe3\x90\xaar\xc8F\xe1XmFT\xb4\x9f,\x82\xe2=\x1c\x1e\xdb#\xa4[\xecV\x13\xfa\xeca\x1fn\x94\xaa\xa7\xf3}v\xe4&amp;\xf0\xaa\x90\xe8\x84\x85\xfc["%\x0fyFeO;\xd2?\xed=@\x8d\xbeq:\x1fw\xf6\xa7zXG\x17+\xe0}\x167C\x9a\x83%\x89_G3\xd9\xf5\\\xb5!e_\xd8^^\x8bU4e\xe3\xf7 \xf8\x94O\x8bx\xd0v\xba\x8b4\xd4\x8e\xf2X"\xc7Y\xb4\x18\xa7\x85\xa90\x95\x941\xeaPzT\xa9\t\xf4x\xe8N \r\xe3\x05\xb7\xc8\xf2\xb9\xdf\xff\xcb\xba\'L\xd4q,!!n\xad]\xd6\xa1\x92\x84C,\xec\x0e\xd0\x83\x87\xb0\xa3^_\xe17:\xb9\xd3\x94\xf4F\xf8\xc4\xd4\xb7\xbak\x8a\xbc\xab*\\\x8d\xf2\x80\xe5&gt;\xa0\xed\x1bU\xce\x18\xaa\xab\x9bg\xb2\xf2\x8c\x90=&lt;-\xf5\xe8\xd8\x06"Q\x16\xf5\xf4i\x18Fc\x19&amp;W\xb7\xf2)p\xce\xb1\xcc8\xf2\x86\x90\x83\t\xfe\xa2i\xf0\xf6\x96\xce\x1fv\xdf\xde\xa6\xd15j\xb8\xbdT\t&gt;#\xa7\x12\x95\xc8\xb9rR\xbf\xcfg\xa0`\xccQ\xbe\xec\x1d\xc8\x89\xeb\xb3\x8aC\xf0tr\xebV\x07\xaf\x93\xab=\x08\xb5J~\xb9\xde\x19\x13\x81B~\x01K\x0e#\x15\xd9\xf9l~\x9a\x19|T,\xa8emk\xdd\x9e`\xdf\x12|\xcb7\xb7\xd4\x1cD\x1cP\xb7\x00\xbe\xb1\\ \x08.8\xf9\x93\xc6\xb0j\x01W\xbf\xc7\xe0@\xe1\n:\xcf(Ozi\xcb\xd8\xfazZ%\xca\x13\xce\x17\xe5\x9c\xed\xfb/?\x87\xcf\x89)zn\x91c\xd4\x04\xdb\xfe\xae7\x9d\x0cXH\x91\xcc\x8c\x86\xb7\x87\x14|\x06w\xe51\xd7-}!\xb37e@\xae\x03#\xfff\xf0\xff[\x99\t\xd3\x83\xd0\x84S7\x86\x16\xf8\xc99\x11L\xa8\xfc\x85\x99\xa8\xf10d\x1d\xf8\xdbseF\x1d_\x88\x04tF\xe8\xfb\xaci\x9aH\x84\xa7\xe8\x88u)3\xcf\xf8\x0e \xe8[\xc5\nH\xc1\xf3\x1fL8#\xf6lQXl\xee\xdd\x91\xedf\xf6\x9e\x13HG\xbatn\xc6\xf7\xc8?\x9a\x98Y\\\xbf\xd0/\x9f\xff\x8a\x95\xb5\xf6E\x10\x16[\xa8\xe3\xf8\xffi\xa9U\x03\xd9J:\x02\xfc\x87-y\xbcO\x12\xbe\x94\'\x0f\xf7\xed\x858\xec\x8e\xa3\xbd\xe7\xfb\x1a\x80\xe0Ro\xc3f\xf9\x9aK\xd4\x9c\x8a\x06\xd2\x05\xc4\xb5\x80\xc2#OM\xe0\xaf\xe8\x8f\xb7\xe2|?"\xb1\xe6\x87\xe1U\xea\x87h\xaa\x93W\xd3\x8a(wc\xe3=\xac\x08\xac\xbeg,\x88`\xc9\xd8\xa2\xcd\x8f4\xc9+4qk\x83-\xa2Ev\xc5}D*\x00\x9e\xf4\xc3\xf6\xab\x86G\xbfIB0\xd71\x95T*\x1e4\xdf\xd7\xf0\xc9\xbc\x1b@\xeaG\x7f\x05\xa8&amp;G&gt;\x05p\x95\x049j\xe4\x14 \x07B\xf6@\xa8\xfe\x9d\xf8&gt;\xab+6\xac\xfc\t\xc8S3\x8a\x97l\x9f\x11\xf8\xcf\x04J\x0bg\xe7K\x8c\xbe\xc4\xa7r\xf7E\xdc\x84\x89T\xea\x12\xe1\xf2\xf76r\x94\x85\x9a\xa7\xa0\xf4 }\x13\xddQq\xa1{v\x98\xf1\xd9\x02ny\xab)C\xca\x16r\xf4_\x94\xa7\x021=\xa10\x0f-v\xc5,\x80\xb7@gH\xd6\xcf\xe7"\xce\x19\xe1\x18\x92\x8fCG\xae\xb0c\xd7l\xbf)r@\xc4\xa69\x13\xca]\xbe\xeb@\x9c\x12P\xe0Q\xd9\xe7\xfc\xa8"\xb0\x9d\xb2\xfbu\n\x13j\x9d\xbbnX;\xfePw\x8e\xc9\xc0~\xe0\xe2\xb6\xa2]\x182+\x02\n\x93Al(9\x82\xaf\x1aa,\xaff\x15U\x10\xb1\xfc\xa3\n\xa3~\xec\x9c\xd2P\xa8\x12\x8f\x80\x04\xb2\x8d\xffK\x1e\xf4X^\xccz;\x13\xf2\x04I\\\xac\xdfH\x98\xd5\xb9\xd1\x19\x01|\xda\x82\xcc\xfbFV$\x1e+H\xf0V\x15\xbd\xa8LK\xacj\xbd\xe2\xc2W\x04\xb9\x8e\x84Q\xf1\x8fx~L\n\xbcJ\x13\xd5\xc32\x97@\x97*\x81\xda\x16\x93\xebH!\xdf.\xbc\x7fi\xbb\x05\x90\x95W\xc1\xfb\xc9]\xcfJ3\xba7\x05nV!H\x84PI\xa7Ywl\xdf\xfei\x041\x95s\xc6\xb646\xce\x1b\x86\xfc\xcf\xc8(\x88(\x97\x81*\x16o\x98V\x1f%i\xb3L\x80\xd7\xe1\xe8I\xed\xea\x83x\x80\xb7\x9a\xddze!\x06\xc9\xd8\xaa#\xc7\xf6\x02\xa8\xac\xa7\xbe\x03\xd2\xf7}(\xf8s\xa3h\xf4\xff\x87\x03D~lK\x7f\x9b*\xcf\xb2\x1c\xe7\x97\tZ\xe5\x96\xbb\xb7\xf1B-\xe3\x81Jg \xdc\x819M\x8d\xe4\x1d\xa2\xe7\x7f\x916\x17\xb1\xc8\'z\xc9\xf4\xcb6\x9f-h\xb1\xbc."f5\xf6P\x824\xa7\xe2\xa2\xcd\xe7\x10\x9b\xfej\x8b\x8a\x86BP &lt;\xe1F7\xe1G\x15\x80\x91\xb6\x96\x89^h\xc6]E]\xd5\xbc\xc2b@\x1d\xcd\xdf]\xdb4\x81\x90\xd4}\xfd\x0fC\xe2,\xaf]+\xc4\xbf\xea\xe6\xd4r\x8a\x91\xc93\xa3h\x8e\'\x98\x1a\x18l\x81\n~\x98\xb0}\xb9\x06\xb1L\x8fN&amp;\xc8\xcc\xa2pw\xe9\x87E\x02\xe6\xdb\x19J\xc4\xa5\x94&amp;\x1b\xfc\x99\xeb\x0c\xc2r\xf4\xfb\xa07\x99\xac\x85\xc8]y\xdb\x90&gt;\x9c\xe8\xa5\x1c\xb8:,\xd0\x0f\x1f\x08\x9dY\xa3:M\xa77\xc1\xcf{\x94/\x19\xc5!\x97\x13zI\x84x!1\x12i\x14}\x93\xed\xe2\x1e$\x94\xb0\x01\x16S\nn\xf0\x937\xcb\x83\xfc\xbat`\xcf\xcc\xf4\xf2cD\xa1d\x17\x92\xed\xc1\xcd\x9b\xa3\xa7HS\xfa\xbb\xb3I\x90d=\xd9\x01\xed\x04Q\xa3\xbfTD\xfa\xea\xe63k\x0f\xc5\x9a\xa1\xae($-E\xb4VuMO\xa4|\xf8^xn\x9bm?\xb2\x99\xd0\x9e\x8d00\xb7!B\xe3\x8f\x84Jy\xfb\x9eC\xedi\x08\x9d\xc6\xec\xedD5\x1a\xb8)0\x03q\x93"\xed\x95i\xdf\x9f\xf4`\xcd\x0f\x92K\xec\xa7\x9b\xf2\xc3p\xde\xbc\xb1\xec\xf6\x9dNqH\x90\xced\x00\x0b\xf4e\x9dk&gt;\x06$\x9d\xbc=\x19{\xa9!)\x11\x19Y\x99\xd6W\xe4\x87\xb1\xe8N\x11\x8a\xff\xc8e\x81\xb8$\x14\xe5\xfd\x9d@\x89$\xc3Y3\xa8\xa2G\xbe\xa6a\'\xebv\xda\'\x9c\x05\xf0C\x04/\x95\x13U\xb9\xd1Q\xc8b\xb9\xb6\xf36\xdbOv\x87s\xc7\xf2\x8cL_\xd3\xcb\x9c\x81u\xed\xda\xcb]\xca\x03\xddhf\xe0t\xbd\xe3\xed\xfeji#\xeb\xe3\xaf\xe4\xdc\xf3\x04)\x07\xde\xd9\xa0\xb0\xdc\xc3n\xbdNr\xd1\xa3/\xb0\x8c\x14\x1c\xd7\x9f\xa9C]\xee\xc8k\xca\x1b\x8dl8\x0f2R\xc4\xa7!\xa1\xf2\xb1\x7fo\xe1\xbe\n\x94\xda\xa38\x1d\xc3\xfa;o\x1b\x16d\xcbx\xab\x99\x0cOL\xed\xe6\xd1Ur8\xa1\xa9_I1\x1dob\xd0V\x87\xd0\x9a\xccy\xee\x93$)\x0f[sz\x1f\xdb@(\xf1&gt;\xbe\x11\xbd(\xc6~\x16xm\xc0\x14\x15\xfe\xaf\xb6\x08\x7fSX\xb4\xbc\x86\xdc\rg\x82\x17\xff:n\xbf\xe0+0q\\\xba$#&gt;\xe3\xc9\xf6\xd3XhTu\xfd\x83\x1f\x16W\x8f\x19\x9c\xd0c\xa8\xf2`\x03\xe7\xd2b\xdbO\xd5W\x9d\xed\x9e\x0f\xe3\xc7\xb1E\xe8m\xbe\x90\xba\xf1 C\xbd\xe6\xf4\xe8\x01\xe3C\xe1\t\xeaHqG\x0c\xc0}\xc0\x89\x0f\x96\xb5&amp;KBM\x19\xea*\xb7\xc4\xc1\x1b\x1f\x94\x01\xd8[\x96\'\xf5\x9b|\x13\x98\x8d\x91\xb0\xbb\x8d\xb9\xb8\x00\xa1\xff\xfe\x90\x87\xba\x97M^\xb9\xb32\x9b\xf6\xcco\xdd\x14\x84\xab\x80.\xac\xfeiq1l\x95%\x01\x1f\x17\xe7\xaa\xb6\x8a\xda\x90#\xca-`\x10\xa8\xbf\xda\xc7b\x95#"\x88\xc2G&gt;\xaag\x14${\xacW\xb5\xca\xe5\xf5\x9flA\x16\xe1\xfc\x8b\x17\xa5C\xce\x0fff\xd9F\x7f\xd2Ej3\x0cjd\xd8\xf6w/\x86\xf5\x94X=\xff7[g\nS\xc1w\xe0\x19&amp;%wV\x0f\x18\x1e`O\xc9\'\xae\xf9\x87m\xeb\xe3\x9f\xc5O\'\xa9\xa9hr\x92\xe7$\xbd\xeeP\xa1\x9d\xa7\x1d\xf4\x1c:\x1d\xa9\xf0\x93\xa9\xdfz\xe4\x89\xa7WR\x1b\xf9\x87LJ\xa6\x0b\xf5=\xfb\x04\xbc\xa5){Jg\xd8I\x12\xa5\x9f\xddM\xe0\x8fz \xfe*\x1f\xed\\u4\x82{pzK\xd42(\xce\x80~\x9e\x86r\x02\x91a\x9b\x831\x08\xb1\xfd\xc0\xeaS\x1046\x9f0)\xfbzB6\xc4\x8e\x18La&amp;C\xb9\xe1\'#\xcfA0\x19\xbajA\xf9\xcf\x1d\xden[\xaf\x9c\xcfa\xea\xf6\nu\x0e\x83\t+\x1cCk\x06\x11\x05\xc133\x84\x9bF\xa7,\xd3\xc3\xd8P\xec\x1fw\x17\xf3\x1f9?\xe4\x00\xf6\xfc+q\xdd\xf7\xec\x03Q\x93\xea&amp;\xa9\xcf\x87MJ\x9b\x86\x05\xad\x83\xc0d\xfa\xdc\xd5daV\xac\xa7\xa0\xac7g\xed7,\xe0\xfc\x96\xf4&gt;7_8\xb2\xbfL\xc1Ep\x800\x00\xab\xab\xf8\xc4\x02\xee\xe1\xb9\xb8\xc4\xb3\xfd\x843\xea\x86\x9b8\xf5\xa4*\xc3\x8f\x98\xf8\x93N\xd1$0\x94\xb7\xf8\xc0\x90\x044e\xdb!o\x13sR\xf0\xbd\xce\x88\x12\xe48\x81\xc0\xfa\xbcL\x954\xbf\xcaM\x0c\xabf\xb9\xf2\\\x13\xda\xc3\xc5\x1c\x02\xc4\xe23\x03\x9b&lt;5\xf2J\xdd\xfd1b\x08\xa9\x80w/\xe6X\x91\x06/L\x08_V\rj%\xf5\xec\xd0\xa1$\x85c\xe2\xf9\xf65-4\'\x02\x04&amp;\xfd\xa1\xfc\x10-Z\xfeC\xe7.\xce\xbf\xc8\xfa\x7f\xdacYc\x8eh**1#\xa2\x08\xc3g7\x8e\x88\xb1\xe0\xfd\xbf\xc0\xf3\x94\x01\xcd\x93\x8a\x04\x8f\xc5?\xe7\xa6\x1cB\xc8\xe2\xcd9\x8f\\l\xb9%\'fz\xbf\x01\xef\xd4\xc0w\x80\xbf\xc2 +N\x89\x8c$`\xe7\xe3\'H\xce\x93%\x8fz\xf4\xc1\'\x04\x07P\xf8\xfb\nO*\x1a\xcd\xbc\xb4=\xee\xa0\x19.\xe12\x8cw\x80\xc8\xed\x87\xf6_\xa7*\x90@\xbf;\x02\xbe\x96j\xc5\x8c\xd4IiY;Ad\xaa\xfb\xc3\xf4\x1d\x05\xa4\xfeN\xfdI\xf6\xad\x9a&lt;\xf47}\t"\xd9\x9c@\x89\xe8\xc4t\xa5\xfaV\x10\xa6\x0f\x16\xa5\x0e\xacb\xfd0\xd4\xd1\x90\xfe\x96\xdc,\x88^Q\xc5Z\xb0G\xf6&gt;\xb9F\xcf\xa6\xd0\xa5&lt;\xe1\xf0n\xd1\xeb\xa2\x88\xd6\x9a\xe1\x1d\xbbZ\xa2UR\xfe,\x1e\xacT\x1a\x04\xd8\xd6\xfaB3\xaa/\x18%\x00\x91\x06\x86\xfb\xa9`\xb9\xd44\x1f\x0e\xca\r\xb4\xb8c\r\x04\xa3\xbc\xd2Y\x9d \xe8\xf6\x03{\xc7\xf47\x1e\x91m{\x16]\xa10\xe9\x1f\x99\x03\xfa\x06\x1f\x1e\x97+\x00%(\x93bqio@@iy\x90\x10\xab\x14\xbc\x88\x8b\xe4k\xdc\x0cPDX\xb1\xca\xaa\x80\xf6\xd71d\xa7\x0b\x91C\xe3\xee\x02\x14 \x8e\xd9!\xee\x86\t\x911\xfc\x9d\xe32\x93i\n\x06b\xd4\xad\x18\xcd\xfe\xfa\x0e+\xaa\x89\xe3\xc8\x85$\xd588\x8c\xd7\x99l\x11\x89\x9a\xb4\xeb\xc5\xa7\x12\x9a1x\x8dt\xa0)4L\xdff?\x08\x0b\xa9e\x10(\xf0\x10\xc2\xde@`ve\x19\x94\'\xbe\x18\xfd\x872\xf4_\x89l\xc1t{\xb0T\xea\x9a%\x9c\xcf\xb8\x87\xb7|\x9b\xf8\xa0\x13\xf5oV\x9ca\x97H\xb4\x84\xf9\x03\xa63\xdd\x04\x1f\x18\x12=U\xcfL\x9f,R\x0e\xbe\x07\x8f\x16&lt;)\x82\xe5M\xc4v\xdf\x82\xeex/.\xf2\xc3\xd9\r\xe1\xa1n\x0b\x9c\x0f\x86\xb4/=%+\xe2z\x99\xec\xd3\xe2\xf0T\xc0E\xe3\xc8\x7fxu\x1f\xd0\x8b\x02\x90b\xc2M\xd3\xe7L\xab\xf1\x01\x0f~\xc8%`;\xfb\xf5\xf2\xae\x00^6\x8b\x9aGV?\xef&amp;=\x0cc\xcb\xf9\xfc5^\xd3\xd0\xe4p\xae\xe7mu\xbd\xefr\x10\x93\x07nM)\x8eT\x122=\x15J\xf2\x18%\xe0\x80\x89Q9U\x8aW\xfd\x9e,~FK#F.\xfd\xe4\xdd\x0bB\x18\x0e\xb6b\xcb\x99se\xb3\\`[ZG|\x10\x89\x97%\x93\xcf\x84\xac\x89\xcb\xe0\xd2*\xb0\xa8=\xb8&gt;W\xfd\x85\x87^\xff\x1f\x15\xda\xc8\xe9\xcf\xb4\x8d\xe5\x10\xa7\xb1\xc27\x94x\x16\x8d\xc8\x9eL\x97\x86nWB\xdecY\x0f\x84\x8b\xe2\x0b\x165\xb4D\xf8\xd2\x81\xaa?W\xe1\xa6\x82@g\xe3\xda\x1e\xd2&lt;\xafn\xe4S\xce\xe6\xb4}L\x88\xe7\xa0\x19\x9d]?Fh\r9v,\x16\x8e\xd1\\\x80O\x86w\xb5t\x10\xef\xe4\xb6FyPB\x1c\x8a\xc9\xd4\xc2\x12\x83?\x99\x1fW\xe9\x07\xe6\xd5\xe8B\xb6#\xec\xb95\xdf\xe2\xa3\xac:k#h\x7f\xa7?\xd2\xd5\xdfa\xd5\xb4\xf1\xb7x0}2\x19\xaa\xac\x19\x1a\x00D\rc\x8b\xab\xc3\xfb]\xeb\xf1\x8b\xd1\xccG\xa5\xc4\x17\xba5\x1f\xdc@\xb4\nR\n(\xae\xca\xc7j\x95q\x10pG\xecE7/\xd9\xc0u\xdc\x01}]\xcc\xee\x7f\xddc|\xb1\x9b\xe8\x15\xa4_\x0e\xab\xeb\xed.\x0b\xe9\xf9J\xab\xe4r\xb8\xb4\x82\x88\xb6\x01\xd5\xb7s\xa2K{\x08\xf1\xdfY0\xaa\xd5\x02\x97\x81\xa9r\xe4\x81}/\x1ex\x80\xf4\xb9\xacUC \xdd\xb6\xdct\xcf\xf1R\xa2\xcf&lt;\xd1\x03\xfc\xaa\xcd\xbf\xc9\x15\xef\xf0\xa0\xea\xa9\x05\x17\xe5BA\x0fxS\x06\xb7\x8fy\xed\xf9\xa3\xf2\xd0\xaaFm&gt;!\xdd\x9f\xea\x99\xccr`)\xf3\xdaS;\x81\xe6hdeL\xe2\xb1\x05\xa7\xcah+\x82\x84\xd4\x1e\x9e\nA\xb3.\x15 \xf8\xdbP\x829\x92\x17$\x04\xfa\xb4\x17J\x8cK\x92!\xaes\xcd\xfdkk\rCN\xff\x89`\xa6\xa5\x9b\x9e\xdd\xbb\x1e\x92\x95\xbd1\xeer\xbf\xb8\xabo*b:\xa7%L*|\xb7\x85\x00S;\x03\xf4oe\xc00\x87\x92\xbe\xbat0U~0\xd1\xd8}\x89\xf3\xaf\x15L\xbcj^\xa0\x17\xdcV\x13X\xcc\xcd\xe6\xddu\xffo+(\xe4\x9e[\xbdJ\x1ax\xb21x$\xf9QQ\x16sv\xfd\xf6\xfa\xc9\xad\x9b\xdd\xe9\x13\\e\x03\xb7\xbb\x81\xc3\xfb\xc3\xdb\x19fF\x88\x124\xe1\xab\xb7\x06\x9b\xfd\xaf\xd0\xd3&amp;\xc3\x85\x99i\x1fC\xc8\xc0\x0e,\xda\xe7+l|A\xf7\xe7&amp;\xf1\x1c\xf9r\x87\x9dv\xc0R\xe1\xdc\x8b)\x8d\x018\xfa\xf9k\xb1t\xa3\x1f\x83\xf8\xfal\xa1\xe6/\xa8G\xc1\xff\r,\xd9\xec)\x86K\x7fn\xcee\xc2\x11\x89S^#\x08+\xa24\\?\xb9\xfc\xc9\xe9O\x9e\x7f\xda\rU\n\xfe\xbfZi\xa3\xeap\x9c\xfa1h\xce\xd6)\xd5\xc1T_"\xc5\xf1\x198#w\x01\xb9s[\xd8|\xef\xcc\xcb{UZ@\xb1\xf2\xaa\xdc\xe5\xe4\'\x88\xcb\x18I\x18\xedy\xe2(\xd5\xb0\x14\xefCf0z\xfcQ\xf4M\x80s\nmk\xe7\xb5Pxx\xb72\x85\x97j^\xdb\x0e3\x84E\xc7W\xf9Ph\xa0X^\xdd\x0f\x89\xb7T\x05\xcc\xc9&gt;u\xd4\xe0\xf4\xc5\xaf\x01\t\x81\xff*P\x02&lt;\xce\xd7\xfcV\x18\xb7\'\xcc\xbb\x1a\xc0HB\xe0_7\t\xc9\xe4\xe3\x14\x92\xa0-&gt;\x1c\xaa\x8f\xeet\xe29\xcf,\xb7\xa9Y\x98.\xd2MT\xd4%KI\x01c\xd7C\xe3C\xbaU\x86\xa3=z\x80\x17\x803\xc0}\xcc\x9aj\xf6\x93K\xf8\xf1\xcf\xc2\xf9\x98\xc4t\x8e\x06\'b%\x11\x1fg\xdaenQ\x0c7\x0b\r\x19\xc9x\xef2g\xc8\xf4\xe0~:\x8c\x9a\xa1\x94P\xfb\xd0\x06\\\x9c/%\xfaHi\x0e[{\x06\x14\xd4\x9c$\x13\x87\xad\xc3\xc5\x86\x10_\x93]\x97\x8c\x00\x18\x93$\xe5L\xaf\xae\x85\xb8M\xe1"\xcb\x89\xdf\xa3C\x8d}O\xed\xcb\xd9b\xeet\x01\xce:\xe6?Ae\xa3e\x1d\xf6v:%\xeb\xb1\x93\x99\xcb\xa5E\xf2\x8dGIO5@r)\xd3\xbc\x05\xbb3\x1b\xceu\xfc(&amp;F\x81z\xf0\xd3\xc2q\xae\xcf\x97\x11q\x08\xd65\x89=\x18\xf8:\xee\xa51j\xca`\xbeI\xf0{\xaf\x19/(\xd8Y\xe7%\xab\xafU\xe4=s\xe7\x8e\xb0}\xe8B\x92\xee\x97\xb6L\x8ed\xf5\x82\x9e=1K\xf6Y]\x02\xd4o/a\xf4\x8f\xe9\xb9\x863BE\xc5\xe4\x0e\xc17\\N\xe2\xd0\xe78\xd2Fte\xd6\xa5-Q\xec\xef4\xee\xbaZ7\x95}\x82zKhTj\xab0u\xedL\xaf\x19\xde&lt;P\xee.\xed\xe8V\x1f\xa6\xa1m\xef\xf4gY\x80\x028\xc5\xa0]\xecM\xd3\x17\xc6}\xc8\xaelt\xe5rA\xa0r`J\xe9\x9f\x9b\xacV\xa9\x84\x97\xed\x99\xf2\xe7\x04\x1a\xa7d\x14\x9b\xe0c\xf8\x9f~\xdb\x18z\\{.\x8e\xee\xc0\x1f\xb1\'O\x89\x1a\x05l\x82\x86\xdb\xc1\x935\x02\xdd0{\x11\x84,\xfb2a\x89S\xbc\x92|\x8d\xbak\x16\x89J\x99ua\xa7\x12\xc6\xb7\x00\x02\xf7\xf3\x9e\x8c\x8b],\xab\x0e\x9f\xf7!\xe5O\xbc\xedQ\xa5#\xa1g\xfa\xf7$y\xad\xea&lt;W_\xc3\xc4d\xb1Y\xa8\xa2E\x94\x99\xc8\x8a\x91\xe6B}\xfb\x15\x94\xeb\x14\x8d?\x18i\x9c`\x06\x10\xf8X\x9c0\'F8\xd7\xec\xb8\xd3\xfb\xfe?\x87!\x07\xd0\xbd\xeb]\x1c&gt;Y\x0b\xcb\xe7I\xd3\xb5\xed\x0b\xcd81XX;&amp;B\x10\xa32]\x1e}`th%\xbc\xbd.\xb2\x83L\x89\x87\xd0\xd1\xaf\xbfy\xab\x00\xe2\x99\x8b\xdb\xaf\xa82\x17\xc2\xbd\x19\xeb\x19\x99\xc2\x85c\x87\xbaG\x13TT\xf2\x9b$\x0e\x06\x864$\xf2\xf1\xca\x1fc7\x8cl\x0eI\x8cnS\xbc\x90.\xd0t\xc7\x97C\xf2\x8e\x96\xb1\x07\x04\xa6\x9a\x8c\x1d\x87\x88\xfc\xb0\x93\xbc\xeb\xc2\xab\x90\x14\x13\x02\xb6y\x9bB\xb8\tg\\\xf3n]\xc1\xad\x821\xfc\xf9j\xeb\xec\x87\xcc\xb1\xe7\xefo\xaa\x0b\x8f\x1f\x97\x8d\xc8\x1fbh4\xbf!\x8b\x81q\x82\xbe"B\xa2\x9f\xe4Z\xb7\xc9\xca\x9bi\xcf\xd9\x9b\x824pk\x19+\x9a#\xbc\xa2\xc7f\x8e5a\xddC\n\xe5\xa4M?\xf3\t5l\x84\xe0`/\x9d\x00\xdc\xa3\x0ew\xe5lw\x0e7;IF\x89N\x98OJ82b B\xffo\'\x90w\xec\xe3\xb8\x96\xdc\xd8\xee\xf9g^\x97\xcfe}oA\x0f\xfd`\xc5\x10\xf9xi\x13\xfc@\x14\xd7kj\x1e\x16\xa3\x9a\xf2\xc4\x04w\x989\x05\xbb\xdb\x08CY1\x96+\xbcp\xa5\x0f\x1c\xc3\x03\xd3?\xa9\x18\xe2\xa8~\xadE%\xf1\x054Y\x97\x80\xd5MY\xcd\x98\xcd\xf6\xe6\xe9\x8a\x96\x9a\xf8\xf0\xa8\xd0\x82C\xfb\x16\xbe\r\xb2\xbc\x80\xe5\xaf\x04\x0325\xc2x4R8\xd1\r\xb4a\xda\x10\x1e2\x06\xaf\xea\x02\x96\x024\x036\x96\x17\xf8\xc9\x0b%\x18H\x18v\x9e\x8c\x80r,\xde6,\xddL6\x9as,\xbb`\xbd}\xf0o+\xd1J\x90\xc6`\xd9.{Gi\xc5\xf4\x03\xd5\xb2\xf9W\xc3\x88\xbb\xaf\xca\xf0L\xf5\xb8}\xa1h\x14\xc8\xf78m\xb13D\xcd\x84xh\xf3\xa0\x11\x13\xdf\xb9\xc7\x01\xf0:\x89\xb7\xd1B)9\xb2\xa9\xbf\xf3n\xd9\x85P\\\xc9\x97\xa9\xe1\xa0\x9b_\x04)\x9d\x06\xc0\x0f\xa63tc(\x842|\xed\xb6T\xc7\xbc\xf2\xd4\x8f\xec\x13d3)\xf9\x8e\xc1l]8\xd6\xd2\xf7Hd\x12\xb2\x93\xbc\x1a\x1c\x87\x11W\xe5\x06$\x87]\xc9,\x90\xd5\xb3R~\xbf9p\xb3\x92y\'\x00\xb2\xcd$\xf8\x86i\xb4\xe2ja\x1a\x07r\x94\x198\xb2\x07\xf2\x9fGa\xcc\x81\x10\x97\x8f\xd1\xfe\x90\x13G\xb0\xfb\x02KL\x1e\xb2Z\x94\xa7\xdb\x19\x9b\xc9\xe1v\xc8\xf6Z\xe5\x01=\xb9\x9e\x18\xa4[6\x13\x8b\xff\xa1\x15\xf8\x83\x1a\x13\x1c(\x00\x81e?\xf7\x9aR\xd3\xb1\xa5\x86\x07J\xc8F\x04K\xb1\xda\xe6e\x10\x7f\xd6\x99i\xc0Pj6\xee\x87;\x8f^\xdf\x8e\xa3\xfd\xff\xec\x97\xdb\xdd\xd2\xa6o-\x13\x04\xb2i\x19\xcc\xc6\x94$\x1fZ\x91^/\x92\xa2\xb4\x98\xcb\xabp\x9c\x7fl\xa2\xd3\xd6\xf2\x013\x0f\x00\x0b\xcceK\x8e\</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Perfect Pro Condor 973373 Carro De Limpeza Multifuncional C/ Saco Coletor Preto</t>
+          <t>Barraca Para Até 4 Pessoas Camping Iglu Homefy Azul</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>96</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>99</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>32% OFF</t>
-        </is>
-      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/perfect-pro-condor-973373-carro-de-limpeza-multifuncional-c-saco-coletor/p/MLB28201233?pdp_filters=item_id%3AMLB5124129244&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB5124129244&amp;sid=affiliates</t>
+          <t>39% OFF</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_636759-MLA96153269857_102025-AB.webp</t>
+          <t>https://www.mercadolivre.com.br/barraca-para-ate-4-pessoas-camping-iglu-homefy/p/MLB51716412?pdp_filters=item_id%3AMLB6014887492&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB6014887492&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>b'RIFF\x160\x00\x00WEBPVP8 \n0\x00\x00\xf0\xcb\x00\x9d\x01*\xc0\x01\xc0\x01&gt;m6\x97H\xa4"\xa2($3\xd9q\x00\r\x89en\xf54$\xeb\x94\xae(\xb8\xccL\\\xff\xde~`\xfbh\xda\xff\xd1~=\xfc\xa7\xf9u\xe1\x04u;\x82\xfe7\xf8\xdf\xc7\xdf\x97\x7f\xee=Z\xfe\xa9\xff\xb5\xee\x13\xfa\xd9\xfeg\xfb\xb7\xe4\x87uo\xdd\xefS\xdf\xd1?\xdf\xfe\xdc{\xc3\xff\xc9\xf5\xc9\xfd\xc3\xd4;\xfao\xfa\x8fL?g\xafC\x8f\xddON\x8f\xdb\x7f\x87\xaf\xdc?\xdb\x8ff\xbf\xfa\xd7n&lt;M\xf3[\xec\x1fv~1\xf1\x9fj?\xce?0\xff;\xd6\xd7\xf8\xff\xf4\xbc=\xf9k\xfe\xef\xf8o`\xbf\xcb?\xa9\x7f\xa5\xf1S\xdd\x94\x01?I\xfe\xcd\xff_\xfc/\xb2\x8f\xd3\xf9\xb9\xfcw\xfa\xbf`&gt;\x0b_\\\xf6\x02\xfd\x0b\xfb\x1f\xec\xd3\xf5\x8f\xa4\x8f\xab\xff\xf9\x7f\xaf\xf8\x17\xfe{\xfd\xeb\xff\x0f\xae\xbf\xb3\x7f\xdc_\xff\xfe\xeb\xdf\xb9\x83\x8b\xa5C\xa9\x94\x9e@J\x87S)&lt;\x80\x95\x0e\xa6Ry\x01*\x1dL\xa4\xf2\x02T:\x99I\xe4\x04\xa8u2\x93\xc8\tP\xeae\'\x90\x12\xa1\xd4\xcaO %C\xa9\x94\x9e@J\x87S)&lt;\x80\x95\x0e\xa6Ry\x01*\x1dL\xa4\xf2\x02T:\x96\xb1\x99\xbf1\x1c\xe6`\xfd\xd3w\xba\x9e\xbc`\x85\xc4\x03\x0e\x8d\xcb\n\xf0]*\x1dL\xa4\xf2\x02R"F\xa6\x0bN\xff\xf9\xf9\x87\xab*\xad\xf9\x95\xef\xfb\x15\xf7\xff_\xfdx\xa7u\x97y\xc9\xe5#\x1dY\xbe4\xf9\x10\xfe=\x006K\xcdE\xbeYsV~\xf9u2\x93\xc8\tP\xde+?\xfa\xfa\xe5\x06\x84\xc6\xf9a\xfej\xdeC\xd0\x92\xbe\x06\xb8\x10\xcd{{\x8cd\xc3\x16\xae\x84\x1bQ]\xf5\x1b\x8df^\xe52h\xc5\x82\xe9P\xeae&amp;W\x0f\xba}\xd6\xd0*\x9f\xd0b\x00K\x9f\xd9\x8c\x90\x00O|\xba\xcf7\xd5S\xc4Gcn\xcf\xdb\xb1)\x8f\xf2\xa6\xfdQ\x9a(U9%(\xea\xa4V\xa5\x80\x17\x8e\x14\x95\xfb\xa5$\x93\x81\x0c\xca\xf3\x89\xbf\xe2O\x80\x06\xfa/\x82\xe9\x98\xd5%R/\xcd\x9e\xaa\xc0\x8f\xa4k\xac\x1d\xf5\x1f:}8\xff\xebC\xea\xdbbK\x182\xf3\'\xdb\xda\xe4|%\x1b6T\x98L\xa5w\x9f\x8c9,\x81\x1c\x0e\xb0\xb3\x89\xab\xee\xa7\x1d\\\x9e\x02\xab\x1c\xd8\xc4v\xf2U\x9d\x13\xbe\x8b\xe0\xbaeD\x98\xe3\x85I^\xc3\xf0a\x16\xbf\x89\xa4\xd63n\xa1_\xc0\xa51\xc4\\9\x16\xc53\x8be7(q+,\x9d"\xa0\x96/\x18Q\x1cm\x81V\x89\xef\x15\x04@u\x16t\xa6\xf2\x97\x04@X\xa9\r3\x07e\'\x8f0T\xbd\xa5\x0c@\x7f;\ro\xdc\xde\xda#z\x9f\xa6\xe7\xf4\x9f$\xd1\xce\x11\x1ab\xfbg\xd5\xd2fy3\x0e\x17\xde{\x9e\xcee\x18\t\x1dZ\x07\xff/\xf8\xdf\x05\xbe\xac\x1a\x86U\xaaB\xf8\xa9{\x81\xdc\x8a\xd0\'\x9f\x1a\xfc\x1d*\x1b\x93\x85,\x85\x87=\xc7\xb77e\xe6\xa3\x9d\x85&lt;j"\xaf\x08\xaa\xe4qT\x9e y,\xf4\xc5C,\x0b(\xae\xf0\xe8\x0b\xce\xb1\x87\xf6Hw\xf6F\xca\xe8\x0f\xad$I\xcd\xb0:w93r\xb2\x91\xc7i7YFNf\x13\x87L\xe6\xe9\xad#Z\xcc\xc6A9oQh\xf5\x86q\xcf\x8fmB\xf45\x84\xcewv2N\xa9h\xc1yc%\xe8i\xc2\xc1\xf2\xc0\x9e\xbbA\x0f\x90\xa9\x13u&lt;c\xd2\x1c\xa1\xb6 f\xf8\xc5\xce\xb5\xc0+\xd5\x183b.6~\x80\x8d"\xe3\xfc\xe4\x03\xc5\xc1\x05\xf43\xe2\xddF\xa5\xc5\xbe@\xcd\x1f\x18\x8dLB\xc3\x03\xd9G\xff5n\xd4\\\\\x88\x90\\\xa7\xda\xf6\x13\x86\xbc\xcd\xc2{\x83\x80\xbcS\xccy\x94.\xa3\xd6Z\x15\xbb\x19`\xcb\xeeg\x1bGy~\x07J5\xcc\x1bv\xb8\x12\x16q\xba\xd4\x7f\xb3\x14\x9a\x0e\xae\xa7H]\xdc\x9f\xb4\xc1E\x19\x9d\xaf=6\xb7e\xc8\xb6P&amp;\xd0\x1a\xa1\xd2\xa1\xf9\xbaF\xfe\x19@\xaa\x81\x8c+\x08)\xdeq\xd5\xc2S\xe4Aj\xbc\xf8\x92\xf8V\xfcM\xa8\x9c\x97\xa4\xc0T\xbd\xae\xefG\xab67\x8a/\xdd%\xdfJwu\x98\xb6\x00\x0e\xe34\xac\x16\x83t\x858\x16:\x03\t\x9d\xe5\xb4Q\xdd\x17\xe8\xe0\x1d\x05\x07\xe22\x95gF*4`\xc3\xe1\xb8F\xe8_\xf5r\xa4\x84Zdx\xc7\xa9G\xa7\xae\x84^\x19\xf7\xa4\x05&amp;-\xc8]\xb1\x9f\x8d\'R\x00\xa3\xd1\xbe\xb6\xca{}\x1e{\xbe\xd4(\xef\x01\xb87r\x9c\xea_\xd9m\xe1m\xedH\xbf\xe8\x97\x87\xf3\xe3s\x8e\xc9\x89\' \x10\x17\xf9\x9f\x82\x01\xdc\xa0\xf4t8\xb2\x83\xea\xd6\xfe\x05\x81\x8a\x9eU_\xf2\xec\xd28aq\x07\xb8\x91\x82\xe9P\xeai"\xf6\x12\xfc\xcc\x00G\xf6\x01vJ\x17\xd2\\\xe1\x85\x90X\xbc\xa0\xf5\xdbcZ\x8b\xfa\x87Qq\x19\xf1\xc5D\x9a\xdc\xd9Eqs\x00~6\xcf\xeef\x8a\xb5\xc1"\xecC\xd5&amp;\x9a\x8f\xb6\xfd\xd4\tP]\xf56\x13\xa8\xfe\xa0\xef\x87\xb7\x19;\x89\x1537#!ED\x89q\x07\xf2"\n\x83\xe8\xff\x9evH{\xc9\x9bu\xca\xdf\xcd\xb5"_m%\x8bo\xd1\xadJ\xdc&amp;\xb08m\x12I\xf5\x81\xba\x92\x800N\'\x051\xfd\xfdE\xef\x07\xf1I\xb4\xd9}\xac\xecB\x98Fr\x17\xf7\x02/\x10f)c\xbc\x88\xfc\x9d\xf5\x8b\x04x\xcec\xd1$[\x10\x18\x87\xbd\x94\r\x1e_\xe3\x02\xb3\x04\xbc\x1f\x9a\x85\'\xb5f\x15\xc0\xf9\xa2|T+\xff\x01\xed!\xda\xee&amp;\xd8DR\xd0\x89mk@S%z\xada]\xf3\xa5%\x81\xde(\xd2\xab\xd5p\x95\x8e*\r\xab\x98\xaa\xb0\xa1\x01\xd3\xb9@W\x9f\xb5\xf0\xbby\x04\xdbQ\x0f\xa2\xa1\x0b\xf9\x88\xc4\xe9\xcf\xbd\xf4\xceP\x12\x13\x08lr;\xd8\xcf+\xfd\x9et\xc9&lt;\xd8H]j\xa2\x1e/#\xd2;\xd0)@\xb1\x81R\xba\x9d\x1eZ\x91Sj\xba\xe4k\xa6\xdfJ\x8aSP\x89\xa8\xdd\x1f\xd7B\xb8%{\xf3\xe3\x8c\xee\xf3\xfd\xf1s6\x95?q\xce\xecl\xbcK\ng\x86\xbe\xac\xd9\nP\xe9\x95\xaa\x99\x14h\xe5\xaa\x0b1\xe3\xad\xc4\xaf\xba\xf0\x06\xd9B\xda\xdcgh\xaf\x99\x97\x1d\x14k\xd9o\x8f\xc4o\xc1\\R\xd2m"\xf7\x9b\xb6\x8b\xa1\x0f\xd6\xa3P\xce\xd2\xfe\xda\n\xc6:\xa7\x7f\xef\xa7Y\xf9"\x0eo\xc7\x12\xabA\xee\xc6\xb6\x8fS\xcc\x0f\x03\x88\x85P!\x8a\x1b\xe8\xbe\x0b\xa9\x94\x9e@J\x87S)&lt;\x80\x95\x0e\xa6Ry\x01*\x1dL\xa4\xf2\x02T:\x99I\xe4\x04\xa8u2\x93\xc8\tP\xeae\'\x90\x12\xa1\xd4\xcaO %C\xa9\x94\x9e@J\x87S)&lt;\x7f\xd0\x00\xfe\xff\xb8p\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x00\x08T\x8dY\xc5\xc9\xdb\x80\xf6\xffN\x7f\x00\xefVX\xc9 H6\xce=\xd8\xabn\x92b#5\x1d\xe8\xb2\xd2*o\xb2Vt\x8c\xb2\xc5\x8c\x0b\x9f9\xcb\xe3&lt;h5\xca\xa5\xd8\n\xc3N\x8d\x93\xa3\x83\xda\xd5o\'L[\xdf\xef\x18\xe7\xad\xb9\xd1\xb9\x87\x82\x07\x8b\x12\xb5.\xbf\x87x\xc5q7\xc2\xac&lt;\x97|\xcc\x8d\x8a\x1eW\xfb\x13\xda\x19T\xa0\xd5\x8f\xa9\xf4k\x12u}8\x1cH\x03\xd9UL\xdd\xf5]\x99\xb1=1N\xbd\xa0\x18L\xf8b\x9f+\x00$\xfe\x9fq\x7f\xb7\xee0\xa9;_\xee\xaa\xe1?\x06\x11\xae\x16\xdd\xf9Y\xf1\x9a\xf0\x9b\xe9\xce\xc4\x0b\x82\x15\x86U,HI\xaf\xf0o\x19\xf6h\neX5{\x05\n\x0f\xaa\xc0\x00\x18\xf8\xae?Z{\xef,i\xa8\x84z}O\xef\x14U\xb6Zd\xcfa\x0f\x8d\xb3\xc3\xf5b\xaf\xebW~\xd6j\xbb\xf2\xe4\x91\xe4\x8fa4\xf9\x89|{e\x9f\xa7#\xa0\xa8\nT\xbda\xcfs\xff\xf0\xd0\x8c3$\x87\xfcd6\x10\xb0\xffY\x07am0\xd9H\x12w=\x05\x01\'\x0bj\xfa\x0eh\x89y\xbbX\xe0K\xbca6\x88\xb6\xbc\xb5_g\x0e\x0b\xd77\xd7\x8f\x1f3\x0f$\xa9\xd5\n\x1c2\x04\xd6\x1c%\t\x1bI\xe9\x1e\x18_\x9c$\xc5\xf0\x7f\xf4\xf3\x99u\xec\xff!\xba\xf1\x98\n^S\xd4\xf6\xe6\xf2C\xf7\x14\xaa\xb9\x849"-\xf2\xc85\xc7\xe7\xd0,\xe3\n\x0f\x82\xa4\xb3zK=\x01\x9f\xda\xd9\xde\xe0|\x13\xd8\xa3\x8d\x14@\xc5\xd4W\xce\x07,\x13\x96\x08:3\xb9A*\xaeBu\xb4\xf7\xa3\xe6{\x9f\xff\xd7\xd3%%\x8bU\xde?\x81\xe0\x0e&amp;X\xaf\xc2\r2\x9f3\x87\xf5\x81\xa84;\xa721u\xea\xfe\x7fX\x9ac\xcf5\rv\x8f:F\xba\xaa\x9el\x19F\x1b\xb5\x8b*\x15\x0e&gt;[r\xc1\xc1\rT\xe4t\xeaV\x8a=\xc1\xaf\x0c-\x00\x7f\x8b\x83b9\x14\xb8\x8f\xf4"\'\x12\xbfT\xddi\xaf\xe4&lt;\x07\xdf\x93\xa0\xf8/coKh\x00\xc1{n\xb8\x8fZ\xb8\x19\xca#\xcbay\x86\xa9\x91|\x9a\x011}&amp;"OX\xc3\x13{ w\x90\x13\x1c\xb2%\xf3\x16v\xa8A30A\x92)\xfa)O\x19\xd16\x9e)\xf3&amp;&gt;\x90c\xf9\xda\x84+\x16L{\xbf\x0e\xe9c\xc8W@\x9b*\xe2&amp;i\x1f\x86e(X\xac\xdbJ\x0e\xd8"\x98=kc\x12\xf9\xfenBP\xd2\tB.\xb0\xa1n\xba\xeb\xe0\xe2\x15\x19\xa0K\x00V1\xbf\xdeup?\x80x\xa5A\xa9\xfc\xfc\xa5\x97\xb8\xbf\xe1\xdd\xe8rV\xad\x19\x14\x92\xc6\xfa|\xf7\xfe\xcb5\x82\xb1\xb2\xd9\xad\xf0\xb6\xb79#\xf1\x14\x9eDC\x06\xd6\xf6\xcb[\xadw\x8f\xe2/.X\xa2m\x87~4H\x00\xe5\xe5A\xdc\xab\xc1tZ|K^BH\xbc\x9c\xed@\xed\xb3\xf3\xccv\x0c\t\x04z#\xca\x88X\xc6\x19f\xbb\xa8\xf6\xe5\xc7\xe4G#\x08\xca\xe6\x1a\xc8H\xedM\x85\xf8_k3\x10\x02,\x99\xdd\x91\xe2\xb8\xb4\x90\xb5\x12\xd2\x05\xeauv\xe0\xce\xe1\xaf\x8aNX{\xfd\x93\xb0\xaf~\x17\x9e4\xc7\x7f\xaa\x15\xc6mE$\x18\xf4\xc2\x98\xe8\xf5\xd4s\x82\nV6[\x90\xb0r\x05\x00\xa7\xaf\xa4jC\xd0i&amp;\xcf-&lt;\x90\xabP\xc0D\xe1\xe0\x18=Y\x05g\x1a)\x07\x0c\x0f\x10}5PZ\xff\xe27\xb8\x0c\x12\xe6\x7f\x93\x84t\x8e\x0b\x83k\xf2Xds&gt;\xfc~X\x0b7\xe2\x84\xcdH\xcfI\xa5\xd6\xb2\x9bb\x02\x12\x86;\xee&lt;\xc7\x1f\x9cIiK\xbe\x04`4\xd3\x88\xe1g9\xb2_\xd3\xd9H\x92\xe1\\\x91f\xc8\xfe\xeff\xc6u2]y\xd5xal\xaf\x95\xaegE|\xb5W\xcd\x06\xfd\x8e\x0e[4\xfc\x9b\x1bb}o=(+\xcb\xddb\xe7\x1d\x8e{.2\xee\xf6\x19\xa6\xad\'\xe6c\xb7\n\x13\xe9\x1f\x83\x9b\x06~\xba\x96\x83\xc9\xe3\xf1\x9b.^\rT)\xb5\x80?BX\xa5i\xc5\x9f;\x04D\xdd\x15\xefqG"\x91\xc9t\xaal\xb3\xc5\xc36_\xf6\x0e\x01z\xb4laH\xafh\x97&gt;\x81\xeam[Hd\x99\x15\xdd\xfd!\xbfR\xfd\xec\x88\xe0\x1dx\xae\x82\x05\x92\x11\xe6\xa2?\xab\x1b|\x17\\\x96\x95\x7f\xda\x8bt\xd5\xe3\xf9f+\xea\xf2D\xec\xa0\x9e\xcb\xd1\xd4\xf8\x02y\x1f\n9\xa4\xe4P\xdd\x0c\xb6\xa9)\x8dB\xd9\xa0\x96sx\xf6\xa8E/\xc4\xf0\xb7\x9f\xca\xba\xd1]\xec\xfe\x88ME\xe0:\xe2/\x1b\x8f\x1cE\xb9\xd3#z\xab\xe7\xff\xd3\x97\xe7\x83yS\xf0]d\xa4t\xc3\xaa\xe7#\xd8z\xcf\xa6j\xfd\x80C\x0cME3ES\xa9\xea\xf7\xdab\x16h\x99b\xa5}V\xe6]\x8b\xfe7\x9e\xfb0\x9aE\xec\xc4\xc7j\xa2r\xb7\xa8\xd3\x84\x87\x9e\xdf\x85\x16g\x05/\xe7*\xa0\x07\x15Do\'Wn{\x18\x08a\xd4\x9c\x10C\xa9\xf8\x83\x9f\x8fz\x1cg\xc7K/\xe3t\xb2B\xfa\xa7\xed\x9e\xc5\x8e\x93h\x1e\x99Kw\xd8\x8d\xf6\x9a\xbe\x10\x97]\xbd\x05*\xd8\x03N\xa6\x0c\x1e\x8b\xcd\x89\xed$\xb3!\xder\xf8\xe1\xa5\xbb:;)\x15n\xbfP*\xb2|\x94\xb7\xbe\xe2\xad\xdc\xa0\x9c\xf3\x10\xd2\xd0\xae\xe8\xe2Z\x96\x80\xb9\xad\xe1\xc81\x1c\xdb\x1b[\x1f{\xbe)p\xfbe\x02\x86t\xe0\xef\xbd\xa6\x00\tO\xb3\xf3T\xd0}\x81\xd7\xe6\x8eGH\x88\x98~\xcc\xeb\xf3$y^\x01\x19I\xdd\xd3\x14\xdf/\t\x80y\xfa\xae\xbc-\xbd}\xd0\x1f\x98K\x19O\xc0%L\xf1\xa8\xbbC\xd4/\xb7\x1ebK \x96\x95-g\xd2\x07M\xf0\x04\xc9\xb2\xda\xde\xc8\'s\x19S\xd5\x1b^\x9d\x06\x98\xde\x1c=\x1e&lt;\x9aZ\x8bXr+\xd2w;o\xc3\xde\xcd\xb7\xc9~\x00\x90\xef\x18KC;\xf6\xf5\xe2fUt\xb1\x1b6\xd5\x13\xbb\xbeTR\xc8\x1d\x19\x0f\xb4\xc5\xff\xf2\x0bi\xa6\xb3\x95\xa4L[\x95\x18\x8dC\xe1V\x06\xd6\r\x0cl\xb4\n\x8e\x8b\xec\xaey\x8b,\xe0\xc3sr\xd6\xfbr\xb6\xac\xef\xc2\x0f_f\xbc\xdd:\xde}E4\xa2Q\xff\x84br\xc0s\xb7~\xf6Ei\xee\xe6\xa0\x0b\xf1{3\xf0\xc4\x0fx5\xdf\xcd\x95\x93\xe9\xdf\n\x9bBG\x1a\xb1\r\xf6\x08j\xecL\t\xbb\x8d\x8a\x9a\x94\n]\xceO\xffR\x1aBz7\xf5\xe6\\\xd9\xdc\xcf\x11\xa6\x8e\xfdsfw\xc4\x82\xce\x19;/T\x0bt\x9b\xfe\x08M+v\xcf+\x03\x04\xf37-/\xe9\xbe\xe4#\xf0~\x11\xb4\x1a#u\xb5\xaa J\xba\x15tr&gt;w\xf7\xf4kfU\xb3\xe3\x1d\x88\xfe\x90_\xa4wy\t\xc2G\xf6\xa3\xf9q\x93\x86\x1bK\x82\xf3\xc8\x96\xfc\xb4\x04\x8f\xbbs)\xa2N\xeb\x0f\'\n\x80e;;\x92\xf5\xf0\xb9o\xfcJw\x08d;\xbc\x8f\x88\xaaq\xc1\xa9^\xddN"\xa9\x1a\xbd\x80\x81\xab\x0e\x80\x109\x00\xf2\x1d\xb5\x0eQ\xa7\\\xa1\x9a\x1d|\xd5z\x9f7\x8b^\xde \x9c\x08\xc1\x07\xa8\xd1\xe1\xb5&lt;\xe38\xdf1P\x85?\x15:\x8c\x8cy\xe7\xbc\xa4w\xf9\x87\xfd\xa3\x17I\x96\xe9v3\x94j:\x9cD*,\xb1h\x11=\'\x97\x88\t\x88\xd0\x7f\xb9\\:\x94\xde\xa7\xb8\xd2MQ\x05\x1eN\xce]B\x10|\x93C\xe7\xd9\xf3\r\x84Q\xf5/b773Kc\xe4\xde]\x95"\x01+g\x19\x17\x90\xd1\xcc\x1f\xe3/\x13\xf4\x96A\xe7\x81\x04[m\x16\x0e\x8e\xdd3\xd7_\xc8Q\xb2\xc7\x1d\xae\xb1|\x11u\xe9\xe0\t^\xeeQO\x91sEJ\xfa\xd3eA\x82_)\x80\xd2\xcf\xc6\x08\xe5#\xd2\t^\xa7\xa5\xc0\xefg\xde\x1d\x1e09\xc7\xd3\x1b\xc7\xaf\x87\x16\xdaP9O\xe5\x04k\xc9\xde\x9aD\x9c\x1b\xf9oj\xbc\xdd2&gt;\xee\x18\xb2\x11\xed\x9c\xdfZ\xb3G\xe9\xe4\xe3\xfb\x85?Al\xfd\x96\x06\xcc\x95_\xa2\xb0.c\xc4\xdd\x80\xc6\xb3\xfd\xfb^\xe6\xfarG\\\xdfN\xc46V+\xdc`\xa4\xda\x05\xdc\xca^\xed;\x83\xea\xf5\xda(\xaa\xfc\x82\x06K\x8c\x86\xdbS\xf3\xe7\x1e\xaek\xc6\x11\xe0\x83\xe0G\xd5\xd0{\xde\x9a$A\xe1\x822\xad\xc4\xd7]\xfb\xff\\\xe0\xf6[\x86G\xb2c\x99\xf9\xd0r\x9c\xed\x05F\x00\xdcr\xabWr\xf9\x03\xca\x05\xfb\xf7\xdf\xbf\xa8\x11~\x98$\xbc\xd7\xe6\xb8\x8eh\x89\xed\xc6\x9f\xf9\xaf\xcd\x97\xb5^\xfcX\x8a\xe6\xea\xdd\xdb\x85\xe4\xa5\x94\x99\xc9[$}\xd2\xac\xe9x\xac\xf2C\x05T\xd4\xe4\'r\xd7\x8c#\xcc\x95\x98\x11\xd0\xcd\xf1\xbc\xf6\xcb\xaa{\x97\xaf\x91\x84\x89 \x1b6!\x9b\xe5\x1b\x1c\x82\xd0\xb1\x9c\xc6\xf5\x93\xa5\xa8\x1c\xc8R\x97\xf3\x05\xc5y$ \x95\x93\xdd\xcb\xd3m\x9c\xf7\x1dl\x1a\xb7o\xe0\x13\xbe\tL\xe1&lt;o\x1b8\xa2\xa0\xaeZ\xe5n\xa8\x9b\xeea$\xd5a\xaa|Gt\x1fq|\xe6\x81\xa1\xb3\x7f\xbb\xf3\xd0\xc4\xc1\xd5{\x7f\xc3N\xdf\xb3\x9e5\xdeqEN\x03\x10E\n\xee\xfd\xf8\x9b\x96u\xfb\xcf\x97rc$\xa5LS\xc7}\xf2\xec\xfb\xc4\x96-i\xb9\x97.\x94\xb3R=&gt;53\xc0\xf0\xa3\x92\xf9\xb2\x9b\xa5\xd0\xf0j\x19fY\x7fh\xbf\xdf\xdaL86\xa1h\x01\xfc\x04x!\t\xa1\xac\xe8p\x0b\xf7S\x02\xc2E\xb3\x92\x16\xf1c\xe9\x1e\xba7\x0c!\xdbV\x95_\x9e\x05K%y\xf8\xa4G\xcc\xf3,\x01\x01\x1d\xa2\xd0\xac\xa7|\xf5\xd3T"Gn\xf1\xdb\n:\xee\xe2\xe1/O\x96KF\'\xa0K\x97#.\x04\xfdi\x15\xe0=\x9a~\xeb\xe4\xb1\x11\x99\x0c\x1e\x0e9,J\xfa\xe8\xe6p\xde\xe2?\xe7\xcc ]3\xcan\x83/o\xad@!\xf7\x94\x8a\x8d\xd6S\xce\x17Vy\xe0\xcd\xd9\xbd\xff\xf9W\xbb\x98\x9d\xe1\xb3\xda\r\xcb\x08\x0e\x03\x1a\xe3YN%\\\x9d\t\x07[M\xc1\xd0\xbd\x814\xa1C\xf3\x8e\xf9\xc4]\x93\xbcc\xc6z8\xe7\xe4[\x11f\xd0\x7f\xd2A\xe4Z2\xd0\xfd\xbe\xd8\x97\x84E\xd7\xcck\x9c\xe9\xf0\xf8w#n|\xa5\xd7\xd6\xf8i\xe8\x97X;\xf0WcP\x12\xfbH.E\xfb7\x0c$\xcf\'i\x03K\xb2\xf9\xd9\xbb\xc5\xd3\x9a\xca&amp;\xa2\x83{(*\x8bP\x8d\xc4\x8d\r\xc0\xb7\x86[{\xdaN\x9e(&lt;72\xf29\x92\xb9\xa0\x0b\xb2\xfc\xf7\x88\x9fZJ\x83\xcb!Q\xd6\xd7\x0f7\xffg\x1d\xb9\xd2\xd7\x10\x9d\xbeq\x9d\xeb{\xb6\x900\xad\n\xc5.\xc5Z\xb0\xe7ih\xf3N]\x1e\xa7\xd2\xff\xa2\xc1-\xc6i\xca\x032\xcc1`\x93\xc5\xe0I\xbe\xe9\x06NzR\xbd\x0e\xe9\x9e\x07,\x9a\t\xf3_\x83\xad\xf1S\x8c[\xab;RSG\x8d\x8a\x19\xf5\xd5\xcc\xde`\x89\xd2\xc6\xbb\xbf\xcd\x11S \xde\x14\x82@\xac\x83\x8e\x98Q\xeeB\xff\x88bwN\xc0\xadd\x82\x8e\x01\x8b_\xba\xb9\x8e0d\xf8K\xc3M/Y\x99m\xe7\x13\xfbV\xdf\x9b\xc6\xaf\xed \x9e\x8e\x01\x0bh\xbb!`\x8a\xff$\x05&amp;\x8c\x19\xfa&amp;\xda\xd5&amp;\x93y7\x87\x84\x81\x08\x14%\xa1}\xea\xc3X\x90\xbec\xc8\x97\xe7s\x0e&lt;i\x9f\xa8\t\x92\xf5\xc2%[e\xe9\xea\xef\xb5\x1aHo"\xbfB\xa7{\xec})\x18\xd1\rr\xd38\xc2,\x84\xfa\xdb\xbb9\xda\x0e]"\tG\x99\xbf\x8bc\x8c]\xd8\x9fw\xf6\xd2\x9d:w\x93|\xff\xd4\xa2\xbeP\x04~{@0\xab-s\xd2\xaa\x0f\xcc\xcb\x8d\x0e\xb8KZI\xa6|O\xa1;S\xdd\xd6JV`\x96\xdc\x12O5\x14\xed\xcd\xf5\xebM\x80\x1a\x7f\r\t\x01+I\xa9|\xa9\xcd\xe6\xa4\xe2\xcc\xdew\xa1\xfa\xee\x10\x0c\xf3\xa5\xd0\xb3\x97\xff\xda\xf28I\xd4\x86Wz\xd9\xae9\x88zZ\x1a\xba\xd7N\xf1\xa8\x87\x979r\x0bC\x8d\xdcH\xf2c\x02\x9c\xb4\x84\xac}\x1b\x90\xbfz\xd3\xcf;H\xd2\xfd,\xf2=\xf1\xafK\x88\x97\xb9\x12\x90\x8e\xa7X\xab\xad\xec%\x8a\xe2}\x1c\x0c*\xc7\x10T\xf8\x00\xc2\xe6\x04\xb9\xcd\xf4\xa3\x8d\xf3N1\xd0\xd7\x08IG\xe5\x96o\xf7f\xf0A\x19\xb1`\x9eV!\x11\xa2\xfee\x9c\x97\xd2\xea\xca\xde&gt; \xb3\xe0\n\x970L\x94\xbe\xe0\xcd\xa5\x80H,\xc0P\xe5\xa1\x11\xfa\xe8\xca\xa7\xecL\xe0\x94%\xfdE~\x0c\x18\xbf\xbdj\x0b\xe6&amp;\x99\x82\xee\x00\xb5\x1b!\x80Ik=\xda\xfes\xf6\x92F\xae\xcc8\x08\x0f\x84\xf7\xe0\x01#!&lt;)\x9d\xf3\xe2T&gt;.l\xbb"\xe4\xd5\xd1@\xd6/\xed\x14\x90\xd6\xb0ce\x03\x07\x8a\x94\xdd\xcck\xb8\x8dC\xa6\xac3\xf3\xbf\xc6\x0fV\xd2\x0fL\x0ew"\x1b\xbe\xb0\x98\x10\r\xa9uw\x81\x0e\x8d{{b\xe5\x08\xcb\xf5\x11\xd2z h\x9c\xc9ay\xc0\xbf\xdc\x17Y\xd2aJ\x80u$\x03\xdck\xef\xf9\x82\xf9L\xa5\x91\x14\xf7R\xf1t\x14\xd30\xa1\x04Wfr\x16\x96\xeb\x99\xa7\xb8\xc7+\xcb;\xccA\x01\x13\x10\x04\xe1\xf3TT@\x81C\xb5\xc2\x16ps\xf4&amp;\xff~\xfa\xef\xf7_g\x0f\xe7\x15\x12d\x1c\tdH\xc8b\x0fr_\x15\xa8\x10\xd4&amp;\x1a\xd1\xc8\xb5\x0e\xa2\xfe\xee2o\x9c\x80B\x97\x03\xea\xefoj\x92\xac\xb9#\x8f\x01\x0c\xad\xd8\x9d\xbb\x8c^U\xa8\xc4s\xcf\xce\x12\xf9\xb7(Q&gt; \xdf\xa7q3[\x15\x8b\x1d\xf5\xb6\xf0\xec#G\\\x15\x9f\xba\xe2\xdb\x14T\xc4\x89\xa1fg\x05\xb8\xfax4\x10\xbd\x17\xd9\xbc\xe7\x1b\xc1\x93\x94\x0b\x16z\xe3bRk\x17~\r\xe1\xe2\xc4\xeew\xbd\xbb\xcfu\x1f\xe2!\x816r)\xa5\xbf\xc4\x15\x97\x074\x00\x9ewe\xa4\x97\xaf\xb0G\xfec|}\x91\xa5#\xc3\x1a\x9c\x19\x18\xda\x1e\xbe\x04\'\xbc\xe6\xb0\x81_\xd2cU\x8b\xfc\x04nEZ\xea\xf0\xe0\xe3\xfe\xb7\xf8\x83\x06,M/\xf7\xd6\t\x0ci-f\xf0&amp;\x04Qj6\xf8Zv|\x04\xd7y\x86\xc9\x9f\xa3\x165\xc8&lt;\xa5\\J\xc3E\xfc\xfdqc8HE\x07\xdcS\xdf\x8d\xb0[j`\xae\'\xb7\x8a&lt;\xf6\xb1\x08\xd2\x01H\xe0c\xfb+\t\xb0K\xd2\xf8o\x8a\xaaV\xdd\xe9[7\xb8\xc3\xd6G\xc1\xef \xbfg7\x1f/\xf1\xc8!\xdf\x98\xecr\x88\xbf&gt;\xa2|\x18\xcf\xeae\x10bWU\x97\xe8Hp\xaf\x88o\x80\x0c\xfa\x03\xa8`!8\x90\xd7\xfa\xe67\xa9\xf8\xfa\x13\xc2\x19\xf0\x81\xd5\xe7 \xa9U&amp;\x90\x80\x942\x12\xc2r\xf42\x1a\xeb\x93\xcc@\xfaKN^\xbd8\xa4?\xe4vV.\xe00\xf6\xfa\xaan\xa1\xdd\xac\x84Lw}bNI\xd7\'\x1c\xdaI\xbb\xa5\xc8\xe84\xe0\xf5\xe1\x8f\x1b\xf8l\xea\xef\xd7\xe9\xdak\x10l\x86&amp;\x93\xe42\xcb\xdar/-\xc3\xf6\xdf\xc7"2o\xa4\xd6(\x00@\xdf/\xf7.TE\x87\x8f.FR;\xaf\xdb\x99\xff\xe4\x1bF|\xa1!\xfa\x9cV\xeb\xf4d\x96\xf2\x16\x01\xb2\n0\x9e\xdeRO\xc2\x02\xd6\xa3\xfc\x8f!\xc0\xcf\xfa7I\xf6[%\xae\x90\x8d\xb50\xc5\xcd\xde\x7f\xda"k;|\xadX\'\xd8\x06\x86s\xba\x17\xb8\xfe0\x884\x96N\x16\x06i\xdd`\xd7\xe0"\xf8O\xd8l\x0b\x1fU\xeb\xf2^6\xd5lv/2\xdem\xd4\xa3qf\x83\x86_\xfd\xb0\x87\x81P\xdb\xd0\x949\x9a\x0ca8\xbfO\x87FD\xf6\xc0\xb0\xb5u\xd8\xc16?\x94\x8d\xd6\xfe\x0fZy\rZ\x0c28\x94W\xfc\x01\x13\xb97f{\x82$\xb2VZ\xc0`\x8b\xff\x9f\xae_s\xf9\xfe\xbdD\x9d]\xc8\xe9\xd0\xb5`\xe1\xf7$+O\xd3#\x11t\xfc!q&lt;&lt;K\xccR\xceo\x1f\xf3\x97X_]Qa\xaa`\xbdv[e?\xf1\xf0[\x16\x06&amp;][i\x9d\x7f\xc2\x9a^\x8a\x99\xa9\xa3\xf4\x05aO\xf1\xe7\xe4\xf3\xe2\x1b\xb9K\xb5\xbe\x1f\x8f\x85\xc8\xba\xb7\xc5\x95\x8d\xfa\xb6\xa1\xa6\xb5|\x92beH[\\\x0bf\x0f%\x83o\xc9)\xaa\xf9\n~\x15\x8b\xa5\xb7\x96\xc6\xf5&gt;\xc7V\x8a\\(\x7f\xf7T\xe8\xe1PO$\xcd\x14\xb1-\xf9\xcb2\xf9KA\xb5\xd79\xdfP\x87\xf0\xae\xb1\x0e\xba\xdd\x93\x03\xe6\xb2\xc8\x83\xe9\xc5\xfd\xc0Rzs\xa9\x83/0\x94\xd9\xf0\x9c\x8c`d\xab\xfe\x9e1\\\xff\xb6\xa2\xe6\xb0(\x90\xf7\xa6%\xdd+\xde\xeeW{\xab\xcc\x10[\xfe\xea\xf9\xbfL\xb9$\x037\xab\x17-\xb2\xc4\xe9m\xd5d|\x83\xc5H\xa9\x8b\x14\x1a23,V\xac\x90\x0cE\xefSZ[\x1b\xb23S\xbf\x9a\xf0\xceY&gt;\xc7i\xfd\xdb\xe2\xc4y\xf44(\xb2\xedg\x0fj\x1cDu\xbdp\x8c\x01mL\xa4\xdb\xe0\xbb\'v]\xa4B\xa3^\xa8{h\x12|\xfbw\x9b\xd3\x05\xb4\to|\x85\xae\xe6\x007\x9e\x99\x1cX\xbf\x97\xd8Bd%\r\xb4\\a\x8e\xd6\x1c\x08\x83g\x05\x14t\xdfJM\\\x9e\x1b\x8a2\x19\x148]Q\xc6\xf7\x85\xd4\xc0\xe8\x14\xa4\x9a\x01Z\x15\x9c\xf4\xe9\x19l\xb1\xa2\xf7\x98t\x86\x1bwd\x91\x04X\xd3-\xfd&amp;~o\xa6#\x8c\xe8\xa2\xe0a\xf1\x02\xf9C\xb5QH#\xf8\x8fam5\xa3\xf1GD\xbb\xf5\x15\x99\x84QBH\x0b=8\xcb\xc8\xc9\x1e0\xab\xa6\x15\xbd\xba22\xe0\xe1[\x93\xb05\x9e\xf9j\xb0UA\x1d\xd9\x03g\xb0?\x8aN\xe5\xcb\x06G\xa2\xfe\x8d\x8d\x99\xcc\x07]O\xe8p\xb9\x03\xb4V\xdd\x9e\r{\xefm\xfdSj{\xa7\x89\x04\xb3\x19\x16q/\x89\x0c\xe6\x92W\x13n\xfc\xa6\xcb\xb4K\x9a7[5\xa5=?G\'s\xc4S\x8bI\xae\xc4\xea\xef\xd6\xf4\rU\x07\xe0LlPnW7\x9a\x05\xf8\xde\xfe\x04\xd2k\xa7\x87"5\xb94\xb5e \xe3\x92\xc41\xffIt\xe4G\xd9\xe1\x19i6\x16g\xe8z\xb5\x86\x14:d\xdd\x1c\xc84\xd9\rfU\xbc\x1a\xb2\xce\x1e]t"\xfa\xe2\xa0I2\xc2\r\x1cfHD\xd3k\xde\x1e\xd2Y\xc8\xf3\x1cG\x19\x88\xbaMNGRD}?\xf4\xde\xdb\x1b\xd1\xec\xf1\'\xf2\xac\xa2\xf5l\xd6\x00AV\x0c\x1fvaiy\xfa\x19\x13\xc5\x02^\xda\xa1\x0b\xce\xfb\xc7\xaf\xe7*\x98&gt;\xce\x91\x8b\x17[\xde\x97HY\xffS\x05I\'\xb0\xb2A\xf3\xd6\xc3\x9c\xabQ77\xf1\xf6U\x0be\xea\xa61\x82\x1eI\x88|\x16j\xaf\x9c7\xc9\x99\xca\x9b\xe0\x16q\xbf\xbf@\xaf\x02^\xb6,\xe0\xaf\x7f\xa2J\xe4\x06\x9ce"c\x1b\\T\xc3\xcf\xe7\xb7\xd3&lt;\xe63V\x92\x1cX \xf0"\xbd\x14\xe5\xd9\xbb\xd1n/z\x90\x8fMr\x93@\xd7c\xee&gt;gr\xe87\xf1\xde-\x16\xa5h*\x13\x80JL\xf0g\xb8\xc3D0(;\xff\x0c\xe99\xfd\x83$7\xf5{\x83\x94\x1c\xb7.w\xd6\x89Ta\x08\xcc|m\xd8O#\xa1Rd\x87L\x13\xe8S\x05\xf9\xb0\x8a\xa9\xae\xcbQ_\xaeJ\xa7EtCo\xd4\xc6l\x99\xe9\xe0\x91\xdf=\r\xc0&gt;\x94\xdc\xb4\xc3V\xe4\xf42\xa3^1\t&gt;\x9a\xe8\xfe\x0fk\x8f0q\xb4\x84\xbf\x10\xb7\xc9\xf1\xa9\x14C\xdaLf\x1f\x94"\'a\x9c\xd2\'n\x19\xeb\xc7\xe4\x86\x022\xb0\xf8\x90K\x08\xa7\xc4\xe3\x03\x89\xf4[\xe33\'o-a\xef\x00\xc3\x0f \xb3NJ\xfe\xc9\xa6\xb3)\xa8RETT\xd0\xb5\x8a\xb6\xac\x80\x1c\x1f\xc6LttC\xef_\xe7q[\xa3\xd1!\xcb\xe4\x02v\x89&amp;\xab\xd6y~\xc4,;\xb4\xa1I\x14\xb5\xad#\xb2{z\xbcxb\x87\xfb\\\x1b\x1d\xfa\xf6\xce\x1czl\xd71\x03\xeeO\xaa\x1e\xf0\x9d\x8a\x8a|H\x0c4+c\x1c\xdf\x19p\x96\x99RP\x08\x86\x04o4\x14\x16H!\xa8n\x9ad\xbb\x1d\xc2\xb7u_p\x1f6\x1c\xeb\xee\xcf\x12\xcd\xa9a"\xcd&gt;/T+\xea$\xef\xc2Y\x92Ag\xd6f\x9a\xf8=\xb5\x0b\r\xc7&gt;\xaf\x81\xfe:\xe5\x99\xbc\xe9\x96-\x0f\x838i\x00.1\xb9WO\x7f\xee\x88\xb7\x82Fs\xd2I\x89\xa2$\xad\x90\xeb\xc8d\xf0\x8c\\+D\xcaL\xc4\xf9H\x9d\xf7\xb6\xa5\x8eo\x8c8c\x03\x1a\'\xca@+\x05\xbc\xd0\x96\xf5O\x824\x81N\xfe\xdd\nxY\xbaB-eZ\x8b&gt;%\xae~\x84\xf4@AA\xee5\xfe\xc8C\xcao\x1e\x9c\xab\xbc\x1c\xd9\x8ac&lt;\xbaL\x8f\x13d\x1b\xff\xea+{\xfaj\xfa\xe0\x90\xd8+\xf6\x7f\x11Y&amp;S\xf1\xa9\x86\xa3\x8f\xb1m\x87\'u^[Z\xaa\xdf\xa6\xdbz\xed\x14\xaa\x0c\x81\x86\xe1\xd8\xa3PZ\x1f{\x97\xefu\xf0Bh\xde\t\x9e\nT\xe5Q\xde_\x9b;IO*\x19+\xac \xb4\x7fP\xef\xe0\x16\xaesT\x19\x81\xd4\x9cq\xc2P\x18\xd9\x1f\xf70\xfa\xac\x1f\x19=s+\xdc\x11q\x8f*7/F\xe1\xa8.\xd9B\xbd\'v\x00%\'1\xdf\xa6A\x9bK\xb5;\x8b\xadG[\xe0\x90\xc4\t\x02?\xcdP.\xd6\xf0\xf6\x7f)\xe4G&lt;|\xd5\xe8\xbeZ\x05\xd6\x04b\x15\xdb\x94h\xdd\xf3\x95$d8\x8c\xb5.\xa9\xc0@5a\x94{\xa9u\xdc\n\x81&amp;\x0bf\x86R\x94&gt;\xc6N;m\xd6\xd3\x8b\xe8\xdc\x0e\x80\xf0}\x04LH\xad\ra$\xbcw\x98/\x97\xdfw\x0f\xa0\xda\xd9\xf5\x0c\xd1\xcb\xb6yv\xd7O\x86\x85\xba\xcf\x19\x8f\x9f\x15\x12)\xa3\xeb\xdb\x1e\x17\xd2\xd9 ]\xd4\x1a4\x88\x90\x08&amp;\xea\xa7\x84M\xa1\x1a\xb1\x82\x82\xee(\r\xdc\x04\x8b\xf6\xb7_o\xf8\x9a\x8a\x11j\xae\x84\xe8\x98\xae\x16\\&gt;\xf5GI\x05\xfeY&gt;\x11\xaa\xe1\xa9\x90\xb7-\xaf=\xdc\x9b\x80\xab\xf2\x9f\xee\xc78\x94\xa7\xf6Cs\xf5e$!\x9e7D\xc4&gt;(\xb1\x8c\xd1\xa4\xd0=4\'/Mn+\xc3\x1b].p\x02m\xa5\xf7S\x97\xfa=,.q\xf2\n\x0f(%\x01\xcb2fA\xa4\xffH\x18\x87\xf3w\x16s@\xdd\xc0\xd0Ic-1\x9f\x82k\x0e\x18l[`\xad\xb4^\xf6\x9c~\xe6\x1eg\xf6\x03\x9bc\xf4h\xf2\x99\x16UH\xc6\xb7\xd1\xc7\xa7\xd3&amp;\x0e\xa9\x8d\xcd\xd4\xdb\x07 \xb7\xae\xe8\x14\x16\x8c$\x876\xa4\xc9;\xb3\x97Ht\xa8\xa2\x16P\x8c\x8f^\xd1+0\xf4l:\xaa\xbe1yW\x9b&amp;h5\xf8\x9a(Z\x81~\xac\xdd\xb8\xa9\x94wvx\x0f\xfe\xbeh\x12p\x08\xf6\x08\xb7\xb1\xcfI\xb9\x89A\xe2\x97\x88\xf6\x0eIv\xc2\xb7\t\x86\xc4p,\xb3\xe8\xe6\xca\xe5\x06\xd2\x19\x0et\xe0u\x9e\xeeuD\xf9v\xeb\x8b\xbbf\xee\xba,Re\x91\xd1\xf8T\xf4\xff\xc1OnF\x84\x99\x8c\xc9\xd9\x85cz\xc8v\x83\t\xd7\x07X\xc1h\x0f\xf5!\xa0`\xf5\x92\xa8\xe3,/o\x1d\x9e\xc7\x8e~,\x80\r\x92\x9a\xe5C\xc5m\xe5n&gt;\xcc\x9cF\xc1\x8a\x02K\xd8\xa0\xa3j\x9bo\xf8\x84b\xb4oI\nA\x95\x7f\xceh\xcb\n\x93\xf4\x0f\xdc\xd6&gt;\xed6fJ\xad\xbf{\xbc\x01\xec=\xffSqv\x99\xa2\x94\xc9\x9e\xb3\xe4\x84\x9d\x147|\xaf\x1bv\x91\xda\xc3b\x82\x0c5\xf4\xaf\xd1c7\x9bm\xb0KS\xd0\xcf\t\xd8F\x99!g\x9c\x94\xf50\xd4\x0e\xd9QY\xbf\xe2a\xbaTX|\xcd\x04\xb2F\xddXc\x0e\xb2\xbdm1cw\x11yL\xe6M\x08\x1c\xee\xea7\xee/K\x07\xe49m\xc7\xf0\x97\xb7\x16\x886\x1f\xb7R\x8b^\x0f\x1bT\xd8\x94\x00Az)X\xc7\xff\xe5\xcad\xc3z\xa9\xf5\x0b\x96\xa3u\x85\xa4:4P\xf3\x8cm\x7f\xe2\xd0\xb0\x07\xb1\x85\x80\xc7v\x9d\x03\x06M\xb2d\xd3\x01\x9fs\x0fq\xf7\xf2\xeb\x1f\x07\xaf."\x9a\x95\x86\x1e\xd4\x82\x8a\xf0\xfe+\x81B\x85\'\xa3\xd3\x16\x84\x91\xdc\xd1\x8a$\xad\x86\xfc\xa5\xee\xfaM\xea\x0e.\xef\xca\x16\xefy\rx\xe3h=z\xa2\xcdg\x91Q/\x0b:"\x8f\x01\\\xb9V\xfaPz\xf4{\xc8\xd7!J7\xb0y\x7fe\x99\x15\xa1F\x08Y\x15\xda\xad?|\xb3\x9e\xe6\xc3b\xaf\x0e\x1bY\x83\x1a\xb9\xe8{\xcb\xf6g\x99k\x84\xa8\xb8&amp;\xfa\xfe\xa6\xbf@\x81\x10\xa0^%\xc6\x05Uh\xa5\x9do?\x01\x95\xe0\xb8l\xd0u\xd1^\xf7\x8d$\r\x95I\xf9\xe3\x10\x01\xa8\xd7w6\x1bn\xcb\xfe`\xd4`!\x86\xa5\x08\xe43\x05\x12\'\xda\xfa\x9d\x10C\xe9\x17\xbc\'\xec\x11U\x9d\x03\x1c"\xac\x9aC\x85\xeb\xd2\xad\x98\xcf\xeb\xfa\xc4\xdf\xa8\xc1\xd8\x82\x064\x08:\xad\x13_z\xa9\xb2\xc1\xff\t\xad\x9e\xc9\rd\xf8\xf4\x8b`j\xc8E\x90W=\x8a;@N\xb5XuT&gt;\xa7tC\xa3l\x91\x1bSm\xb2t\xa1\xa2\x0fC\x7fR\xc4\xf4\x18\x18\x1fw\xe1\x06~7\x83\xc0\x1c\x9dI\x86\xfcK|\xa8\xf6=v\xd2_\x0f/\xb4\x16/\x0c$\xab\xdb\\:6JB\xed\xd4um\xa8\r\x04\xb9\xccc\x9b\'a&amp;^]\xf5\xca\x1b01\xb9j\xdf\x7f\xd4\x1d\xb2\xf2\xa2\xb2\xdf\xa8I\x1e\xe3@\xb2\xec\x96(-C\xf2\xc96\x1a\n\x06\xc7\xae\xe1\xfe\xd2\xcf\xe7\xc7U\x19\x8ekc\x93dm\x86\xc3D-\xe7\x07\xe7\xb2\xe2[\xfa\xb6\xe9\xbc)\x92n\x9d:1;\xc3e\xc0M\x00\x95$\x05\x1b\xa1\xb5K\xd8\xedgH\x8a\xd1\x06bU0\xc4\x00\x18\xad\xcd#\xd6\xc7\xdfzS\xfe\xe8\x8f\x81F\xfe\x9f:Nh\xbd\xb3\xb4:\xce\xa7\xad%PY\x80h\n\x13\xbea\xefa\xa6\xa6{\xf6\xf1\xe7\xbaw\xc3\t\xba\x0f+c\xe1$\x17m\xa5$\x1a4\xf8\xd2\x8a\xf8\xb7\x86\x03\xdd\xb1ZS\xda\xd8\xa7\xb9\x06n\xedr\x05\xbd\xad\x17\x15{\xa7,8\xf3b\t\xdf\xe3\xf8)\xbc\xc5\xa4:9I\xe4\x8b\xa2\xa2r\xd6\xf8\xda\x8d\n\xf1B\x9b\x1a\xbd\xe9{\x15\x00R3\xcek_\xdf\xefe\xaa\x84&gt;\x00Y\x16\x0fu\xb53\xe1\x1bP\x8c\xdb\xc8e(\xe6\xb8\x1d\x02\xe1\n%\xaa\x892\xfd\xc4AY$R\x02\x92\x02\xa6@q\xb9\xc4S\xae\xaa(\x8d\xad_\xe1\xcd\x01\xdc\x93AC\x93\xbe|M\xa2F\xef&gt;\xf4\xb0\xf4\x89\xb4\xba\xd4\x98\xb9g\x17\x06k\xf4\xec\x1b\xa8\xaf\xdc\xb6\x01q-8\xcf\x18{\x11\xc9\x9d\x16\xab\xf0\x8f\xa2,\xeag\xdcu\xa3g\xd5tdqp\x1d\x0c(N\x06\xac\x96\xd7\x9b&lt;r\xe1\xac\x95\xcb\x96\x94\xf0\x8a\xc2\x8a\x8b\xb7\xb2\xa9\xe9d#\xceP\x8c\x9a\xb1\x8ca\xd7\x1b\x11p\x15\x0cL\xd6\xde\x93\t\x00\xe0\xd0\x08]\xbd"\xea\x00\x0c\xd1\x90\x85\xd7\x89\xdd\xe9o\x0b\x88\x05\xff!zv\x1b(\xed\xde\x90\x00\xe3=\xbb\xeeQ\xdb\xe6\x08\x08\xc1\x8a\xb6Fs\x1a2XO\'#N\x1c$\x8d\xf8H\rZ,\x9cJ_\xe9O\x0e\xa0\x87\xb3\xca\x7f\x1f\x08de\xde\xcd\xa6\x8d`\xde\x9b\x84_C\x84\x8cF\x02\xc8&lt;b\xf8l\x84\x93\x15\xa9a\x8f[yahP\xf9M\x17fZ \x89Zg\x92\x93\x98\x02\xa2&gt;\x88\x1f\x8d\xfc\xdc\xff2W0\xf0\x8c!\x0cJ\xe4\xfa\xebc#\xc0G\xad\xe5W\xf8\xec4\xc8\x97\x92\ry\x12\xd4AB\x03\xe3W\xb88\xf8[R\x9c\xac\xa2\x1bP\x9f\xf7&lt;\x11\xb7\x82\xb3\x95\xd3\n\x1c\xde&amp;\x8b4\xa3\x9c\n\xda\xde-}{\x89R\xd57;E\x04a\xdd&gt;\x17\xcb\x9b\xdf\x86\xc6U]\x14\xd0\x88\xe5\x90\xe5\x10%\xc6\xd3\x1c:\xbd\xac^\xe5\x9c\x8cO\xd7\xf0\xebo\xdb\xeb\xa0\x9a\xa1F\xd50\xd4\xd2\x9e\xab\xac$\xe3\xad\x19o\xf7\xe2\x96r\xcb\xdeR\x92k\x881{\xc4_\xbfF\xab\xd4\x86&amp;9\xad\xd3*\x17\x9b\xfe\xa7\x1b$\x9e\xedM\x80\xc5\xc8\x91\x02J(n\x95\xb9\x00\xb9\xbc\x8cD\xde\xcb8@\x9e\xae\x98\x93m\xd2\xb5Iwy\xd8\x05%4Z\xdb;\xd7\x9c#\xf2\xfav1\xf6\xc3\x02\x88A\x93\xdb\x86\x95:T\xa7Ts\x08\xf0\x1d\xd1\x04\xa0s.\x93-\xc9\xf1\\\x9c\xb08\xb8\xd5\x05\x90X\xf7\x92\xfc\x915\x1e\xfe-\xe2\xef\xbc\x99T+\xefW\xa4\x81\xe2&gt;\x92\xfdd\xad\xeeU-[N\xa9\xe1\xd8\xd5Ai\x93\':\x10\xc5%\xe1\xfd\xcc[o\x1e0v\xd7d3\xc6\x19\xa8\xe4x\x86[\x15\x15\xa5h\xe5\xabq\xbcE\x178\x87\xa5\x9a!~\x128T2v0\xf7S\xcd\x8d\xb6+h\xd1*\x9d\xbb\x02*K\xa8\xea\x80\x89\xb0q=DA\x0e\x1e\x18"\xb6B\xfa{\xd6cX\x05\xfc\xc5\x80\xff\x90\xf79*\xa4n\x1f=\x91\xcd\xaf\xc4\x9d\xd1\xe6O\x99\xf6\xe9V\x04\xfe\x97r\xfb\x07N\x13n\x92\xe0\xeb\xa52P\xaf\xaf\x12\x9e\xde\xb18$\xc2?Z\x05\xa9PjJV\xa4o\xd7&lt;T\x17\xb5\x97\xdb\xa0\xf1\xa8qbw\xf9\xe8\xaf\xacK(\x1c\x19n\xe7i\xf7\x174\xcd\xee\x03\x1cbg\x9b\xde\xe2{&amp;\x87\x9f\x84\x81\xcf\x00\xbf\xf3\x05\xf6zc\x04\xd9(\xe8\x89\xe5\x9d\xe2_~\xce\x1d=\xe5/\xb2\x98\xa2Z\x9b\x8c\xce#\xf4 o.~\x89S\x10\x00kC\x07^\xf3E\x10\x04\xd4\xa2p1\xe1\x9b\x88\x91\x94\xf7&lt;\x93T\xd2\x85\x0c\xf5\xaft\x86\xc0\xa7\xdd\xbdJ\xcav\xb8\xb2\xd7\xa5\xc3\x9d\trI\x96\x99\xdf\x10c\xd0N\xb3X\xdb\xf8\xffS\x82\x03\xbf\xab\x10\x07\xc6\xceS\xed\x00\xd4"Wi\x1e^^Fn&amp;d\xe9\xd14\x1c\xcd\xd5\xab\xce\xdc\x007h&amp;\xc6W\x18\x00\x00\x05\xe9\x84\xab\xae\xe1\x99\xb1c\x0f\x88\xac\xd2\xaa\x99L\xf1\xe5\x1a\xe5\xf4\xa1\xf0\xe3\x14\x01[\x97\x8dbT\xe8\xc1;\x1e4&gt; \xf9\xcb\x19\xb3\xc9\xbc\x0f\x81a\xd9\xfc\x91\x1f6\xf5\xb1\x90J\xac\x98;\xc5\x9fp]\xb2\xb2C\xb6\x1d\'m\xfe\x1a\xffT\xa0+xB\xb5[\xa5\x98z&gt;"}o\x8e\xde\xb2?-BMEz\xfc\'\xd9\xef6s\x19\xd6\xf5p\x97Q\xd6\xf5phFA$\xc0\x1b/L\x9e\xfd\xf4\xa9\x8cZ\x99\xc8@\r\x18\x84m0\xb9\xad\x83\x98[\x8b\x8d\x03\xae\xec\x90I\x02\x91\x0eS\xbaH]hm\'\xb8\x04\xff\x0e\xfc\x7f\x83\xea`\xf1"\xb2bu-W\xf8\xeb \xcf\xc6\x00\x87{\xba\x057\xbb5\xa1\xf4\xcb\xb4W\xa7\'X\xe2\x84&gt;\x12\xe1\x10sf\xa4\xf1S\x1dm\xf84p\xbc\x8b\xae\x80\xc0\xe1-\x93ps\xedb\xdb\xd7`\x86{\xe4\x1c{$\xb1\x16V\x8b\xf1\x9cc[\x0b\x12&amp;\x0f\xd3\x9b\x10\x90\x10\xf2\xb8\x147P\xdb\xb8\x01Y.\xbap0\xc3F\x94m\xe2V\x19&amp;w\x12\x04\x8b}\xc5k\x9b\x86\x00\xab\x85\xc7Y*\xce*j\xe2\x93\xc4\x10\xe1p\x0e|pI\xde4\'\xb8\xb1C4\xd7\xad\xcbVQ\xd74\xf5V\x01\xcft/g\xc5[\x02R@x\x1b\t\xa4#\x94\xd4\xee\xea\x13\r\x84\x84\x1f7\x96\xf9\x06\x10\x02H\xcc\xf9\x0e\x00\x00HF\xb0\xbe\xe9\x8f \x8b\xc4w\xdaj_\x82O\xe9\xc8\xcf\xb6_\xf0\xeb\xdc\x98\xfc\xda\x81NCY\x86Q\x8f\xc47c;8P\xa8\t\x92I\xdd\xbe2\xa6\x9f\xc2\xdd\x84M\x159\xf4\xa5\\C\xf4\xff\x0f\xf6G\xd5+\xd5M\xd22\x83\xc4\xc7\x19 RB\x14\xca\xdcbL\xdcsb\x80\x0f1Z\x0f\xd1\xf3\x89\xf7+\x1c\x06K\xfe&amp;?\xf4\x91\xbd\x14\xfb\xa0[c\x18%\xd1f\x96\xeb\xaa\xb4l7\xbf\xe7\x9a\xdf\x00\x8dr\x17\xd0\xb2$nK\x96\xb2\xe3O\xd6\xe5\x01\x95\x19R\xa4\xe2)b\x7f\x0b\x80\x8a\xd6\xe5\x0f\xb0?\xb4.\xb8\xee\xe6\x19\xc6\xc9V\xbb"\x0c\xbf\xa6\xcf%\xfdv\x80)\x86\xc4VX\xfb&gt;\xa0N\xd7\x04\x8e\xb3\xb2\xc9g\xa7f\xc7\xfb\xfe\x97\xa9\xa8\x97p\xce\x8d#\xee\x80.5\xa2y\x1e\xdb\xd1;\xa8~\xaf\x8b&amp;M$\xdav%\xfc\xc4\nYGz\xcd\x99\x92\x94IKg2t\xf6\x81\n\xb8\x80\xa8\xae_\xe6\xc0\xc1cG\x9c\x18\x1c\xc9\xf4\xfd`\xc5\\8\xb3\t\x87?\r%\x9a\xa8O\x80\xb7,\r%\x89\x17\'\xe4E/o6\x0c\x19b\xedJm\x8be\xad\x13\xcd\xd69L\xf6a\xd7I\x8a\x91\x154\xb2\xe8B\xd8\x91pZW%Q\x92\x00\xa9\xd17!1BY\xc6y\xe5\x84\x16\x08\x12\xf8U)\x83\xd9\xcd\xa0q\xccM-\x97r\xbeM\xec\x8b\xf0\xec\xa8+X\xff)\xd9\xf0;4\xc2\\~nk\xfe\xaf(&gt;\xd1\xd0\xeb\x00R\xe1.CWR2k\x87\x05`\x89\x0e4sL\xc4\x9bg8\xa5\x86;m\xa2\x839\x80S\xc6\xdf\xb4\x1c\xba\xd5I\xa9\xe6\xae\x06$7\x99\xd5B\xc6\xbe=\xc0\x98\xc2\xa0\xccf\xa0\x10/\x9b\x91\xda\xe5\x84\xff*Q\x97\x94$-\xbd\xd1\x1a\xe5E_gv_\xbac\x93\x92%\xa0\x91\x9d\xa5F\xfb\xf6z\x1d\xcag\x10\xfbN^\x1e|\xd6\xf7\xb1\\\xaa\xe0ur\xb4\x8b\xd6O\xc8]\xabb\xca\xdbD\x96\xed\xadw=@\xcf\x1d\xe1\xc0T\x1b\x83\xbe\xa6\xa7\xa2F6\x8boA\x0cN\xe4qo\x89\xc9\xf0\xc9\x91F$\x87)\x9cT\xb9\xac3\xfb\r u\xb1\xbd]\x1a\xc5\x81\xad\xea\x15\xb6n\'\x87c\x8a\xbf\xb3mT\x87n\xde3\xd8Sd%\x86=\x83b\xc1\x96f\xff~\x86\xa6"\xab\xb6\xa8#.o\xd5\xdb\xbe\xd2\xd9L\xb2\x9e\xd4`;u\x00\x89`\x02\xdf\xbfT\xb8%r\xda\x88\xd0)\xb3\xeag\x98h\x82e\x08\x0b\xdc\n\x05\xc0\xc1\nI\xe9(\xd5i\xf92\n\x99,\x00$\x95\xcbZj\x98\x89]\xf9\xd7\x9e\xec\xf7\xb8:\xe6\x14\x17\xcc\xfd\xee\'3?-i\xaa\x1b\xaa\xbc\x85\xe1\xe0\xc8\xfb\xaaA\xf8\x0b\xad\xad)S&lt;\xf1\x1d\xb6\xc5\xd9\xab\xab\xf72~b\xd0\x15q\\p\x92\xdd\x8c\xcba,.\xb1\xdc\xd4u\xc8\xb2\xf5\xe4.\xcf\xfb\xfd\x17\xea\xe1|\xfapdt\xed\x7fl^\x0f\x8e3\x0be\x86\x08\xba\xbc\x17\xeb/\xab\xcd\x8ck\xc4\xb5FH\xcd\x11\xd6\xa3\x10j@r\x9f\xed\xf4\xb3Qsg\xd2\x06Z$p\x86\x9d\xb9.z\x04\xc0\xac\x1eZA~k(\x04_\xa9h\xdcb\x82P\xf7*\xf6\x8e\xf1\xe1\x81\xf3\x99\xae\x87PtL\x83\x0e!*y\x08\x98\xb5\x93\x96\x06C\xf5}\x1f\xa5p\xee\xa0)X\x07~\x12Y\x98n\x02B\x00\x11\x10\xd42\xa8Q\x80\xbb$\xe4p\x85i\xda\x8f\x9c\x9e\x8e\x0cO_\x8fMxKy\xbf\x8b\x8ad\x92F\xc9\xdf\x86\xa1\xe2A\x93\x1b\x9d\x1f\x9bt\x10K\xe5\r\xa3n.\x93\xd1\xaf\x8e2\x06\x02o\\\xac\xa5\xa9\xa0qyW\xd0\x84EM\x98g\xf9\x9a1\x12\x9f\xb6\xfbD^$\x87;\xf4\xab\xc2\x95N\x8d\xa9\x19\x0b\xd6\x8b\xb8\x1c\x03\x1eJ|;\x93\xf6\x02H\xa9m\xa1$\xa1\xfc\xdeP\x12\xf1=\xf9*\xcf\xef\xe2\x10O\xffLXZ\x14*\x9e\xdc\x13QE\x8dG~\xb82\xd9\x9e\x1a\x92UU\x05w\x7f\xa3\xa2\xc1gy\xcd\xa9\xe9H\xc6I\xe2)\xd7\xa6\xb5]\xeb\x1c\x02V)\x94\xc9O\xcdWm\xa8S\xfdO\x96\xf9=\xcb\xf6\xecB_\xff\x06\xdfZ\\l3l\x1a\xc0\xa1\x8d\xb9\x15\xc6\xc4\xd8&lt;\x17.;Yt\x81pUl`\x00\x1e\x1f\xf8\xfc\x0b=F_\x14\xc1\xf1\xc8eg\x00h@\xedO\xcb\xe9\x9a\\T\xfa\xa7T\x8e_\xe3.v\x85\xe3\xcbK\xf3\xc2\x06n?\xff5@\xb3F\xa3\x08\x8ao[\xb1\x9c\xe7\xfc\xc8hZ\xfc\xf9\x0fP\x94\xe2\x17\xfag\t\x0e58w\xe35\xe9D\x0cC4\xe9\x94\x06\xb6V\xe2-\xe7\xfa\x1d^\xf7q\x7f&gt;\xe1\xf0Q\xa6R\xf4\xfe%\xa6\xdc\x94;\xa2\xa3\xf5}\xba\xd0\xda\xa4d\x9c\x9d\xbb\\\x96\xb0\xe4\xe8\xf3\x03\x1dD\xe8\xeb\xf5\xaa+x6\xff\xd2\xc9\xb2s\xb6r\xe1\x1b^_\xc38\x86\xca\x1a1ib\xf76DEq\x98A\xd0G\xff\xb7 \xce\x81\xcb\xcf\xf2\x85\xef\xfez]~_\xa7\xb0\xc5E\xc2Z\x99\xfa\xce\xfc\x92n\xe2\xa0\x9d\x8d\xb4\x9eM\xe7\x8f\xcc\xfek\xa6\x9d\x1f\x9e\xa9!v\xc0\xfb!]\x05/9xv\x04&lt;\x13\x86\x16\x03B\xdd\xb5]?\xa9L\xc47\x8d\xbb\x9c*\xf7H\xc1)\\?e\xff\xab\xc6\t_ C\xe4\xd8\xe7\xcc[\x7f\x80{\x0ba.\xae}\xf4`\x18\x13\xb6\xac\x9f\xcb]\x92\x02\xe1\x1bX\xff\xbe\xd8\x828\x92\xc8\x9e+\xbd\xe3\xba\xdap(\xf7\xa1\xe6G\xba\xcd{\xd0\xa7\x1c\xad*&amp;\xfd\x9bkkBQ\xed&gt;?L\xa2Z\xf1\xf3BR\xbe\x9c\x89\x17Y)\x9d\xb0\xbc\xce\'7\xad\xa7\x94\xd2?&lt;8\x16n\xbf\xa2\xaa\x1d\x99\x8f\x8c\xbe\xbe\x86\xea&gt;\x1f;\xd8t\xdd\x06\x99\xe6hjgTD\r\xcc+\xa0\xf97\xf6\xc1\x88i\xe9*[w\xe0\x8f\xb8A\xc6Z\x91\x9b&gt;\xb1\xf7\x8d\xcb\x13\x99\x15\x92\xf4P\x04\x0f\x13\x8d\xdd\xac\xa3\xad\xe6\xc8\x9b\xdc9\x97\x90\xb2\x13\xe0\x8c\xa9\x1c$B!\x98\xe3Sc=\xe3\xde\xb9\xb6+j\x1d\x1d\xd0\xcd\xfe\x07,\xc6\xb8\xae4\xbfk\xc9\xf7\xff\xf2\xa2\xc6p\xa4o\x17\xcc\xfc2l\xc6a\xd0\x9f\xa7\x901\xf1\x8d\x9d\xc2\x010\x84\xb07\xeb\xf8\xe6\x8c\xb8`\r\x80!tbe\xe6%\x07\xc3\xa8}|\xbd\xa5^\xdb\xe3\x1d\x1dR`\xe8c=a\x80\x80\x9chN\xaa\xa8++\x05\xb3\xfa\xd1X\xff\xb5\x90\x98j\xf1\xd9\x90\xdd\x03\x05\x8f\x86\xec0\x9e_\x10\x88\xe5\x13\xceEMccy\x1d\xa7\xc1\xef\x8a\xe8\xec\xafD\xf5\xf0\r\xce\xe4,\xbf3\xf8\x85\x97\x97\xe2\xe2\xf4Ko\xec\x95\x88\xc0!X\xe6\x08\x96\xcb\xae\xd5^^e\x17"\xc0\x03\x02\x04\x06\x8a\x1cc\x836e\xc1\xd1ja\xe7\xb7\x07\xca\xf3\xa8{\x02E\xe9\xfa\xdf\x9b\xc8\x82\x04\x07A`\xd7\xd8\xfa\xade\xe4&lt;\x97\xf3J\x7f&lt;\x1f\xa5\xc4\xb0\\\xec\xa5\xb4OE\x81\xe5\xd6\xe9\xeb[\\br\x0e\xd5\x83\xf5\x89\x16\xb1\xd4\xe6\xe4\x9dr\xa0\xa6^\x1e&amp;/\xc9\x00\xe8\xd8\xcd \t~7\x97\xbc\x88`\x00e\x0c!\xe1\xc6\x97\x94)^*\xb3\x98V\xdf\xfa\xdb\xa2d!\xe5\x16a/\x0b[\xe8w\xdf\xab]\x8e\xab\xfa&amp;,\xafOuU\xb2/\xfeK\xb1\xd2U&gt;}\x17\xc5\x7f\xb8\xb7\xd4\xa90@\xedVi_e\x18\x1e\xda\x1a\x04\x8a\x12\x08y\xf43\x00\x80;\x8e7\x9c\x9f\x99\xe9\xba\xfba\xe2\xc3\x1a\xff\xe11^\xf6\x89B\xfa\xc3W\xd2\xd2sx\x1dF\xe3\x89+jJ\xc1\x9c\xfa\xba\xc5/\x9b\xb9\xbc\x84\r\x7f\xb74\x91j]\xae\xab\xec$i\x151{\xa7\x9fH3\x7fTB\xab\nZ\x1c\x95\x986\xde~\xf5\xc1\xc3\xf1\xa8\x8f1\tcII.daD\xf2\x1fG\xfaY\x05\x89t\x88f\xca\x81A\r\xf1\x02\xde&lt;#\x19HOZ\xf2\x9f)\x1b.L\'w\x1b\x10&gt;\xcb\xa4\xaf*Y?\t\x81\xa1\x96\xba\x80\xa5\xa0g1,r$\x0e\xc8\xa7?\xf5qV\x8d\x91c\x83i_-f\xc4s8\xbb\x80P\xb3\xe6\xe7NY\xfd\xf2=\xe1\xdf\x98\xa6\xab\x0c\xbb:L\x8e\xdeY\xd5\x8e\x95\xaf\xc6\xe7\x879\xad\x7f\xf3g\x03\x9at\x0b\x7f\xd3R\x91\xd8B2\xe9\xaf31\xe0\xb5\x0b\xea(d\xf4\xc9\xb2\x14\xc9\xf3\x14\xa4\x19\xad\xaclN\x0b\x1a&gt;\x1e\xd8\xa2\x7f\xc5\xa59\xf3\x0f\xff\x8b97\xab\xf0I\x1bO(\x1c\xbf^\x88\x99\x18I\x1fgX\xba\xe1\x0f\xdd\x10\x17&amp;P\xce\x18\x99\xaf\x81\xc8o]|}&amp;\xc80\xb6y0d\xfc\xe9:\xde\xd1\xd9#l,9[\xed\xa7\x9f\xf6\x81\xa2\x11\xdc\x81\x14\x16\x90\xa5n\x11oK@\xac\xb1\xa7\xb1\x00\x01\xe4\x00%#l\x97A\xbf&lt;\xa9K\xa1\x06\xea.\xc7\x9d\xab\</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Klm Kit Sds Plus Martelete Ponteiro E Talhadeiras Jogo 3 Peças 20mm E 40mm Compatível Com Todas As Marcas</t>
+          <t>Kit 4 Camiseta Dry-fit Sandrini Masculina Academia Caminhada</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>59</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>135</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,219 +649,249 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>47% OFF</t>
+          <t>41</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/klm-kit-sds-plus-martelete-ponteiro-e-talhadeiras-jogo-3-pecas-20mm-e-40mm-compativel-com-todas-as-marcas/p/MLB47892578?pdp_filters=item_id%3AMLB5360733834&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB5360733834&amp;sid=affiliates</t>
+          <t>55% OFF</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_694311-MLA109933866197_042026-AB.webp</t>
+          <t>https://produto.mercadolivre.com.br/MLB-4592320910-kit-4-camiseta-dry-fit-sandrini-masculina-academia-caminhada-_JM?searchVariation=186408020317&amp;pdp_filters=item_id%3AMLB4592320910&amp;extra_comm=true#polycard_client=affiliates</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>b'RIFF\x14,\x00\x00WEBPVP8 \x08,\x00\x00\xd0\x10\x01\x9d\x01*\xc0\x01\xc0\x01&gt;m4\x96G\xa4#**\xa5\xb2\xeaQP\r\x89g \xbe\xf4\xb9\xc6y\x98\x10\x07\xbb1\x0e\xdby\x8f\xday\xd9\xe5\x11\xe6q\xa7\xe5/F\x17\xc6\xff\x9b\xeb\xf7\xfb?\xf8\x8fW\x7fM\xfe\x9d|\xd0\xf9\xb4i\xcf\xf4T\xfa\xd8`\x95\xfe\xd4\xf89\xc5\xbfE\xdc\xfcw[\xfb\x8fj\x9fc\xcf\xb6\xfc]\xf1\xf6\x00\x7fU\xbf\xe8zv\xf7_\xd2_\xb5&gt;\xc0\x1f\xa9\xff\xf1yY\xfe\xd7\xff\x8b\xd8+\xf9\xbf\xf7_\xd9_y\x9f\xf7|\xd8\xfd\x81\xfbW\xf0/\xfb\x17\xd7\x07\xf7+\xdaD\xa3\xb0\x12\xed\x80\x97l\x04\xbb`%\xdb\x01.\xd8\tv\xb6\x16#T\x06{b\x97\xb9\xa9}\x16\n\x99J\x96\xf1?c6O,\x8c\xecW\xb2W\x190\xb8\xc9\x85\xc6L.\t8\xf9\xf3\xa3\xf0\x98\xe3"\xb5\x18\xbd\xddTt{\xbb\xb0G\x90\x10g\x8co\xff\xc8\xdb\xcd\xb2+\x85&gt;\xe8\x85\x0cam\xa1\x9e\x82\x9dY|\x8808\xc6\xe9d\xc2\xe3&amp;\x17\x190\xa2\xbbu$\xa5z\x8e\x15F\x9al\x1b\x98)\xf8\xcb`\xb5\xfdg\xd9\xda\xda\xe1\xfb\xd3`a\xcb3\xfc"\x99\xbf\x9b\xea\xa0?\xff\x1b8\xab\xef\xc6\xbf\xadg\xa0M)!\xfb\xb3\x9eN4\x165J\xc5!)\x81\xd6L\x0e\xa5\x9ata\x93\x1d}\xca\x81\x0f8\x92\x14\xc4AL\xf4\xfem\x04\\\xaf\xfaB8`\x8dW%\x86Z\t\x00b\x8d\x8fz\xce_\x19F^\xe8\x92\xa6\x84\xf1\xd0\x9c))B\xfe\xdcs0\xc8\xbf\x92\x18x\xf9s\xe1\xeb\x87\xfdDk\xaa\xa4\xae2aqt\x12\xd4Zt_\xcb\x12\xaa\x98\xf6\xf2\x05\xc4Uhd\x93\xd0;\xbd.3\xe99\xa6\xef?\xdd\x8e&amp;\xf8\x9fo\x82,.\xdb\x07H\x83\xe4\xf8\xefD\r\x01\x18Y\xde\xbf\xff\xfaMI\x83\xe7z\xafU\x05\x8a\xde4I\x90\x95\xd9Meqg\xb5\xdb\x04\xe8\xf9j$\xd4T\xf7\xeb\xf7L\xb2p:\xc9~n\xfa\x1f\x83\xa2\x80,\xc6\x8a\x1e\xfeY\xff\xaeaq`\x0b\x90\x01\xa4a\x06\x02\xd9\xee\xd6\xd7&gt;\x073\xf7=,\x85\xd1y\xb9\xbfyz5c\xd5\xdfH0\x7f\xcc\xef/\x92=0\x87\xe3\x9a\xce~\x06\x9fo\xa2c\x18Dq\x94S\xf5\xc9\xfd\xef\xe0\xf3/\xd6\x89\x91\x1e\n\xe6\xd5\xaf\xe3\x92S\x04\xb2D\xe1\x96\x1e\x7f\x84kk\xf3\xc9m\xd6Y\x92\x9c`\xcc!\x9e;\xd73\xd2\x04]jh\xa8(@\x9c\xc9\xc9\xc1\xb5\xdbW\xa9W\xbf\x95\xecD5\xa9U\xbe\xcdn\xbe\x12\xa2c]o(6\xb3\x96\xda[\xdb2Wd\xbbf.&lt;\xb7\x8c\xb9\xfa\xb8\x08\x88\xf8\xec"\xe9\xf6\x1d\xfa\xfaY\xadQRY\xd0c\xaa\x7f\xe2\xcc\xc6D\x93\xcf).\x81\xa3\x16\xb4\xe7\xa3;\x11\xacJ\xf4\'\x80\x90\xa1u\x06\xb4\xb6U\xd9\x0b4\r:\x94\x1e\xcc\xd9~\n7\x08\xbcrLm\xbe\x8d\x8eul1Vw,\xb1\xd8\xdc\xbf\x08\rW\x02\xa6z7Z\x16\xb2i\xebG)\xa1G[\xd6\x95\r\xc3\xea6\x8d\xd9\x109\xac\x92$!\xee\x96\xfb\xf3\x94\xb8\x0b\t}\xe4/\x0bw]\t\x18\xe4\xa9\xf9\xbdm\xd0\x0f|\xc0\xa2\x9d\xdee\xb68\xdb\xbc\xb9\xec\xe1\xa9\x08AM\x917\xd6\xc2\\%\xb9\x9f\x0e\xb5E\xb4FH\xad\x13\x11\xeb\xa6\x06am\xe8\xa0\x05\xad\x96r\xf5\x8f\xbf\xcc\x00]C\xbb\xa8\xc4\x04^\xf2BB\xfd\xf9\xa2\xd5\xd6+F\xc4\x19_&lt;\x9d\x85!)\x10\x0b\xb8r\x0e\xee\x9c\x98\xba\xaap$H\xe6\xcb\xd3\x07\x019\x8aZ\xd9\xb4\xdb\xeb\xe4\xf8\x1cg\xd2\xe3\xd4\x8b\xb21\x04\xbd\xc8\x0e\xacA3\xe3\xde\xc0\x81\xa8A\x87\xaa\xf7*k\xb4\xc53\xfe\xb6-\x82\n\xf3\xa8\xc3\xb9\x90\xa2:\xde\x0e\xc5\x98z\xe4\xdd\x14\xb2\x1346\x94@|\xbd|\x0f\x86\x070\x0f}\t!\x9f7\x14\x92l0\xed\xf0`s\x1eFe\x87T:\x9dpi\'\xaa\xcd\xc0\r\x1d:\xe4&gt;\xb4\xda\x8fm\xdd&gt;\x97\x0c\xf6\x95\xef\x1d8b&gt;=l\xc2}$\xe4\xb0Y\xe5\xd5%\xa8\xdc&amp;\xce\x9c\xc0C\xca\xe8\\\x87\xee\xee\xe2\xa9o\xees\'\xb8\xc0\xeb\xf0Y\xadw\xe5\xcc\x9e:\xcbU\xb4\xa7h\xa68&lt;\xcb\xfc\xcfh!"b\xe9J\xc7}\xaf\xcd\xb2\x0f~&gt;\x87\x84\xa2\x8fF\x9e\x13\xab\xd5z\xf9\xf5\x1e\x16^\xd8\x8bNBk\xe0\xc4\xd2\xce\x06\x15;"\xaa\xbf\x088M\x9e Q\xf8\t\xe0v\xa6%\xc8\xd8\xe6G\x8d\xc7\xb2\xf5\xe6\x14\xf3\xd5\xd1~\xe6,!GC\xb5\x8e/\x17\x8e\x80V\x90b\x16_\xb1)w\xa7\x17\xd4\x18\xc2&lt;V\x13\xc3C\x01\xd3\x9aVo\xce\xfa\x9b\xd5{\xc1\xed\xb7\xbcr\xb1V\x07\xad\xa2\xb0\xf9\xcdhCt\x98Z&amp;\xec"\x9c\xe3"\x87\x0b\xbcMo\x93\xf0\xae\n=\xd8\x16\x94;\xcd/\x02{]G\xee\x08\xfc\xc3\x02NQ\x96E\xd2l&gt;\xe7\xc9\xc6\x8a/\xcdM\x18_\xb06m9F\xa8\xd5\xee\xee\xfd2\n\x87\x9b\x94\xcd\xc5|\xf1W\x9b\xc9v\xcc\xb5\x91SU\xa7,\x88\xefI\xe6\x7f\xdfO\xa1\x9f`\xad\xcd#o\xcb\xc1G\x16t\xbb\xce\x9d&gt;\x88p\x04Z\x01\xb5\xa9\xfaJ\xd7\xb6\'\x92\xc0p4\x9d\x7f\xa4\x06B\x0e\x1dV 6\xf0\xe83\xf9\xe8D\x8c\xf1\xf3\xacZ\x9e\xd7\x1a\xed\xeb\xc9\x1d\x9e;tf\xcaL\x9f\x82`\xf0*\xfa\xa5\xbe\xea{\xd0\xb6A\x96\xafC\xb4\xef%q\x89h\\\xdb[j4wV\x92l\xa6\xa1\xadCe\x08\x89\x1c\n\nA\xa2v\xd9VR\x99\x82\xa3,\xb6\x95\xec\xc8\x0f\x005["\x93d9\x95S\x10\xda\xa7\xc4)\xde\xe5\xa6\x1e\xaa\xca\xb6j\x87\x91\xedJ\xeeg\x03\x01QQ\xea\x05 0 \xa0{\xab}\xac\x1b\\G["$\xbb\xbf\xa5n-%\x99M\xfb\xec_\x10@\xce\xae\x11\xf8\xe3\x893N\x88\xb1\xbf\xdc\xd1\x93fC\x7f|s\xef\xb79g\xbet\xf4#\xd3\xe2\xf1\x9a5\xc2\xa7e\xbd\x13\'^+\xea+h\xf4\x16w\x99\x92}\xceV\x93\xc7\x9c\xcd\xa6\x01\x08Q\x87\xda\xa3\xb2\xd8~1B\xc85\x0b\x95hc\xf2_\xad\xea\x17\xa1\xf7N\x17\x7f\x95DQ.\xf7\xf24n\x9b\x95A\x18\x7f,\r\xec\x98\x9f\x98\xec*\xcd\x7f\x82\xdc\xd9\x17\xe4q=u\xbe\xd1\xe7\xc0\xc1\x90\x16\xb2t\xc8\x9c\x03&amp;\xcae\xb8d\x18\\\xda\xf8\x90\xdb\x85\xf3\xc8\xf9\xd5\n\x19\x06\xd7\xc4h\x84\xa7\xddB\x02\xfcG\x9e\x1b\x08m\x87v5M\x8a\xc9\xbe\xcep\xf2\x02QD\x92\x18\x82\xbcX\x13on\xf0\x0fzl\xac\xb2\xdd\xfe\xd0\x84\x06\x9f\xd0tQi\xccR\xa7\x97\xa1\xa2v\xf2\x8cZ\xa5\x80\xad\xbf\x99I\xd1Z\xc0i\xf5\xfa{\xe0\xa8v\xe4\xac\xb7\x1f\x99\x1d\xc6\xbc5\xbd?\xe0\x9a\x99\xe4,=\xb4\x88\x0fHq\xc5\xa9\x14i\x95\xc1\x11\x19\xa4\xdf\xf3\xe2\x89\xaf\x17\xc1\x01{\xac\xd8\xb5\x19W\xc2{\x15e\x18!G\x06#\xddf\\\x89\xb7\xf9\xfdnv\x8b\x82xp\t\xfa\xe0Z\xc9wz0|\xc4-i1\xaa\xe2^\xdb\x13T\xe3\xb8\x04\x83\xcdE)\xbe\x11\x08\xa6\xdbJ\xb1O\xbd\xf0J+\x94?(w}d\xfa!f\xb7\x94S\r)\x14\xc6\xb7\xfb&amp;\x91\x9blPA\xdf\x89\xb9\xe5\xde\xfc{\x12q\x90\x813q\xf4\xafq\t\xbd9Y\xf1\xb5=5\x87\x12z4\xdc8\xa2\xedu\xd7\xf6)\x9e\xa0\xb1\xa6\xe9r\xdc\x04\x80/Vh\xdd\xa2\xd5\xe8\xd2\x07\xa3\xba\xda\xda\xb8@\x12w\xcf\x1a\xffP\xda\xa5\xdb\xc9\x9e\x128\x13\xc1\xeb\xd2O\xdb\xe6\xfa\x19\xd1$\x10\xc5\xf9\xbc\t\t\xcc\x02\x1e\xafrp&amp;\xf2q\xee;\xf0X\x8c\xa2\xb1\xa0\x80\xb6K\x15\x85\xb87Z\x96m\xb4\x8bz\xe6}\xd5$\x88\xf4\xfc\xa9,M\x8f\xde&lt;L\t\xc1lf4\xd6\xfc\x8b\xa5\x96I\xcb\xae\xf7\xfe\xd8\x19\x15\xf8\xeb\x99\xa4MsV\x8aCWr\'`R+\xaa\xa6\xc7\x7f\x1aj\x9bmk7\x92\xfdt\xe99ge\x99_dLr\xee\xb1\xf3\x9b\x87\x067G\x8b\xab\xb7\xafn\x95w~\\\xb9\xf1\xdal\x8d\xd5h\xf9\xf7C,\xcbO]\xb6\xe95[\x95\xe1J\xbb\r}n\x8b\xcd\xac\xfc\x98\tv\xaeO\xa4M\xae\xc45\xc1\x17]\x95\x9e/0\xce;\xefA\x10tn\xb6\x1b\xb97]\xc6{\xc4\xbch\xd2\xd5X\xd4\xc1\x00\xfbn\xd46\x0c\xff\x07\x14\xfc\xc1\x0c\x81\xe5\xf1\xd8\xd4\\d\xc2\xdd\x1cJ\xed\x9ajY\x9c\xb6\x8d\rY\x90\x8d\x01\xd8\xcfG\x80\xc0\xb5h\xf0\xb4\xfc\xd9`N_\x1d\xe53\x9a\x8d6\xf5\xa0\x07\n\n\xfc\x19OY\xa4\xec\x04\xbb`%\xd6+\x10\xad\x06W\\\xb12\xf4\x00\xcf\xe8\xee\x1fG|j\xf9jc\xb0k}p\x02-\xe4\x83\xbbe\x87B\x07\xf7\xbd"\xeb\x1d\xf9d\xc2\xe3&amp;\x17\x19J\x1b*\xe4\xd9YqP\x00\xfe\xf7Z\x00\x00\x00\x07\xd8\x18\xe1A#:\xd2?\xba\xea\n\xd7e\xdaS\xf7\xb0\x1f)\xe0s\x8d\xcc&gt;\xffN]4\xc5\x93m?\xa7\x11\x0fp\xad\xe2z\xd2\x12\xa6^\xde8KA\xc5";yI\x9f"\xd1\x96\xae\xcc\xaf\x02U2G\xd4\xcdGQ\xea\'\x9e\xd0#\xbe\x87Eb*\x11[\xbc\xd4U\xa0+r\xd9J\x15\x9d\xe2\x16\xdf\xbc\xa0Y\xdf{\x8b\xdd9;\x8f\xa0\xdcO\x9b\xd4/\x9d\xf6\xa5 \xee\xe8yo\xfb\xf6&gt;\xbc\x1a\xa3\xe5BG\x7f\xfef\x10\x0c\xc6\xf2V\xe3uc\xd85\xf7O\xa7\x7fYY\x1cK\xd8\xa3\xc1\xa4\x9a\xbdj,\xd3`\x9e\xe6M\xbe\xbb\xa1\xd0.\nd\xc6\xfa^-/\xd6\xda\x00\x04\xf0$\x0bh\xdd\x11^\x10\xf9\xe2\x9fOV\x82O\x17\x9c\x9e}\xa9\xb7\x0fX\xc7\xf9\x00\xdc\xb7L&gt;\xf5\xb4\xacO\rh]\x86\x82(\x1dmJ\xbeS\xcc\x92\xf9\xa7O\xef\xc0\xcf\xb1&amp;`\x7f\x1c\xa8\x0c\xb6\x08\xdb\xbd&gt;S\xc6p8}\xf7\xc7\xd7v*\xbb\xdd(\x81\xb0!y\xd4\x06N\xbbr{\xf5\xa1\x11\xb5\xd9\xc9u\x86\'u(\xab\x9f\xc5\x1f\xfc\x15\xba\xea\xf5\xf4\xad\xcc\x8f{\x88\x8d\xa2\xe4\xe4\xdf\xaf\x1b\xf87\xd0\r\xc8\x1f\xdd\x03\xb1\x94t&amp;q\xbe\n[=o\r?\xd6\xfbj\xa1\x16\x98\xffJ\xe9\xdfu\xa5\xe8\xe8\xc7C^(\x97275+\xff\xda\xf4\x85{\xc5&lt;\xdc\x7f\xa4\x980\xc7\xa0o8wJ\xba\xac\xab+\xea\xb3\xc4\x14\xed\xdc\xd8\x83\xf5du\xe5O\xbc\xfa\x04\xdeF\x08\xd7\x93\xf9A\xe2\x99D\x13\xfb\n\x0c\xfe\xa1\xc9\xd5\xdd\xa5\x8a\xd24\x05\xf5\x8a\xca\xf0y\xf3#\x16\xc4*H&lt;\x98Q%x\x850\x9eVh\xf2\x0c\xddUZ\xa1#I\x04H\x14NCEH@\x19\x18\xdbP\x97\xe6\xe4,4\xb0\x94\xf0\xa8\x93\x1fX\x80\x00\x03\x89\x17\xbct\x12\x16x8;Y\xaa\xb3\xb2\xb4A\x7f\xa5\x11\x02\x1a\xf7\xb2\xef\xd0\xb6\xe0u\x943\xdal\xf0jS=\x0cef&lt;\xa3l\x0e\x1ea\x1f\xb9g\xf5\x90\x1c\x92#\xa8.\xef&gt;\xbe\xbb\xaa\xa7\xda!\xcf\x9e\xbe;^\x8d6\x9bL\x04\x86\xedi\xca\xd0&gt;\x11,\xdc\xf3\x8c*0\x0e\xbf\xd0e\x87\n\xc9\x0f87xrs\x1e3+\x9d._\xc2\xd4\r\n\x95)M\xc87\x8a\xf3y\xc8\x86\xd5\x96\x8b;?\x8e\xc7\xe4\xc6Z\x1e\x83\xc9\xccJ`I\x8d\xbb\xe7\x04E;{H\xbdj\x9a*E\\\x10\xce\xd9\xffc\x12S\x16B9xO\xf34\x8bUY\x86%pe\xd5\xd4_#\xd3\xe6\x9d\x7f\x95\x06\xb5\xaa\xad\x14\xf9\xb8\r9v\xd8\x1c\xbb1si\r\x13\x8f"\x15SI\xc8\x8f)"\xb1\x0f?a\xce\xd7\xb7/#G\xe7\xafZ\xf9\x07%ali\x13\xb5\xf6\xf1\xb7\x01\xc8(\x0fF+\x87p\xc5\xc4Gf\xf8c]\xaf\'\xe8\xb4\x9f\xda|\xb8\xf1&gt;\x99\xe7\xd5\xb6\xd9\xb0\xc8\xd3\xc1\xc4*9x\x15\xe5\xef\x11D\xf5D,ukR\x99\x91\r\xc6\xfff)\xeb1y\xb5\xc28:\x1a-\xd5\xbf\x02&gt;\x1e\xc1\xceJ\xe4\xe2\x83\\\x1f\x10\xbb\x15\x87\x1e\xe0oNB/I@\xce\xb6v\x97S\xde\xc8Z\x00\x0c\xbd\xc8AE4\x065\xe6\xa5\xc3\x87\xa3\xde\x95P\xce\xfd\x13\xe9\x04\xb7"7y\\!:\rg\xff\xc3\x99\x19R\xa3\xdb\x96\xed\xcd\x9e\xd5C\x14\xb6\xed\\\x01\'\x86\x85\xee\x98\xf4\x91\xe3\xa8\x18\xceV\xb4)\x16\x11\x16\xa9\x84?\xa2)&lt;\xf3t\x9f\x9c\xdc\xf5r\x1bmJS\x98V\xe6\xe3\xd9\x13\xe8\x0f /&lt;\xc3\x1c\x97\x9e\xdehB\xd2\x12Ag&gt;\xd7\xa5r(\xbb\xcc\xd1\xf27\x8d\xf7A\xb3\xa9\x8eK\x02\x16z\xf0\x99\xf0\x1dHK\xc2\x90TI|t\xe5#r\x98\xb4\x81c\xef\xb0Sy\xf5\xebf&amp;\x84\xa7ex\xe7T\xa6$\xf7\x81W\xa0~0\x13q\x18RY\xb7r\xa7\xc8\xbb\x9e\xa0\xc7\x03*\xfe\xc0r\xcb\xba\xc7\xe1\xb6\xf4v\xfe\x8e\xe7\xbbJ\xa36\xe4\xd9\x17\x18[m\x17\xdf\x144F\x8d\xc6A\xf9]\xd5Re\x0c\x17;\xb9!\x96\x06m\xaf\x16\xb8kp\x8f\xac\x95Sk&gt;f\xcc\xe6-\xac\xa4\x89\xcd\x81\x97\xd9\xa72\xcd^\x9c~\xa6\xec\x19w\x86\xf1\xf4O\xde\xb7P\xe0\xc3\xa4\x9f\xf0\xc9!\xe3\xb2|A\xedg\xfe\xa0\x94\xb3\x00\xb8\xf9#\xe1\xac4`\x1b\xf0\x98\xfe\xf3\x84\xa1I\xacIU\xaa\xbbz\xc9x\xd2q;\n{\xec\x93\xecZ\x1cZ\x14D\xb8BL\x86\';Bj\xb4\x8cf\xf44\xc2\x9b\xbb\xd3\xd8*8\xd9\xc4\xde\xec%\x1a\xf2\xf1\xf8\xe3\xb9\xce24\n\x1bv\xaf\x8a\x9c\x83\xec\xd3\xd1C\'\x99F\x06\xaf\xaf\x14*\xb5\x898l\xa7AP=\x855\x12\x1djHGK\xadP+b(\xea]\x85\xf7K\xd5=\x82Vf(\x16\xfc=\x12\xcfJ\x14\x82\xcd\xed\x15\x8c\x81\xa6cP\x035\x99\xf2\x82K\xda0\x1bn\xe5\xebe\x03+\xe7\xd7U\xf8\xd0\x8b\xff\xc9\xc9\xe6a7\xe0\xe2\x97\xde\x8dRw\x88JD4\xcb\xf8D\xc4\xcc\xbb\x99S\x12U\xe0h|9\xc4\xbb\xe9\x06\x85\x9a9\x9fO\x92\x81\xd4\xa2\xbf\xed3\xc6\xa5\x91\xd9F\x9d\xa4}[9\xd5\xe3|\xd6\xd5lb&amp;\xeaa\xa2\x9e\xef\x1ej\x8b\xe4(\x87#\xdao5b\x86i\x9a\xfa\xf0\x8a\x9br\xc0\xec\x99-4\x80\x84xy\xe8\x0b\xf0\xe9\xfd\xa74\xd5N0\xeb\xfb\xfb\xc0t(X\x99\x9d\xbaf\xa7\xb7\xcb\xf0\xd1&amp;n\x18\xb3+\x1c\xd9\x0e\xae\xe1\xd9H\x91\xce\xc8\x10\x0e#\x17\x98\x1d\x01\xb3\xf7\xbc\n\x16\x16\xe8o\xc7\x14\x1cP\xc3\xb0\xe4\xfbPs`M4\xf8\xe5\x13Q\xa1\xbd\xba\x06X4\x9e\xd3`\xd6\x8f%\xc9XN\xab\xba\xa9\xdf\x16=\x1d\xf9\xbf\x15W\xa1;&gt;$\xdc\xb9\xba\xd7\xaa\xb5r6&amp;\x86\x03\xc1\xa8\x1e\xf4\xa6\x8a3\xaa\xd5\x87\xd9\x15k*\\\x99\xe64\xf7W\xf3y\x16K\xd0\x9a\xc5\xcdc\xcdS\xd9\xc5\x8b{f\xd5\xe8\x04"A\xd8@\xabO0 \x88\xed``m\x01\xd8#\xf2\x04\nPp\xcf\x02\xdf-\xd5\xe9\xb8\xebQ&amp;\xef\x04\x7f\x8b\x81T\x97lu\xf6+\xfd"\xef\x05\xa8\x8dAQA\x08\x9a\xf1\xf6\xa8\x9dK\x9c!\xef\x88\xbf\x13\xe8.}\x1f\x8f(\x8a\xbb\x1d7\xd4K\xa9\xac\xfd\xfeU\xe7\xf3(\x86\xb4\x9e\xef\x82\x05\x8bY\xb5\xde\x95~Xv\xfdr\x94\xc1\x0e\x04\xdc&gt;\xaf\xf9\x9c\x1bs\xb17K\xab\x87\x8d\xb2\x02\xf1\xb7\xe7\x88\xf5\x9f\x92W\xd3\x9dO\x8dI\xf9\x95\xc6\x84\x0f\xf0\xd0*\x969l]\x10\xe3u\xf1\xe4\xe5\xda\x9b\x89.\xbf/\x11\xc5\x0fe\x1d:t\xa8\xfc\xddQ\xb2\xe2qi\xda#\x0c\x01\xea\xe5\xe8@\x8c\xfd\xbe\xb1\xa9\xb3\\\xf2.\xc8\xe83\xfc0\xb2F\xa9\xe0\x92\xa9\xe7\x07,\xf1\xa5\xc6\xdcX,c7\xb6lHAe\x81\x04\x1e\xe8m\xc6\x01{\xe5L\x16\xfc\xed\x05-&amp;\xe6?\'\xablp\x12\x18\xd3\xee&gt;r\xceQa\xce\xc5\xd5=G`\xcc\xe6\x08\xae\xe6\x0b*\xc2b\x0e\xc2\xf8\x17\xc7\xe5\x96Isv\xd4\xe9I&lt;\xbaJDL\x9a)U\x1e\xa4g\xde\xc6KF\x0c\x9a\nq\xc1\x12\xcbD;\x83\xf0\xcf\xebX?\x8d\xa1\x1e\x04\x18\xa2a\x10\x10m\xb29\x12E\xad?u\xc1Q\x02\xd5\xad\x90B\x12y,\x12\xf7\x8dRH\xac\xa2H(\xa3\xb7;_\xe2\x1fv"\x8fd\xe4\xbe\xd4\x1b\x01!e\x04\xd33\xa3^\x1eLe\x9b\xd6\x1c\x00\xe4~\xfa\x05\x12\xe2\xf7L\xf6B\xbdH\xce\xb5F\xc8s\x1eA\x18\x1f{t\x08y\x1d\xfc(\x96\xb2%\xa9\xe1\x80\xf0\x89(V\xe4\xd7\x8a\x15|,C\r\x18W\x1cvt~\xe5\xb1\x87/m\xf3\xac\xa0FP*\xb5\xc5\xbf\xd4\xb9\x93b\xbc,k\x91#\xe1\xa2GP\x07n%\xdc\x9d\x06!Y\xd7|\x02.\x15\xa9.g\x10\x12\x1e&gt;\x91\x00L\xe5\x8c\xe2\x99v[w\xe9A&lt;\xb5.\x9a`Q\x18\xfd_\x1f\xc6\x7f5\xb3\xb5G\xf5s\xeb\xeaD~R\xcc\x06\xac/\x19\xdb\xc3\x8bT,XMm\xd43V\x8b\xff\xe9\xaa\xe8\x02\xeb\xe6\x13\xb1\x0b:\xe0Ap\xa0\xaf8Uu5\x1e\xe9\xc1!Q%n\x05d\xb1\xa8\xaf\xe9\xfff\x85i\xb0\xbbt\xea\x84\x91B\xee\xad\x13\xa2\x0f\x19=f"\xfbu\xe2\xcf{\x1f\xf4\xa2\xd4\xc2\xc6\x7f\x15\xec\xe1\xc4\xb7\x0b\xe8\xba\xaf\xfe\t\xbd\xb7\xfd\xa2\xa4\xc3\x19\xc7[1\x11\xf5\xd3\xb5\x16_W\xb8\xbf\x08\xf7\xbe\x9f&gt;D\xff\xbb\xb8C\xe0\xcb\xe8\x13\xc7\xc5\x7fh\xcd\x96\xae\xe8\xb10\xdb\xfc\x7f\x0e\xab\xad\xfdT\xf6k2Ah\xf537h\x02\x91O\xa8a\xbb\xfcFV\t\x16f\xa6J\x80g\xa5a\x84\xbf\tU\xb6\x9f\\\xa0\x8f\xa7\xb09{\x06m&gt;\x92\x94\xa3v\xb73Odm{\x867!\xe3S&gt;\x9d\xd3^\x04Ssb\x8b\x12\x8d\xfb\x99|p\xa0L\x0cTggg\xfe).\x07\xd8\x13\x8d\x9fH\xdd\xc9\xdd8\xf7D\xf00\x87\xd3\xbbiF\x05\xfeca\xb8\x1ahw\t\xb7\xc8}X\xf1\x14*\x934\xab\x9c&amp;~\xcb%\x11\x84\xd8\xfb\x18R\xe1\xe77\x93z\xaf\xe6\xdf\x9d\xe5\x98t\xbf\xac\x9e\x05WQ\x17VO[\xae-pr\n\xe3\x83\x9e\xae\x08\xcb\x0f\xda:\xff}\x14\xf1rLr\xd4\x99\x08]\x19\xe2N\xcc\xfc=\xa5(w\\I\xcaj\xbb/&lt;\xd7\x16\x97\xa6E=\x93C\x90[\xc2\xe5\xac\xb2}\xed\x02z\x80%\x13\x8f\x94\x1dI\xad0\xa5\xfa\xe3\xbe\xc8\xc9\xe3i\x98m2X4#\xa9\'!\'\xf8\x1e\x9b\x97\x03\xaa\xca\xaam\x81\xf3A\x9c2\xff\xb0\x0b2U\x90\xd9\xca\xe9\xa1\x10\x8b\xc9\xe7\x06\xfen2-|N\xf2\x985\xe11D\xbe\xa7\xdeM\xbba\xb9M\x9ct\xa9\x08Y\xd09\xacq\xcc?\xca\x87\x8d\x86\x13\x02\xdd\xe9\xec\xdb\x85\xf7\xd2\xcd\xcaoE\x01-\xd2\xcf\xe0\xd72\xa6\xdc\x02\xc3\xc1y%d\x9f\xe2X\x14Q\x17\xed\x88\xb0\x1c\x0e\xf8\x87D\x1e\x80\xf0[\x1e\xce\x1a\xec\xd5\\\x8b\xfbn\xf9\xd0@~\xdc\x95\xa5\x0fJD\xab\x9bB\x08\xdf\x14dUV\xf4[\xb6\xcc.F\x98\x0e\x0f\x10\xc8\x0fY\x0c\xfb\xb1\xed7\x0e\\\xef\x11j\t\xa6\x89\x8a\x17\t\xb5\xab\xeeB\xaa\xe0X\xfciS\xcc\xad\xdf\xb7\xbc\xec\x89\x88kjf\xd0[\x0ch\x17\xe9\x1f\xa7\x0e\xa65\x97\x87\xaa\xedFk&gt;\x1b\xdb\xd8\xa0V)8N\x11m\xef{\x98\x16\xdb\x7f\x14\xaeZz\x0b\xe8qP\xd5\x86\x9cd\xce\x08O\x00\xc0W\xc6W\xea\x82k\xd7U\xb63\xfe\x10\xb6f\xf4\x95\x8d\xdfu\'\x0b.\x12\t?\xa4\xfa\x02&gt;t&lt;\x802\xce\xcf\xdb\xf9\xc0\x86\xde\xd3\x15iD\xe6Y\xec\xc0\xeaF\xf1I\x90\x12\xeb\xe4a\xa4\xf03\xdb@\xd5~\x98O~\x04\x9c\xc0\x10\x8e\x15d\x18\x0c\x0e\x06UD\xbfY\xa1Wva3\xd6\xa1\x0bg6_\xdc\x16u\xc9\xccy\xd4\xbeE\xd2s\xec\xede\xa2\xc2\xc3\x99\xf6\xce\xa9\xafr\x1b\x80\x9b6\x93\xdb\x8b\xa5/\xc7\xdd\x83\xba\x8f6\xde\xaa\xaa\xc9\xae\x1b?E*jc\x0e\xb5\x1ey\xe5\x01\x9d\xa7\xbb\x89\xe80\xef\xfd\xff\xfd#\xdc\x80\x850\x13#\xebh\xec\xfa\xf0\xfao\xd9\x89\x16\xc4!IS=\xf7\xf2\xfc\xca\x10\x1c\x1c\x7f\xfb+\x18\xce\xa8\x11]\x92\n\x05n9\x12,\xbc\xb1\xceb$5\xab\xac\x01L`\x00&amp;t\xf1}\x83\x81\x1b3\xb9b\xdf\xb6L\xf7QF\x10\xf4\xb2\xd1\xcf\x85\xcez\x9d \xc9*\x12a8o\xec"\xcc\\\xc3\xeddr\xd5\xeben\xd8"\x8aQA\x06\xd9?\x8f\xd8e\x91\xf8\x9f\xba\xbaF\xf1\xae\xec\xdbw\xd2\xfd\xb9\xaaRI\x00\x07\x95\xcc_Yf\x11\x96\x84\x94\x8e\xe6\r\xaeA\xec\xbce\x8c\xa9\xdem\xb3C\xe0\x0779h\xff\xfa\xf6\xeb\xe2\xc48p\xffB\xdd\xfb\xbb\xf6a\xdc&lt;\xc4\xa5m\xdar\xf4`\x1e&lt;$+\x98\x97\'d\x8d\xa2\x87\n|:,\x0bX*H\xa2p6\xe3E0-\x85\xb6\xe8Lw\x0c}\xb0\x88.\xd0\xea\xfe\xf6E\xe8\x0f\x8a\x8b\xc0\x10\x8a\x89\x05Nd\xaca,v"2\xbe\x19X\xa9\x99-\xe2v}\x96e\x19#]G\xe8\x9b,\xd5$,\xd3\xb6\xc3\xc1\xe5\xbc\xef%[\x10\x82x%\x00\x00"\xdeVQ\xbf\x062\x7fb2U\x81\xa7Qj\x9a\x80K\x1ceb\xde\x98\xe6\x81~\x11,^\x0er\xbf\xb1\\\x1d\xc0a%\x15h\xff\x83m\xe7\\%\x17\xe5\x9a&amp;\xbc3\x18\x85#\xe5\x92\xc6\xe68\x81\xc7\xa4\x83\xe3#iS\x86\x02\xf1\x89f\xed\x8a\x06&gt;\x98s\xa47\xe1\xa7\x99\xf52\x86\x08\x848\x82\x08\x91\n\x9f\xe4\x87\x8f\xc3\xaa\x19\x99\xb7\x19\xe3\x1eh\xf4\x100\xc8\xe8n\xc0Y\x02]@\x7f\x19\xc6\x12\xaa \xd4\x0f0O\xbe9\xcf&gt;\xae}`4k\t\xf2\xd0\xf1&amp;\xbd\xceZ\x03g\x8d\x8dp\xd4\xe0\x96\x87l\xd1\xe7YDF\x16\x8a\x01\x84\xd0\x1fm\xeb\x86\xd4\xad\x0c\x026\x80\xbd"\xe2\xddT\x88[3\x11B\x8co\xd9\xc1!\xe5\x01\xc34\r\x82;\xc2\x93\xd8\n{\x88\xd6\x85\x82\x88\xa72:\xfa%{+\xbf\xda\xb6\xa4\x1b\xe0H&gt;\x0e\xd5\x88(I\xd1\xf0\xcc\x81\n\xbd\xdd\xa0\xc0\x89U\x07&lt;.Yl\x10\x8a\x0c^\xad\xfa\t+\xaf\x1b\x8e\x002`\x0b\xe8\x0c\xf8D\xf5\xa87\x067\x06%\x17:\x96E\x13\n\x02\x9c\xcb\x05{:+\xc2\xf5\x17\xd80\x85\xabV\xf7\xa2\xa5\xc0\xa5\x84&gt;s\xd1p\xae\x01\x13\x07V\xdb0\xee\xe2}\\\xe3\xb1\xfc?\x90W\xe3\xe6\xf5x"\xc9me\xdd\xc6\x0f\x0c\x96]\xa8a\xcf\xd3\xa5\xd7\x14\xc1\xcaQ\xb5\xbet]\xc6\xc4\xb6\x11;I\xf3\x94\x7fGl\x8a\xe9ZkqwX2\xc2\x96\xcf#\x0c}3%\xb1\xb6\x97\xe7|b\xeaY\x18\xe2\xe5\x07\x9d\xb2\x07\x1a\xd6\x82\xb3\x17/\xbf&amp;L\xd5\xd4\xaa7\xdeW[\xbex\xa9\x1dA\x8f\xea\x14\xc1!\x03\xf7\x942\xf7\x91\x85x%:\x1dL|o\xfd\x010\xc3\xa7\xa3\x8e\xbf~\xe7\xdf\xe4\xb1\xd2\xe1JQ\x88\xb17\xabs\r\xb1\xf2q\x185\xf6-X\xdc0*\x0b}|H\x81"\xd6\x7f\xe2\x8b\xec[\x93\x9a26zm-\xa2\xff=\x99\x80:\xe6\xac\x0b\x06\x99F\x0c\x9a\x85y\x8c7?\x06\xb1\x88\x1a\x16\xcco\xa2D\xb3(\xbc9\x05\xa0\x94\xde\xe3K4~\xca&gt;,\x9e\x0cb\x16\xfd\xdf}\xd7\xc6)\xb4\x8c\x92\xce\x8e\xe9^\x1d\xdbj\x80\x10\x12\xc9\x01A 9\xca[\xdeu:H\x89\xfa5\xdb\xe5\x8e\xd4\xa4\xf3\xc8r\xca\x95\x9f\x17A \x1d\x8akO\x17*et2\x00\x88\xfb\xac\xd61CY0\xc26\x83h\nb*\x87g\xc4poN\xa2\xe7\x1a{\xb5X\xf4\xe7x\x16\xd8\'s{\x93`\x91\xa2T}\xec"\xb6!s\x1f\xb8\x8f$\xe7\x8b\xa1e\xf0\xaa:\xb2w\x9b~7\xaf\x9f\x00x\x18\xcd2\x0c(*\x02t\xe7\xba\x19\x83\xfa\xbf\x80.&lt;\xc5\x90\x13\xf9\x07\xa9`$Gx\xf4bE\xba=aH\x07\x05\xc4k\xf6k\xe0P\xf4\xce+\xac\x0c\x830\x95M\xb8\xf4N\x84-\x08\x8e\x0eN\xdc\xb0\x1b\xa4\xcf\x97\xfc\x89\x9e[\x9b`\x0bE7\x96C_\xde\xef\x91\xbeO\x06\x1f5\x17\x08[\xc1\x10\xcdXn\xbb\x8ci\xbdf\x9c)\x03w\x9aZ\xbeme}\xb0\xc9\xdd\xb3\x9b\x84\xff;\x9e \xb9\xed\xdfzS\xc4:b\xd4X\xcb\x91S\xe9\tl\xd7\x85\xe1q\xeb4\xa7\xc7\xd0\xe4\x162\x8bKD\x9f\xe2\x0c\xf9\x1e=\xb6H#\xfe\x94\x89\xd8&gt;\xf4_\xfa\xdd\xa6\xb6\x03#.\x13?\xe1%\xc6\xbb,\xe65\xa8\x9e\xf6\xca\xc8\xce\xbe\xbe\xb2V\xb397\xbe"w\x13P\xa1\xefy\xf9\xc1\xe4\xfd\x10p\x1dhX\xf9f\x89JZA\xc2\x7f\x94\xb1\xf8\xe1[\x9b\xf0Z\xd1\xbe\xd0M\x0b9\xd1\x89]\x03=d;\x87\x1d\xfe\xc4\x01\x0e\xafF\xb6\xc6\xbd\xeb\x17\xd6\r\xbbD\x81\r\xe7!iRt9a\xc3\xb8:\xd8\xc0\x93\xd2\xd3H\xdbt\xca\xb2~\x8e#\xf2\x97\xdcJ\xe1H\xc3\x0f\x99\xf2\x12\xef\xd3$\xde\x12jG\x1fm\xbdcfCM\x94\xc1\x18\xf6\xa1\xd9\xec\xb5\x08(\xaa\x17\xfba\xdb\xdb\x85i\xbb`\x02$\x0b`\xbb\xb9c\x0b\xbf\xb1\x8eP\xc6\x9bF\xf2e\xe3G\xb1S\x87\x80\xab\'U\xd0?\xcd\x81\xc5\x12?q\x89\xfb\'\x9fo\xc6\xc19\x805\xce\xccM\xfc\x8d\x9d\x9e\xbb\x86\x85\xd3o\x00\xca\x18i\x93\x9e\xfc\xb3`\xb8\xf8 \x81p\xe6\xbf\xe9\x8a\xe1E\x9a\xb5f\x1f\x014\xf6\x03\xf17\xfbO\x08\xe8\xc2\xfeX\xcat\x87\xb5\xf5\xe1\xd8(\xeb\xc3v\xfeV`z\xdaB\xe6\xa5Zr\xfe\xd5r1p\xe0\x0f\x9a;\x9d\xca\x00\x1b\xc1b\xd7\xc4\xdc\xa0\xfd\xb2\rA\x1d\xe6Z\xc5\xcd\x97\xee;\x8b\x0c\x11\xb0\x1a\x15\xe5L\xc0\xec#j\x928\xe3\x87\xa1\x86\t\r\xfc\xb0a%\x97\x8d/\xa7{\x8cF\x8a\x0b\\\x17\'\xbe\xa9V\xc1\x80H\xb0\nh\x1a-\x9f\xc9\xdf\xf1B%VF\xe9\xea*\xca\xfa;\xa0?W\x1b\xb8\xb5\x1b*\xad\xba\xecR\xbd\xb4\xf0\x03a\x8f\xe2\xc7\x8d?\xac\x04\xd2\x84~\x02\xaf=P\x88u\x04\xeb\x9d\xf5DE\xbbB\x7f,\xff\xbfU\x9a\x06\x05-d\xf5}\xa2\xb0A\xa2w\xef\x87\xcf/\xe2\xbfP\xce\x01\xf1j\xe2K\xa1V"\xe9\xcf\xdd~\xf3\x1f\xbfd\xd6\x98b\xdc\xa3\x12+\xa0\x00\x85T\xe7}\xba\x98Y\x9a\xbe\xde\xea\x9d\xdb\xb4\xb1+8?I\xdb\x08\xa6\xa7\xaf)\x90\x8fp\xd4&lt;8\xc2\xdaG%4d\x0b&gt;\xa0k-\xdf\xc2\x9d\xea\xcc\x04EE\x1fP9n\x045\xfcN7\x02\x1a\xdf$EG\xe8\xcdj\xba&lt;t\xc1\xeb\xd9n\xf7Z\xdcZ&amp;\xa7\xc4\x8b\xdd\xceY\xb7\xd8\xa1\'\xfd\xa0\x03s\x89\x12\xeb3\xc2\x94b\xbf\x1a\x03\xb9\x1cY\xa8\x1c\x9c\xebFp~g\x8e\xfaFX\xf08\xab\x8c\tD\x95\x04\xf0\xa5d\xc9ti\xa8-G\x03X\x81[\xe2\xc8%&gt;\xf3\xa0\xa7\xdc\x0b\xba\xa8\xa7\xf4\xb8\xb6p\xa6\x9b\n\x8bKK\x03\xc1-\xb1\xce\xef\xfd\x87\xe67\xafP\x0c\xbd\x86Y\x0eJ\xde\x91\xa9\x83r\xa5\x1c\xbb\xd2\x8d\xe58\xcb\xab\xe1\x98\xb5\x9f\xb1\xe3rv\xf7\xe5\xaa\x8d93\x152W4p~\x05b\x01\xae\xca\xaf\xc3raL\xa5nv\xaf\xf0\x84\x98W\x96\xac+\xc3\xa2\xf2\xc1\x0e\xdd\xbf5\xe1&amp;\xb5\xe6 \xe4\x10\xfd\x03R\x9a\xe6B\x14\xed\x1dX\x95\xc7KQY\xacE\xcb\xe3B\x1f\x00\x1b\x906L\x8f\x03\xbcg\x81\xf2\xb7G\xb4{\xbao\x0c~\xa6\xe9\xa2\x15.lR\xe0\xd7\x1b\x9b\x13\x14\xd1\x1f\xf5U\xb0\xb4\xbfv\xb6\x87\x13d5Je\x1a@\x9b\xb0\xf6RR#}5\x99S\xc9d\xbb\x98L\xf9U\x94wJ\x91d\x90pA\x1b\x97\x91\xfc&lt;\xad(E\xf8\x89 \xa9c\xdf&lt;`\x81\xbe\t)\xd8I\x82\xf1\xaaV\xc7JW\xa5\x9b\xa7\x8b\x1c\x07\x04st\xa8\xb69\xe5y\t[\xd4\x1b\xe9\xe2U\xc6y\xf4-\xfe\xe4\x15\x80\xe6\xf4\xe8\xb4\tY-f}6\x08~\xe2Ds\x1c\x9c-\x8b\xda\x19\x99\xda[J\xe9\xc9P8\x90\xf2M\x9d\xd7\xa1\xf8Bt \xee\xe9;w\n7\'\xfa\xcf\x14O\xe1m\xd3\x8c\x1c\xc9\x90\x13\xc7k&lt;\xbf_\xccN\xbbe\xb1\x9d\x95E\xf1\xcd\x9d\xbf\xfb\xab\x06\x85\xdfL,HBdK\xec\n&lt;\xea\xf0\xda\x8f!\xd0\xbe\xb5z"\x0c\xe88\xd2sq|\x98C\x11\x01O\xe3 Is\xbd6s}\x82\x15\xe4\xab\xfeu\x9e\xf0\x86,L\xf8Wv\x1a\xbd\xfd;]\xf2\xdb\xc4\xfd\x9b8n\x10\xb2E\xc9u\xfa\xeb\xd64\x0b\xffW\xd5m\xfe\xf3\x9b\x18\xae\xab\xc1D\n\x90y3\x02\xc9kCr\x03\x0b\xfc\xda\xc7Lj\xba\xda\xa8\x84\xa6\xdd\xf5\xd9\xee\x9c\r\x18\xb3\x00\xc5Z\xf3\x12\x06;\x03\xe7\x069E\x9d\x0c&lt;\xf9\xcd\xf8\x95\xedm\x8f\xf9\xa9\xc3&amp;\xc3Tb\x05\x8bG\xd2\x18\x8f\xf0\x93\x81\xd5\xc0(\xfc\x08\xc7\x95q\xe6OX\xf6\xb5\x8d\xd4\xcc5H*\x90\x1dq\xe2\x107\xc3\xff\x15\xf8\x11I9R]\xc6\xcd\x0f\xf8\xe0\xc3\xb4\x19\x15\xa8m\x82t\x85.\xbaM:^\xe7\xf1Ec0[\xa7]\xe9\xa4\xe1\x94\xa2\xac\x13\xca\x91q\xfaI\x876\xbepB-\xd7\xa4Nj\xa3\xfa\xe8\\\xa3{\x94\x90\x84=\x19\xf1J\xf1;+\\\xc0lW7\xe4y\xa0\x07y5F\xcd}\xe4\xecTv&lt;\x10\xd7\xc4\xb5\x994\xa3\xb9\xc3}\xfa\xd9\xf5P\xe2`\xad\x1f\x90\n8\x8c@\xebJ\xfezI"Nu\x0f\x1b7_\xa2-tw\x0c\x9a\xd9I{I\xa4\x8c\xa2,\x0b\x1bb\\!\x84\xb0\xd3\xf6\xc0\xad\xea\x1d\x8b\xb5%\x16\xad\x9c\x9fA\x85\xaf\xb0o\xcb\xd8\xdb\xd8\x9d\xe2\x91\xbe,\x9f\x8d\x9d\x95\x98/g4\xcfL\xb1\xe67\xd9\xc3[.&gt;h\xf4\xa1\x8dEC\xc0\x91L\x14\xd4\xc4/\xacj\xc0y\xbe\x13&lt;\xde\xb5J*\xbe\x90\xcc\t\xbb\x1f\x04&gt;\\Hi\xa3\xe4\xa7\x0e\xc5\xdd\x91\xa9\xb6\xc2\x99\xb3\xa5T\x82\xcer\xef\xa9\t\x9b\'\x9d\xc6n\xa4\xc0\xb8{\xe9\xf7&amp;\x19\x9b\xd3zz-\xf4-71\x04\xe6\xdf\x84\xaa\xa855\x1d&amp;\x9aA\xafk\xd3\x00A\xb8\xc3c\xfa\xb3*\xd5\x82\x85\xe0\xd5v\x1c9\xe3\x9e\xc9o\xed!\x85D\x0f\xef2\x03?\xc4\xc6\xc3\xe7n\xa8\xf3g\\a\xa9\t\xd4\x80\xa4H\xc7\x97\xc9W\xc2K%\xbeM\x96\xe1@\x1a\xaf?\xb6\xbf\xa6\x84\x10zQ\xc3\x963\xbbP\t=\x84\xffa\xdf\xa8!\xb4wr\x0b\x82\xf9=\x1cU\xbb3\xe9K\r\xaf\x14b%\xe6Qb"\x17\xc2\xfa\x985\xf0\xa8\xc0\xbd\xc4\xfaH[R\xb4F\xa2\x8b\xfb\x1f\xa6\xe1\x17\xa2\xee\x1f\xf7Q\tk}\xbc\xab\xdd;\x05\x91\\\x94\x0f\xe7;s\xe2\x87\xca*:\xdbPq\xe5\xa3\x96\xc5\x06\x97\xb6&gt;}\xd1O\x80\xed\xcaMv\xc2\x9dB}\x918\xfaI\x18\xd1\xf0\x7f{\x03U&amp;h\xc8\xab/\xb4D\xc7\xfc\x03\xc3\x9b\x0en"\xd6=\xe4\x7fw\xd1\xcb\x00p|T[&amp;\xb1sJ\xc1\x15\xcf\xf7\xb5\xa3\xc5\x95q\xd8L\xbeP\xfa\x04\xf6t\x9b\xdd\xc8D]$\xa7+\x93\xa0\x8c\xd06\xf2\xf6\xaf\xefr{\xdd6Q\xbc\nu-\x9c\xfd\xf9,\x05\xfe|P\xe2\x9d\xf2?\xfd\x07\xfd)\xf9\xe1\x8e\x0b\xea\xf5}\x1d\xadp\t\xff\xc6\x89\xd9\xd0\x12\x8c\xa9BhRBim\x1a,\xba\xff\x83y\x80`\x07\x02\x05\xf8\xc1\xc4_\xf5\xf4\xb8\xa1a\xc60\x04*\xe4\x827\xbf\xdb\x8f\xa5p\xd6\xd4\x8e\xe9\x85f\x97b2\xea\x86w6d\x8b\xef\xa9. \xb8\xe1F\xc4U(w\x0c\xad {\xd6n*\x19$NwzQ\x01\xd3tO\xf1\xe0\xc3\x0f\xd1\xf5C\t\xd2A\x9cZ\xf2R\x03\x86\x9dH\xb7\x16\xe7\xe7^\x0c\xe4\x82\x1f\xe8Ye\xc0\x81r\xcee\x13;\xdb\\V[J&lt;e&lt;\x9e\xe7S\xf5H\x006T\xca\xe5\x19\xa5\x08\xce\xba\x8e\xb9\x9d\xe50\x95\x8fYv\xf8\xcb}\xd5\x84\xc5Ft\xf5\\g\xdd\x03\xa1w\x8f\xc6\xae\x80\x7fw1Wz\xca\xf3\xaa\xd4}\x8d\xd6\x0f\xbd\xe2\x99\xafs\x1e,\x7fo\x88\x9d]\xd3\\c\x9090\x16\'\x88\xd4\\E\xbe\x18\xa8\x14\xf3by g\xb2s}&lt;c}\xdf\xb4\xbet\xf4\xaa\x87+\xf6[\x85\xa9 @\xa9\x7f\x14\xaa\xb5\xc8\xf6+\x97\x1b\x89)L\x11\xd0l`D(\x85\x84^\x9d\x8e;\xf4\x13\xea\x00\xcd\xc6,F[\x8e\x16\xb0t\xd3s&gt;\xd7\xf5\x01\x139V\x9aF\xba\xdd\\\x8d\n\xfdJ\xc3\x9f\xe8\xaf-3\x9f\n\xa5YZ\x81zu\xe22\tT@\x7f\x81\xb1\xc3\xc1\xd1\xad,_X\xb0\x98\r\x0e\xe3\x91\x95&amp;f\xf8\x8d(\xe2\x93]=\xd6s\x8e\xfb\xf5\x91aY\x8b\x1c\xf1\x88m\x0c\x94\xdcX\x1a\xfb\x8ff\xea\xc6\xef\xa1jl\xeaX\xe7(r$v\xaa\x85\xa4)\x16\xac\xe7V{\xd3\x82\xca\xa1KN\x19\xe8l\x94G\xabr\xffx"\xbd;y\x1b\xa4dGU\xe1\xe9\xb7o\xd7\xf2~\xe6\xce\x95\xf1]\x9bn\xe4wu\x8d\xe0{\x94\xc1\xd2\xfb\xe5W\xc8\x00-mBf\xb0\x85hM[\tan\xe7\xe9\xc9+\xee\xac\x1aW\x05ia&lt;h\x17&amp;\x07\x95\xa5\xee\xc9l\x87\xcd\x17\x1bJ\xcd\x01\x9b\xb6#m\xca\x0f\n\xa3\x86#:\xbc\xecC\xa3|\xff\x81\xa8\x93\x8bG\x82\xb2\x91\xfa\xc5t7\xb2D\x9a\xabb\xc0\xd6m\xfbY,@\xf2dx\xe8l\x98\x0c 9\xef!\x98g\x7f\x168\xc1}\xae!\x11\xce\xb5-\xce+\xe5\xfe\xf1%\x95\xa2v\xdb\xb2\x00G6\xd7\xc3I\xf5\xb3&amp;`\xd0\xb9g8\x08\xdai\x90\x94\xcfu\xf0+\x16\xf1Q\x19\x15\xbay%\x1e\x98?\xb8\xb7\x0e\xa3s\x89\xff\xeb\xd1\x87\x05\xf0\x87T\xe5_LT\x9d\xe0\xea\xfdS\xf5p\xd8a\x84\xcat\x08\xa4#\xbc\xa7\x86W\xb5\x16A\x07\xa1K\xb5/e\'}m^LT\xd9\xd4\xa3\xcc\x13{_\x9eK9\xe0$.\x0c\xcf$\xd5$a_\xba\xcbF\xf8\xb5\x08L\xb1E\xaa\xbbWB\xbf\x8f\x97\xec\x96\xd3\\7\x14\x15+\xc3e\x0e\xf1\x13\xf4\xd2t\xcf\x19\xb3v\xd6\xa4;n7\x96\xf7\x0c\xa7\xb4\x90\x0b%\x16\xfcm\x1d\xb2\xea\xe8\xef\x15\xa4\xe0\xfbN\xd3\xd6\xcd\x87\xbc\xce \xfdwO3\xbfl\x92m\xf1\x17/\xb8\x13\x94\xe1y\xb3\x83-=\xd1KI\xd8\xe1u\x06q\xc8\xa0\xb2\xb4\xf3\x01*\xa4\xcflp=\x1e\x02_\x0fEE\xc4\xde\xcf\xab\x1f\x8e\xff\xe5@]]\x98 \x85\x92H\x18\x07\xe2\xd4\x82(\xcep\xa5\xf8B\xc5\x14\xf4\xb3 \x07e\xe1gC\xd4I\x81\xf0\xad\x13\x1e\xda\xf7\x9b\xc6\x04\xa1J\xcc\x87`\x8b\xc4\xfb\xf9\xb5\x07\x8duH\xfa?\x8f\x88\xbb\x0c\x0c\x8e\xd5[e\xd3\xad^\xeb\xd2\xa9L;\x86R\xc1@\xcaJ\x9bFyN\x8d\x8a\xa6fSZ\xd8\xe3oJ\x9c\xa8=cm\xde\xac\xf0\xbb\xe8\x14\xd1\xe8\xf1\x85ujK\x07\'*\xe0\xb3C\xaee\xc8Vuq\xd3)(\xa3 \xa1Sy*\xab N\xbc\x00\x83\xbb\x0b\x90\x9c\x88!x\xf4\xea*\xe5\x10\xa2\xf7\x97\x12\x81\x18Vpt\xeeE\xd2?\xad"\xf0vcCI\xb6\xb1\xc6\x847"\\ \xa7\x82z\x0b\xb1G\xe5\xa8\xbaW\xee\xab\xa7Q\\\x930\xe3\x15\xaf\xf1\xc1jq\xb2$d\x96\\|\xc1\xd3N\xd7P\xdb5\x1b\xc5\xfdGc7\x131\xd6\x99\xafo(f\xaa\x1a\xd2\xeb\xb8N\xb9PK\xd6\x86\x11\xb1\x82UL\xe3\xd2c3K\xed\x15z&gt;\x95&lt;\x9c\xe2\\Q\x10a\x1a[\x876\x19`\xa8\xb7\x92\'\xb6\x8b{\xdco\x95\xff\x80K\xe7\xdf\xbd\xe7\x95f\x95\x19s7m\xec\xf0\xf9\xc2\x9c?\xb6\xfaF!|\xab\xae:"4~\xd4\x81W0\x8ca\x90d\xc7\xee\xf00\x80\xde\x08\x96&amp;\xcdC:\xcf\xcc\xbe \xeb\x8d\x93\xb0\xc2!\xf5S\x99\x92Oq`f\x12\x06\xa2\xcc\x13\xfb\xe2\xb1\xc8\xa2]\\\xe5\x01|t\xb8y\x025\x06\x81\xd3Hx,\x7f1\xab\x840=Fs\xb6\x10r&amp;\'\x82\x13w~\xc5v\xbc!x$\xec\xc9\x87\x12\x96\xd4\x9f\x05\x1b\x8c\xf1\x99&lt;\x1es\xfcJP\x935^\x0b*%x\xfc\xcb\xf1\x1fj\xf9\xf4\xc1q\xc1M1\xeap\x02\x94\xff\x0bzV\xba9q\t\xe4-\x19\xf8\xb9\x12\x1b\xbek\xac\xe0\x0cu$\x9a\xf2\x9c\xc6\xaf\x11^^dcW\x80\xf8A#&gt;\x1ch(\x0c!\x0e\xc5c\xaa5P\x9ce\xec-\xcdC\x94\xee\xb1\xbb\xc3\x83]_V\xec,NujL\xc0\xfdOz\x9aa\x99\xd9v\xd2pMCP\xaf&lt;I\x07o\x19\x02R?\xe9\x88\x86\xf0\x1at\x9dQj\x94\x8e\x95y\xee\xe0\xa4]\xaa\xa4\x9f\xe606\x8b\x1b\xfcCe|\xe2\xb9\xda&lt;\x84\xbc\xf6/r\xac\x03\x81\xe4\xd1\x90\x0c\xb6T\x1e\xfe\xc4\x81\x83\xd2\xd5\xdd,\x9d\xe4{8\xbd\xcb\x95\xbbKQF7&lt;0\xeay\x82\x14Cgna\xe7N\x16v\x04\x17\xa5\xc3\xad\xf8\x96\xbc\xb0z\x01+n;\xe2\xbf\x81gC45\xceC\x87*\xe4\x13S\xf9w\x84\x9d,J\x88~\x1bN\xfe\xc0\x1b\x19W9\xda\xd7s)\xd2\x9f\xf2\x0c\x8c@H[n*\xae\xc1\x98\x91\x01\xed\xd0\xe7eS\xc7\xc9\xbd\x07n5\xb7@\x19\n\'i\x08\xcb5Q\xe0Sl\x8f,:8V\xd2l"d\xf5\x17\x9bg\xd4\xf37\xed\x0c\x08\xbc\xd7!-\xef\x97\x0b\xbe\xbe+\xe0xu\xbf"\xb8M\\\xac2\xd1\xad\xba\xd8\xaa\x96\xd5\x00\'\xd4g\xfasK\xfc\x9a\x16\x8a\x07\x7fPV\xd2\xb8M\xa4%\x996\xf1\xa9\xbd\xf92\xbeF\xbe\x89|h\x9c?\x10\x99\x01\xf9,41D\xe9\xb8\xc6\x10&lt;\xcaM\x050\xc9\x18$tp\x0e\xd3r;\x18@\x8b[Uu\x8f\xbd\xf0\xa1\xbe.\x94\xde\x89\xf5EM\xf7\xe1k\xdbW\x06Z@\xe1zY\x05\xfb\xf0\x10Z\xa0\x8c\xa3\x1e\xe70O\x8a;\xfe\x17\x07x\xc9^\xa2v\xcbE\xf2\xe3\xf9[&amp;\\\xba\xed\x9a\xed\xd4?\x8baM\x07\xd0`\xef\xd0\xdd\xf4\x9e54\xda\x93".p2\x1b\xd5\xf0\'\xbd\xa4o\xd3E\xea)\x17\xa1\x11\x88H\x881\xc4\x15\xa1k\xf9\xd1\xf8\xd4K\xfd\xe2\xe9\xa3v\x13\x19\xfbL]Q8c\x80\xc3\xcf\x95\x91\xe2\xbf\xcb\x1b\x85s\xec\x837K\x8d(+`\x0e\xb2\xa1!\xf4\xf5\xf0\x9f\xd0\x86\x920\xf5\xa4aV\xdf+\xfe\x06\x03\x16\xd9\xb4*\xbe\xa8-\x05R\x0b\xd7\xb5\xec\xe5\xddr[-\xea\x92\xa8q\xc34\xb4\x94J\xef\xc9\x80Lt\xaa\xfas\t\x9a(\x1e\xa4\xa8x\xea\xa6\xd2*\x87\xfd6\x17\xac\xc4\x1e\x13V\x12^\x9a&amp;\xda\xc9j\xc7\x9cw\x19\x91\xf9A\x17\xd565\x85\xa3Zm\xd3\xb3"8m\x08\x13\xf0\xee\x10\x004Wm\xc5\xa8\xfc{8\xcc\xd4\x95\x88\x9e\x9c\x10z\x12\x05T\xd7\x08UP\xbe\x8d\x97\xb8\x81$34\x90\xcc\x02\xe3\x14\x90\xa1\xd3,&gt;\xbe\xc9\xfe\x83\xfb\x04\xc1Gebmt\xb7\xf8g\xf8\xda\x7f\x93\x16h\xa5\xe1\xff@j\xc6\xc7NH\x0e\n\x07m\x82\xd2\xf2\xb1t\x91\x14\xc0\x9d\xd8\x82\x03\x02\xbb\xad\xb5v\xac\x19\x1d5K\xa73\xc9\x97\'+B\xe4Q\x15\n\xa3W\xe0p9\x00\xeb\xec\r\x02\x17Q\x1dY\xe1\xc8\xb9\x1d%?{\xbb\xdc\xd4\xf0\xf04m\xf1.\x80+\xe3-\xa9\x9f\xff-\xca\xb5vn\n\t\xd9s,\x15[j\x1c\xcf\xa8\xf5\x16Q\x1fL\xb7X\xca\x91\xf9\xa5\x94{\xf5\xcdM\xe2\xcec\xfd\x1d\xcf\xa5\'/\xaa\xc8d\xdf\xd2\xf1"\xc8\xd0\x18#\xc5w\xd4O*\xd12G\x15\xc6\x82\x16\'\xfbRs\xc6\xc1F-\xcf\x9c\xc4&gt;\x0bY\xce\xb5\xa0\x04w\x9a&amp;\xff}e\x98L=\x99\xe5CC?\x08\t\x87N\xfa\xe2\xef\r Ei\xc6\xca\xa50\x1f\xd7\xcf\x07-&gt;\x88\xc3\x94C\xbf\xa6s|\xecVw\xc2\xe7\xa3\x08\x88\xe7\xb7\x06I\xdbz\xea\x9c}\xe3\xdd4\xef9\x02Wio\xfd05\xf0\xe4\xf8\xea\x15"]\x7f\xf0\xd7\xce\xf3\xaf?\x96\\\x9fQ\nFE2\xd5\xa6(+\xb9\xc7\xc8\x8c\xa80h\xe0\xd2\x1d\xdd\xb4\\\x8d{\xac\xae\xdf@F\xb2\x01S\x04\x9fbPA\x9b\xfb!\xb5\x86/\xc0&amp;9\x14\xe0\xc1\xd2\x06PUq\xf1@\xc6\x12\x075\x15\x1f2z\x1b\xc8\x05\xfb\xd0\x8ba\x18\xe8\x99\xe6_.\x12\xe2\x1bL\xdb|Nh\xf99\x85\xad\x1f\xcc\x13\xabJ\xa1N\x90\xd6\x13\xa0}\x99\x9b\xdf]\xc9\xf5\x9a\xd0\x9er\xf5%\xb3X)]u\xd4\xf4\xb4\xbc+\xa5\x98\xd6\xb4N\xae\xdd\xcf\xe1\xdc\x93\xda\xb8\x1c\xf4\xe0?\xe0\xb1\xa3\x86\x84a\x8c_wjZ\'0D!\xb1\x97\x97\xbb\xc6\xeb7\xa4\x83=\xdf\x98\x0biN\x1d4t\tJ\xb2\xcaLEI}\xa0\xcd\t\xfb\x11\x1c\t[$.$\x06\x8e!\xd9I\x0e\xe8N\xc9j\xb7=\x0fap\xc1\x90\xc31"\xc1\x08\xc35\x85{XS\xe4z\xa12:\x94\xc0\xfd \x7f\x83\xa1L\xea\xec\xb4aa\x86\x1c\xd2k\x06\xf4\x86Q4K\x01\xac\x87\x1b\x0f\xcc\xf9\xe4\xc0\x14ov\xe0\xf4\xaf\xf5\xfcNJ3\x8e\x0fd~\xc3\xfe\x9f)\xbd\xf1\xed\x92`\xed\x1d9{\xad\xb8\x96\xaf\xaeP\xb3\x8cX\xd4\xee\x02\xd1\xc9ely9)\x1f\x17W\xe1u\xa01\xe8\x13H=\xc8*7Pu\xe4\xf8n\xd8D\x0b:1\xf3\x9ez\x80\xfc\x0f\xcb\xd0`\x0e\xd0x~&amp;6e\x99\xe3\x03s6\xdc\xb1\xa3qk&lt;\x03ab*,\x02\xa3\xa0p\xd31\x8cG5\x14\xa5R\xef\x9f\xf0\xea\xb6 &gt;.\x8e\x8cJ\xc7\xc3\xf1J/\x7f\x9e\xe3yJ\xfd2i\x9bB.X\x04^\xca\xed\xcc\x99K\xef\xd5\xdd\'\xd5\xa0\xec\xc5Z\x81\xef\n\xad\x06\x01\xdbT\xfe\x0c\xaeA\xa0\x1d\x91\xc9\x917OJo\xcc\r\x90\x13\x1f2\xb3\xd1\xa9\xa48\xb4\x9bvW%\xfe5\xeb\x8e\x8a\xdf.\xf0u\nEs\xbd\xf4\x8ctb\xacI\r\xefA\x07\x04\xfd\xc8;\xa7\x08\xf7\xeaa\x00s\x04N\x12\x1f\xcaL\xc3\x9e\xf4F\xfa\xc46\x8bRqF\x9b6\xfb\xb1W\xa7*\x9d\xa7\xa8\xdd\xd7Y\xd3\x12z\xed4\xdd\x88\x10\xa3\x140]\xe3\x91\x82\x90B\x81\x02\x9f3$A\xe1\xd1B\x03"\xd4\x8e#\x9d\xb9\xd9\xd6\xe7\xaaPU\xb0\x04j\xbf\x98\xaa?=j\xe8\xbd\x90#d\xf5\xf20\x82\x7f\x99\x82\xb5$\xf8%\xca\xb9\xa8}\xaa\x06\xca\x91\x0bm&lt;\x1d\xff\xe9\xbe{b#zi\xf3\xeb\xe16\xbbf\xab\r|\x96\xf7\xe1\xf1\xb2\xefU@{\xfd\xa0\x9d\xf8$X+m\xfb\n@\r\xe5U\xd5t\xf1S\xcc\xadm\xd0\xad\xe2\x08\xb6w&amp;$6\r,Q\x1f\x94\xa4\xe6\x84v\xc2d\x1f\x8e\xbc\xe0\xe2W\x86\x10\xd7\x905\xb0D\x0f4\x9fL\xa8\x19l\xc9\x84\x01\x96\x96\x81\xaf\xda\xf0\xb0f`ym\xfe\xd3\x80&amp;\n\xb6y\xbe\xa5\xc24\x98\xae\xdd#\xfdz\x821\xb20\x9c*{\xbb\xe6\x98\x12\xcc\xa5\x90n\x8fI\xd37\x81\xdbr\t\xd8\xfe\xde\xcf\xa7\xf91!}\xd4O\xf0[\xa6\xc0\x82#6R\xb3FK\'\x07\xa0XPCl\x1d\x08\x043\x85\xd8Q(\xb2bNM\x12(\t\xaeA,\x82\x89k\xef\x83G\xb0Z\xcb\x12:q\x0c\xd4\xf9Ka4\xdeT\xd7[\xfa\xad\xe7~\xafk1p\xf4&amp;\xc1;\xccb\x1a5\x15\xe4!Q\x1f\x14\xb2\xef\xe5\xf8\xf1\x1f\xca.\x7fX\xe1[P\xf37\xf3\x9f\x9b\x04\xa6\x9a\xa8_\xcc\x91,\x9c\xf4T\x97\xe2\x1a\x8d\xaa\xec\x1c[\xc6\x8d\xf6\x1a&gt;\xdaK\x01=\xa7\xc5\'$\x9c\xecC\xaa{\xfa\xc6\x9e\x8d\xcd\x969\x99f\xfbn\x9c\x18\xfc\xa4\x99\n)\x0f2-\xf7F?\x06\x18\xfa\xb65\xc29\xbe\xf5\xb6\x19\xd12s \x1eWE\xdd\x86,&gt;\xa5\x0b\xbf;|\x19\x00\x00\x00\xeb\xee\x1d\x10q\xf1p\xe5jB+t\xf9(&lt;\\S\x05\x9e#Y\xa5\x9bF\xf3\x0c\xcb\x01:\xb4\x99\xac\xcc^\xd4\xaa\x89k\xeb!6\xc2G\x18\xdd\x83\xc8\xb6\xc76\xe8\xc3g\x19dm\xaf\x83\xa9\xe9\x10t\x16\x01\xcbV\x83\xc6l\x81ga\x13o\xc3*8h\x04\x1b|4kq03\xfcFo\xaa\xd0\x00\rA(E\xfa\xa9\x8a\xa53\x9aI\x87@\xce\xda\xce-\xc0\x16\x86\xe0\xeaq\xe1\x8b\xe7k\x13\xd7+:L\xe8EZ\xe6\xfb\xb6Mi\xba[\xda\x15]\x99 \x12\x938VSK&gt;\xc6\xdc\x941d\xf1\x11\xd4\x80.\xb2\x91\xd4\x9a\x86;6o{1I|{d\x00#Np\x9a\xeb\x0e\xdf\x9d\x9f\xb5c\x1a\x0b*\xbf\xec,\xe1g2V\x8a\xba\x92\xe8]\xa17\x1d\x95\xcb\xcd,\x11H\x9cX\xa1\x90\x1e\x0c\xa8\xbe\x7f\xc7&amp;\t\xc6\xcdp\xc02\xc0\xe5\xd2\xc2\x86\x0e\x80\xbb\x0f\xe8\x81\xccs\xa0 \x16&lt;U\x98\x90+$\xfc?\x1c\xf9\xfb\x1c\x08&amp;Z\x9d\t\xc6\xaf8\xb01&amp;\xa70\xdf\xd43\xdc}L\xec\xd9\xab\xe5B\x03?\xe2\tc"\xf3sN\x8e/\xb1\xe1\x05l\xc1{\xae\xfa\x0f\\\xc1\x8eJ\x89~C;\xa2;\xa4v\xf4\xbd\xbe^\x89\x83^b\x9c\xe5D\xaci\x84\xdbc!1\x0ca\xd3\xa7\xda\x95\xb0^kOL\xd5q2H\xba\xc6\xf3\xd7qk\x90\xb2\x00\xf3\xe4@\xbd%t\xdf\x838\xf0V\x08\xb1\x08\xb0\xf5\xbd\x07B:\xf7l6L\x8c\xb0\xcf\xb5J\x03\xbdl\xba\x8a\xb3%\x15\x9c}\x9a\xedQ_;8\x1a\xa1K \r\xe4\xd4\x1a\xf1c\xfbv\xe5t\xc3\xb7\xef\xed\xdfgxk\xe5\xfe\xd1W\x1b\xf5\xd2Z7\xc0\x00.7\x1c\xc0\x00\x00\x00\x00'</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kit 2 Refil Para Mop Giratorio Fit Esfregão De Microfibra Rmop5011 Flash Limp</t>
+          <t>800mlgarrafa Térmica Água Squeeze Inox Academiaquente E Frio</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>36</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>59</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>06</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>37% OFF</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/kit-2-refil-para-mop-giratorio-fit-esfrego-de-microfibra-rmop5011-flash-limp/p/MLB29509211?pdp_filters=item_id%3AMLB4197810629&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB4197810629&amp;sid=affiliates</t>
+          <t>39% OFF</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_996264-MLA99926132931_112025-AB.webp</t>
+          <t>https://produto.mercadolivre.com.br/MLB-5265791338-800mlgarrafa-termica-agua-squeeze-inox-academiaquente-e-frio-_JM?searchVariation=182801268962&amp;pdp_filters=item_id%3AMLB5265791338&amp;extra_comm=true#polycard_client=affiliates</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>b'RIFF8=\x00\x00WEBPVP8 ,=\x00\x00\x10\x03\x01\x9d\x01*\xc0\x01\xc0\x01&gt;m2\x95H$"\xa2!\xa4\x94\x8a\xf8\x80\r\x89gn\xe1o\xbekt\x01\xb2\x9c\x1f3\xffk\xdd]\xa1\x7f9\xe5\x1b\xc8H\xd6\xf7)\xfd\x1f\xec\xdf\x96?0\xff\xc9\xff\xda\xf6m\xfaS\xd8\x0f\xf5\x8f\xf5\x87\xd6\xcb\xd5?\xf5\xdf\xf8~\xa1\xbf\xa5\xff\x81\xfd\xae\xf7\x8f\xffg\xfa\xd7\xee\x9b\xfb_\xa8\x07\xf3\xaf\xef=h\xbf\xb7\xbe\xc1?\xcc\xff\xc4\x7f\xf4\xf5\xd4\xfd\xca\xf8K\xfe\xc5\xff\x1f\xf7\x0b\xdac\xff\xff\xb0\x07\xffN\x05\xefU\x7fU\xf4\xa5\xe3?\xe7\x7f.|\xf7\xf2\xa5\xf0?u}\x982\xa7\xda\x16\xa5?3\xfc3\xfbO\xf2~\xd7\xbf\xa8\xff\x9d\xe2\x7f\xca\xff\xf5}B\xff"\xfe\x81\xfes\xee\x0f\xd5\x8fq.\xbd\xfe\xd3\xfe\xff\xfa_a\x1ff\xfe\xaf\xff\x03\xfcO\xe5W\xc2\xe7\xdd\x7f\xd6\xf4c\xeco\xfdo\xf0\xff\xba_@\x1f\xd0?\xb0\x7f\xbf\xfc\xdc\xf8\xe3\xfd\xe7\x8a\x7f\xda\x7f\xdf\xff\xcd\xff1\xf9i\xf6\x0b\xfc\xc3\xfb\x1f\xfc\x8f\xf0\xff\xe6\xffh&gt;N\x7f\xee\xffY\xf9E\xee\xcf\xeao\xfd\x7f\xe8~\x03?\x9c\x7fx\xff\xbf\xfe7\xdbk\xff\xa7\xb9\x9f\xde\x0fe_\xd8\xaf\xfe\x05W\xc9K}i\x86\xb0\xd8\xb0\xd8\xb7\xcf!\x92\x96\xfa\xb9\xe3\xe3$\x05\xdf\x98\t}\x12\xed\xdc\x88\xe4\x0c\xc6\xb0\xd8\xb0\xd8\xb7\xcf!\x92\x96\xd6\xfc\xee\xeb\xe7\x94y\xcc\xd5;4\x9f\xf4\xee\x1c\x0bOR\xf0\x11\x12\x9b\x8cr f5\x86\xc5\x86\xc5\xbey\tt\xf3AS\xc5\xea\xb7?\xd4\xbc\xb7\xb6\xd5\x80\xa0\xbe!@i\x10a\xa6i\x86,\x19:\x87\xc2&amp;LI\xc9o\xaf\x83\xe4_Z`\x8d\x17;\xe6\x13\x91\x07#\xab\n\x19a\x0c\x94\xa2\xd6U\xf6*T\x14 \xf3"\xa6\xb9f?fa\xc2\x19\x9c\xf8\xf4\xfauq.U\x83b\xbb\xb4\xeb\xe1\xe4\x04\xc2\xae#\xacX\x8b\x885d\xb3*x\xe7\x17:\x89\xf8\xd8l[\xe1\xf3\xa9\xf4\xd8\xe9"\x03\xb5\xffIT\xdd\'u\x16\xec," \x95(\xe5\x19\x00z\x9c\x03}\xfe\xaal:\x90\x0e\xd2\xc5]\x99+\xc1J\x05\'\xf8\n\x98\xd2\xe8\xc0\x823\xabBy\xdf\xcdJ\x97\x97E&amp;\x96#\xf4\xb7\xd6\x8fs\x85*&gt;\xfc\xe0Q\xf5\x8e\xdc\xfe\xa8\xb8%|m\x102\xbaKw?h\x9e\xbem^\xd9QD\xca\xc4X\xb33M\xd8f\xaa?G\x8cs,d!\xb1kLZ\xc0\xba[y\xd3\x13\x90\xb0\xe4J\xb5\xa6\x1a\xb0wI+#b@\xd1\x12\x82\xb4\x0bL\xc8\\W!\xa96\xbc\x91\x184w\xb4~\x18i\x07kr\xc3]\xfb\x8d3e\xf3\x01\xa0\x04j\xd5h\xd7A\x07B\xb1\x9c9\x84 \t\xe6\xce\xfd\xd3x*\x84.3:\xe2\xf1N[\xca\xecg\xca\xec!\x92\x94C\xd3\xb0j\x7f:\xdf\x0b\x12Wz\xaaW\xcb\xc9J\xd9\xb5^\x850\x97\xe0QG\x89\xae\x19&lt;\x97U&amp;\xe3*\x9dZX\x8f\xe7m\x192a\xa9\xbe6\x0e\x18\xd6\x1a\xb2\xb9\xd1\tw5\xa8\x1b\rP\x07\xb2\xf0\xccId\xaba\n\xa4pe\xab\xee\xf4\x05\xe5\x87\xa6\x0c\xd1@oh2@\xbeU\xde\xe5C\xb2o\x83\x9b\x8a\xf2\x98Et\xc9\xa0\x0c\xb3Xj\xbfS\xd1RvU\xec\xf0 d\x1c\x11\xbe\xcb3\x9e\xe5=\xbb\xb9Y|\x94\x04r\x8aJ\xfb\x8a\xb9(\xed\x89;\xf9\xd2\xcc\xa8&lt;\xd3v;\xc3\xe6\x93\xdeE4\x84\xae\xb0\x16\x03\xce\xf8\x8ea\xae\x9eRp\xe3\x83o\x0c\xeb\x1e4\xde\xa0z\xa7K\xd8\xd9KN\xd4Y\xc3\xf7\xce\x841y\x80t\xa1\xe5T%\xafu`\x13\'\x8d\x19\xe6\xeb\xcc\xe3\xdf\xa7#\x94(\xcfX\xcf-\x86j\x88?S\x91\x8d\xe4v"^&gt;\x99X\xb4&lt;NDI/P\x90\xe3_?\x85C\xa2q\xfe\xd4\xce\x80b\x936\xa3Zf\xa5-\xf29m8\xcd\xda\tw\xf2\xd9\xb6\xf0\xa2|\x05\xe8\xd6(\xe2\\U@\xa9B\xfb\x86\x1e^\xd0\xa4\xa3n4\xe2\xe9r\xf6\xc1\xa8iU\x85\xb6\xc2\xa1aUG;\xc9\xbe\xca\xddbp\xaf[\xcah\xe8\x95\x92!L\\\x85p\xe8\xf0f\xf2\x02\x8c\xd8\xca\xb66/xv\x81\x19n\x832\xb3e(K\xf7?A\x80\x8dc\xb3\x1b\xb5T/&gt;\xe1\xaf\x10\xc1\xac\xe5j\xa4\x95(7\xea\x00R\xc1&gt;\x0b\xac\xa3\xd4%\xc8\x8cZf\x19\xcd\xf6D\xa5\x80m\xf7\x97\x11\xb0\xd7[\x979\xfd\x0b\xe3&lt;\x03\xdcti\xbd\x8a\x8a\x10a\x98\x96\x0ceO.\xca^\xba\xed\x98a\tL!@\x11\x1a\x18&amp;\xb9D*\x0b(\x88\xa2\xc31\xd0\x88\x19\x8do\x80\xd8\xb7\xcf!$\x07"\xe6\x10x\xeb\xc5\x86p\xb0j\xf1\x91j\xb7\x03\xcd\r0\x98%\xa9(\xeb\x96\xd0\x8a\x10\x16_\xac\xf3\x9c\x00\x12\x8b\x14\xacj\x8e\x00%7\xb24\x8e{\x0f\xdf\x90\x00v\xd6\xeb\x8d\xf3\xe6\x15\x9eBK/x{\xf6\xabE\xc4v_\x03\xa0\xcd\nt\xba|\xff\xea\x04\xc4+`\x08{\'H\xfd\x10D,$\xac\x98n\xbd\xaf6\xab\xfbn\xc1\x9919\xe6\xf0h\xa2\x16aK\xf8\x85\xe5\x90\xbc,|\xb26\x9b\xefb(\xa4\x1a}(\xba\xb8\xa1\x9e\xa2P\xc2\x91\xa7\x92\xc7K\xdc\xfc\xb5\xcb\xad\xfcx\xc2\x8a\x970hh)y\x88\xa1\x94\x02Y\xe6g)\xdd\xc3\x98\xc5g\xe6\xd20\xd9hHS!\xde\xfe\x06\x1b\'`\x1a}b\xf4ts\x7f \x87\xdc\xfdi`\xd0\xe8\xe9bmJ\xfbF7*\xdc\xca\t\xd8\xbd\xdf\xfc\xe2\xc6\x1a\x1e\xb5\x05Wu\xe9I\x15\xfd\x02\xed\xdd\x96&gt;}\xda\x8d\xbaV\xcb\x919t\xb7T2cu#o\xcd\x06\xce\xef`\xb0\xa1\xf7\xd4n\x11\xde@\r\t\xaaT\xccA\xb2C#\x1b\xfb\xf0\x8eTM$\x13\xd7\xd9\x03\x93\t\x9c\xade:\xdb\x9d3\xc8\xa8\xb7\x04\x98\xc9A@\x88\x8e?f4\xf6\xaa\xc5\xbc\xe7Ky44H8w\xe7\xba\xe6\x82\xc12@\xf6\xfb&gt;\x1e\xe4\xe3\xf2\x96I\xe5\xe8(y\xad\xaf\x11\xfb\xe1\xedI^\x88\x97\x96^i7\x89\xd9&amp;xI\xc8k*p\x94"\x18S\xd8\x81Nl\xb1\x84\x01\xc66\x17\xec\rq\xde\xb7Wo\xc0\xc3%\x15\xdc\x91\rd\x97\x0b\x9d\xb2Z\x01x?\xef\x88\xcd\x8c\xf6\x00\x9c?\xcd\xde\xff\xf8P\x17\xbb\x86*\x9b\xffN\x1a\xf2Fet\xbd\xb8 \xb75J\xdby\x88\xca\x8c\x98\x11\xf4\x0e\xb7\x8c\xe8\xa7\xd2\x9a\x03\x18q\xdd\xb4\'\xd8\xa6\xa2N\x1a\x0e\xa1\xfa\xcb\xae\xf5K\'\x94\xfa!j\xf2\x08\xba\xdbm\xef\xd4\xf4}\xef\x91\xd1\xc3\xad&amp;\xd5\xd6\x03\xf3h\xce\x0cWN\xa8\x96m\xe4P4\\tblk\xa5\x06:qN\xf8%\xf6\xdb\xb3\x8f\x03UX\x8e\x03\x9c\xf6M\xf6&amp;LG\x92\x9aK\xdc7"\xd9\x07|{\xb8\x18\x85\xd2\xaf\xe5\xfd\xa0\x1f\xe3\x0c\xdcc\xf6\xcd}\x1f\xcfT\xcdP9P\xf9\xabj\xc3}\xb8]\x0c\x88\xe8\xd2\xc5\x91\xc8B\x9a\xf6\xa8L^\x16\xaa\x00\x11\xa1a:`w\x13l0\xdb\x92\xf3&lt;\xe3$X\xac\xf8\xfcb3\xc5\x01\xeb\xc6\xbb\xcb\xaa2V\x00\xc7\xc3\x1a\xed%\xb10\xbb\x1b\r(\xa7\xed\x1a&gt;pX\xed\xc1\xf7&lt;\xaep{\x0eazf\xffV:wiC\xf6\xe5\x13\xa9+\xf5\xc1l\x1d\xed\x81\x9ea\x97\xae2\t\xd8-\x00*N[\n\xdd&gt;\x02\xb9$\x10\xe5\xdc\xa7F}\x1eS\xca\xc8C\xeb\x82\xbaLy\xddr\xe8\xa7\xe2\x99\x91\xe3\xb9x\x96\x13\x96\x95)\xd3Vya\xc4\xf9\n\x9f\xeaY\xd8\xf0\xff\xfb\xad\xceR\xc3\x98\xa1\xc727\x19G\x14\x0f\xd6 ns\xe1\xbai\rn\x90\xd8\x8d\xca\xf5\xef3\xe8t\xd4\xa0\x9d\xf6m\xb3x\xa9\xdc\xbcf\xce\x88,\xb7\xc7QXF\x06\xdf\x0fV\xa5\x0e\xc3\x8de\x02}2\x03\xb8\xd4L\xbco\x04\xb2\xe63\xbc\xbb]\xba} \x1a\xa4\xeeDj\xd0\x8c\x02\xe5\x88\xb8e\xeffV:\x92\xa5b\x183yQ\xf7\x8f&amp;\x8d\x8f\x8c\xbe\x80\xa6 @_\xa7\xfe\xf7,^\x1c\x92(\x8f\xeacL\\\x14\x86U\xb0\x8cD\xaaB\xfc8\xcb\xc4\x99z\xed*g\xdba\x84B\xee\xb6\xf4.a\xe6\x11\xda\xd6\xf0\xb6f|y\xad\x86\xbc\x1d4\xbb\xff\x90\xe4\xb2\xe3\xcd\rW\xf9\x80\x07\x0eU\xc00\xe9n\xb8\xdb5d$\x94\xab\xd9\xec@\xfe\xda6,6-\xf3\xc8d\xe1y\x031\xac6,\\C\xbeJ[\xebL5\x86\xc5p\x00\x00\xfe\xfa\x08\x00\x00\x02\x1b\xb6|A\xc2\x9e\xc2\xa7\x96\xcef\x1c\xc1\xf0Z\xea\x91;\xa3\x04\x90!\x8fZs\xb6&lt;yN5\x92,\x86\xe2\x1ax\xcb\x9b\x16\xd7k\x8f\n!\x8bL\xe6o\xc3\xc5\xae\x96\xe2\xdf\xe8j#\n\xe7Hd\x06\xf6\x99t\x98\xec+\x8cj:\x8cl\xb8&gt;\x15+m\xad\x84hX\xbe\xef\x85\x8e\xa4\x8fL\x00\x061:\xe0X#\t\xfb\xa6\xf6*R6[\xe3\x85:\xfd\xcd!\x00\x1b\x8b\x95\xe2\xac\xe1\x17r*\xc1\x08\x9eF \xa0\xd3\x8a\x1d\xbb;,\xceb0]\xe0\x14l\xb4\x82\x94\xffxQO\x1ey\xf3#\xffy\xb3\xf2\xee?\xcbA\xecwP\x95\xf90\xf4\xb9\x80\x860\xa3_\x05\xabz\xe0\xd0\xf7S`\x93\x00\xed\x9d\xb3\xb4\xe9\x95\x8a\x93\xd0\xc4\xfb\x8a\xdd\xcf\x9c\xa1@\xc2\xb5/\xef\x13\xb8\x01K\xdf\xcb\x85\xf4d\xfa_\x89\x14\xb1\xe8\xfc.\xe3\x89\xe6,\'Ns\x80\x03\xdf\xe0\x9f\xc7\xacw\xaf1P\xb6\x81\tP\x89|\x84\x8c\xfa\x1dV)\x84\x90ql\xf4\xa8\xf9,Z\xc1\r\xc5\xcdpQ\xcd\xb9\x17+\xed8h\xa5\xdf\x02\n2\x8d36\x10\x0f\xf5L\xb7p\x84\xdf?\xa3\x1e\xd0\x8c5\xe5\xbf\xbf\x88/a\xb7\x18\xed\x16\x13\xc7x\xdeJ\x11\xf3\xea\xbe\xe6\xf8\xcfs\xf0!#\x9b\x08Q\n\xd4-\xa2\xa6\x87O\xb1\x16Y\xe5\x16\x8bJ\xc0\xf7\x81\xf9@Y\x8dz\x97\xa1V\xa8\x0f\xcb\xcc~\xfe\xecG\xe072g=\x92\xf4\xc1\x03\xa3+#\xf4\x18v\x03\xe5\x17\xdd^\x92y4^\x88L\xfa,\xd3\x9fX\xc9)\xfc\x14#\xa7+\xadQ\xab\xf2\xd8\xe5\r\n1\xaf\xd9xhr\xa5\xc1\xfdDi\x923g\xdd\xb4\tx"I\xa7\x14WyQ\xac\x7fO\xce\xbb\x92G\xeb\xc4\x81\x9e\xfct\x15N\x9c\xfcd23\xf3B\x1fN\x00H\xfe\xb3\x17\x98\xdc\xcc\xc4\xd1\xde\x8f\x9a\x96":/ \xe8\x99\xc2Z&lt;.\xcfn\xff\x93\xe4g$\x86\xc3\x02y@\xc8\xf4\xae\xeeo5\xec\xfb*\xfe\xb5\xe9\x8b\x1d\xec\xa6\x1a\xec@Tz\xf8\x12\xd7\xdb(\xb6\x85\xbe\x9c\xe8\xe8\xc4\xed\xb8\x0e]\x9b@y4i\xb3\x9e\x8d\xf3\x94\xa6\xe3\xe3\x97XM)\xa7\x1b\xe3\x0e\xe3\x11\xa22\xe5G\x89\xe3\xc1I\xc2\xbbg\xd9.\x9e\xfd\xcdQ\xc4{\xe1\xfck\xa5\x8e\xaaoS\xd4\xe5d\xd1\x99szn\xde\xfcd\xa0\xca\xd6\x94\xc0^LK.Nh\x129\xcb\r\x89\xdc\x8e\x8b&lt;\xf7\x0b\xdc\xa6\x1c\x02@\xef\x91y\x8d^\xee \x8ej\xc3\x99\xba|\x088\xfa[}\x90\xa9\x9c\xf9\xf7\x9em\x98\x82Y \xae\x12Y)\x90\x019\xa6\n&amp;\xab\xed\x83\x8a$m\x10\xc8\xa9\xa20|\xa5\xed\x87]h{\xe8#8\xdc\x1dG\x05u\xfc\xdf\xd0#1ZU\xcdH\xc29\n\x08\xd6&gt;2\x17\xfe\xcf\xd5\xa2\xce\x97\xb1\rx\x07\x19\x8d\x17\x82\x8b\xcf:64E(\x159\xdc\x1e\xb8Wu$\x12X\xfdM\x18x\n\x13\'KQ\xfe\x15\xdcx\xd6$)\x1d\rO\x11%V\x0fR(Ac\xa9\xa5\xe9Y\x83\x8am\xdf\xa9\xaft\xb1^\xea\xac\x1d&gt;\xcb|\r\x8fd\x085t\xa4\xd4]\x11\xd6\xb1\xc7\xf5{\xff\xec\xc9T\x17\x17\xfd\x96\x17\tp?\x89\x14\xa7\x11\xca\xbbl\xd7^"\xe5\xdf\xa2\xd1\xd4\x81a\ti\xf3\xbe\x04\xe6\x04\xd2hzm\xe9]\xae\x19haq\xf8\x1fF.\xab\xa8\xbc\xf4\xab&gt;\x14\xe5\xb7Ab\x81\xdfF\xcf\xe1\x8f\x9f\x06\xa9\xe2\xac\xbe\xd5\xf9\xc9\x07\xdd\xb2NI\xad\xe7\\}\x06t&lt;eDn]\x82$f\xe6\xc0\x0f\x85\x89\x99q\x96*\x03\xf8\xc6]o\xb5\x05nv\xb0\xf6\xcd\x89*]&amp;%\x88\xc5\x11/\xb6\x80|\x99\x0cB`\xba=\x01R,\x14\xd9\x9eTv\x1e\x0c\xea\xaa\xf4\x16;\xf7\x00\xd8\xa6\xe9\xb6rl\xd3\xb6\x18#f\x14C\xfeU\x18P\xae\xda\xe0\x0f\xa7#\x89Yy\xdc\xa5\xdf\xbb\xcf(\xf6\x8b Gr\x063{\x0b\x98\xaaRiM0L[S\xb2\xe6\x17\x81\xe3\x80\xe6\xa5"\xc1\x08\xeb\x9a\x89\x94\xb3.\x02_=\xf5\x01\xe3\x80\x8f\xbe~k9\xd3\xf0\x18|2\x8c\xea\xa7S\xc9\x0e@S\x86+x"\x8cX\x95\xee\xb7B$\xd2\xb2+5\xbd}x\x1e\x0b-\xef&amp;a82\xce\x98\xd2\'\x0e\xcd\xf7&lt;\xd2w{Q\x00#7\x1f\xeb\x88\xf0\\\x12\x89\xacQ\xb0&gt;|M&amp;\x16\x9a&lt;\xa5\x00Bp\x19gzg\x98\xefx\x89\xca\x9fT\xa1\xa6\xe6\xdd\xbd\xbab\x92\xec\xe4\xca\x12~*\xdc\xd8i\x15\xa7i\xe7\x84\xbe\xe1V\xa5\x13\xfd\x17\xbea?\xac\xed\x9f!\x00\xf1\x9c\xe3\x1b\xf6\x1a\x07\xea\x8c\x1b\xb2\xcc\xbd%\xcd\x075Y\xf7M\x8e\x17\x1a\xc9\x8b\x1f\xb8\x12\xd3\x91m@S)V\xf2\x82\xad\t\x8aj\x0ce\xda\xb8\x08\xb0\x97\xbbj\xc9\x81\xc6=L&gt;DPl\xdd\xd5X\xf8\xab\t\xafj(\xe7!\x06\x94\xf5\x08\xab\xeb{\xfa\x7f\xfcF9(\xb3+X\xc1\xe1\xaf:\xffM{\x82\xf69H\x9d7t\xd6K)\xa8g\xc3I6\x97zJ\xc3\xc2(;\x8a\xf49;\xc3\xabJ\xb7E\xc9\xf6n\x15Q\x17k-\xc6;\xc7b2\x9b\x82\x1a\xc7]T3\x0e\t\xd6\xae6R\xc9\xdb`qV\x81\x96\x87\xaf\xea4V\xef\x97\xdcp\xee\xc8\xe4\xc8\x8c\xde\x96\x1f+\xbf\x81h\xb2\x1c\xddT*\xcb\xfd\x0c\x12_\x15\x97\xdd\x15R\xfc\xe1\x18\xf2\xd0i\x82\xaa[\x1c\x03W"\x1b\xe0\x06t\x08\xb1\xcb:\xf3Y\x9c\xae\x1f\xf0\xbc\x95\x19\xfe\x8d\x08\xa9\xd7\x1d\xa7+:\xb7[\x04j*\x81;#\xbc\x18;\xc5\x0c\x9fs\xcb&lt;\xce\xb4\x988\x99t\xdc\x0c\xec\x02*ZK\x99\xecG\xf4AHX^. s\xfa\x07\x13\x1c\xf3\xd1N\xe1\xc1\xa8\x12\xdc\x07\xfc+\x8b`:H\x01\x1b\x08\xc04}H\xb8}av\xcc\x87\xa5\'\x88C\xc4\x13]\xf3zr\xaei\x1a%\xe46\xa7i\xdf\xc2\xcd\x0c\xdf&lt;\xe5\xa0\xe8\x17 !5k\\\xbe\xb7&amp;)b%\x87\xee4\x85\xa06\xef\xcc\x91\x1csq\x87L\n\xe4~\xb6t\x14\x8dE\x8e.\x0c\xb66\xcc\xeb\xedq\'\x90\xa1&amp;\x9c\x07\x16l\xa9\xcc%\x95\xb1?M\xecu[\x14#\xca\xaa\xdcH@\xa8H\xeb\xea7\r\xccZ&amp;\x97\x9f\xf9[#\xa5\x8b8e\xeb3\x8d\xc3\x02\x12\x96\x8e|\xc7!\xd6&gt;\x98\xe0\xa5K\x16SA\xc5\x9dd&gt;\x10\x91\xe5\xabp\xe5\x1bfT*\x93\xd6m\x02\xe7\xf1l\xb6D\xb9\x00\xea?\x8fCU\xafV\xc1\xbc\xd7\xad\n\x19\x87O\xfc\x8d\xa0BIp\xa0\xeci\x9b\x9a"\xc4 \xca\x07,pyo\x89I;\xf1\x93S\xc1+\x80h\x85P\x15\x01\xaf[q\x7fj\xcf\xf8a\xc1q\xeb\xbb\x8f_\xd63\x12\xacO\xfb\xc89z\x84\x9c\xe8\xa2\xe3\xb5z~\x0e2\xd6B~\xfa\xf6j\x05}\xc1\x06\xdbn\xe5S"U\xaf\x02\xb8\xd1\x8b\xd66\xf8\x85\xe7GV,\xac.\n\xd4\x06{74\xb7\xf4- \x99\xa4\xbeAiE&amp;\x83%\x1aOS\x82\xe5\xa7\t\x8e"\x86\x88\xb5\xb4V*\xb6j\xbaDWWv\xad\xc2eLZ\xe6\xe4\xa7|\xea\xca(F *\x90\xd1\xf2&amp;\xbb}\xf2"\x16\x92\xc4\x08\xd9\x10\x11\xc8\xcd\xe6\xb4\x7fS\xd1p\xbfp\xe8\xb6!a\xd0\xc4\x03\xa7^1\x11\xcb#\x85\xd2\rb\xb5\x987\xe8\x9c\xfa9\x9b\xe7\xcb\xac\xa5\x95\xc1K\\\x99f\x1d:\x8c\xa8q-\x8f\xcf\xa2_5\x0e_\x1c\xa6\x10\xd8$g\xeb\x96~\x0f\xeaa\xdd\xe2\xd4B\xdeL\x82\x8eZ ^4\x07B\xe5\xfb\xd0[\xd62\x19\xd0\x80#\xc2m\xe3;\xd5K)\x99\x9a:\xb93t\xfds&lt;1W\xf0W\xb2\x81B^\xa5\xd9]\x17\x90\xa7/\xd0\xe7\x90\x96\xee\xec\x9dg(\x11P\xf0\xcc\xcc\xb5\xcf\xe7\xf4\xee7\xa08\x9b\x85\xe5fi~\xfdF\x97CW;V\xe4&amp;-\xfe(\xb7\xad\xf8\x97\x1f\x89\x95p\xc99\xc0gD\xa1\xf1v\xad\x87v\xb3\xe6\x10\xcf\xc8\xfd\\T\x14I\'\xb8GT\x1d\x94\x00I\x82\xa4~\xaa\xd5\x07\xf3^=\x90?\x02&lt;\xe8\x9a\xb2\xe2\x0b\x0f-\x9c\x8e\xd0\x0e\xaf\xea\x08\x0b^\x86-6\x93+\x1cHdv\xbf\x8dx\xcc\xe3V(\xd3\xb1\x99_EOj\xf4e\xbf\xd4\xe9o}\x0f|\xba\x99\xfcc\xeaU\x1e\xd1\xeeXIy\xe8n\xfb\x80Vj;\x8d\x18Q\x9c\xb0#\x8b\xc5\xdc(?^\xc6"y\xa9eoLb\x91f\\I\xfevn\t\x9dy\xb6y\x8bS\xde\xa6$8,\x0f\xe9\xf6\x97K\x83@\xcd$BRQ\xba\xb6O#\xa6u\x93\xe3\x02\xdc&gt;R\x99+\x96{\xaf\x82\x11\xae\xdb\xdc\t\xbeF\xcc-\xe6LU]\xce\xc6$\x13b\x8d\xc4\xeb|\xc5N7\x92\x9b\xc27\x8d\x07\x0f\xe1\xca\xb9\xd1\xc1\x17\x90p{\x91x\t&amp;t\xc74&amp;Ed\x14\x0e&gt;\x1c\x92?+\xc7lc&amp;\x9a\xe8\xcb%\x18\x89\xf83\xb7lG\xf1\x7f\xad\xd3(\xabb\x86G\x9b~+\x17\xe7\xde\x04c\x16\xb1O\x12\xeb\xe8\xcf\xd9O\x8dw\xaf\x1f~l\x88-\x9c\xa9.\xbfj6\x84\xe5{#E\x06\x18\nX0\xdf\x98\xbb\xa90G\x16uDc\xf3BH\xba\x01AU\xe7\xb6xT6\xffK\x9743\xe6i\x9d\xcb\xfeEp\xd4\x87\x1f\x88\xff\xec\xf5S\x06S\x90\x01I6\xfas3D\xcajS\xa71?\xe63\xa9\x93\xfc\x7f&amp;XK\xefo\xff\xeb\xf8\xbf\xca\xe2.\xac+\x04?\xf5J\x8c\x96\xdd\x9a\x85y\xbe\xb5s\xc3K\xd2}\x1d!\xcb&gt;\xc2\xb3\x91\xaa\xabr7\x8dX\xb4\x0c\x0b\x80O\x97\x854K\x02:BVY\r05!\t\x8b#\xd1S].\x91\x8a\xb1\xd5\x19({R7\xe6\x94\xca_+\x01\x97W%#\xa8\xb4\x02\xda\xe6\xfa\xe9\x10\x15|g\xc2|o\x8c\xbf\x1c\xceT6\\W0\ng)\xf9\xf3;k9\x7f\xeb\xe5\xe1\xaf\xe3\x06\x00+\t\x91i\xc8\xbe)\'|\x8fV\xbf\xe3\xa8\x05\xb6\xd2\xec\x90 5\nn\xaa\x9c\x9cI\xd2\x06k\xe6\xfc\xc4\x8d(\xdb;\xdbyL\x18\x9c&amp;\xc8wd\xab~y\xbdv\xdd\x18\xd4\xccA\xd3\x90G\xecM\x05AI\xd6\x95\x1b\x15g|\xc0\xa6r\xff\x7f\xa7\xda\xe2\x1b\xafJ\x9e\xe6\xeb\xd4t\x9a\x08\xae|\xa2S\x81\xc3\xc9}e\xeez\x13\x89\x85u#\x91O\xbf$\xe0"f\xb8\x95\xcf\xa2\xb3\r\xb1s\x8a#\x8c\xf1\x13?&amp;\x9d\xa2&gt;\xac\xbf0\xa1\xfe\xb4\xde\x1c\xdc\xf0\xdf\x9f\xfc\xd6\x8d\xb3\'\xcd\x93l\xf9\xdb\xd7E\x1cv \x84\xe1\x0e\x0b\xf1\x06\xf6\xb2[\xd28\x18\xf2\x811Y\x84\xd9\x89\xe8\x95\xde;Msg\xf7\x075C\xd4\xc8=\xbf\xe5\xbe\x8a\x9cs$;&amp;\x1cz.X\t\x02#\xf6\x1fF\xca\x11qd\x9f)\xc2u?/m\xbeog\x06Y\xcdQ\x7fH\xf4\xa7T\xf5\x9e\x0e6\xeaA5p\x89\xde\x82\xa5_J\xa6\xfc\\K\xe7\xce\x17\x91\t8\xba3\x1d\x06\x89\xabu:\xce~\xf5\x80H\xd6J\xb5t\x87.\x15\x97\xd5\xae\x9ev\xac\xf7\xd3\x05\xee\xe4\xb8\'\xe8e\x87A\x8b\xa4\x1a\x02\xc8\xb7\xa1\x1am\xf1\x18C\xdb\x96&gt;\xfd\xcdH\x9b\x9b}h\xcc\x16\x1e\xdf\x00\xdc\x1d\xf4B\xcc\xb7\xeeN{\xee\xe0\xfb\xfa\x04\xc3\xc2c\xa2\r\xc8\x9d\xb8!\xa8\xa5\xbaKx\xf4\xe5N\r\x13X1\x11\xf0\xf0E&amp;\x1d\xe7\x00\xd2\xe7\x9d\x1ej\xdd\x19\xdd\xa0\x1a\x7fs\xc1\xf3\x80\xac\xfc\x01\x84\xc0\x8bC.\xfa\xdb\xa0SP\xe0D\xebW^\xd5:\x03\xe4\xe05\x8c\x05)\xbb\xd6|"\xdcw\x08X0\xfe\x90&gt;\x12\x8e-\x96\x1b\x10\xf2D\xca\xdb\xdf\xc06\x97&amp;\xa3\x8dxG\xec\xde\x9b|d\xbf\x99=\'\x18)\x95uh\xaf\xf2\x18\xe8\xc6\xe9W\x1c\xfe\x9c8\x02B\xe4\xf1\x0fpl\xa8\xc96-$\x98z\x1a\xdb\xf6\x85l\x8a\xfa8"]B\x9fZ\x86\xfe\x10\x9f\xb9\xe7"\xfa2\x16h\t\xaf\xfeJ9QT\x06H\xd8\xd09\x87GN\x08Y\x15\xa3 \xea\xae\xd453/\xec8\xff\x03\xb6 \x93\xaf\xc3O\xc9\x93A\xc1\x16\x8b\x17\xd8\xb5}J\x84\n\xbf\x1e]\xe4\xea\xa1C*\xbf\x07\x7fa\x06\xe8\xa5\xe6V\xb4\xebtc\xdf\x16\xec\x86\xd1\x8a\xde\xa0\xcd%\xd1\xdaxF&lt;]\xd8x\xad\x96\x8e\x83T\xe7p\xf9\xd2\x8c\x9c\xf9\xee,\xf0\xb7\xc8\xba\xc5_9\x0f?\x18D\xcc\xdd\xdb\xeeu\tx\x01\xe5\x0fs\xf1\xb1\xdb/\x8bO\xb5~\xaf\xfeL\xe8y_\x99\xd3i\x19c\xe9\xbc\x01B\xf5\xe5\x97\xa8\xa0\xbc\x8c\xbc\xfa,\x0e\x81\x1f\xfa\xaf\xad\xe8\xd0\xb2\x97\x1eG\xea\x9au\xbbT\xf6\xe4\xeb&gt;\x16D\x8dwo\x00Wx\xb7\x17\xf0\x10\xda\x98da\xcb\xc2\xc7\xf2\xa03\xf9\xe7\xa4Z\x0b~+\xb2\x95\x92\xd4\xc9\xd4-z\xe6p\xd6U;2\x00\x07\xc4}\xd8\xc1\xae\x9f\xd3s\xdf\x8b\x0b\xee\xf3\xef\x15\x96\xc6;\xe9\x90i\x15\x16\x92\x18\xc7p\x99\x90\xc6\x84\xf8\x0e]EP\xb5?\xe8 \x9c \x11.\xc6#]\xc3\xe8La(Q\xecZ\xa2\xc5\x1cz\xf5\xdfI\xe2O\x1a\xda\x97a\xf8[\xd7f&lt;\xde\r\xbd\xc1\xb3\xf0g\xba\x822Y\x08\xe2\x16\xd6\xdb).\xd5\xb3#\x88\xddB\xf1\xd4\x04\x88W\x90\x0f\xb3\x8aN\xc0\xeb`\xf4\x0c\xb1s\x87F\xa0\xb9S\x14\xdc^p\xf5\xe3\xe0\xfd)\xb4i\xfe\x1a1\xc4V\xd1\x0c\xd0T\xddJ\xc1\x00\x1b\xb9\x1e~\x99\xd8l.\xf2n\xbed|\x88?\x8e\x1fn_\x18\xc4\xa7Q\xfad&gt;\xff6\xc2\xda\xe1\xde\xf0\x99\xc5\x19\xe72\x85yj&amp;\x99\xb4\xee\xd7\x07\xeb\xfd\x9c\x9f\xbf\x82\xa9F\xf5\x10&gt;}\x92\x07\x83\x18\xa8\xe2;5\x9d\xb5\xff\x0b\xb4!i~\x1fQ\xe0f*\xe8i\xc2 \xd5\xe6B\xa3\xbew\x98\xe8X\x85\xde\n\x0bgpQ\xf8I\xf7\xf5v7f\x88\x9a\xadD\xd9\x80\x88\xbc\x05\xd7\xb0z\xce\xef~Hbqx\x851\x1b\xba\xbf)\xbdv\xef\n\xa6\x02\x1d\x1e\xe4\x0c\x0e1GYXG\xc2\'t\xbb\x94\x14\xa2g\xd31\x9f\xd2\xd6\xde\xe5N\x06\xc1HUd\x98W\x01\x11\xc6\x15P\x81\x7fG\xa8\x06\xefm\xd0\x9bf\xb6\xdf\xdb:]xC\x89\xf8\'\x04t\xd3t{\\\x9e\x18\x83\xbe\xcaw\x15\x83{\xabel\xe5\xd1XD\nF,XrOB^\xff\x03\x01\xb0\xa9\x07p\xbf\x0fXeEc\xd9\xdee\x95\xf1\xdbo\xab@\xd2\xa6\\\xeel|VX\x83v}\x153\x00\xae^H\xa7\xc7L\xb7a\xe7\xe5p)\x9f\x82U\xa4N\xc1AdT\xc2\x15)/\x9aJ\xf2qE{\x8a\xc3\xfca\xa8\xa2\x8a\xbeh}\x91&gt;K\x0f\x92\xa1\xf66z\xf5\xd8\xb0F/\x8f\xfe\x90\xf8H\x94g\xe4\x95\xefp\x18~|\xadD!\x99\x97;IY\x93~\xf0U\xfa\xd7\x07\x17\xcdr\x1e\x95\xa4\xfafE\xf8\x1e\x8f\x9951\x87\xf4y\x90\x83N\xfc\xd6\xf9\x9c1h\xf7V;?\xf5\xa6\x1f9\x17o/d\xa0zf\xb6\xd5M\xa8^2+7\x87&gt;\x1d\xfc\x9c\x9c;\x17{\xd6\xd9J\xb6\xd3A\x7f:\x1d\xc4\x07In\x84\xbaD\x8d\x8d\x19T5vE\xa6\xc2/.\xe4\x8fl-\x8f\xc4Vw=\x82Y\xfd)l\x92\xe5\xafA\x82`\x0c\xd0//\xd5Zk\xdcCI\xd7e\xa4\xb07s&gt;\x03\nv\xcc4n\xd8\xfd\x0e\xac4\xd9CoS\xa0\')e,\xde\xf5\xc9s\x7f~i\x9f\xcf\xfe\xef\xff\xb7.\xa2&lt;\x8d\xbc\xa5\x15\xa5;\x088\x11O\xfd\x14"\x18VV\xef&amp;)]~\xe3 \x80\xd4R\x93\x06\x99\x88\x8dU\xd0%\xf1\xee\x1b\x04\x1d\xeb-\x83\xe7\x8d\xfd\xda-\x01f1*\x9b&lt;\r\x11\xe4\xb5\x11\xa5\xc0)\'\xb7\x11\x92\x9d\x01\x8c\x88\xb0\x88y\xe4$\xaf\xec\xb47\xcf\x12\xf9\xe4\xda\x12\'\x17\xcc\xc1m\xcf\xa0_/\x16\xb6wvls-u\xe25\'\xa7*\x10\xb7\xab\xe6\x8fS;\xeaS\xfc\xa7o\x84~3,g\xf4\x7f&lt;Z\xbbT\xda6T\xdc\x11\x10\xd2\x01\xfc\xc4\xbe\x1e\x90n%\xeb\xfd\x00\x87\x04\x16\x06\x92\xca{\x1b\xb3R\xa5\x1b\'lr\xd6\xa3\xa4\xa0\xa1\xc6?\xd3 \x9c\xf6\x0b\xd1\x0e\x03(uZ\xfa"\xa9\xba\x1c6\'\xd7P\xea\xfd\xb1A;\x13\xd7\x9e\x17\x0e\xf3\x0b\xe2\xe2-\xaaE\xdf\xcd2\xb2;^\xf0\xb0\xba2\xbb\x96\xd8j\xa80l\r0h&amp;b^\xd2m\xe24\x01\x00\x01\xbdo\xae\'\xd8\xa7\xd7_\xea4i_yb\x83\xf1.\xdf\xf2\xd3\xac\x12\xf1\x06\xc4\x06;\x99\x8e\x88+\x7f\x04e?\x1e\xa6\x93I!(\xad\x99sk\x0c\xd3\x81)E\x19w9u\xf5\'\xafi\xd9@\xd5\x04\xd3\xcb\xb0B#\xb7\x9bK\x04f&lt;_\xa8T\x90AHu\'\x1bg\xb1\xacb4\x9eel\xf5\x88q\xedwI\xe2\x9f\xf8\x99\xe5R\x9b\xfa\\\xab\x03]\xe2P\x93\x05\xa7\xb0\x1d\x8di\x1b9\xd5\xcaD\xaa\xb9\xf5v\xf2\xa2\x07\xff\xb2\xec\x8d\x1c\x96\xa3|\xc4z\x06f\xe7\xa0\x93i=8\xe9\xac2\xa3k@\xf8\xc7\x96\xd5\x80q\xad\x85\xed\xe4R\x98\xe4\xea:\xe6\xdc\x04\x82y\xa8V\xd5\x92\x83\x81\x94=\xce}\\\xa8\x87HN\x8b2X\xdf\xc7_i\x86\xc3$3_n\x14B\xed\x0e\x10\xb5\xc6\x97\n\x9f\x17~\x8d\x0c\x08e\x03\xe0\xa3+\x13\xff\xa7\xb7\x1f\x19\x1aO\xb3\x7f\xc9E\xd7\xc9@l\x15X\x97\xf7\xbb\\\x7f\xe7O|\x04\xc1\x8a\xe4\x91D\x02/Q\xae3\x98ug\xa2S\xa6\x85\x98\xce\x0f,\xd4Q\x1aN1\x0b\xb6Y\x90\xdbA\xff&amp;\x9eg5\xaf"\x9a\'\x89NLQB\x93\x8d\xcf&lt;\xed\x99(^w\xe12\xda\xf14\x92\x8c\xa7 I\x1ao\xf7\xd7\r\xba\x90\xecZ\xef\xc1\xc3#\x9ea\x82X\x86u\xcf\xce\xc6\xc4_tr\x0f\x8e\x04.s\x10\xc5\xb9\xe8TA\x08\xeeI&gt;\x9fK\rAYx\xebD\x1f\xa0\x1b\xef4\xea/\xb4}\xfam\xb4\x0e\x8d,\x14\n\x08\x0c\xdb\t\xb4O\xba\x99\xd5|\xab;\xf9\x93\\\xde\xdf\xe9p\xd5\xf4\x9c\xd2\x00\x94\x13\xbc\xaf.\x98%k\x03YE\x1c3\x16\xdc\xf8\x93\x06\xf9}zK0\x12\xf9\xd1~\x85\xe4\xb4\x15\xf2\x1d\x916\x9a\xa9\x91\xedk\x96\xd8=F\x1d\x8b00\x9b\x088@}_\xa6\x97\xbf\xb5\x1f\xe5\x1bh\xf9\x0c\xb0\x92o\xf2Ko\xe3\xf1\xbd{\xd6\xbf\xa1\x1f\xa7\xfd\x9bq\xca\xd7\x9b\n\xcf\x13\x1a\x840\xdd\x01T\x88b\x93\xdeT\xbd\xbc\xa6\xc8j\x15t\x89u"s\x93\x9au\xef\x9d:p\x0bu%\'\x8d\xb9A\xd7\x03\x0f\x80\xc3\xc7h\xcd\x9f\xa1\xa8J\xab\xad7\x96Z\xe0\x04@%\x83\xe7\xe1zX\xb8h-\x91\xec\xa8l\xedbDjp;\r\xc9\xc42\x0b\x08&gt;\x19\x01\xa8\xe5ak8\xb4\xc4lQ\xf1A\xa0\x068\x01-3i\xecp\xd3d\xf3\x01\x0f\xec\xc8\x0e\xd4&amp;\x11\xda(B\xdb\xaf\x92\xbaSxm\x04\xf7 K\xb2\xea\xf8\xa8*d&gt;\xf6\x92j\xda!\x9dHL\x9e\x05\xb3&lt;p!}\xd1\xb8\x01l5c\xcc\xc1\xdchq\x04\xa8\xc78\xef\xe4\x8a\x10\xbe\x0c\xba\xdb\xeb~\x03\x90\x85\'\xa4\xd09\xa1\xb9\xc7\xbc\xd7\xd8\xe5\xb0\xbef\x10&amp;=Q\x8a6\xcfq4\xf1Kj\xa0X\x16\x05\x1ee&gt;\xe8J\xb8\xb4\x98\xbc\x82\x9c\xf3\x84\xa8\xd5h\xf3\xea\x1f\xa8\x15\xef\x86\x9c\xa6\xac\xdbr\x87\x95\xd0\x87\x9b\xa9\x9du]\xf4\xa4vM\xe7M\x10F\xde@)\x13\xa7\xae2*\xfd!m\xa7*\x9a\xc9\xed\xcck\xd1\xc5\xe6\xcc\xd8\xdc\x90*\xcb=\xf0\xa7\xc4%\xf1\xf0l\xf3\xa3\xb4jU5\x87\xbd\xdcY\x8d\xce\xa4%\xb8\xc8\xfd\xf9m\x19\x95\xe6\x82\xb7E\xb3aZ,]\xb1We\xb1\x13\xba\x91q\xb2\xa3k\x11\x95\xa8Q\xd4*\xd4)\xd1K\xfdna\x8c\x93\xdc\x1f\xc0\xc2y\xc0g\xf2\xcc\x9ci`\x8f\x99\x8f\x02\x89\xbd\x01\xa4F&lt;\x82\x1d\xe3\x8f\xe3fh\xe2\xd3+PS\xf9RkGU\x91\xb5v\xae\x92\xef\xe7\xba\xd4[(\xa7"\x9d\x1a\x03(\xa5W \xb1\xf1\x96\xc0c\x12\x98\xfenu\x9c\x87\xb0\xe6I\xf7\x12\xad.\xb9a\xed\x95\xee\x96\x18c\xa9\x88G"\x1e\x012\xa0\xd8\x17\xddNlt\xa8\xb2\x06\x0e\x11\x08^\xd2\t\x91+\xb9\xde&amp;\x86\x86\x1e#.k\xa0\x19D\x1d:3\xc7DW\xef\xa5\xa2\x18\xb0\xe2b\xe6\x1eW\xb5\xb1\x1e\xed\xe9\xec\x08c\x1b&gt;"\xff2\r&gt;\xcb3s_&lt;\xd3U\xf4\xb3\x0cyR\xec8\x87\xe83\xbc3\x89.\xf2\x01\x99X\x069b\xc3Q\x9fD\xb4\xe88\xdew\x0b\x0c\xca!\xccM\x99\x9cu\xfby\xd96\xe7\xc4`[\xdc\x9a\xf3Zb7M\x01\xc7t\xb1O\xe3w\xb7\x1b\xabp\xaei\xde\xff\x87^\xdc\x8c\xb7\xfb\x94\x1b\x91\xac\xa6p\xbcR\x8a/s\x8e\xd5\xe7\xd8\x17\xfd\xda\xd8\xc1\xa4\xc1\xf3\xef\xbd\xdbc^\xa2.\x9bX\xd7\x93\x92H`\x12]\xd67\xfd\xb9\xa3vdp\xfb=\xfb\xa3rS\xb1\x8d"\x8c&lt;CGkE:\xfcg\xb7QR\xf1\xb1,\x10o\x8d\\\xe2G\xd8D\xa1\x86o\xb6\xdaI@&lt;\x1d\x1c?s\x83\xff\x0c\x04\xde\xd2\xf6\x15~:a_[p\xc1O\x8b\xf4]b\xd1RN\xe8\xecR\xb2\xc3\xe0\xbe\x92\xc6\x18\x07F$|\x96)\xbfK`\xd2\xe4\xe4\xf7\xc7\xb4\t\xb9\xa3\xe7\x1f\xfca\x96\x1b\xed\xbd\xc1\x13PH\xe7S\x0f h\xae\'\x16\xa0C\xf0G;N\xfd\x12\x9aA\xe0|\xc0\xe3Jp\xf2\nf\x87\xb0F\xb7FY\x87\xf0\n\x1a\x8e-\x90\xc9Q\xcf\x0bC\xa3C\xba\x0b\x81Z/\x94\xb3\xafa \xc0\x91\x9c\x93/\xc1\x89jX\xce\xa9c\xd3\xad\x14\xca\x00\x0e23I\x96\xe2/\x05T\xa0Cg\xd6\x06\x8e\xc3\xbd\x9bo7\x17\xb6\x96\xbfHr\xa6\xd8[9me\xa5\x04\xc7l\xe6t\xdc\xd7y\x9c\x1f\xec\x16M\x0c\x9f\xca\xd9+\x95\xcei\xb4\xc1\'\xc4\x9f\x05W\x8d\x856\xe4!\x1cS\xd0\xc7\x18I|\xa0\x96\xe9Tl\xdc&lt;?\xf3m\x05{\xc1\xd7\xd6h\x98\xdc\xb3\xd8\xbda\xc4\x82\xfa&lt;\xd8\xb7 &lt;\x82\x03\xce\xd5/\xf2\xb0S\xbb\xa9H\x1c&amp;\x05\xe8y0\xd3\x87\xb7\xb4Y#K\xb62:\x00\xcdKik\x9d\x08\x86\x8cz\x016\x99fwcH+\xb68N\n%\xf2J\x075\xb8\xd4\x04K\xfb\xd4\xef\xe1B\x9f\x01\x88\xfa\xed\x88\xcb\xfd\xfbq\xb1\xceu\'K\xd4\x8c\x81\xcd2?_\xba\xda\x86\xec\xd9\x98(\xbe&gt;G\xf9\x8c\x99H\xe8\xa8?&gt;Gr\xe16sbI~M]\x87:\x05\xc9\x81\x82\x97\xfc\x00&lt;\xc5\x1d#vx\x0ey\x0b~\xc6\x8e\xadh\x8f\xaa\xe2\xcf\xbd\x81\xa2\x8c\x952[\xb6x@/\xad\xa9\xe0a\xb9\xf4\x9c\x01\xf2Q?\xd0s\xe3S\xa8b\xb5\x9e(\x03\xf3QtUxh\x9b\x12{w\x0cZ-\x11\xb7\xa8\x1c\x80`b\xc7\x14\x0bPK\xa4\xb8\x9e/\xc4\xc6\xcd\xd3E@J\x14Y\xec\x8aA\xd68\xcd!"]t\x02\'*\xf1\taN\xd5\xb6Qj\xa3\x98\x04\xf3x\xe6\x87a+\xdfAr\x0c\xe8\xcc\xb9^\xf75\xe3\xd4\x88a2h\xf0\x82\x8c\xdc\x85\xe4\xb5\x180\x00\x01qm\xa6\xcd:\xc8\xe7\x01\xc8s\'\x9a\xd7r\xa1X\xc7@`\xdb\xa4OI\rtw\xe5HA\xcf\x17z \xbb\xc0~\x11\xcc\x98\x9bxHE\x89\xd6\xb4{rj\x12C\xbd\xb1\xd8}\xb4#\x8e\xf6.\xb0@;\xf1\x10\xae\xa8\xaf\xb2\x03X\x97_z\x15\xd2Z\x85\xac\xc6\nr\xb3\x94\x85~\x87p\xe8\xddx\xe8\xaf\x93[\xadm\xa8~J\xab\x83\x85p\xca*3\x9eU\x99\x84\xb3p\x8a~\xb90"\x89&gt;\x9a$\xd8B5\xefI\x8fP\x928\x1e\x12\xad\xc9\x93~\x1d\xf58\xed\xe7\x97\x83\x98=&amp;\xa1\xf4\xd2w(o\xc2\xa1\xa6\x85\xefk\nI/\xc5\x16Lm\x1a\x90\xcf\xe9\xc1\xb9\x90gM\xceo\xd4\x9eE\xe2"mV&amp;I\x153\xad\x9f\r\x94\x16\xd2\n$\x9bS\x85\xbcN\xe4\xd1\xe3\x82\x98\xa5\xe5\xbc\xf7\xc3\xeb{\xd7D\xe7\xd3l\xf4e\xb4\x13\x1a\x8c\xca\x90v\x10\xc8\xb3 lM\xadS\xd3\x95\xfd$\x94\x94F\xa6\xa4\xf2\xa9\x01\x02vg\xa7\xc8f\x86\xa8\xd6\xf0E\xed*\x9b5\x92\xd6\xd5\xad\x94\x1dV\xd2\xfa\x0f\x07\xce\x18\xa9\xd7\xa5\xe9\xe6\xc6bf\x07\xd0V\xef\xf2\xd9\xa5\xa8\xd7\xaf\xe5\x85\xbd\xa1\xdfPpL%\xec\xb1UxyQ\xf1\xf7z$\xaaq2\x8d\xe7,h\x8b\xf1/\xad^gQ\x97\x96TZ\xb6dP\\\x9cA\x05%N\x86\x17\xe7!ep\x1f7\x00\x0f\xdb$6\x8a\xd1\x87\x16#\xb2\x0e?\xcd\x1e\xa8\x8c\xf6]\xc4U^\xb9M\xeaV\x15\x8e\xf7QTa\xbd4JcX\xf3\xe0~i\xf5M\xc1\x95\x94\xf1\x8c+e\xef,\x91.+\x1d2\x10dL\xc4V\x8d\xa09(\x95\xfc\xf2\xa3\x0c\xed\xb6\x0c\xd8A\xee\x82\xc6\xa1\xb2e\xbc\xa2\xc0\x81 \xd5\xd6\xd6\xe7k\x0e\x95y\xcc\x88\xdd%\x93\xfe\xb5\xcdO;"1`\xcb^\xe7\x06s\xf8D2Q\xb6\xae\x10\x9d\xfac\xa2\xe7\xec\xf8\xb6 \xb8z\x86\xc3\x04\x1d#6\xdajE\xf2\xf8\xc0\x16\x08\xdbJ\xe9\xd4mM\x11\x9f0\xf8\xca\x1b\x18\xb1\xa8\x88,\xad\xfe|%\xf9m\xde\x8aT\xfe=\x08Ca@\xa3 \xca\xc7\x04\xb8C[%t\xd8?K\x10\xf03B\xac\xdf\xa6\xf5\xeb$&amp;e\xdd\x93}\xff\xf0(4\x05\xcfK\xf3\xfb\xad\x8a\xf9;\x08J\x8d@\n\xc2\xa7a\xe4\xd6!-\x11qIE\x0e^Q\xee0\xda\t\xbb\x9c\xb8\xb1q\xaep\xee^\x94\x15\xcb;\x04\x82.\xd9\x0c\x0e\x00]\xad"\xa6\xa8\x1c\x8d\xcc-\x84\xa7\xe2\xc0\x8c\x9a\x87\xcb\xcexo\xbd\x83v6\xcat\xe2f?\x94\x91c\x13c\xfe\xb5\xbb\xea\x14\xfa\x83\x9c8\x16N\x04\xca\xa8k5!\x9f\xd2\x8fY\xd9\x91*\x00\x05\xcd\xa1\xaa\x0e\xd7\x935\xc2\xd7@4\x0cUQ\xe4-\x12\x97$N\x03n\xe8\xdfZ\x9c\xce\xa0\xdb-\xa9R{\xca\xa5:N|@\xf4\xdea\x93"\x1f\xfb\x8c&lt;\\,\x81\xe5\xa2\x86\xab(\xfb\x1d\xe4y\x89fs\x06\x81\xb1\xdb\x85 D\x92\xaa\xeb\xd3\xda\xc4\xf2\xfbl\xdep\x9b\x9d\x8a\x01m%\xd5\x80[{\xff\xd7\xaf\x1d\x80{&lt;k\xf1&gt;\n\x99a\xb2\xdf\x17\x10\x91\xc3w\xb5\xce\xfa\xbel6b\xd7\xc0\xbc&amp;@*w\x9d\xad+\xc0Q\xc2\xb6XLa\xbc\x80\x8f\x97&amp;\xe7;k\x80\xdc\x80\xe2~]j\xd9A\x07\xcb\xc3q\xcb\xca&gt;\xfe\x81\xa5\xe5\xe0d\x19_8\xf0\x91\x08Y=\xe8L\x1c(\xd5\xcc\x03\x17znj\xc8\xc3\xfcN\xf7\x08A\xf8\xa5\x83\xe5\xdc\xea,EPJ\xd2\xdc\xf4\x16\xdc\xfex\r\xef\x8f\xc5\x06\xb1\xa4\x15\x1b\xe3Bn\xb6v\xe6\xbf6reO&gt;\x9b\xed\x95\xe0@\xc7\xf6 \x89\xc0\r\xa6\xc7$\xd5\xc7c4\xbc\xd6|K8\xd7\xb01\x02\xef0)\x80\xd5\xfc\xaf\xdc\xe1T9\xb0\xe8\xb8#f\xa7\xd7\x8d%T\x08\x042\xe1\xa4\x18\xce\xb8_C\x84[\xd8\xa2\x00\x02v\xf8S\x7fm\x04\xfa\x17Z\x03\xca\r\x102.L:\x16\x85\x06\x7f=\x9fW\x15e\x9a[#\xa7\x92\x9agW\x98j\xd38\x82\xf4rs-n\xdaL\x1d\xe4\xf6\xcd\x7fz\xad\xafM/(o\x9a\x9c*\xd8\xe9q\xaf\xfb\xac\xba\x02\xf7\x00\xcc\xcc\x1dCN\xbf$x\xc2\xae}\xc2O\xb2\xb0\xf8^#\x17v@\xa0\xdf\xb8\xf5\xfcV\xe7R\x88\n~\xf4\xff\xd9\xc8\t\xb9\xe5*\xbb\xc3/Dz\x80J]\xd9"\xa7\xc6yr$aMiE\x0c\xa0&amp;\xa8\xfa\x0e\x17=]G\xf9,~=U\x10\xda?\x90\xec\x0e\xab\x17j\xf2\xb9^K\xf2\x15]3\xc6\xfe\xaa\x04-\x0e\x95\xc5\xa5+Zf\xcd\x99\x99\x98\xc8\xd0\xf4}\xe3\x8aO\x12l#\xdc\xc0\xaf\xdd\x02!\xf2\x16Bm\xaf\xc7L\x9b\xd3\x97\x92\xed\xc3\xc5\xb5\xf1\xde\xf51\xce{\x99G(R\x97\xe5\x0f\x07Z\x97\xb3U\x9d\x9f\xde\xa0\x00\xa1#|ps\x8f=\xbd\xf3\x05\xe0\xe4\xdf\x91\xdfRM\x90&amp;\\R\x12m}\rKM\x07\x04\xfd\x97\x15\x1a\xe8\xa3^5@\xf6\x06\xb9\x1a\xf0\x9c\x84\x81k\xc9\xcb\xddW\x04\xab\xb3\xd4\xdb\xf5\x85\xcd\x83I\xe0\xcc\xbbE\x9b\xf8\xff\xba\xf5\xad\x17e\xf6N\x87\x9d\x1f"3\x94\xa1B\x14^\xbb\xf3yv\x00\xd0\x88\xf25\x8fGh\x8d\x11}j\xbc%\xe6\xea-O\xdf#\xbf\x17]\xce$%k\x97a\xa9\x1a\xb0\x85\xcd\x90~v5u\x8e\xc3\xfd\xf5Y\xe0\x08JG\xbb\xbav\'!\xc5\xa1e\x16\xdc\xa4]\x1c-&amp;\xe8s\x1d\x14\xa5s\xc2\xadn\x9a\xd7\xd1H\xc0\xab\x92/\x9b\xe9\xa9^\xc1P\x91[MW a\xeb\x1c\xde\xad\xaf\xc4\xe99\xf9}\xec\xe3\x11nn\xa8\x92\x0c\x90\xdd\xec\xf2\x9f\xeam\xd3Q\xd8-\xdb\x82\x15Y\x15?\xed\x16q&amp;\xe3\x1a@\x19C/\xde\xf5*\xe3%\xdf\x82\x8bm\x9c*a\xed\x89\xb5\xc8+*\x01\x15\x8b\x95\xfa\t\x9dm[\xaa\xd3\xec%\xc8A+\xd5\xc9\xeb\x1e\x86\xd3\xb1O\x8e\x15||\xc1\xfa\x92{Mv\x93\x07\xd3\xd6"\x9df\xa4\xd0^\xa0vw\x12\xe5\x91\x1e\xe1&lt;\xb1\x13_7a\xa8\xf8A6\xea\xcb\xe5cMbt\x0b\xa2?\xf9\x93\xdeE\xdf\xf2\x05\xf1\xa5\xf1\x8d\x00\r\x957\xcfQ\xf5\x061\xda4#{\xe3q\x90F\x0eG\xc5\xa1R\x9d{\x7f\xd95\xa9\xc4M\x0c\xfaAW,\xf7^P-@\x0f:\xf8\xdb\x1d~\x1e[\x0e\xe3q\n\x04\x93&gt;\xa5\x12\xe0)\\\xb9qe\xa5\x95nQ\x1a\xb7\xca\xfe\xee\x80z\xefXr|\xab\x86a\xcf,\xc2D\x85\xfa\x82\xb0X\x9d\xfd\xd3\xb8\x95\xe7\x0bJ\x0c\xb9-\xc1\x98\xf3|\x9d?q\x89\x8bUa\x13 Q\xe03\xc3\xeb\xf5\x85}=T\xfe m\xddV\x87Z\xa6\xc1\x9a\xfb\xab\xbe\xc6\x8b\xd0-D\xce\x99\xae\x1f_\x1c\x19/I\x8d\xda?\x98)\xa6[\x17\x8ah\x8e\x19\x99\x9f\xcf\x97\xecl&gt;c\xb4\xfb\x92G\xf4\x82q*\nk\xe2\xc7\xbb\xfa\r\x9b\xf9D\x14\x88\x1b\xa8R4\xb5\x13\t\x8d\xc7\x94$\xf4b\xb0\xe7\xf1\xfe\xbb\xebuJ\xbb\x9e\x8d@\xd5\xc4Mw&gt;G\xdd\x98\x8biu\x95F\xe3\x1d\xf4\xe6\xc4I7\x83\x9e\xaa_\x9d\xf9\xf8\xe9\xaa\xc5`\x90\xdc\xe6\xe0\xa4w]\x89\x82\xe5\xfb\x01v@%&amp;}\x8a\xdd$\x95\xcdNI\x8a\xa4\x7f\xb0\xd9pH\xd7&gt;k\xe0\xb6\xd77|\\\xe4\xbf\x14e \x02\x8b+\x8f\x0b\'\x8akq\xc4\xd5\xca\x81R\x1a\xb0l\xcc\x0b\xbb\xd7\xce&lt;#\x9b\xf7DlAf\x9eL\x15N\xac]\x11\x08g\xe3nx\x9f"8S\xd9/\xb6\xb6\x88\x95\xb67\x92\x07\xef\x1e \xf8\xfbv\xe7\xbck8\x9e&amp;\x02\xd5l:]\xfe\xd4\xc1\xf6\\bzv\n\xa29\xafP:\x0ee\x8e\xd4\xb6\xad\xa2k\x04J\xfd\xe3\xe5$\xe6\x8f\xef\x87.Ci\xd7\xa2~\x18q\x81\xe5%`\xdf\xf8\x98\'\xe0&lt;\xd4\x97m&lt;s\xee\xcf\xdbkeI\x9f\x8ct\xaa\xbe\xdf\xae&amp;\xe7\xc6(n6w\x9f\x8a\x83\xdc\xb4P\x07\x83!h\x92^\xce\xebk\x8fJ\x07O\xc0\x06\xbah\x1f\x18\x13\xe3o\x1fR\xdb\xae\x15w\xd1?@\x04;\xdc\xeb\xd3\x85\xcf\x85\xc0N\xa8\xe1\xaf\xb0,\xb4js\xb7\xa8PxQ\x1dc8\xb5\x87\xc2\x8c\x96p\xb8\xc8\x06\xec\xda\xc5\xceJ\x15\xb6RTw\xf6\xad\x82\x96{\x1e\xb8;jH\x0e\xe7\xed\xcaK\xbe\xb1(\xaa\xda\xaa_3\xb8?JZ\x96[h8\xdcr\x17d\xe23u\x10\xe4\x14\xbat~\xdc\x15\xed\xd5\xd4+\xfb%\xd4\x89&amp;\xfd\x0b-\xc6\xd0XdF8s\xfb#b\xea~\xe4\x9e\xba\xd8\x8d\x0cU\xbd}\xb3{P\xf2\xcf\xc3\xc0\xbf\xee\xd5\x8ec\xb9YG\x89Wb\x13)h\xb1-A\xa1\xa4\xf3C\\\x8d\xea\x81\xc8\xcbh\x0e9\xab\x1f\xff\x88\x95\xf2&gt;@f\xc2I\xc3k\x81\x81\xfb\x15\xa7\xaa]\xc6\xc5\xdb\xf8\xc9\xa0^V\xf2t\x1f\xb6\x81\x99gw\x00\xee\xb0W\x07P\x95B\x10\x18\xbd\xed0u\x06\xc5Eu2y\xfb-\x8a\x0b\xcd\x13\xb8\x1a\x8fZC\x86?&gt;\x82\xc8\x8b\xb1\x97\xaa\xf1xV\x0b\xc4\xedp\xe5\xa7\xcf\xf8\x17\xce\xe0\xd1\xa1\x11&amp;\x91\x17\xc0\xdf\x1f\xc9N\x19VP\x87S\xf5\xe0u\xe6F\xa0\xa6Hz\x97\xbb\x0f\x0e\xc4)H\x9f\x19\x16\x06\xb0\x89\xb7X#q\x84\xc3\xe8L\xaaDh\x04m~\x0f^\x92\xb2\\\xac\x9a/[\xda\x1c\xd2uw\x1f\x1f\x96p\x81\xfb\xd5\xa1\xedsW\xff\n?[\xfa\x8b\xf9\x96\xf6\xae\x90/\xda\x02\x1a\xe4\xaf\xf8\xc3\xb8I\x92\xdb\xdf\xd1\xaf!7}=\x196\x07\xaa\xb3[\xda:g(\x1cn\x86\xd5u\xb8\xdf\xc5\xf5_\x1a\x08\x1b\x02\\n:\xd8!\x89\x1dOQ\xac\xc8\xc1?\t\xd3\xbb(\xedvV:\x0b~\x0co \xd19n\n\x17\xfc7@\xc4\xb1\xe6\r#^\xf8\xed\xe7g&lt;fs\x9b\x1dpr\xd7r\xaa/\x12\xa5b\xb9(\x9bE\xc2\xbd!F\xa0\xd6\x8d\x13\xc4\xd3&lt;b\xbc q\xe4\xda\x91uo\xcb\xaa\xbc\x86(\x8b\xf0x\xb1\xcb\xa80K\x18Xg\x18.\xa62\xcb\xd1e\xdfE\xcf%\xefw\xa6\xf1\x05\x16.\xaa\xc3\xa4\x13l\xb7\xd1\x93\xd7\xd86\x87\x96\x84\xa7} \xd7\xab\x81\xda^&amp;\x11\xab\x1f\x0f!*\xbc\xd2\x89\xfc\xb7\x13\xbc-Q\x88\xcfB\x88\x1c\x83\xce\x85\xf0\xf4\xfdI\x98\xa5:\x04\xd6\x83\xaa\xb4Y\xd6}\xfa\xef\xf3?;e\xeb\x95\xb6\xcd\x9a\xd3\xefIE\xae\xaf\xed\xd3V\xc8\xfc\xa3\x08Q\x11\xe5k\xee\x92\xeb\xee\xa5G\xe1\xee\x82\xf5\xdb\xae\xfd\xc4j\x15q\x93u{\xbf\xaf\xa8g\x8d\xd7\x976&lt;\xae\xeaT\x85D\xfa\xae\x15TZ\xd7\x89(x\xc5\xbe#\xf8\x0fx2D\x02\xa8\x1as\xc1\x01\xf0\x89\xe7\x8d*\x02x\x80id\xf4-\x93\xd3\x0cpl\xccW\xe4}\xdc[\xa2FZ\xf8;\xda\x17\x9a\x0bO\xab\x83\x87:\x17\x87\xd9V*\xab6\xc7\x7f\xc8:\x95\xbbeL.\xae\xa7\xd4L\n\xb58\x17J6eC\xda\x1aK\x0f\xd5\x80\xb9\xcc\xac\xe5\x85\xfa\x15\xf1\x05\x80pz\xfcuD@X`DH9\x10\x15\xbc?\xa2\xad\xef&lt;d\x08va\x85\xe6\xaa\xe0g\xb8\x05x\xad\xa9u\xc9\xb2\xf2-T*\xca+\x02\xc6&lt;\xea\xeff%\x8b\x86\xed"\xd1\xf61\x08\x08\x0c\x0e\xd4\r\xb3\x89Q\x1f\xe7K\xf8w1\xfd\xf3\x97\x1f\x14\x89\x1ay\xccK\xd4j&amp;-\xc1(a\x89`5F\x1eX\xc3\x05X\xdf\xd3\x052\x85%B(%\xfc\xc20dK\xbc\x8a\xf2z\x9f}\xe2\xf9\xdb\xc6\x8eoW\xbf\xad\x93\xd4B\x87\xde\xf0\xe4UKN\x86\xdcn\xb0\xa3\xa0\xbd\xa6\x1cY\xd4\x92\x8f\x84\xd4\xfb\x82\xc8\xc2\xad\xcf\xdenP^V6\x8bz\x1a\x06\xb7\xb3\xb5:\xa9\x17\x81\rC\xed\xa6[\xaf\x9b\xd6\xfa\xa7\xd9\xc8\xfa\xad\xfbW\x9c\xf7\x89n\xff\x0fV\x90\n\x12=\x06\xa0\x90\x02i#O\xf4\xc7\xf1\xb8\xa8\xcfy\x83\xf7\x7f[\x19\x98lp\x0e\x926{\xc2;\xe6\xb7\xf6\'Q\x0f\xa5"\x08x\xa8\x8b\xe5\xb2\xbe\x9d\xaa(\xba\x9aJ\x9e\'L\xb2H\xb8\xe9J\xbb3\x13&amp;\x04\xdf\xcc\xb8\x98\xb9zAhC\xf3\xb0\x0f\x04\xa6\x96\xc7\xd3{\xf4v\x99G\xb1\xb2\xb1Z\xee\x95\x18\xe8\xb9\xb1\xaf\xcb\xdb&amp;\x03\xd5\xba,s\x88v\xa3\xb4\xcc#\\]\x86\x9e\x0e\xe8\x92\xe5*W\x0b\xb2Yb{\x8e\xbc\xab\xd9s\xf6\x80rO\xf3,f\'\x97\xe5\xecU\xcf\xb2j\xe1(\xc0Q\xc2\xd1\xc4\xb6\xf1\xf2\xe2\xca,*n\x8f\xca\xd8\xb7{\xfb\xdcSE\xd2\xbadI\xf5\x19}\xe0\r\xda\xf83\xf9\xa6\x8e^\xe3l\x8a\xfa\xe0i\x96E\xb6\xa3\xef\xc3VK&amp;\x008\xb9\xed\x8amD\xc6\x91\x1c\x8a\xe9.|\xe2 \x99\xa7\xfc\xdd\x99\x81\x03\xe3\x0f-\xb8h\x08L\xf3\x18\xfe\xe4\xd3T\xa4\x1fA;3\xb2a\xe4\x1d\x82`1P/\xfd\x892\xaf_\xb2\xbb\x1e\xcbx!\xd4\xfa\x0c\x1f\xc7\xb37\xb2x\x0b\xc6T\xc4\xc4\x0c\x18\xc1\xd5.\xac$\xc8\xce\x0e\xd3\'\x85\xe4&lt;\xf0\xe6\xff@\xbdj\xd65\xa2G\x9d\x18b\xbf\x11lB\x18\xaa\xa6w\xe4-S\x1b\xee\x90S[\xa6&lt;\x7f\xc1\x94\x88\'\xe0p\x9b\x052\x8a\xbf\xd1\xaf\xec\xc9w\xd8\xa3b]\xd6\xbeyr\x84x/\x94,\xfd(a\xbf#f\xf8\xae2\x9a)\xbba`s+\x9faX\xed:\x01\xc0\xdac\xb5\xe7R\x8e\xa5\x14&amp;Z\x0c\xcd\xd9\xa7\xa2 \xd6N{\xdc\x9d\xdf\xefZ\xff(\x89\xef\xc8\xb2\xf4\xa4w\xe8R\x01\x11\xeb\xf4H\x84\x1b\x92\x9f5\xbe\xecy\xb6j\xb3\x86$q5.&gt;\xb3\xca)\xfa\xb9\xeat\xfc\xa8\xa3\xd1=:\xe6f\x96u\x9d\x81\x14f\x18\xda\xebg\xd9F\xb7`xPL\x98Y\xb9\xd3\xdd\xdd\x87\xd2$\x05\xd0\xf4\xd6\xa7\x86[\xa3\xe4\x15op\xb5\xc6\xc6NZ\xb7\x12.\x0e\x036\x1f\xcb8\xc2g\x8d5\xdf\x1c\x83\x9d\xf2Lt[_\xca\xc3\x9d=Z\\}\xc7\xb1\xfa!\x02\x040\xa9\x87\xba2 \xb5\xa4g\xe4\xecM\xebu}@\x86s\x8fP\xf3\x88\x96z\xfc\xdfG\xfdLn\x86\xdf\xb0N\xc8\xed\x95\xfb\x00\x9f\x93\xce\xab\xf6n\xa8\xc9\x89\'\x917\xe0\xe5\xad\xa8\xeb\x0e\x1b\x8e\xc0\xab\xb8\xac~\\S\xfc\x8c\xcd\x0f\xf0\xe2%\x87#\xdeP%\x08\x86\xbap9r\xc0\xcfh(\xc1\x7f\xb0Mhm\xc93\xd5\x14\x8a\xc8\x98\x08\x17s3L\xd0\xa3~}\xbc\x04\xa0{\xf8m\x15\xc0d\xa8t\xbe\x03Cr[\xb2p\xb2\x99\x81\xe7\x9a3\x93\x8e\xec\xd6Z=\xe1\xe4\xc3\xc9)\xfd\xed\x90\x8d\xd3\xe8,\xa1Z\xfdA\xf1\xd5t\x9ak\x83\x06\x9d\x1e\xfb6\xaf\xccA-\xf3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Espremedor De Limão Aço Inox Manual Forte Resistente Goumert Pratico - Efigen Prateado</t>
+          <t>Calça Tactel Jogger Com Elastano Active Wear Void Verão</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>44</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>199</t>
+          <t>68</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>10% OFF</t>
+          <t>15</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/espremedor-de-limo-aco-inox-manual-forte-resistente-goumert-pratico-efigen/p/MLB57553562?pdp_filters=item_id%3AMLB4534315079&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB4534315079&amp;sid=affiliates</t>
+          <t>34% OFF</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_705348-MLA99579919952_122025-AB.webp</t>
+          <t>https://produto.mercadolivre.com.br/MLB-3904422855-calca-tactel-jogger-com-elastano-active-wear-void-vero-_JM?searchVariation=186002428195&amp;pdp_filters=item_id%3AMLB3904422855&amp;extra_comm=true#polycard_client=affiliates</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>b'RIFF\xd0*\x00\x00WEBPVP8 \xc4*\x00\x00\xd0\xf5\x00\x9d\x01*\xc0\x01\xc0\x01&gt;m4\x95H$"\xa7)\xa3Q\x9b!0\r\x89in\xe1j\xb3\xfdy\x9d@\xe6\xb4\xb1\xfa\xeec$+\n8&amp;m\xeb\xe7d\xf4\xb3\xbc\xdd+W\xe3~\x04\xfa$\x9df\x17\xfbu\xd4\xca\xc5\xdc\xde`:\xff?\x84\xc5\xf7\xf6\x9e\x80\xfd\xa5\xe9+\xfe\xbf\x90\xd7\xe0?\xe1\xfb\x08\x7fD\xff\'\xeb\x17\xfe\xff\x98\xdf\xb2x\x1c~\xf0\x13M\xdfI\x91\xa1\\\xf5\xcf\xdd\xc8,\x02Q,\xe4~9a\xeb*\xed&lt;Z\x96\xa6\xac\xc0/\xe6\xd5\x9cwQ\xc6\xae\xb9\xd1_\xe8\xca\xc3\x86r\xac\xe27x\xd4\x0b/\x9f\x11|\xc0\xc21\xc9\xb4\x7fCw\xe6\xf6\x10\x83&amp;M%\x06\xdd\xf11\xdf\xd57\x93=\t\x93e\xd5\xb6\x82\xbe\xfar\xd3\xef\x81\xd6\xd8P\xc0Z\xbf!\x10s\x06mA\xef\x9f\x17@#\xe9\x97\x9f\xb1v]\x888\xe2\x9f-4*\xc3\x8c\xe4\x94\xdfK\x86-\xd4x\xbeo\xe7*7dF\xdc\t6\'O\xdc\x17w\x93\xd9n.\x01\xe6\xf9\x11P\xc5Q~\xe5\xa1f|+\x1c\x93p\x18V\x81\xac\xa6\x96&lt;$\xcfT\xac\xc8j\x17\xf1I\xe2\x80"u?\xf6bT&gt;\xee\xeb\xce\x1eK\x8av\x12\xd8\x92\xd2+\n\x03\xa3:&gt;\xe8Q\xc4H\x18F\x19\xc4\'t&gt;B\xd9\x83\x13\x0bM\x088R\x13]\x8d\x83\tX\xad\x95]\xb4\xbe%g\x00\xac\x84\xe7\xb8h\x9an\x9f\xa0\x8d\x8cC\x7f(\x14\xe9|\x13BZ\xd1\x83Ug\x91\x00\xb0*\xef\xe1\x03\xad\x056ZD\xc0\xeb;\t\xbe}\xb4\xb3\xe7\xbbN%m\x12\x7f:\xba0~\xbd\x19\x04[\x16\xd6\x87\x0c\xb5\xc0\xc0*\xf0h\xf6b\x84\xb4\x92\x8f\xd0B\xe3=\xf6G]\xc8\xc4Pl\xb2\x85\x12\xbe_\x0eL\x06\\\x86\xaa-\x02a\xea[\x19\x89\xf1&gt; (\xd8\x8d\xaa\x06(i@\xda\xefl\xb3\xd6v\x18\xa2\x1a\xa7\x7f\xc4[\x05\\\xe0\xa3 ,s\x1f\x89z\xf0Q\x80\xe2t%\xc9\x02,"6\xd8\xde\x8dx\xd0\xc8\xa9\xce1w\xe2\xdbw\xa3N:\x88\n\xba\xb2\xd8\xe2 8bT\xc1y\x87\x0e\x1ar\xd8\xb4\x01\xfe,G\x7f\x9a\xe6\x87\xa2rX\x0c\x92\xb7\xb5\x8a5\xf1\xdf\xf1\x1a\x9b\xad\xa1:\xdc\xb75_f(\x80(\x07\xb8\xb8\xc2\xb6\xba\xb08J7\xa8-v\xc5\x99A\xb7H\xa8\xa0a\xf3\xe9\xad\x1e\x97h\xbd\x0b\xbb\x8d\xe0~\xf1\xca&amp;b\xe0\x0f2p\xb9hSm\xcd,\x91\xd0q\x13\xa8|\x85\x87\xac\x93\xb9\xbdc[jE\xd0\xd2\x94\x83r\x83To\xbb\xcdkM\xb8\xe8 v^Z\t|vm\xc0\x14\x97f\xe3\x93\xe1\xe3B\x1f\x04\x17\xab\xb3\xa6\x1a\xb09E\xbb\xe3\xd6\xe6\xeb\xda(\xd5P#\xd3\xb4p\xc4\xf0y\xaeO\x9e/\xcb\xa0\x1a\xe4\xca\xc3\xa3\xb8\xf9\xac\xeek\xfd\xc1 w!\xf8\xcf\xca\xc61\x80\x1e\xdb\xd4J\x1d\xd5\xa4\xda~\xcfH\xf3\xad!\x19w\xbb\x18\x1e\xfa\xa8\x00=\x86\x1d\x94\x8f_\x98\xbfy\xf20*\x13|\x16\xaf\xc8D\x1d;\xb5\xdb-\xb4|\x8e7`\xf4c\xcf\xa9\xe1\xaf=j\x13\xd7pr_%\x8a\x90\x05J\xb1i\xb4|\xa6A\x9c\xdf\xff9\x1cG\x1a\xc0\xe0\xf2\x18\x91+l\xec\xa2\xfe\x98Oc\\\xf3\n\xccMu\xe6\xf5T\x8d\xffl\x11\xb2\xce\xfc8\xeb\x91\xdd\x98\xfb\xab\x9f\xbf\xc7[N\x10-\x0c9\x8d\r\xca\x01\x82tj\x1dB2?+\xe0\xcc\x9f\x16&amp;\x9en\xfba\x96\xea:\x03n\x8cd(\r\xfe_Vni\xe1\xa2\xe2T~\xc9\x1b\xf8(z\x05\x96\xf0\xd9\xe4\xcb\x83\xc0U\xc7\xb3\xf4\xdb\xfa\xf8\xff\xff;\x89\xae\x1eg\xba\xa6\x9f\x07}x\xe58m\xb8=\x86\xaak\x86\x1fl,\xfb\x97\xdc\xef\x10_|\x06&gt;\xa6\xe5a\xfa\xc9TZ\xdf\x85\xab\xf2\x11\x07N\x0e\xb8@\xa4\x14\x99Li{W\xff\xfa\xd7+\xf5&amp;z\xa7j\xab\xef\xd6@?\xcf\x89\xd1\xbc\x04B\xa2\xe4\x18\xffB\xe93\x132\xc1"\x1a%\xf5\xdd\x11\x10\xd7\xa9[C\xc4O\xda.\xc7\xdbQ\x9e\x05\x0c\xb6Y\x84!\x00q\xe9\xc4\x0b+_j\x06K\x83\x06I\xf5\xc2\xea:\xb0\x10\xa0\xd9\xf8\xca\xf8\x8e]}_$\xab\x0e?e\xf4\xa8\x86\x0e\x9cL\xb3\x07\xdc\xcd\xf5\xca\xe0mi\xb2\xa4-\x9f\xff\xd2;\xc6\xea\n\xefN\x8d\xdd\x90\x87\xe1\x14U\xce\x88-HK\x96c=S\xafdR\xc3\x90\xc8\xdd\x01\xe1\x12A1\xc8\x05\x8a!\xaag&gt;\xc4A\xb4\xce|\xbb\xd2\xef*I\xe5|Z\xb8\xfb\xf8L\xe9\x99\xf3\xaf;\x1e\xf5\xf76\xa3STB\x85@\xe8\xfbK\x8e\xd3\x15\x848r\xb0\xe2\xf6\xdec\xd4\x87\xbe\xc4Zg\xa2"\x1a\xf3^g\x86\xa8\x1dPlH\xfa\x93\xf7\x9c\xbe\x9cB\x81\x9b\x1f\x8c\xebx\x7fw\x17\x05\x01\x93\xf0\x9bQN\x01Y\xd0\x13\xf7\xf6\xdcd\xa9\xff\x00=\xc8wM5\xce\xa6\x07\x10\xb3\x16p\x9f\xc7\xdd\xc0\x88j\x9d\xe2\x9e\x00\xc1\x0e\xc4\xd6f\x06\x8cT\xcf\x9f5\'\xf8"\x18\xa2&lt;\xdf\x0c\x8b\xc9\xcb;\xd3\x01\xcb\xdfD\xe8\x83I\xeb\x8d\xe1\x81\xed\xfcB]\x82\x02\x98\xadQ\xd5\xf2F\xfe\x8e"\x1cb\xc4\x80\x9d\x85\xbb\xbe~\xf1/e\xa1\x1b\x8b\x86u3\xa4\x03\x97\xea7Kp\xe1\xfb\xf8\xe21\x11\x86B\xfe\x01R@aw]\x18\xbb\xb5\xfa\x07\x9c\xc9\x88{A\xde\xaeW\tS\xb1\x91\xe0(-h\x98\x87LP\xd4r\x1bW@\xc9\xe9\xbek\xc6JUR\xc5n\xeaZG\x98\xdeZ6\xab{\xa9a\xd6\x92\x9d\xe2\x9e7E\xe2\x8by\xb9z0\xa8yp\x86m\xa0m\x15\x8dF\xc9\xeb5}\xff|#&amp;\xafS\x8d\xa7gi\xbdbj\xddN{o\xd9\x8d\x8d\x93\xe6B\x16\xc0\x8d%G\xd2\xfd\xd3^!\tk/Y\xf2&gt;\x13xM\x00\xfd(\x8f\xddGe\xb0~\xd6\x95^YO\xf5\xe1\xf4\xc5w\x9c\x02\xf1.%\xf1s\x90r\x8c\xac\xccj3\xbfem\x9c\x8d\xde\x1aq\xb2n\x98\xd4\xae\xc6\x17u\xcfm\x9a\x86\xf0\x9a\xf3m\x1c\xa7\xe0\x92\xea{\xf0\x9b_\x8c\xfa\xa2\xdc\x04\tLC\x0b\xf8\x04#\xcf\'4+L\x11D\xfd\x01\xc6\xf0\x03\x94|H\x02\xc0\x0b\x9b\x85\xdc(\xa3\x94\'\xa41m\xfc6\x94\xe0\xd8g\xec\x1d\xe6\xd8=\xdcg=?l\xea\xe4u\xe91\xcc\xafO\xf3\x8b\x14+\xe6\'\xe9\xb5\x1b\xb2QF\xb8r\x9ff\xc3\x0b\xbe^\xecB\xafh7\xf0\xdb\x9e\x94(\xe9\xe4\x91F\xc0\xea\x80LH\x9a\xabG\xc2$\x95#\x7fF\x02\x82I9\x1b\xe8\xa5\xe3\\}\xf8\xa4]\x9bv\xd3;Xe8\r\x1bMo\xbc\x1d\xa6i\xb3x\xcd\xb9\x88\xffL\xc0\x90\xd7\xbb\xbe\xad_\xc15\x8dK~\xca\x17n\x8b\x0c\xfa\xf5\xac\xae\xb3@I?\xbb\x8e\x13\x14\xdd\x1aa\x18\xd4_\xd9\x7f\xc5\xe1\x87\xfc\xae\x93&amp;\x959\xb4KV~)\x1d\x14f6\x8dY\x1d\x87\x16x .\xe2"-\xa6Kw3#\xe3H\x027z\x02w\x9c\x7f\xc6;3\xaeqp\x1f^g8\xbb\x8aR\x08N%\xb0\x1d\xcd\xba\x9c\xac \x15\x07\x14\x84\xf7bh1\x93\x85p\xac}\xed\xd8_\xf5FL\xcfE\x8e\xa1\xc5%\xd4t\x0b\xee\xe9\xd62\x11Q)\xa3~\x92A\xc3ZjgM\xc3U\x89\xce8L\x8a\xb6\x84\xb9\xeb\xfe\x1f\xa05Otn\xb3\xf4\xbd?@;}\xd2F ,y\xb6I\x11\xee\x1c\xb5\x15\x0cY\xbd\x94\x17\x86M=`:\xa9\x9b\x7f\xa8\xfa\x11\xe7f\xcdf\x9f\xea\xbc\x86\xfa&lt;*\xc6\xc4i\x0f\x1c\xbf\xcb\xd4\xb0w\xac&amp;$\tl3\xe9-\xdc\'.\x1d\xe1HE\xf1\xef\xd3!\xf7\xfb\xc6\xca=\r\xc2&gt;\xe0\x02H\xf4Z\x82\xc5\xd0\xf4zfUl\x80\x06\xfc\xce\xed\xbf\xc1\xe34XXZ\xbb\xffZ\xa1\xb8D\x878\xe5\xb5\xa0\xc2"TCc/&lt;v\x8e\xbc0\x00\xb1\xf0\x8d\xc5WZl\x10\xa9\xe8\x1e\x96%\x1e\xd6\x89;T?\x89(\xc8\xb1.\xba"\x90\x8f@\x00\xfe\xfe\xba\x0cN\x1c\r\xb9\x8d\xf3\x8c9\xf4&gt;t!#v[{\xcboS\xf2\x17+\x7f\xc1s\xff\xd7\x13\x8d\x17\x0f\xd4\xea^\x7f\xc8%\x02\x19\'\x17\xcb\xeb\x13GW\xd6\x1a\xc70\xc9\xf8$\x9b\xb4\xf5\x82\x94f\x7f\x89\xb7\x1cuV\xbbr\xee\x06\x9cxU\xdb\xbf\x1e\x15\x0b\xecK\xfc\x90\xcc\x1b^\xdcPH\x82\xf3\xce\xde`7\xf8\x1b"\x12Wu|\xfd\xf2\xa9\x86\xbbZFU|\xd0{39\xb30\x0b\xaat\xd4\x9d\xf00\x83\x93\xa0\xd8\xcf\xfe-\x04\xc3\xe6\x06\x95i\x8b\xba\xc6776\xda3\x0c),\x14"\xb3\xb5\x1a"\xac\xbdP~L\x91*\xcd\xe6\xa3\xbb%\xca\xcc\x7f\xfc\x80\xa8I\xfbmA\xe4\x9e\x8a\xdd\x7f\x82\r\x16\xe4\xba\x0cF\xe5U\xd2]\xbc\xb3\xaf\xfb:\x8b"`\xf5\xb5\xc0mU2\xe1\xdd\xc1\x07\x19\xdb\xdbd\xf4e\xfa\xa9\x10K\xe5\xf2\xda\xfavZ\xe0X\xc2cc\xcb\x18)r\xec\xb1v\x88P\xf1\n\x93\xb4\x10\xf0kC\x00\xc8\xe9\xa04\x8d\xb8o\xb5\x1c\xf2pKW\xf8\xd1p\xc9\xddT\xc1\xf2837\xce\xc1W\xd8\xd7\xd9\xee\x8a\'pY\xf4\xa8\xf0\xaa\xfe\xfew\xbe\x15P\'8"F\xba\x08\x07\x92\x86\x02\x92\x9b\xf6\xf8n0\x8f\xc1\xbd\x0bf\xb7!\xcb\xb6\xe6r\x99$\xde*)\xf8\xfd\x9c?\xff\xa3mt\x11\xce\x06D\x9c\xc1\xa1\xaf\x1f]6\x7f\xabs\x89.\xfau\xc2\x90\xb1\x91:\x80\x04\x00t\xb2\\\xe2P\xaf\xb7\x18\xe8\x0b\xb4\x03A\x97\x14\xa5x\xa2\xc2\xabhk\x05\xd16"\xb8\x84\xb2\x80f\xf2wY\x162Of\xd1\rP\xaf|\xbc\x014\xb9\'\x8e\xcc\x84\xa0z\xc7\x03\xbc\xa7I\xc3\xed\xea\xc6{\x17j\xe5\xa6\xc2\x94\x8b&lt;;\x96\x7fdE\xef;-\x94\xdb\x89c\x12\xe7t\x9c\xd8\xef\x00S\xac\x02\xd4\x83Y6b\xbbo\x81\x17\'\xbd\x8a\xb5\x03;\x1c\xbe\x05\xa0\n\x8a\xecP\xda\xa6u\xc5\x7f\xdcAiN\xefZ\xb9\xac$G&amp;\xe6\x18\xec\x9a\xfaz\xdd\xe4Xa3\x94!\x00\xfeg\tb\xbf\xf0\x80\xe9\x02\x80\xaa\xf0\xf0\x0f\x06\xdb\xc7\xbfvt&lt;Y\x1aT\x9f\'OI\xccJ\xc6\x98\x88\xe2\x97\xd4aq\x8b\x1f\xef\x9d\x99\xf5\x03\xe4\xe4\x0ck\xdc\x03=&lt;\xe4\x1f\xd6\xd6\x0fNh\x8e\xc1\xf5\xf8w1g\x14\xdc^\x04C!\xc8,%m\x8a/\x0f\xe5\xd2\xf4R\x84U\xff\xaf\xa9\xf8\xdeW\rhx\x17sM\x9b?\xb1\xcfC\xe7\xb3\x1b8\xd8f\xddY[\x88T\x89\x96\xb2&amp;\xdd\xa3TC\xf1\xa9\xeb\xf5\xb8\x1bs\x99H?\x9e2\x06\xd8\xabG3c!\xf2\xbb\xecH\x8az\x0e\xda\xb2k\xbaM\x9f,\x7fd\x17\xba\x81\xce9\x91\xb8(\x00\xc7\xe0\x81i\x9c\xf4\xa6\xa1\xc1\x92~|8O\xfe x\x11\x91\xff\xab\x8b\xff\xf6TB\x8d^\xe7\xca\xec\x8c\x18\x1c\xe4S\x8b\x8a\x1eG\xe8$\x7f^\xd00\xd7wF=r\xee\xb1\xa9\x0f\xd1\x12\x8c\x8b#hc\x14\\\xf2o\x17\xfe\x06W\t|m\xc9\x07R`Y)\xd4\n\xf7Y\x1ds\xca\x1fu\xdb\xb4\xd3\xbc6\xd2\xddU\xec\xf2\xce\x94\x96C\x85\xbc\x97L\x88wr\xb8\xba5@\xa1J\x1aq\xa5k\xf8\x8cZ\x88M\x07\xd1hP:\x1a\xdawA\xe7e\xdb\x10\xdb\xce\x90\x17\xaf\xf6\x90\x8c?"I\x1e\xfb\xff\x07\xad\xf6\x0c\x94\x9cb\xe7\x18\xf8\x8c\x8c\x89\x0c\x113\xa5\xbf\x90}\t\x14\x9a\xc2gc\x0c\x1c\xc7\x01\xf5\x84os\x9d\x90\xad\x0e|\xe1\xd5d\xc7\x14]|\xa7st\xe9\xb3\xe2\xe6\xc0\x83(6\x81\xcb\xbb\xdf\xb2HL\x1a\x9ctO\x92\xff\x18$\xe4\\F9\x06\x0bm\x0e\x12\xba\x9e\xec\xbe\xadx\xfcj\xa3+&amp;\xe7\xc3\x1141\\\xbaK\xbb\xe5\xbdX\xdd\x0f\xe5@XC\xd9!yi\xefBV\x03Y\xab\xff\x9e\x8e\x8e\xc3\x8e\xc6:\xd0R[\x19\xe1\xf4\xff\xbaL\x19\x08&lt;\xdcGI\xd9\t\xd6\xa2\n\x0f\xaa\xda\x8e\xa7\x07\xde?=\xc4\xe9\x9aII$%\xf6h~H\xb3L\'\x08\x1c\xa3\xab\xbew\xe4=\xc0?\xfe\x8d\x04\r\xb2h\x05@\xbc&amp;\x9f\xf4\xd0\xed\xb4\xa61}\xba^q\x0el\x00\x03\xa3\xde}u\xeeBU\x12\xfcf\xab\xc7MkE\x92\xf0\x9a\x05\xc3\xe1nJ\x04n\x84\xa5\xb1\xe9@\x08\x1c\x0bc\xd4\xbe\x0f$\xacn[\x19\xfb\xc7\xae\xc5-\xfb\xf6}\xda\xccw\xdb!\xc2\xc4}\xba\xfaH\x88\xe3\xa6\xdd\xaa\x826\xdc a\x9eiql\xd1\xe0\x16/\xfa\xe6\th\xe2\xaa\xbdtu;\x8b\xb6\x14\xab\xb0\xc3\x13\x05z\xa1E\xcd\x15\x84\xbb\x12\xd1\x19\xb5\xd0\xd6\xc9o\xc6\xd1e\xc9\x18j\x02\xbebJE\x05\xed,\x0e\xe6l\x16F!=\xbc\xb4\x80\xf8QO\x8d\n\xfe]\x0ca}\xf4\xed\xa1`\xb7[;X\x9fD UZZ\xf9\xab\x1c\xc5\xb23S\x853\xa2\xe05\ny\x8a\xca\xab\xc0O\xfb\xbc}H\x08\xf3\xf9k\n\xba\xf4\xb7+\xb0\xee\x9c\x17\xd9}\xae\xfd\xe6\xb0\x88\xe9\x1ea_\x82\xf4\x18\x1a\x95\x08\xfc\xd7x\xb5\x1f\xfc\xfeq\xa3\x06I08\t\xdb\x8d\xe8h\xb0\xbeX\x85#\x9c\x8b\xf4\x00\x1c_\x07\xce:\xea\x8d+\x90W\xc7\x95\'\x94\x16\xado\xd4rX.Y#!\x9bvt\x80~\x82M\xd1\xe9\xd3\x1f\x98\xa0\xf9\xcb$\x92\xbd\xcbL\xed{:\x84\xeb&lt;M\xd9\xd0\xa0\xbc\x18\xae\xabvTDj\x87\xf2i\x11\xfe9y)\xfa\xec\xd3\xbe\xb6\x8a\xc7\xceF\xdd\xac\x067\xa3,EF\xe3\x02\xe1}\x99\xf4.\xd1\x1d\x03\xe6S\xd4\xcf\x1d\xa2l\x99CSmP\x86\\\x81\x14\xe1\xe6)\xf8;\xc3O\x8d\xf7i)\xdb\x1f\xcc\xd0\xd0\xb7&lt;\x94\xfa\xd2\xf4\xb2\xb8g\xacb&gt;\xf9\xd5&lt;\x18lk\x83\x13RY\x06\xd9\xe8\xd3\xda1\xfa\x8dY\xf3W\xc9s\x1f\x83\x91\x0f.\x1e\xba\xcb\x1e\xe81S{!w\xdb\x90&gt;\xe07\xc3\xa2\xe0s\x9d\xfa\xa5*&lt;\xd2\x14\x01\xf6[\xab\x8f\xc30:h\x1dW\xe3r\xdb\x92\x9e\xe3\xc7\x8cU\x969Z6\xdd[\x83]\x83\xd9\xd9=V\xb7yhq@*\xbexMM\x96l\xa8-\xd0\xb4\xdeH\xf1\xe8)\x987\xc9\xf7$\x1b\xa4\xa3\x80K[\xdb\xb3u\xab\x80\xac\xc2v\x96\x10\xa2\xf2\x1fM\xf6\xd6\x9cx\x88(\x9e\xdb\x92\x96\x94\xbf\xf4w\x84\xac\\\xb7\x7f1\xaf\xc8\x00\xfe\x0e3\x82\xf7f\x17\xdd7\x17\xcb\x90\x04\xf2\x93\xb1\xabd^\xd0\x8f\x0e\xc3\xb4\xc2\x85\x03\xfd}\xf1\x97\xcf\xda\xa5+\x074\x82\x9eg\xbd\x83\xf2gtjpj\xc6\xd0\xe2\x12\x1a/\x85\xca\x8eSn\xe5\xe3\xf6\xca,\xc9\xe2\x8b\xc8\x03G"\x85s\xc7\xba\x9a\xd4\x01\xb1:ty\'\xb1\x17\xa1\x95h\x8f\xdfA=\xf6\xd4\xa1\xea\x9a\xc5\xb3\x8d\x82%\xb2\x1e\xd3\xe9#Y \'\x1d\xf0\rd\x86\xe90\xf1\xe5\xec\x9d\xe9.\xf63\x01RR\xf8\xae/\xa4wvjW\xce\xdc\xa9\x0b/\x00\x89\xca\'\xf8e.\xa1~ m\xc9q\x033\xbc\xb9|\xc2&gt;G\\\xd5\x8d\x00\x83\xfe\xaf\xb8\xbe\x93\xd8\xe9%\x87\x15\xf4x\x0e\xbb\x93\xc6\x98\xeaz\x12?\xde\xa0\xa0\xcc\x91\x08\xae\xcbJ\xa1\xa9\xd4\xc8\xdf\x1d\xe3#\xeb\xa0\t\xc1$\xbe\xf1\x9b=L\x1e\xe5\x85\xf1\xe2\xf8\x88?\x98\x0ev\xd6\xca\x96t\x177\xc0\x0c\x1f\xc3Z\x88o\xfa\x87\x8a\xc97\xc9z\xe0\xe8`na\xfe"\xae\xa0\x8f\xd5=;o;\xed\x1fy&amp;\xc0\xc7\xeb\xc1\xa1\tB$B#MH\xb2FOt\xb7!\xfa\xa6\xf1\xe0B\x99\x92S\x1e\x8d\xe8\x0b\xb4w\xcf*\\\xe5\x0bX\x89|\xbee\xfb\x95\xff\x91O\x83\x97!\x8fK+\xde\x88\xb7\xf0A\xd6\x02\xdc~\x97:\x8a!\xd9]\xe2}\x0b\xfa\xfcq\xe2\xfd&lt;:\xea\xb4\x88U\x0e\x15B\xcd\x80\x82\x10\xa1_Y&lt;\xfb*\xc3Gy\xfb\xafqr3\x1a\x9a\xb5\xd7N\x03!\x1d\x16\xcb.\x18\x7f\xc5\xad,\x8a^\x8e\xff\x80\xf8+}\xcc\x87$\xe2W2m\xc3\x10`\xe5\xce\xe1o-\xaa\xbd\x140\x88|5\xf3\xf4\x89o\xbe\xb9\x04`\x96p\xb7&lt;/\xd2G\xe8\xc8\n\xd5\x90\xc1qn&lt;}t\x83\x167\xcd\xfd\xa8\xe8{\xe6\xa0\x97\x96\xf0B\xd6g\x01\x0bu\xf7[go\x7f\x90\x8d\xb6&lt;\x10\xf6,\xa5+\xab\x1c\xdc\xe1\xfef\xa6Aa\x11\x16g\xcb-\xf8h\xe1\xb4\xbb$\xef$;8\xac\xbd\xba~\xa3\x84\xfa\xcbR\x87I\x7f\xd5\xd8b\x1c\x8b\xaeST=18\x0b\xf8\xd8z{\x05L\t\xfe\xef\xf6\xe6\xbfI{\xebbG\xe9\xfd\x8f\x9c\x94\xca\x83k\x84\xc2\x04\x8bL6O\xbf\xf1\xd1,\xda%\xa8\xa3S\xb6yC\x0c\xdd\x86\xd7D\xe5.\x94EY.\xf8sN\x15NN\xa3c+\xcf\xa5\xe7\x1f{\xc8\x1c\xedQx\xf87\xfd;\xf8z]k\\\x822\xc5\xa3p]\xddv\xfa\xcf\x80\xf8\xc3\xb9\x0e\x1f\nx\xf1\x06\x03\xf0\x8f\xd1z\x81s\xe9\xde\x01\x00\x92f#w\x9d\xe5=x;B$\xa5\xdb\x8b\xf6\xd3k\xdc\x8a\x87\x98\x91/\xb8\xb3\x98F\x1e\xdde\x87n\x96\x11\xa5x8\x97Z\xcd\xc2\t0\xe18\xa7&gt;\x02\xe4\x1bIB\x81\xec\xc0BO=\xc9C\xe1;\xb2P\xfe\x16\xea\x86\xd5\x8f\x1e\x99Kq\x8cR\xa9B\x86\xee#\xc3\xb3\xb2\x1f\x98\x00\xcd\x81\x11\xc3b\x8eT\xbdA%\x13O\x9b\xda)l\x01Z\xf5\xc2\xff\x15\xe1E\xffVOW\xaa)|\x80\x1c\x80\xc6\xe4\xfaX\xb83Gr\xa0\r\xe1\xa8\xfd\x1e}\x8eb)o\x97\xeb2\x84M2.\x0fj\x93\x89J\x19G\xdd\t\x83(\x05\x86[@\xc6\\]\x9b\xe1v\xa6\xd8\xb1\xd2O\x15\xeb\xc7\xbd \xda\xc2*\xbe\x17\x08R8\xda\xbeu)\xe1\xfd\xd0\xb8NyP)u[\x12+\x9a\x153\xc2E\x80\xfa\xeb\xf4\xca\x1fm6\x10\xba5&amp;a\xb5\xe9[\x02\xed\xca\x0e\xb5N7\xb7\xea/\x1c\x96\x07b,\x85\xfd\x15\x87\x8bj)\x08\t\x10\xf2\xdc\xff8\x88\xdfZ\xbbZ\xdb\xee\x93\x1c\x1d\x91\xb4\xd8\xb5$\x85g\xdeu\x10\x8c\xe8\xea\x9a\x14\xcf\xe1=+\xe0\x14\xad\x0f\x0cH\xa7\xdd\x1c\xd03\x98\x01\x10\xe2\x92\xafV\xc3u\xf4#\xa1\x12\x16\x84\xbc\n3Y\xea\xd2\x03\xdf\xe4|8&lt;\x08\xa7\x90\x1b\x91\x18U\x9bH\xd1\xc5\xc0\xdbk\x03A\xf7\xf0z\x90/\x87zW*\xd38@\xc3i\xfe\xb6\x98\xb8+\x1bJ\x15&gt;\x93\xe8^\xc3]\'\x08$~\xc0\x7f1\x87-\xdb\xf3\xb4\x1a\x15&lt;\xc3\xcf\x00\x02\x8a\xf3\xb9\xa4\xd4\xdal\x94\x9e\xa9=\xe3\xe2\xd8Xg\xffs\x8c\xa8\xee\xfd\xf8\xeff\x08\xf9C\x08\x9a\x16\xabl\xb4\x854v\x88^\xa2!LG\xe7\x89\xca\xce\xe6{M\x9d&gt;\xc0\x9cww\xe4\xa3\xd59\x83\xcdx\x8eZ\xcc\xc1\xb0uV\xb0\x0b\xdc\xe0\x04\x12%\xea a\xa8.p\x9a%\xb0\x12_"\x8e\xd1!\xd4\x92\x0c\x14\xe2\xef\x81\x88\x0c`(};7\xce\x0c)\xd6\xb5\xce+\x1e5\xa3\x826\xfc\xeb\xbc\xce\xbe,z\x93\xd5\x80{\x96\xe6\xc0\x02\xd8k\xaeV\xcdc-q=i\xcb\x10\x16\xc8rV\x05$\x1cC&gt;\xe9\x83U\t\t=\x8d\x07\xb7\x08\x8b\x94w\x82t\xfc00\x7f\x8b\x8cG\xe53 Sl\xbc\xbe\xfe\x16\xfa(\xae\xb5\xb9\xf2\xa2\xd0w$\xf6\xce\x0f\xeb \xc5\xfaJ\n\x05}\xe7%v\x97\x0b\'\xce\xf1I\xd136(\xe6$\xf0\xe4W\xf9w\xf3\x98\x00\xd1\xa5\xcd\xcb\x12\x88\xb9\xbe\xd4\xfeR\x9e8\xc0\xd7\x8c\xb9\xf8#\x9a9v\xca\xd46\x12\xba/?\xa4m\r\xf2Q\xef\xe6Q\xe8\xff\x92\x9aq\'\xd23f\xcf\xfe\xd8G\xb1\xac\xc8`\xaam\x92\x02c\x82\x82\xd7I\xf2G\xaf\x98\xe7J&amp;\x89$d*\xde\x02\xbeO\xe1\xfa`\xf0\xc7\x1c*\xb1\x98\xf2? o\x8c\xe0\x9f:\xa4\xe8\xae\xc3\xb9\xa1\xf3-%A\xd1\x89{\xee\xcc\x13\xd0K\xa6\xcc\xf3\x82\x04N\xb0\xaf\x8cn\xb2\xdb[=p\x1d\x85\x97\xc4\xa2_\x838\xf6\xa3\xbe\x12\x93\x0e\x8fi\xcaC\xd4\xf7\x8b\x04\x97tg\xe4\x17W\xad\xfck^!\x0eW\x8e^Se\xe9\xd2\xb6\xa8;\x0c\xeb!+\x02\x1a\xf90\x04\xd1\x8d\xce\xb5\xd2\xcdH\x96X~\x18\xf85\xa3V\x96\x10\xc7\x8a\x06\xe1\x7f3\xa6\xfa\x01a\x89\x07H\rn\xc1\x89\xcc\x19\x08[O\x15\x02\x1dV\xc0\xaa\xe6|\xb0\xa7sk\xd2&lt;R\xb8\xf4\x07T\x06\xd8\xc1\xcd8\xf7s\x7f`\x1c9\x06\xf2\x0e\xe5L\xb9\xe7D\x9d\xc3o\xb9S \x8f\x0b\x93\xb98\x07\xdco\x97\xa7\xf3I\xcaw\xc8\xb6\x14&lt;O\xbc&amp;bW\x9fd\x1c\xac\x08\xf3\xc8\xaf\x14\xa2\xb9\xb2\x861\xdf\x12\x16W}\xfe!\xa2\xfe\x99Q\xfd\xc7\x980g\xde\xa5\xa1\x04\xbb\xa0B\xcf\x0c4\xa8aV\x06q\x87\x93P\x83\xe6\x93\xe8\x103p\xe1\xd7}\xcc\xd8z\x17"\xcc&gt;\xce\x9e\x8ba\xef0L\x18\x9d=\x15\x13\xe8S\x01\xce\x84\xe7^\x03\xf2\xe60(m\x85\xe2/\x94\xcd\x1c\xd5J\xeaD\xcf\xef\xa1a\xbd}\xf4\xa0\x95\x12\x1fNp\x15+uV\x02\x1c\x97\\\x08\xca,u`\xf8?\xee\xb2\xdf\xc1\xd1\xf1TT6\xb0R\xd9*\x11m\xd8\xf9z~Z+g\xbb.\x0e\x9e\x19\x04p\x15\xb8p\xbe7O\xd5b\x87\x8c\x88YZ9&gt;\x069T\xbbn\xebf\xf0\xf7X\x81[\x11[\r\xc5\x8cVF\xe6\x92\x93|\x07\x0c\x15E:\xef\x98\x01\x83\x15\xf0\xf2[\xf5\xc9s\xbaj\xfd\x87\xb2M\xbes\xdc\xa8\xc7\x1f\xa3\x9d\xab\xca\xa5\x8c\x08w\xc7w&amp;o#\xa4\xdb\x8a\xf9k\xd9#\x9e}\x03\x8f\x85\x89\xae]\xa0\xac/\x886\xd0\xa2\xf1&amp;\xaaHVF\x952z\x9d\x85\x90\x89\x0fe\xd7\x1e+\x08\x88\x94\xaf\xb9t\xbcy\x98\xc5\x96\xea%\xe1\x11\x12.\x97\xde\x9b\xf6\xb3\x85\xd3t}(\xffz\xe5\x15p\x15\xbfp\xf17\xab\xff\x06\x87\x91O\xc8\xa7&amp;\x01\x91\xac\x11\xac\xeaL\xc8\xf3\x1ar\x1d\xee9-:l\x88\xb4\x84\xcf\n*$P\xaeS\xb0\xba\xd0z\x8a\x15\xa9^|\x97\x19\xbd9\x95\xf6\x0f\x88\xd8\xc4Q\x12D\x87W\x97?MFEc\x14\x06-\x9ea\x12\\\x03\xb8&amp;\xb3\x19\xcd"2(\xf9\xa9\x05\xf8\xa6\xd5\xcce\xdf\xd1i\x919\xf0\xb76\xa7\xb6\xc3\x8e\x8e\t\xa3#\xfdw{\x05q\x94\x03\xb8-o\x05\xf0\xe0\xdb\x19C]\t\x06\xa7\xe9u\xa2\x81j\xbdC\x1a\xd3\x04\xfe\xcbl\xba\xba\x1dj\x7fr\x07\xf1\xa1\xa9\xc5?\xd3\x88\x124\x85\x13\xe8\xac\xa0\xa5\xc4\x8e\x16\xb0\xc0\xfe"\xe0\xca0`\xfe\x84\x9b\x9b;\xe4\x8b\x89\x10\x88u\xeb\x87\xc5zE\xd8\x9b%\xfeT\xeaa\xc5\\\x0b5\x8ao\xaaL2\x8bGv\xde\x02g\xf4\xe6k\x8d\xbb\xe9\x0eD \xf6\x9b\xeb1!\x88~U,w t\xb6\x9ae\xd7\xd6\xf6\x08\x03s\xd6e@\xa1\xeb \xe9:\xa4\x1es\xd2\xcb\xd8!\xf4!\xfej\xb8\x03sS\x1e\xd9X-\xf4\xba;r\x87\x9aIQ\r\xcd\xd9&lt;\x03:\x8b\xf8\xb3M\'m\xe5\xae\xda\xdb\x92s\xc1\x83\xa3\x8b\xe9\x10\xd3f\xf9\x1bv\xcdy\x90\xd6L7\xb9E\x92\x14Y6\xa8\xdd!k\xf9\xea\x16T\x9ev]\x9cq\xaa\x0e\x9bW=?\xdc&amp;\x97@H\xfb\xe5\xb9]\xed)\xe5\xd9l6=\x9c\xe7\x90X{\x04\xb3\xce\xd8N\x18\x14\t1\xbdS\xb0@!j\x0c6\x92\xbc\x02:v\xa9\x93W\x7f\xd2\x80\x8a\x07\t%\xe6%\x17\xaa\xe4\xf5\xdb\x86M\x1by\x81\xa5\xa3\x85\xbe\xc0\x9b\xfd\xa4&lt;\xdcW\x8bvY\x03~+,D\x92\x8a"=\x83A&amp;t\x06\xee\x1d\xb4\xb7\rjfmu\xd1a\xb7:\x00\x928a\xad\x9d\xc1\x15\xcf\xea\xb1\x9c\x13Hi\xf0}$/\xa4[\x18\x15"cU\x89\xfa\x86i\xa6\xfci\x04\xf8\x10l\x0f\xb1q\xaf\xcf.\x915\x107\x1c*i#\xb0\x17S\xb1&lt;\xb0n\xed^B\x7f\x80=\x9fg\xc1k\x16^\xfb\xf57\xe2\xa0\x19\x9cY\x15\x97O\x8d\x10\xfb\xd7\x9a\xf4\xd5H6^/\xae2/@\xf16\xe4\x0eP\x0c#\x07w\r\x86\xdaU\x9e!\x83/p\x9f\xcaL\xc4vE\xf5B\xab?v\xd3~\xe7(\xd0\x96R\x9c\x90\xb9r\xa4?\xcf\x13\x10\r\xad\x1b\x0b8\x0c\xacH\xdc\'\x10\xc4drx\xb9~&amp;\xfc\xcbG\xe7N\xf2\xf8z\x16\xdeE\xd6\xf1G\x8f\x95f\xaa\xe3\xef\xd3\x8awR\xc4\x96\xd7\xa1\x80\xc8\xb2\xc2\xfeZ\xa2W\xfc\x0e\xf4\xcfDV\x96\xc2\x17\xe7\xea\xfbB\xd8\xca\xd1\x80r\xbeV\xe5?8\xe3F)&gt;\xc8_y\x1d\x9f1\x8b_\xb5\xd9\xf6\x87\x98(\xa4\x92C\xb70\'\xc3E\xb5\x8c\xa9\x0f\xd6i\x14\x9bh\xf1\xb4\xe3=\xfa\x84\xcb\xa6I\xcb^\x90\x1bR\xf0s\r\xde\x9d\xecB\x98dd\x85\x08\xf1\xefr\xfb:b\xf83\x02\x92\xcf\x06\x89\xaa\xe3\xb2nL\x82\xf3\xa0.\xd0\xd3\xe8G\x94\xaeb\x8cd\x11e\x0f\x94R\x0c\xe5/M"\x14\xde/\xab\xfc\x9d\x953kY\x04\xa7\x9cg6!;\xe2\xc3\xfcL\xe0G\\ k!T\xa4\xfc\xcc"R\x16|\xb7%\xecA\xaa\x91\xe9\x1a\xda\xb9\t\x03\xd9.\xc1H|\x07\xc6\x86%(\xd6\x10\xd5\x03\x9b\xb5\xe2j \xc3\x9bc4\x0cy\xf0\xb2;\xb2.\xdc\xc1\'{\xcd\xc5\xe5\x9b\xf5\xbd;5+\x98\x04D\xf8\xcf\xad\xe5\x8e\xe44/\xcb\xa2v\xbeD[k\xc4\x92AE\xb5E\xebq\x04&lt;\x80\xfc7F\x07;\xca\xdd\xdef\xbepa\xb1\xbe\x0f\x15\xd8\x08\xcai\x8a\xa1\x11\x16\x07C\xb7\x9dV:\xc8\xd5\x84\x99\xe8\xcd\x9fJMo|\x95\xee\xbe6\x9fx\xc0f\x0b\x1b\x03\x81\x18yx\xdb\xb5{\x1b\xd2\x1a\xe2\x86\xd6\xe99\xabvI\xedBa){\xcd\xban\x9e;\xb4_\x13b\xd9\x1b)\x90\xc9\x181C2:\x1eel\xc2\x18T\xfb\x1fh\xf1\xf4\x84\x1e@\xc8\xd1\x82HH\xe4\xc7\xca\xcf&gt;\xbcw*1\xd0b\xa577\x145\x8a\xba\x8c+|E\x0bN\xca\xce\xfa#.\xe4T\x0c{\x1f\xa6\xe6I\xe1\x05\x0e\x9d\xa4\xbd\x94\xd9\xf1\xae\xbb-V\xa4%~\x8a)\x8c\xd4\x93+\xf0\xa7q\xdc8y\xa8\x9e\xf2|\xbb \xc0*\xb9\x81\xb9\xfd\x14\xc1\x05\xf2\xbd\xd4D\xa05o|\xc8\xe0\x1d?\x0f66\x19 {\xc0\x8f\xb0\x03\xd32\xf4\x1a\xe2\x1f\x1b\xfeqo\xc9\xef\xcf+\xfeR\x90\x89\xd5\x11]\x97\x91\xa3b\xac@b\xa8]q6ja\xec\xd6Q[\xdb\x19\xd3\xc8\x87\x8d\xdc8^\xce=\xed\x1cz\'v\xa7\xc7\xfan\x1c\xe3\xdd\x03\x99\xad\x82\xd5\x01\x8c\x96i5\x08e\r\xcc\x8c$\xfb\xf5=\x8d}%\x1e\xd6\xb7&gt;\x0f\x97d\xd3d\xf7\x1e\x18\xcf\xe6\x0e\x04\xf6\x8d\xc8\\\xdb2\xe0c\xcf\x9b\xe7F?\x14\xbd\x9f\x1fb\xbe\x10\n!\xad^V`M\x83p\xe96T{\xbe5\xb7\x81\xa0\xa9`\xd3\xcb\x1dAj\x01f\x0f\xcbb\xd9\x9es\x82?\x87\xee1\x9f\xff\x8d\xb3N\x13\xccI\x85\x13\x18;1\xe7\xc9\xc0\xcc+\xf1\x9dg\xbc\x86FU\xc9b\x1fe\xbe\x84\xde\xf3\xd2\x81.\x90\xac\xcf\x02F\xe3Z\xa6\xa2L\xca]\x1dZ\x97\x16\xf6\xe3%eE\x921`8.\xc32%\x0e\xd0FxI*\xb5A\x1a/\x05\x8f\xed5\x17\xfcM\xc3\x81p\xc2\x05\xa2\x85}L\x81%\x8eC\xc8\xe9\xa6f#\x96\x9f\':O\x97&lt;s\x8e\xc7\x12\xfbMF\x15\x93d+\x1cx\xe0\xb9\xeb\xef\x1a\xd6\x93\x043j\x12\xad\xb0K4n\xda\x199\xb8\x13{\x0f\xdd\x84\xb4!\x84pZ\x10)7[\xdc$\xe8\xe3JM}\xf2\x8a\xd6\x99\xf1\xdc\xe3\xdb=#\xfb\xdcs\xd2\x86q\x8d\x94i\xf6\x8cs\xd1\x89\x83\x83\x0cEh=\x85\xe58d \xd7\xc7`?\x81\xe9e:\xc5g\x14\x90\xf8\xc8\x05\xd1%K\xfc\x91.\x96\x95/\xcb\x12\x8b;\x05h\x90V\xaeF\x84.o-\xab\xbb\x02\xee1\\\xce\x9f\x1f]\xa7AKi\x8fk5\x8d\xa3\x1f\xb8\xdfQ_c\xdcl\x81Eh.)\x0b\x00!\x06se\xf5\xdd\x10\xac\x0f\xc8\xfa\xc6\x14\xd8\xa2vu\x828\xc5jD[\x02\xd6/%\xa5\xfe\xcfS\xec\x9b\x87K\xe7\x1e[\xe1]\x9b\xf1\xe9\x90H\x93\x15Kb\x1c\xe6\x8f\xa5\x8d\x999\xf5\x1b(\xc9\xf3t\xd2q\xd7\xe3\xf9\xc8\xe0\xa0c\xabq"\xaf\x9dXd\x87\xe4\xb2P\xa0\xac\x1d`a\xc3\xc5\xae\xbb\xa1\x81]\xc8\xc2\x8d\x8f\x80\xce\x02\xc1Y2\xcb;\xff\xa9.\xab\xba:\xbd\xdf {\xf1\xcd\xa9\x87\xe6\xbcAH\x9b\xa1\xd0U\x90\x02\x01}\xe2&lt;}\x0e\x98\x87\x9bn\\\xe7\xee\xac\x02a\xafs\xf7\x8c\x1d(|\x11\xd9x\x96\xbf\xe7\xae\xfb&gt;\xe6\xb3\x93\xce\xc6\xff\x17U|\x8em\x90\xdd\x08\xf5\xad\xecUcf\xea\xe3\xe1\x87\xa7;\xbep\xef\x0eqtW\xb0Pd1\xdc)\xd6$\x82\xb9L\xd5\xa3)T\xef\xb5"Z\x9b\xc5\xe0\xd6\xcb}\xdb\xf3\xa6\xbe\x13\x03O\xad\x1feO"\xb8\xd2\xabv9\x00T\x172\xd7\x87\x9bM-\n*vP\xdc\x93\xa2\r[\xee\xe0.\xcf\xa0\xbb\xfb&gt;g\xe0\xf3z\x00\x04fC\x8b\xf6n\xa3j)\xcad\xb4\xa1\xf3\xc5\x1al\xe6[\xea\xb8\xcb\x95"\xda\x0e\xdb\x88\n\x85\xb62\xf6\xf7[\xd9V\xc9\x82!\x16&lt;\xa4\x10\x80O\x87H\xfd1\x1d\xf0\xadZ\x10\x16\xc4\x96\xbe\xf2\x02\xb2\xe4{F\x8b$\x1cy[u\x1e\xd2f\xbb\xb2\\\x10\xc9\xb1k\t\x84`PV\x0e[\xae$\x14tiO\x8b\x9f\xa0\x9fm\x01\xdf\x1a\x8f\xd7S\x99\x8d\xab\x89\xae\xce\xba\x11i\x82\x14\tO\x05}&gt;\xc3\xd7X.rK\x85\x8d\x1bA\xb1\xebg\x81o\xa8\xe0\xc0\x91f\xa0\x15\xa1\x87\x88)1\xd8B\xbf\xee\xacZ\xbbV`\xd2A\xad\xe9\xec\xc6\xdb[\x84\x10\x9a\xd0\xd1\xba\x01\r2\xa30\x8d\x1f\xb6{\xec\xd5\x00\xac\xfc\xec\xe6g\xe1\xed\xace\n\xe1\x90/M`\x0f\x02d+:^\x92\xa9\xe8pw\x17\x835\x92t\xe3\xdc\x03\xec\x0c\xfb\t\'t\x05\xc54f[\x01&amp;\x0b\xe0\x18&gt;\x08/+\xc6l\xee\xea\xca\xcf\x1f\xaa\x84\xb8\x9e\x077\x9d\xdb\x81\xa8\x9e\xd3\x1aF\x02+\xd3\r\xf1);W\x00\x8b&lt;M3\xe7\x1c\xdd~a\xde\x1c"\xa3\xb5\\\xfeQ\xa18\xb7&amp;\xfe\x98\x869\xbb\xfeQS\xdbi\xdf\xa8\xc4\x9bw2\xe65\xf7\xf8\xe9]\xf6\x9f\xfe6T\xfe\xbe\x06\xacyg\xf9\x19\xba\xd2\x96\x805\xd9\x1d\xc7\x80}\xfd\x0f\xcc\xac\x17\xfcW\xd3+\x90\xc1\x0b\xae\xf1\xae\xe7r\xdcA\xe0\xb1\xbfR\xec\xfa\x18\xa8\xe7\xbc\xb7\xf3\xd4\x7f\x8a5\xa3\xf1l@\xc5)s#\x8f\x8a\x05\x0e\xe2\xf2P\xf6+0\n\x83\xba\x9d_r\x8c\xb3\x8cA\x85\xd9\xaen@\xcf\x9f\xfd\x0e\rZF\xa8\x0c\xe0\xf1#P\xc5#\x8e\xaa\x12\x96\xd0\x91\x8e\xa0\x94j_?\xeb3N\xf7\xcdZ\x1e\x07\x1dZ\t\xd4\t\xcc\xe1&gt;$\xda(\xeb\xc4[3Ze\x0e\xd7\xc7\xbe\\\xba\xe8\x11~\x9cC\xc3\x8e,&lt;\xb6\x95\x1f\xad\xc3\xbdz\xb6\x86\xd9\xf1\xc3\x87\x87y&amp;\xa2\x06\x9d\x1eF\xdc\xb6\xeeS\xfd^\xa9\r\xdf\xb3\x02\x13)FwN\xbeb\xf1\xf44\x15\xfa\x01\x1a\xb0\x05\xf7\xb4\x11\x19rV^!Tp\r\xf0p\x0c&gt;\x8bR\x14p\xfar{,\x0eE\xf6;\xfa\xb72g\x82t\xc9\xb3\xc4\xae\x0b$\x80\xf9\x0f\x8b\x1cdq\x86u\x8bm\xa2R\x8f\xc3\x0b`\x972\x07\xfd\xfd\xc8\xec\x19\xcd\x95\xc7\xf4\x90&amp;5\x074\x87\x13\xda\xceiG\x06\x0e4\xf0\t\xe9\xab\xc7\x8d\x16\x87\xf7d@(\xea\x1d\x8cy1j&lt;\x99\x13\xdeK\x01\x85\xc5\xac\x16\xf3\xe6]J\xc3D\xb6\x9b\x87H\xa1\xc4\xb8\x02|:\x93\xf0"}\n\xeb\xebx?\xae\xa6\x8b\xcc\xab$\x0e\xfb\x88\x9f\xf1&amp;\x1b\xd5m\xe2\x00R\x83\x8a"\x01\x011v\xaf\x87\x80\x19}$%{m\xe6b5\xf2#^t//\x07\xf69SC\xf4\xfa\xd1\xa35\xbf![V\xc1\xb1\x1f\x17\xaf\xfav\x96\xbc\xe7\xf0H\xc93{s\x04\x1a\x7f\xa5\xe3\x80n\rd\x98&gt;a&gt;\xe5i\xf8\x1b\x04\xf3\xf6\x1d\x97\xd2\xe5\x96\xfa\xed\xee\x05\xac\xf4(\xba"x\xc9\xed\xbbt\xb6\x96)8\xb2\x1b\xae?\xc0\x0b\xb5&gt;\x9a\xd4-\xc8\xc3)\x95\x13\xad\x94|\xfeK\xea\x8ciW1Q\xa55E\x1c\x8f\x91\x7f.\x86\xdd\xa3(7\x1e4@mj\xd2\x9eV\xd3\xa3$$\x86\xed\x8b,f1\xcaN-(\xb1yW\xaa]\x8ax\x1f\xa1\x923\x92"\x16\x9c\x0bqPCc\x89\x18k\\U\xe2L\x82\xdd\x9eD\xa1B&amp;d\x06l^\xe5$\xde\xf6\xcb\xb9o\xd5cx9\xed\xea\xf0\xb8\x08\xdb\xae\xa3\x91\xa5\xe3\xea\xb7\xe5F\xfe\xeeW\x89\xc6\xf3\x84q\xbdO\xa4\x94K;j\xd7\xe4\xf7\x19i\x9a\x85\x0cPN\x07]A\xdb\x8c\xe5\x89X\xe0\xb2\xec_\xf6\xfc\xee\x1f\x9b\tc\x04\xe2\xc4\x0b\x86\xcd\xf0\xdb7];\x86\xea\xcc\xe9\xaf\xe8\xa8\x0c\xfd\xb5\x98&gt;\x1e\x06/{\xa5\xde\xf8\xf9yb\xccTwh\xe6)o\x94\xa7Ea|x\x03\x16\x8d\xfaX\x1cIp\xbd\xb0\xec]\xc4\t\xc3&lt;vQJ\xde^\xb5?\xbc\xf9\xa5k\xf2\x85\x83\xecR\xb3\xe0\x07\xc8\xb6\xc0\'\tS\x0b\x92\xe4\x90\x1f,\xec2r\xa1\x1d\xb4&lt;"\xc5h#\x94X\xbb\x86\x8e]|\x8d\xd9$\x89\xcf\x07Hv\x80\x94\x0f\xa7\x7fK\xc5\x1a\nEDBv\x99L\xcc\x87\xa8\tD\xc3\xce\'\xfdRp\xd0\x1f\xca\x9e(2nM\x06\xa7\x1d\x81]d"RY\x87\xcc.`\xa7\x83&gt;\x1e\xfe\x81E\xaet\xf3\xbagV\xe4d\xe2\x12\xac\xad\'\x82\x0b\xf5i\xdd.\x82|\x7f\xd9.\x05\xc6\xbc\xd0\xf8\x82\x87\x0c\r\xf9\x80\xa1~\x80Z\xee\xf8\xae\xa6\x0e\\\xf0\x14\x06\x1e~\x9a\xb5\x89\x82IJoX\xfb\xe4a\x91k\xedP\x9bp\xf7\xc9\x9b)!b\x147\xf0\xf1Or\xa3t\x16\n\x8c?\xc9\xc4\xc9\x9b\x98\xbb@\x1b\x8ey\xd7\xad\xc2\xfd\x86"\x8e\x89\x01\x1f\x8d\n\x15u\x91\x8bF\xb0o\x83\x84\xbc@=1\xac\x98a\xab{\xb7\xda\xb7*\xd3q}\xc0\xc0\xf5\xed(\'\x04 _\xf4?-\xda)\xf6"\xbb\xd1\xee\xe2\x81\xc8\xbeIu\xf1\xc0$\xdebdvp\xe7[\xad47\x19\xa7&amp;F\xff\x05Q\xcb\xb3tf\xdc\x0eZ\xfb\xec\x08\xde\xc6\xf1\xa7lUh\x88\xc5}`\xca2srU\x90\xcb\x85?\x8e3\xaaTP4Y\xe3^\x1b-e\xd3\xb9\x0fV\xa3\xab\xcbeJ\xda.{1D\xd7}\x8c\x1dl\x13\x9b\x08\x82\x08a\xb4J-\x92\xc4$\xa3\x87\x84\x17$:\x99\xc0\xef\x9d\x8b\xed\x13b\x85\xee\xef\xc8\xefJ\x87|\xc0\x82&gt;\xa6\xb8\xab\xb6\xd1\x8b\xaf\xa4\xfcK\xa1\xd4\x03\xe0\x82\x83\x02D\x97%IP\xff\x91uXTp\xb7\x13\x17&gt;\x81&gt;\x9c\xaa`l`\x85#\xac\xf0\xdf\x8f=\xf5x\x0e\xd8\x83\xa6\x9e\xa6\xfd\x0e\x1d\xad\x9131\xd0\xb7^N\x10`\xc1\x19Y|\xd2\x07\x1fa}\xcf\x0b\x07\xe8\x92\xed\xca\x1b\x13\x94?\xcc\x9b#Or\x80?s\x86*\n\xfd\xaf\xc9Na\xbbzE\xac\x8a\xe8\xdc\xf2&amp;\x94\x97n\x90l\x1c\xfc/\x0f#I"\xe1\x13S\x026\x94,G(\xc8\xebZ\xcc\xce\xeaz~\xee\xd5~\x06\xeb\x96\xd9nbD\x9cQ\x04\xd2s0\'\x8c\xa1\x08^n\r\x98\x14\x9cO\xa4\xa2\xe6\x17\x0e\xce\xb3\x94\x04e}_\xab\x0fe\xd0\xd9\xffO\x94\x8d\xa8\xce\xfb\x7f;\xbd\xe6\xc0\x9b e\xb1\xd6\x14\x1fS.\x1akS\x16\xb4\x86R\x03CmT\x0fu@(\x95\xe74\xb1\x02\x8e\xcfq\x80X&gt;z\x14-Sq5\xaa\xcax\xc6\xa1\xbc\xe0\xb2\xa2\x0c\xad\x12\xd2\xe2U-\x9e\xc9\xc5-\x01\xb4g4\x7f\xb0\x8c|\xf4\xc6\x93C\xec\xf0\x93^4\xcc4\\Y\xae\xc0\xdb\xaePK\xc8\xaf4\xf0\xd1&gt;\x02\x97\x00\xc2\x19N\x18-\xbad\xe3\x81\xa9\xf2\x07S\x98\xa0\x8dq\xf0.\xc3-Hu\xd0\xed\xfb\xdc\xe4y \xf8\xa2M6\x9e=\x90\x84\x17\xb9\x8cn\x01\x99,\x82I/\xbfR\xba,\xe7\xf7n?\x9ah\n\xc6\x891\xb3Rpo\x01C_\'\xc6I`\x92\xdd\x19\xb4#\x1f\x07\xbb\x98\x9f\xd1\xac\x8eQ\xe4l[p\x800\x91\xdat\x02\xa4\x1e\xf2\x02\x0c\x07U\xf7\r\x90\x8a\n\xe33.\x80\xca\x04\xfcP;\xb4\xcb\xa54\x89j\xc0\xd8Fqe\x7f\x90q\x9c\x98r\xb4t\xdc/Oy\xab\x8fM\xe6\xc7e\xb1\xd4\n\xf6nA\xee\x8f\xfeGU\x04Zx|\xefl\xb7\x0fD\xf7\xab\xd5\x11^\xc4\xc4\xe37\xae\xd7\x1cb41|9\xb5o\x92\x88\x87\xfez\xb4a\xe7y\x88\xe6\xac\xa4\x01\x04L(\xe4K\xd6\xfaT@\xb33\xb5uK^\x87\x1d\x19\xf9\xb1\x0c\xa62\x1fz\x14\x8e\xa0d\xd4\x82\x03\x84Khls\xce\x9a\x1c\xc9G\xe1\xd7-Z\xb7\xe4\x9a\xac\xef\x0c\xa6\xf3\xc1+\xd3\xc1\xba\xfd\x8a*\xb8\x0c/\xac\n\xe8\n\xa0\xb6\n\xb3\x1c\xcb\xe52\xb5\xad\x9a\x11\x0f\x1a\xf7\x1a\xc4\xe5%*+%\xc1gF\xba\n\xb7\xafb\xaa\xa9\x16\x0f]\xd5=\x7f\xff\xdd&lt;\xfc\xe69XRG;]\x18\x9evuo/A70e\x80\x92\xbf\xad\xbbD\x86y\x13\xe5Z\x96\xd0\xf36\x0bZ\xc0v\xf2\x17\x16~w\xf5+\x08\x08pI*= \xb5\xa7\xe2d\xdc\xa3\xe1\xa7\x87-\xb4&gt;\x1b&amp;2P\xb2\x0b\xd3\x90\x93\xb7m\x87w\xfb\x86},Mt\xaa\x07u\x1e\x98\xf5\x12V\x89\xfc\xec\xf1D)J^\xfbM{\xf5\x84\xa2\x83w\x0e\\wk\x00&gt;\xd0\xb6J2\x02\x98]\x91\x8d\x9e\x89,\xa2\xff*7\x9d\xaf\x05\xe4\x04\x907\x9a\x1b\xb2\x96}\xc0\xa1U\x19\xd8\xaa\xd0\x90\xf0h@\xb0\xa5\xfaR\xf2\\\xc8\x964_\xa0\x01\xa0A6,\xcb%\xaa\xe7\xa8\xa1\\\xea\xfe57:7\xe9\xd3\x88\x17V\x01\x97A9\xe5U\x83\xa6\xeds\xb2c\xd5\xe2\x0e6\xea\x94G\x9cv\x1f\x89\xf1\x83N\xdd3\xa1v5\xbd\xf5*\xc2eOsU\xd8"!\xc4\x92\xe0\xf4\xcf@\xf60\xbcrs8\xe2\xd1\x8cP~&amp;;\xea\xbb\x12&amp;\x0c\x80-\xd6\xd6\xd0o\x82\xd1a\x93\x14\xd5\x89\x89\x01mbG5\xe1)\xe7?\xd1\xbf\xcfF\xa0Z\x1e\xf5\xfd\xfe\x16\x1d\xdf\xafNK\x05B\xd4\x9cW@(\x19\xcci\xe8\xf3\xc9\x08/rxZ\xfd(\x98\x8fR;d\xc8m\x00q\xef\x9f\x1f\x85j\xbd6\xde\xb2\x1dV}C\xdeU6\x80\xb2\xf4\x1a\x86\xe9\x11\x06WF\xa7\xc1\xc5\x94\xd0\x19\xb6\x14\xfe\x8b\x1c\xc5\x9d\x8d\x89A\xf4\x7f)v\x0f9/\xab~&gt;\x90\xbe$y\xdd\xdb\x8f\xb5\xeeq\x06\xb94uKmn\x10\x85\xd5\xb2\xa0\xd7\x94\x93S\xaf\x0fA\xc0\xeeU+\x0e/\xac=U\xc9\x88\t\xe23\x8by\x02n\x95ja.O\xa7n\xfb\xdd\x8f\x148\x9d?\xb5mV\x95}R\xd0\xca\x9f\x8a5\x1f\xc2\x91\xa0\xdbMjtc\x8e\x94!\xfe\x00\xa1A%\xdaaL\xde\x16+\\\xd8\\\xc0%1E\x17\xcd}_%\xcf\xe5\xdf\x9c:XuCu\xb3\xcft\xc5k\xc6A7NQ&amp;\xdcG\x06B\x14rb\x8eA\x8f\x8a\xa6M\xa5\x12\xe4\xdecb\xb1B[\xe0hA\xcd\x1f\xcefs\xd6\xe6`\xe2\x10\xee\xe9\x8e\xc2\x08\x90\x1d\xa8\xa3\x10+V\x98v\xdd\xc0\x00\xcb4\xe3\x8d=U\x83\xeb6\xa6\x9b\x0fQ`\xc6\x01.\xa57\x9e\xc1\xe9LH1\xe4\xc5a\']\x15"\x9f~\xab\xc4\xcb\'2\xa4P\x08%w\xb4:y\xda$\x06:`d\x9f$J\xdc\x9a\xbf\xbex\x835\x9b|\xce\xa7\xe7\xea\xb5\x8f\x06Q\xd5\x16\x9a\xc9\xca\xe9\x89W,\xf0\x0c\xcd\xd2\xf8\xd5\x80\xb3Lvc\x83\xd3#\x98.\x15\xbb\x10\x97\xd8\xa0\x03\x96\xbd\x03\xbbU\xf9\xe4\xd2U7\x08\x8c6{P1\xcc\x15C\xcd\xd2`x\xe8Ba\\\x95v\xa4y\xa9\xcd\x03\x8bx\xd5+\x08\x94iB\xcc\x84C\xf4\xc2L\xa6\t\xcba\x89\xdc\x8c\xc6-\x0c\xfc9\x7f\x19,\x0c\x1b?&gt;\x00&gt;S\x93#f\x89H\x8dB~F\xef\x0c=A\xc2\x1d:F\xf5I\x93\x9f~$aw2sh\x02\xa0\xbdShb\x06z\xe8N\xd7\n\xc3~\x9c&gt;\xd5\x1e\xe9\xcf\x17\xd8\x8dsl\x7f}\t\x9e/X\x1dTR\xd3\x9c?wg\n\xf7\xe6\xf8\xc9\x1c\x9c\xb3\xfe\xc1\x9e\xde\xe7qx\xd93`\xc2\xeb%/\xba\x7f\xcaJ\xf1\xc1\xc4\xe4\x0bxE;g\xea\xd0\xae\x8dz\xcf\xf2]\xec\x83 \x01C\xd1\xc7t\xa2\xf4\x02\xf4\xe5\xa40\xa2\xebB\x83\r\x93\x99\xb3FH\xf8kQp\xe6\xfb\x1f\x1e\x06\xef\xc2&amp;\xbd\xdfz\xcdC\xce}F\xdf?\xc0r@\xe8M\xd7\xce\xe8%\x9e\n0\xcc%\xde\x08K\x19\x82u\xd4\xd3\xe0\x1a\xbbX\xfa\xe6~Z\xb1rIB\xbb\xc7,\x91\x1aR\x1bz\xc5\xaa\x01\x94zs\xf4\xd4\xb2\\\xec\xdcQ\xf9\xd5-+\xf4K\x10\x1fuf6?\xe4\xa6\x9c\xaa\xef\x1c\xeb\x8b\xa00\x9f\xea\xcc\xe91\xc1\x93\x16\xe2&amp;\x13_\xad\xc7@u\xe97Z\xf7Md\xc0\x04\xe5\xcdHY(\xb5\x88\xf9\x01\'\xf7\xfd\x0b\xcf:F7,\xd5\x9f\x13\xcbW\xf2L\x0fD\xf1w\xc1EWG\xb0\xcf\x0c1\x9d\x0c\xf0.\t\xcb&gt;os\xf60\xed\xb3\xef\x04c\xfe\xaf\xc9~\xe9J\xd2\xf5Q\x8d\xa8\xc5\xfaO\x87\xac\xaaZ\xf8&gt;.\xfa\xed\x1dY\xbf\x9c3\xf2w\x99\x80B\x8e\x15\x0eY\x9e\x82\xf7\xbdF\xd9\xafP\xe6\xa9j\x7f\x01\xe5\xd8ox%\x96\x98iET\x0c\x04\xfc\x02\x84\x02y\x14.\xea\xf0E\xd60\t\xaa81\xfb\xc7Cf\x80\xfcoe\xbcp\x1dd\x80\x95\x99\xfa\xd8B\x15\xe0 p\xfc\x9b\x8e/Kh\x9a\nZ\x0e\x12 6d_\xa2n\xa3\xf5\x044PI\xd4=\x934s3\x9b\x98p\x92\x83\x1e\x1f/(\x9c\n\xe1s\xae\x1c\x01\x11\xc3\\$,\x89D\x01\x98\xe1\x88 \xbdI\x85\x94\x83\x9cdQ\x08Ml\xba\xbam\xe2\xf1\r\xd7\x82\x1c\x92D\xfc\xab10\x96\xb2\xf1g]&amp;\x91\xb8\xedv\xd0\x81\xfc%\x95\xee\x95\xc9\x06\x8a\xe5=i\x7f!\x96\xc5\xab8/e\xf4\xa7\x8bo:\x98L{+\xbb\xc6=i\x16\x982\n\x9e\x15\xfe\xb5\xd1\xf6\xf0&lt;DG\xb7\x1e]\x1e!\xd4\x87J\xe8g~3\xf4\x0e\xd0\xc3\x10\xed\x88\xcf\xa6\x145@\xbf~\xf4\xad\x1c\x91\xec\x05\xf9U\xeb\x93u:\x81W{_\xdc\x10\xe58T\xc7\xdd\x1b\x84x\xd1\x85\xf2\xb4+^"\xe9z\\\xe1l \xb7\x1d8T\x96g\x81\x0cs\x93W\x95\x10\xda\x1c;X\xbeE\xa6)b5\xb4X]\xeeLZ\xc3\xba\xefz\xa1\xcbCnP\x82\xa0a\xadNa\xfa\x14\xdah\xfa\x8f\x8a\xfe*u|z\x17\xa3\x8e\nU\xf0\xdf\x0b\xeesK\x0c1\x0e\xa0\xd2\xc9\xbby\xb5W\xd0\xbe7U\xe4(L\xeb\x16:\xa4*\x0f\xa7\x1d\r5\xef\xb5Ub\xd4^\x99\xb68U]N\xbc\x12gy\xc7a4\x17\xf9&lt;\xc6]\x12\xe6F\xbd\xf4\x9f@j\xab;\xc4LG\xc4)\xb1\xc4\x8eN2t\xd2\xc5\x97\xd0\xfe\x1f3\xf8\xd4\xa3\x17\x92\xb7r\x92}\x10ty\x148-\xfe\x8f\xa0\x8f\'\xf1\r\x98\x8d+\x82\xc9H\xda\xab\x92]j\xa3A\xfb\xff\x81L\xf8\x19\xcbm\xbf\xd8\x05\xbc^\xa8\xab\xa7\xe8\xf6\xad#6G\x90\xada\x0c\x1b\xf4c\x89\xfa\x0cyo\xca\xf3?j\xc6\xc3J\x04\xa6\xf2eR-h\xdc\xbcQ\xd0a\xbc\xdb\x16&amp;9\xd0A\xef@\xd7\xa5\x83\xb6\xfbW\xe9\x8dU[\xee\xc06\x87j\xb60_pn\xaex,\x18\xd0\xcd\xd9\xde&lt;[f(h\xda\xcb&amp;\xd7\xab\x8f\x88\xc1\x0e\xb8L\xbc\xd7p\xdd\xec5\x9aj5\xebB\xba\x87\xcf\xacy|33\xff\x1c\xc8\xb9\x82\xd1\xd9\xab\x07=\xe8\xea\x07\xce}\xbc\xce&lt;\x98\xfe\t\x9dewfW\xca4@Q\xc6O\xdc\xf2\xffL\xd2I\t!t\x0f\'\x8d\xe2\xea\xf4l\x82\xd6\'\x1aL\xb5Xg\xf8\xc9\xa2\x1b\xd5Z$\xe0\xb60\xff\x97\xc6$\xe3\xf1\x84\x05\x8c\x8a\xb2\xe4",\xd8\xf3\xbd\xe8u"\xfd\x9b\xfb\x10\x9e`\x83\x90\xda9n\x89\x12\x1b\x86\xf4\xf1\x1d\xd7&gt;\x10\xb0\x000\x11\xce\xb9G\xac\xdd\xbc\x0c$\x10PD\x10\xefLi\xa5\x91\xc8_b\x00\x00'</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Endoscópio Digital Otoscópio Câmera Ouvido Celular Tablet Medical 3.5v</t>
+          <t>Kit 6 Cuecas Boxer Polo Wear Microfibra Sem Costura Original</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>67</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>159</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>38% OFF</t>
+          <t>99</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/endoscopio-digital-otoscopio-cmera-ouvido-celular-tablet-medical/p/MLB27730279?pdp_filters=item_id%3AMLB3833154469&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB3833154469&amp;sid=affiliates</t>
+          <t>57% OFF</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_777019-MLU78153175420_082024-AB.webp</t>
+          <t>https://produto.mercadolivre.com.br/MLB-3756911067-kit-6-cuecas-boxer-polo-wear-microfibra-sem-costura-original-_JM?searchVariation=180847149118&amp;extra_comm=false#polycard_client=affiliates</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>b'RIFFd%\x00\x00WEBPVP8 X%\x00\x000\xc4\x00\x9d\x01*\xc0\x01\xc0\x01&gt;m6\x96I$"\xa2.\xa12:)\xd0\r\x89i\n\x15\xcc#\xf6\xfa&lt;\x8e\r\xb0\x14\xbf\xf7\xc6s\x84\xe3\xe7\xe8\xff\xb8\xf9\'\xf9\x07\xd4\x7f\x8a\xfc\xc0\xf3\xb5\xf3\x81\xd6\xbf\xf4=\n\xfe;\xf7\xef\xf5_\xe2\xffx9}\xf8{\xa8\x8f\xe4\xbf\xcf\x7f\xd7zyCSI}\x01}\xd4\xfaw\xfdo\xf0\xfe.\x1f\xe4\x7f\x8e\xf5;\xea\xff\xfc\x1f\xf0\xff\x00\x1f\xd0?\xa5\x7f\xc1\xfe\xf1\xe7\x9d\xe1\x87\xf5\x0f\xf9^\xc0_\xcb\xff\xb7\xfe\xd3\xfb\xbf\xff\x7f\xff\xdb\xce_\xd5\x7f\xb5\xbf\x02?\xcf\x7f\xc0u\xbc\x12\xfdt\xb0\xb8\xe8\x05\xe3E\xe5\xf0+\xc7\xd7\xc9\x81sq\x06\xb0P]m\x96\xf6\xfc\xbd9\x80\xde\x9a\xe3\xeb}\xe0\x1cexwg@\x83\xea\xf1\x96\x1ap8r\xaf\x85\x0e\xc2\xb5\x1b\x05&amp;\xec\xb24*\xc9\x86\xa6\x1d\x95\x15\x8e\x8fr\xcb\x16\x15\xb6\x17\xee\x02\x1eL\xff\xee\xcb?\x11\x0f\xf3\xb7\x18#\xa4\xee\xb5\xeah\xcb\x84.\xab*\xd02\xd9\xf8\xbf\xa3\xa5\xear\xa0 9&lt;\xc5\x97\xbd)\x1e\xf3\x85\xb3\xd4\xe4\xad\x98ja\xd9QX\x8f\xf2l\x06p\x95\x86p\xe6\xfc\x16v\n\x957\xb4\x95:\xc3\xb2\xa2\xb1\xd2\xb6`\xbe\xde\xcdc9\x81NV\t2\xca&amp;\xf0\x7fc\xa4\x8c\x18\x97C\xd3\xe1\x8b\x81\xe1\x12y\xfc+\xb2\xff\xe3N\xb5\x08\xe2\xd9\xb2i\x0et\x00t\x1c\xe1\x9dC&amp;\xcf@y:Lu\xe8\xcb\x0c\xff\x0b}c2\x0c\x84\x0c\x157\xab\xa6G\xba\xab\xb8\xbd\xc1\x93\xaf\xcdl\x91\x1b\xb0\xd3\xb3\x89\xc3\xf8\n\x8c\xaa_\x04\x11\xc0(I|\x92\xf4\'\xc0\xc7\x00S\x0e\t\x07\x89\xa8\xea\xc9t?l\x8cM0\x17f\x01}$2\xa5c\xc2A\x8d\xcd()G\x10\xf0\n\x1b\xf0\x81\x90d O\x00\xb4\xf9s\xf7\x86\t\x8cI#\xba\xa0\x02\xc4\xffwJA6\t+f\x1a\x86\xae@|\xa6T\x95 \xe6\x1a\x1cC~ai\xbc\xea\x81W\xc7\xb2\xc1\x93\xe8\xd0\xbe\xb9\x93\xcf\xd5\xe8(-\x7f\xb1\xab.\xe6o\xdf\x84\x0c\x83\x10?\xc0\x14\xefP\x19\xde\x07\x86z\x8f\xf1\xe0\xf0A\xc3a\xcd+!=&gt;-\xafG\x93\xbb\x02[kl5\\\t\xd5\xd7y\x7f\x92\xf6\x1c\xa5\x05\x8d$R\x07\x80\xdd%mn\xef\xec\x14P1\x1d\x9d\x03e^\xb3\xfa*{4\xa5\x7f;*+\x1c`G\x9d/GT\xe5\x16\x8a\xac\x94\xca\xd5\xff\xa7\xc63K\xd0\'\x07\xd1\xa60\x14s\xcb\x8e*\x08R\xd0\x91\xd5\xccK5\xfb\x88\x9d_\xa9\xf0V!\xae.\x17\xcbm\xb3\xbaR\xa4\xb55oZ\x15\x87#\xc1\x1d\xcf\x1d\x93\xa1\x0cD?\x1e\n\xc7J\xa5\xf1?;\xca\xd5\xfc\xc7\xde\x8coV\x87Db\xeaoy\xa5\x07\xdc\x93(\xa8\x9a\xac\x15\xb3\xfa?[\xcd\xe0\x1fZ\x10\x9e\xa0?K\x97\x83\x16\x11\xc5\xa2\xa0\x84\xb2\'\xa8\xcc\xad\x8c\x84\t\xd4\xd3\x93\x02\xcd0f\x142\xaa\xff\xb1\xbb\xed\xcc\xca\xffL\xe5\xf0\x81\x90\x06\xf3p\xc53\x92\xf9\x8f0\xc3\xb0\x898\xe3o\xceg\xbc\x99\x14\x13|^\xd0m\x1a\xefF\x07T\xf5\x0f\xac-))L\x1f\xccs\x11\xef\x03%\xaa\x83\xf2g\x1f($Hn\xdd\x1an\xe9\xddH\x9b\xb4\xbd\xdd$\x16\x93&lt;\x9b\x80v\x89\xcb\xcd@0\x98fA\x90\x80\xe9\xc1\xad7\xb5\x8c\xbe\xe1\xd5H\x1eF\x13}\x0f\x84\\{!\x87\xd8tlyp&lt;=,\x16\x9eB\xebH\xce\x89\x0e\xe3RV\xcc5\x0c\xd4\xe7\xfe;4\xb7\xb9 \xf3\x9f\x90\xcc\x84\x00\x1e\xdcU\x11nVS\xde\x8a\xda\xe5S5\xf7\xaa\x82\xdf5\xe0\x06\xf6 \x97-5\x1c\x04Y\xfe\x9e\xf6\xa74?\xf7#\x1a[g\xf0\x0eQ\x97U\x15\x8ei%\xf6\xc1\xccC\x92\xcf\xe9\x13\xa5\x173\x19\xa4\xb0\xc7(\xac\xf2\xa3\x91&lt;\x94\xe5D\xe0\xca\x9a\xb5\x95\xcc\xd8\xd4\xf792\xcbH\xebz\xa2;M\xd8W\xcd\xdc8\xd5g_`\xbad;~\xb8,\xb3\x91m\xeaM\xd6\xd9\xd1:D\xf3o\xb2\xdd\xcc0V:U&amp;\xb0\x9a\x9c~\x11X\xbc{\xc0\xff%\x1bneS\x06\xc3OM\x94m\xc5\x8c\xb75E\x8b\xd7\x13\xf1\xc0\xe5\x1a\x8b\xfc\xc3\xde\x1a\xf1\xdd\xaf\x12\xcbe\xf8\x0f\xe6\xfa\xa2@$\xd3bJ\xd9\x86\xa1\xd7\t\x04\xc4\xd4LH\xdc\xa8pl\x1agT\xa3Le#(\xac\xf0\xa5\xd0\x9a\x8c\xfa\xe4\x1b\xbf"s0\xd4\xc3Z\xd9&gt;\x8c\xf2\xa9\xdfHF\x9a\xafT1\x1f1\xa5\xdb\x14\x07\x80+\xd2\x12_8\xf0m\xf2\x8e\xc1\x88\xc92\xec\xf3\x06\xd3 \xf5\xe4jk\x9fj\x87\x04\xean\x8a\xc35z\x8f\xb8m?,\x0fy\x9d\xc7\xd3\x88\xa6\x1a\x98v?\xb9\x94\xc59\x02\xf9c\xf4l\x9a\x07\xa5\xbf\x81\xb5\x8bw\xf63\xf5?v\xa5\xcf:\x1c@W\xa6\xeb\xc8h\xe8\x00\xd66Q;\x9d\xc8\xef\xd0$@\\\xda\xc5\xb20\x1a\x9b\xda\xb2\x81\x0eh\xc8\x96lP\n\x8e\xba\xacg\xd9\xeb\xddH-\x8a\x82\x04XE\xb5\xf2\x0c\x84\x0c\x10B\xb1\xa1O[_\x94L\xe8G\x8f\xaf\xed\xff\xda\x06\x84\xe5%n\xcc5\xc5\x84z\xad\xd6\xf6\xb1\x1e)\xf5&gt;\n\xc7\x19\x1a\xcd\x87P\xc3\xeb\xc8U\x06\xd6\xf3\x06\xafb\xae\x99\xdcj\xf7VF\xb3\x98\x94\x1e\x06|O\xe5\x109\xf6\xf4\xach\xca\x98ja\xd9N\x0c\xe3&gt;\xa5\x1f\xb0\xa13Q\x1c\x9d\xcb\xc6Y\x0e\xedIw\\.&gt;\xe7P7\x0b\xf8\xcc\x83!\x02\xfb\xe5\xdfz\xc7\x0c\x13\xb8\xc4E|8\xe8\x16\xa7"\xb7\x12\x19\xe2I\xfb\xcf\xa9\xf0V:=\x97`2^;\xc5\xf2~\x90\xf3\xc3K)ac\x13\xa7X|\xba\x84\xee&gt;/\x0e\xd8$\xad\x98.J\x12Y\xaa\xbc\xb0\xf9:\x9b\xa1IQ$[\x84:\xc7\xed\x19\xf5\xb9n3\n\xca\xde\xa1}.\xc6p\xb9\x82\xe7\x81\xd6&amp;\x02\xda\x98vTV@\x9a\xf9\xd7\x9c\xf6R\x94\xa4\xe0\xb8f\x0e\xb2\xec\xfc\xc1j\x01p\x9d\x9a\'\x04\xd0F\xc9\x88p\x04\xcd\tnJ\x1c\xf8+\x1d+f\x1a\x85\x99\x13)\xb5\xa3\xbc\xa8\x1b\xe3fB2\xd7)\xab\x07\x19\xab\xca&gt;\xd2E\xde\xf0wL50\xec\xa8\xacqPA\xac\xf3x\x84CJj\x03\xbf\x8a\xb2\xd2\xd6\x96MZ l\xfe\xb1y\xb0\xce9\\1.{\xcd:\x16\n\xa5\xb3x\xe3\x83\xbd\r\xbd7\xd0\xf4\xe6WNO\x00\x00\xfe\xff#\xa6\xa9\xa0G\x04X\xcb\x11\x05#\xe3D\x86\xdf\x87\xe9\x19\xed\xa7\'\xbf[\x1b&amp;\xf1}\xa3\\\x14\x06*\x15\x06\x04\x13\xf1\x95\x06\'\xad\x80\xea&gt;u&lt;\x9a\x85\xd8\xaf\x86\xb4\xc2ovoi}\xf1\xf3.7 \x17+\xd0.#\xc6\x9a\x14Y\x10h\xefqp\xc0\x92\x1e\x1a\x82\\V\xcd%\xf7\x88\xdecZ\xdd^R\xcb\x9d\xc8\xf5\xa8"f\xf6\xe5\xfd\xe5\n\x99\xbeD\xdd]\x1f\x8f\xf2Wu\x99=zR&lt;@\xdf\xb3\x95+L\x98\n\x8d\xabse~\x02!a\x83\x9a\x10C\x94\xa8yO\x1f\x04\x08\xab\xb0\x1a\x95\xd8\xf6\x7f\xd7\x81OC\x00\xeap\x91\x98\xf3\x00e\xa9:Z\x04Kp\x1f |\xd3\xff\x94\xb3F\xe1\xae\xca\xea\xfd\xb0\xc6\xc2\x8aUF64\xd3R9\x95\xaa\x8b*\xe3F\xb2Z&gt;\x920&lt;S\\\xcc\x8aFd^\xe7B\x85\xb4\x02\x9a\xd9\x08\xd0TT\x15\xae\x84\x96:\x9dB*d\x88\xee\xe9s\xd27\xccp\xc3\xba\xe2\xb3)fw\xb35\x1f\xe0R\xb2\x94\xb7\x110j\x83\xb3o\xa8n\x17\x9a\xfa\xfdnF\xaaf\x1b\xe5 \x7fG\xb7\x03\xdb\x88\x189\xe7~\xe8\xa6\x14\xddkA!G\xe0c\x87\xe7\xafm\x9f\xc9\r\xefES\xf6\x97\x89\xc6\x9b60\xdb\xec\'\xf5\xcbz.\x06\x89\xea\x81P\xe8%)\xaf\xafB=\xe1\xee[\x8d.\xc2\xd8\xe4\xf4.\xf1R}tT\xc3\xe2\x7f\t\xa4\xd2\xf6\rsM\x9d\xa4\x9a\xa7*#\x9b\xbc\t\xe3\xbe\xb1\x00\x84b=h\x7fT\x1c+E!\xc5\xb5\xfb\xc3\xaa:\xc7\xc3\x02\x94\xe9\xad\xc4\xfb\xf7\x1a%\x89mRUs\x1dx\xe8!\x17\x8a6\x1bS\x1b\xb7\x10\x9d2-L\xd1`Q\xb0`N\xb1(V\xc9,\x8dsmz\xd1\xc4e\xebu\x81\xe8\x8a1G.G\xfc,\xc7;\x97\xc2\x1e\xc8\xe7\xfcJ11\x9c\x9f\xb9\xb4\xa2s_\xdc\x94\xb1F\xc4dLhj_\x951K\x07\x04\xeay\xbd\xa8\x84\x86$X\xad\xcc\xbf;\xe02\xca\x00\xfeXK\xb01\xc0\xb1\xd3\xa8\x98j\xb7\x87\x83\x04J\x84t\xe8\xc7\xc2E\x8e\x98\x06zH\x19\xd5\xf3\xb6M\xf4\xbb\xd7\xa8\x0e\x04xUj\xc2\x89dY=\x05\x9f\xd3t8\xf4\xaf\xda\xf1\xfe\x1c\x90e\xbf}&amp;\xd1\xe0\xf3CB\x13\xf0J\xe3\xddCm\x97~\xfd\x9a\x87L4\x9f-\xec\xcco\xfeN-\xce\xe0\rx\x06\xcc\xf6@}r\xcf\x1c&lt;2\x93\xc9\xd0\xd6\xcf\x14I\xb6\xcf\xfdym\x10D\x95\xab\xd8\x13\x02\xb1B6E`\x1f\x9e\xd5\x98\xf0t\xa9\xbe\xa8\xa5\xb1n~%\x92\xd1k\xb4\x0f\xfd9\xd3S\x1f\x81Z\xf9\xdd\xf8\t\xb3\xcc\xa7\x85QS\xb8\xcbr\xd8\x03j\xbe\x84\xfc$\x01\xe6-N?\xa4&gt;\xa9W\xbbV\xa4\xe3\x15i\xcd\x01aR"26l\xe9x\xa8\x8aT\x1d\x9a\x98g\xb0\x0c\xf2\xb1]\x01Z\xab\x95M\x9aZ\xb1mn\xd8\x98uQ\x8d\x01\x9a!\x98\xfe\x9dN\x99\xd8\x1d\r\x13U{\x12\x15A\xa9)\xa4p\xae\x9f \x12)\xb6\x9d\x8b\xfcJ\xf9\x9cF\x87\xe4\x03\xfb\x10\xd0\x95\x87\x0f\xc9\x0b\x0c\xf0\xb7\x85ca\xa0\xf4C\x8c"\x12\xd1\xfe\x0e\x90\x96m\xaaD\xf0\x92J\xf3J\xac\':7\x92;A\xaa}&lt;+\x18\x96M\xee;R\xd0\xf37\x08%\xcbU\xa2e\xd8#c" I\xc670p\x13v\xf8\xef3\xe9@\x03X\x82L\xc3\xb9\xe3\x98W\xd1\xce\x8bZ\x80^\x9a\xae\xae\x1b\x1bF\x87\xf3\xdd\x9c\xfc3W\xb9\xcca\xc4$&amp;\xd3\x01\xc5\x15\xedf\xdfi\xc9v2+\xbdg\xdc\xbe\xd6}\xd0\xdb\xdeo\x0fP\xdb\x1f\x91\x03#\x8fy\x80\xb9i\xe7c&gt;1L\x0e\xd3\xa4\xe3/\x87\xb6.\xa2\xeb\x19?\xc7\x9aY9!C%\xf1\t\xba\xd3\xb4\x9c\xcfZ\xe0\xb7\xc4\xcfC\xdbd\t\xd4D_\xf0;\xd6\xfcN\x00\x8fQ\xa5}\xd2c\x8f\xcaw\x89\xe6I\xb9-\x17\xa4\xe4\x95\t$/\x8b\x93\xc8N\xedN\xea\xdfi\x00\x91\x02\x88\x91\x86\xfa\x9a\x1b:x\xe2!p[\xe1\x8e\x1d\xd7O\xe5h\x1aH\xec\x98E\xa7\xb6\x8c\xc9\xa7\xac\x18W/\r\xfc\x16~K\xbe\xbb`V$B\xdeZ\x86\xc4A=\x80\xc49\xcb6\xa2\x0ci\xcc\xe80\xbf\xcc\xf64\xd1\xa5\x92\x85h\x04\xe6\x03\x15\xa0\xe8\x1b\xbf\xfd\xcdmH$\xf5\xce\xaf\x02\x0e\x06\x12{\tS\x04\xf18\xbbV\xca\xb9\x97\x7fG\x8cBY~\xa8Yo\x9a\xbd\'*\x1cl\x08\t\xfa\x83\xf1\x87\xfd\x84\x06\xf7\xcb@\xc7u\xdeQ\x14=,\xf1\xe8\x99r\xb6\xca\xd1y\xb0\xfd\xf9\xc9z!\xf3\xc62D\xe0A\x04yt\xa2\n\x01\x13\x99\xbf\x88\x12\xb6\xda\x92\xc3-\xadk\x98y\x05!\x18\x12\xaf\xea\xe6\xa7\x8eD\x99\xe4\x14\x0cC\xbaG\xf8\xee\xdd\xcb\xe2^\x89%T\xb7\x895\x93o B\x8fb\xfa\xef\xf3\x7fv\xbfH\xa8\xf8\x94\xfb\x11\xc2o\x01\xab \x9cl\x9e\xc8d\xf7\x95\x94\x17\xc5.\xab\xd7\rvU\xcc\xb7\'\xa6#\xbb\x1d\x9e\x00z\xbb\xf2\x0f\xd9(\x84\x10\x04\xaf\x17O\xb42\xfa\xb5F5{\xb3\xc2w\x9b\xb8\xd0\x04h\x16\xeb\xb2\xcdae\x8c4fw\xd9\x0c#z\x12\xf9\xc3\xf7~\xb7\x8f\xe6\xc5F \x19\xe5&gt;(\xfcS]\xb7\x83\xbe\xb0\x8eg\x88&amp;7\x83\x97\xc0\x9a\x03\xe7\n\xc1\x9dT\xca\xe4\x04\x16\xbc\xdf\x985\xf4\x85 \xbclE\x86\x82\x0c\xeb\xf2\xa6\x82\x10*\xc1\xa6^\x00\x87F\xab\x17\x8a\x82\xee\x88G\xa2\xa9\xeb\xf3\xbb\xd6\xc1\x98\x9c%/-\xaf\x80\x9d\x1di\xd3\x84\xa8L\xe4\x0f\x8b\xae\xb0\xbc\xf6\xc7B\xb6\xdd:\xec\xb2\xf9,\x84\xa1\xc8\x06\xeco\xa4z\xf4\xd9\x1f\xd9\xe5n\xbe\xed\xaf\x8b\xbc*\xd8-\xbe\xd3\x12\x84\xa4_&amp;\x97\xf0\xa4\x0c\x96kK\xebb\x10Yn8\x01\x85\x15\xb9f!`\x1fL\xcbD\x04uZ\x13R\x10A\xc0\xaeX\x9a\xae\x19\xc5\xeflr\\\xa9\x8c\x01&gt;\xdf\xe2\xec-$S\xa3\xba\xe1\xfcbU\xed\x15\xcc\x8b\x02\x94\x02\x94&gt;&gt;\xef\xc1\x90"\xf8\xbfhsX\xa1\xf2\xaf{\xc4\xd1\x08\xe5r\xe7!_\x9fi\xf5\x9e\xd3&lt;\xc8\x10\xec\xfc\xd19\xfb\xd40\xeb\xabN\xde\x15\x99\xb3\xbc\x07\xb7\xbb\xb9\xb5\xa9\xa0ro;`\xdf\xd8&amp;4_\x92$\xb6\xce\xff\xb05\x940 \x0e\xc1\xf5\x96\xf3Y\xb3i\xac\xd8\xfb$\xefO\xd1\xef\x1d\x9d\x8a\xa8\x10\xdd\x04O`koC*\xea\xd5k\xe6\xb7\x95\xd5\xbc+\xefpd\xf7\x11T\xbeO1\xbfsJ\x13"w&amp;\r\x8a\xd8-\xc9Y\xeb\x8b\xe6\xf5\x8eB\x1e\x06\x12\x86?\x1b=\xb4\xf1\xf8\xcd\x8a\x1c\xcf&gt;\x8fTB\xfa\x84k\\\x8f4h}\x1c\xdd\xcf\xf5\x03\x8e\xd5\x12\xd1~G)\\\xbc\x8a\xe5\x85\xa5\x9d\x8a\x01\x81\xe0\xbbq\xb5L\x1c`[6H\xf7\xe0\x12\xce\xc3\xbcqWH.\x83\xbc\xeb\xcay\xf0\x16^:p\xd3\x0ba\xd5\x82:\x9a\x07KA\\\xb1\x80\xda\x11\x12\xccRa\xc7N\xdf\xce^5gd\xab\xf9\x8a\xad(\x16\xf7\xb6\x8f\x1c\x8e[Y\xddP|\xd6f\xc7z,\xdbU\x9f(\x1f7\xa3V\x80\x1fkK\x95U\xc1\xce\xcf\x8fA\x9c\xdbg7)\x88\xb9\x8d9\xf3"\xaa%go\x8c*/\xde\xfc\n\xfe\xc9\xe6?L\x81\xc9\x8b`\x9a\x94&amp;9\xc3\xef\x98Z{\x17\xbd\x189\xbe\x1e\xd0*G\x1a\xfd\x16\xfe\xb9\x15\x9e}S\xe9\xcc\x8fhl\x8fr\x96\x04\xc2\x8c8Ku\xa3\xeeTPC3\xba\x03\x838\x92\x80\xb67p\xc1\xef\x06\xed/\xa8\xac`\xe1\xb3D\x08\x01l\xe6_5\xb6\xaf\xb8\x84\x03\x91\xcb.\x16\x93\xe2\xbdxx\xb2\xd6~ZL\xbf\x934m\xb1\xfb\xc6?2w\xae\x83\x1f\x81\xb2\xd9\x92\xfd\xc6J\xef4[/\xd1\x8b\xa7\x13\xa1\x08\x18\xa1l?&lt;\xf1I\x00\xfd]g\\\nQC\x92&gt;\xc0\xa3\x15=\x18+\x89[\xbd\xd3\xfa&amp;\x00\xa70\xdeVA\xad\x1b$qH\t?\x12cf\x17b`3\t\x1b\xc1\x8f\xeb\x96t\x9b\x19\x826ml\x86\xba\x85+\xabb\x1d\x8e\xc4\n\xe5\xdf\xd1\x94\x98\xad\xd4\xea\xd7\x19O\x89)e\x82\rNJ\xee\xc9\xdf\xd8\xfdVj\x9f\xf9\xbf\xcc\xf0\xdd\x1ej\xf1(3\xd1\xb5\xb94I\x12\x1e`\x0e)kd\xf8\x91k\x10OnTeM\xbc\xcc\xeb\xfe\xe0\xf8\x9f\xd0@\xb7\x82/0g\x1a\xcc4jsqXF`\xb5a\xadx\\\x94\xa3[G\xe2W\r\x84`\xc0\r\xa5R^\xc4\xe2\xc9T\xaa\xbfr\xd5\xd8\xe3\x92\xf7\xd0\xe9\x8f\xb8\x9e\xc9\xafVv\xbb\x8a\xad\xe7r\xe2\xebt\x00\xea\x81\xff\xd5E\xcd\xbch\x84\xacq\x99\xad\xcb\x8c\xdb]dA\x0f\xbdjW\x0b\x96\xb0\x0f\xd2\x92\xdf\x95|3A\xac\xaa\x17\xf6u1`\x97.\xa8)&lt;\xb1\xad=S{\xd8eX^\x84\xbeHL\xba\xb2\x80\n{\xb3[\x93$_\xc8Z\xe8\xf4\xf8\xe7\xa4\xb6R\xf0a5\x00\x99\x94In\x05\x1e\t\x15\x00\x9e\xfa\xb3\xa6\xc6aP\xdc\x0c8 ~\xc9\xbbaA\xc2\xad\xc2B\x19\xf2\x12\x19\xa6\xda\x1b#\x0cZ\xc6\x8f\xce\xba\xf6}\xb3^=\x15QN\x84Y\x1b\xa1k\x96\xa0AQ\xb8\x07.~E\x1e&amp;\xebm\xa2\xcf\x90K\x93x&gt;R\xae&amp;\x1a\xda\x95T\x1a\xf9\xb8\xd7M\xc7_\x02\xd0\xa3\xdd\x8d\xff\xf1\xc09\xbb\xe5?\x13\xe7\xc1\x83\x823O\x02\xdc\xf3-\xfc\xc1\r\x9a\xbc\xd7pX\xdf\x17#\xf3\xc0\x9dg#1\x9f\xfe$v|\xbe\xd2Qt\xde0T\x98\x81\x15\xeb\x87\x98\x80\xfcT\xcdI\xc1\x02\xfc\xc6\xe5\xb4\x1e\x0c\xdc\x95x\xb7\xe4\xf9\x805\xaa\xd1\xf0\x8a\xe7\x0bMk8\xdc\x94)R\xc3Mr\x0c5x0\xa0\xd0\xa6`\r\xd1\x0e\x8e(F\x8cdz\x94\x99\xeb\xaf\x88XM\xa7\xfd\x1b\x1a6\x15\x16[\xb0\x12\xa0F\xed\xb1yB" u\xab\x7f\xad\xfbV\x1f\x8f\x0b\xa7d\xcd\x14.\xb3u\xe1\x98\x9b\x84\xf0\xda\xfa\xd7\x0c\xb6\xadw\xd1\x15\x8c9\xefv\r\xa2\xe6S\x02\x9e\xe8\x07rJ\xc8s\xf9{p_\xb4\x07\x1f\xb5\xf7\x9d\xe0\xf1\xbb\xd7\xb0\x82xSd\xd0\x90\xb0\xc2\xea\'\xc5\r\x80\x0f\xdd\xf3\x1f\xe9\xea\x19,\xc3\x07\xe8\x92\x8f|b\x8fC\xb2\xf2s\xe9\xd5,\xba\xd3\xcc"K\xfb\xd6\x9b\xda\xe6Z\x1e\x8eXk\x14\xe7\x9a\xcfG\x156\xc7o\x1e\xa64\n\xae\xf8\x85\x86\xed\x9a\xe2\x0c\x98 \x02\x95\xc2t-]o\xd3 (vm9\xd2\x9b=\x933\xe4u\xcd$\xfe\xf1\xab\x9cG\xc2l5\xe3\xdaXD\x8f\x19p\x0e\xc6\x05\xa12\\\x96\xc4\xc8\xae.\xf9\xb2\x88\xe9e\x89#\xf5=s\xdc\x1a\xff\xc7"\xea9\xa8\x8cL$JQ\xb6\x90\x9c\xb5\xe6@\x93\xb5\x8b\n\x14v\x894\xb5\x9f\xf1h\\q\x00\xf8roj\xbb\xac\xcf\xd8\xd2\xcb\xb7C\xec\xa3\xf8\xf6\x15\xc7\xb7\x19\xca\x02\xeb\xa9\xc9,4e\x81WAyC\xdd*xG{?\xea\x16\x12:2\xa3o\t\x97O`\x0f\x8b\xa1\xd3\xc6wGB\xf4Q\xf3xd\xf5k\xf1vz;\xf7\x7f\x95\xa4&gt;\x96\xf1\xd1\xce{b\r\x19\x15? \x93\xd6\x0f\xceLp\xb0\x82*g}\x9aN\'\xfc~\x85\x1e\xf8d]\x97\x8e\xa2\xaah\x8ai%M\xb0\xad\xa2\xe0\xc1\xf3F\x86\x1c[\xee\xafss\xf2\x99\'p\xb9\xd6Z\xcd\xb65\xc7It\x95\x0f\x96\x1b}]\xeb\'Q\xfe\t\x9d\xa6)\x1a\xec\xf2%\xbe\xbd\x06\xad\x9b\x11sc`S\x82\xa7\xd8\x90U\x10\xae\x125\xb6`\x80 \x82\x84\xc1\xda\xd6\n\x03=\xf9\x14 \xd4\x03O\x91|\x1f8\xbc\t\xcc\xa0\xb7\xf8\x127\xa3\xdf\xe0\xd4\x1b)"G\xcc.w\xd0Ie\x13\xd4($+\x94\x85.\x05\xe8\x1c\xe7!2\xbb\xf0k\x84\x7f\x07\x17\xba[\xe8q\xda\x88}\xb7\xb7(\xc9\xa8V\x0bJ\xf7\xf8\xfd\xb7\x81=\xb1\x1e\xa0?\x0f\x0b\xd7@6\xd9\xfd0\xbbS\xab*\xbf?t ;\xfe\xa4\x1diM/\x05]u\x80m\xb3\xf0_\xe3\x03\xc4[\x980S\xa9\xf0\x99\x11\x965&amp;\xe4\xda\xe7\'\xfe\xac\x8e\x1a\x87M\x08\xfb_\x17QN\xa3?\x97\x15vD6\xa3\x8a%\xced\xdfj\xf3\xf2\xce\xe0\t\x03\xf4\x9f\x1f\x0b\xbaw@\xbfdM\x18\x90^\x881\xcd\xa5\x9c\xa34\xfd\xd6\n\xcd\x06\xdf\xa6\n\x80\xba\xc1\x8c$?R\x1b\xa9b\'\xae\xd0n"\xcd\xe0f\xe4?A\x06Z%\xbb\x8f\x0c\x1e\xf0$*4\xd2\x1f4`v\x13\x00-S5\xed\x92\x15\xe8\xac\x86!\xfd\xfd~1Kx\xa7\xa9\x88g\x88\x9c\xcc\xa0\\\x98\x06\x10}\xdb#r\x08\x83\xcf\x19f\x03\xcc-\x0e\x19\xd4P\xcd\xc11F\x98\x19N\xf4\x89\xdf|\xca\x10z\xd3@\xa2z\xdb\xac\x9d\xbf\x89\xc9\xeaw\xd3\xc4\xe7\xed}Z\x1b\xd7v\xd1\x8f\x87\xd3\xf0\x8e\xc3}\xe6;.M\xd2\xbcN\xa1^F\x0f\\\xe8\xc1\xfb\x1cw0%D\xf0\x04\r\xc7\xffn\xb0/\xf1nX\x02\x14\xce\xbe\xcd\x1fEUZ\x04bJG\xb3p\x1d7\xd32\xc2\x8bS)\xba\xad@\xe2\xc7\x01v\x93I\x14\xdfF]\xdc\xea\xfe\xed7Z\x9a#}A\x86%\x93^\x81%V\x91NF\xff\xa0\x82\xd3A\xe0%g\x8e\xdd8L#+x\xb1\x02\'\xdb\xbdG\x9a\xb7\xa4;\x04\xdeC\xdc\xf5\x03\xa6a\xfft\xb8\xc3\xa3\xf78}\xd1\x04\xd0\xcf\xe1\xc7ytQ\x92]T#\xe0\xa2\x17Q6\xf9\xc6\xe2r\xc5\xe9t\xac$\xf5\xdf\xb0\x1bI5\xe5\xb7\xa6\xdd\x8a=\xe4\xf4\x89^\x16\xf2\xec\t\xa2\x8a\xfc|&amp;G\xba\xb6\x01D\x04\x17Z\xb4_\x9a\xdb\r\x8f\xff\xec@\x1ac\x86\xd3\xb0/\xc9,\x9c\xcb7\xa6u\xdf\x8f\x11\xe8-\x98\xed\xe5n?\x0c\x80\xab\xa7\x08#\xe2\x84\xe9\xf9\xb0\x83\x82#\xdf}\x8a8\x13\xd4/W\xa7\xe15\xf8/hc3\xcc\xe0\x9ek\xd7\xfa8MqZ\xc69\x98m0\x9b\xe9\xd6R`\x92\xb1\xcd\x0f\xd2\xda \xbc\xf8Th\xdb[\x96\xe4\x7f\x0e\xca\x8c\xf4h\xfa7+A \xe0&amp;/\xaa\xc6\x06\x7f\xe0\xa0V\xcc\xd5\x8c\xfa)\xd3s\xe8\x9c&amp;\xcb=\xe9f\xe0\x92gt \xa5~m\x05\xd0O\x96\x80\x1f\x9e\x1dU\xadZ&amp;Y\xf4\xb7.\x8cR\xec\xdb,\x88.\x0eq\xf5}\xa6\x13\xc6\xbah\x1e\xc0zX\x8eP\xcf\xd6xO\xc8G\xc7\xed\xc7\x16b\xfc\x06\t\xce:\xab\x91\xe6\xf1\x95\x88\x98(\xb3OC\xa2\xe2w\x89\xb9x\xab\xc1\xb7\x9f\x81G\xb0\x92\xd2\x8f\x8e\xac\x18$\t\xf8=\xafF\xb8\xdb\x18\x0e\'wzm\xfa=Or\xb3XUS4\\\x18\xf1V\xbd\xfc\xf8\xdb\x9cu{\xc3:\xa0\xa1\x91zg\x91\xb8\xbfC\x98\x96\xff\x02b;i\x98g\x9f\xbe\x9a\x17\xbbK\x17\x812\xd2\xa9\xf6xA\xcc.\x95\xb1t\xb0\x1a\x17V(8\xb0\xd3$\x08\x00\x15ui\xcc\x8d\x94_\xc0\xde\x99\xfc&gt;V\xb6\xf4\x17d\x96\x06ALN\xe1H\xc11\xf5\xf3\x7fT\xd4\xd7b^\x08\xc0\x0f\xa9;g#\xa9bG&lt;\xc0\xd0\x06\xd8\xde\xb1\x169\xe5\xc9\x94P\xfc\xd1\x05\t\xbf]\xa4\xa1T\xe2ce\x89\x10F\x1eR\x92l\xfb}\x1d\x9a\xce\x84\xa0\x1e\xe6\xb2\x8a\x96^&amp;x\xd7\x9fJ-\xca\xcf0\x17Pg\xc6]\xc62\x07\xd1\x85=R\x9eW\xb3\x84\xd5\xc1\xc0\xcb\xcb\xf4\x85#.\xf92\xf6\xcf.-j\xd1\xc1\xfd\xa4\x9d\x1f\xe3\xbc\x15\x17\xba\xef\x04\xa8S\xb4%om\x05\x87}\xf3?\xe0\x16\xe9]z\xd2\x03\xa2T\xfe\x82\\\x01\x9e\xef\x96\x88D\xb0\xe6p9\xf1\xc1$\xf4\xf5\xc8_&lt;\xb7\xcc\x13\x95\xed\xaf\xf6\x14\xd1\x16\xc3//\x88\xa9\x1a\x06\x87LO\x194\x15\xb3\xb1\xa0\xb7\x8e\xeb\xad~\x8d\xa0]\xc8=\xb0\xba\xfcv\xe4qs\x19\xf6\xf0`2\x05Qp%\x99\x85\xc4\xf5\x1cI\x87\x8fC+I\xed~\xfa\xf0\xf3t\x19\xaf\x83\xe4\xcf\xc4\'\xc9wLg\x129\n\xc4l\xde\x0eG\x8f\x86E\x879T\xb8\x15\xa3\x84\x97\xad\x7f\x13\xfb\x1c.%\xef\xc0Lj\'\x14\xe4/\x85\xc6\xc5\xcc5\x08N\x8e\x14\xad\x8f@C\xa8R\\Df\xce\xd3\x9e\xc3\xe3s\xfe0{\x8b\xec\r\xdfR\xe9\xeb\xd3\\+\t\x06\xb9\xe3\t=\xe8\xabY\x80\xf3y\n\xc8\xb8\x12\x1d\x11\xd6\x15%\xc3\xee\xcerSI\xfa\xd5\xbd\xb1t\x17\xa6 \xca-\r\xc5&amp;4\x95\x90\xcd7\xc0 \x17\x81|k\x13\xb7jLS\xf6o\x87\x0f\xa3v\x95\xaa\x04\xbf\xef2\xe78\xce\xb2\xab8\xbb\x15\x7f,(D\x1a4&gt;\\7\xf0\x9b?]R\xe7\xc6\xe8\x8b[\x02\x9f%\xa9\x05\x91\x9elx\xa0\xc7@\xee\xd6P\xb5%e\\{Z\x946\xfd\xeccjQb\x97\x15f\xb7l\xba\x10[+tT\xba\x0b\xb6@{\x02\xab{+\x85\x13\xf4%u\xed\xbb\xe4*\xaa\xb0\xcdC\x8f\xb0\x88\xf7\xde)\xb6\x7f7\x8f\'\t\xe7\xad\xfa\xb0\x12\x8c\x1b\x7f\xc6\xb4\xf3\xfd?\x06\x03\r\xfc\x7f\xcc\xdbv\xc0\xb3\xc0K\xdc2"\xbf\xfc\xba\xe9(,\xe8\x81c\xcb&lt;/M\xfe\xee\x00\xb6Jb\x80D\xcbP\x84\xc9$\xc5\'\xc2\xb3$\x97\x04.\xef\xbf3\xbc\x16\xd7\xc6\xf0\x82\xa0\xbf/\x83\xc7\xb63\x006"Y]\x17\xf1"u\x0c\x95}\xcakZ\xff\xe3f\xb2\xd3G\xf4\x90$v?\xc5\xa9\x13\'\xca\xe6\xb3U`\x90\x83o\xe6\x1b\x10\xa3\xf4\xfa\xfe\xce\xf9\xceZ\x0c\xc7\xc0\xe1\xc0\xd4\x9d\xd6\xe8\xa5\xf3\x12\xaeL\xa4\xfa\xfb\xa8=\xa4\xdf\n\x17\x0c\xa7\xf57q\xd6\x80#\xd3\xf4\x9a\xb0\xa6\xeef\xef95\xa6\xae\xe4{\xb0\x1e\xae\x8e5\xbdH\xc0oA\xd0\xd3\xee\xd4\x14\x95V\xe3\r\x056W\x98`\x1f\x99N\xbeS&amp;2\'"\xec\x18n\xbf\x9f\x97\xe06\xb8\x05\\\x92n\x14\xdf\xcbQ(#}/6e&amp;&gt;2\xdcS4\xb6\x11}\x0b\x87\x1c\xff\x18\xa0a\xbd\xe0"\xf4\xdd\x8b\x1d\x01\x03\xf2\xbb\xc0\xd3\xa6G5\xa9\x16\x02\x19\\O\xce\xf0\x00\xd1@\tW\x95\x80\xe24/L\xdd\xb4\xdfD\xbb\xc5\xda\xf3M\xa2\xb0\xaa\x90\xaf\xe0#\xaa\xe0(\xaf;\xfb_v%V\xde\x02C\x04w\x904\xfd\x17\x84\xd4\xd0\n\xbb\xb9\x06X7s9\x07\xd8\x9e\xc09\xcf\xe3\xdf\xec\xaa\xd2\x8dT\x0e-X,\x0fP&amp;h\x92\x96\n\xdc7M\x10H\x8a\xb2\xc7\xfc!\x1d\xd5\xdd\x1d\xf6\xa5.\xda\xadH\xb7\xc4rQ\x85\xc1\x96\xcd\xd5\xa6\x0ee\x86y\x95\xe2\nQ8}\xc1R\xab\x12\xa2\xf9\xba.\x98\xeb\x16\xb6FC0\xb0\x93\xe4\x85\ry\xd4\xa1\xb9V\xdb\xfdpr\xe1,\xe1]7`j\xb4H\x19_e\xe7\xfe\t\xf8P\x83\x94\xca\xb4\n\x94\xef\xe6}/\xb0\'bbN\xab\xd4\x9b\x91\xa4g\x0c9\xb8\xe2\xaa\x03\xd5\x18\x83\xfdRj\x83\xca\xc1\x95\xc5\\)\x11\xca\x8aD\xde\xfb\xf5\xc1#Q\xcf\xf2\x08m\xfe\xe6\x86\xeb\x13~Yl8\x7f\xa5\x0c\xb7vg`\xd7\x15\xcc\xf3\x92\x19\x80\n\xc0h \xbc\x17\xb4n\xd1?+wS\xa4\x91\xcaZ\xfd@7\xeb\xfe\xed\x10\xeb\xe4;\xcd\xd1t\xd78V\x94\xac\x97\x88\x87{\xd4\x82\x87\xd5\xc7\x07\x88\xc0\xf8ax\xdf\xce\xc5\x7f)s\x9e\xa2Ez\xc5\xa6\xd5q5a\xd4\x84B\xb3\xf0\x1b\x7fu\x7fX\x83\x8a\xaf\x00\xec8\xf6\x9d`^\xfa\xde:\xdb\xa4\x98\xef\x83\xdeD2\xf8\xaf5 \xaf\xd1\xc4\x92\xcd\xc3\x91G\x90t\xa8bM9\x87\x0f^\x03hy\xc9\x8a7\xeb\xc0,O)\x858\x08w\x07\xcb\xf7\\&amp;\'\xe2\xbe\xeb\xb9h\xf6\\\xac\x99\xcb\xa2\xe1}4)\xf4\x03\x8f\xd3{I]1\xeb`\r\xa8\x8b\x83\xd9\xda\xff\xb2\x91\x12_\x965}R\x17\xbd\xf4\xa5\x05 w\xf3\xb8\x90+we/\xfe\x08u$\xc0\x89\xe5\xd2z\x97\xe0M~\xc0\x8d\xf8\xdbT\xdc\xcc\x94\xf3-T\xbf\xb6P+\xfdy \xbeL]\xfak\\2\xa7\xce\x91\x05$\xd5\xb0\x03u\x00)\x88\x89w\xc6)\xf2\xa4\xaa\xc2\xf3\x10\xf5\xafO*DR?\xe8sb\xba\x08\xd7]\x13!#,\xbc\xfdeZ\xa4_b&amp;\'&gt;\xf5(\xaa\x0f\x1e\x9c\x00fB\xa1z\xe8\x9d\xc1\xb5\x00\xee\x89\xce\xc9T\xcc\xbcn9\xc4\xe7\xbf\x9d\x9ai\x1c\xf3\x07\x11#l\x94\xa4\x0c6B\x92\xd8\xcfR\xee\xd3V"\xae_\x05\xd4pV\x9c\xe4\x8c\xda|\x91-\x82\x98\xb5n\'nD\xca\x84\xdc;Xg\xed\xec\x85\x85\xb0\x02?Fwk\xa9\xba\x92\xbe\x0e\xfa\x00\xa1su\x99"~%\x11~}\xe36\x05m9~\xb3\x0e\x1ar\xda.\xc7\x1a\xa5\xf7\xcb\x87\xc8\x8c\x0fR\xd1\x00\xab\x0b\xa7\xff\xe17\xbfO\xe9\x9c\xa0\x84\xf9\x96\x9b\xccU\xbd\xf4\x96\xe6\xb2\x86\xf2\xf1\xc1\xff\xe1g\xdc\xff-z?u=r\x91\xac\xdc\xf7\xe88~H\x1b\xd6\xab\xe4\xab\xb0(\x12\xdb\x9d/\x82\x1a\xf8\xf2L\xb5\xf8jx\r\xdd\xbe\x8e\xc8|0:lQ\x01\xc2\xea\x88\xa0\xd0u\xe7L\xeby!\r\xea\xa7\x98\xa0\x81&gt;\xcc\\\x87&lt;\xbb\xb7\xac\x00\'\xe5\xed{(\xbc\x96\xe4\x95%\x80\xaf\x9d\'\x11g\xa2K\xbe2\xda\xdf0I=\x03\xe6\x18\x84\xc2\x08\xf8f\xdd}\xb6\x1a[\xf0Gn|\xc9O\x8d\x1f\xaaz\x9el\x8fR\xab\xbau\xc9\xb6_L@\x10\x11k\xe9L\xfa\x08\xd4tK\x16a\xa6\\{I\xc2\x01\x04Q\'\x95-6ln\x0b~\xb9*\x9a\x90`\xdc\xcc\x8cT\x9b\xd5\x00\x0e\x90\x85n\x87f\xec\xa8\xf8\xbb\xb2\x19\x16d\xc2d\x13\xc5\xc2\xc1\x83\x9a\x07\xc0\x17V\x15\x91\xae nj\xd1\xf4\t\xe44\xcc\xac\x87&amp;\xed`&amp;$\x8e\xdf\xc8&amp;\xbc\x95\n\x0f\x15&lt;d\xc8\xc8\tW\x8d\xceEw\xc7\xb2\xbf\x87\x96\x17\xe0\x86C\xa3\xc7\xdd\xbcJW\xc4\xb3\x902\xb4\x91\xab\x92\xdcF\x8c\xf3\x01\xdd\x88\x95"lEb\xed\x9a\x1d\x15\x9f\x0fOR\xd4:\x84\xd2\xffx\xa6\xd2e\xbfW.\xcc\x08\x9a\x07T*\x85\x07\xde\xc4]\xcbnVx\x97\x89j\xfc\x10\xa2F\xf8+\x15\xcc8w7an\xd2K\xb3\xad\xb6\x8c\x1a1]\xac|\x8a:\xd9\x0b\xa5\x03\x0cFz\x10\xa7\x8eA)\xc8\x1a\x9e\xa5\x06a\xeb\xd5\x90a:\x9d`L%\x04\x9bL\xa7G\xb1s\xc5$\x81\xf3\xf9\xb8\xdd\x193\x96;\xf4\xd7\xee\xfc]\x90A\xbc\x9dK\x11\xea\xd5\xb6\xf4\x1fM\x0c\x96\xdb\xbc\x8b\x85Y\xd8\xa8|Ec\x17j9*\xba\xd7Z\x02\x805\x16\x92"Q%\xfc|%4w%\xde\xae\x87a\xe4\xbb}\xd3z\xaa\xb3\x0b!\xbf\'\xae\x8db\x12\xae|3F\\i\xe0\xf4oIh\xeb\x02\x00\x8fp)\xde\x92\xb8N\x16~(\xbf4\xbf\xb8\xe5\xf9\xeb\x19y\x13\xb0\xda%\x0b\xdc\xaaV\xa6\x02D,\xdc\xe2\xfe\xd7\xdb1\xfc\x11\x82\x83\x124h\xd7@\x18|\xd3\xf1\x821|\x96\x89\xf0^\xbc\x12\x10I\xbd\xe5d0\x195\xf2\r\xbbX\xac\xdd\xb1c\x93\xed\xb4&amp;\xa2B\x95\n\xf5\x02\xa1\xe6\xa1\xf4\x971\x82I\xf0\x9a\x8f\xe9x\x1f#\x86\x8aT\x86h\x05\x89\x8d\x1a\x1cZ\x0f\xe0\xcb\xd0\x90^0\xd8\x14G\x16x6m\x1acRN\x19\xef\xae\xa4\x8e(\xb3|I\xeb\xaf\xf7\x1fH+h~N\x89\xb0\x86\xd24\xca\xe7\xd0m\x19%\\\xe7I\xb8\xc9Cxb\x92@\x98\x08\xb1a\x00\n\xc8\x99\x99K\xa5\xac\x1aI\x8d\x1fy\xd0\xae\xf8\x83p\xc8\xfa\x19\xf0x\xbe\x88\x82I\x14~\xab\xcb\xd5P\xcc\x90\x91!f\xf7\x1e\xe8\x02;d\xe2\xa9\x0f(?XD\xd62\n.P\x1c\xde\x03\x1b\x9dm\xf3\xc3\xc9O\xf1\xb9\xff\x14*\xc3\x8f\x18\xd5W32\x1b\xbd\xb5\xc6\xe0\xf4I\xf7P\xb2\xfbV\xbf\x9a\x06\x84oR\xd5\xa2\x95\x9f\x05\x0f\xe52\xbaxi\x17\xd6|\xe5\xe6\xba\xccy\xccE\xcc\xeb\x08b\x1d\xb1\x93\x19\xc8TBry&lt;\x87G\xf6\xe2\xc1\nq\xda\xfe\xdf\xdf\xf2\xebsUj\xd1\xa0M\x8b\xc9P2\xfa\x17\xf1\x98\xa3\xcf\xf5I\x84"\x86\x9c=V\x96\xce\x80\x11\xd0\x845.\xf5\xc44\x8d\xca\x85K\xca\xea\xafm\xf4\x8b\xd8L\xe6\xcf$S\xd0\xa5\xe6\x86\x0b\xd3c\xbe\xe7\x9d\x89?\x8d\x83d\x04\xb0\x11&lt;#\xef\x97?g?\xa2U\xfc11o\xcf\x91\x95"qXg\xef\xb7g\xa9G\x08+\xf6\xc5\x0e\x955\xe3#\x97\xd1%\xa1\xb5\xa1\xedb\xc0A\x8e\x7f\x94\xa0\xfd\xb6\x8a\xb7[e\xd9C$C\xd0\x0b\xf5H~\xc0\xa3\xfb9\xf4\'\xcd\xf4\xd0\xa7\x1c\x00\x9a \xba0\x03ve\x9aWe\x1fQ\xf5C\xf1\xbe\xe0\x89k\xf0\xb87\xc8\xda\xf5\xb30\xb5\x8f|o\xee\xd4\xa7\xfd\x1b\x97\x95^\xce\x91\xeb\xf6\x04\xac\x91\x1e\xb0\n\xa6\x00\x16\xbei,\xa0\xbc\x90\xe0\xc2\xd4cW\r\x0f\x97\x8d\xabE\xcf\xb1\xb2\xbfh\xda\xac\xf5u\xa9\xff\xbb\x1a\xcf\xf4\xa0\xb8\xc7\xacI\xc5\x12\x01\xf0\x94p1\xcd\x8c\xea\x93\xc4\xc8\x1dPyB|\x05\xad&amp;e\x88:~t\xe0\xfe\x17\xe7\xd64\xb1\xa3\x1f\xa7\xd3\x10\xe3\xe8\xa5\x12\xe8\x17&amp;\x1d1&amp;ey1\x16\xa1\xf0.\x08Os/\xa4\xfa\x8c\t\xc7\xf2b\xd9\x89\xfb\xca\xd3\x8b\x17\xb9\xf5\x94\x17.x^\x8e\xb3\xfe!\x11/\x18V\x1d\xd2{I\\\xa9\xf9\x13GRzfKm\x8b\x12o\xdbiMeT}\xb9\x1b\xfe\xb4\xf0l\x8f\x0f"G\x05v\x07\x82\nm\xf2\x9eP\xaf\xf6S\x07\xb2(Y3\xf2"j\xac\xc0\x82HK\xbca\x90\x0ed5\xd5\xf2M\xcf2\xfc\xbdkI4\x9a3\x82,mE\x11\x1cAl\xe5\xa2\xbb\xf5\xbay\x89~\x0b\xd65\xce\xc0\xd7\x8e\x8b+\x1e6S\x0b\x94\xdd:Q\x91\xef\x04\x0f/\xdf\xbd\x068=m\xfcJ\x19D\x13.&amp;\xed\xe8\x9eZ\x16A\x04\xc7\xea/:g,K\n\xd2\xfa\xe8\x0c\x87\x9e\x1e\x93~\r\x9b\xe5\xfcI\xe5\xa9\'\xd7\xbeif\xa7j)!52]7-\x1b\x8e\xf9l&amp;\xb4\xbdt\x82\xb7\xb9\x04;Tx\x8a&lt;R\xe6\xc5o\xf0i\xa6N\x97A\xab\xfb\x14\xb3\x8dzl\xf4\\\xb9+Y\xf9U\xa4\xe3\x9c\x18&lt;7\xb8vpc\x1d\x92\xd3x\xc1\xa5\xb3\xdd\xbb\xcb\xc6\xdf\x05\xcd[\xa7\x16\x9e\xb9L(\xf3|DW|\x8e\xce\x84\xf7E\xf3xN9\x8a\xc1,r=\xca\x07\x8e\xb4\x1e8\xa9\t\xf8\xde\xf3\x0e\x8e\xd8\x07\x9c\x06/L\xaa\x9f\xfa\xf8)\x86x\xfa\xee\xccC\xc7\xb4\xe6\xa4\x15\xbc!\xf2\x1e\x96N\xa3\xc3\x9a\x0c\x88\xb5\xbd\xe8\x1d\xe0\x8azL\xedE\xfe5~j\xe5\xcev\xf41%\x18\xf5\r\xa1\x97\xe4\xbb\x93\xb1\xd9a\xdb\xbc}=/\xd7X\xc8B\x9e[\xd2\x18\xfes\xfd\x89Gm\xdc\x8e!y\xbf\x1d\xea\x9bl44\xa0\x9c\t\x93yG\x9dl\x9e\xf1\xd5,\x95\xef\x82\x19\xca\xd8~\x10a\x1c\xc6\xa4\xf1\xe7\x8b\xa7|&amp;\x9d\xfek\xaa([\xd1\x03\x83\x93H\xd0\xea\xc1d\xe1\x96\x13\xd8\xca\xa0\x9a\xb4%A2\xd6\xf40\xcdb\x9aE 4PUf\x82\xeb\x16g\x82\x99\xd7\x0cXy\xee\xbf\xe4\xb8e\x8an\xf7\x87\x81\xeb\xb9*[\xc7\xe4\xaf\xf0\xa0o\x9f\xb05\xa3\xd0\x99\x1b\xf7\x88Kj\xeb5\x8a\x1a\xc9\xe4\x04\xd6\xc9\xde\x83\xb8(k\xf3\x19\x84\xc6O\xbf\xce\xe1\x1f\xb1\x07\xd2\x9cb\xe5A\xefD\x91\x98\xaa\x85S(\x9d\x87\xeb-+\xef\xb1L \xa8(\x0f\x89\xa7\xed\x9a\t\xdb+\xe7=Q\x02\xcc\x94\x93T\x90F%\xc9&gt;\xee\xf5\xd4\xd5\x17\xcdj\xc4JO\xfb\x86\xf1S\xb7r\xe6\xe5\xf1+\xd3\x8d\x98\x1d\xa1\x1b\x82(\xf3Yf\xfd\xd7U\xab\xaf\x12A\x8e\xf1\x1f\xa7\x02W\xac\xb5\x88-\xe9\x11\x9e\xb3\x9c2\xf66\x07O\x03! \xddi\x11\xd9\xb3\xe7\xa8\x92\x857\x8f\xd6\xac\xe4t\xb4aj\x8c\x0f\x1c\x99\x04Z\x9c\xe6\x97\x97\xa3\x14\xba\xdc\xcd\xb5\x06\xfaR\x85J\xc7\xa2\x98\xc37I\xe9,\xe5\xbd\xe9\x95FQ\x94y*\xb1u\xa4\xe7\xed\xb3n]C\xa18\x1f\xf8\x0bR\x90Qh\x0e\xa6\xb7Z\x9a\xc5a\xf6\xdd\x01\x82\xaaU\x12\xad\x9eC\xfe\x02\xb1\nx\x82\xf9\x0b\x1e*\xbf\xb7\x10\x0f\xbee\xec\n\xf4g\xbe\xc0\xb4\x86(\xae\x0c\xa1.\xceQ\xf9]s\xb0\xdb\xb0\xb90r\x9b\xfe\x19\x89#t\x08\xa7\xe7\xb3\xa6\xdd\xf8\xba\xe1Qk.\x83Q\x1a1_o\x01\xf9"\xce\xee8\x84^\xf9\x82\xd0bOA&amp;\xa5BS\xa5A\x1cAm\xfe\xe0s,K\xf06\xcf\x16\x9e}\x1e^\x95\xd2\xc2\xa6\x96n\xbd=\xb8\xb6\x80\x00\xee\xa3\xea7m\x05\x0fN$ )\xe3c\x97\xc7\x00DG.\x9cW\xe5 N.n\xf4\xc8\x9a)\xd9\x7f\x93\xb2\x7f\xea\x87\xe0\x9f\xcc\xa7\'\x1bC\x11;A\xe5\xb2\xabP\xbc\xf3\xa2MN,\x01\xf1\xa4H\xc1\xc7\x04\x9a\x1b\xc2\xcc\x97\x87Y\xcb\x89\xcb\xf0\xd7G\x17\xb2\xd3\xb56\xf0\xf4\xe2\x00\x05\x9aOu\xf7\xf0\x96\x86\x01\xa3\xc9\xd4\x95\xcb\x82:p\x98\xcaE&amp;\xc3\x87\x13\xd4\xcfu5\xef8\xb0~\x98\xeb\x1b\x18\x82U\xb9\xf6\x8e\x80\x7f\xf5\xc8\xd3\x10\x95\xb1\xa4\x18Y\x82\xca\xc8\xa7\x9a1\xc4n.\xe6H4\xc4\xef5#\xfb\xb6\xbb\xa2o\xf9\xf7\x18\xd0\x05\xed\xa8W\r}\x91\xa0P\x95S\x1d\x08\xcec\xe4\x077\xf7Cu\xeeZE\xc3\x85\x04\xb6*\xd1#\xe2\xe9p\xd90O&gt;\xbd\x8e#g\x12\xf9g\x17+\xc2\xc1;T}\x0f]p\x97\xa7n\xbb\xbf\xb7*[\x9e\xea\xd9\xb5\x1b0\x17nA\xc9$\xe4\\_\\\xcf\t\xc5\xee\x8b&amp;9\xa5G\xfa.\xb72s\xa0\xb5H\x00"\xaf\x8a\x9a=}D\x96\xba\x1c\xc2\xdb\'-\x93\x9c\xd3\xc0\xd1`\x81\x1a\xdd&amp;c\x8d\xf5g\x1f\x10NM&amp;&lt;)\xaa\xd6\x1d\x8c0\xaa\xd9P\x07\xa7\xd0h\xd6\x9e\x87a\x9d\xa8\xc4\x067\xc4\x18\xf6\xdb\xe9\xc6BmV)\x97\n\x86E\x84\xce\xf2\x85\x82\x9e\x18\xa7\x19\x86r$n\xddWX\xc9$\xe6\xa4\x9c\xc2\x94\xf0\xa7t\x1e\x0fy\xac\xef\x13\xfd*\xb5\xdf\xd1\xf7n\x1f\x8f\xec\xba\xc6*QHu&gt;\xa6A\xb9\xa0\x10mj;~-\xdat\xcc6\x17\xf4\x1b)\x1c\xc3\x15Z\x8f\x9eOq\xf4G\x0e\xf5s\xb2\x83\x84\x80\x00\xc8 :^\x94\xae\xa4\xf7=[\xc6]\x82\x1fog\xab@\xfb\xc0\xbaX~\x03\x06oj9\xf9}1\x15h/\xe1b\x03E\xff\xba\xe1%N\n\xd6\x1e;\x81\x03)\xd1]+\xdf\r\xcb*\xbd\x08\xd5\xceGc\xa5\x06\x05j\xe7=L\x98\nU\xdc\xc9v}\xe7\xdcB\xb9\xbb(\x88U)\xff\xef\x08IC\xea\x13f\xab\xc2\x0eZ\x1a\x92\xe9Dr]ad$@\x06\xc1:9_\xee\x91\xaeI\xb8q%\xbc\x9f\xa6\xc3\xd1@\\\xc1\x0e\'\x1f\xdenC^RB\xa5\x1e&lt;0\x11n%ss\x99\xb5\xf3B/o\x03\x8c\t\x8b\xc0\xf0iL\x05p\xef\x93\xc7M\x87\x1bJL\xc2` \xedr\xa2X#Dq)\xf1\xd6\\e\x91O=\xb0FH\x91T\xe9_P\x92\x0b\x7f\xce[\xbb\xdd\x89\xe7\x9b\x1b\xa6\xbeH\xdf\x8b\xebE\xf7X\xbc\xff\x11.q\xc94\x91\xfe7)\x0c\x98\x15t\xaf\xcd\x94\xb3)\xbe\xf4\x81iMc\xa4\x96G\xa2\xc40\xdep\xb0\xac\xa3\x00&lt;\x00N\xf3H\x9e?T\xbc\x01=\xa5\xa2\x054W\xf4m\xe8\xe6\xeb)\xa4\xc2\xcbO\xdb,\xb0\xcd\xe5{o\xf5@\xe1E\x8d\x80O:?cSJ\xab?\x02;\xb7\x14WAKkY\x97\xbf\x8d\xb7\x8f\xf0X\xf11\xb8:\xbd\x05\xeb\x89\xf8\x8f\xb8\xa6\x13s\xa6\xebY\x9c\x0c\x90\xf7&amp;\x085\xc2^\xc2\xfe\xedF1\xe3\x91\x12\x84\xc5\xcb\x98&gt;iC\xfec\xad\xbe\x0b\xcd\x0fVR\xf9\xf9\x85\r(\xe3\xe6\xc1\x12Tx\x9a\xf9;\'\xb3Yu\xc1V2!\x9by\xd1\xe1\\\x00\x08\xcfX\x1aF\\\xa4\xefB\xfd\xef\xf3\xae\x9f\x04\x1b\x87\xbf1\xc9\x1d.\xcc\x84\xa7\x13~\xff\xb1\xa3\xb7\x1a9m$xw\xe0.\x81)t\n\\\x9c\x079\xa8R.\xab\xc8_\xf0\x97q\x8a\xbc\xcdL\xca\x91&amp;Pb\xae*\xa7\xd0\x9d\'\x9d\xefW\xd2\xf9\x87\x7f\xbb,\xe2\x14\xfdg\x9e\x804o\x8cI\x8b\xcb}\x7f\xfd\xdb\x15\xd4\x13FO\x8do\xf9\xda\xa8\x94\xf5\x8b^j^\x11)\xc7\xa5\x9f#\x8c\xbe\xcc\x0fl\xf9\x16\x10\xcf\xd7\x17UA\xf9x\xd6\xee\xaf\xfeY\xd0\x8f\x01}$\x82U\x00\x00'</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Suqueira Transparente P/ Bebidas 4,5 Lt Super Promoção! Transparente</t>
+          <t>Conjunto Fitness Virginia Top Shorts Meia Coxa Cintura Alta</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>34</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>497</t>
+          <t>69</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>72</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>59% OFF</t>
+          <t>72</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/suqueira-transparente-p-bebidas--45-lt-super-promocao/up/MLBU1153632449?pdp_filters=item_id%3AMLB3822305971&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB3822305971&amp;sid=affiliates</t>
+          <t>49% OFF</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_730816-MLB78414996620_082024-AB.webp</t>
+          <t>https://produto.mercadolivre.com.br/MLB-5184808828-conjunto-fitness-virginia-top-shorts-meia-coxa-cintura-alta-_JM?searchVariation=186114253503&amp;pdp_filters=item_id%3AMLB5184808828&amp;extra_comm=true#polycard_client=affiliates</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>b'RIFF\xa6\x18\x00\x00WEBPVP8 \x9a\x18\x00\x00\x90\xa0\x00\x9d\x01*\xc0\x01\xc0\x01&gt;m6\x98H\xa4#%($\xf3\x98\xd9\x00\r\x89gn\xe1v\x01\x03a]od\xe3\xebz\x0b\xdd?\xde\xf1\x9a"+c\x7f\xaf\xff\x93\xee7o\xdf\x98\xef\xd9\x9fT\x1fP&gt;\x80\x1f\xde\xbf\xbau\xe3\xfa\x1d~\xc0u\xca~\xe7\xfaa\xea\x854\x1f\xf9\x9e/\xd9.\x13\xef\x03\xe1\xc6n?\xc4\xf3\xfbO\xf6\x81~4\xba\x8b\xb1I\x89\xc0\xdb\x13\x81\xb6\'\x03lN\x06\xd8\x9c\r\xb18\x1b\x08\x0e\xdc\xab\x15\x00\xb0\xcb\xdb\xea)\xcc6Co\x8e\x0c\x97\x9c\x19/82^pa\x06Y\xc0g\xe4\x13\xcc\x00\xa5z\x88\r\x8d\xd73\t\xfalZb\xb9\xa9P\xd7;\xa782^pd\xbc\xe0\xc9y\xc0\xb8\x96\xddW\x9f\x9a\x89PF\xbf"\xd9\xc0\xcfi\x08\xf6J\xe8\xd0\xd8\x0c\x9dy[\xa3%\x93\x81-,Q~X\xa2\xfc\xb1E\xf3G&lt;\xfe\xa5\x7f;\x17\xc4\xd4(\xa3\xf4\xac\x11\xf1\x7f.\xe0\xc2\x13\xed\x85s\x1e\xa9\xc5\x9cZ\xf1;\xb8u=T\x06\xd8\x9c\r\xb18\x1bbp+z\x13k\xef\x01\x06\x87\xbb\xfa\xed\xb9`\x9d\xec\xf6\x16\xae\xb8\xf5\x13\x9d\'sO\x19\x8f\xeaZ_b\x8ff\xa3F\x19\xa1\x1a\xeb\x06|\x19/82^E\xd8\xa5\x00\x97\xe4\xb5\xaf/L6\x04!^\xf1\xb5\x97\xa0\xfc]\x08\xd2\xe5E\x9f\x1f\x91\xa7+v*\to{\xfe\x91~X\xa2\xfc\xb1E\xf9\x03\xde^\xc4\x8c\xb0\x98\xde\x87~\xa1-\xa1m\xbf\x9cuo\xe7\xe5fRC"#\xe1b\xd1f\xc7\xf2\xaa\xda"\xdc\x0b\x1c\x80u8G\x9a\xa7\xb0=\x89\xc0\xdb\x13\x81\xb6&amp;\xfa\xae\x15\xec\x7f\xff\x15\xe5XbGt\x17\xae\xc0Q\x11zo\xd7q\x85\xb1\x8fSR\xe1J\xeb\x85\xc67\\\xda\x9e\xe3\xe1\xec\x92\x07\x03~\xce\xed\xba\x80oP\xd9\x90]\x84k\xac\x19\xf0d\xbc\x97\xe7\xf5^\xac\x9c\xd9N\xde;\xe5\x03\xb9\xbd&amp;\x0e\xbf`\x07\xa2a\xc7Z\xa8\xa0n\xcb\xe5\xe2\x98\x19\'\xcdO\xf2\xe6\xb9\xd4\x17O\x19*%L\xb6\xce]\xd77|%c\nR\xd9\x98\xc1\'5\xe0m\x89\xc0\xdb\x13\x81i\xdf\x90\xca\xed\xee\x04\xb6At \x10\xe5\x016\x08\x0cU#t(\xd4 Giy\x14\xc6\xca\x9d\x10eq\x86\x9fn\xd3c\xcd\xd85\xe4\xc8\xd5\xa4|J\t\x8a/\xcb\x14_\x95\xc4?\x0cw\x9a\xf2\xb5R\xbc\xba\xa7\x10\x87\xcc\x96\x1b\x8f\x0b\nZ\x96t\x9e\xd7\xe5\x01\xce5\xfa\x0e_\xb4\'\xffx\x1d\xf4tlLzW\x9c\x19/82^E\x9b\x05\xdeO\x93a\xa9\x19tQ\x7f\x17!\xd76\x9f\x00Z}\x94\xfdf\xc0~|:\xf5|\xcf\xe0.\xd0\xaag\x15d\xb3}5\x9a\x9a*\xb2\x06\xd8\x9c\r\xb18\x15\xabd\x0f\xe7D\xb5\x9bdy%^r*9\x9f\xab\x8e\xbe\xec\xc7\x15\xdb\xfee!\xe3\x02\xff\x0f\xbey\x84T?~\xfcP\xe6\x11Q\xd48:Yk\xe8#\x8e\x08_\'S\xd4\xecw^\x06\xba\xc1\x9f\x06K\xc8\xc2\xee|7\xc8\x9eo\xd6\x9f\x8e\x88\x1a\xbe\xfe-J\xd73\xd9F\xde\x8f\xa371CH\x10\x96\x91\xd0\x1c\x99\xc5\x84\x8c\xff\xba\xdf\xa6\x98\xd1\xf9e\xa53\x13\xf7\xec\x11\x8e\x95\xbe\x00[a\x1a\xeb\x06|\x19 \xdeD\xac\xc7\xf3\xb5\xc8x\'V\x89\x85D\x06C\xea\x10=|\xe6\x81&gt;\x0fr\xcd\x002\xad\x86!\xab\xf7\xdb D\xe9\x9c0;\xec\xdd\xd6\xb4\xefU(\x97\x96\x99\x8e\x966,X0,J\x86\xba\xc1\x9f\x06K\xcd\xac\'&lt;\x1es\x05;U2\x93\xd1\xf4\xae\xc1!\xf3\x8ch`-t\t\x19\x82~\xf5~K\x1e\xf7\xb6\xe4\xb3\xf6\x08\xe9\xf3\xeb\xf2\x81\x98\x15~X\xa2\xfc\xb1E\xf9[\x07\xdc\x90,\x1e\xc6\x0b\tI\xaf9_\xdbg2\xa9U?\xb7\xf1\x8f\xf9/\xd6\x0c\xf82^pd\xbc\x87&gt;%\xb8\x89\xaf\xb2\x997\x0e\x03J\xfaT\x18\xee\x1e\x03\xce\x93\x81\xb6\'\x03lL\xde\x17\x98\x93\xfc\x81\xc5\xc6\x07\xa2\x7f\xea0\x81\x9f,\xb3\xecJ.\x98\xfc\xcf\x83%\xe7\x06K\x95\x96\x88\x8b&lt;\x8b\xc1\xc3\xe3]P*\x92\x97\xf0gV\xb6\x8a6\xf3ur\xfc\xb1E\xf9b\x8b\xf2\x8a\x15\x15\x08\xce\x8c\xf0\xd9f\xe7K\x9f\xbc\xe1\x05\xaa\x96\xad\xd9\x14\x04\xcf\xf7\x0b \x9aQ\xd9\xa7\x1e\xf1-\x9fS\xb7\xc8\xbf\x81\xb6\'\x03lN\x06\xd8z\xe6\xec\x88\x11\xd1u\xff\xfa?h\'\xbf\x8d\x99\x19&amp;\\)\xd2\x05&gt;\xae\xe7\x91%h#-\xb3\xe9)\x00n\xfeI5\xb1l0"\xfc\xb1E\xf9b\x8b\xf2\xb8a\x97k\xaa\xc0{\x11\xc4_|\x8fl\xb2S\x84\xa1\x7f\xf1\x90XN\xd5\x8eT]hh]S\xd01\xb7\xce\x93\x81\xb6\'\x03lM\xf5\xea?\x0eBU\x92}Q\xe6\x95B\\8\x03\xbc\x1c\x19\x01\x06.\x84/82^pd\xbc\xe0\xc9y\x19\xd3@\xa9\xd4\x9d\xafT\xeaX\n\x89\xfe\xec\x0f\xbaz-\'\xc6\xef\x16-a\xed\x90l\xdb}\xfd\x07\x86\xba\xc1\x9f\x06K\xce\x0c\x97\x934\xa9%\xaf\xc2e\xd6}&gt;\x0c\xf2\xea\x0f\xe9q\x07W\x1b\x0f\x9fK\xf4\x93\xa6-\x89\xc0\xdb\x13\x81\xb6\'\x03lc\x9f](\xf3&gt;\x0c\x97\x90\x00\x00\xfe\xff\xc6\x84\x00\x00\x13\\\xda!8\xb6\xf9x\xbdP\x8dW\x13\xe3\xf0\xe7Lt@\xbf\x1dT\xb0{\x11\x03[[\xa3aJ\xc6\xa7\x14=/ \xcd7\xa3d?\\\x02]=\xec\xc0\xd7\xa4\xcdb\x05}\\H$\x1dWO\xf7\xcb\x95Z\x9aC\xb3\xadN?\xc8\xb5\xbf\rE\xbbrI\xce\xcfsok"\x1c+\xbd\xc8\xcf4o\xed\x8e\xe2f\xa6\x97\x0e\xf1\x12\x9f\xf3\xf0\x00(o\x81\x1c\xce\x08\x05\xd7a\x1c1\x14\xd9\x05\xf7\xb6\x85\xd2O\xe2;2\x9b\x1d\xa2\xb5T\xa4U6\x04\x14]P\xa2\x10ep\xbd\x80\xcaH\xecp\x08\x8c\xc5\x14\x12LG\xd5y\xc7\xc8\x8a\xac\xd0=W\x18:\x8a\xf6\xae\x0b\xf5\x1f\x93m\xad\xd2\xb4\\x\x1cu\xb2\xa9\xf0z\x98\x14&gt;\x9b\x90&gt;x.\x0f\xcb\xb4VBpffd\xa3N\xd0\xda\xa0\x8co\x9e\xf8\xb6xi\x95\xd1N\xac\x8a\x0f\xc5F\x04\x9a(!5\x9d\xf3\xc1\x05\xf1YG\x07\xab\xbf\x16\xbf\xe2\xbfn\x13\xba_\x93\x16\xe4\xc1\x1fpZ\xae\xc8\xa7Tr\xc4\x80\xdc\xdf_\xe3\xa8\xc8Q\xb5\x1e\x10\xa3\x8d\xdet\x83 \xddq\x1e\x9aJq\x16\xf7\x02\x04(,\xb3S\xc3}\xf01qT\xe0o\x0b\xbcG\x06\x85\xe1[Hn\xac|\xc5\xff$\xfb\xbb\xdb\x8cH,[\x81\xde\xe3\xe4{\xd53L)\x16\xb1\xb2\\\xfe\x0b\xfcO\x8cy\xca\xad\xa5\xc2E\x878V\x15\x94\x02+\n\x9fH(\x7f\xac}i\xde\x13~\xa6\x934XUo\xd6\x95\x11\xc2w\x88\x0f\xac\n\\\xf5zMho\xee\x0c\xa1)y\x1c&lt;\x1f@\xc7\xa4\xd7\xa4\t\xe0\x9b\xfa\x0cd\xb1\xe71\x7f\xcc\xda\x8f/\xc5\xc3\xe2\x88\xd9\xe3\x00\x9f\xe1\x8d\xfbD%j\xad\xa5\x80\x14A\xaf|\x0f\xd7\xdd3\xee\x10\xado\xae\xc3\xb48;|\xed\xbd@P\x00\x86\xd4I\xb7)\xed\xa59EzB8\t&amp;\xef\xf9l\xf0$DG\xb8\xf5\x0b\xf9\x01\\D\x11\xb8W\xdc\x08\x02a&gt;\xeb\xbb\x81&amp;\xebi\xcao\x85#\xd2\x99\x83s\x0f\x1f\x06\xcc\xd9\x85\xb99\xa8\xf7\xad&gt;!/\xdea\xef\x83[\tIC\x07\xc1x\xd9\x05\x94\x07\xe3\xad\x1c\xf4\xcfr\xdb#7\xfa\xdc\x03\xa7\xba5\x11\x7f\x9c~\x8c\x8c\xd8;\xc3\x07Y\x02\xf1\xc5\xb3\xa9)\x19\x88^\x02\xb8\xed\xe6\\+\x84\x87\xcd\xfc\xc1\xcf\x18A;\xfe7*\xcbM\xf2\xee\x1c\x8b\x93\x9c\x83\x8fv\xae\x07\x1blr\x8b\xa6\xac\xf8t\x02~\x03\x8a\xf9\xca4\xe7Xj\xca:\xbf\x81f\xe9P|N\xa1J\xea\x15\xfc\x14q\x8f\xd3"z\xcb\xdd.\xcd\xab\xb0\xef\x05\xf0\xb2X\xc6\xearW\xd7%\xcf&gt;l\x95L\xcf99M\xc59$A\x11\x8b\xe4c\xdf\xc5I\x8d\x00\x1c\xd8\x91N\xf8\x00\xba\x1f\xe7Z\xb2b\x99Y\xb0G\xf1\xa7\xfa@\xe0\x8d\xf1\xe1\xdc\x05\x81\xd3\xe3A\x17\x9d\x99{Gh\x9d\x8d3\x1c\xf5\xa6n\x19d|\xf3g\xe3\xe4)\x8b\x03\x9e\xd5oG\x88\xb3\xfa\x03@\x8cE9\xd6U\xdd\xb9\x174\xba\'\xe5Y\xcf\xbd\xfa\x0f\xd9`\x9d\xb3Y\xaaK+\xce\x8c8\x18\x90\xf7X\xda\xfe\xc9\xe8\x1c\xeapnA\xba\xbao\xab\x04/\x8dE\xb1\xe5@\xd2\xed\x10\xa5\xafbb\xc9\xb7%O\xd3`d\xcbV\xa3\xda\xe9^\xd2g\xe4\t?_b\xbe\x94\xe0\x95\xf6\x8eoF\x98\xd6\xd1R\x04 \x85\x8c\xb4\xd3\x86\xa3G\xb5\xae\xfd\xcc2\x0f\x7fA\x1043/\xe3`+\xfe(\x16Y\xab\x9d\xe2 \x03|a;\x13\xeb\xb4\xf0\xd3\x0fD1\x9b~\x0f\xc8\x7f\xca\xaeU\x06Iw\xfeA(\x8f\x0b\x07\xe8:\x8c\'W\x95\x06\x19Z)\xe8\xc9h\x92%\x97\x0e\x81l\xc8{\xff\xa0\x99\xe7b\xa9%\xbeH\xd0\x9b8\xdf\x83\xdeQO(\x0f\xf6\xd8\xec\x8e\x93\xdfz\x8cD\x12\xaf\xb8\x8c2\xc4Z\xb7d\x1ft\x8aN\xe6v\x07\xa4\\\x03\x1e:\xffQ\x0c\x04/\xa7\x89\xbc\xb9\x92\xdd0\x86\xcf\x11\xafO/\xa7\xec}\xd8\x87\xd3D\xd2\xeb\xc8\x0b\xdf\x18\xeb\xe7\x8d\\/\xd5R.~!\x9a\x1e\x9d\x17\xf7B\x1f\xe6a?\xcf\xf9\xc1\xe8K\x8d\n\x1e\xb9L\x9a&amp;\xf5\xb9\x18\x1dz]Y\xea\x0f\xd1\xc2w\x05:\x14\xb05c\x93\xdfdL\x81\x1f\xb8[\xd6{\x07\x8c8\xa0\xdbM\x84\x01\xf7\xd1i\x9b\xe5\'YqhfW=8|\xfc\x0b\xa6\xb2\xd0\xa1\xfa\x1b\xf1X}\x03k\xcf\xfc\xdc\x06\xd4M\x0e\xa0M3Q\x170\xef\x87S\xa84\xce\'\x1a\x8fz4)\x15T\x18\xe7yX!IU\xcd\x88%\xb8pT\x87\xc7\xa9ps\xaelv\xf7{5gP\x1c\xc7\xaf\xac3\xc6\xa6L\x82#54\xc1_\x9e%6\x1e(Y\x8e[|\x11sy\xdc\x03\r\x89\xa5)\xda\xb3)%\xfe\xd3\x1c\x1a\xe1\x8a@\x95\nR\x1f\xe1d\t$\'\xd7\x1a\xd6\x0e1#c\xb5\x06(;\\\x0b\xca\xf3\xec\xe4:\x7f\xc0\xd1u)\x84l*\xb86\xb9\x89\xd8\xbaK\'X:!8\xe9\xb1\xb4T\x19\xf8+\xc6\t\xdc^\xb9C\xf8\xd8\x08@q\xfc\xc1.[.K[\x81Z~X;\xb5\xe2\xcbr\xd1\x12\xb81N\x96d\x01\x0c\xc4\xfe\xb6\xefy4\xe6\x07\xea\xd8c\xe1T\x00\\{\xeb\xd6-\x0f\xb2\xd4\x99h\x97\xd1x\xf8`D\xd3\x9f\xcfl\xf2\xd2\x9bjG\x13\x86\xbe\x89\xed\x95Z\x0c\xe6\xcf\x9f\xe7\xf9\x80\x81\xff\xde\xfex\xa0m&amp;\x81\x83\x04\x85\xcd9J\xadN=\xfb\x1f%\x90\xbf4\xb3\x03\xe2s*.\xac\x85\xea\xf8\x1b\x8b\xf9\xaa@\xd8\xe5\x97\x83\xd1\xf8Q\x14@3\xd2\x14&amp;&gt;\x9e\x03\xdbf\xe0\xf0*\x87\xff_\x86\xac\xd1\xf5\x16l\xb5E\xf9\x97\x0b\xb6\x9c\x1b;~_\xd4M\x87&gt;X\xf2\x0eXw\xc8\xd2x\xcb\x9c\x91Ww\xe8x\x0c\xcd\x16\x1c8\xded\x9d\x16\xc1\xd3:\x95\xcd\xf0\xe4\xfc}N\xe2\x87R4\xcfO\x94\x90\xca\xa2w\x1e\x03\x9f\x10zU;?\x87\x15\x7f=\xfa\xec\xa1\xf2\xe8\x12\xabWa\xb6\x91?\xf1\x14\t\xea\xb6\xb0(\xf97*R\x93\x99\xa3S\xd0*V\xc3\xbbg\x86D\x842\xa2\xfe\x97\x92\xe1\\\xebhSl\xd4`OV1;\x9b\xb0\xd2;o\xa4\x13\x15\x1awz\x05\x9b7\x92\x1b\x8e\xfa$\x89\xa3\xd0\xf8\xe4l\xacew7\x83\xaa\xdce\xc2\x08\xe6\xc4\xdf\xa8g\x9c\xb9\x016KZ\xc3\xf5\x9e\xed\x83Q]f\x13\xc1\xb4\x0c\xdb\x03\xd4M\xaf\x15\xca/\x1cGm\xc6\xf26\xa4\x04\x02#7!\x84T\xf6C\xddN\x06]\xc1\xfe\xc6?g\xaf\xd54I\x089\xe0h\xe3)\x1e\xd5\x1a\xf3\x96\xd2\xefJS.An\xd7U\x0e\xa1\'\x98)\xa0\xf5Y\xd0\xd5\x03/c\x98\xc4\x1a\x84\xcc\xdc\xe7\xbf+rS\xb1\x18\x81\xa4\x16\x02\x7f^\xaf\xd4\x1e\x83\x04\xf5\x96\xc9p]:\xb3F\xd2$\xb3\xa0L\x17E{\xe7\xea\x06b\xb3?\x04\xb0\xd8s\xd0{j\x024\x12\xc4efhV\x1f\x93\x9c4AG#\x1a\x01\x18\x94\xce\xa9%\xd8\xdbJ\xa5\xec\xa3Rxz\xa1^@\xbc\xe4\xc3.\xc59\xa4\xaf\xf5\xc9\x7f\xfd\xf4\xd6M\x89\xd9\xa3w\xf0\xccw\x96$KK\xcd+\t;\x05\xd7\x0f\x1dt\xc2\xfba\xe4\xa8\xf5\xad\xa4@u_\x03\xafl\xfd\x15\x89\xaa\xe9\xa3=\xff\x0b!\xbbC\x9e\xd2V\xe4Z\xcd\x87\x07\xa5\xd4\xef\xef|\xdc\xe2a\x8a\xceh)+\xd18\x8et/\x9d\x93\xab\t\x17\xca\x8d\xaf\xf2\xe9\t\xd2\x93R\xf8\xa7#w4\x80{\xa8d\x7f\xb6\x9f\xd4\x05\xefZ\xb0\xc0\x0e\x8a\xa7\xa1\x12\x87I\xc1 \xef\xba\x9f\xe9\x7f\x91\x18B\xa9\xe6V\x1bJ\xd2q)\x1erbAa\x9bu\xacpZ \x95(\xbcxW\x1b\xf4\x16\xdcz4`\xe6\x1a\x18\x14\x1e\'&gt;\x88\xba\xac/=\xcc\xa2\x1f\xeb\x803\r=\x9dd\xe1\x94M\xb3\x06w\xbb\xae\xee\xea\xb0!y\x83\xcb-\x08\xf1\xbe\xb6\xa0\xf2\xf0\r/&amp;\x16\xf1\xc4\xa4$?\xd0\x17\xef\xb4\x9b\xe1\xfe*3\x94\x82\\\xe4\x08\x84\x05\xb5j\xe9\xc6\xa5m\x19H$\xf6\x87*2\xbf\xb9\xa2\xe7\xc4\xb7G.f\xbe\xc8\xa6\x0f\x16\xbf\xea/aX\xc2\x91m\xfcM@\x06\x92\xed\xb8\xbb\xd3\xdbh\x9b\x04\xbdJ\x0c\x96J\xd4GZ\xbc\xd5.\x90\xd5\xc4\xd2\x80\xfa\xbe\x81_\xb2}\x04I\xa9f\t\x98\xfaE\xf8\xb8&lt;\xc7Ea \xdcp\xb0M\x06\xc4\xe1\x91\xb3ix]\x89\xc8"H\xcd8\xb5\xd3\xc9\x9b\xad\n\x96\x9e\x9f\x8dU_b,uL\xe7\x8bP\xcb&gt;\xff\xf2\x01l~\x028\x9d7m%%\x06\xcdc\x9c\x17T\xeb\xdc\x88\xfd\xa9\xc8Lj\xbc1A._\x8c\xa3\xefA4\x7f\xa5\x82\xcf\xfdV1\xaa\nbC\xad\xa1`bMX\x13a\xed+I\x1c\xb4H?\\\xb6C5 \xf0HH\xb7\xc8\x0b\x1e\xf7\xb7=\x9c\xa2\xbfJ\xa8\x83\xf3\xd4\xe2]\x85#,R\x17mA$\xf0\xcf\x93\xf6*\x02\xef\x00TQ\xa1\x87\xbec\xb2.\xda+\xa3Z0\xb7\xab\xe9k$\x99U7\xfca\x9a=\xeb\x0c\'\x93I&gt;u[\x11\x82\'\xdc\x1d\xfd\\7\xfb\x89.\xe1|\xd6\xb9\xb7\x0b0@\xae\xc4\xfb\x1d\xd9\x06\x02\x9f\xf3\x0c\xea*oo\xee\xdf\xca\xdfc\xb4\x14\x0e\x98%\xca\xfe\xf4\xcd\xff5)};\xabM\x83\xdd\x07\xc7\xfbu\xe8\xa2CA\x80R\xac\xe6j\x18\xd7\x07\xbf\x83B\x8c\x92\xa93\x9c\x8c\xcf\xa8\x97-Dk\x83\xeb\xbd\x9b\x82\x13\xf2\xa6/Q?\x05=\xac\xec\xa8O\x0e\x9d\xef.\xfc\x94\xbc\x0b4^\xbe\xbf\xe4\x8d\xf8Q3`\x91\x17O\xa2\x9dA\xa7\xb39\xd8\xdeg&amp;m\xa6x\xfcV\x19\x98\x92\'\x15\xf5\xb2z\x07G)\xdb\xe9\xe1\xf6?\xab\xeaWa\xe0\xdb\xe5;\x8e \xe8\xe8(!\xabjA\xe9\x8c\x1b\xd0\x00\x06\xfcT~-4/r\x91,\x94\xed7\xdb\xe6\xd2\x10\xa2Ei+\x9b2i\x8a\x91e}+B5\x08\x18\xab\xf9&gt;Cky\xbd\x89\xde\xe8x\xed\x01\xe3|\xfc\xd1\xda&lt;\x1e\x06V\x92\'\\\xcb\x00\xb0*\x1c\xa35\x98Xx\xca\x05j\x0e\x04\xbe\x9a\xda\x10\xbd\xbf\x19\\\xae&gt;\x00\xc0?\x9ehi\xf1#\x0c8\x8b\x0b\xcc\x7f\x08\x8b2p\xc6\x81\xc1^\x93n\x1b\x035\x01\xbed!\x05kzRx\xb4U\x9a\xc7\xcc\xab\xe7\xe9e|\xd5\xcbd\n\xc3\xcd.yA\x81K\xf7\xce\xaf_wf\x1c\x88]\x06\xde\xa4{U%N\xdb\x00uBf\x90\x1e\xc1M\xb3c\x00/\xaa7y\x1b\x9a\x9fx\x83\xb3\xfa\xe0\xe0\x1b\x92\x8bG\x94c\x15(c\xc8\xafd\r\xa1\xa1e\xb1\x950f\xcd@\x8epv\x99\xb7\x81\xf9_\x8d\xf1\x8c\xa3\xe2\x91\xc3\xf0m\x0c#\x15J\xf1`c\x1f*h\x0c\x1c\xbaD\xee\x1d\xa6\xbfxl\xf3wq\xbb\x8e1\xc5m\x91\xd5N\x17\xb3\xd7}\xee\xd2|d\xb3\xba\xae\xf2\x9f:8FW\x01}\xc6\xe1\x92dB\x9bZ\x90\xe5B\t\x97\xb2\xcfqJ\xea \n6\xf0\x918\xfa\xd1\x98h\x05\xdc\xdf\xe0#m\xa8\xbbH\xc3\x93 \xf4-IX#\xb8\r)\xa2,\x18q\x1c\x87`\x92\xc6\x01\xcb"}G\r\xa6\x85\x8b\x03.\x1fd\xdf\x18o\xdc,G\x98V\x0c\xb8\x08\xe3\n`\x9d[\xdf&gt;H\xdd\xa4@\xaa#\xce\xb4(\x12\x87\xaf\x9c\xb6&gt;\xd4@\xe6\x17\xfd\xc8\xda|\x86\xae\xa5$\xaa\x80\xa92E3l\xd8{,\xd4\xbb\xb8\x8f\xdf\x10\xfeAN\xbd\x03\x8e\xef\xab\xdb\xc3\xd8kJ\x8fhI\x15\xfa\xd9p\x1b\xd8\xc8\xfd\x1c\x1dL1\x89w-i\x95\xb1\xc4\xbb1\x14\xa5}G\xd6\xb0\x13\x85\x02\x01\x8f\xe8\xbe(-i\xdf\xde\xb1\xcb\xc9\x022\x8e\xbdFs\x03\xb2d\x9a\xeb\x96\x995\x05\xdd\xad\x05P\xe2Z\x83\xda\xf1\xf5h\x8c\x13U.\xbaE3\x82\x11\x0b:S\x12L\xe1(\x8b\xf0@\xe6\xb0b_g"\x83\x96\x17*\xf0\x99\xf9\xa7\xd7\n1\xe8\xb3~\xac\x7f\t}\xa7\xef\xb8\x1c:\xc0f\x8e\xd3\xea\x92\xd4\n}\x1f\xa2zuc{\xa3\xe8c\xc6\x8er\xebZ\xc6|\xafL\x04\xf6\x1d\x87\x06\x8f\xc7\x19F\x80&gt;\xe3*\xa8\xae\x97\xdc5#.9\xba\x10\xac\xd7\xe0}\xeb\xec\x96;\xfc\x1cFq!\x8e\x81\x99\xfe\xb2QvJ\xfc\xb5\xa0\xff\xfa#\x08\xc1\x0b\x91{@1s\xf8it\x05`\xc3a\x8bt\x8b\xf0\xd9\xb1\xd2\xb2\x98\xbf\xfd\x0e\x18a\x86|\xf3\x14\x88\x02\xa0p\xa6uM\x12\xbaI\xa2\xe3\x7f:G\x039Cq\x93\x16\x07v\xff4\x1b\x93\x86r\x81R\xbeR\x95\xb2\xfa\xa7\xb5~\x9e``\xb2S\xfeRF&lt;r\x9b$h\x99D \xb8O\xf9\x13$\xc6\xf6}DKm\x96\xf8\x19\xc2\xbe\xd9\x0e)5x\x07\xbd\xa5\x13\xec\xdb\x9a\x08\x86\xb3\x9e5\xbf\xfdn]i2\x8c/c\x8e\xe6\x9c\x82C\x01s\xcenYY\x83\xf1\xebv\x9c+\xd9\xfa\xbf\x14\xb5\xdajsgb\x14\x06Hy\xb6\xe7\x93^\x16/\x93rJ\xa3\xb8\xea#b\xecq\xae\x95\xf8$O\x9aLp\x9d\xd1\xb5|\x83Z\xfb:\xa3;\xc0\xd5\x97\x13\xde\xd3:\xe5\'\x00\x85\\\xc4\xc7W\xfe/4\xd1\xb8\x99\xfcS\xe81\xcc\xd3&amp;ZK.\\!Q\xbd\x0e\x04\x13\xfc\xd0\xa9\xf5\xe4\x06u\xc3]F\xc64\xd7\xabUfA\xadA\xef\xdb\xda\xa1\x93\x85\xa6xi\xf6k\xe4\x1f\x10O\xb5y\xd1v\xa0\n\x82R\xd7\x02R\xd8\x7fqb\xcc\xbc\x8d\x90\x84\x81a\xd6\xef\xba.h&amp;:O~\x96\x1c\xe0\xc4\xc9X\xd83\xaa\n\xd2\x92\x87Ln\'K\x85F\xa9{\x97\xe7\xa4\x7fv\xd3\xbf\xdc\xb0\xa8\xfcg\x1a\xe4\xe1\xa3\xce6v\x00\x14\x0fq\xb7\x15\x99.\x07\xef\x92m\xc4\x1e\xf3=\xf5a\x12\x8e\x9bE\x16\x06`\xf7\x08\xb2\x15c\xf6\xd52N&amp;\xe2P\x00`\xe2:tx*\xb0\xd5\x83\xb2\x84\xb4m\x94Pr\xe0\xaa\xa5\x8d\x98[I\xc3\xcf\x05N&gt;x\x8a!\x98\x12\x8bJp\xa17&lt;w\x12\xe9\xd9\xcb\xa0\x1e\x0e\xa3|\x91nc|t\xb7x9\xe5\xe9B\x16YO;+&gt;\x1f\x84\xa0s\x94\x8eJ\xc9\x93\xe96\xfb\xbc\xc3F\xa94\xf0\xf6\x1cn\xac]\xee\x07p\x8e\xaf\x1e\x97\xe1\xac6\xbd\xc5\x7f\xa7[\xea)\xe4q\xe3\xe7\x87\x97\xebaW\xd97\xae\x7fX#\xbc&gt;xs\x84\x8f\x9f9nHkzJ\x16\x15\x1e\x0f\xfbk\x9c\xe3;\xff\x94\x92r3\x0e\xf7\x06\xacP\xf2R\xcc\xe4\x9592\xe0\xc0\xee$\xa2NW2\xfe\xa2\x97\xe8\x91\xc0\xe6o\x07EkS\x8a\x81\xa1M\xf9\xac\xa3\x9b&lt;:\x12\xdd\xbb\xbcG\xbe\xb9\xd9\x95\x88e\x8e\xe6=!\xc3K\x98e;\x9e\xef\x95\xcdP\x10\xb6\xf4\x9e_8\xf3\xed.z\x86\xea\xf8\xc9\xd9\xea\x14\xf29o\x8d\xf9\x99\xa6B\x9a{U\x9c4\x9e\xbbs\xb3\x99\x10[I\xe1\x9ckxB\x93]c\x8f9\x8fJ\x95\xf8\x96v\xadZj-\x08\xd4\xb2zYe\x04X\xc0A\x89\x88\x7fq5\x0c\xd4\xc42\xd0\xed\x00\x01\x9a\xcf\x07\xf7\xf2\xcc\xae\x04\x10\x7f\x00\xf8_\x8eA,k~\xd9\xc2\xe9\x85\x88\xe1j\xbelL\xf2}x\xb6\xa6\xd6\xa0\xfag%\xbc:N\x89;=\xb7\rD\xa0\x92K\xc2\x94D\xd9\xc7\xf6\x99\x16\xba\xda/&lt;\x01\xb2\x02\x15`Y\xd2\xab\x81_\xbc\x95o\xc6V\xd3Y2e\x02\x0c-\xe0\xd9\x90\xba_\xd2\x85y\xa7\x88\xf0\xdb"\xea\x8d\xe4i\xb6\x81\x1b\x83l\xea\xe3\xc5E\xe0|B\xab1Q\x1f\xb4\xf3\xc4\xdb\x95\x1a\xc5b1\x1a\xc2*\x1e\xfaME\x12\xd1\xbf\xc7\xee\xa6\t\x8a\x9e8\x8e0\x01\x1d\xe7\x1c7\xc8]\rx\xa2^\x9b\x02\xcfI\x9d\x99\x01\x1e=&lt;O8\xc2\x16\xb1\t\xb3\xc9\x85\x7fR\x8d`p\xca\'\xad\x0e]\xb0\xd2\x1a\x8f-\x1a\xbb\xbfd\xca\xe9S8_\x81\xd4\x9f\xd3H\x15\xfbH\xb5\xa9\x98t\xce\xf5Q\x07\xa2\xc1*5\x83q~\xdf\x18PPi\xe9\x12M\xf4\xd0\xaf^\x174\x11\x0f\xb5\x16]\xa38\n\xb2\xc2\x00z\xda\xad\x7f\x84pY\xf8\x03\x05\x00\x02P\xe0\xbf\x1c[\xca\xaaz\x7f\x9dj\xc9\x8bu\x8a\xb4J\xd8\xabr\x82\xf0\xc5\x89\rz\x04\xbf\xa3^\x07\x80\xae3K\x01\xabi\x10T\xed\xc9\xedS\x13f[8\x90\x16Q\x96\xc3\xd4"\xc1"3\t\x8d\x04/\x8ej\xdc+1\x18\xd38NYF\x91\xe7yg\xa1;\xe4\xc1\xf1&lt;w=v\x15\x87\x1a\xbd\x1d\x90\x1b\xf4J\x11]\x12$\x08\xe7\xc0Y\x03\x08H\xa4\x87\xa8\x14({$#\x07\x0b\xa6\x88\x86\xcc\xb9w\xa3v\x1f\x00$\xb5q\xe4\xd1\xed\x8a\xaf$c*w\xd5\xd7B\xe1 }\xb4\x83\xa17\xe9B\xae\x9f\xd4*;\xdc\x0b\xb3\x9c\xedI\xbe\x18\x1d\xd0(\xc9J&amp;\xa7?\xec\xca\xd9\xd9\xec\xf6\x0fX\xb3&gt;\x8e\xfc/\x16\xab&amp;HJ\xf8\xfb\xdc\x02M\xc2\xcdb\xb8\xff\xf7\x02\xcd:/\xf6\xf9\x14\x8bC\x18\x87\x15\x18N=\xf9&amp;\xb7\xd2\xa5\x91\xb7X[L\xac\xf9\xc4$\n\xba\xf2\xd01\x88\xf7\xc5\xa1\x89\x88\xe7\xe2\xb3\x02\x98\xe7\xccs\x02\xf5\xfc\xbcQ\x0e~\'\xa8\xaf\xc9\xd6 .8\xbb~\xffZ&amp;\xca\xc4\xef\x80I.\x8a\x94d\x9a\xf1\xc8G\x89\x7f2\x8c\x9c\x10P\x80w\xa7\xec\xff\x82\xe0\xf7\xac\x08\xc9[\x94&lt;\xb9q\x1b\x0eu\x02\xbb\xbb\x92\xe7%\xc5X\xc0\x81\x10/L\x17\xefs,T\x97\x0b\x8c\x1e\xfc\x10\xf1\xbe\x95\xc4\x04\x04\x17\xff\x96\x18\xcd\xab\xfb\xaaqF\xdf&amp;h\x9e~\x95\xb6)\xbb\x8c\x1eO650\xae%.\xa0e\xe3~\xc3\xe9/M\xe1\x03\xb2\xdam78\xe2\xf1R\x16\xa2Y\x8cDQ$/\xd8\x9c\xd7H\x0b\xf0\xcb\xaf\x9a\xa06S\xd5\xfed\xb3\xe2p\x041\x99\xdc\xeb\xc6P\x80\xda\x1b\xb8lW\xdf,}\x80Z\x9aI3\xf7\x89\xccK{\xca1\xe9\x01\xaah\x1a\xb8\x01\xe8\xef\x8e\xc4g\xe4A\xde\x95\xd6\\\rG%G{\x1d1$\xc9W\xb0\xb2\x14\x185\xa0\x11\x01\x9de\\Q\xdfZ\xec\xc5\x1c\x97\xb9\x1d\xd8\x1a*\'\xe4f\xeet\x97\x87\x8ax\x9f\x8bM\xca`c\x05\xdc\xfd|\xce\xcau\xdf\xa9\x15\x16\xd3\xb9\xcb\xd2ii\r}\xc9\x11\xbf`\xa7?\xff\x7f\xfc\x99\xc4\xa8\x00`\x8c2@?\x93\xf1\x89\x0c\x8a\xc2t\x93\xc7\x9d\xcf\x91\xd2cM\xbd43\xf3\x84O\xd6A\xb5\x81\x18\xc4}3\xbdu\x8b\xf5\x06\xbe\xe3q]xf\xef\x10R\xd6x&gt;\xda\x0b\xa2\x97j\xb7\x01\xebA\xab\x89\x8e\xf2q\x81V&gt;m\x89Q\x94#G\xd4\xd1]\x0b\xee\xe9\xfc\x9cK\xdf6\xb8\xf3\x0bn\x83\x06ZE\x04FMY\x898r\x8a:\xe5A\xa9\x8b\xea\x98\xbeb\xdeA\xbf\x04Q\t`t\x1a\x1b_\x9bl\x14\xc8\\y\xd9\xc4\xfd\xd8\xbd\r\xcd\xf8\xe0}\x90;\xfe\x82u\x07p\xcb\xf8\xf4/N\xea\xf4c\xd5\xe78\x01\xc4\xc65\xacC\x14\xf1\x1bZ\xf8jHS\x80\xfe\xf2,\xfe@B\x80\x133\x1c\xf3\x07\xa0\x14\xb0\x14\r\x12\x15;\x8e\x00\xeb\xb4\x0cv\x00\\&lt;\xb2"\xbcz&amp;P\xf2\xd9ku\x01\xef\x97!\xc3\xec\xaen\x92\xafv\xd9\x0c\'C\xe4\x83~\x05{\xefs\xc39\x94\r\xe9^\xa2\xa3\xcb\x08\xbbF\x8c\xc2\x8e\x80\x1eI\x8d\xea\xfd\xc3\x16\x14\xfd3h&gt;\xcb~\xe1\nM\xb6mtk5\x0e\xb03k\xac\x01T\x0fe/\x91w\xe1\xf3\r&lt;\x05,,\\\xf0\x86\x0b\xe9!\xe2{]\xf5=s\x13\xfc\xaf#\x1e:\x81"\\@D\x84\x02\xf2f\xbd\xb8\x9biA\xe5\x8d8{\x03t#$v\xe7\r\x99\x04\x98\x00\x0b\xcec\xe9\x0b_\x06\xf8\x81\xe7\xde\x18\xbaZ\xcb"\xb0\x99\xde\x1eb r\xeb\x04\x86\x95F[\xedzt\xa1\xf2\x82\xb1\x0f\xde\xb8\xf3\xa7\x89\xc4Gjbsa\x1a\xd1e\x87\xe68\xea\x19\x18an\xef\xa4\xa8\t\x83\xbb\xdcc\xa0\x15\xebP\x99\xb86\xad\r\x7f\xf0\xeb\x7f\xb6\xad\x0e\xfc\xa6\xa2\xdc\xd8\x03\x8f\x9f\x99\x10.K\xc5\xbc\xbc\xa9k\xc0\xf1\x82Q\x9b@=\xfet\xc5\x15\xd9\xe0$\xfb\xfd\x89l\xd3\xeb\xe8\x1e\xa8&amp;\xa1\xc2}\r\x95kh\xe0o&lt;\x100\xea=]\xde\xd4\x16\x01\xf7\x9b\xd9\x1a\xdd\xe9\x95\x1b\x13\xa7\xbe\xcd\x81\xd2\x98`f\xf69\xcd\xadL]\xc5\x95\xca\x9e_Zju\x85\xd8P\xe9\xe0\x00\x00\x00\x00\x00\x00'</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Guincho Elétrico 3000lb 1361kg Cabo De Aço Para Quadriciclo Jeep - 8x Tech 12v</t>
+          <t>Capa Protetora Colchão Box Casal Padrão Matelado Impermeável</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>78</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>99</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>39% OFF</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/guincho-eletrico-3000lb-1361kg-cabo-de-aco-para-quadriciclo-jeep-8x-tech/p/MLB56697110?pdp_filters=item_id%3AMLB4213164577&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB4213164577&amp;sid=affiliates</t>
+          <t>63% OFF</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_740232-MLA107635997983_022026-AB.webp</t>
+          <t>https://produto.mercadolivre.com.br/MLB-4002919471-capa-protetora-colcho-box-casal-padro-matelado-impermeavel-_JM?searchVariation=183132347992&amp;extra_comm=false#polycard_client=affiliates</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>b'RIFF\x9cQ\x00\x00WEBPVP8 \x90Q\x00\x00\x10\xa8\x01\x9d\x01*\xc0\x01\xc0\x01&gt;m0\x95G\xa4"\xa4\xaa\xa5\xf0\\\x89P\r\x89in1\xc8\x93\xd7&gt;M\x8f\x0b\x9a\x95\xd0\x1er\xaeQ\xbfD\xecW\xf4n\xbc\xdc\r\xfc\xef\x82\xdf\xda\xfbn\xff\x97\xe0o\xeb\xbf\xd5z\nb\xef\xe5w\xf6\xbf".\x07\xf2\x8b\xd8_\xddO\xc0z:M\xd3\xf3\r@xK?\x83\xea\x1b\xfd\x0f\xfc\xbf\xaco~\xcf\xda\xbdD\xfe\xf0{l\xfaE\xfe\xd8\x1f\xfd\xf7\x97@\x80yx\x04\x01s~\x98\xc5\xa3\x03hH\x1b\xdd\x1f-R$\xf1\x99\xaaU\xc9\x05\xeeECZ\x8b\xfd\x19\xd5\xa3\xe3h\xea\xba@\x9aQ\xe2\x8fJ\x90\xdd\x816jt\x80Y\x82\xa6\xc8\xa2\xb6\xadi\xd1\x01\x12\x95\x9e\xb4\x0b\x0f\xaa\xe9\xd1\xc9r&amp;\x92\x08G(Q\xedW\x8d\xef\x1ag8I\x1e\xfb\xc9\xff\x04\xe70\xef\xedk;?\xd1\xfb\x12\xaaJM\xb4\xcb\xf1g\xe2\x86\xda\x9a1\xfbn`Zj\x89\xef\xb7\x11\x8d\x9b\xb8\x02:M2P,~Rj\x06\x9f\xb0\xc3\xf9\xdb\x18/AR\xaef.\x16\xa1pq\x15#\xf6dJ2\xc5`\x90;Hb\xd1\xd5\xa3\x1f\xbfc\x0e\xdcw\xa5\xa5\x9fe\x9f\xf2W\x84 \xdb3\xccc\x1f\x8d\r\xce\xcc\xa3\tj\xaeL\n\x966?Q\xf4Z\x9e\x98\xe3\xfaBF-4,\x90.m)\x1a\x19fI7\xb3\x19K\xd4\x807\x89$\x9e;(0\x7fK\xbe\xbb\xe2\x85QE\x87\x00"\xebm\xeeLa\xf4\xc3\xc5j\xb4\x1e\xed \x03\xf9\x8eya[34\xdd\x9cMU-]b\x19\xf8n\x18`\xb8\x1f\xd5\xd1\x98P7\x10\xa9\xacB\t\xb7\x1c\x89\xc9\xda\xb4\x17Hy\x03/\xdc\xfe\xec\xe8\x81\x02\xa9\x8d\x80N\x00\xd7\x8c\xbf\x93\xf1\x97\xe1c\xb6\x1c\x96O\xcdsp\xa87#\x01\x0c\xbe\xee\xea \x03\xf2\x92G\xe9\xec\xef3C\xa5\xe1};*\xc6q\'\x1c\xca\xce`\xf4\xe3\t\x8a%\xfek=\xe8\x97\xf9\xb4@\xd7f\xaeE\x01\x7f\x9f\xde$\xd0\xf6\x02T\x97]J \xa3a\xb5\x04\xf6-{\x8f\xc5K&amp;U1iQ\x8f\xb8\xd2^A*\xf9\xaa\x05\xd6Dw\xdd\xf6;\x98\xa4\x84*\x08T\xde\x9b\xb5x\x1b(#N\xc5\xa9\x14\xb7x\x13\xe6\x96\xaai]\xb2\xf7\x87\xf1\x97\x0fp\xb3\xd4\x0e\xb9pJs*\xf3^f\xe9\xb4S\x17Bl8\xcbI\x0c&gt;BkE\x91\xd9\x80\x87U\x12\xd5\x05\xc04\x84\xf2\xdd\xd3\xb6\x12\x88C&gt;\tL-\x9e\x95e\xfe|R\x8br\xcd\xb3\xbe\xe7(I\xb8\xc1\xf9u\x9e;}pZ0yq\x80\xe6\xf2\x9fp0\xf8\xde\xbb6\xd5\xea\\IM\xc1\xa6Ns\x02i#\xb2\xc7\x04P:\xe2]\x95_\xac\x1cq\xdb~%\xc2\x144\xc4\xe72*g+G\xe3\xa2ad6\xce\x1e\xc6\xc7X\x16y\x8a\xb3\xbe\xd2\xef\xf8\xdc\xfbCe\x01\t&gt;\xb9\xfafwo?\xdf\xdb\x05\xc1\x83\xff\xb2\xb1\xb4\x16${\xfb\xc2$1\xc2\x16p\xb1s\x1c\xfbZ\xedzo\xf8\x02%_\xa1\x15|*3U\x12\x8b\xc8\x81\nN)\\\x9d\xb4@:v\x9f\x0c\x004q\xfa\xe1\x07\xfc\xd4}%S\x06\x81\x8c\xf0)\xbc\xec/\xcb\x8d\xf9\x98\xe3\r/\xe57\x7fP\xe6V\'\xf7ZPD%\xfa\xde\xfaK\\\'\xd3\xa1~)p\xcfd\xf4\x96l(,$1\xbc\x12&amp;\xd6G1\xa2\xe0\'\x18\x08G\x03\x87\xc7nF"\n\xb8\x06\xdc\x9b\xdbw\xdfO\x12&gt;\x8c7\x9d\xfc\xb2\xab\xb4\x8f\xa2[[\xbcQ?e\xa4&lt;\x82\xda_\xdf\x92\xa5\xdb\x1e[\xbf\xfbzFP\x03\xb90z.-1\xd5HA\x9e\x9e\xbf\x18d\xc2\x7f\xd6pw!h\xc5l\x94\xc7(|\xe5&gt;s\xec\x85\xc2\x8b\x02V\xe2\xe8\x9d\xccn\xb5\xda\xde\xb8b\xb3\x8d\x8d\x05\xe6\x99{/\xdc\xbd\n\x97\xfa\xc6O\xca7\xc9wcj\x93\x18\xaa\xc0\xca\x88\x887D\xe7\x99\xf0\xd1\x05\xd4\xc5rl\x92;\x85\x92\xc5\xd4&lt;\x1c\x18\xd6\xb3\xc2\x00\xa6\xfc\xdc\x84^g\xa3\x98\x80\n\xb0#\x99\xb1[\xe5A~\xe7\x10-\xeb\x98\x06\xf1\x82\xf6\xeaq=~\xb5-\x07\'H\xba\x1e|\n\xb6\xad\xd2\xf9T \x8c\x0b\x1a\x880\xea\xe8\n{\x1a\xc0\xaf\x03\x06Dh-\xa5\x1bT\xc8\xff8\x9b\x91D\xce\xee\x1d\xf0\x13\xe3\x03\xbe\x8a_\rw\xb7\x8dbw%\xba\xf7\x113\x8d\x0fc\x9a\xaa\x81-|M3\x97\xdcZ)\x15\xd8\xdfV\x0e\xd0\xef"\xed\x1f\x9b\x9d{\xf1\x1f\x86\xe4j\x86\xb2\x8b\xa0\xa4\x94\xd1\x04\xfa\xefIl@\xbc\xb3\xd64\x1ef\xf6\xe7\x1d\xfb\xd9\xdb\x08\xe3\x88a\x8fPm$\x18\x97O\xd6~\x1a\x89\xa6\x01\xe3\x1c\xfch\x18\xaf\xa0[\x18\xa5f\xdc\xcb\x137\x8e\x17\xd44R\xaexw\x00$&amp;\x1f,\x0ei\x04X\x0fG\x9b\xed8\xac\xd3\xfdr\xd6\xa4N\xbeu\xfe\xe7\xc8l\x8c\t\xe1\x00*u\xce\x9cF-[\xe0\xc0G\xde\x89\xbb\xa5\xbc\xb3\xdb^\x96\x05\xd5w\xd0\x86\xcf\x9b\x8e\xe3\x05\x00\xf7\xef)\xc2\x19\xed\x16\xf6o\x0c\xcb\xd3?{S\x82\xb4%\xb0\xb5\xf3N\x8dQ\xc8F\x14%Z\xff\xa2\xb9N7\xa4\xd6\x97\xd9\'t\x18\xed{\xc3\xb5\xb7[\xfc\xb7x\x12\xcf4/\xdb*\xae!b\x81\xb6\xcf\\\x03n\x13\x16\xe2";\x93\xc0\xa3\xacWD\xf2\x91\xd0#\x96K\xd5T\x15\x82\x8e\xf7\x0ft\xa9\xff\x0b_\xb9\xa03\xf0C\x02\x0ed\x96\xd6\x9bA=r\x07Dx\x13ZZU\xf9\x123\x91&amp;\x05f\x8f;\x85\t\x97\x04\x14\x1a\xa8\n#.\xa2dhG;\xb5\xce\x8c\x18\x14\n$\xd5\x96P \x1b\xf6\xe5\xa6w\x92Y\xa2&lt;\xe2\xaaz\xc1\xa0\xe6\xd8*]\'\x8f\x13e\x1f|]\x82\xc7\xffe\xa6\x11\xda4v)%\x07\'\xbe\xe6Wyi/\xc4\xc1\x88\xa4\x08U\x0by\x86a\xaf\xab\x1d\x9f7\x18\x97\x98\x9e\xebD%-?\xb2\x00t\x82\x7f&gt;\xde\xfa\x83\\\xb8\xbei\x14\xdd\xfe\xfb\x9a\xa41`M\x91\xb7k\x8b\x1e\x0cEL\xd7\xff\x81\x0f\xc7\xe2C\x01\xd8V\xcd\x00\x9cp\xa7\xde|:\xfdv\xe7\x91F\xfa\xe3\x08L\n\xc5e\xcc\x8eqE]K\xb5H[&lt;@\x8dU\x9e\xb6\xb8\xd8v!7\xf5f\xfa\x86f\x99\xda\x94U\xe2\x10+\xea\xd0\x98_T\x977&amp;\xa6R\x84\xa3vXBs\xd0\x11\x89\xcf\x9a\x16\xcb\xe5\x89\x86\x8b\xc0\x81W\xbe\tb\xca\xd2%\xc0\x9d\xffI\xd9\x00\xce\xcb\xbas\xe6V\xa1&gt;E\xcaA0\x00e\x16\xbc\xe3\n\x14\xbc\x98b\xab\x1f\xf5i\xf7\xa1\xf5\x89\xb5~q\xf2\t^\t_@\xee$FCL\x10\x1c\xda\xb8K|\xebA\xb0\xe7\xbc\xca\xf4\xf4\xb7L\x9fzI\x19A\xb4\n\xe7\xdau(t\x80,?\x05T\xfd\x06\xcc\xa3\x93B`\x8bc\rFDBQn\xc9\xb4\x0f\xd9\xe5Z\xd0\xdc4\xb8\xc9\x12\x92Rk\xdeK=\x91S*Z\x05qO\x99=\xc7Ep\xac\x9eC\x16\xbd$S\xcb*\xbc\xb1O\xff\xe5K.\xc8\xed\xa0\x13\xa4\x8c:\t\xf0&gt;\xafAcn\x96~k\x1d\x05\x05X\xc2\\\xeb\x12\xd2BpLfu\x07\x94\x12\x81\x8e\xdd@\xaa9\xf5pXX]\xfd\xd4f\x06W\xd2;\x8cz\xc7\x88\xca\xda\x0e5\xd4\x06\x9c}](75\xa8x\xdf\xf7KQ\xa8?\x97]m\x85\xae*A\xa1\xa3\x1di\xf4\x05\x91\xc5\xf9#\xcea7\x7f\x94\x96\xec\xbe}\xc5\x11\xee\x7f\xa8u\x04&gt;\xd4\xe0\x0c\x13\x8b\x91\x919`\xf8\x9fr\xc7\x81\r\xc1\x0bOe\t~\xe6m\x11\xaf\xb1\xafM\x176\x8c\x08\xb2?\xfa5\x91e6RI\xed\x96]\x93v,\xf6tt=\xda\xf4\xf4\xb3\xedh\xef\xbeJX&amp;\xed\x15\xc9\x80\x85\x8a.\x87Q\xf6&gt;\xaf\x16jt\xe8jAaD\xb7~\xab\xfb\x85\x80\x8e\xf8N\xa4\xba\xf7\x0e$gV\x88!\xc2 \xc0g\xa7\xe3\xc4\xe9\xfc\xbc\x8e/@\xfbXk\x7f\x94\xc3\x80\xc2\x05\xe5\xc1\x13\xb5\xad\xbf\xbdB\x98\x8d\xd1\xf4\xe2d\xd0\xbe\x1b\xee\x9c\xd3Dm\x97c\'\xf8x\xf1w[`\x1fEvn\x1f=\x90!^\xe6h\x04\x15z:\x90,\xb5\x92\xd9\xf6\x81\xe1\xe5\xdb\xce+\xcdQ\xfc\xd3\x7f\x13pwza;3Z\xdcY\x00G&gt;\x7f)\x07\x19\x98\xc3\\\xed9CQ3V\xec\xa8cY\xdb\xaa\x19\xfa\x9f\xd9\xd4\xbc\x83\xc7\x93\x93j\xe9z\x97N\xfc\xd7\x90\x06z\x9b\x90_\x7f\xc86\x11\x172"\x81\xbf,o\xf2\xc6\xe9%i4\xdf\xa2\x178\x8b{;z&amp;\x8b\xa6\x83s$\x1dM;\x14%\x85k\x12|\xde[|\xd9\x8d\x8f#\xfa}\x9b\xee\x01P\x1a\xed\xa0\xe9l\xcd\xf9\x112\x14g\xfdVo\x80\xff\xd6\x91N\xedp\xc7\x7f\x86LN\x80\xd1^\xd6\x97\xb56\x8b!7b\xbf\xbc\x9c2\x86\x1a\xa3\r\x14C\xba3Y\x90\xc2\xa1t8\x94#\x00\x1d\x0e\xe8[W\xc9\xe1_\x8d\x1f&lt;%\\{\xeb\xefW\xff\xfe\x1d3\xda\xe3V\xf0\xb4\x1d\\\x93\x00\x01\x9f\x8cj\xe8\x13\x80ti\xca\x0cMY~*\xfb\x81\xfb\xe8\xe5\xe1\x0f\xf7\xfeu\x1a\xb7&lt;\x19\x17\xb5\xd6\xa9K\xdb\x0b\x8c!\'\xd9m\xd0\xb7\x88\x8f\xa9\x01\x91\xd4\xf6HB+$\xac\x0e\xc5\xd4\xfe~\xde\x16\x80\xc1\tc+0\x9eiB\xc4V\x87%\xbdi\x15\xb4I\xccS\x109\xe4kW\xf2\x19\xd6C\xc3\xc6;\x8a\xc7\xf0\x0eSJ\x16\x15\xe9\xcc\xfcV(\xeb\x84\x9e\xbfE\x88Vy\xda\xc9~t\xf4t\xd6\xcb\xeaU\xadz\x978\x87\xd1\xdd\x8e\xa6\x97\xeeZ\xe1\r\xecM\xa4&lt;\xef\xb6\xc7\xbf\x87\x1a\x93\xfa\x93\xee\x19$\x1c\xc9\xc4\xbcK\xa2V\xca&gt;~/\xd8\xf68\xc6\xa3\xd1\x17\xb2\x8a\x01t\x90\xc5\xcd\x84\xf3\x0eQ+\xa3{?h\xfe\x9a\xed\x0f\xd8\x9f\xe1\xd2g3W\x81\xfea\x98Y\x9d\xca\x1fm\xe1\x82\xdd\xa2&lt;\xb2F&amp;\x8f\x9d\xfc\x89p\xbf\xc9\xf8\x03\x8a\x9e\xd6\xeb\xd5\x16\r\x97\x12\x062\xea\x00\x05\xd5n\xd8\xb37I\x0b\xdcgZ\x86\xf0l\xfeHe\x94-TP\xad]\x15.c\xeb \xe9\xcb\xb0N)\xf47\xa7\xdf,\x00\xf9x\x13y\xfb\xad\x8f\xf0\xba\x0e5\xe65\xa4\xee\x91\xfe\x13\x17\xf9\x9b\xecn\xda\xde\xf6\xf3\x8bB59\xdc\xe7\xc6W\x9a2X*D\xfei\xe8\x84\x8d|\r\xdd\xff\x9c\xba\xa6\xcd\xf8\xff\xcc\xf3\x96N\x92\xe7\xf1\x84\xdb\xa3\xa1y\x98\xbc\xd4\xc2\x0bXi\xa7\x9e\xbad\x94\xb9,\xa1\xd1\xaa\xdd\x18?{E\xe9\xeeg\x81\xa5oG=\x0e\xea\xdd\x1c4t\x8c\x89rW\x84`#\xba\x8b\x10\xbf\xf3r\x8f\x1eF\xff\xddW\r\\9_\xf8\xc7\x1d\xe1sr\xba\xf2\xb0\xa9(\xf8\x1dw\xcb~\x7fj\xb2\xd2S~\xdd\xbbhU\xc3\xf1~\xaf\x16D\xb8\xd7\x9f\xfb\xc7C\xf4\xe7\xe5\x82\xf8\xb6\x1d\x86\xdf2+\x04\xc0w\xc7Y\x9a\xbc\xf5 T\xd6.\xea\xfbD\xa8-Y\tk0Y7\xbd\xff:\xfb\x13=eIB\x9b\x84\x11@=\xd6\xe2\x1f\x9a\xb9\xbd\xd3\xb7\xec\xcf\xb5\xf5\x8b\xffar6\xe7\xeeb\xaf\xff\xf9\xf6\x1c\x9ebg\x1c_\xb0;55l&lt;eaCn\xe6\xdc\xd1\xf3M\xe5\xad\'\x14\xb3;?\xe7u\xf1=t\x7f\xff\x9c!\xf5n\x87}\xc4`}\xd9\x07\xfd\xees\xacq\x88\xe3\xbb\xdf\xeb\\\xace:\xb9\x96\x83\xee\xdej\xde\x81E\xc2\xcc\xad\xf9\xef\x9eT\x0f_&lt;\x8eyBF\x8bJ\xda\xf8\x8b\xcd&gt;\xdd\x87\xb3\xb5o\xf5\xb37\xaa\xa6\xfe\x15\xac\xc8\xff\x90U\x92KX\x1dm\x93f\xde\xeb\xd7\x1dm)\x9e\x9c\x87\x88\x1a\xcc\xfcIz\xc7\xfd}\xd9\x87Cvyx{\xf2\xb3q\x91\xb4\x19f,\x7f\xff\xecX\x1b\x0c\xd4\xbf"\x7f\xb2\x95T-\xe5\xcf\xc0=\xe3\xd0x\xbd\xa5\xe8;V\x01G\x11&amp;\x84B*\x91\xa9Y\xee\x08VU\xdc\x13yJ~\x9f`\x1f9\xb2n\xd7\xc6\x0e\x19\xa5:~CD1:\xf9\xf6\xa4\xa3\xfa_=\xb2\x00\xae\xff\xdf\xdcu\x91e\x19_\x94#z\x9f\xf7j]W\xcdE\xb1Z\x7f\xc2E\x8a\xf2O\'\xe8R\xea\xb4=\xe6\x1co\xdd9\xf2\xd1\x1c\x7f,.\xf7\xfb\x06\xffw\x08\xf3\xca\xbc\xd6\xean\xfe\x8c2\xb1\x8bE\\\xce/s\xe5\xfc@Ww#,\x86\x9d\t\xca\x959\xfeH\xe9\xd1jhaU\x95\xde\x0c\xeb`2\xe7wM\x83\xde\xc4\x9a\xbc\x80\xcb\x8d\xf7~a?\xff\xc1m\xdc\xaf\x8e\xc5a\xa5\x9f\xeaO\x1e\xd6\xbf\xf8A\xaf\xe5zU\xed\xf9\xf1\x0b8\xb0n\xde\x9a\x99\xe4\xfc\x0e\xe8t\xb4\x9b\xe6\xb3o{Y\x1b\xa0*\x92M\x07\x90\'\xa8^\x15\x97\xe3|\xb4\x0cnW6\xc0\xc4\x9c \xee\x7f4s\xaa8hJ\x96\xfd\xff\xfcX\x7f/Y\xb0~\xa4\xa1\x1d\x94\\;5O\x8ft\xb3[\xf7`\xe7!\xfa6\xce&amp;\x9b.\xef\xab\x12\x98\x86b&amp;Z\xa3$\x7f\xcc\x9d\x0f\xfcO\xdc\x9f\x90\xdb\'\xa8W\x96&gt;\x9f\xff\x88K\xef\xeb\xc9Q\xcd\xae\xd1\x02\x01\xc0\x86\xc0@\x01\xa3\x9b\xc2{\xfa\xbbE&amp;a]\xe1d\x9cY+\x0bC\x06\xc2\x1b\xe9\xeaN\xa8}\x9f#\x80\xab\xde\xbeU\xb8F\x8d8\xee]\xdc\x83\x7f\xe0\xf7BgL\xff\x9d\xaf4\xfb\xd5\x81\xae\x15\xac\xa2\xa7?\x89MU\x87ox\x8a\x1c!\ns\x02\x1e\xc5\x99\xfc\xb5\xb7\xe7}]\x9f\xa8\x06\x1e\x1f{U\x15\xfee\xd2o\xff\xf9\xac\xdf\xf6\x9a\xa6\xf2\x93AE{\xf0vO5\xf0\x13\xfcg\x95\xfe\xf5\x93\x9a\xd5\xd0A\xc3\xe0\xdc8\x00wq\x1a\xe9\x92 \xc5lBN\x15\xf0\x0e\xfcT^\x90\xa7|\x15\x06\xb7\xc9\x1f\xff\xfdm\xddJ\x16\x01\xa7\xf4n\xc9\xff\x17n\x87.\x89\\\xc0)\x07W T\x9d\'\xee\xac@g\xae\xfa\xd5z\xcf\xfb\x1cP\xf1\xcb\x1b\x0e\x00\x00\xfe\xd7\x07\xe9\xfb\x87\x08\xdfmt\x93.\x0e\x98Q\x00\x18\xa2\xd9\xe7\x1e,,/\x8dz\x15y\xb7\xc9N\x04K\xbb\xa8kC\x82h\x8bz\xcf,r\xb3[z\xe0\xff\x8a"\'\x95\x08\x00\xc8\xa4\xd9-\xf4\x81\xebz\xdbh\x0f\xf3\x17E\xa2T\xbf\xa8\xca\xdd\xd5\x93.\xd9\xf0\xfbe\xfd\xa4\xc1\xda\xa3\x15\x04\xc7(\xeb\xa3R\xae*!\x83\xdf\xac\xf9Coh\xd4g\xe3\xf2\xa8{\x93\xdc\x91\xde\x1b\xf0\x93a\xb7;\x91\xf61z\x06s\xab\xb5KP\xce\xfa\x85\xe0\x0e&gt;I\xdf\xa6\xaf\x91\x0ej\x99c!\xc5\xa5\xa5V\x1e \x11\xe2\xbd\xd3\x89oU\xbc\xb8k\xe7x\xfd\xca\x0f\x8f\x88\xda\x96\x86!\xd9ZM2\\\xeb\x89\xdd\x90\xbcw\xb2\xd1=N\xba\xf5%\xfe~a?\xae\x15\xcb\xd3\xa0\xa0!\xa3q\xde\xbe?\x8ec\xc4\xa6\rY9\xad\xfc!\xcd\xa2\xed\xc8C\xa9\xfdW\xf2z\x0b\x9a\x1a"s\xf7 \x84z;\xe5L\xc9\xec\xccKT01y\x9f\xac\xc9\x16\x9c\xe5\xce\xa6k\x0e\xbd\xb53\x9e\xd5\x11RF\xf9zi\xf7qy\x92\xa1\xb1WJ\xf0Mlu\xff4G\xd7f\x13\xcf\xa7[^\xfe.\x90gW\x7f\x89\x00\x05\xb68\x00&amp;w*:\xa8-i\x13\x93\xa7\x0c\xbf\xb7\xad9\x96\xdf\xe6]\x8a\xda\xe6\x8a\x7f\xaa\xac\xf0\xe7\xa8\xa7mq\x12\xae\xf7\xf1\xf7\xc2a*\xd7\xc4R\x8d/\x1a\xa9\xb1\xff\xcd\x89\x88w\x89\xea\xe7\xfds\xd9S6\xf4,\x0c7\xed\xf88\x8b\x073|y\xad\xe6\x05\xfe\x87R\xbaM\x10~}\xba\xf6\xa2\xf1\xce\xd8,I\xec\xd2\x8d\xbd&amp;!j\x8bC_4c\xfc\xf1#\xb9&amp;\xe4\xf3\xe9\xaf\xdf\xbc\x85^[\xf0i~\x93\xc6\xd5\xc3\xec\x9d\x8bn/\xba\xc8\x04R8\xa1\xebO\x16\xa9G0\xec\xf7\xffb\x9f\xf8o\xf5\xef\x7f\xfe\xc4\xb98\xc9\x90\xa8\xcb\xa0C\x9f\xc7dB\xb1\x88\x18@W\xc5\xab\x15\xd5&gt;W\xf8\x9b\xcb\xffoQj7\x98\x90\xc8\x9b\xc5e\xb0\xf2\xb9\xce\xdc\xdc\x14\x8aqIB\x8b\x01B\x01\x05.\xbd\x080\x92\xdb\xde!:ZN\xecQ|x\xa0\xcd\xf4\xa2\xa4P\xc5\x85i\x7fODu\x93\x98v\xcc6?\x89\x9fim\x88\x98S \xb38\xa9=MQ\xc9^\x90\xafa\x06\xe57\x9ddxn5\xbb9y\x88\xb7\xff%\xa4\x8c\xa5\x16.{fB\xb3\n\x91\xdf\xe9\xc4\x01n\xa6\xb8Z\x1b\xbf\xdd\xc0\x81\xc7\x94=D\xb2\xe8\xa7\x8a\xf1\xc0F\xa5\x13\xf6\xb0\xf8?\xfc\x04\x88\x00\x02\x95\x00ng\x8b\xdb\xc8GG[\\\x9e\xd9\xc2\x06\xac\x90oT\xda\x1dhN\x17\x83\xb8\xad\x80\xabgC\xc4V\'\xfe\x9cxI\xa3@\xe9\xa5A\x13\xdd\xf2\xee\xfeoP\xea\xa2\xfb\xc91-\xb3\xa6\x9c\xf3\xd6\xd13\xd7\xa7HI\xff5\xb5\xdf\xbc\x7f\x02F\xe9\xe2\xaf\xc6iL\x7f\x07r=\xd7\xea\xe5\x16\x80\xcd/\x8d\x81\x88,\xc7\x91nG,\xe1\xfd\xd3;\xaf\xf4-x\xf4G-\x8f\x19\x14\xb3\xdb\xec\xdb\xe3\x9a\xc4\xf4[\xbd_\xd9y8(\xb2\xa5\xe2\xd7\xf2\x0c\xafA\xf0*\xc2\xf4X\x8b\xff\x9en/\xf3A\x14\x0f8np\xcb\x19\xaa(\x01\t\xdb\xf7)\x01\x86\xcb\xe7\xcf\x98\xaa\xe0\xe2\xbb\xba\xb8|\xd2\xecm\t!\xecJ\x9a{0\xb6=\xed\xben/\x16/\x0b\xd3\xad\xbe\x17w\x00\xd5r\xea\xee\x10\x11c\xdbq\xdd\x19\xce\xdd\xfa|&amp;\xca\x9f\xfa\xbcD+\x17\xa2SL\xee\x0e\x9b"(\xf3\xd4s\'\xa4\xe4\x19\xa8\xd9\xbb\x9c\x06\x10*\xf9\x8d\xd6\xc4\xc8W\xcb\x065X\x04\xe2e\x99F4%9\xc8(!\xe3\xddD\xc7[\x89s\xf7\xa6u\xc3\xc6@\x07\xea\xbd&gt;\xb2e\xd1\xbb\x80s\xa7\x19\xa0\x05\xdc\xb1\xd1M:\x07\x89IHa=\xd4\xe9\x12S\xac\x19T@\xd1\x0c6Q\xaf\x008\x1e5\xc9\x15\x82DJH\x80*\xaf\x0e\xe7\x94\xd7\xf5\x91?\xfa``I[\xfb&amp;ns\xc1p\xab\xf5u9\x9a\xc7\xf00\x11\x0cl\x0b)\x18\xb0\xee0\n\x142\x1fM\xc4@MQ\x9e\xfaa\x93\x06I\xab\x1a\x8b\xb5\xf2\xdev\xc8\xa4\xec\x14\x8f_X\xb6\xb7\xea\xa8\xfc\xc2-w\xe9\x10\xfe\xa3\xcf&gt;\xf6\x8a`\xdc\xe1\xf7\xf1\xc1\x8d\xe6\x9a\x81\xf1\xe7\xa2]\x85?\x90\xa1%\xa4&gt;?\xeb\x87\xa1G\x9d\xff6\xf8\xf4R\x0e\xc6X\xa5\xd9\xbd\x06\x00\x1f\xed\x98,&amp;\x0b\'\x11\x80\x00\xb1\x03 F\x82 ,\xdf\xca\xf6\x04\xe9\x8d6)\xc0\xc9+q\xf5I\'\xe8\x13\x85e\xe3\x87\xc9\xdb\xc5y\x05\xc0E\\\xff8"\xe6\xe7[\x10\xbe\x9d.\xa9\xe1J3Ca\x01{te\xd0\x1e\x18\x12\x08{\xd1\xdf\xad"A\x18\xcf\x84\x99\xa4(\xec}}v{\x95\xcdXD\x16\xda\xdb\x1cl\xfc\x0c\x8e/\xf3\xe2\xe2\x14\xad\xb5\xbd\x02\xf6\x19\xa7tf\xffb\xe3\xbaQ\xe1`6\xd5\x17)\xcc\x1f\xae[&gt;?\xa6\x10\xc5q[\xeeA\xc3\xf3\xbaj\x86PA(\xcb\xeex\xda\xac\xfdE\x8a|\x81\x96\xdf\xe0\xce\x95*\xc5J\xc8\x13\xca\xfcG\xe8\xe0\xabo\x94\x06&amp;o\x93\x9b\xea\xf9\x9d\x94\xed\xd4\'\x8c\xd2\xf6\xd1p\x7fc\x17\xc13B~P\x10\xb7qi4(\x01\xc4_\xad\xa4\x1f\\r\x17\xf6\x06\x03#\xbb\xf1?\xc469\xb0\xbd\x9a\xfc\x8b\xf9:\x1b\x80\x98\x12(\x80\xd8.\xef@\xd2\xe2\x80\xaey\xa7m\xeb|N\xf0\xc7g\x12o\xd8i\x03\x01\x056\xf5W\xdf\r4\x0b\xac\xf35*\xec_\xee\x87\x9b\x98\x1cN\xebd\x19\x93\xb9&gt;\xf3-1\xce{nU\xb3\x1d\x0c\xbe\xf8H\xb6}Y8|,\xab\tr\xc2f\x92{\xdc\xc6NB5t\x02\x13\xe9f\x0c\x96\xbe~\xd6\x97\xccX\x00K\xe74\xdd}T\x91\x17\x95\xd6\xb1\xe8\xfe\x04G\x8c%\x836\x02\\o\x9a\xf0n\x03\x96\x05\x8f\xdf\x8bC\x88\xf7R\xbe\x8e?\x95\x1eF\xd79\x8e\x16\xae\x1b\xa2\xecO\x9c\x93, \x11\x81\x04\xba;\x18\xd1\xd8\xbb\xa96sI\xe3\xa6&lt;\xbf\xbb\xc0^\xf0gW\xe3\xea\xb7\x1bL\x1f\x1c6\x9f(\xce\xa4a0\xd9\xdfE\xcb\x1f\xd2\xccT\x9e\xf4\xfbxS\xa1\x03T\x89\x83\x16\xe8\xc2\xfbK-\xf3\xb5\xca\xc6\'\xb9!\x9cNt4\xec\xc3\x8e5\xa5\x0f\x17V\xb0\xcc\x7fZ\x04\xc8\x0f\xeefvL\x19\xefJ\x9e\x85\x9a/j\xdc&amp;\x8c\x01\xbe\xb7b;&lt;4SX\x8c&amp;`\xfc\x86\x1a\xa4\xf1\xb6\xd2\x19\xdb\xe3!\xe4\xe6\x87\xfe)\xc6\x84\xad\xd4\x1b_\'\xfa\x9cuo\xb72\xc1\xb0;\xe2\xcd7\x85\x95_\xb3\xea0"GC\x1e\xdf\x9b%tD\xad|4\x82k!\t\x8c\x9f\x97h\xbf\x81a\x99\x8e\xe5\xf8\xc1\xb1@\xaa\xc4#\xd1&amp;+\xce\xaa}\x81|\x1cu\x0cTwE\x07[\xa5:M&lt;\xc8=\xe3\xa5\x85\xdb\xf0\xe1\xb8ptgmv7\xb0\x9cAQ0\x04\x8f\x9e\x1a\x9e\xb5\x04\xc0\xb4\x1b\xb0.D50\xb5\x9f2\xbae\xd8=\xcc\xc1\xfd\x81\x88\x11e\xfb\x93u\xd8\xfa\xb1\r\xa8\xc1\xd2\x1e\xac\x9f\x16bY_\x17\xfe\xb1P\x98\x85\x99Rz$/\xe9\x19\xd7_d(\xea.[i\xa8\xb7k\xd1\xc6\x94\x85j\xfb\xadN#\xc8\x0b\x1e\xf3\x99\x1c\x13\xc4\x98/\xc5\xf1&lt;\xc9\xc5[\xeb&amp;%\xf8\x86\xd2NoS@3~I8\x91\x10\xe6\xd0Mw_\x05UO\x87\x1d\xeb\x13\xf5\xa4\x11\xf6\x93\xd4\xe65d\xa6\x11*\x89\xdb\xa6\xb6\x7f\xf80\x9bPm\xb3\xd3h\xcf\xaf\x10%\x14`\x03I\xf1\xcb\x8d\x10\xb5\xb5\'$\x99\xe2d !\xf6\t&gt;VR\xab\xcd\x85\x04\x8e\xb6\x02\xe5\xfa\xe3\x89\x80\xa88\x0e69(@qi\x89\xbf&amp;\xf4\xbbyO\xfdz\xe9^`\x90.\x7fk\xe8\x05fx\xf6\x07\x7f`\x06\x95\'5qu\xb5\x87\xee?\xf6\xdbI8{][\x0fO\x8e\x8d\x1a\xae}\x88&lt;\x07_Kk)\xb0\xbd\x04b\x94\x1a]\xcb\xa4 \xbb\x7f\x9e\xa2\xe0O.l\x1dz\xe7\x85\x8aE\xecq\xf5Zf\xb5\x08\xea\xb0\x05\xa9\xe4\x14\x02\x93\n\x0cIS\xd4\x1aj\x17\xc1\xd2\\"\xb4\xc1\xfe\xcb\x8c\xd3@\xc9hB\x95S\x1d\x14\x8e4@\xb1F\x8bW\xb1A\x9e Wr\xed\xce\xf7p&lt;\xaf\xff\xb0\xe6\xca\xc5J\xac\x87\x08\xee\xb2_\xe4\x07KG{(\xa2\xa5\xd1\xb2O\xa9S\xffF\xe6\xcbT\x15\xc2Z\xe2F\xd5\t\xa0=w\xe2}\x01\xb6\x981\xa7\xe2\x12\x06\xe6\xb0A]\xff\xc5\x14\xb6\xc7\x9ab=\xa5\xb2\xe1\x17\xaf\xe9\x94\x0f\xb4x.\x93\x9c\xa2\xa6\xd5\xd5\x9f\xe6\xc9[\xcd\xe0\x18-\xc7\xee\x87f7\xe2/\x9e\xca"\x04&gt;\x03e\xf62\x88\xe8\xdd\xd5:\x0bY\'\x96\x94{\xd9\xbb\x90\xd9\x80\x9aY\x02\xc2\xf9%\x19Q\xd9\xaf\x05-\xac\xb0`D\xdb\xae\xe8??\xfb\xe2\xfe\x0b%\xee\x84\xa8&amp;QQ\x11\xf9\x12\xa7:\x16\x8f]fI\xe7\xcf\xb1G\xcc{sb\x8aSD,#\x83\x11Xd!J\x84O\xa6\x87\xa2=\xca\t\xe45;}\xf2&amp;\xdcj\xc1\xcf\x01%D`J\xaeI\xecj\x82\xdc}\x004\xf1Bz\xf1\x92\xed\xebV\'`e\x10^z\x96h\xfc7\x9fB\xd1Eu\x80\x97\xb2\x99/j\xa2\x01\x13Z\x7f\xdb\xb2\x92\xe5O\xd8\x94\x99g\xa20)\xc3\x90\xab\xe4\xac\xbdp\xba*M\xfdG\xf6\xcfo\xde\xf9\xa2%Q=\xf441\xd0;\n\xd9\x9a\xc0&lt;i\x9b\xd1v\xf4\x12f\x92\xe7\xcft\xe4j\xed\xfa\x89^o\x11\xcc\xb62\xadr\x0c\xb8\xcd\x15\xd4V\x94\xfd\xb2$wA\x8dYT.\xfd\xab\xda\xa5s\xf1#\x98\xf3o3\x98\xfc\x1cs\x03\xae\xa4\xf4\xc8# \xa6\xe6\x99\xa1\xbf\\\xdb\xa2\xa5\t6\x8d\x07\x9d\t\x96\xd7\x91\xf5\xb5\xa0\x98\x83\xf6\xb8\xa5\x04\x81\xb9Y\x1b\x95(M\xb9\xa8x\x8dF\x9f\x12\xc7\xb8\x1f\x91\xc9\x7f\xa4\xb7,\x94\xc2\x14\x9c\x93S\x9d\xa7RC\x93;\xa5*C\xd7\x91\xe9\xbf\x0e\xfd\x82\n\xc0\xf1\x1a\x0cia\xb8\x03~\x89\xf8\x9c4\xe0\xc5\x0bs\x03\xfa\x15+\xb9M\x88~\x16\x88\xd7\xcc\xa0o\xbb@\xde_#\x9bf\xcc\x8d\xd6d\x00F\xa7\xa4\'\xfd\xef*\x17]#_\xcde`.\xe9\xea\xa1\x0ey\xff:\xf3_`\xe7o(\x02n\x82\x86E&gt; \xc8\xcf\x03.[\x9c\'\xa1\xcdqSs\x9a\xe3 \xed\x90=.!\xb9\xcd\xad\xb2.M(\xb6\xbf\x87W\x9aEr|O\x18K\xa8v\xf3;\x04/\x95|\xac(\xe5S\xf5:\xe9&lt;}\xba%\xf5}\xee\xbaG\x83\xed9\n J5x&lt;\x00j?\xe4\x98\xef\x11\x94\x96\x9e\x07\xa8\xf2\x93t|QA\xe7\xbf\xfb\xc4?\xe4\x1a\xfdy\xa5\xb8\']\xd6\x87\xa9*g\xfa\xc7\xb9r\xec\x86)maU\x1b\x1c\x10\xf5l\xe4\xc7uc(6\x01\xab\x9f"\x88\xdd\x95n7\x05\x1e\xdb\x1f\x97\tD3p\x1b\x9b\x8e\xd3tg\x97\xf3\xb5\x8d\x98\x8a\x04\x04\xe7\x14w\xe1\x8f\x9f\xe5\xf2\x02\xef0\xac\x92\xfb\xa2\x80R\xf0/\xa6m\xd2\x05\r6i\x85\xdc9+\xdd\x86\xb0s-0\xb1\x9a]\xcbF\x88t\xd0\xfe\'9\x8c\x90\x15\xd6@9R\x1c\xe8\xd2\x9b\x8b&gt;\xbf\xe3\x8dS8\xb6UM&lt;\x13\x05\xd0\x1b\t\xbd\xa0r\xf8w\xd2\x03,\xb7\x9b1\xfcs\x8f~\x0b\x1fy\xa4K\xf7\xc1\xda\xfe\x7fs^(\xbb\x1c\xef\xc8\xfc2\xbc\xf0&amp;\xa5D4\x03?O\xb4\xb4\x18\xce\xe0u%\x97\x1a9\xac\xf0.\xaa+\xd3\xac\x1c\x1f\xa2\x06\x19\ta\xea0\xe2\x1d0\x06)\xe6\xb1\xb2\xb2\xe3Z\xfb\x17\n\x17O\xa2w\xb9\x85kS7\xadp\x92IK\xe9\x96\xd7\xea\xca\xec\x12C\xad\xd4\xe6\xcb6\x13\xfc\xb0:\xe3g\xd9%2H\\-[\\e\xaf_\x9e%\xa8\xc1}\xf4\x10\x16\x10(c\xda\xfa\x89s\x98\xe8\xfb\x17\x87E\xf6}^J,\xce\x8c\x01\x8a\xaeF(~K(M!\xefZV\xec\x92.&amp;\xf3&lt;\xbe\xce_h\x14\x02\xbaa\xde\x1d\xab\xa9\xa3\x17\x81P\xe6E,B\xb48JN}\xe3\x0c\xb0\x9f\x9f\xa3\xf7\xebk\xba6y\x15b\xf4\x94C\x1d\xf5\x9c\xccm\x7f\x9b\xe88\x89)I\xe8\'\x7f5\x8c\x17\x03x\xd5\x7f}\x1f\xfb\xb3u\x95\xbb\x90\xc5\xa8\xf0\x1aw\xf7\x14\x88\x8b\x12"\'\xab!\xfesb\xfe\xfeTvQ\xc0x\x0e\r\x8d\x189\x18\x88\x81\x08\xc2\x978k\xe66\xd6y\xe3\xb3\xcaX\xbdw\xfa\xce\x95e\xcbWIn\xb3\xeb\x815\xa5w\xc4\xe9\xd5Z\xc1\x81A\xd6\x98\x1aV\x0e*\xde-+WG\x89\x0e\xd9\xe7\x95\x9c\xa7bBr\xc9G\xdb")Y\xf5\xf86sm]\x02l2#y\xbd/\xd6$,?g\xffW\xfbl\xc4\x98\x0c\x99\xe9\xd5\xc1\x8c\n\xf6\x95\xa5\xb4sF\x9e\xfe\xec\xbbb\xd7_\xc0]H\xe5&lt;y\xca!\x07$\x12\x1fy\xff\t/&lt;\xbd\x0ea\x87\x1f\xc3\x97\xc6\xc1D\xa0T\xba+\x95\xe8\xda(\xa2\xcb\xc8S`\xc4\xf1\x10\xfa:\xd6\xd0\xe3\x9729gm\x9a\x93c\xafkf\xc9+\xc5\x10}^}\xb9\xa59]\x93\xa0\xe7~y#\x9e\x81$\xc2\xf1DS\x86\x99\xaf,#\xf1\xfa\xd8\xfb\xdfC53\xdan7\xf8m%\x17M\r;^\xfd)\x0b\xa3j\xa0WV5\x0c\xa9+)8\xd6\xf5\x9ao\x9e\x0b\xc2\x8c\xb4Pmay\xb0\xa3}f\xfd%b\x0f\xec\xfe\x8f\xde\xfd0}I"\x1a\xfct\xefS\xcfV|\xe9Vv\xf6\xec.\xb9\xc0]P\xe3\xd4{@2[E\x96\xff\xbf\xd7\xf0\x12\xef-\x0b\x82Hp#\xd9\xf5\xb1\x8d\xc8\x13\x0c\x917\x87\x07\xba\xc5\xf7\xc6g@q\xc0\xa3{b&amp;\xe3\xfe0\xa4\xdf\x93\xe3\xd7iE\xc1\x08\x1c\xb0\xbf\xaa\xca\x0fS\x0cQC\x01&amp;c\xe8.\xc1\xa3o\x18\xad\x86\x06\x1d`\xc1\xc7z|\xe8l\x8c+\xc6\xca~\x17\x88$\xc6\xf2\xcdA\xb5\x050\xb4\xb7\xb5\xf2\x050q\xfcX"\xe3#\x8fo9#h\x80\xd3\x9e\r\xe7\xa3\x19\xf8\xa0^\x0f\x07\x13\xcae\x12\x92\xb8\x19f\x85v\xe2q\x06\x18\xdc\x03M\xdf 8\xa9\xc5B\xfe\xe5%\xbc\xf5&amp;\x02\xeb8\xf0H%\x078\xf7W\xa1\xac`\x12\xfb\rSNj\x0c\xbctsf\x08k=\xd0\xcf\xfa\x16E2\x95\x8d\xab\x89\x08Az\xd9\xa6^d\xd9\xb0\x00z}t\x14\xb0}\xe1\x91W7?=\xd1`\x92&lt;\x9agY\xc0\x02a\xdf\xa5pw\x94Z1&gt;\xad\xc6\x94\xfe\xde\x085\x88\x06\xc1\xc3\xc48\xf6*0\xd8?Cx\x1c\t\xfe\xf9\x90\x8b\xe3\x13a?dc\x81\x83\xe6\xa7U\xc0 \x07\xe9\xc0\x9b\xc1\xd52\xc9c\xabU\x93\x9c\x0f\xb7\x05\xa7lk\x96N\x14\x05o\r\xc1=\xea3F\xa1\x0b\xce\xbbW\xfc_A\xa3\xf6q\xa0\x8f\x0b*\xac\xbe\x92\xd9\xd8\xaf\x9f}@,\x03k\xb1E\r&lt;|\x91\x87TL\xf6\xdf\xbe\xe6\xa7\xa3+\x80L\xd2\xdc\xfb\x9b\xd9\xb1\x98\x0b\xa0|\x1bq\xd1\xbar9b\x13\xc1XU\x07J\xf8\xcd\xefX\xfa\xf9\x91\x19\x8e\x99\x0e\x14\x00\x04\xa4{\xc3\xf7\x16\xdc\xb7\x9f\xd7O\x85U&lt;\xa0\xd3\xff\x12\x87jD\xcc]pRar|\x14\xc3\x02+2\x1b\x9d\xa5\x19\xcb\xc5\xb0\x98\x17\xf9\xeeg\xc2\x00a\xc6\xf5\x81\xf4\xe1\x13?\xd6yHOH\xf5\xe55\xday\xa2\xa7\xacK\x17S\x8b\xb3r\x1a\x17\r\xf6 \x16\xa6\xe6\xa9\xa2_TG\xa0\xc0Mwm\xa7\x1c\xc1B\x0c\xe2\xd4\xd9N\x87w\x84\xfb\xcd\xd5\xd3)\x91&amp;\x1a\x08\xd7\xcc\x9a\\\x85\x825\xf2G8\x07K\xd3\xea\xed\x9eH\x86\xdf\xca\xb7\xb2\xa7\xcf.\xba\t@\xdf\x14TX\x90(\xe0\xc2\xfd\xaa\xf67\x86\x8d\xaa\x90\\\x96\xd6\x169\xde\xaf\xc2u\x92\xa0\x89\x9c\xa6W.\x1e\x958fA\xd0\xf3g\x0fjZ\x7fW\xe0\xd1\x88\x03\xfen\xae#\x93\x11\xa2/F\n\x86\xb0\xba\xd8\x06@\xea\xf4\x0b\x81UZ\xc0J)Q\x8c\xcb&lt;\x00\xaa\xd7\xa4V\xd7\xdaH\xc3.P\x13NtK\xd3\x04Y\x9d\xcd\xe7\x99\xa2\xd3\xd2\x87^\xe0\x9d\xdf\xddi\x1e\x94\x99F\xeb\xe4\x18\x10P\x0f\x90k\t\x08B\xae\xe12\x7f\xf2\x0e\xc8\x97\x90\xf9\xe8\xa3*\xc7\xac\x1c\x9e^q\xa4r\x15\xdaJ\xcc\x9b\xed\xc8\xa5\xfb\xc9\n\xc8\x85Ga \xbbRq\x92\x97Q!\xcf\x11\x14\xd1z\xf8\x9b\x1c\xc9r\x1a\xc7\x05\x1c\x12m\xfe\x8f\xde\x96\x99\x11\x91\x8f|\x02\xb6\x11\x19\xb2\xb72\x0e\x166\xed\x07uG\xa6\xb4p\xd2;\x83t\xba\x9b8\ru\'6i\xe2\xa3CZ\rH\xb8\xc4\x04\xc0\xd5\xd90\xfe\xa6\x08:\x08\xfd/P2o1\xbf\xde\xef$\xff\xd7\xb6\xfaN\xb0"\xc26\x00\rV\t\xaaz\xad\xaf:\xc9X\x8a\x02\x11e\xee\xbci\x9b\x8dC}\xe1\x14\xff\xbc\xb1\x86\x84\x89K\xcb\x9aT@%\xf7\x8f\'\xa9\xab\xc4P\xf9\x83/g,\x99\x96\xab\xfa\\\x99\xcf}\xb9\xbbuT\xb5\xb5E\xb0\xe4\x86vl\x93\x88m\xde\xe3\x14\x9c\xb9\xddE\xb3\xc0\xb9_G\x97\xdf\xfc\xdc\xd0\xf9PN\xc2\xc1\x1bQ\xddH\x8c\xed\xf6\x90P`\x92 \xc8\x9a\xd8\x88\xaf\xc1=\xc7\xdbQ\x8b\x0fG\x03\xdd\x8c\xcc\xc8\xec\xb70~\xfd\xe4G\xcb\xcb\xe2\x8a\x0fX\r\x89\x05FLa\x9c_;X\xa1\xaf\xc4&gt;\xb5\xe3\xa4\xf5_ON\xdc\x0e\x04\x7f\xc5\xcd*1\t\x95\xdaY\x03x\x11\xa7\xd9\xe3Da4\xf6\xf8\x1e\xa0\x90\xf6\xe3(\xe1NG\xafi(u\xf9 \xaf\x82\xf7\xe7\x96\xf0\xb2\xf2\x0c\x9a\x118\xc9R^\xc8\xdf\x92X\x9ffb\n\xc7&lt;\x9f\xa2\xfd\x8a\x96U\x92\x82\xf3{A\'\x7f\xbc\xc8\x08\xc7\x14\xb4\xa5\xe3/\xb6\x04\xef\xbe\x87T\xac\xa2\xeee\xad\x97h\x10\xf8\xf6\x96\x81\xd2\xfc\xbc$\x94\x08\xde\x8f;\x93\xdd\x05v\t\xc3\xf0|\x1f+\xcc\x8c\xfc\xd6 \xc6`\\\xaa\x14\xa8\xcfE\x9f?\xad\xe5bd\xa1\xe1\xc2R\xc2~\xd13^d7\xcb\xfcA\x80\x96\xc1\x1c\xea\xfb\xb9XV\x9cWD\xc9\xac\xe6\x0bYh\xd0\x0bM^\xa9\xe4A\xca\xe7&amp;\x89\xb9\x92\xa1\x88\xc3K\xc9_\x9c\x03\x8au?\x96\xe8\xf5\xa1Y\xe0-\'\x02\xf2\xd9/\xf9\xae\xd0\x0fcE:\x14\xe9\xe8\xfa\xbcn\x84~6\xc5\xb2K\xfdA\xa7\xe5\x0f\x0c\x07`\xaf\xe1\xe3\x96\x0fR%I\xb24\xdff\xcd\x92L\xa5\xe0\xa5\xaay\xd3\x10\xd2dI\xffj\xa0\x9f\xdd\xf7\x0f&gt;\x89)tk%\xa4\x9e\xf2ad\x11g\xc3Vk~\xec\xa6\xd0n&amp;L\x0c\xc4E\x1bS\x86"g\x8es\x0e\x86\x1by\xd4\x9e\x057@\x10\xd0\x11\x84O$:\xa9\x94\r\xddvz\x95\xffdwgf;\xca\r\x83\xbb\xfe\x94\nv\xadE\xb9\x1f\xcei;c\xccC]\x0b\xd4\x10[P\xcd]\xb9q\xe4\x1a\x8dy\x89@\x8cF\xa4\xcct\x9e1\x06\x0e\xa2\xd1rE\x98ws\x9b\xd2V\xab\x16\x14:\xf84\xf6\xa1\xbb\xbe?u\x95\x06\x13\x82\x8b#u\xc5\xa3\x02\x83\xaeh\xed\x00\xa18T\xf3\x07\x16\xb8\r\xaa\xb7,{-&gt;0m"\xd3\xba\x89o"\xee6\xc4\xb9LC\xe2\xd2L\xc3\xe9.\xb2\x82\xe6\xb6M\xadf@\xa3\x9eVy\x06#Xl\x86\xc9\x16\xb4\x07\x11\xc21\xc0\xec\x13\x1e\\\x96\xb5\x17t\xc81\x15R\xf6\xe9\n\x836\xd7\x1b\xccH\xaa\xd3\xd7\xb5M\xac\xac\x0c\xd7U\xb1d\x86\xdbn\xd1\x88H\xba\xeb2\'\x8aJ\xa5\x9a\xf5\x97H\xd1\xcf6\xa2\xcf^\x95\xf2\x1d\x84\x13\xc6%\xb5\x85\x81\xed\xb9\xb7\xaa\xae\x8f\x9b\x95\xb3\xd6\x85\x1cF\n\x99c\xb5\xea\xcf\x04)n\xe5l\x15\xfd0\xeeQ\x7f\x8d.\xa03\xaf\xb9\x12\xfbK\xcb\xbf\x15\xe6X\xab\n\xf4\x19i\xab\xb1\x98`\x06\xa6\xf8\xb5\xb4\x9c1\x99\r\x05\xf3\x81\xbe\xa3\x0b\x86\x1dQ\xb5\xf4\xe5\xee\\BbSj\x9ai\x05C\xbb4~_\x97"\xb7\xa7\xd2(\xf5\xa7\xce\xe0\x87\xf0A\x8a_\x8d\x99\x15\xdb;\x07\xbd\xdb\xc6\xa6\xc5\xe4\xc65\xda!\x81\xdbD.\xb4\xc0\x87\x1e\xea]\xfeK\x1e\xa1\xf0Ss\xe8\x1bK\xce9\xefP\xe8\xd3\xf7\xa3\x8b\xca6\xd6\x03`:\xe5\xe1\x8e\xbe\x8bqvK*\xc4\xdaw\xb7\xd2\x18C\xc1h*)K3ZJ$|^$\x19L\x15\xd5o\x15l$6\xb1\x9ax\xed\x8a\x18\r%\xa6\xf7\xf8\xd5\xc3q\xfenHw\x01\x0c\xbe\xf5\xd7\xf2\xb2\xfc\xbc\xa9\x10H\x18\x1d\x9b\r\x95\xab\xc8q\xfc"/\x0cL\x81P\xe0\xa46us\x1d\x18c\xa1\xf7h\x08\xaalR\xdc\xf6\x80,\x7f\x12\xaf\x0b3\x8fH\xbfO\x1e\xf4}\xd9+\x88w\xf0\xf0Mr\xea[\xf3=Ra\xd1$\x08Xv.\xd6e?\xde\xe0\rX\x92\xe8\xd6\xac\x7f\x16\x8b\x99\xbf\xab\xa7\xe46\xc8\x1f}\x85\xc1\x92/\x9b.\x96\x96\xd6\x1e\x96\xfbo\xdb\xd2\x19\xa3\xbft\x17\x19lQ\xd9\xcd|_\x9b\xfd\xe3n\xef/Z`C\x97\x00i-@;|\xb4y/\xe5\xb8\xd5J4\xc8B\xa1]&gt;\xa1\xed\xb1\xa2 !4R_\xe9!\xd8\x01R\xfaE\xd9\xf2\xb0\xc1\xbf\x98\xfb#\xda\x15\x02\x88\xd4\xfa(!6\x1cs\x83\xfdp\x91:#\xe6&amp;\xbd}\x0c0nO\x13s\xfe\xa1\xfd\x93\xb2Ca\x1b\x0c*)\xb9\xca2\x1dig\xa7\xf3\xd3\x87\xdd\x82\xf4N\xdf\x90\xe9\x11\x16\xa9Wy\xf5\x06\'\x80({\xe5\x9b\xf4\xb2\x0f\xd8\xb5[\x8d\xcb\xe8\x8f\x9d\xc7D!D\xce\x87=\xae\xb1\x00\xc1\xe1\xa1\xc3\x03\x04v\x17\xccZ\x94}\xc1\xaf \xfc\x12[\x030\xbb\x08I\xf2\x84y\xcc\x03\xdd\x82F}\xf5&gt;\xe7\xcb\xc8\x9b"\xb5]\xa5\n\x1d&gt;\xb0k\x11\x10\xc9\xa4f\xa0\x96\xef\x02\xd4d\xec;E0H]p\xc0\r\x8be\xe5Z)h)n\x87\x1c4\xf7L\xfe-&gt;\xc1\xaa\x14\xf4\xd4Z\xaa\x9b\x90\xd0\x10&gt;U\x9b\xd2|I\x0c(\xc0_k\xb9l6:\xe58\xdbw\x9b\x9b\xac\x8b\xf1T\x87bW3\x1a\xee\x06\x89\xbdl\xf7\x93\x83?e\x90E\x82\x0bP\xf4\x0e\x98\xca9,\x12\xf7\xf3\x16:\x9f9\xffp\xb0|\xc3\xc4\x0b\xb0j\xa1\x06\xe2\xd0\x00\x8eB\xccM\x01\xa8cV}8\xef\x18\xbc\xe2Gu\xdc$\x7f\x98M\xb9\x8a\xd1P\x02&amp;\x07\xcf\xfb\xafP\x8f`\xa0lM C\xb2\xf9\x0c\xafea# \xe8\xf2\x8aV\xa3$\'\xa2\xfdE\x91~\xf7X\xca\x10\x96\x15\xe0a\x1e9f\x1f%\x843t\xb1FY.L\x0b\xef\x18`\xaf\xbd\xd0\xc4\xb4\xa0\x81+\x99\x96\xae\x16\x04\x13C\xee \xb8\x1b\xc3\xc6\xb8\xc4\xc6\x94\xbc]\xbbq\xaf\x14\xb6\x1a6_p\x12\xcb\x9c{\xf6\xaa\xf6\xc8\x9a\x9d9^\xb9Y\xe4qA7\xb1\x8e\x0b\xd63\xe15\xce\xc1\xf3\x8dV8\'\xc4\x00p\x8d}y\x91\x95\x8a\xb9\t\xab\x0cO\x00\xf2XB.G\x8d\xf0"\xf0\xf8&lt;\xf0\x8cg\xd5\x86\x88\xe6\xa4\x89\r\xf1\x94\'\x86]D\x08\xea\xe5\xd9#\x86\x88\xe69\x04\x88*y\xd7C\xbd/\x80\n\x05\xde\xe1"^\xb4\x8d\xfc*\xd72\xe4\x01\xa8KD\x9e\x88\xa7\x05\x1e\x0c\x89\xbc\x0e\xe23\xb9\x8a\xa0\xed\x99\xe0\xc8c\x8d\xbe\xf1\x05\x01\xcb;X\xa2D\xb5\xbdM\xab\x7f\xabj\xf3\xe3i\x12\xec\xb9[\xf4\xbe\xe9`\xa8M\xc5\xf6\x10~{\x1e]&amp;\xca\x0c\xf2\x83\x10\x1d+\xe5\xd4\x0c\x8dl\xc3sT\x81y|`x\x18\xd7[&gt;\xc4\xe3\xaf\x90\x94\x1dJA\x08{F\x189\xe6\x7f\xfa\xd7o&gt;9\rS\xc7\xbaqM\nJ\xc1\xbfFQ\xc4\xbf\xf1\x8a\xf2;+\xa2\xfd\xf9\xa1\x84\xd0\xc25\xbb\x17E\xe2^\xb26\xc9\x9b=;\x10\xc3\xab\xd4\x02\nE6lzW:qo\xb5\xf7i\x06P\xac\x1f\x9a4Z#\xdf!\x9b\xec\xdfP\xca\xc38\r\x05\xc0\xcf\x92\x98sh\xfc\xc1\xb2\xb7xX\tC\xdb\xf9e7&gt;\xa4j\x08\xc9\x87[G\xa2\xf8\x92\x87OkG\xd3\x85\x9e\xfdT|\xac*\xbcf{\nyF\x01\xf4b\xd1^3\x14\xc00\x8e\xea\x96\x96\x1bt\x05\xa7\xd0\x06K\xef]\xf92d\x81\x05\xcb3\xd5\x1a\x93-e\x04\xb1S\x12S\xa5,\xcb\xb4C\xafN\xc4S^\\\x80\xc2\xb5\x9e\x9e\xac\xb8$F\t\xb8\x18\x0c\xcaE\xfa\xdc\t\xea\x95\xb2f\x86Qf(\xac\xf4\xaf\xfd\xe55Z\xfd\xad\xfbh$\x9a\x89&amp;\xf1WD\x98\x90\xc4\xfc\xa0-\xb5\xab\x8b\x90\xc1-\x87%\xd9\xef\x1c\xca&lt;?h\xce\xe2J\xedA\xac;WX\'\xdc\x8f\xe6\xaa\xbe\xff\xd9\x03\x16#Oc\xd4C\xff\xa6\x06\x0fw\x03~0\xa2\xe2W\x8d)\xb5-\xc5y\xe0|C\n\x90\x81\xea,\x18=\xcc\xfc!\xcf\xf89\x9b\x96\xacR\xa0r-\x0f\xe7c\x8f\xb4s\xc6\xb9#\x05+6\xa6\xf0\x03\x1cQ&amp;*\xf5A\xa6\x18\r\xc9\xc4S\xf0\xfb^\xb8\xb7\r\x14\x9c\x80t\xe9\xb1\xf2\xe1\x19\x0e\xcf\xe0\x83\r\r\xa3\xdc\xbcd\xb0" \\\x9dd\xe56\x8a\xfe\xca\xb7^/x\xa1\x15\xed\x14\x92\x03\x9aH\xae&amp;\xc0\x0fL\xbd\xac\xdc~\xd8\xc1F\x90VN\xc4\xf7\x15\x98\xd5\xb09\x9d\x10#\xf3{&lt;\xeb\xf1AWDs\x1ba\x19\xe4\r\xb7\xdcHC\x94\x7f\x95kC)970t\xb6\x11\x12}\xbfU\xa1\xd1\x8c\x82\x10S\xab\xb7u\xf5H\xfe\x91t\xf0m\'[\xfe\xde\x8d\xdaBw-9,\x02\x9a^\xf5\xceV\x89\xb8\xe9\xc3\x07\x8b\xd6\x8cX\xcb\t\xd6\x02sU\x1d\x16\x05\xb0x\xc4\xeaO\xf6N\x1ay\x9cC\x9c6\xabuZ\xc0o\xf4x\'\xd9N\xfe|\xf1\x00\xd2\xef=\xa3&lt;_F\xa6p\xd6Gr\x8ek\xe0\x9fM\xd1\xd7\xa5\xde)\xc7\xe5\xfeY\xc2\xc1\xba\xdeR\x98\xfd\xcaLKf\xd4\xb4\xc0\x90\x04\x99\x08X\xf6\xdc\xc9g\x13\x19\xb2\xaeo\xde\xa1RG\x13t\x02\xfbP\xb6\xff7\x12p\xcd\x8f\xc3\xeaA\x1b\x05\xdcM:B_p\x1ea\x83N\xaf+\xd1J\xef\xb7g\x97\xc3^\x94\xe2\t\xb2\xe6\xf8}_\xdf\xfb\xde\xf7\xdeYa\xe4\xa2\xa8\xad6U:\x88{\xf6\xc8\xdf\xbf2\xfe\xfb\xb8\xe2\x83\x83\x02\xf0\x8b}-Z\x06i\xd2y\xd4_i\x93sWb\xb9\xeam\xd3\x96$(\x149\xc7\xc4F_\x02\xaa\xde\x0b\x1eFLZ&gt;\x1cD\x8e\x8eCI+s\xc1\xe2(\x08\xaf\x08\x82\xe26\x1a%\xb2\xa3\x1bDt\xed\xf5\xc17\xf6\x98hs\'\x80\xd4H\xabJ\xf7\xcdK\x1d\x9bkl\xe5^]~d\xdb\x10\xfc\ti~\x84\xff\xe4`\xe4\xb0p\xfaS\xa9QH]\xc1\x1ar\xbdS\x91\x02^.C\xd5ur\xb9\xb6\x1e\xe1\x01z\'M\x00\x84\xc7\xc6\xf5\xd5e4\xfb&gt;W\x0e\xf5v\xce\r\xaf}\xbd2\xe1\x9e\xb5 x\xd1\x87\xc5\xea\x8d\xc9\x9e\x9d\x0b\xbe\x1f7(\xe9\x0e\xa3\xa7U\xed/\x00\xb0\xcf\xaeo,\xc8N1\xeb\xd7\r\xda\x9f\xc3\x97\x00\xf1\xe9l3\x9e[]0i#\xb1v\xb4\x96\x99\xc41\xebND\xc8|\xa3\x970\xe4)\x82\x914\xad\x14}\xc3\x83\xca\xd2\xab\xe2\xe74"=\x84\xfe\x8d\x19\xf9\xdf/\x1aqb6\xf3\xad\x1a\xc4\\P\xcfx\xcb\x00W\x9aY\xf1\x1bZ\x85\x9dD\xf0\x98b\xa8\xf2\xe4\xf4:84Q1\x1a\xde\xc6\xe4\xcdh\xfb\xa8\xac:5\xda\x18t\xeafq5#eq\x01\x8f\x0c^\x81|\xb2\t#qIcm\xc6c\x00c\xd8\xc4\xee\xfb\x9a7\xe2*\xec=\xe4\xa8\x91w&amp;\xb1\xed"o\x1c\xe2\xc9\x89\xbd\x1d\xb0\x07R\x0e\xd2\xfb\x8dS2[\xb5\x9c\x9f]Y\xb5|\x96\xc3#\xab\x9c\xf8Nj\xcc\x08\xd9\x0f\xbcWb\xdc\x80\xeb\x0f\xaf\x8c\xea\x1bD\xbc\x08\xd1\xb1\xa3\x88E\x1fkJ\xcb\xab\x01\xcad\xdfk\xe2{\xa2f\x8c\x0b\xcf\xdbvF\x11\x06y\x02\xae )f\xa4Yj6\xb4kA*\xf0\x06NA\n\xa9:JccL\xf5uX\xc7\x14\xd6kG}h\xc8\xc3z\x05r6\x05\xb9\x98K\xe0\xe5\xd3n/1\xafLg\xe0$IJ\x02\x15\xf0\x1f1M=[\xf7i\x92s$\x02\xe8\xf4j\xf8\xd5\x99\x05gbz\x9b"Q\xd1\x06\xdd\x12\xb1\x92D&amp;\xbb\xccz\xe1\xd1@=\x1b\xf1\xf8\xe3\xf0\xef\xb0:}Us\xfc\xbc\xff3\x03]\x07\xbf\xa9\x84\xe9\x0e\x1e/\xdd\x9a6\x10\xf1\xe1\x92H\xaa#\xc4\xb7&gt;9\x8f\xf9C\xfdeH\xfcyD\x1b{\xbb\xfa\x8e\xd9z\xba\xd1&lt;\x7f*\x05\xb4\xc3\xacc\xd2\x02B$\xa0z\xdf\xb1|\\W\xd1\x8a\xcb\xe0\ndt\xee\x80\xe9\rC\x0b\x97Bz\x1bi&lt;\tT\x0b\x8a\xd4\x80\xe3\x04\xd6\xd7a\x98\xe4\xca\xd5\x82\x18\xb3-\xb3d\xd4Y\xc2\xebu\x8f\rf\x02\x06%\xca\x81-\xe3\xdb\xf6^\'\x0c8)\\\xa5W\x0b\xa9\x10+~TZ0\xf1\xb8\xedsXy\xe4\xbco;%\x8fg\xf4Y\x1caoC\xc60\x13=\xda\x8b\x1c\xa7O\xbc_\xe3\xc1B\xe4\xb3\xae\xd2y\t\xf8{\x15\x1b\xb1\xd8q\xbcv8\xd4\xf6\x9b\xd95aj\xa8\x84\xd5j\x19)j\x9ci=\x06\x93\x04`\x80\x8e\t\x00\x85\x16\xf07PQ\xe7\xcb{\x101\xd1\x85\xb0\x0c"\x9e\xe7\xa9\xf2Z\x88d\x00{\xf3\xed\xdf\x90\xb0\xdd\x84\x1d\xaa\xc0\xe7\xb3#\x01\xf7[x\xe2\xa4\x95u\xba\x1f"y&amp;F7\ti\x19\x85\x98t[\xd4\xb3\xd3\xe1\xe3\xd9\xf6M}\xbe\xe3/\xb5R\xf6B\x99 \xfa\xf5\xcb+\xaf+\xab\xb1\xdbp!\x83\xc2q\xfe\x80\x83\xddHc\x9b\x99N\x1f\xd6Z\x9f!\x12r\xda\x1afP\x1a\xc6\x98\x8e\xb5\xbc\x82K\x06\x19\xf3\x13\xec\x85O\x02E\xa7\x07+\t0L\r\xb0\xfc\x0f\x1b\x11_\xb8\x9bD\x95]\xb8=\xb5\x05\x81\x08[\xbfJ\x85\xd9\xee\xe3\x92\xcd\x93\x02&lt;\xa5d\x80k\xde\x8dnn\x8f&gt;=\xd4om\xbf\xa7\x0cws\xef\x84\x032q\xb0\xae!L\xcb*\xe8-\xfb\xcb\x88\x98~\x17\xd6\xbb\xcd\xcas\x97\xb3\xe5\xaa\xcf\xe9S\x00\x81\x8c\xe5N\x05\x927E\r\xa0G\x12\xce\xdf4T@ B"\x9b!\x81\xa7?Z\xbd\xc7\xfa&lt;\xad\x04\x94\xd9\xf9\x05%\x06\xdb.\xc1!\x7f\x06\xf9\xc98S8i\xbc\x84dU\xb7T_m\xd7P\xf1V,\xd2d\xe4\xdb .\xcfu8]\xdc%\x95\x13\xc6\xd1\xae\x89\xaa\x83\xfa@\xf0\'\xdbT\xd8\xfe\xf2\x04/\xe4\xef\x17a,\x03b\x06\xc4zD\x95mE\x95\xfd%\xc1V\xee\x8a!=G]\x92Z\xe6\x92M\xa7T\r\xec\x81\x84\xfd\xf0Fo\xa6G\x12\x18\xa6j|Sx\xfan\x91S\x1biq\x83\x95&lt;0\xca\xd2Y\xad_\xb3\r\xf2\xf4\xa9O\xa9\t\xac\xb2p\xda*\xdfT\x9c\xac\xffG\x03H\xa3\x01\x87m.\xae\xbcn3\xbaMR\xd5m\xe4\x80\xca\x85\xe1\xed\xf4\xd8\x15bG\xf6(Dr\xdd\xc6^\xacg\x86\x11\xce8\xbc2\xc3\xa3\xf8\x8b\xab\xf9\xec\xf46/\x8a\xb7.6\x08Y\xde\xa8\xbe\x93]\xa3\xf7i\xf6X&amp;K6C\xee\xb8\x02\x11\xde{\xdd\xa5\xf8&amp;u;\n\x8a\xec\x8fO\t&amp;#x\xb8"\xe6\xc8Q\xe0\xb8\x8e.3\x06\xf6z7V\xe8S\xde\x97l\xb6\x91+$m\x16\xd0v\x02\xfb\x99\xfb~\xe5\x7fz\xf2\x12\xaaj\xc5\x05\x9e\xa9Al5\x92\xa8\x80\xbd\x90\xa3\x08;\x84kJRZW\x8eG~\xb4D$\xa2)_~\x9e\x90\xaf&gt;O\xb3&gt;\x98\xa3\xed\\E\xfb\xa7\x07\xd8\xc8S\x8f\xd2\xc0\xe1\x8e\xe9c\xa5\xd9\x8f\xe1q0t\x91\x03C\x1f\xf6l\x97N\xc6\x9f\xcbe]S&lt;f\xb8\xe1m\xa2K\xb9\xb4W|P\xa1P\xd5\x05\xe9\x00\x9f\t\xe6\xfaw\xe3\xe9\xb1\x97\x84j,\x1b\xef\xe5\x02\x9a\xae\x90\xc8\xab\x06\xc3\r\x9fI\x87\xb9"\xda\xec\xc1Q\xd7\x18\xdbnMu\r\xdd^48\xd4I\xa8\x818\x88\xb3X\xeb\x10\xc9\x0eO/\x83$\x1e%\xc5FE\x10$\x07\xbarX\t\x03\\\t\\\xca\xafy\xdb\xbc\xb2\x91`S\xc22\xdb\x8ea&gt;-\x8c\x8a\xbc\x89\xe5\x81\x94~v\xb0\xc4\x96\xd6a\xbb;)^\xa1C\x8c.\x1e\xd2\x9f\x1fmp\x01\n\x83T\xfc\xb8\xacY\x1f\xe0\x14c\xb8\x16\xec\'\xf5\xb2\x1b\xd2e\x87\x8a\xbb\xe9\x19\x81\xbdq\x8e&gt;\x88\xd01J\xe8\nu\xc5\xcb\xdfC\xd6\xfbngm\xdf\x15\x06*.\x02@\xc7\xe3\x01J}kJR\x19\x12\xb8\xcfp\x0f\xb0\x96\x80Q\xd9\x80*\xcdQ\xcb\x00\r*\xafu\x1d\xd7/\xcc\x1a\xdb\xeb\x8f\x92\x82d\x8353e\x95B)\xc7`\xcd\x1fx&lt;p_\xda\xf6\xcc\x81\xec.\x81\xde\xf8&lt;\xce\xc4\xec\x03\xd2l\xb4)\xc1\xb5\x92\twh\xf2H\x18&lt;\x90F\xf8\xfc\xb0X\xc7\x02</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Par De Pistão Amortecedor A Gás Portas Móveis Armários 80n Força Normal Jomarca Prata</t>
+          <t>Balança Digital De Precisão 10kg Davely Cook Cozinha Para Uso Domestico E Profissional Fitness Ideal Para Dietas Treinos Alimentos Confeitaria Nutrição Branco 10 Kg</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>34</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -846,609 +901,106 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>61% OFF</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/par-de-pisto-amortecedor-a-gas-portas-moveis-armarios-80n-forca-normal-jomarca/p/MLB25249994?pdp_filters=item_id%3AMLB5054601214&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB5054601214&amp;sid=affiliates</t>
+          <t>42% OFF</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_942964-MLA100063613989_122025-AB.webp</t>
+          <t>https://www.mercadolivre.com.br/balanca-digital-de-preciso-10kg-davely-cook-cozinha-para-uso-domestico-e-profissional-fitness-ideal-para-dietas-treinos-alimentos-confeitaria-nutrico-branco/p/MLB65131882?extra_comm=false#polycard_client=affiliates&amp;wid=MLB4083251613&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>b'RIFF\xc2M\x00\x00WEBPVP8 \xb6M\x00\x00\x90!\x01\x9d\x01*\xc0\x01\xc0\x01&gt;m4\x95H$#"!\xa5\x95:\xa8\x80\r\x89eA\r\xda\xd0{\xe0\x8d5\x90\xfcQ1\xf8\xe1\xc3R\xc3\x11Y\xf0\x80u\x0f\xce\xfeL\xf9\x12\x87/\'\xf93\xf9\x97\xd7q\xd1~\x1f\xfc\xb1\xebx\xb2|\xd6&lt;\xc3\xf5\x7f\xf4_\xdc\xbf\'\xfe[z1\xfd]\xec\t\xfc?\xf9\x9f\xfc_\xee\xbf\xe8=\xa7=u\xf9\x8f\xfd\x9d\xfd\x87\xf7y\xffc\xfbc\xee\xd3\xfb\xf7\xa8\x07\xf3\x9f\xf3\xdf\xfd{\n\xfd\x03\xffp=]\xff\xea~\xdd\x7f\xea\xf9L\xfd\xbb\xfd\xac\xf6\xaa\xff\xff\xec\x01\xff\xff\xd4\x03\xff\xff\r\x8f\xa5_\x99\x7f+\xfe\xa7\xc4\xffA\x1e\xdf\xf6\xbb\xfb\xbf\xce\xb6\x14\xfe\x1f\xfc\xdf\xfb\xbe\x88\x7f3\xfcK\xfb\x1f\xf0\xdf\x91?@?\xcd\xff\x97\xe1\xaf\xd0\x0f\xf5=B?\x1b\xfe_\xfe\x1b\xfb\xaf\xed\xf7\xf8.90\x0b\xf9\xff\xf5\x7f\xf8\x7f\xe1\x7f+~Yf\xd1\xf6?\xb8\xde\xe0?\xae\xbf\xf6}\x89\xef\x99\xfc\x9f\xfeO`\x0f\xea_\xe1\x7f\xf6\x7f\x8a\xf7\x80\xff\x1f\xffo\xfao\xf5\xbf\xbc\xde\xe0\xfe\xa4\xff\xc7\xfe\x8b\xfd?\xc87\xf2\xff\xeb\xbf\xed\x7f\xbe\xff\x9a\xfd\xa8\xf9\xb8\xff\xe7\xee/\xf6\xdf\xff7\xba/\xeb\x97\xff\x02\xb4\xda\x10\xe3\x85hC\x8e\x15\xa1\x0e8V\x848\xe1Z\x10\xe3\x85hC\x8e\x15\x97\x14oQ@/B\xfe&lt;\x80\xb1\xc5;\x0b\xd8!C\x8e\x15\xa1\x08\xdf\xcc\x13\xb0\xbf?\xaeev(s\x00\xf3\nZB\xb1\x10\xc2C\x15x\x85\x14\xcd\xff\xfe(\xf0\xd8Z\xc6B\x90\xfaP5\x95t\xea\x86\xfa\x9d&amp;\x8e\x19\xf7\xc21\xda\xebK\x1a&amp;\xb7\x1d\x02_-\x06\x84uMkn\xf5\xc4\xfd\x9bD\x08\xd0\x0cd\xed\x03\xcc\xe4f}\xad\xc0\x8e\x7f\x02/w\xae\xb1\x16\x947\n\xb7?\xc9\xf8\xff\xd4\x80\r\xfa\xd8\xa6\xfaj\xb5\x8b\xfd\xc2w\x91\xee\xdf\x18\x92\x1e\xa7j\xe4\xf4\x9f9;N\xb1t\xc7\x1b\xaa \x99\x16\x1cZ\x11(^&lt;\xb6\xa0xV\x847\x91S\xa0=a\xcf\xd8H\x1c\x04Ks\x93r\x03a\xd4\xbbZ\xd6\x97\xf3q\xe3\x1a\xe0\xa9\xc9\xe6\x88\x85\xaekz\xf3iD{\xa8r\xb0;\xdc\xa3\xaf~$+\xb9\x1c\xc0J\xddt\xa8\xb6\n\x10L\xbb\x88\xdc+A\x1bJ\xf9Ob\xd7\xff\xcdB\x8e\x1b\xb72\x99\x04\xa7\x88\xb3\xe8\x18!\xc9\xb2,\x8fx\xefO(\xbd\x98a\xe6R|\xf2\xfet\xb0\x0b\xe24An!\x1b\x02w\x14\xcd\xacZt\xacW8\xa1\x1dO\x94I\xa28]\x89LG_m\x86\x81\t\x9d\xe2N4\xa6\xbb%\xe5JU\x0b\x95\xac|S\xc1\xa6\x84n\xa7\x85\x12\x02\x16e\xa6\xb0Z^\xf9y\x99Z\xa3Hn\r\xc3\xca\xe3:\x94\xec&lt;\xb0\xd1\x99\xe8\xa1\x10\x8eo\x0b\x9f4\xdb\xd0\x871N\xce\xa0\xcd\xd3\xeb\xf1\x0c\xc8cv\xe4e^\xed$\xf3#\xd6\xd9n\x9buF\x8b\xd2\x1c\x84O\xff\xfd\x11\xa4C\x06\x1e\xc1\x80\x94\x0e\x9c\x8f\x82\x14\x1e\x9dM\x96A\xc1\xcco\x9f+\x98v\x1b\x08V\xcfO\xd0\xa1\x1c\xd6\xeem\xe8~\xa2\x10\xfe\xdd\xb8\xc1h\t\x1e`\xc8\x15\xd1(r\x99U\x0b\xc8\x91\xb7\x8d\x9e\xe1\r\xae\x08%\xfe\x18\xbe\xff\xf9RD\x92\xdf\xea\x16\xc0\x19\xf2\x1e*\x82\x14-\xdb1x^T\xe2\x0bJ\x06\xaa\xc9\xadu\xa9!K\xd0\xa4\xa6\x97\xe1\xffc0l\x0f\xd6\xaa\xa9\xe4\xb7\x8a];2\xd0\xf3\xed\x03Ate@\xbd\x90_\xa4\x949\xaf\x87\xd7\xbdH|`\xa1\xa7\xebx\xdc\xfe\x826\x92\x9a\xbd\xe2\xe1nqN9O\x87\x96?\x9d7g\x88\x00A\x82\xf7T|\x12\xae\xee\xf3F\xbc:\x105\xe2\xd3\x14\xaa&gt;\x93\xac\x9f\xd9\x07\xf7\x1f\xc9\xdc~\x80)\x8e\xfb\x91\x90*\x1c3\x9e\xfdE^\x15\xf7\xde\xf69\xda(\xd9u\xeeZ\x11\xdf\xc0\xbd\xbd)\x91\xe9\xed\xa4\xe4s\xa1\xfb\xf5\nRk\xa7\xb7\xcad\xa1\xaa\xa8\xbc5\xa7\xc7,\xd6\x01yV//\x8b\xea\xea\xb6\xb4o\xe8\x8d\xef\x88@\xb8\xe4\x18a,H\xfd\xca%\xa3Xa\xb0\xd4\xbe)\xbelG\xf1\xf1{\x94j\x18O\xcf(\x13\xff[\xc0E\xbd\x0c&gt;\xdfQl\xb2lv\xb0n\xb7k\x95\xbd\xa6\xa6\x08\xee\xb7H\x00d+\xc2&lt;a1\x19$5\x16~\x7f\xd4\xe3\xe3\x18\x91L\xfd\xf45Q\xcb\xe2\x93T\x01\xa4\xe1\xcd\xb7\xa2\xcfE!cL\xe3at6!\x13mm\xb4s\x93"\xf5U$\x16AZ\x92\x1f\xf6\xc5\x97g\xa1\x88\xe9\xe5\xf9\x93\x9ap\n6!2-\x7f\x80\x86:\xf5\xfa\xaf\x9aQ\xf3\xec\xb9\x81\x18%\xcd\x99QT\x9a\x1b\x9d\xb1\x98&gt;\xd1\xe7\xff\x8a\x00O\x9b\xea\x8fD\xc6\x94C\x0bf\x94\x9f\xc0f)c\xe2QQ\x12\x95\xc4&lt;\xd2W\xfd\xd5\x07\xea\x98\xe1\x15G\xc2\xf8\xa1\x97\xe2\x14\x8d\x87\x17.wm\xb4\xc0v97\xd4Yl|b.\xb4m\xef\xb9k\xe8\xa1\xd2\xb49|\xa5\x1cx\n&gt;,~\x11\x94\r\x97\xab\xc4y\x08\x01\xd6\xa4Fd2\xf4\xd1\\\xb9-\x9e\x10\xc7\x8dA\x8c\x86&lt;@\xd7\xe3\x04\xf4\xec\xaa\x91=\x13\x03\xe2\xfc3\xf7j\x94!\xe3\xe7o\xcd\xa4A:\x86j\xda\xc4\xf0\x04F\x7f\x17\x99\x86\xbf\xe0\xb6\x1f\xaf\xfe\xeb\x15\xdf\xd0a\xa0&lt;`^+\t\x90_\xe7\x01\x1e\x12\xde\xa6\x18V^N\xc5K\x16\xf7\xf0\x963\xbaS\n\x92\xcc,\xa0\x96\xf2\xb2\xb3[\xa0\x02|\x05\xd0\x97\x10W\xbd\xf1\xb8yZ\xa3F1"\xcc\xda\x0f\xe1\xa5\xd3x\xf9\xee7\xd4\x9a\x1c\x15\x03\x96\x90\xc0\xc3\xfb\xd8\x1eUh\xe4_\xe1\xa6\xdb:\x00\xa0z{\xabxH\x00\xca1\x0c(q\xcfZ\xcf\xc1t)a\x1e\xee\x9a\x98\xe2\xe3\xa0\xf4\x15 \xe0\xd8\x0cH[\xc3y\x10\xbc4x\x98\x0c\xad*\xd8-~R\xa7\xac\x01\xd5)\xef\xce\xfe\xe4\xfa\x88\xab#\x12W W0\xce\xe0=\x87\xd5\xa4\xd8\xc2\xb1q\xc5\xb2\xd7\xca\x02%\xb7\x10(\xd1V\xaf\xb4\xe4\x13\xc8\x97X\x97\xe0-Ot|&lt;ud\xbaK\xee\xb5\xb6F\xf1\x1d\xabU&lt;"\x0eqAK\xd9\x16\x08\xa9+\x1d\xd2\x1b\x0cV\xe2\xcb\xaf\x9a\xd0^o&lt;(?H\x06yU1\x07\xba\xbc\x00+\xdd\x9fD\xc1w\t\xca\xe6\xdel\x07+\xca\x06\x0f\x98\xdba\x87l\xda\xaf\x81\xd5\xf6s\xb4MV\xb0ss\xf54pd@&amp;\xc0M\xa4\x05\t&amp;R\xba\x06\xc6\x03\xa5mZ\xbf\x1a\xe70\xd4&gt;\x82\rw\x0e\xce\xf2\xeca\x7f\xf5/\xfe\xd1\xa6~D\xe6\x19\xd8CKJBN\x9c\x87\xad#\x9c\x0c\xedf\xad\n\xdfP\xf5\xbf\xea\xea\xc4\xf7\xbe\x14?X\xbf\xff\xce\xc3C^=a\xa3\xce\x9f(\xb4\x1c\x02-\x84\xb8@EF_\x7f\xf6j#7\x9e\xfb\xbf\xe3H\x19u\xcc\xe5C\x161g+\xf5|^|\nMIO\xce\xef\xa4\xbf\x01QC\xde\xa5\xa5.\xf4\x99\xc7\x97\t\x94\x85s\xcdeH\tt\x86\tS&lt;\xa0\x8et\xf5\x8b\xab\xcf\xda\xdf\x1d\x86:\x1e\x08\x16 \xcc\x19\xb8\xd7\xa5\xa3\x86\xf3\x06z/\x1aj\x96\xcc&amp;7\x14\xfdk\xb0O\x9a\xc6~\xb6&gt;\xe2\xc4\xa1\x9aC\xc3\xf6\x99\x83~]\xb9\x14\x14\xdcP\x06 6$\xf2\xf7\xca\xfe\x1e\x95\xcb\xb7\xcf\x19\x89\xe9\xde\x99\xdf#\x8c%\xd0\xcc\x00\xbfB\x9c}\x14t\xde=\xf4\xfe!\xc6{{QgF\x0c\x7ftAi`r\xa5\xfa\xbdg\x07&lt;\xca\xff\xb3\xb7v\xab\x15\xa2\xb5y\x1cv\xab\xf1\xec\xfav*\x17\\\xb7\xb3/\xc4\'&lt;M\xfb\xe0\xbe \x8f\xd2\xd7\x9b\xc0[]\xd7\xd6O\xbe\'ME\x98\xf3m\xff\x03B\xc2tjL\xa7\xe2\xee\x10UD\xcd\x07K\x13\xf4F\xb6$\x0c\xa7\xd4\xe9~i\xb63\xedl\x93)\xa5\xe2?\xf4\xe0\xbe\x7fk\xf3\xc0\xd0f\xdeL\x10$ B\xd7V\xf7\xd9\xbe\x8f\x92\x1d\xa5\'3\xcfs\xd5\xcfF\xb3\xcdaS\xa4p1\x19\xbfJ\xd5\x1f\x10\x97.I}f\x9d}\xc8\xb09\xa0E\x9a+\xcdI\xcb-\xb9\xfd)\xad\x08F\xd6\xa4\xec\x0b#\xdfJ\x150"\xe2\t\xa5o\'\x18\x9eN\xdf\x07\xad\xe2m\xe8Z\xee\xb21S@\xc1\xb7\xdd\x16\x9f\x97aB\n\x0bG\xfe\t\xab\xca\xd3\xd9\xb7\xe1r\xce1\xda\xf3h\xa7\x13\xe0t\x08&amp;m\xd7\xc1\xdd\xb5=\xcb\xda\x0fF\xa3\x9b\xb2\xe2vs\x90\xf4\xd2Q\xde\xc4.\x0e\xe6\xea\xbf\xc7\xa3\xaah\xa2y\x9a\x11\x11\xfas\xe0\xc0f\xae2\xfe\xc4\xab\xf5\xfcJ4Q\xa2\xd4\x99\x9a\xb0\xb7O\x98\xd9\x901~\xf7v\xd2\xc4\xa6I\xf3\xc4\xab\x02\r\xfe\xe5~\x94\x9e\xf4\x99D\x13\x96c\x9f\xcaO\xca&amp;:&lt;\x97\xf7\xbbo\xe8:\xeb\xf9x\x1as\x02\xfeZk\xc1\x9c\xa5\xfd"\xa0\xd9u\x06\x84uM\x07\x96\x88\xc5\xcf\xc4O\xcc\xa2\xa4\x81\xf2\xfeG\xc7\\&amp;\x9eY\x7fIB\x11\x98\x88\xef\x1f\x16\xb1\xf6_\xd3\xc4\xfd\xcf6\xb4IS\x88\xdbF\xa3\xe5V\xab\xdcF\x9b\xcbB\xa4\xdb^\xe2&gt;\r\xaff\x97\x00\x08\xfa\xaf\xaf~\xa2\xc2\xfbA\x8e\xdaBS\xb4\xda\x10\xe3\x85h\x7f\x9b\x82S\x1b\xf6K\xcb\x90\xa1\xbd\x92\x07g\x01@\xd8t\xbf\x19\xac\xb3\x92\xf9\x049\x01\xcc\xcas!,\x15\xda\x1d\r\xb9\x1a\x11\xd57hGT\xdd\xacr\'\xb6$\x1e\xbf\xb7\xc3\x8c\x06\x84u\x96\r\x08\xea\x9b\xb4#\xaan\xd0\x8e\xa9\xbbB:\xa6\xed\x08\xea\x9b\xb4\x0e\x00\x00\xfe\xffM\x00\x00\x00\x00\x00\x00\x00\x00&amp;\xa1U,[\xc9+y\x91H\xc3\xe3\xd4/\x0e\x8b\xaf\xfa\xdfe2y\x99\x8c\rf]\x06\x8cq\xad-\x95\x96\x0c\x06\x88k\x85\x8dc\xa3\xc4{\xe2\xefD\xacLwY\xa3\xfd-%A\x87\x0b%K\x93\x95 %j\xbe,\x96\xd8\xa3\x84\x14\x04"\xdf}\x97\xaf\xb9+\xc0\xaaX!i\x18\xc22\x1d\xccw\xb5\xae*\xfd\x85\xde\xed\x12\x13\x1cS\xe5\x1d\xc5"\x88\xec\xbf\xd2\x10,\x06\x0ed\xa7n\x17\xcd\t0\x10"\xa2\x11$\x00\x00\xf9KY1\xbf\xbb\xde\x9bO\'/*\xf3l7{!"\x0fc(g\x80\x11\x1f\xeb\xf5\x16d\x98\xc2\x11K\xf8y\xa9\xc9\xff\xb4\xa2\x9es\xa2\xc2&gt;\xd0&lt;\xeb\xbf\xbdJK\xa6m)\x87\x84\xe3\x7f\xa9\xc5\xa3\xb8\x8d\xd3\xf6k\x7f$\'\xcbw\xa9\xc3\xab7o\xcc\xc6\xff\xf6X\xbc\xa5\x12:/\x7f\xc9\xbbk\xd0s\xe8\xb1\xcb\xe6s\x85\x8b\xa1\xa4\x80\xee\x13\xe1t|\xf6\\\x1b\xa4n\xb0V\t\x84\xc2\x0c\x9cK!\x83m?7\xc4[\x14\xcb\xde\xca\x16\xe7?-Lm2H\x02=~\x82M\x93,n\xcc\xdbIH0pB\xe2(\xfc\xa75\xf9c(4Ye\x8fF\xf1\x89\x87;\x94:\x07\xf0A\xfc\xe8\x8b1\x14b\x9a?\xa3)\xef\xa4V\xc7\xc6hV\xb8\xfdo\x10/\x12X\xfdS\x83\x05\xa3\x8b\x08\xb4hGK\xf3\x91\xbb\x99\xb2=\xbb\x9a\xdc\x99N\xbbY\xe2\xc3M\xb7\xfa\xf3\x86\xdd\x18\x9c&gt;\xddN\xdfkV!\xcf\x18\x14\xbarh\n\xaa\xb8\r\x87Bw\xfa]\xd9\xa5+\xf7J\xfc\x16s\r\x04\xd8\x89a\xbffZ\xe3\xc2=#C\xae\xa3\xe1\xe3~]\xc1/K\x17\\\xef~\x01V\xdb\xa1a\\\xf1C\x91p\x05\x10C\x1fC\xb3\xab\xdf\xfc\xd7\x9d\xbc,\xc8I\xda\xe1C\x04\xc0G1/LO\xe1\'%\xed\xcb\x0cq\xf7\xdc#w\x04&amp;pJ\x8a*\x8a\xd6"J\xe8\xcd\x85{$`8\x96c\x12\x06\x8e\xc1\xeb\xdf\x99K\x9f\xa3\xb6c@\xa0\xdfj\x94YI\xf7(\xce/\x023\xfe\xe6\x17\xb8n\x14.\x8d\xce\xc1\xfc\xd6*\x03\x9e\xd1\x038w\xa7\xb2b\xb9\x03\x8ck\'\x84HZ\xa4\x91Q.\xf8\xfa\xe6=\x04N\x91eVS|-`r\xcd\xea\xdfs\xc7[eb\x8f\xf5k\x10\x0c\xa2\xa4\x1c\x0b\xd4\x98\xafb-&gt;\x06\x8dh\x9d\xfa\x0f\xf9\xc3\xe7c?\xd4\x80I\x86\xc3\xe4\xae\xd2\x1ef1\xe6\xdf\xa4\xe3?\xfb\xe1x\xf1\x9f\x7f\xf5\x03|3\'\x80\xde2\x84\xc9\x97\x1fq\xba4\xd9\x19s}B\x95\xcbz\xcdqt\xf9\xe8\x92\xaef\xa4\x80\x01\x7fn#GOf\x9eU,\xbar\x86\x12\xa3\x8e\x01\x9c\xc4\xa0\xc0\xcd\xec\xb1\xa9l\x0f\xc4\x8e4\xf0\x8aJ\xc9\xd6\x96N\xe7e\x91s\xd19\x08X\x11fO\xf5\x0c\x06\xfd\x03_~S@\xc9\xb0\xe3e\xb9 \xb8\xe1\\\xe0\xd6\xdb}\xe5\xc7\xe4\xb2D\xe5n\xdb\x91\xfd\x9cWSE\xb9\xd4\x9c\x80\xcd\xd9\x87\xd0\x82\x87\xc5\xfa\x9bjB\x16\xb8\x8e1\xd9\xab\xb8T=6\xa8~7&amp;O!\x82\xb3\x7f:0\x01\xbe/\x82\x81\xf3\xb9\xa4\xcb\x01\xf87\'\x8e\x1d\xfc\x86\x86\xe9f@)\x01\xc4O\x0e]W\x9aMx\x8a\xd2\xd4\xa3\x8d\x88\xef\xe8\r\xa7r&gt;ZKK\xd4"K\xb5\x07\xe2\x97?\xe4\x8agx\xb2\x8d\x7f\xdf\xd8\x8fo\x95\xa7\x9b\x0b\xb7\x0f\x0eO\xb0I\x8c\x00_\xe2+\xed\x89\xbd\xaf\'\xaa\xca\xd7\xe2}\xdcI\xcc\xd4|)\xe8q\x91i\xc6\xe6\x17@\xdfe-\xa8\r@\xf8\x15\xa4\xf3\x80\x03*\xcc\xc8\xcd\xd6Z\xff\xde\x1aD\xa9\xa2\x13\x86,\xc2\x99\xf7s\xf7\x1dQ8`\xcf \xa3\xbagP\x18\xec\x13dv\x83X\x9aRz\x8a\xc8\x06l\x06\x1fW\x92\xad\xa8\t\xc0b\x16\xb4\xd6\x1c\x81\xff\xe8D\xa2\x93!"\xdb^\xd5\x18u}s\xb0\x03\xe8zf\xf23{;\x7f\x84\xce%\xa6*\xd8\x815\x18\xc8\x0b\xa5\xd5\x84\x85\x14\x1e\xad\x00,u\x0b\xb0p\xdd\x8e8\xafGH+K\xea\xffa\x98IzW\x80\xfci\xbcQ\nQ=\x13\xb6:\xbazsx \xdap\t\xf6:\x01$\xd7fS&lt;\x07\x1b@\xca8\x92\xaa\xd8J\xcd\xa2\xad\x9a.\xd5F\xe2\xdb\xac\x96\x80\xed\xfd\xf9\x9bY\xb8\'\x9e\x02\xe4\xff\xbdJ;\x94)^\x10\x8c\t\xb8\x90S\xcf\xbf\xf1\x97\x90\xbbY\x16\x88MU\x8d\xf5\x8c\xc4\x96*\xfby4\xab\x06p\xa32-kw\xa7U\x1a\tTY]\xcc\x1f\xf5\x1f\xa1\x00\xb9\xea\x84\xf8\xd5\xd0\xfe3\xf8z\x93s\xed\xdbU7\xa7\r-1\xa22\x04\x95\x02\xaf\xb6\xd6\x83\xf0\xdf\x19\xc8\x9d\rd\x034\xf7\x12\xb7Z\x0f\xdf\x9e\xc7\xdc`\xaa!\tQ\xdeE\xaa\x81=\x1e\xa4\xf9\x83_\x04c\x14;)\xee6\xd6\xeb+\xa3\xc2\x15\x86&gt;~\xa9"\xf3ms\xb0O\x0f\xfc\x15\x02\xd5\x8d\xc8\x0b\x06\\\xc2UBR1\xfbi\x8f\x96HQHu[\xba\xc6\x9b\xb9\x86glK\x85\xb7\xe8b\xdb\xc0\x01f\x19\x90\xf54v\xca~\x7f\xc5Iq-\x1a\xf6\x12w5|?\xa4J\xfbwn*\xea\xf0G\xac\xf9\x1ek\xbf\xaf\x18\xfd\x04\x99[_\x94\x88\xb0*v\x02\x81\x06r\xb4E\xc8\'\xbb\xba\xd5\xc0\xb1\x13k\xd3\x02\'\x17\xf5\n\x1eclt\xe0\xcb"\x8c\xa9A\xe7-G\xd4\x95\x9c\x9d\xc4,\x81\xbf\xd3v[\xf2h[6[{\x15i\xb8lk\xf6"\xe8j\x86c\x8b;\xc8o\x08\xfb\xf5\xfaY\xce\xf3\x10\xb0\xe23\xf0\xcb\xb6[P\xb6aM\x12\x8f\x1dO+\xdc\x8d\xb6&amp;m\x1e&amp;S\xe4&gt;v\x1a1\x96\\\xe4V\xef\xcf3z\xfb\xd9%\xfcM2$w\r\xe3\t\x1e\xb5,\xce?\x02v6Y=\xd0m\xc2\xac\xd7\xber\xf6/\x9ay\xb8\x1d\xff\xe7OH\xe0o\x01\xf5&amp;\xdc.\xe2\t\xa0u\x87\xb3\xbdY\xaf\xbb3\xa3\xc4%\xe0i\x17\xc4\xd5&lt;n\xe2\xd6\x00\xe1@\xf5\xde\x19^\xbd(d+\xe9,\x17~\xc5\xec\xfaY}\r\xe33R!\xdb\x9el\x8d\x83&lt;\xbd\x0c\xc5S\x96\x18\x8eS\x15p\xb2\xb7^ \\zp\x1en\xa8\xb4\xfc\xd4\xad\xf1cr\xb80\xde\xb5\xfbx2c\xc50\x1f:\x08\x02H\xa2\x9a\x071T\xf9\xb59\x8d\x17/\x05;#Tpb1\x80\x90H\x85\xab\x13\xce\x04\x0b\xe1\x840v\xbb}\xc9\xe85\x10\xc2\xe0\xb5\xed\xb3\xa8\x7f\xd7.\xba-\xb2\xf4\x16\xfa\xf0\xaaq\xb4\xa6\x07\xf9\xf9\x18U\xe7\x82\x93,\xdd\xf3J\xaaJJ\xf6\xe8\xa6\xae\x9eT\x88\xd9Sws\xa1\xa4\xb3\xd3\xb8" \x8a\xfe\xc96\xff\x9c\x83QP\xaft\x96\x82\xb6\xe1\x97d*\x13\x7fo\xc85\xeb:\xb4\xdb\xe9\x10S\x04\xb1\xd20\x9c\x8f\xf6\xfa\x904E\rIox\x16\xfa\xc0\xee\xc0\x04\xd3\xe6\xb1\xdf\xe9\xe0\x0317\x7f\xb51\x8d\xd77H\xcd\xc98\x85\xe9T\n\x16\xe8{\x9b\x0fb\xb8U\xcf\xf9\xaa_\xef\n\xc6\xd77\x9b\x93\x96\xff\xa2bwVa\xc9Ca\xae\xc0\xe4\xc8\x86\x7f\xcb[(\xfa"k\r\x89\x193I\t\n\xdb\x05\xa4\x19\x8e\xa9\xe2\x19\xd6\x10K\x00\xc8\x07\xd5\x11\xe8\xedD"\xf1\xbc\x80N\xb6W#@&lt;\xaf\x1e\x1f\x85\x15\xff\x8f\x83\xe2\xda7\xde\xc1Y)\xf9N#\xb5y\x02\xc7D\xf9\x0f\x10\xc2\t\x8a\xed5\xbc\xb8\x12\xb5|\xc8\xcc\xc5\xf6R\xd2A\xa86)\xf4\xbb2\xf5\x8f\xe5p\xefL\xc1|\x0f_X\xcc\x9ab\xc7[OYU\xf6\x8a\xd52\xf3-\x83\xac\xf8Z\x97\xd6\xb3H\xa3\'\xdd\xaaN\xfch\xf4/&amp;\xc9\x88/\xb8\x1f\xc2@\xbc\xad-\xd3\xb2\xc1\x98\xe5\xfaq\xd5\xebtJ\x06C\n\xf1\x18dq\xdc\xee\xd4q\x01\x9f\x9c\x99p\xb4h\xa6VI\x9d\xd8\x10\xd0\xf4S\x00\x1a\xd1\xb5\xc2\x17a +\xca\xf7\x92\x1b\x05O\xdap\xc6\xb0\xe7R`\x05\xdc\xdf\x02\x9f}\xd7\xc0I\xd1`\xa9S^\x9d\xb8\xc7\x9e\x1d\xb6\xa2\x9d\x11}5\xddx\xe1\x85"\x9aFd\x9b\x1d\x14\x80\x81\xecy\xc5\xef\xba\xd3!\x1d~\xd7\xa7d\xdfP\x00Rk\xc8\x1c\xabLa\xe3\xa0\'\xe50#t\xb0\xecM\x1f\xcf\x0c\xc5\xd4\xb6,&lt;\x00[{\xcbu\xde\xcf&amp;!\xd2g\x05\x86\xe13\xbf\x91pZ\x8b\xec\xc2t\xd3\xf9w]\xc4+B\xa3\xb2v4\t\x98`\x9b\xc0\x80\xaaldv\xd1\xce\x0fLw\x0e\xcaL\x1b\xeb\x7f\xe7\x9aIZ\xa9~\xbc\t\xab\xf5#\xdd\x0e\xb4f\x80Z\xc3Ml\x0e\x13,\xe9~\xbaL\xc5}+\xa0\x18\r\x1f\x95\xd4/\xb7\x90\xe7ux\x14Cd\x8e\xf3\xc7)\x8dNloQ7\xa4\xee\x83\x8eJ\x13\x92,/\xbe\x98\x84\xa1\xa4\xe2:\xa4\x11\x15\xc5\xf9\xd4b$\xaf\x19\xdf!\xa4e\x90\xea\xf5p6\x8d(\xf0\xef\xc64\x92\x02\xd6S\xa6\xa5Z\xdfZe\x02\xab\xef;\xfe\xeb\x93\xae\xfd\xc5Q\xf5SZ\x88\xad\xae\x1eKI\xdft\xcc\x05\x92\xf8\'\xe3!\xd1V\xd4`N\x86\xf7\xa0\x1c,\x10%\xab8r\xe0|t\xf5\xa2\xfc-Y\xf6!|\xc2\xa3`_\x1dm\xbc\xa9P\x0bHu\xbb\x87\xa1\xaf\x02\x18\x93\xaf\xb8{\xed@\xb3\xab\xe5q\\\xe2\xe3\x01\xcdU\xaf\xbcT\xa7D\xc4D\xc2[\xd2\x87\x02^\xacY,\xc2}\x11\xc5\x90\x80Q\x00+|\x03\xb7`4\xd4\xfb3\x17-TK\x1f\xfb\x81^C(\xb7\xdd\xf0r\x07\x91KH0Z)5f\xfe\xac\xa3\x9a\xe7\x92S\xda!\xb5\xb3\xab\xb4`O\xb9\xb2F\xfcq$\xd3+ZQ\x04\xa9\xcb\xd4\xdaz\x0b\x91\xff\x8b\x83\x14=\xec\xa16\x01Y\xf7h\x8d8\xfbvp\xa0z\xb0&gt;\xeb\x94\x00|\xf1\xc2\x82=(\xabd\x83\xcc\x05S\xe0\x81#8G\x92\xfb\x17\xc3\xcaQ\x00\x1c\xb8\x1a\xb4\x0e\xf4\xc1U7\x08\x1b\x9cH1\xe9K\xa5CLRT#Q\xd0\x0b\xf5~\x9fh\\\xdaU\xbdj\xfaa\x9e*\x9d\x86\xa3\xe0\x9b2\x16\x19!\xc7\xa7\xca\x05B+\x8f\xe8\xc5&lt;\xf2\x87\xb5\xfdX.9\xbc\x9d\x9eD\xf5\xd6\x9b(\x14S}L\x02\x0e\x11\x9f\xe9\x12\xc6\xfd\x90\x80\xf7 %\xff\x14\x13eE\x8e\xe0~\xb0\x1c\xda\x9c\x16\xa4jY3\x05\xbaH\xfe\xfc\xa8\xd5\xde\x03\xdem\xe3\t\x06E\x03\x91G\x98\x86\x9f\xc9;b\xa8\xe83\xbd\xa4\x7f\xfdS70\xc7l\x9a\xdb1\xb82FV\x8d\xba\xbe\xba\xbd\xe2\xd2\x90\x0b\xee\xfa\x17\x15T\x00i\x1f\x88E#\xa2*\x1a\xe3^&gt;\xba\xe8ywF\x86\xfd\xaa\xf2S\xc4\x1a\xeb\xaa\xce\x14\xe5\x14Q\xa0!\x0b\xd8w3\xa4\x8eN:G\x826\x1bH\x95@[5\x13I\x1dOf\xa5yY\x9f\xbb\xb2\xd9\xb5k\xb5F\x0b\xca\xeb:`\x867uL\xf329\x94l9\xe6\xf1*\xcf\xbb\xb0\x87\xe9\xaan\xeb\xf9\xab\x8b\x0b\x83\xd11i_\x00\x11C\xb4\xdc\xb7V\x9e\x0f\xc01\xc2\xd7\x8d\xf2\\\x01iI\xd6\x9f\x8a\x0f\x88\'\x98\xed \x04\xc1\xb7M?\xb0\xb3=]w4-\x8b\xebwN\xa2PM\x0f\r1\xd1\xa3\x10#@G\xe04\xf1\x02E\xe0f/Hf\x01\xc5x\x19\xc9;u\xf9y\x91\x86\x14\x14\xb9\xb2Br\xe9u\x12\xabn\xbev\xce\\\xd7\x14Q\x1a\x05\xd7JR\x1d\x01Bt\xc4\xe2\x0fz~EQ]\xcd\xe7\xeb\x87g\\C\xda\xc1\xbf\xe8!\xdc\x8b\xefbB\x7f\xa0BDLS\xabS\xfd\x0b\xeb\xec]\x05\x00\xcd\xc7\x8b\xed\x93\xacA7\x1bT\xbf\x13\r\xd0yAbI\x16\xe2\x96\x98\xd9\xce\xf12\xd1\x91\x01\x1e\x90-\xb9Y3\xb6\xd2\xa5\xf0\x0bp\xb8\xd3\xcdn9?\xaf\x00\x15\xb8\xd36oO\xaa\x17\x10\xa2\xc4|\xf8od\x04\x10\xaf\xa8k\xe1EY\x82\x91\xb4\xf0&gt;\xf94\xf7M\xeeIT\xd6\xea\x86\x85\x88\x9dI\x1f\xf28\xa0d\x0c86\xb3I&lt;\x9f6`\x87\xd2h\xf2a\x18\xc5\x03\xebN\x05\xab\x1c\xe3\xd2\x8a\x11\xf7A\x18\x89V),\xb3\xff7\xc5\x86^J\xd5+\x0e#\x90Ix\xc0@\xaa\x08\x12\x02\xb8\x1d\xb5^\x9b\xc97\n\x17\xabl?\xc0\xd7\xc1;h\x12g\xc8xR*i\xf2oF\x92{\xfd\xe3\xd1k\x91\xab\x9f%\xe0|\xe6\x7f47\x83cD\xfe\x96\xc3&amp;\xaf\x0f\xa8}\xd4\xa0C\xadY\xab3\xf2\xccn\xb8\xee\xed\xb5\xfb\xa4q\x83\xac\x8bB\xc0P \x8ff.k\x1d\xb7\x15\'ZV\x94\xde\xee\x1c]%6ft&amp;\x0f\xbe/Q%\xc4\xedw|\x87Y\x8b\xb9G\x93\xd9\x0eIj\xe1\xb6\xf5@\xfd7\xeb~g\xbd\x85&amp;\x0b\xb0\x17\xd3\xd73}\xef\xec\x84\n\x10L\x94\xc1\x04y\x7f\xeb\x16s\xdds\xc7\xea\xd6/\xce\x80#\x88\x85:Q\xde\xbc\xfd\xbe\x117v\x1b\xa3m\x19\xa2\xd7qv:\x11\xa9\'&gt;\xa1\xaa\xf5\xe3\x08\xc4[\xed\x01p\xba\xd1\x9f\x07\x94LkIO\xe2\xb3\x01\xb0"\xe4\xe2\x80\xf8\x19PLr\xe5\xc17\xfd\x94\xa0\xed\\\xe1\x074\xedCp\x04\xa7=N\xf5d\x8b\xdd\x81\xbd\xe3m\xb8\xa3K\x91Jq#\x18\n\xf4\xa5\x8f\xdf\x9d\x9f\x87%\xe39\xdf}\xfc&lt;F\xef\ru\xb2\x8c\x0f\x05\\\xa2PU\xb2\x95rL\xe3G\x0bg\x91\xd8\xa9x\x9ek\xc0\xca\xaa\\1\xfb~V\xd9\x81\x1c!\xb7(\xf1\x96\xcb\xa3\x8e\xb5\xbf\x9a\xc5\xb8?@\xc1M\xbc\xb1\xbb~It\xe6\xd8p\x94\x878\x92\xa7\xc9\xfc\xe7\xcd\x89\x97\x01\x7f-Rw\x0f!\xc4\xf6\xd6\x0b\xbe)\x90\xa5\xf8W.\xd5\xb1;\\\x8e\xe4\x9f\x93\x06\x9bs\\\xd0\xb7\x9dD\xd9\x93\xa4\xeev\x12\xe56\x10\x15\x7f\xf2\n\xb5`\xaf\x018\x8a\xca\xc7\xaf\x08\x9d\x1d\x1f\xc4\xe4-oZS\xf6\xcb-\x82\x15;4:\xaa\'\xb0"Xd\xbe\x19\xban\xed\xd7\xccK\xd3}\x94\xa2\xf5c\x8dG\xe5\x9d\xb8\xd7\xed\x95\x15U\xb9\x98\x1e\x85\x00\xfc\xe6\xb2\xcd\xc3\xdeIW\xb0\x929E\xe0#@.w\xbeo\xf7-\xaa\x1f\xa4\xcew\x19\x96\xf7\xef\xfdd\xfeM\xeb\x96\n\x0e\x97\xf1Z\xb6eZ\xb7`\x00\xc0t\x99\xfa\xbe\xb1\x81R?\x19#\x82a\xd3\x00_*\xfaO@\xf5\xe7&lt;"\x98\x88\xe92\x876\xfaL\x9b\x9d\xdfZA\x86\x967\x05B\xc9\x99\x99\t"uN\x8agY\xce\x99\r\x99\x80\xf4\xa1\x16\xa6\xab\x19\xe7\xff\x81\xf3x\xa2~\xc9\'\xe5\xc9\te\xc1K\x01\xb9\xab\x04\x14\x7f$\xc8\x1bK\x10\x02f6\xa5\xb7Nf\t\x04\x81\xab\xa953\x8e\xe6\x06\xe9\xb9\xc2\xb2\x9e\xbdcm*\xbc\x9c\x9e\x0c \x1fVx\xbf\xce\xdeF\x94\x1c\xa7DS$U\x13xaH^\xf5\x02t\xf0\xf81\xcd\xaf\xc89\xf8\x7ff\x1d|\xfa\x0b-\xb3\x16\x16\xf3HM\x89\x06\xc4:\xe6\xce\x01\xe1\x99syjHJ\xa6\xb92-$%}y,\x1d\xe9L\x88\xe6\xb2k\xc0\xa7\x9f8\xa4\xca\xee\xd9\xe8\xc9\xc6\x80\x93\x92\x00_8CcS\x87\x10\xdc,/\xe9\xbax}.\xd0\xb1;\x0c\xae\xbe@\x07\xee\xe7t\\\xbc-\xd9\xb8B\xd2\xc4\xc5G=\x90\xf7\xc9\x94\xae\xd1+g\xafTLegV\xfb\x1f\x96\x9d\xe5v2\x85(\xb6\xad\xf5Y\xe9H\xe6\x12\x19p#@&amp;HIq\x1c\x06\xd2s\x92h`\xbc\xdd9\xa9\'\xd8=Z\xd2\xe1\xfd\x99cF\x1d5\x1f\xbd\x9a?DT\xd0\xd0l\r\x93\x9f\xe0R(\xb6h\x890^\x9a;\x08tI\xc6_\xd3$\xc0\xa5\x896\xd1\xf5\xd3\x8fH_j,\x1c\x9e\x0f:\xfc\xc4\x1c&amp;\x19\\\x99\x9e\xb3Gs\xa9\xf9S\xc6\xa3\x80\xd9\x88\x86\\\xdd\x0fte,\xef\xf8\xa19\x1c\xd3\xbbG="\xe7\xbae\xff\x87\x14NC\xa6\xc4{3\x1ei\xc5\xa0a-\xd2SEO~\xf4,8a\xc1&lt;\x89\xc4k4z\xfd\xc3\xc0\xaa\x8c\x0b0\xe0\xffQ\x1b\x18\x12~A\xa31h\xb9\xed\xa5\x84\n\xc2\xaf\xd9\x0f\xec\x97\xeem\x17;\xd3\x0b?\x9e[\x05\x91\xd5 \xc9\xa3\x1fr\xea\xf4\x8f\x0f\xb0\xe6D\xdb\x07p\xee\xd4\xd4\x99\xc0\xd4cI\xc8\x160\xc9q\x832\xcf\xde{\xcb-\x19\xea\xe3\xaf\x07\xf73d\xa5\x1e^C\xb9\x8c\x1b\x04\xac\xf9I\x98\xcd\xd6\x89\xfcHg9\xac(\xaam\xafh0)\x1c\x0f~\xa9\x19 {op\xda\xa2x\\\xb3w02q\xf8B\xbf1\xb3J:*\x94\xd7T\x86MzW\xbd\x10\xe4\xab!B\x0f\xb9\xbc\xf2\x86\xbd\xaa\xfd\xf7\xe5\x93\xef\xd7\x96\x01Psgp\x8b\x05F\xfc\x15\xce&lt;V\xfbl_\xfe\x00\x16:X\x11\x1dI\xb0\x99\x98\xbeFp\xfd\x11\xf2\x82\xf9\xd5\xb3\xec"\xbd\xea\x8c\x84mF\xfc\xb7\xba\x01\x935\x88\x1d+\xa5X9\x17\x88\x9e\xfc\x81\x07\xe0! d\x91\x91}`\x07n\xd5\x93Q\x04.\x9f\x85K\x88y\xde\xf0\xa2\x13\xc8\x8bI}~J\xba#\xd7\xaf*\x8f\xfd \x12M\x19\xe7\x1e\xcal\xef\xb4\xe6\xda\xfc\xe4\x16\xc2f\xae\x13\xb0?~8$B\xc8\xb7\x1e#\xee\xa8\x0blh\x1edc\xd6h\x02\xac\\\xf1x3\x8f\xbblX\xae\xa9\x04`&gt;\x8a\x9c\x8b\x1c\xb1\x1c\xa7\xb0_\xbe\xc5\xd0\xf5zR\x9c\xd6b\x7f\xccg\xb2[\x19\xb7\xdc\xfc\xb3\x10{\x19\xb0\xe2\n\x8fmA\xd3\xe04\xe9)t\x90\x8b\\\x1b0\xa4\xbfL8\xdd\x04\xb3}(\xe3\xf3qhV\x17\xd9\xb9\xb0\x185\x83y\xd6\xe1Zm\x0b\x97\'\\\xf0M\x14\x92\xe9Z\x14\x84\xc4\xaa\x81\xd7\x98\x01&lt;\x84\xa2\x0eh\xf6\xc5Px#j/\'\xf0:\xfc,\x8d\xa1\xd2\tc&amp;\x13\xbf$6\x0f0\x8bcA\xb8\x1c"}\xe2l\x0c\xdd(\xf79\x19\xbd\xb5\xd5\x1b\xb0j&gt;\xa6OB\x92\xa0\x02\x80\x0e\xb0Z\xbf\x06\x7f\xa8,W\xc0\x88[\x8dA\xe4\x118t5\x04\xad\xcco\xd7\x91\'V9P|!\x11\xda:\xec\xa5\xbc[\x075\xdf\x9eva\xaa*?.\x12\xf4\xb8*\xb0\xf0\x1d\x13\xc1-\xe2\xfcF\x17\xdf\xec\xa9&lt;\x1bK\x12\x95\x87\x17d\xa2\xbe\xe5{\xa8B\x02~\x84\x12c\xf9\x9e=\xc8~\x04-\xc5\xb8\x8b\xe1sv2\x11My\x0e\xda3n#\x8d\x07vE\xd3\xb9_\x8b\xd3ATg\x17)\x8a\n\x8d\xdfE:\xffX\xcdX\x8f\xb4\xc9\x95\xb2f\xe8\xdbZ\xf7\x82\x8f\xb4\xe8p_\x81v\xfa?\x16\x99O\xbb\xc7\xc0\xf2e\xf5;\xca\xa2\xa2\xcee\x9c\xccb\xfd5*J\'B\xbc2\x01\xc3\x19\xa6j\x95\x9d\x19\xd1\xeb\x8f\xc34V\xd5l\x9f1O\x9f\x00\xf1!\xcb1\x186\xf3\xc3\xf8(\x8at\xe6A\x15\xab\xe6\xde\xc2\xfc9\xa5U\xc5\xe3\xf1\xcb\xd8\xd1\x86\xf3\xc6\x90\xd5\x99\xf4\x8bPY\xca\xc1\xf1\xff\xd1M\xda\xe4h\x10\x06W\xd8f\x834n\xf6e\x12\xc6\xab\xad\x1c\x12o(QC\xda\xa8\x92;\xc6Dd-;\xb7\xfe~~v\xa2Ay\xd1n\xcaN;\x1e\x81\xbf\xac\x9d\xf7\xa6\x94\x834\xd9\xb9E\xdftI\\\x956\xbb\x01\x9a\x0e\x95\x9f\x89\x8e\x81g\xb1\x18x\x99\xc2U\xcc\x16\x84\xd9\x1b\xae\x1d\x15B\xcb\xb3^4\x12\xe4k\xd7\xd7\x04x\xfd\xfc\xe0q\xfe\x9d\xb0 G\xfd*\x94\x1e@\xcba\x90\xd0\xd4;\x89F\xda\xb5\x97f,\xa7\xab\x14:\'n^3\x830\x0b\xef\x03\xe8Q\xea\n\x16zo\xa6\x9b6\xdajlm\xd4\x0c\xce\x96\xf8\xb1&amp;`\xa9\xaa\x8c\xc18U\t`\xa9\xb0\x9c}\\\x93b\xc8\xfc\xfe;\n\x0f\xeeR \x94\xd3}\xae\xb5z\x99\x80)"\xa6`\xa8\x9f\xf7\xd6A:B-\x1d[\xb6\x8cN\xd2\xff*"\xc2\xf0X\xdc\xff\x88\x91l`1\x91\xfc\x0evV&gt;\xaa\xfc\x1b\xdf\xc1]@q\xc0\xe7\xb7q\xb9\xab\x9a\x11\r\xa7=\xcebz&amp;\x17?h\xa9\x0f\x11\xf5\xc5\xe6ZOu:\xb8aW\xd9\xd26\x88\xc6X^\xaf\r\tW\x87x\x9a\x87\x98[\xb8.\x862q_\xa5\xe8+\xfe\xd7\xf6`I\x03q\x08\x84F~Z\x9adH*\xdf*\xbe\xa0\xb8Y\x9a\x8e\x99w\xe4\xf5"W\xa4\x14\xe5\xb2\xca\xb4t\xd0=\xd5t\xf6"\xcb.\xce\xc6\xdc\xd4\x1b\x80\xe8iJW\xbe\xccF\xfd\xf9\xcc\x00\xbe\x07\xff\xbc@.E\xce,\xe0\x99\x08\xd7 \xfd{:\xfajol\x9f\xf84\x8e\x8d\x90\x11\x05&amp;\x82\xda\x89Qx\xaa-z\xfa\x90HHqnvb@\xc8q\r\x85x\xce\xacQ\xbbvh\xa0\xc3\x87\x04{\xa7+t\x9c=6\x86\xa4#J&gt;M\x98\x1f\xad7\x86pYf4PF\xd5\x94\xba\x01f\xbd\xcd\xe5\x88G\xaa\xd2\xe9\x17\xf3m^\x95\xc4\xe0"\xa0\xecVh\xf8w\'@\xca\xf0\xc0$\xd9\x88n\x82\xde\xf6\x13\xbf\x02\xca\xd5\xf8\x04\x9d\xe0}\xc9"\xf1\xd8\x9c\xd6\xc1\xbds?\xd8\xbfZ\xe6\x94\xfcl\xbc\x01\xa2vz\x05\xbd\xbd\xb6)\xf7\xcd\x18\xe2:\x84\x80&gt;\xcd6\xad#\xc2\xe3\xb0gqK\xf2\xad\xe2d3\x0f/;\xcd.\xf5\x93V\xaa\xc7\xa5\x05$\xd90"\xdb\no5\x06\x1a~\xe2$\xce3\xff&lt;Ua@\xa3\x1a\xabNk\x0f\xa6\x95\xbd\x8e\x9e\xde\x86H\x05i\xd6\xa9Rl\xc4!&amp;\xfeZ\xd0\xd3\xb7\xf5\xb6\xba\xaf\x11\xca4W\xe1 \xb3\x01\xb7\x89\xf1\xac__\xad\xf1\x8f\xa7\xb7\x84O\x9d\xaf\x05\xfc\x14\x0f\x0fv\x92e7\xd5T\x00\xd2\x81\xfa+\xbd\xf68\xba_\xcf\xd6\x95\x12\x96\xc30\xb4\xe9\xf6V\xc6 i$\r\x06qX\x97\x16Q&gt;\x7fj\xbc\xff\x9eM\xd9vt\xa4(\x0by\xf5\xe7c{\xd61\xda\xb5\xeaaM\x13\xe0\xe3\xf3\xad\xb8\xa4\xa2\xc92\x11\x9a\xc9\x14\xacO\xab\xf5B\xcc\xff\x96\xe7Z{?\xf8\xb3lI\xe9\xde{\xef\xc0\xd3\xdbd\xabw\xb1\xae\xa1\xcd1\xc5a`\xca\xc9}\xf3\r?j\x12\xd4\x1f\x8f\xf3\xc8=\\&amp;h5\xa7\x05\x91\xa90\x83\xb1\xe5\xf2\xd8\xaf}\xc0\xe0\xf2-\xb3%7\x0c\x98 \x7f\xba6\xdd7\x1eI6\xd6\xe5\x8c\xa5\x94\xb2\xd2\xdc\xe2\xab\xeb\x00\x98\xd0Q\x81\x1cz\xd0?*Js\x13~\x88.\x82\xe8`\xe7\x1aY\xa2\xbe\x90f\xb0EZM\xd8s\xa3\xa7~\xed\xf3\x1c\xb3\xcbx\x97\xd1\xfdIV\xa0\x0f6zC\x8e\x9c\xf39M#\xc4\xbf\x82$v\r\x9d\xfb\x14d\xdcuTf\x9d\x03+9x\xc1\xe3o\xab\xae\x01\x89tBd\xc2\x83\'\xde\x14\xbf\x13\xfb\xaa5S6H\x7f:O\x8e\xaf\xb7\xf8\x14\x17\x81\xacEO\xa4\xaa\xb8\x88\xe7O&gt;}\x0f\xd6Po\x15\xe5\x0eR\xc5O\xe5G\xe1QH\xdb\xb5\x1bE\xb5b&amp;\xee&lt;\x11\x84S\x97\x94\xc4\xa4w\x87)\\e\x0b\xec\xdfv_\xac\x1d\x89\xbe\xa4\xf0\x1bz\xe7\x8ci\xbeQ\x97\x15\xfe\xd8\xa4\x84\x83\x9c\xad\xca3\xed\xda\xf0\xeel\xaa&lt;p\xd0\x89\xd4"\x86\n\x90\xfcN\xd4d\xe2\n#q\x13\x98\xfc\xa9I(F\xb9~p5;\x13\xd3[\xd4\xf95\xe2^\xdd\xb0\x91\xfdJ\x191\x9c*\x05Rx\x15\x8c\xd4\xf0\xce\xbdqyp)DA\x16\x18\x97\x80@q\x1e8V\xbd\xd4\xbe\xb2\xa0\x08\x02W\xff\xea\xc5P&amp;&gt;a\xe3\x9d\xf4\xdd\x9b\x9c=\xb3\x83\xeb:\xa9:),\xcb\xf0es\xe2\x1b\xca^\xfa\xc2\xc4\xe8x\x95\xc92\xae7\x9f ^l\x93\x9b\x8bE\x89v\x16\x9a~\x19(\xb1\x11\xd9\xc8\n\x07\xb5\xf8\x0b\x8f\x16\xd2\x17T\xb7\x0e\x0c9\x0b*;\xc8\x86\xb8\x8b0\xc9\x81\to\xb4\xe3\x8e\t\xb02J\x1f\xa2a\xf4:\xd6H\t6G\xc5H]\xee\xf5\xeb\xecV\x8f_\xa9\xabq\xf8hl\x8f\xb1\xd9\xa4\x9a\xd8f\rY\xa7\xad.\x0bU\xf2\x97\xedp\xaf\xa6e\x04K=\xb9\x019\x99\xd0G\xa5\xa8&gt;\x13S\x90\xf0\x88\xdd=\x14\xedC2\xcf\x10y2\\e\xea\x9f\xec\xa6\x14\xf9\xb9\xbf;\x93K\xa7\x8c\xc5\xfae\xb5\xb5\xd9&amp;\xf9\x06\xc6\xa56\x90\x98\xd4u\xf4\x8c\x8b\xec\x0f\x170\x01\x81~(%m\x9f\xf9\x93\x9d\xed\xe9{\xa67\xc5\r&lt;\xdf\x11Ui\xd8M\xbf\xedQ\xd6HDj\x1b\x10\xd5\xfcR\xd5+\xe2\x8d\xec\x89lkF\x80g2\xa2\xb8\xa7[\x91G\x0f\x9b\x13|B\xf3WM\xc4c\xa3\xa7TO\xe1\x80a5s\xb9\xa2\x14UOs,\x92\xc3\xe7\xbci\x05\x1c\xe8\xc3\xc1\xbe\xf8\xee\x04\x0c\x13d\x00\x82a\xefL~R&gt;Tn\xf8\x1aw\xd2\xdf\x15\x17[\xc46\x0f\x05\x0e\xb6w\xe3\xb3\x8d*\xfa\xb0\xd1\xa2\xc3\x92\x89\x8e\xfc\xc4\x0c\xd8\xe4Fa*lnmB\x1f\xda\x8e\'\xaa|Q\x02\x17\xe7\xf7\x8e 1Lr\xd4DIC\x19\xc92\xeb\t\xfe\x92\xf9\x07N7\xc6\xe93T~\xa0\x16D\'QdA\xc3M\nYd\x9a\xccB2 n\x84]\xc6~H\xa5f\xbf\xc1\xad#vX\xf5:\x01\x92\xeeO\x1ft\xa2U\xc2I\x03H\xba\xf8G\xf5\xd9\x11:\x8d\'R+)*\xdc\rR3\xfb`bE\xa3\xf4-(\xb4\xd9)\xdd=(\x93P\xb3\x80\x9f\xeaj\xf5A\xdf\x8ee_\x17Y\xb7\x18\x07\xc4\xa1f\xce\xad\x9f\xe4\xd5\xbf\x04\xda\x94g\xe8-\x8eC$\xeb0\xe3\xd7\xa3\xfb\xedY\x84^\x00Z\xeah\xc1\xca\xdd\r\x88XH\x1fm\x01\x9e\xa2\xa3&lt;"c\xe8\x1f0h\r\xe3eQ\xf8\xafG\x0b=\x1b;\x86q\x94\xb6!g\xe2$\x9c\xe7$\x8a\xc4\x1f~x\x1a-\x98\xd8\xb1\xe0E@\xc3\xb5_CT\xc4k\xc09#\xbb\xf7\xcaZ\t(\xc1t\xdc\xad\x0cP\xd7R\xe5F\xdc\x98\xe0\x1d4\xc1}\x82\xc8\xae\x86\x83\x96\xb9\x97\xdc\xe9s\x1c\\\xe5\x0b\x13M7Kn\xccR\x8d\x95\xf8e\xc1\xea\xdf\xad\xbb\xd5ty\xaeU\'rD\xc8\x80\x89\xc5\xaf\xa8ES\x04\xa4}\\\xaa\x9a\x1cpRG\x1a\xd5\xc8\xeb\xdd\x8c\xa1\xfa+\x96\xdc\xcc\xf1&gt;\xe1\x9c\xe8\x89\xf0\xa4\xb0#\x81\xda\xdd\xd3\x89w\xc9\xba\x1b\xd2\x067\xc2\xa6\xa5\xca\xf6U\xad\x9b\xb1\x9c\x91\xdf,\x9b\x02\xc4\t\x8a\xdf\xee\xff\xca\x96\xbbRY\xe3V\xe84\xfa\xec\xfc\x9bkz\xb6mR\xf0y\x08\xd4p\xc8X\x96.:\x92{Uk\x81\xab\xed\x8f\xa9\xf5\xc2\xf3S\xca\xb1\x8b\x1b[B$\xfe\x9e5\xba\x836\x80\x97\x19S\x83\xa0ddh\xc3\x05\x10BK\xa4YJ\xf6\xe1\xc8{\xa0k\x0b\x9a4i\xb2\t9\xd4\xcb\x8c\xd0\xbd\x81\x00\xdev\xd9\xc7\xf22\x1f\x80\x96\xbd\xf8\x1f\xd0v\xec\xa7\x10w\xc2\xed\n\xf6\xb8\xddV\xd2\x8c\x12lG\x1b\xcd$\x04*H\r\xf07\xe6#\xb2\xceWn\x19\xadb\x91\xa2\'\xdb\xf5=\xdb@2lX\xe7\x99\xd8\xf5\x9e\xb1#D\x1e\xa3\x957\x13\x85\x0f=B42\xe6:7\xfd\x15\x00\xd1\xf9\x99D7\xc5\xb8\xcai\x13h\xb8k\xcd\x86\xa6\xc6\xcf1?\x03\xb0\xdf\xb4\'gM\xc4{\x8a\x12\x18\xf2\xef, P2\xa7\xb3iaSnJ\xc1\x9c\xe4\xf4\xdeT7\x07\x07\xe5y\x0b\x0e\xff\\\xd2\x15]v\'\xf77*\x92Y\xf8B\xde\x08?\x0fo\x8a\x8c\xb9pA\xae\x14,\xc9\xb0n\xbb1\x04\x9e\x9e\xd7\xd4\xbb\xac\xb07\xe6\xbcq\x076.\x8e\xe2\xdc:s-/\n\xff\xe9\xc3\xfa\xb6u\xa9kY\x19\xe8\xc4+\x1aU\xfc\xc0\xcf\xc0\xe2D\xcdT%&gt;"I;\x95,jmL\x03\tL\xc6\xa4\xed\xe5\xe2\xd8\x7fw\xa4\xe8x-\x01z\xf3\x99\xbe\x92\xfc\t\x80\xb5\xd2\xdd\x87\x19P\xaf\x96\xda7O2\x8e\x93\xe9\x15/ww\x17\x17*"\xdf6 \xd8\x93\xad6&lt;\xab"O\x06o)\xc7\x07\x13\xc3z\xedG)\xa1-\x00\xf9\x16n`\x1a\xc4ig\xb0\xb6\xc8\x9e\xe6\xef\xd5?OM\xd4\xdf=`Zo\xab\xc5\xaa\x81\xfa\x985U&amp;\xa6\xc7\x17c4!QZ\xd0$&amp;4\xc2\xc4o\xf9\x92\x1a\xc1\x9e\ni\xe6dc\x01\xa62L\xff\x83^\xe6\x07;\xa1\xa6\xdc\xc8\xe2\xa12d\xfcx[qmL\xaa:L\xe2&amp;\xf0\xc9\xa3G\xd5\x80:\xce\xe9t\x87U\x8b\x9c^\xd0Ar\x98K\x92\x8cj\xfb\xc5c\xfe\x04\x10\xac\xa3Q\x9a\x9c2\x90Hh\xa0\xbe\nWs$\xc7~h\xd9\x8df\xe4\x14(|\xbd[\x18\xf0$\xea\xd2p\xf4\xa6\xfcX\x1aQ\xd6/\x8b\xd9\xb3h\xdd\xf2\xa7\xd1\xfcZ\xd1\xf4&amp;\xb7\x14\x91\xd0\x9dH\x05%C\xb1\t\x9c\x992e_\x96\xba\x11\x85\xa2\xb3\x80\xad\x8e\xc7\xbbc\x03;\xc9\x10GK\xbd\x8e&amp;}\xf2\x17\xa7\xcfY\xde\xa8\xf4\xb1G\xea\x83X\x12\xdc\x02h\x05-a`\xd3\x0bs\xf4Y\x1f@\x1e)\x9d6\xb6Y_p`Ha\xfb\xe8\xa9\xb9\xc6\xb4\xb0\x9e\'\xfb\x12x\x91\xd5U\x92\xf3\xc2\x80v\x1a\x93\xcbq\xd2{_uv}\xeaD\x11L\xc9\xc9\x11\xd2\x12\xec\xff\xb4\xbc\x0f-\xf0\xea\xf8\xe6o\x0b\x88\xae\xfd\xbet~\xaen\xe94\xbdR#)\xfd\xe8\'\x177\xb0\xa5\x8d\x10\xd7\xdb\xd0\x12m\x06if\xcf\xa8\x90\x9a\x90\x89=\x1c\x06\x18`$\xc4B\xe1g\xc5Ii?\x0f\xe1\xc2\xa0\xf8\xbc\xcb \x92T8)_\xcaIQ\xd7\xd2\x87\x08J\x14o`\xd4\x10:\xb4\xe5\x1d\x90\xc2HK\x97/\xa4\xff\xf1\xca\xaf\xdd\x84V\xac\xbcLt\xce\xd6\x917\xa2\xa9?\xc7\xd2\xef\xa4_9\x89\x8a\xaa@69\x89\t\x94{\x01\x1e\xe0:\xd4\x06\xb5\x7fWVC\xcc\xef"\x12$&amp;?;x,A\x17F\x85ky\xba\xc2\xdf\xd6)0\x1e\xd1T\xbf\x89\xb3\xd1(\xbbyiS]u\x90\xb1\x1dI\x85E2\xf7\xa3b\xb3YI\x10u\xa4\xbc\xe7\x08\xc8\x8f\xd3Y\xe2M1C\xdc\xea\x0b\xc8M\x9b|T\xbe\xd8\x8b\x1cn\xe8\xa6\x14+\xab\xa2B\t\xe70J\xf0\xe7\xed\xfec\xec\xa0\xc2#h\x9c\x10eK\x19\xd5N\xc7U2\x92\xac \x1d0\x17g2\xd7\x97t\xe4\x92\x10b\xa9\x02E\xdbl\xa4\x06z\xb5\x04t\t\xa7\xd9@\x08\xd3\xc6\x90d\x9a\x1fg:\xc5 5i_\xfb\x84\xa4Pl\xc4P\xb5\xe5\x94\xaf\xc6\xef\xe3\x05.\xcfa\xb2\xffl\x1b\x91\xd9\x19F\xad\xef\xfb\xc7\xe3\xa1/\x92\x08\\\xe2p\xe7o\x96\xdd\x9b\x10m\xe9vM\x85\x17|\xd8\xc6\x17\x0fR\xbc\xb39\x8aUN\x88\xd1\xa6]\x02\x88C\xf3\xb3\xd1Fb+\xe4\x04r\xe0\xed\xe1\xdb\xc7\xbd\xcd\xfc&lt;\x8b\xb1\xb2\xd3O\x88\xf8\xe5\xc7\xff\xb31\xcd\xf2\xc9\xc7\xed\xb0=&lt;&amp;\x95D\xc5\x84`\n\xf0\x15\x1fre\x881\xda{\xe2\x88\x06\xdeH\xf7\xd1\x93\xe5q^\x80\x95M\r\xbc\xc2\x84\xee\x0b\xf8\xb4\xcb\xe5\xe8\x9e\xbd\xfd^E\xa4\x9a=\x04\x8b\\\x9cR{\xaa\x13\xbb\x07y.%c\x84\xf3\xd7|\xe8c\xc9F\x08\x99\x1d\n\xc7\xd8\x00{\r{S\xe0\xa3$\x1a\x07\n\x82w\xd3\n\xc7\x1c\xe6\xe7\xca\xc8\xd8\xde\xad\xc0\xb3\xda4\xaa7,\xd2l\xb8\\\x1c\x9e\xec{\xde\x9c\xa2\xd1\xf6B\xcf)m\xf0QZE@\xc2,\x93\xd1\x07\xd5\xbf\x1b\xc7+?\xdd\x96&amp;&lt;G\xe7\xbe\xacL~\x9d\x86S \x100#\xa8D\n8\xd4\xde{\xcd\n\x00\xa6Y\xc1\x8a\xa0p\xfa\xb3s\xa3\x1e{\xfa\x85\xfb\xe5{g\xb5\x08\xb0z\xc0\x85ul\xef\x183\'V\xc4l\xbfi\xc1\xe8i\x0e\x1f\x11\xda\xc1\x19\xe4\x82\x15\x11o\x8b\xcb\x06\xc0v\xb9\x9a\xcc7\xb2C\xf9\xcb\xa8\x0ey\xd4\xd7\xcf]{\x92)\x98\x1bzs\t\xb6Q[\xc5\xdat]s\xe8\x15\x83k\xda\xc4rG\xfc\x9a\xea\x1e\x8ad+\xe8\xae\x85\x07\xda=]\xd4\x01Z\x86\xc1f[\xb0\x0c\x85J\x91\x97\xbe\xbc\x8dQ\xa1\xdb\x13T\xe0d\xcdsJ&lt;?\xf1V\x99]\x9aW\xd2\x14%\x80,uV[\x8cF\x05\xe1\xc7_P\xd3\xcaD\xea\x168\xb9\x85\x8d=\xe0Y?g\xb3\x05\x93jZN\xdd_\x04U\x8aF\xc9\xf0v\x15c\x86\xbb\xdd\xad8{\xf3\xd4\x90\x1bf\x7f\xf9\xe5d\x1ee\xd3\xc2t\xd9\xeb\xa7&lt;D"\x10{\xed\x89\xbb\tm\x97\xfc\xb6[\x07\x0f.\xd0\xd2U\x8e\xc7\xea!+\xee(;\xfc\xd6\x814\xe4EJ\x84;\xdb\x1cX\xff\x16\xf4\x95\xa8\x1f\xa6\xa0\xaf_\x883\xbdtw\x05\xb0\xcb=q\x06y\xf3ie\x083:\x1d\xdd\x9a\xf3id\xb0\xc3o.\xafs\xce\x97\xfeM\x89\xb3T\xe6\xb5-\xe3\xb5\x11\x8cs\x85\x9e\r\x94"\xb0A\x86\xe2jE\n\xc7[\x82\xd9\x03\xa2\x9f\xdba\x82\xf1j&lt;@J.\xca\t\xc0\xb8\xce\x90\x9d)D4\x88\x92\x86\xe2m*,\xb6\nm\xa3\xd2]\xd1\xdc\x80\x87\xd4\x84\x9aWIu/\xa1\xb5\xda$\xa0=\xc5\xc8d\x80;\x8dR\xeb\xf40(\xe9\x95{\xf5\x1c\xef.\x97\\b7\x16\x98h\xe2M7D\xc1\x9a\n/\xe5.x(\xa1\xd9\x87\xbd\x96`cfm\xf6{L\xd6\xeeIKVXb\xedSm\x10\x8f\x1a[F`\xb9\x05\xff\xdf\xf3\xbe\x15\xf4\xbd\xf1\x195\xae\xedu\xa8\xfe\xa0k\xb7\x85j\x83\xac\xa1)\xd1\x80T\xd5\x90\xf5\x0e\xd2\xb7\xd3\xf4\xc6h\x16\xe6K\x0b\xacC\x05x\x94\xca75\xa4\xa1s1\xc6f=WFY\x95\xa1#\xd7/+\x8a\xa4\x02`\xa7Q4\xf6\xde\r\x12\x8a=\xd6\xbd&gt;\x8fD\xf2p`\x0f;\x8bJYr\xba\x9ctv\xea3\x03\xb7\xca\xe3\xc9e;\x85\xf6\x98\x10\xe4\x99@\x08\xda\x82\xedd\x99\xd8!\xe3\xd7\xef\x8dk\xa8\xb3\xb6\xd3\xbbiP\xa3&amp;\xfa\xf8v\xb9*jei\xf6\xf3/\x85\xf7\xca\xe9-`\xf4\xf2F\xc3\xb7\x1a\x9f\x12\xaf\xfb&amp;8\xe8{q\x86\x14a\xcesp\x89\xb0*\x83wu\xeb\xd8\xf1`P\x19v\xf4e\x83AK\x0b\x92\x04tn&lt;\x17\xb2\xc9p\x04\'Z\xb1l\xff\x131|\xae:\x94\xfa\xc6\xe3\x94\xde5\xd8\xc2\x81I\xa3p\xa9\xfbC\xc0\r@\x8f\xc7\xd41\xe0\xc0\x05U\xd2\x17\xf1\x8c+\x97m\xa1Zl\x8aEB\xf7\x07\x85\x84\xa6\xca\x8b\xa9\x1cr\xc2\x0b\xaf\xce\x17\xc8\x93\xef\xc6\xaa\xa1\xfe\x8b\x08\xcdu\x7f\x11Q\xd4N\x8c\xb1\xc26\xf3\xd8\xd1\xbb\xc7\x91\xe5\x9d\xf2\xb7\'\xfe\xdb\x0cl\xc4\xc9\x01\x03&lt;Y\xa4\xe8\x07J\xa4\xc0\xa4q\xc2\x9b\xa6*\xa0\xe1)Z}q2\xad\x93\xd8iy/" -\xb4\xe9\x1ay\xc2|8\x16\xf5\x08;\\qs\xd5\xb2\xfaP\x10\xaa\xb1\xcaw\xe0\x0e\x14\xa1jY#\xb9\x82\x0cw\x84\x849\xd8O\xd3\xb0O\x87\x95\x8b\xebf\xc9\xedk\xc3\x97\xb5\xd3\x9c\xc8\xdd\x9e\x0f\xaa\xb5\xdf;`\r\x191\xbcc|S\x88P\x98O\xd3#\x84\xe1\xce{\\\x7f\xa5\x16\x16\xcf\xd9\x86)\xa5\xf1Px\x9c\xfe\x81\'\x07\xfc\xf7r$\xe7\xfa\'Q\xa5,\x1b\xd4?\xca\xdb\xa2G\xd4\x7f\xa4\xc0\xf7\xfdb\xca0S5\x02 \xc5\xad\xcd\xf3\r\xc2\xf1\xae\xfe\x9b\xf1\x9a\x1fQM\xac\xb6m\xb8\x14\xb7\x8eFVM%!i\xc6\x98\'\x81Y(\x9f\x02\x07K\xc6o\x1c\xa0\xdc8M\xee\xa19W\x82\xe4\x85U\xd0\x9aJ`N\xdaM\xfaK+\xe22\xfcp&amp;kk&lt;\x95\x9f7\xe1\xc8\xd0\xbc:\x96\x17K)&lt;\xfd\xba\xec$]\xfc\x07\xdaZ\x89zt\xbf\x84\x06B=\xfa\xaeB\xdc\x8di\xd2&lt;\xa0QZ3\xfc\x9ap5\x8a\x8f\xd8\x84\xfdX{\xb5\x03\x82E\x9d\x9er\xa2=\xa0\x9e\x1f\xf1O"\x8dV\xf6\x8e\xa6\xbd\x94?\xf4\xd3\xef\xddc\x10\xe0\xbe\xb3\x99\x0c_\x95\x7f\xaa\x9f\xeeK\x17\xd9\x07\xabx;\xb3\tG\xbe\xb4v\x99\xa1\x13\x16\xa1U\xd9b\xdd\xe51e\xd8\x04s\xa9\xc9\xc5\xd6\xc7\x9c\xc6R\xe8\x17\xbf\x8a\x96\xa2\xe2\xf4\x08\xb2\xf1\xf6s\x00\xe4\xef\x16\xeb\xee|\xfc\xb6\xb1\x83@\xd9R\x8b\xd9\xfc"\xdc\xdaH@\xf1\x94\xdc\xb26\xd8!\xae\xa03D\x8fO\xf5k\'\x8c\x06\xb4aw\xb11x\x178s\xe9\xf7\xb6\x1f\xea\x8ag;\x14\x18l\x07\x002\xb0\x9d\x05j\x05\x1f\x81\xd8\xa0@ \xd3\xb5y\xda\x85\x87\xe9\r\xca\xa80\xd7\xb1\r*\x1f\x1a\xc3\xfa\xdc\xeb\x878O\xf3v\xd3\x0c\x12m\xd9\xf8Q\xe8$l\xf8\xe5M:)\xa1\xf3Y7\xc5\xbe4p|\x86\xd7\xa5&gt;\xce\xebJBx\x9cQ\xf4\xd5\xf6\xb1\xd0W\xa0\xcb\xc9\xe35\xe9\x81\x03:3`\x98sW\x16l\xe3\x8c++\x16\r\xbb{\x04/\x0fV\xb5\x8d\x92K\xb8XRA\x19\xaab7\xd4\x7foVrd\x88\x1c\x1c\xc0-(\x19\xd8\xa2\xe8\x99\xdd\xdc\xbb\xe50r\xfe\x1c\x9c\xe0\xbe\x19\x7f\xc6\x8b\xe9\x1c\x8b\x1d\xb1\xdf\x17\xf8\xf8\xa7|\xf8:\xa1\xe1\xe0k~Y\xf8\xd1&gt;\xa3TJ\x8d\xb3\x02E\xf7V\xf6\x84\xa3\xe9T\xc5\xe0\x9b|Q\xa5\xf4\nhd\xa0\x01\x84@\xca\t;\xcd]\x83W\x0fz\x0bs\xe2\xde\x04\xf8\x19,?!7\x9a\x8d\x82</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Mini Bateria Infantil Completa Com Banquinho Instrumento 5 Tambores Brinquedo Menino Criança Kizumba Sortido</t>
+          <t>Kit 4 Potes Acrílico 3,8l Organizador Geladeira Rebirth</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>64</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>199</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>90</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>58% OFF</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/mini-bateria-infantil-completa-com-banquinho-instrumento-5-tambores-brinquedo-menino-crianca-kizumba/p/MLB62681535?pdp_filters=item_id%3AMLB6011420542&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB6011420542&amp;sid=affiliates</t>
+          <t>67% OFF</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_758915-MLA99952945695_112025-AB.webp</t>
+          <t>https://www.mercadolivre.com.br/kit-4-potes-acrilico-38l-organizador-geladeira-rebirth/p/MLB56422271?pdp_filters=item_id%3AMLB5721467738&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB5721467738&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>b'RIFF~&lt;\x00\x00WEBPVP8 r&lt;\x00\x00\xf0\x1e\x01\x9d\x01*\xc0\x01\xc0\x01&gt;m4\x95H\xa4"\xa2$"\xf3\xdbX\x80\r\x89gn\xf4\x99R\n\x89\x8e\x1fr\x07\xad\xd8&amp;o|\xe9\xfc\x0f\x1b\xd7\xc6\xf4I\xf9\x7f{o\x98\x0f\xdbO\xd8\xcfv?\xf2\xdf\xb3&gt;\xec\xbf\xb8z\x80\x7fD\xea\x19\xf4\x10\xfdt\xf4\xe8\xf6X\xfe\xff\xff\x0f\xd2\xbfT*b\xdey\xfd/\x7f?\xa0}\xdf\xcb\xd2\xf6\x7f!\xe0\x87f\xcf\xee&lt;\x11\xfd\xd3\xf9\x7fB;\x9ev\xe1o_\xeb\xffi=\x82\xfd\xe3\xfb\xc7\xa3\x04\xd4?\x1b\xd4\x0f\x877\xee\xbe\xa2_\xce\xff\xcc\xfa\xca\xff\xbb\xe6O\xec\x1e\x9e\xcfh\x9f\xbc\xbe\xd2%)\x91\xaa\xfa\x8d\x94l\xa3e\x1b(\xd9F\xca6Q\xb2\x8d\x94l\xa3e\x1b(\xd9\x02\x10\xff\xfa\xe3\x19\x8c\x87Py\xc3\xa1&gt;?\xb1\x1d\x8ci\xff\xf1\xc5\xf5\x1b(\xd9F\xca6O\xfbk#\xf3\xedR\x80l\xcf\xa4\x7fE\xfa\xbd\x934\x06]\xf2Q\xd8\xfa^P\xd0\xbd\xf6Q\xb2\x8d\x8d\xa1\xbd\x1e\xaf%\xb8\xdd\xe6\x9cx&gt;\x8b\x08J\x03\xc4\x10\xd9\x13\x19\x1bI*\x87Y=\xba\x9bC\x8b\xf6\xe37S\xff\xfd\x91\x7f\xe2\xa4g\xf1w|^\xe9\x0b\x84\xb4\x89 ]\x1a\xc4\xbd\x1b\xf0"2&amp;-\x0b\xd60\xb2\xba\xa2\xa1z/G\x94\xf6\x9eG\x99\x9a\xfa\xf3\xb4DTY\x90\xbe\xdfD\x1c\x04W\x02$\xea\xde\xfa\xc3\x99\xd4+N\xe4\x92\xf1/\x82\xfe\xf3\x9a\x96%\x8ek\xc8?&amp;&amp;\x93\x9e\xb6\x02\xa6\xf0~\x8c`\x99o\x83c(\xfd\xaa\r_\xff\xfc\xc1\x8d\xc3~)\x0e\xe0\xe3\xfc\x87\xfc\x1f{\xb2\xde\x96\xc8;\xd6\xd0\xcdZ\xdd`\xfb\x00f\xc1\xab\x98\xbeT\xfc\xbd\xadX\xbd\xd02D\xb0\x1f\x11\xfc*\xd4"#:\xf5\xaf\xc2\x07S\xa4Mj\xebfF\xe6\xfbZd\xb7\xef\xa1\xd2fg\xd7\xc3\xf1\xcd\xca\t1\xd41\xc1\x1c\x05\x08\xe9\x92\xe4g\xb4\r\xde\\Wwcq\n9l4\xa6\xee\xcb7\xae\xa9\xa8\xda\xc2\xbf\xf5\x1a=\x99\r\xea\xfeo\xee\xca\x0c\x9f\x01\xe8#\xb6\xc5\xe0|\xb0&gt;WQ\x14\x9a\xf6T\xbf\xd7%n\x17\xf6|q$\xbd\x91[\xf6p\xa2\xe7\xa2\xa9F\xfa\x03a\xdbre8\xc5?9\xf2\xaf\xd6\xff~9\xcd\x10\x90z.\x97\xeai\xc9\xb0\xe8\xd7\x08-\x9e\x9f\xf4Q\xdeK\xb0w\x11\x0e\x15\x9cg\xec\xdd\xfe\x8f\'\xc6\x88\x85ZJ\xce\xb8D\xc8]NFV\xd6Y\xc1xf\xe5\x82\x13\xb1\xa8{.F\x8e\x89)\x0e\xd3\xbd\x06\x89\xd1a\x7f.A\xf7\xc6\xbe\x8a\x08\xe7EoQ\xfeX\'\xc3\xba\x0bnm\xe6R+\xe9\xe9\x03+\xa0VR]\xbe\xa3\xa9\xe2\xda\x13|.\xab\xc2\xd1!\xbcBp\xab@\xed\x87@8\x96\xd6\x91\x91)\x056\x94\xc2\x1d\xb5)\xe9EI6\xea\x82a\xfc\xb2\x0ej`\xee\x18"a\x84\xf1\xbcD\xb7\xc6a?^]H\xba^\x17?r\x92f\xfe\xe3\x1d\t=\xd5-\x9dh\xa2\x80\x0c\xab\x19\xc5\xc8\x1d\x18n0&amp;\xc1\xd5\x8ceP\x99\x1d]\xa6\x08+U\x16\xc2&amp;ti\x886`\x94\x82\xcfN\x86\xd5\xf6\x1f\xc0^D\xe7o\xb4rE\x99z\x1b\xfc\xd9\x9e%@\xcf6\x84I&amp;w\xfbF\x1b\x97\x0fq\xeb\x03\x81\xda\xc3?\xe2sy\x13\xa4V\xdfD R\xe2\x94\xfc\x1fIz}ol\xb7\xbd\x0b\xde\xca(g\xfa\x1c\xb4^B\xd5n\xa0(\xea+\xba0\xcf\'A{\xce\xe4^SiU\xb6\xd7&gt;?c\x1cxt\xe1\xe5\xc9j\xefS\x92\xeb@\x86\x82\x14\xf4\xfa\x10\x00\x81p:\xe0?\xf2\xf5\xceU\xd9\x12\xb3-\xcb\xaf\xd94gF\\\xdc\xd8\xcc\xec2\x9eE\xd4\x80\x0f\x92\x9d\xe8\x08X\xbd\\\xcbB1\x06t\\\xd5\xaex\x97\xe7\xcfn\x01*\x1f\xec1\x9ai\'\xe6\xa3\x1fS\xdf]cd\xfe*\x00\x02\x9e\xb2\x0ekJD;T\xf8\xd5\xf8onQ\x8f\xfez\x9dI\xc9\xa8\xc4,\x00\xae\xab\x83]m\xb1-3\xeeM\xf70\x1c@\x8e\x9e\xdd\xfe,X\xdaF\xca\xcd&amp;\x9e\xe1\xc4\xb5\x9b\xfa\xb7\xc3\xb8\x15\xbb;\xb4\x00\xf4i^\x9aW\xf4\xc7\xa3\xeb$\x93=\x16\x8b\x9fVqz\x14\x08d\xd2\x0e7R\x1d\'\xad$%\xa4\xebR\xe4\x92\xbe\n\x97\xbf\xfca\xecI?l{\x05\xc1\x92Y\xdc\x02L\x11\xe7\xa7\xdb\x94u\xd9T\x13\xb3l\xec.\xa3\xff!\x87%\rV\x18\\\x08\xcd\xfc\xcd\xfd\xd4\xf9"\xf3l\x8d\xf3\xc7)\x02t\xebF\xbf|F\'\xbdJ/\xe9\x80\x14\xba\xf0\xb7\xf0\xc9\xa5\xe37;\x0e_\x0e\xb3rb\x8ap\x8dBx\x16Z\xf1\xeeAg\x81\xa3\x9096\xb3\nB\xdc8\xa9\xa4\x1eL\xb8\x9e\x06a;\xce2)\xc2\xca\xe4hlY\x98x\x12e\x93@\xc1\xd0\x19K\xfcC\x06`h\xea\xe3\x9dO\x17\x10\x04;\xbf\xc0,\xb5r\x1d\x86\x08\xef\xb4|\x1b\xc1\xd8\x7fO\x90\x8e\xdd`\xcbo\x8e\x1eE\xd8dM\x06\x02\xccx{\x01\x86\xe0\x19\xa5Z\xdc\xd8g~\xdd\x0c\xc4\xdedO\xecH\xe9\xa4\xd2F\x87B\xe1@\x8e\x8d\xe4N9\xab\n\x94\xfe\x1a\xf8$J:\xc6n\x9fQ\xd6\x8f(Q\x1c\x02\x92Jf\xe0K`\xbfN\xd8\x91T\xb9\t\x01\xd5\xd29e\xbe\x8d\xa5\x01N6\x1b\x054O\xd5m\xd1B\xa7P\x06\xa0t\x8b!\x9cv\x9c\xa4\xaf6&lt;N@\xb2R\xb6t=\xbc\xdd\x01}Y\xd9\xf5\t\'\xd2\xee\xf1\x9eoNJ\x1d\xdf\xb7\x95U\xb4C\xfd\xd4\x89F["\x97\xd3\xc7\x10\x1f\x93\xbcc\xa3\xb7\xe6\x97\xc2W\xf1\xc5\xf1\xc7\x06p\xf4z\xe85\x82\x02.\xc9xL\xcb\x11\x81\xc4Wg\xee\xf4z\xfb\x05\xd6\x1c;*\xd0\x8a\xc2\xc8\xd9FU&gt;/\xb4\xc94\x9b\xf4_\x89+\xff\xf9\x06\x92\xee\xf9\xa0\xf1\xee\x92\x1e\xba\xd0\xf2frd\xcb\xf0o\xe74\xc2\xa7L\xaf\xd0\xeb\x95\xef\xf7\xafL\xb3B\xf54\xd0\x17\xe5\x04\xfd\x7fD\xa8\xa4P\xec\x15\x0c\x08\x92\xc0;\x08\x10O&lt;\x9a\x84%\xa4J\x1b-g\x1b\xfe~\xa9a\xd3S\xc9\x98i\x90\x89\xd9\x0b\x88\xf8\xc4Vp\x9d/\xa83cV[\x1d\xcf\x9e\xa2\xde|\xdc\xcd\xe5oY\x94{\xa63\xbf\xc7r+\x1b\x9d(\xe2)\x1a\xf9\xd6\x9f\x9a\xee)\xbe\x16\xb68\x10\xfc\xfbE&lt;\xf7\xa6\x04\xc1],\xb4}\xa2\xfa\x87\xacG\x8e\x1d\xbbH&amp;4\x88|\xb0\xa3e\x19\xd89w\x18p\xfcv\xf0C\x80\xd9\x86\xca\xc4~\x0c\xcd\xa1\x9az\xb1\xf8\x05\x0f\x9aI\xcdu\xc3E\xa7\xfe\xf5]s\x7f\x91\xe9\xa3\x13u\xd1\xb1;\xcd\xcb\x19k\x87\xa8\xd9\x9d\xf1\x10\xbd\x15x\xbf?\xcd\x90\xfc\xa9\x1a\x1b:qZ\xf1\x02\xf1z3m\xbb\x919i\x85W\xe6\xce\x0b\xa3\x05\xe92Mw\xfb&gt;\xe7\xe3\xc0\xf4\x89BZ\xb0$\xed\x06\xb9\x98\x83\xfc\x8b\xdc\x11@\x8c0X\xbb\x0f\xc9U\xdc\x92\xf2\x86!\x93U\xc9\x10F\xdf\xe7V\x03c\xc3$\xea\xef\x87\xe5\xed\xa0\xd0\x15gec\x83\xe4h\xc1h\xc1\xd4R\xdf\x14.\x00\x02]\x94h=M\xd3\xeb+\x17\xaa\xc7#\xc6M/\xd8aV\xb9\x98\xcb\xc0\xc2y\xe9\xb3\xcf\xe79#\xf1A\xbdK\xb4\xc8\xd9\xd3p)y\xac4gH\x864\x1c\x05\x9dC\x04\xd8;\xfa\xf5x\x0f\xec-\xc5\xb0\xceR\xa7\x1d\x8a$\xbe\xac\xdal\xb0\xdd\xe2\xb8\xda-\xb9m\x15\xc4\xe4)Af}\x8d\xca\xd6\x1c\x13:\xb5\xb2\xb7\xc2\xd9\x93+\x08X\xb8\x90\x96\x19v\x11\xfc\xd2\x9f\xdc\xc4\xe5nQ\xd8\xfadh4\xa7\xfc\x11bB\xd2&lt;\xf6%\n}E\x10\r\x1c\xa1p~\x10&amp;\xd21\xb8\x02:\xc0b:\xe0X\x90(-\x1b\xa2\xe3=u#5x"\x12\x14?w6\x1f\'\x04\x89\xfe\xc1\xdf\x1a\xb9\x0c\xa2nX\xa4\xaf\xb0xJU\xfa\x9e\xb9\x94\xd1\x83\xd4u\xdc\x8e\xe4w\x08\xc8\xa88/b\x03\xd8\xd8\xd0\x82\xc2\xdd\xe4\x89\xf7\xc9a\xbbl\xa2\x06\xd2?;g\x8f\xe1\x9aQjc@\xe9X\x15\xe3\x03p}\xd2\xf7\xc8\x95\x9a&amp;\x05\xd2\xb0:B::\x1b\x9d%\xcf\x88\xd1\xea:\xeeGr;\x91\xa1K\xc3\xd5&amp;@\xba\x05z\xf6xr;\xc4\xa4\xe3U\x8d\xb7r\xf6\x0cJ@\x0c\x0fg\xe9}8\x84L(\x06`\xb4\xef\xcd)WK\xbfL\xb1\xfc\xa6\xb9+_R\xf7B\xd7\x1e\x14l\xf3S\x15\xfa\xb3L6\xee\xdc\x1f\x88?\xdb\x94v&gt;\x98\xf4\xc8\xa8\x84\xf5X\xe2\\ihmE\x93\x83\x96-\xb6\x9f\x882p\xd2XV\xbe\x139X\xc5\xa6e\x93\xab\xca0\xe5p&lt;\x82=\x10\xb5\x94=\xdc\xab\xd7\xbft\xd8\xc1\xfd\xb9\xb1\x92\xb2R\x18\x95\xd7\x01t\x8a\xbc\xe9\x91\xaa\xfa\x8d\x94l\xa0Q \x9dm\xf2\xe8\x1c\x14\xd3\xb3v\x05p\xd1\x88Wm\x0ci0G@\xe5\xb7\xa7\xf8\x8d /[SRE\x11\x8fO\xf2R\xdf\xf4\xb9\xea\xc9\x1f\xe6d\xf4\x9b\x8fCu\xa3t\x86f\xcd\x837_\xc7\x17\xd4l\xa3e\x1b(\xfc&gt;-\x82@\x98Y\xd6FO)\x1f%1\x05\x81^\x99\xd5\xb1Z"\xd8Z\xc3\x04\xb3G\x14\xee\x08\x0e\'\xc9j\xdf\x90\xa0\xe5&lt;t\xb3\xd2\xf6\xb8A\xb2\x8d\x94l\xa3e\x1b(\xd9F\xca3\xeb\x18%\x98\x96\xf2Q\xc0C\x95\x9d\xde\xd5\xf8\x10\x91\xaa\xfa\x8d\x94l\xa3e\x1b(\xd9F\xca6Q\xb2\x8d\x94f\x00\x00\xfe\xff~\x80\x00\x00\x00\x00\x05\xfa\xe7)r\x04\x02xP\xa4\xbb`?Os\x80\xaedM,\xb7\rYGv)*3q\x9cBnle(\xc7;J\xf0\x0eC\xae)\x93\xa4\x08\xe3v\xd7\xdd]\xc4\xd1\xaei{b\xdb\xf1\xd1\x86\x86\x11\xdf\xfb@\xe6W\x166\xa7d\x11\xc9$\x0f\xa99BOo \x00C\xc6\x01\xc4\x8d\x8cs\xf7&gt;\xe7Y\x13{"\xfb&lt;\xb3\xeb\xe7V\xe1\xed\xbd\x85\xea\x97\x98Y\xee\x1d\x80\x994\xe25\xf7\xf1\xc7K\x8f\xae\x94D\x95sxZ\x07\xa8\xa1#\x1bo\x9d\xec\x96\x06&lt;\xed\xedn6Jq\x19=\xb0\xda\xbc\xf7\xd6\x9dL\xb3\x9e\x02\xbb\x1a5\x10\x11X\xa1\x12\n`f=\xdd\x7f\x13\x00Ws\x0eg#Y\xd5\x8c\x13\x11b\x97\xed\x0e[\xe7\xb6+\x85\x1fv\x7f16\xcdf\x1at\xc7K\xc0\xe0U\x15G,\x11\xfe\x18\xdf\xa8\x11]i\x1e\x7f\xc8G&lt;\xc9eD\xba.\xc2\xc7\xbe\x932+_\xd5\xe7H\xadS.\xd9\xc0\xc7\x92+\x1c\xeay\xde8c5b\x1ecR`\xd2\xe2\xd8\xfc\xa2\x9e\xc3)\xd2Iy\x08{.\xa1\xc7W\xc1\xf2\x9bf~\\\xc0&amp;\xea\xf9,Y\x99\xf3\xd5\x17^[j\x15}\xdd|L\x9e\x80\x18&lt;8\xbc\x92\xf2\xb0\xc3o\xf0\x06\x85=\x03.\xcd\x0eR\xb7D\x14\xd3\xda&gt;\x8a\x7f\xb3"\x8d\x94\x19\x19\x8e\x1a:}&amp;\x87vU\xfc\x12\xfbx\xf0\x12i\xb3\xffU`!#\xec\x96\xc3\xb2Q\x0c\xaf\xdcQ\x99m\xff\x8dCE\xf2I]\xd3{\xf4$\x8b\xc8&amp;YW\xd7\xd7\xf6\x04m\xb7\x8bm\x99\xa9\x14sz\xf9\xf6)\'\xb7\x1do\xa8\x1c\xf0\x90\x16\x18\x8a\xed\x812e\xa0&lt;\x16J\xb4\xbc\x8d\xb0#pF\x8e\x9f\x8d\xc0QSW\xae$\xa2\xc6\xb4\xc17\xf1t\xb2\xcamS\xdc\x9f\xd4\t{\x97V\xec\x0f3ZCg\x8eo\xe5\x19\xf7\xefl7A\x85\xa2n\xf9\xb3\xd8\xd1\xf8\xf6l\x82q\xe5fB\x97\x02\xf0\xd1U\xabVk\xce\xbd\x95\x96`\xc1F\x7fR\xf6\x19\xb8\xec\xee~Dtx5c.\x9b\x99\xb1\xcf\xb4n\xbc\xf4\xf5\xc6;\x03\xf6\xde}\x94&lt;\xd6U9w\x06\xcc\x05\xc8\x9dt\x0ev\xeb\x1c\xbd\xa0\xb14vo\t\x0f\x89,!\xf9Z\x11e\xeb\xdf\xe1\xd7qs|\xf6\xac\xa8\xf5\xe2m(\xeeY\xbfz\x82k\xb9\xc0\x8c^\xc3+\x8b\xe3\xd3\xdb\xe1\x80\xf8\x88{\xfeY*\'ng\x08\xc3\x80cp\xef\xf5\x93^\xaf#&gt;\xb7O\xa35h\xffK\x18\x91Z\x8e\x02\xe4\xf2\xf9gJ&amp;\xc9&gt;i\xae\x10\xdfO\n\x19;\xda.\xc1X\xa7-\xedFfi\xe0Q\xc4\xa7\nG\x8fO0\xafbe\x1a\x19+\xa0\xffX\x14\xd6\x7f\x8e\xdd&gt;\xdf\x05\x12\xdaB\xb5\xb6B\xe3\n\x9d\x9e\x02\x10\x19\x06\x17\t\xbf\x93a\x19\x82!,As\xb8\xdb\xfdb&gt;w\x0e\xe8\x9bs\x90\xd5\x98\xc1\xab{\xe0JE[\xef\x9f\xa5\xda\xc3\x84E\xed\xe0,}\xc1v\xc4\xcaZ|\x9a\xff\xc6\xdd9\xd9^~\x08\xfa\xfa\x86v\xdf\xbd\xabB\xb5Yhw\r~\xf7G\x07\xe7\x83\x07\xa9\xca\x8b\x18\xf9by\x04i\xb2\xba"\xdc:v\xfd\xa8\xa9\x84U\xfb7\x96c\xe9\t\xda\xbb\xe5s\xca\xd3\xad\xf6\x93\x98Q\n\xb8\xc3\xf7\x13\xc7\n\x066\xfb3\xd3\xd2E\x12\xcb$\xa0\xe9o\xd5\xa7\xf5As\x03\xd2\xd4\xa6\xd1\x88\xa5\xe4u\xef\xeaV\x97J\x9aU\xc5\xfcT\xc5&lt;\xc5\x8a\x12\xd5\x87*\xba\xd8~R\xb2\xf1x\x7f8\xc9@\x1f\xe8h\xcfD\xd1\x01\xa8\xb6.\\\xb8\x9c\x03\x8a\xfa~\xe54nj_~\xf6\xb3\x99\x0f\xa8\x7f\x16\xfa\x93\xd4u\xd6\x80\x84\x94,\x98\xa9\xcc\r\xab\xb1[m\xa25_8\xeb\xb3\x10qS\x9c\xfb\x85\x85\xc6\xe0\x83\xcf\xc3\x98\xa7\xd3Y\x00&lt;\xc2n?\x9b\xa5\x94TY0\x1d4\xb5?A\x8f\xe5\x1c\xf3/d\x13\x8f\xc9n]\xea\x96rY\t\xd4*\x03\x1fe\x15\xb1\xfb\x0c\xe0\xcd\x1e\x04/\xdd\x00n\xcf\xf5\xc9;H:`\'\xfee\xf8E.\xa0\xf8\xe7\x0e;\xc7\xb0Q!\xc0\xd66~\x909\xbc\xb4\x1a#g\x08\x81\x11Lv=]\xcb\xcc\xc9JE\xd9\xcb\xe8\x8a\x9a\xd1R\xbb\x1d\xdaZO\xc9\xde\x91\xfc\x90\x7f\xce\xabe\x98\xe4d\xc6\x8ff\xfa\xe6V\xbc:7v\xab\xde\x1d\xfbu\xc2-^\xdc\x06m\xf5p\x11\x1e\x8a\xb2\xc8X\x93\x1d?\x10\xd9\x0c^\x00F \x0b\x8d^\xfa\x83\xae\xc9L\x8c`\x85\x17y\x0e\xe0\x98&lt;\x99.\xfe\xef\xd3V\xa4h\x82n\xd7&lt;\xa1.\x9e\xb2R\x0b5\xea\xb1\xf3\xbe\xaf\xfe\xb2f\x8c\\\xc0\x18?\x85\xdf\x13\xad \x10~%\xa4\xdb\xec\x82\xa9cWs\xeb\xe1[]`\xfa\xba\x00\x8e\x00\x12\xab\x8b\xdd"\xf2\xa5\x1a\xad\\\x0c\r4\x88F\xb8j\x85\x07\x12k\x05+m\xff\x14\xdc\xf81\x86M\xf79$\x00\xc9s\xeb\x0e\x8c\xa2\xa2P\x9d\x8d;\xccwb\xe1P\xbc\xc4]\xb9\x02\x94\xa6\xce\x86(!&lt;\xec\x1c\x19 z\x80\xcd5\xaf\xc5\x16\x18\xfa\xee\xfb\x1a\r\x1ax&gt;o\xb8\xf3#\xc3\x9aJ-\x85\xd4\xe3%n\x980x`\x92&amp;r\xf8\xbc\xde\xf3#\x81K\xad\x06\xda\x0f\\K\x1d\xb09\x0e\xa5\xca\xf5rG#&gt;\xe1]c*\x00X\x9fuU\xe0\xcb\x96iH\xca\x97\xf2\x0eW/!u\x19\xd8a\xfey\x10\xc2\x99\x0bm\xc2\xfc\x87\xf4I\xa4\n\xe9\x14\\&lt;_\xc4{\xcbp|\xad\xfc\x8a\x92.\xba\x94\xd6j\x8a/\x86\n\x9e\x8f\xe4\xc7\xb8/\xa4("\xfe\xe5\x16\xc7\x17%\xc4\x97\xac/\xad&lt;\xadzk+\xba\xed(\x1c\x18m5\xed\xd3\xf6\xc2 \xb4\xc4\x02\xaaSX|\xe7\xcd\xc8k\x93\x14n\xbdaJgG\x06\x82c\x17&gt;\x97\xb0_U\xdf\xdaF\x0cnbr\xf3\x80\xa6J+\xf2\xfd\xeaU\xc9\xb1\xbe\x03\x95y](jpm\x0c\x15\x0e)7\x10\x8a\x84\xd0\xf2\x06\x98\x17\xd5S\xf7M\xbc\xbaz\xf4\xb9}3!-c.U\x80l\xcd\xbb8\xee\xb89\xb8\x19\x06\xe7\xa8\x1f\xd15\x9f\xa7\xd3\x1dC\xc9=\xd2\xd0\xf3\xc3d\x9c\xdc\xbd\x86W\xbag\xc1wn`|&lt;4\xfb\xd4\xd6\x9f\xb9\xb2\x1f\xf2\xd5\r\x10BZ\xa8\xf8m\x81\xa7 \x93\x8e\x17\xc1\x90h\xd5\x0e%b\xee\xa6=\x9aa\xe9\x18\xb6v\xac;\x06&lt;\xd8\xef\xeb\x0e\x0f\xa8\x93\xebuGD\xbb[\x9f\xbc\x7fGEa\x1c\x15&gt;\xae\x93\x1f\xa0\xdb\x9e\xb1\xc7e,I\xd2f\xfaQcG]\xb8[5\xba\x11\xdb,\xc5\x03ie\x96\x98\x03\x83\xf7\x0c\xadD\xd3im\xc7\xe8q\x1cI\xa2\x99\xcf\xfe\xd6\\\xbd\xb8\xdc$h\xd6\xce\x15p\xe6@2#\xb5\x16\xc2\x9fre\xfa#A\xee\x8c\xf8\xb2\x03\xe1\xc8d\xba\x8e\xdb\xcd\r\xd3#2o\xbd\t\r\xd4\xdbZ\x99\xbar\x1f7\xb3\x1c0\x1e\xb5v\xe1\xfdF\x15\xc9]\xbbc;\xf2\xfa\x85#N\xc2\xfd\xde1q\x03F\x90Oyo\\\xe3D\x1f\xcf\xa4\xf3\x18\xf0\x98V\xcbC\xcd\xd3\xc5\xfb\xce&gt;V76\x1cdK\xa9;F\xdf\x07|\x9d\x0fcr\xf04\xe4\xe4\xf6\xa5u\xea\x843\xa8\xfer\xfb\xe5*\xa7y\xa2\x1bN\xe1n\xc2\xe2`=\x0f\x0f\xadZ\xd5\x88&amp;\xf3\xb1\xb5\xf6V\x90\xc3\x07\xdd\x9f\x19\xeb\xf1N\xa9\x89\xaa\xc8\x19\xcav\xae\xb1\x00p\xc4\x08\xde\x80\xf6,\x9c\xad\x9a\x91\xe20\x87\x1f\xf1=o\xbf\xf20\xd4`\xa0\xa3\xf5\xa8\xfc]\xf7(,\x04\x08\x1e1\xf5\x08\xf8\xa5\x8f\xbe\x8c_\xe88\x18\x9a\xb5\x97\xff\x9a\xbe\x8bK}P\xf8t\x0b3E\x89\xf1\xf7{H\xb8P\x05\x03\xbb\xd2\xeb\x06\x8f\x1e\x12`\xa3\xa3\xbe@&gt;w\x87\x9b\x9bq\x82\x08\xc7\xbb\xa1\xfc^\xba=\x80\xdb0\xe3\xb0\x1f\x80\x01\x89vA\x15dw\xf2l\xfc\xaf=z\xdb\x12\r\x9b#\xb6\xd0K\xd1\x16\x9f\xae\xb2g\xbd\xb8\xbe\x03\xd87\x0c&lt;u\xa4$\xcb\x8b\x00\xfb\n\x16\x99\xd5DZ\x9d\xc5\xd8\x82\x06Z\x8eZ\x02\xa0\xef\x1e\xf1f\xe9\xef@\x94r\x9el\x17,\x7f\x91\x96/\xe9+\x93@\xe6(LlvH\x1d$\xff\xd3M\xec\xfe\x0f\x9f\xb6bov\x92o\x7f\x1d\x1f&amp;\x99Y`\x05W\x96i\xae\x0em\x14\x08\x91(\x9a\x1dL&lt;o\xf9\x1c\x12\xfc\x1e\xd7-h\x9c\x83\xdf\x9cs\xe6\xba\xc9\xe7|\x08\xef\x8f\x19\xe1\x0c\xc9\xfc\x88i\xa8xY\xddr\xa4\xe13\x87\x08g\xaac\x08:\xc3\xf1\xf8v\x92\xce\xcd\xf7\xbf6\xf6\xea*\xb9\xca\x80U\xff5\xf1\x10\x91\xc3\xfd\xe7\x1b\x1fV\x80\x86b\xeb\x82!&amp;\xb0/\x82\xc2\xce\t\x91\xa7\xe7\xd8*\xe5\xf9\x90)\x98E`\x18\x03\x97\xda\'in\xd5\xd8\xb4\xea.4]\x11x\x0c\xba\xb8\x94!\xbc\xe0\x81\xae\x94\x9a\xb96\xb8\x06\x81a\x9f\xf0&amp;U\x8f\xb3\xac\x80\xf4\xbe\n\x8f\xf8\x06\xe6\xc4\x91\xd0\x7f\x99\xb2\xc5&gt;\xb71\xee! \xa9\x00R}\xb3$\t\xd3}-\xf1\xddp\xd7j`k\x9d\xd1\xc2l\x92\xc3\x91L\x05qh\x82[\xe0\xe0\xf6\xb9\xba\x88\r\xce\xf9\x00P\x87xD\x9ak\x9d\xc3\xee\x03\x91F\xfd\xb0$\x82W)\x87\x92C\x16W\xf0\xf0\xc0\x82\x8b\\,Y\xa5f+^\x19\xd5i\x9b\x7f\x9f\x99f\x8b/x\xc9\x18j\xaf\xd3\xde\x12R\x11\r\xec\xdc\x7f\x16\x065.G1pL\x01\x92O\xb1\xf0#\xb7j\xe3\xc6+\xc0\xee\x95\x97\t\x1d\xbb!d\x1c\xe7S\xfe\x04\xc1\xa5\x10\xb0\xe3\x90\xa9\x80\x01[j\x91\xc6\x14\x8eQyfh\xc8\xbfm\xc0\xb8a}\xa5Lg\x1e\xf8\xd7\xe0\xc7\xb4\x9e\xc4tGGa\xf2\xb3\xc82z\xec\x0cP\x88[\xf9\x9b\xea\n\x0eCJ\xa3\x91^,\xb7\xfa\x92\xc1\xd4a\x14\xd8E:"\x0eW\xe8=\x06\x90\xaf#DqX\xc6q\x08\xc6\x95\xe4\xc9\xc2\xb9\xad\x12\xdad\xae~\xa4J\x185\xfb\x1c\x99&lt;\x01o/7\xcf}\xc0\xa1\xe6\x14\xb7\xbb/\x16\x89\xd3\xe6\x90\x80\xcd\x7f\xe9\xb9\xc9\xaf\x072\xb3\x84V\xbbG\x12\xf6*\x99\x00\x17Na[k\xef&amp;\x95\xed\x00\x1d\xcd|e*D\xb8O\x92\x91Z\x1b\x14\xbb\x07U\x9e\x99}\xe6\x80.\x96\xa5\xa0\x03\x00\x84q\x15\xfcP\xc4&amp;\x90\xc3\x95\xdf\xd7i*R\xba:r~\x1c\x01\x15&gt;\xcc{\x90\xf9gl\x98\x99\x19\xb4\x8ep;\x86\xed\x90 H\x8eV\x90\x88\x04\x15{V$\x18\xfb\xa5\x88\xdb\x9f\xd5\xa9\xd0W\x9a\xbbV\x91\xec\x019\xfb\xedO\x12\xe2:\xca2B\xf2\xe3X\x02F\xcf~\xce\xee\xdd\xc7\x99{z\x1c\xc5\xe2\xff\xf3\xe9\x97x\xea{%\x02\x9e\xe4~\xb9\xdc\xc7\x9f\xa5\'\xfb\xaf\xe9\x8aX\x8d\x96\x9c\x1aS\xd3c\xf2\x10\x8d\xd7\x9f\xb9$Cy\xe5@&lt;[Iu\xda\xfe\x84\xdb\xfb\x9983\x97\xa9\xa1\xa6\xee\xads\xc1\xa6O\xa3\xa0\xca\xda\xdbl\xc7\xcb\xca2\\\x009\xf1\xe6\x1a\x9b\x12\n\x82\xa1\x8f\xad\xabN\xe1?\xf4\xca\xa1W\xc3Ee\x05Q\xa3\xe9\xd0\xe9\xaa \xf4m\x1a@\x8f\xef4\xab\x0fg\xd3\x8c\xdc\x8d\xa2-\xa9q\x90\\U\xea\xa6\x08\x16\x9b\xe8?\x7f\xac\xcc\x90\xdaz\x10z\xaa\x0f\x84W\x00\x9d\x86\x9e\x88CN\xc7`\xdbM\nRh\xcc\x06\xcf.\x90\xf2^\xd1\xb2\xaa\x82\xf5G\xbb\x9a\xc3\xf8\xf3J\x07\xbdE\xdai\xc8\xa7\x15\x82\xe4\x02\xbb\xd1\x07\x19\xd8B\x16\xc4?(\xd8)\xa7\x0eF\x10\xaf\x8a\x18\x98=i\xa7\xa7\xb2.m\xc6\x0e\x8a\xd8\x06\x12\x0bQG(\xc5%$!\xae\xd2\xa1\x1bO\xdd*No\xd5[:p\xde\xa6*\x96L\xef\x8cP\x13W\x9a,\x90J\x87\xb3G\x0b\xf3\xebl)R\xef\xdc\xdb\xbc\x869\x87Z5\xb8\xbf\x9dR\x9c-\x17[\xdbe\xcec\xd9\x15I\x89\xbd\x97\xc4*\xe2"\x8eHe\\\xe1\xcb\xe7a_Q?\xe0\xf8e\xa8\xacP\x81\x85$\xaf\xffg\xe8\x87\xcf\xe8\x82`q\x94E\xf6nH\x13e\xca\xb5\'\xe6\x8b\xeb\x0en\xc1\xa3\xe9\xb9Z\xaf\x7f\xd4\xc3\xac\x1f\x8f\x1f\x83\xfe\x9bw\x05\xf0\xd0\xc1\x1b\x83\xce\xbb\xde\xf6\x9d\xda\xd4Oi\xaf\xe4C\x15\xa1\xedca%:\x9c^\xa7\xfd\xdda\x8a\x8f\xd0r\xfe\xbf\xc9-\x16\xa0u\xe3\xfe\xb6\x92\xcd\r\x98\xe5\xe0\xc1og\x15\xfcUW\xe6H;\xf8\xb9\xfb\xc8\xb4\x8a\x94\xd8p+\x18\xe7]\x9a\xc2^\xdc_\\\x16I\xf6\xc7\xf8\xd6\xd7\xee\x8b\x91\xfb7g\xd7\xbe|\x0c\xdf|\xe6&amp;0\x85[\x98\xe1T9\x94P&lt;\xf9\xdc\xd9M\xfcVC\xc3\xf5B\xee\xb9\xe4\xd3qmG\x17+\xbe\xb9\xce"9\xd5\x01\x14UH\x1ft\xd3\xfe\x1dU\x96\xe3\xe7L/5\xe0!\xb3\x03a\xa6|\x96\xb5^\xc5\xdd\x02\x9d"\xce_\xf1p\x15\x1fR\x85ID|5\x81\xc3\x83\xef\xed\xae\xc0\xa3\x0fO"\xeb\\\r\xdfe\x98mY\xb6]\xbf\xc2dg\x832\x7fb\x158h\xe6\xc3Y\xab\xd0\x92pe\xdd\x14\xdb)\xf1\xc0\xc4@i\x81\xb1kp\x92\xad\xa1\xf4\\\xa78V\xe2\xb8\xbd\x98p\xd0\x91\xb4\x99\xbf\xc3\xef\xe3\'\xc1 M\xe4\x90\xe2\xafXE\xe5:\x825C2\xcd\r\n\x9dh\xce[,\n3\x9c\xab\xaa\xb8\xd6\x00q\xadz\xf1v8\xffE!:v\xf7P\xaf\xe8\x15\xb8\xbbrz\x92\x05C\xd0\xb6\x19c\xdf\x1e,\xc6\xbff\xc5P\x0b4\xb4\x1e\xc4\\\xdd\xc3l\xef\x15(\xe0\x9e\xfa\xd9\xfd\x9eA\x1dw2\x9d\x9fJo\x80\x81\xa4 \x01\xf7\xec\x10\xca\xb8\xcb\xd0\xa0\xcb\xe6*^\xd8\x17~\x07\x08\x83\xf5\xa0fSr\xde^\x94\xa5$\xc8\xecrc16Q\xe9m\xefz\x8b%\x84\x0cuT7\xe3:\xcf\xd5cUH\xe6R\xd3yo!\x81\xf5^\xfe(\xaa5\xb7+\xc8\xe7G}\x0c\x9e\x82\xc2B\xd2\xcf9\xb2\xee\x07\x0f\x82\nq\xbe\x03)\xa2r\x1c\xc2j|\xfa\xb1N\xde\xb4#\xc0\x93v\xe6} \xb7\xb1\xe1\xad\xca\x8d\xab\xccN\xd1\xe7-\xbd\x87\xc4\xdaX\x82\xa7\xe2\xf4\xf2\x82\x1a^v\xc7\x94\xc9\x18\xf1\xfb\x0eb\xd7\xef\xe2\xab]h+\xc3\xccsZpg%\x80\xd8\x13\xf2\x9dS\xfc\x93\xfd[\xa6\xfdASo\xdb\x1f\x92\xbd\'U-\xeb\x83J\xb6\xc6\x0f\xba\xcau\x83jx\xcb\xa2\x83\xe4\xc7\xe3!\xe0*\xb7\x15\x08\xfcQ4\x01\xebO\xf3iL\x88\xf7N\x82\xfb\xe8`\xcc\xdd!\x16\xeeE]\x87\xd3\xa3R\xc6\xda\xf6\xf5\xbc\xc7\x9b\xefu\xd9\'u\x14\xfb\x98\x8dr\xc29t6\xbc\xb4\xab(\xa6\x00\xc7\xc5\xb9Cn4\x9d\xcb\x92\'\xd8\xa9O/\xaa\xc5\t\xb9\xb9e\xeb\xc9/\x84\xf0^z\xfe\xf2\xfb\xed\x83\xf65\xfa\xe8T\x17\xdd\x96\xef\xb6\xeb\x11L\x98\nj\xc3\x19.B\x84\x17\xcd\xf4E\x9af\xe3\xf7\x849\xcd\x8ee3M\xa7WJ\xa0\xae\xdb8w6\xe7\xd1\x18\xdf\xfd\x98\xc2\xbd\xdb\xe5|\x98\xcd\xe9/!\xf9\x18nuhd\xb4Z\xdc\x13\xc8?\xbbg_\x01\xe9\xf7\xc7\xba\xad\x02\xd7\xadq5G\x8f=|Bw\xcd&gt;\xbd^g\x7f\xf4\x7f\x8fT\x9aQ\xa9;t\x94V\x07jMa:\x12\x18\xdcg\xf1]i\x98\xe5D\x1a\xe3\xf2\xb1\x12\xf4\xbf\xf5c\xfdO\xb3\xee\xbb+\xfc\xc0\xacB@\xd1\x8bw\x80$\x0f\xe9\x1dS%\x99\x9e%\xe2d\xce\t\x06i)B\xec`\x80`\xc8\xf3\x85\xd3\xb8\x18\x15\x89\xa2\x94\x87\x17\xd6{BK\x03\x92-\x1f\x98\xcd\x0e\xd80p\x83\xc8\x9c|\xcb]\x9e\xfbM\x8a\xefX\xe4\x1e\x9eS;\xc72\xf2e@\xe3\xe1\x82\xe9\xc7\xbb\x83J\xc3B:\xa8\xb1\xc28h\xc03\xa7\x19A\xfe\xc1\n\xb0\xf8\xd6o\x8a\x83\xe4\x05\xe0\xa6s\x81\xc1\x93\xb28\xac\xe0\x83\xdf\x079\x87\x14\x08J\x07\xd2R\x13q(\x9dpJ&lt;\x0e\xaeh\xff\x17~|\xc8\xb8\xa7Vj\xa7I\xd8\x1f\xf2\xfeX\xc7\xec\xe5@\xc8[\xb4\x11\xbd\xab/\xf9\xfb\xde\x03`\xfa\x9c?Q\xda\'\xfa=\x06\r(\xbcV\xa8\x91\xaa\x975\xcf\x0c\x19\xebQ\xdc.\xaa\x0f\x04\xab\x86\x84\xce\xb0&amp;.\xc0]\xf4`.E\xb8\xc2%\x12\x07\x90{\xb0\x7f\xedh^\x16\xc5\xa7yf\x9c\x13D\xdb\x80\x03\xfeu\x10\x14p\x89\x98b\xb6:~\xf0e\x03\xf1\x1b\x17\x0b$\x89\xef$^\xbf\xd6\x01\x03\x80\xc0\x15S\xa4\xfa\xd0\x86\x91F\xb2,Uv\xd750\x0f\x93G\x0fr!\x82\xb9\'Q\x08L\x8f@b\xd3n{\xa8\x1b\xa5\xc1\xdc,dX\xf3\xa6\xb7(!\xb1&gt;\xe4\xcf\xd5\'\xed\xd5\x9d\xf8\xcec\xdbp\xbd\x8b\x1e\xc5\x80k\xc3\xad\xccHNfq+\xba\x88\rF\x92\x1coJ\x96\xd8R\x9c\xd3\x14v+I\x84\x9a\x15w\xfb\x83\x1d\xf7\x911_\x08\xd4=h\x9c\x88\xcc\xd4\x97\x96\xae\n e\xc1\xaa\xe3D[|\x99\xc6\xd5E8UB"\xfe\xc2\xd2\xf6/\xca\xdf^~\xc4N{\x11\nc\xc3\ty\xe7\xbe&gt;B\x93\xcd&amp;\xb5b\xd9\x1f{\xed0\x96\xc48ct\xb8\xbf\x18\x11\xb5\tS\x8a\x1f^:\xf1\xff\x81\xdb\x12\xf0\x9e\xedb\xc5\xf2#\xb4L\xf5\xe9\xf2\xbe\xc3V\x1c]\xae\xc7\xa9\x82N#i\xcc\xf4\x99\xc5\xa1\xb8\xe7\x03q\xc3\xda\xec\xe9\x98&amp;\x97\xa7\xc8S\xef\x93l&lt;\x8d\x01\x9c\xe6rf@\xd5a\xf0\x16\x93\xf7\xe6\xa5`\xe6\xf4\x1f\\\xe3ox\x85\x8a&amp;G\x10\xe1\x01b\x16\x15\xac\x1b\x85\'\xbf\x82\xdby\x15Z\xbf}F#\xf3BQ\xf2g-1B\xd2=\xdfL\xbbW\xa2\xbc]\x16\xabE\x0bT\xd8\xe9\xacVTM\x086\x08rb\xa7\x1b\x07Z5s\xfbw\xa2\xa7\xa0\xbd\xa8\xa1\xe0\xbc\x7f+\xfe\xec\x1b\xe2\x85 \xd5\x872\x86\\\'z\xda\xfd\x07q\xbf\x7f\xf1\xa5\x94\xd4\xcbV\x8b\xe9_\xf2Z^\xba\xcf\x7f\x04hcd\x19\xady\xc4Gh\xe0\xa1m\xba\x9f\x1d&gt;d\xbeyT\x86&gt;m\x83\xb7lu\x1b\x86i\xde\xd5\x89z{\xb3\xcbs\ta\x8d\xf9\x7f\xf5\xd8y\x9e\x84\xe49\xa3\xd2\x1aSm\xc8\\\xbb\xa9z\xe2s,\xde\x91v3\x07/Q\xf1\x8fw\x8c\xbdUw\x9a\xe2\xfb\x11\xf1\x7f\x91}\x8b\x1b6\x90\xbaL\x1c\x1e\xfd\xc1p\xa6M6.\xebL\xdf\x94 \xbbB\xafv\xd8\xadQ8YEd$h\x03\xf2\xcc"S}\xe6l\xa5\xbe7w\xf1\x1b\xcf`\xce\xa7=\xcd[\xdb\x10\x93/\x8e\xf8\xae\xe1IW9\xf3\x80\xa4T\r\xb3gM\x07\xf8&gt;E\r\'\xe5C\xbfz\xfc2|\x11aV\xa4\x9f\xa1\xa2\x9b\x9a\x82\x81&gt;6D\xcc6\x18I\x02\xea\xa0?\x0c\x88 \xf4\xa5,J\x82\xb3\xfb\n#\x06\x7f\xf2\xdc\x1b\xf6\x9bnf\xdc\x96\xae3\x1eN\xc4?p\xcc2BRl\x06v%\xda\x01\x14\xe4\x8c\xb0\xcf+T\x0bdl\xac!H%5\xbai\n\x85\xee9\xb8\x90\'5\xf7O\x18\xf6o`;\xc24\xea|9\xc4\xa9\xfe\xfa^\xe1\x05\x1aJ\x03\x06A\x98\xb7nJ\xef\x8c\x1cm\xc3\xf48\xc0|^\x17c\x95\xbb\xda\xa0j\x04A12P*h\x8a&amp;\xb5f]G\x9bHF\xdep-\xb0*\x12M\xac\xf5\r8b\xcf\x9es\xea\xa0!\xafl\x93\xe4\x88\xa4\x1f\xd9\xdcgd\x1f\xeb_\x1aw\x07#P\\`\xd0\xd6\xefn,kV\x8b\x93O\x82t\x19j\x8cdj\x96&lt;\xde\xce\xc5\xa1\xa9\xfd\xafb\x86)\xbcSQ\xfd\x15\xda\x9a\xca\xa7~\x0f\xe6 \x11#I\xb0.D\x0b\xfd\xc6\xf4%\x1fU\xd5Ke?\xb0Ba\xca\xbc\xf9\xae}\x97\xd5`n\xd8\xd7\x86K\xb1\x9d\xb3Y\xb3\xd3ea\xabL\xbb\x808M\xc0/}\xed\xacT\x92\xdf\x0e)\xc8\xa4\xbe:X\x85&lt;\x06iy \xbf\xae\xd2\xf2\xecG\xad\x94@\x08\x91r\x06X\xea\t\x19_6l\xe6=\xad\xc5lZ/\x1c]\x98j\x03\xffL5\xed\x8c\xb4\xad\xe4\x02cZS\xd0\xe9t\xc9M\x82B\xc4K\xdd\x9a\x88\xb6\x0c\xef\xdb\xc4\x00\x8fS\x93\xf0\xecw\x9a\x7f\xa9\x98\xf6)\x84\r\xef^\xcft\xe2\x0f^\xa6\\e\xcc\xa0\xe0\xedF\xe7\xa6\xdf@\xee\x89\xf8`\xa8\xe1Z\x10h\xab\x97\x05\x80\xa6\xd0G\x1f\x91\x07\x7f ]b] Q\x10\x1f\xe5u{:\xfd\xaf\xa5\xf32\xdd\xa3AzHP\x91L\xa3r(l`\xc8G\x9c4x\xb9&gt;S\xf7%[\xeaI\x87\x8a\'\x07\xaaa\xefl\xd2C\x15jP%z\x17\xd1\x7f\x04\x07\x12\xf2\xad\xa7Z\xbeE\xd5\xc1e\xf2\x02\xeb\xa9\xe2\x95P\xf4$5X\xb5\xcf\x11s\xf7\x0b2\xdef\x84\x9f\x1cCk\xc0\xa98K\x03\x8e\x04g\x12YV5J\xff:\xd2\xbe\xaf\xf3\xfaH\xd7\xda\x1b\\\xd4\xcc}}6\xc9\xe3r\x87\x91LO\xe2\xa8U\x16h\xc5MlE\x7f\x0b\xf5\xd3\x01c\xca\x15:!F\xfa\x11\x7f\xeb\xb1\x1c\xd3/\x99\x0e\x12J\x96\xf9\x88,\xb2\xb4\x14\xa3{\xf3P\xcd\x0f\xa6\xf5\x1b\\\xcf\xab\xf8\xd0s\x90d\x03\x00\xa3\xd0;\xec^3H\x93\x12\x8b\xda\x00\x00\xa4n\xdc\tB\x00_\xb1\xd1\xe5J\xde+\xea\x82r\xa6\x17m\xf9\x97\xc5\xd7\x9f\x99cM\x8cz4g\xc8\xed\x08,\xce8\x05\xd6\x10\x16mv\xa3p\x85Bb\xbf\x9e0\xb5\xa0\xec\xc2Yf~u\xe6J\x9c\x90\xa4\x96\xc8\x96\xfa\x98\xe2\x92C\xfb\x12\x17?\x12\xb4\x11\xf6[\n\x8e\x89\x94\xdd(\xc6}\xb1\xd7P\x83\xbb\xdf\xf1d/\xbd@#L\xcf\xab1CS,\xec\xa0-\x15\x07:\t\xc8\x9e\xe1\xd7\xc2\xfdi\xc4Em\x05\x9e\xc1\xd0\x8fb\x0e\x85\x9c\x93\xc6\x8a\\\xe2H\xba\x05#zu \x91qL\x01\xee."\xfa\xa4\xa5j\xb8\xf5\xe0G\xb8\xd0\x14\x02\xc2/$t\xae\x8b\x03\xa5Gy\xa4\x18\xeb\xdc\xdf\xf3u\x06\xdc\xd6\x1f+\xfe%\xc5\xc68\x91\x05\xdar\x95\x9c\x0coH\xc6\x15\x1d\xbc\xff\xc2l=\xe0c\xecn\x85"\x1f\xa7\x93\xa3\xc6\x87\x19\x9b\x14\x04q\xe1cD]\xdb\x90?a\xa5\xca{d~\x16d\xdd\xc5\x034?1\xae\xac\xd4\xcf\x8c\xb3\x92\xaf\\HJ4\x17qzo\x9f\xc6\x15\xd1\xbeTVI\x06\xc1\xc6\x9f\xfa\xb7\x8e\x17:\x19\x85\xa9~\x7f\xfa\\\x9dxC\x99\xa1\xa9\xaegP\x1eIr\xd3Xe\xfa{\x8am\xaa\x80eQ\x1f\\\x991KG\xb0\x93\xe1\x81\xc1/[hN\x9bN\xbd\xdb_y\xb12\x8dC\xf5\xb1$o\xce\\\xd6\x1d\xc7\x10}\xabm\x1e\x07\xac\xcd\x98u\x94\xee \x13\xf2CW\xfc\xe2_m\xd9\xfb\x9348&amp;N\x95\x82\x02\xa1;c\xc9\xbf=\x9b\x13g\xc2\xbb&lt;\xde\xab\xc5\xb1\xc9^\'d%\x88\x94\\T\xa2\xf0\x1f\xf9\\\xba&amp;\xb6\x19&amp;\xc4\xfc\xd6}\x0b\xf1\xab\x19\xc9Z&gt;\xd5\xacYH\xa2\x19\xff\xf2\xe4\x7f\'"h\x8cD\xa0\xf8ns\x99{W\xd0t\xadGt\n\x90\x86+2?\xddY\x102\xbd\xe7.c\x97\xe4\xf8\xd5\x97\x8e~x\xcf\xf5\xf2)\n\xad\xe7I\x90nF \x01\xccN\x03\xec\xae\x8eD\x8f\x02mgjId6\xc7\xe0R5%\x98Z\x92\x17-\xb1\x06\x1f\x10\x85zC\xb4tYp\x8c7iq\xab\x95$r(\x0c\xfb\xe0\xa0\x9a\x00\xfd\x89\xe4.\xc5\x0c\\\x88\x86\x1b\xf6}\x1aXFv\x9a]\x88i^\xba\x11\x97L\x8es\xe9\xd9\x8db\\\xe5\xf7\xc4{n\xad]\x04\xba\x1a\xef\xaaq\xa70\xe1\x04\xfb\xe7!\xde.@\xce1I\xed\xe0\x11\xac\x95\xac\xe3\x80\xf9\x96\x0f\x12\xa1\x06V\xbd\xec\xa2\x07\xbe\x18T\xba7\x9a"\x9d7\x89\x00\xc0~\xf7(\xa6[\xe8/ H\x7f9\xfft\xbb\xfa\xf8\xa25\xe2\x07\x959\xba\xc1]!D*w\x9eS8"\x8239\xa2\xb5\x93\xd50\xbf\xe9\x81/\x11+\xeeuumWP\xa7M\xa58g\xea\xe3\xb52\xf2\xdb\x83\xa1\xb1Y7c\x16\xe4e(\xdaM\xec\xc0l\x9a\x9cLY\xe6\x81\x01\xd186\x05N\x18X\xbcR\xf1\x14\x91T\xa7.y6y0O\xd8#\x9a\xfb\xea\xe8g\x96\xfb\xebL\xe4Q\x06\xef\x84w.\xe7\xae\x80\xee\x8f\xd1\xcd*\xf7\x80G\x1f\x0c}\x032l\x9a\xaa\xad-\xc04\xda@\x7f\x83\xacs\x18\xcc\xfd\xbc{\x95\xb6\x0f\xef\x7f\xbb\x0bh\xa3\xde\x90$\x9e\xca\xf2Dr}1\xc0g\xa4\x86=\xd2\xa813\xd6\xe0\xa41\xf3?~\xa0\xaf%9\x1a\x01\xc1\xf1L\xd0\xffU\xa6\xff\x87\xc9w\xf8\r\xbb"\xc3\x86\x14\xb9\xadN\xfc\xe0\x00\x08\x10\x9e=o\xb7u\x87\x93\x89H\xbb\xaap\x94\x9e\xb3\x02\x10\xc7\x16\xcc3\n\x1f?~\x97B\xca\x14d\x85\x1c)\x1fi8&gt;)\xf5&amp;F\x95}#\xf8\x11\x8e\x1ew\x93\xf3\xea\xc9\xd7?8\'\xc2:\xfa\xf9\xf9\x86\xdb\x1e\x14HP\x90Q"\xa0S\xf5\x95IC\xa9c\x88\x8c\x00\x0e\x07*\xf5\xac\x01\xe8=?\xa6\xb4\xed-D\'\xfa\xba\xad\x06n~\x85S\xaa\xbd\x05t\xd5/\xb5\xb3"\xd3\xe5o|e\xed,\xcfxU+\xc7:\x87\nUM7\x95he\x10l\x01\xcc\x11e\x8d\xae\x85[\xd4\xfa\xed&lt;&gt;9\x7fu\x92B\xa42\x1b)\xc6\xc4%b,p\xc4\xfb\xcb\xc3Xf\x1c\x82\xc4\x03\xc3qvXD\x90\xea\xe40\xa3L\x1b\xae\xbb.\xa9\xd7\x94\xa3Eg\xfek!Cvn\xc7\xaba7\xcb\xd58\xd6\x84\xf4\x112~\xbe\x0e\xb9j\x19\xa9\x90&gt;#\xb4\xfb\xd2\xa1\x9es^\xdc\x0fR\x1b$E\xbd\x96\xce\x82\xc3 \xaf\xa8k\x8b\x8f"\xf9\x81*\x0f\xac\x92\x19^\xe4\xf9\x9f\x1dr\x0b\xfd\x1f\x04\xf17\x8f\xb4\xf7\xc1\x0c\r(\xe5g\x1e\xb4\x8d\xc8\xd2\xae\x81zK\xed\x8a\xbcl\xad)1EN\x9c&amp;X\xb8kk\xd1\xce\x15\x91\x94?\xdb\xa0\xda\xf9aS\xfb\xc7u\xf0\x01\xde\xda\x80\xae\x81\xa3\xc0;y~8[s[\x8b\xd2m\xa0W\x07\xfcT\xa4}$\x81\xab\xef\xb2\xa3\xb7P\xe9\xb5\xfc\xfcXH\xb5\xdf\x86\x8aa\xac\xc4\xa5\xf8\x16\xcdxn3b,\xaf\x02\x05TRJ\xe0\x07\x06q\x0b\x0f\x9b#iK\xb5J`\r|\x8d\x80\xbd\xadg\x9f\xc4k\'\xf8i\x92\x80\x1d]|k\xb3z}\xbd\x91`NZ\xd8V\xe8\xf8\xe0d\xd6\xb7\x13\xfc\x1d\xc5\x8f\xac\'\xd9\xf5&gt;b7\xa0\x1a\xe5\xc2\x86I\x1cN\xc9jI&gt;\x9e\r\x1fI\xe0\x1c\x7f\x1d\x89caH4\xb8xP\xb0\xec\xb5\xc5\xc9\xda\xac\x00\x9b\xcc\xdb\x04\x10t\x03+\xed/\xa8\x9bFG8\xcd\xf4\xae\xc3\xff\xbb5\xa7\x95\xf1\x10\x04\xf9Y\xe2\xb0\xd7\xf4\xf7\x0b\x84\x04\x91\xdeG+M\x91\xf9\xb10c\xfd\x9c\xb2\xfd\xe5F\x10x\x08\xba\x8a\x10\xa2\xa1\x19\xff\x9d\x19Q\xcf(ag8\xf0\xa4}\x00I\xf6\xcdrV\xe9\xac\xe2F\x16N\x90!\xc9\x07\x8a\x9aYL\xd7\x9e!O\xf5]\xaaQ\xb5.\xec\xdb/\x18\x9e\xad&amp;R&lt;\xaa\x98)\xb3\xb8\x19\x04\xa7\xb7\xadOD\x10q\xe5\'\xce\xdf\xe8\xef\xca8%\x95c\xa4y\xffnc\xa4\xf4\x81\xb8\x08m\x93\x8a\xe5\xae\xcb\xf5)\xe9Bh\xeb\xd3\xba\x01\xed6\xb1\xc3\xa2\xbe\xcf"\xd7\x18\x9f\xb46.n\xb7G\xb9}\xcb{{\r\xe9\xec\x96\xa2\xb45bA\xbe\x02\xff\x0f\xd4\xae\xf7Q\xaeOjuH\xed\xd9\x80\xfc\xa9\xdcL*\xf0\xb8\xc4\xe3\x07\x16\xe7\x02\xac\xd0\xdb\x9a?2\xfb\x8d;\xa6\xc5Y\xb2e\xc2\x1a\xe5\x1a\xc4\x9c\x8b1\xf3\x8a\x951#\xa9j\xaf\xf3\xfb\x1d\xc7\xf0\x1a\xc7/\x87&gt;\x15N\xc9\x94@\x18\x17TGb\x94\x188Rt\xf6$)\xacZ#N\x99\xe9\xb1P\x1a\xbc\xb0\x88|\xa6\xa9\x01\x8e\xe0\xf0\x0c0y\xc2\xb9\x85\xbf\x07\xdf\x03s!\xc6mR&gt;*[.\xdf\xda\xe9l\x89\xad7\x94#\x0f\xd3\xe5\x9a\xec\xbbY\x00\xd1\xf3\x1c\x7f\x9b\xf8\xa4\xf1\nY\x18\xfa&amp;qb\x88\xe7$\x82.\xdf\xcbT\x1c\x82\xc0\x80mw\x8dey\x89,\xa1\n\x18\x8d\x81\x13\x1e\xc8;=\x0c\x97.X,\xe8@\xeap$\xd5S\x84\xda\xb3\xc6\xe0\xc0Tt\xc3\x12\x84Y\x8e\xa7\x1d\xfa\xa7xH(\x9e8\xde\xd7\x19\xb4\x0c\xbe~+\xae\x90\xe0\x8d=\xc2\xfepg/\xe8\xdcS\xfe\xce\xec9\xe9{i\x15\xc5I\xe2;\x11na\xa9\x18G\xf2\x8fb1\x87V8\xe6\x13\xc0\x02\x02Y#\xce\xf3\x03b\x1c\xdb\x840\xc0_\xdb\x13\xd0\xec.9\xff*\x03X\xd2\x90\x11\r\xdbt.E\xda\xc9W,"\x00\x15\x03\xec\x12\xc8mS=R\x89\xd2\xd2\xc4\x88^\x84\xa8\xe60\xa1H\xc0\x00]c\xaa\xde\xf9\xd4\x9c\xf1qP\x9a\x11\xa0\xf5\xb9\x06@~x\xfbb\xcc{\x83\x9c\xa5G\xb7\x03\xf9\x80\xe7\x0evM\xfbM\x8c\xca\x8c\x89N\xda\xaf\xa7n\x0e\x98#\x1b\xb7\xc72\xf39\xfc\xb7Y\xa6iU\x0b"(\xb1\xc1\xa62\x98I\xc7S\xb2\xe8j\x9b\xd4{\x96N\xc7Kn\x05dF\xb0\xd1\x7f\xb82/\xe1X\xactQ\x1e\x1ed\x1a\xc8\xab\x1b\xd5\x81\xee9\x11&gt;\xa2\x1f\xe1\x0b\x0f\t\x84:\xda\xd5\xca\xc9\xef\x13\x12oa\xce\xff\x0b\x8f\xd1$b\xac\x8dO\x94S\x9e\x9b\x8d,\xb3\xdb\xf4qb\x9f5\xd5\x85WP56\xdf\xe9\xe8\x95p\xf4\x96\x9e\xf5\xc5rC\xe4\x87^\xd7\xd9\xa6\xd5\xc9\xc9N^B\xeb\xd1\xb5\x9c\xed\xadz~~\xd2\xa0x/h\xb8\xf8/A\xdb\x1b\x19\x02\x089\r\xd0H\x134\xbf&amp;\xef\'J^I\xe0\xee\x8f\xb6L\xffV\x89\xae\xb0W\x9a\xe7\xaf\x91\xe3F`\x15\xf8\xda\xdf\rS\xb1V\x83F\xd2\xaca\xbf\xa8re\x8e\x8c\x18\xb7\x8cV\x18\x92%T8\xb2\x87\xde\xd3\xbd;*\xa9\xca_\x90y\xbe\xf9\xbeeYIYH:\x89\x0f\x0e\r\xb4F_\xb8\t\xac\x11h\xa5\xecP8Q[\x08\x12dv\x8a\x13\x061\xb8\x13\x8f~\n\x8cH\xe1+fp~\xb0\x9d~\xc5\xc6\xf3\xe5\xfd\xd0\xeb\x12\xfeO\xfdC?\xb2\x9b\xb1\xd1\xc6\x0b\x9d\xf3\xa0k\x87\xddP\x95\x15kz&gt;\x80\xafH\x97\x9cYr2XQ\xb7RYL\xaf\x05/\xc6#`Sp1\xf1\xaa\x16p-\xf6J\xb4\x9b&lt;\xeb\xd8l\x7fyP\xf3\xc0C+\xcb\x08\x0eLqJ\xde\xac\x06\xec\x945\x7f\xd7&lt;\x9c\x8b\x12_\xd9;\xc3q\x02?\x84\x8b\x03,\x07H\xf8\xca%\x0c\x84\xec\x966\x8b\x9d\x806\x8a~\xef|\xed/\x14\xb1g\xfb\x19\xda\x80\xfb`\xa7\xfe\x034}\xd77]\x99\x8dhao`HB\xb0\x97}\xc9\xff\xc4\xd1Pd8~&gt;a\xfa\xede\x97[\xa6U\xce\x89\xe6\x0e\r\xda-\xad\x98E\xf2\xd4\x17\xdd\xcb\x9b\x19\xee\xd5\x125\x0fn*\x02\xf7J\x1b\x02\xb19\xa4\x1a\xaa\n\xda\x9f\xe2f\xaaf?\xb0q\xab\xf9\x91\x1d^\xf8\xc4\xb7\x014e\xce0\xe84\xa2\xe1\x02\xa1\xfc\t\xda5e\xf6\x85Z\x1a\xcd\x00U\xe0\x8dI\x14p\xb9\x93\xc1\'\xb03C\xbdb}[\xc3lf\x83\x87\xdfb]\xd4\xbeqg\xf0\xf5\xe8\xffv\xeb\xd4\xa7L\rn\x88\x1a\x96n\x96\xdb\xb5\x16q1u\xae\xd3\xddY\x7f\'\xa2\x99\xd9\x8dg\xcae\xa3d+}\x16p\x00\x8f?\x12qN\xc2\x9a\xeaA\x89\xae\x00\xa7\x8e_h\x1b,\x8eW\x90\xa0\x9d\xfdX@\x1e\xfe\xf0:\xb2\x93\\\x92:\x94C\xd0p6\x83B\xe4S\'\xb86\xf2\xc6q]\xa0b\xden\x10\x9d\x07\x9b\x94\xa9G\xd1\xae\xd7\x18\xb8\xa3\xbe\xdc\xe1,\xfa%\x9c\x82\\\xbd\x8a*\xa7\xbd}\xde\xb7\xf9\xe1J6\x1d\x9e\x94\x8c\\!Y\x91\xcf\n\x85\x9e\x02\x9fo\x91(\x8b R\x9a\\3Pk\xe0J\x00\x80~\xec\xa4$;\xbd\x05\x81\xd1\xbez]\x9b\x13\x85\xec\x89S\xfa\xa3\x8a^e\xdbP\r\x1d\xa7\x0f\x0c\xb8\xe1mv\xa1\x8b\x02N\x91\x1e\xd8o&amp;Y\xabo\xeax\x0e\xa9^\xfb\x15\xac\xe1M\xe1\xc1Hb\x9dosf\xcf5\x0f\xf2\xc8Tg\x85\xde\xe3T3\xa2\xc4/\xa4\xce0KKyo\xd8\x96\xd3\xad"\x9f \x81(\x88N\xa7\xff~\x0f\xdf\x11E1\xd7\x84%\x80e\xb5\xfa\xa4|\x1a\xf3*\xdb\x9e\xec\xd8Z\x19\x7f\x1e\x8ed\xe6\x86\xfe\x98\x0f\xc4\xbc2\x8aN \xe6\x08\xc6Gxpj\xfdMwI(\xc9\x97w\x93;\xe4\xd0\x8e\xa4\x1bf\x8f\xda\\1\r\x83)\xc3\x88\x89d\x1d t2\xd9\x17&amp;\x02\xaa\x80\xfe\xeb\xc6\xc5\tp\xf1\xdf\x10\x95\xc5$,\x89Gj\x9eA&lt;0lH\xe8\xa1\xf1\xcd\x8c\xa5`"\x9daO\xd5T\x80\xf0S\xe9\x8d\xf0f&lt;\xc0\xad!\x08\xe5\x19M\xe3\xa6\xfd_\xa3?\xaa\x87\xff\xdd&gt;\x01\x97\x96}\xa2\xbd\x8f\x95\x15d\xe5\xe2\xac,\xf2w\xcc\x93l%])}V\x1e\xf8\x0fZr\x0b\xcb\'\x9c\xd5\xef\xb9\x80\xf9\xd1\x8c3fR\xaaz\xc6\xb8J)\t\xf9\xeb\x08\x10^\x95$\x10\xbexp#\xd4T&amp;S\x12\xa1\x1b\xf5*\xfa\xfc\t;\xc8n\xad\xb9\xe3\x06\xe7\x1d\x1de\x18\xfb\xc0\xc1f\xf76\x07\xb7\xe9/\x18\xc9:z\xd6\xc6\xfe\xf2X\x1f\xc6\xc4\xc0\x8c+\xa5W\x890=C\xd4\n\xe7\x85\'Y\x11\xc4\x97\xdc\nF#\x19\xea\x90\x1f\x98\xdac\x16\xa8\xe2\xe3q\x16\xc2n\x02U\x06\r\xd2zxI\x18gtx\x15\x02\xbc\'5\xf4\xa5^ &gt;\xf2\x81-\xa2\xb0!\xa5#\x991\xd2\xa0\xb0\xed\'}P\xf4\x8d\x1a\xe1\x9c/\xf8\x88w\xb4\xf4\xe7\x12x&lt;A\xf5|\xd3\xb9\x81\xab\x16{\xac\xdc\xed9\xfaxe\xf15\xe29\xa4Jk\xa9n\xb1b\xe3S(,[\x90\xd0\xac\n\x85\xb8=\xa8\\\x86\xd4\xb4\xe6\xbc\x81\\L\x9e\x1f\xbb`\x12Z~x\x1c\x15\xef=\x17\xcd&amp;:\xe6\xa5\x929\x8bj\xd1\xbd\x86\xce\x168\x9a5\x94&amp;\x06!\x82\xb26\xbc_\xfaA\xd3\x86\xc1B\xd0\x05p\xc0HMZ\xcf)\x87W4\xe0\x1b\x05\x9a\xe8^\xc0\xa1!\x10GF`%J4\xbc\x88[v\'\x8e\xed\xb8M7\xc4\x185\xa2\xf5e5\xdbt\x91\xc6\xbeLb&lt;MCR\xa4#R\xc7\x14\xcb!y\x8d\xa2\x94N\xcds\x1d\xce]p\xacv\xce@\xdc\xde\xce0\xd1\xb6\xbc\xff\xac\x10JagD[#\xf4\xea\xd4\x8e\xb1\\o\x8a\xe5\x1e\x04T\xf3d:\x0b\x11}P\x89J\xa5\x8d\xff\x86\xfe\xd3\x19\xf5v\xec~\xf8\xb2Q\xc5\xe2\x8b\xcca\xedZ\x0bZ\xa2\x94\xbcy\x95\xdf\x1a\xbel\xb8\xf3\x93\xfe9\x81pG\xd2\'#\xf8\xc0]\xd9\x9dC\x02\x87\xa6\xd4f\x1b\xa1\xd4v\xb41\xec\x87a\xe0\x06\x85\x94!\x9a\xa5\xf7\xd7\x1b\xa1s$\x04\x10&lt;sU\xa4\x02f^\x89C_F\x98\x95\xac\x8f5q~\xa4;\xd7\x15Z:\x07\x83&gt;|\xb7)\x89c\\~a\x9dN\n\x90\x10\x16s\x11\x1d]\x90\x039F\xe6\xfc\xa1\x87\xb6\x91\xa1wH?\xdb\x92\x0b]\xbc\xce\xfb\xc7\x08\xb9yG\x80^A\x1f~ \xc3I\xed\xd4N1\xb8\x0f\xd4\xfa1\xc2f\x9c\xecR\xd7\x05x\xfb\xcff\xca\xdddz\x12\xb2U\x16\x0c\xd6\xbb\xc4\x81\xf1@\xb3\x8a+E\\xG\xe9+:\x9dE\xe3\r\x15s\xbaZ\x15\xd1\x08\x0fGQ2y\xa8\x9f\\\xdc\xbb$\xe1\x12\x88\n3^y%\x8b\xb37i\x84:*d&lt;eYZ\x0e\xd1\x18/\x02\xc5\xf5\x86\xca"e\xe3\x9d\x16Q\xc2\x97Z\xd9\x8b\xff6\x1d\xbc\xbf&lt;\xe8\x81\xae\x18\xd7O\\\x0b\xf9\x8b\xb6n\xfe\n\xf0\xe2\x94\xf9s}\xab\xe11V-\x11W\x10@\x81\x1a\xd3g\x87\xc0\xd9S\xde\x8a\xee\xfdD\x80\x1d\t\xd7\x83\x07\x9b\xb4X\'\x19c\x19L\xf3\xc6\xcdh\x919\xc0\x17\x90\x12\xaag\xf6&lt;\xa0\x92\xedc\x7fr\x97L\xef4\xa5\xbfA1\x01\r\x98\xa8\xe4\x06\x14?\n\xc4S\xbaW\xf4\xea\xde\x8a\xb6;\x86\xce"\xf55\xbe\xbf$\x18L\xf7\x01\'`lL\xcc\xd2y\x94\x82%\xd9Nn\x8e\xa5tq\xf3eG\xa2O\xf0\xeb\xa7\x12\xc7\xfeU\xff[Nx\t/\xc3\x0f\x82j\x10d&lt;\xa5mLG\xc5\xc6\xb0Q/{\x13\xb02\xb5P\x1d\x1d\xfa\x85a\xd9B\x15\x19\xe1\xf6\x1d\x06=T$\'\xccD)\xfc\xe0\x9fp\x07\xf2G\x00/wp\xe8\x8b\'\t\xacM_\xfe\xd0\xf5\xce$\xd8\x12\x90)vVgo\x081\x08x\xbe\xb3 \xbd~\xde\xc7D\x87\xa8,I\x112\x15$B\x8dQ-\xc4\xcbF\x96\xbb\x97\xe77\xe9\xeb6\x10\xb8\xd2id\x04\x84\x96/\xcf*\x05\xdf\xd9 r\xc3\xe4VC#\xff\xfeH$\x05\xca\xdc\xa1\xf7_\xac!\xc7\xe8\x02G\xcc\xfc\xce\xaf/\x8e\x17\x96\x10\x82r\xee;K\xcf\xecu5I\xe4p\x03)k\x04\xf6\x8f\x8a\xf3\x87\x8b\x999\ns&lt;\xc5\x12m\x1ef\x19\x04\xae\x8b\xe9\x96\xb4\x13\xa6\x8b\x07\x8c\xd3\xf5\xc5e\xc6\x0e\x8d\xa9\x18}\'\xee|\x17:\xaf\xdc\x809@\xb0\xe5\xa4\xb0\xa4\xd8\x08\x08t +\xdd|\xea\x1e\xfcE,\xb5&amp;=),\xc2U\xc3\xee&gt;9\xf0\xea\x14K\x17\xdaE\x03Q3\ty\x9e\x8dB\</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Kit 10 Unidades Ratoeira Adesiva Cola Rato Aranha Barata</t>
+          <t>Livro A Psicologia Financeira Morgan Housel 1a Edição Lições Atemporais Sobre Fortuna, Ganância E Felicidade 2021 Português Editora Harpercollins Brasil</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>R$</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>54</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>50% OFF</t>
+          <t>90</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.mercadolivre.com.br/kit-10-unidades-ratoeira-adesiva-cola-rato-aranha-barata/up/MLBU3007857169?pdp_filters=item_id%3AMLB5284576998&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB5284576998&amp;sid=affiliates</t>
+          <t>51% OFF</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_922431-MLB94682949358_102025-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Luva Tirar Pelo Pet Roupa Sofá Mágica Luva Reutilizável Removedor De Pelos Pet Preto</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>41% OFF</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/luva-tirar-pelo-pet-roupa-sofa-magica-luva-reutilizavel-removedor-de-pelos-pet-preto/p/MLB66170458?pdp_filters=item_id%3AMLB4574254285&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB4574254285&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_744088-MLA107394051668_032026-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Kit 2 Cortina Led 300 Leds Pisca Natal Decoração Fio Fada</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>44% OFF</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>https://produto.mercadolivre.com.br/MLB-5389076918-kit-2-cortina-led-300-leds-pisca-natal-decoraco-fio-fada-_JM?extra_comm=true&amp;searchVariation=187954248661#polycard_client=affiliates</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_626777-MLB96109552820_102025-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Kit Cartucho De Gás Campgas 12 Unidades - Nautika</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>45% OFF</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/cartucho-refil-gas-campgas-nautika-ntk-12-unidades-fogareiro/p/MLB2043857624?pdp_filters=item_id%3AMLB1188886162&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB1188886162&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_752720-MLB89432546149_082025-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Envasadora Manual Para Docerias E Confeitarias Envase Líquidos E Pastosos Rg-a03 - Registron</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>280</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>23% OFF</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/envasadora-manual-para-docerias-e-confeitarias-envase-liquidos-e-pastosos-rg-a03-registron/p/MLB46071772?pdp_filters=item_id%3AMLB3754614413&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB3754614413&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_821671-MLA100082632757_122025-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Controlador Temperatura Mt-512e 2hp Full Gauge (c/ Sensor) 127/220v</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>24% OFF</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/controlador-temperatura-mt-512e-2hp-full-gauge-c-sensor/p/MLB34281514?pdp_filters=item_id%3AMLB4746240384&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB4746240384&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_984355-MLA95502023008_102025-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Rodo Rodinho Limpa Vidro Cabo Telescópico Janela Sacada 2x1</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>21% OFF</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/rodo-rodinho-limpa-vidro-cabo-telescopico-janela-sacada-2x1/p/MLB25088337?pdp_filters=item_id%3AMLB4161940375&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB4161940375&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_813259-MLA99587329714_122025-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Kit 50 Saquinho Saco Organza 10x15 Branco Lembrancinha Joia</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>19% OFF</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/kit-50-saquinho-saco-organza-10x15-branco-lembrancinha-joia/up/MLBU1744793325?pdp_filters=item_id%3AMLB4291598994&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB4291598994&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_948064-MLB94890710513_102025-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Kit Spa Dos Pés Amaciante Para Cutículas E Calosidades Repos</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>699</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>22% OFF</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/kit-spa-dos-pes-amaciante-para-cuticulas-e-calosidades-repos/p/MLB27418055?pdp_filters=item_id%3AMLB4290073617&amp;extra_comm=false#polycard_client=affiliates&amp;wid=MLB4290073617&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_604844-MLU72604885303_102023-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Par Suporte Quebra Sol Palio Economy Siena Strada Original</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>426</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>29% OFF</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/par-suporte-quebra-sol-palio-economy-siena-strada-original/up/MLBU1730235137?pdp_filters=item_id%3AMLB1876768129&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB1876768129&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_678436-MLB108744448528_032026-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Massa Restauração Dente Quebrado Tampa Buraco Provisório</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>14% OFF</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/massa-restauracao-dente-quebrado-tampa-buraco-provisorio/up/MLBU2778687994?pdp_filters=item_id%3AMLB3909117631&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB3909117631&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_760928-MLB107595402776_032026-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Chave Para Tirar O Braço Axial Da Caixa De Direção</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>27% OFF</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/chave-para-tirar-o-braco-axial-da-caixa-de-direcao/up/MLBU747499881?pdp_filters=item_id%3AMLB2125942131&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB2125942131&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_816203-MLB108651195412_032026-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Descanso Pezinho Lateral Bicicleta Com Regulagem Aro 20 A 29 Marca Homeroarte Preto</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>159</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>9% OFF</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/descanso-pezinho-lateral-bicicleta-com-regulagem-aro-20-a-29-marca-homeroarte/p/MLB65144012?pdp_filters=item_id%3AMLB3902345975&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB3902345975&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_749474-MLA105680422414_012026-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Kit 16 Bonecos Roblox Articulado Brinquedo Personagens</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>34% OFF</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/kit-16-bonecos-roblox-articulado-brinquedo-personagens/up/MLBU3566296448?pdp_filters=item_id%3AMLB5936637532&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB5936637532&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_704985-MLB98376230413_112025-AB.webp</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Pressostato Cebolinha 1/4 120160psi Compressor Suspensão Ar</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>R$</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>19% OFF</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>https://www.mercadolivre.com.br/pressostato-cebolinha-14-120160psi-compressor-suspensao-ar/up/MLBU3402614222?pdp_filters=item_id%3AMLB5661585416&amp;extra_comm=true#polycard_client=affiliates&amp;wid=MLB5661585416&amp;sid=affiliates</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://http2.mlstatic.com/D_Q_NP_2X_624776-MLB91541087399_092025-AB.webp</t>
+          <t>https://www.mercadolivre.com.br/livro-a-psicologia-financeira-morgan-housel-1a-edico-licoes-atemporais-sobre-fortuna-ganncia-e-felicidade-2021-portugus-editora-harpercollins-brasil/p/MLB19320442?extra_comm=false#polycard_client=affiliates&amp;wid=MLB5270193474&amp;sid=affiliates</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>b'RIFFR&lt;\x00\x00WEBPVP8 F&lt;\x00\x00\xf0\xe1\x00\x9d\x01*\xc0\x01\xc0\x01&gt;m6\x96H\xa4#"!#\x97\x89\xa0\x80\r\x89in\xf2j=\x99\\\x11\xce\xe5\xb4\xb1\xfc\x0e\xe3\r\x96\xc4\xd8\xa8w5\x9fOJ\xbf\xe0\xbd!\xbd4\xfaK\xf3\x01\xe6\x99\xffc\xd5\xdfE\x17\xac\xb7\xa4\xed\x92\xbf\x96?\xd8zO\xf1\x0f\xf2\x1f\xdf\xffn\xbf\xb9zW\xf8\xef\xcd\x7fv\xfe\xdf\xfbS\xfd\x9f\xdco.\xfd\x93\xea_\xf2?\xb5\xbf\xa0\xfe\xf5\xfb\xc5\xfe\x03\xf7?\xee\xff\xef\x7f\xee\xff\xc1x\xd3\xf1\xe7\xfd\x9f\xf1\x9e\xc1\x1f\x91\xff9\xffW\xfd\xcf\xf7K\xfcO\x0c\xce\xc7\xff\x03\xfe\xf7\xf8\xbf`_l\xfe\x9d\xfe\xeb\xfb\xf7\xe4\xff\xa5\xf7\xf7\xbf\xe1=E\xfd\x1b\xfb\xb7\xfb\xbf\xb7\xcf\xb0\x1f\xe4\xff\xd4\x7f\xd9\x7f\x86\xf6{\xfe\xaf\x86\xff\xda\xff\xde\xfe\xdc|\x00\xff-\xfe\xdb\xffK\xfc/\xe5\x8f\xd3\x8f\xf5\xdf\xfc?\xd1\x7f\xbc\xf4\xe9\xfaO\xfa\x8f\xfd\xbf\xe7~\x03\x7f\x9d\xffq\xff\xbb\xfeG\xdb\xaf\xff\xff\xba?\xdd\xdf\xff\xfe\xec\x9f\xb6\x7f\xff\xc7\x13\x8eAv\xd3\xd4\xf8)Q\xdaT2\x10\x12\xa3\x8f\xb5\x1e\xbct\x8f\xf2Oi\x9a\xe9\x1c\xf7\xdfd\x1d,\x9e\xaf)\xb9\xcfT\xba\xd8\x87 \xbbi\xeaf\rx\xa2\xbaqs!\xe6\x8c\x94\xa0u\x0bq:\x134C\x06\x9e\x9c\x17"\xe1\xaf\xb2yX\x88\xa0\xb5\xeaa\xfe\xdc\x16\xef\xed%\xe0\r\xad\xb8\x94\xbd_\xbd\xe8S\x14b\xc9\x1d\xa5C$"\x84\n\xb5\xbd\xbf\x9cs\x96\xdd\x97\x84\xe3O:\xdbX\xed\xba\x9c5;\xd2\xee\x91@9\xd3\x05-\x0f\xda\xaaYL\x88\xfb=!\x9co\xbd\xea\x11\x94\x9e\xdcv^\xd3--O\x9ezG\xe4\xb33\xce\xaf\x0fu\xdac\xcej8\x0c}\x90U\x10\xda7\xf4y\xdb\\0z\x99\x1c\x82\x08\xc1\xba\xf5\x12\xc0B\xed\xa7\xa9\xf4/\xb5\xd5\xe5\rra\xa5\xc1\xf3{j\x14\x99\xeb\x83\xa9+\xc5e$\x1a5\x19_\xec\xdf\xf4\xd0K\xa8\x08\xf9\xdc\x99\x83Y\xe8]\xde^v\x0e=\xf5\xfb\x91MP\xfcy\xfb9\xff\xd4\xdc\xbeU.\xb6T2\x04n/\x92\xf1T\xa7"b\'\x8eG\xf2\xeb\xd5\xec\x15\x88\xf2\xdd\x0e\\\xcd\xe5\x87o\xad\xd7\xb8z&lt;\xa9\xce\x96\x98\x80\x12\xa5O(\x9d\x97\x8e1\x84+8\n\xbaxi\x8fNAD\x19\xea:\x9bK\x88^\x0bw\xa6X&lt;naYZ\x95\xc4:\xf7\x88\xd6z\xfb\x11X\xe8\x90K\xfe\x81 \x85O\xf4\xf8.\xb6T[\xb72\xa2zD-?\xe0\x80A\xbd\xe7\xa5\xc1\xbeSQ\x0cQ@\xf0a\xa3SE\x97W\xa9\x86SL6\xa5\x9bL&amp;t\x02\xbd1\xb6m\xf0"6x\xfbID\x9b\n\xb9\x01\xf19C\xb0\xfa\xa9\x0bq\x9ac!\xb1\x8at\r\xcau&gt;\nT~\x91\x10\xa0\xbcG\xa6PS?\x17(\x01HNJ\xa8k\xb2jj(e#\x8b\x85\xf2\x91\xbe\x94\x93.\x8a+\x85\xa2\x1a$\xc2\x0f\xc4\xf3\xbb\x1a\xf8\xcd` )\xf8\xeaAmI\x1f\xac\x8a\xc1\xe5\xe7\xc1\xf1\xea|\x14\xa8\xee:\xc8\xe7\xb1\x85K\x94-\xb6x\x03L\xe0\xe3N[\xb3\xecR\xdeS\x9b\xef\x1d\xb4\'\xb6\x02\x07\xcd\xddW\xb8\xc5X\xc5e\xe8YWn\xb46\xc6\xfex\x8b\xca\xf7L\xb9\xa1\xc8\x1d\xf8\x89\xe9,\x90\xa5y6\x11\x82r\xee]X\xc6\x90\xd3\xd4\xf8*\xc9\xd2\xb9\xb73H\xbc\x9e0Q[G\x1d\x9f&amp;M\xe2\x05\x11C\x91\xa6n_\x05*;7\xfb\xf6\x07*T\x95\xea\xf8\r\x939\x91\xa0\x86p\x94\xaa\x8emG\xd6"\xa9\x8e;g\xed\xc9\xbc\xe8\xf8:BC\x85\x12\xcds\xfcD\xc7\x03\xb0\x1a\xd0\x8f\x9bY\xfcGLgz\xd9P\xc8A \xe9&lt;\xad\x9cE\xa8\xb1-\xb1)l\xb3\xa8\xa9%\xa4\x7f\xa2=0\x87a\'^\xfa\xef\xf4\x12\xae\x9f \xba\xe8\x93r\xf2W\xd9\'\xe6\x8c\xcd\xfb]\xc0M\xa2\xaf\x15\xb1 \x15\xfc*\xc9\x07K\x7f\xe4AJ\x8e\xd2\xa2\x98\x9f\xee\x16/\'\xac\x9d\xab\x16\xc3\xf0\x1f\xcf\x94c~`\xa5\x96\xc9\x87\xc8\x9c\xe7\xe5\x1b\x7f\x9b\xc2\x81\x9c\x01\x87Z\x047\xe2*}\xce\xf9\xe4\xd5\xc7\xf3\xcdD=k\xc9\x024\x8e\x1d\xbb\r/2\x10\x12\xa3\x94\xc1\xf9\xcf\x08\xadX\x96V\x9b\x18W\x00(\xea\xab\xf7\xb7qm\xaf\xa9\x0eK\xe3\x17\x98z\xdb\xff\'\x1c\xf8\x89\x97rv\xa7\xafq\xc4\x83\xc6q\x80\xe6k\x85\x9e\x85\xcc\xc9-X6\x8f\x1b\xac\xbcr\x0b\xb6\x9c\x04\xa8\xce\xf8|\xf4\xb7\xb2\x99P\x10GM\x80\x03\xbal\xbd\xcf\xb2V`i\xa2h\x08\x0e\x9a{\xc5%|\x11c\xae!&gt;\x15\xad\xf0+t{\xd7\xf0\xc5\x91\xabRT\xc1H\xd1\x8d"\xda[Z\x8a\xb5u\xf8)Q\xdaW_ \x87\x90(\x1c\xca"\xce\xf9\xcf\x8b\xafD&gt;\xc7\xae\xbe\x8a\xd2\x8c\'S\xe6+\xe1\x01\xd6\x07M\x1c=\x1d\x97\xcf\xd7\x0b\xa1\xec\xc1\x98o\xe6\x98\r\xdf-P[\x9b\xfaO\xe4\x14\xb3g\xa9\xf0V,\x9f5v\x94W\xcb\xdc\xe1\xf5~\x8c^n\xb4\xc2O\x16\xa6\x0f\xe3\x15L\'\\YG\xfa\xf9\xf8y\x12QD\xc7fP66x\xafI\xc2b\x02P\xde\xdc}O\x82\x95\x1d \x94\xbf\xb6\x0b\xae\xf6a\xc4\x90[Vi\xe76\xe3\xdd\xcb}\xfd[l\x9e\xfe\xbd\xeej\x03\xf5\xea\x95\x1d\xa5CK\x9b\x01\x18\x9e=\xc3\xac\xa5\xcb\x86\xf5\x8bx\xcd!\xc7f\xb6)\xed\xf5\xe3d\xe45\xeeM\xcf\xf2\xce\xf1\xc2\xaf\xd3a%KLq\x93\x98\x99\xedg \xdda\t\xe2\xe7\xe6\x8c\xc58z,\xa8\x06\xcfS\xe0\xa5\xbf\xa8T\x08|\n\xf4\xc4$0d\xc2\xff\x9b~\xd0\xeeX\x0e\x08\xa6\x97\x86\xaa\xf1\x0e\xbcC^\xd0\xad~5tO5F\x7f\x1e\n\xcc\xa5\xf7\xa5\x99\x8a\xc4\xb0LT\xb7\xf61\xb8\x9c~\xc0\xe4\x98d\xd6\x10\xfe\x17}\x95\x10kn\x86\xae-Cq\x8cM\x81\x0c\xe8\x12\x00L\x06\xfa\xcd\x94\xa8\xe4\x18\x8b\xcd\x9b(\xc6&lt;xH+\xda\xb0u\x936\xec\n\x92\x9dYl\xc62)\xd0\xcb\x07\xb1\xbbf\xed\x90\xdd\x1f\x0e\x8f\x1a\x07o\xc3\x91\xda\x17m=O\x97\xcd\x1f\xe0\x1c\xf9\xc7v{\xea\r\xbb\xf3\xa3\xbf\xb4y\xf5Y&gt;\x1e\xf7\xc92\x8brF6w\x9b\x7f\x99=a1$A&lt;Q\x989\xaf\xdd\x15&gt;}G\xc6\xca\xa25~\xc5\x89_=\xce\x9a\xf2B\xe8G\xb8\xd1\xd5[\xd3.\xb8\x0c\x87\x8b\xe8\xb2-\x0f\xb4\'\xec\x0c=\xa1\xe6\x0b\xad\x95\r\x0f\x82\x07\xe25\x0b\xb7"&amp;r\x00\xc4A^h\xfd\x06qG/L;/\xc1-\xbd\x03\x9b@\xda&amp;\xbfr\x8dM)\x90K\xb5\x94\xd0C\xcf\xe5\xf9x\xe4\x17m&gt;\xc8f\x17\x0b\r\x8aVk\x9b\x18B\x99\x0b\xeb\xa5\xd9N\xb8\x99\x97T\t\xed\xeb\xb8\xb5\x8c=\x8e\xb5\x81\xa7\xc3\xd3\x90\xc1\x7f\x08\xf2s\x13\xaf\xba\x14\x83\x14\xca\x9f\xc3U\x91\xcf\xbe\x08\xa2\xc2\xd4\x0f/1\x9f\xb2\x02\xaau&gt;\nT}H\x97\x90\xc4\xfe\xa5)b=\xb6\x06@\xf4\x9ex\x9e\xe6\xcd=O\x82\x97\x16\x1f\xd8\x83\x8d\xdaG\x11\xd3w\xcd\xbb\xc2\x90~\x8fq\xbe:\xcf\xdd;\xe90\xc3\x10  R\xa3\xb4\xa7*\xbewD\xa5\xd07\xfd\xc9d\xe7\xb7\xee\x97\xda7\xd0}\x9e\xec\xa4\xb5\xc9\xe6\xff\xf5\xb2\xa1\x90\x80\x96\x19\x9e\xa9\x04\xa5Gi\xa3\xc5*\x1c\x00\x00\xfe\xfe\xbf\x80\x00\x00\x18\x95\xb4X_ZX\x0bF*\xfe6\xae\x85\xb7^\x10}\xac\x0e\xc1\x02\xbd\t\xf2\xe1\xbfNuM\xd6E\xeb\xfb\x1a\xa0\x04/O\x08\x84\x04\xb8K6\x9a\x9d,\x92H\xaa\xeb~\x08\xa7B\x8d."\xff\xfas_\x0f\xe4\x9d\xf8\xc1q:\xd6\x98\x04\xd8\xd9\x01R?\xf8Z\x92\x95;aUw\x0fEBe\x91\xaf\xe6#)\x8bQB.\xfc\xb1\xc16\x91T;\x98&amp;\xa4\xab;\xd6\xa7\xc1b\xfe\x83fl{\xd88\xcc\x16\xf4\xd5\xcdCZG\xefFW\t]~d\nw#\xe5\x10\x05z-\xb2\x05e8p\xa3\x1c\xd4\xb2\xc1{\xa9\t\xde2\x84T@vD\x15y\xee\x9aB\xf5\xdb\xa3\xf5\xe4\xff\xf6\xb5\xbd\xe3\xb6\x952Mq\xb0\x92\xe54\xae \x86\x02\x0e\x80\xd4\xf8(\xa7)\xb7\xa8\xe8\xa6\xc8\x992\xde\xf6n\x90!\x18e\x92P\xe7"}[&lt;\x0f\xbd\xbap\x83\xed(\x9c\x93mQB\x1b\x88\x0c\x1c\xb2m`H\xe9*\x98"+\xca\xca$AtM\xd1\x90\x14\xaf&lt;\x82,\x90\xaf\xdc&lt;\xe7\xa5\xe0mJw\x83\x1d\xd43{\xdc\xd8\x00mX\x88\x93\xec\x95\x8a(\'\x8a\x98\xac\xf0\xc3\xa3"\x0c\xfe\xbb\x9e\xe2\x8c9\x1aX\xa4N\x0b\x7f\xa2p\x19\xa9I\xc7;N\xaf6a9\xf3\xe0\xb5\xd0Xz\xb7\x97\xfb\xf2\xe0\x82\xb2a\xd4\xc9\xab\xb8\x86x\x00NG=M6\xae\rzNB\x1cFv\xa1?2t.\x80\x89U\xac\xdfg\x11w$\xc7\x11\xdaXQ\xa6\x01i\xd3\xf3\x10\x07\xceu\xba\x9e\x1a\x7f\x0c8\xa0\x06\xacf\xc0\xfb\x96DXZVA\x13i.Hp\x16p\x04\xc4\n\xca\xa7{\xcb\xa8Gj\xeek\x135\x92\xac\x8a\xb4)\x9e\xf1\x16\xdb\xc7\xa0lV\xa9)\xe1X\x90-\xe3\x18=~\xd3G\xbb\xbbR\xb4\xe0\x92\xff\xff\xd2`\xf2\x9eV\x8a\xdd.a\x8a\xe2\x9aY\x9eI\xd4&lt;\xa1"\x16V\xfe\xce5\xa9\x05\xcb\x98\xed\xbe/\x9b#8pSj\xff\xbeWN\x87F\xd1\xf1f\'\xfcy\xfb\xb9\xaf\xa0\x03{&amp;C\xed\x8bCd\xf5\x0ei\x96\xd6Z\x1cz{\xc3\x02\xc1 /2s\xe7&amp;\x0cvJ\x7f7OH\x9a2\xa9`\xf6\x91y\xc43\xaa\xe7\x0e%P\xf8+i5\x8aW\x149\xe9\xa1\x8d\xf9\x00\xae\xa92\xe9\xbfl\x95\xee\xf1\x15v\x97q\xdfl\xce%\x86\xb6\xb2\x13X?\x1dF\x9b("\xdcol\xbbQ\xf7Rf\xd9\xaf\xdc\xe7[\xf1ie\xb9*Zi\x03\x90\xe9\x05\xbch7|X\x9a\xc9\x0f\x0e\x96\x1a\x9f6\x8d\xb4\xb6\x1d\x91\xe5\xba\x87{\xd7[\xc0A\xed\x9e\xceR&lt;*\xc9\x9e\xc2\xaf\xf65\rMc\xbc\x18\xe5m\x99;\x1e\xdd\xf4Oe\xac\r8\xec\x1b\xd5\xbb\x90\xa5x?5:qD\x0b\xf3\xe2&gt;l\xc0\x18C\xae\xe4I[\xfa\x9b;\x9d\xde\xda"\x0fP\x95\x0eGWk\x1c8\xcer ,\x91\x95&gt;o\xba\xfee\x9c\x96fcO\xc9vN\x0fcV\xef\xfb\xef\xe2\x19\x08\x1d\x90\xcc\x18\xd50\r\xc8S\x93x\x00\x08\xc7Y\xe2y\xa3\xb2Wg\xf6\\c\xbf\x94.\x1d6]\xa6\xd2\xde\x94&amp;\xd7\xdd\x9cR\xd5\xfc\xf1\xd7o!\x1a\x93n&lt;=\xbc\x82\xb1\xf9\x883T\xd6\xdb\xff\x05\x1b:\x9c\xd2\xab\xa0\xb7\xea\xa6e\xd6\xe6\xbc\xb6\x13P\xfa\xb9\x8c\x90\x89\xb3g5\xd2\xdc\x99\x8d\xeb;\xec\xb6n\xc2\xc7M\x00^D$\x0b\xedi\xa3\xe8?\xde\xfe~\xcd,\r$x[\xa9V\x8e=\xda\xc5\xfbk6KU+T\xd0\xbd\xa6\xce\xac\x02\xb8\xd3}\x04\xc3\xf6H\x0f\xcc\xbc9\tb\xe5\xda\x8f\xcf\xaf\xb6O\x1cO\x05\xd8\xe5\x1e[\xe5V\x11\x01.\x07q\xbf] _\x88\xcd.;e\nV1\xe9\x11DzL8\xe4,\x94\x13\x1f\xbe\x85\xf94&gt;\x83j`U\xf5\xf3G\xda\xde\x12\x9f\x02\x9b\xd5\xdag\x82Z\x83[{1f\xe2\x1fi\t\xe4`\xf8u\xc7\xc2\xd4\xe5%(\xdb}\x88\xe2\x990\x05R\xae8\x9b\x8b\xd8\xb6\xfc6X\xc5\xa6\x8e\x12|\x87&gt;\x8f\xe2u\xd3?\xf3\xef\xb5\xa1\xd1^\xfd\xb6\xdd\xebDul2\x14&amp;\xd2\xfd\xf2O\x13\xd1\xfd$\x1c\x07\xbb\xc2h\xaf\xa7o:\xfe\x0f\xc6\x13\x8b\xa6\xa9\xb32\x1dV}v\xac\x07\xba[\xf1b\xe4\xac\xce8\xf17Q:\x1fS&gt;iB\xcc\xb6\xc3\x94\x0f\xean{^0\x10\x83U31&gt;cXq\x92\x86\xe3[3No\xbcL\x93F\xa0\xa9:c\xb1,\xfc\x00\xee\xc7\x9b0Ra\x06!\\\x1f\t\xa0\x83\xd3\xf7&amp;\x85\xba\x8aE\x9c\xaa\xd4\x9f\xc0\xd8\x11s\x04d\xb3\r\x11/\xac\xe4\xaf\x8fv\x87\xf2\xf3\x0c\xc0\xbc@\x1a\xb6\xf3\xee5?#\xc455\x8a\xa8J\x92\x96)\xcd\x7fOe\x9b\xe9\x12\xeb[\xb5D\x86|\x07\xf5\xcf\xb0\x13\x1fk\xea\xad&gt;\x15\xe9\xac\xbch\xbdkB\xf8g\xce|m\xba\xa7c\x1e8@\xdc\xea\x96W\x0b\xe2\x17\xdb\xfd&lt;\xcf\xc4\xff\xef\xc1\x91\xbb\xd9\x01/\xa8\xce6\xbc\x1d\xebJ;\'L\xcb\xe7\x80-@\x9f\xbbx\xaf\xed\xa1\xea\xedH\xefhK;H\xbd\xa6d\x13\xfe\x86(\x03\xbb\x83\x1e\xa8\x0cY\xb9Z\xc5\xcc\x96\xb3e\xb1\xc2#&amp;\x92\xfb-\xb2\x99R)V^\x9a\xec\xa7Z\x84\xb1\xcc\xa0\xe9\xbd\xaa\x17\xca\xd6k\xc5uE\x80\x16T\x7f\xb4W\xf4,\x0e\x1d\xdd\xf6\x10\xfe\xeb4\xd1R:\x8a\xd8\x0b\xd6T\xe5S\x07;\xdf\xa5B\xbb\x03\xff\x1ay?\xa4\x9cE\xe3\xf5e\x9ab\x13\xd7\xe64\xd6\xb2\x06G\xae\x9ac\xa4\xea\xdfyP&lt;\xa6~n\xe6/M\x84\x9e&lt;\x84\xa0&lt;\x02\\\x0f\x1d\x875\x82\x98m\xe7i\x87G\'\xed\x11\x86}3\x81y\x01\x87F\x0bQ\x8e\xeb\x10\xddT\xec\xc7\xc1o\x97\xcd\x92\xfe3\\\x14\x91\x1f@@\xdc\xdb\x1e\xd9\xdey\xc3\x02\x17\xcb\x8fC\xcc#\xf9\xf2\x0c\xef \x98\xf35\x13XP\xd8\xe8%\xb3\xe2R\xae\xef\xacAFQn\x8d}\xcd\xba\x9b\x85\xe7\xb2\xa0\xb8*^\xfe\x1e\x87Ni\xaa\xc8\xdf\xe1\xfb6\xae\x97GS\x88\xae\xd3\x01\x1f \x0cL=\x96B\xff&gt;\xc20\xe4\xa9\xc9|\x7f^t\xb6.\x94\xf7Y\x90p\xac\xc1\x89\xfb\x0fb}\xd4\xdd\x8dD+\xa1\x0e\x17\xa9&amp;\x8b\xf5\xfad\xfds\xe1\xca\xd7\xc6`\xc92@D\x84\xa7J1\xffSN\xdb }V\xeb\xcb\xaaq\xbd\xc9\xe9\xd1\x10\x87\xce\xccc\xe7|\x98d&gt;\x83\xe4\\\xd8\x94)\x01\xdf\xe9\r\xe8\x1d\xeb="\x94\xc1Ik\x06(%\xeb\xa1\x05\xae1x5m\x10D2\x05\xef\xc7\x1cg\xe4@\xb1|\xbd\x02\x15\x0c\x1d"fh\xdf6\xd4\x80y\x0b\x07:Z\xfaD\xadv\xd4\x19P\xe9\xbe\x1c&amp;\x10\x8b\x92\xa4XmPF\xae,\xa1\xa6\xe7\xde{\x891f{]\xe0\x8e\x07\x8eA\xb4\x87G\xecJZ\xb7\x00\x96\xfb\xfe\xe9\xf5!9\xf7\x91\x06\xeeU\xcd#2Y\x07g4&lt;\xa6\xadp\x15\xcd\xb1^\xc2\x0c\xa8\xa2A\xb1:gH\xcd\xe4\xe8\x82\xd1e\xb6\xe1n\xf5|\xfaU\x1e\x81\xf9\xadm\xb2fm\xc1\x8f\xeb|1\x9e}\xbb\xbavI9w\xe7\xd2\xc4\x00t\x13\xb1\x86e\xc3D\xac\xd3[\xc4\x16\x08t\xd6x&lt;f\xe5N\x0bY\x03\x96\x02\xf3\x84=\xbb\x15\xa5[\xf1\xd5\xd87\xb8@9\x81;\xc4\xb5C\xc7\x08\x9a\xf7Qm\xf5\xc4\xdeR\x82\xf3\xa7)\x16]\x19\xd2\xfc\xbf\xd1\xd9\xceI!\xb7_&lt;\xb2\xb9\x14\xe7\xec]\x00v\x80\x01\xfc\xb6H8\x8eo\xb3J\x1f\xb3^\x9f3&gt;nkM\xe7\xf6\x9dK\x80#\xadv\xfd,\xac\xbfg\x7f\xf3;\xb8\xe3\xd2\xb6\xb0v\xe3c\xbb\xcbZ\x9e\xe7\x18 ,\xa8\xe9\xef\x11\x1a\xaa\xe0\x7f\xc2\xd7\x8e\x811\xff\x9d\x12w\toL=}u\xa2\xbeM\xb2\x81C\xa4\x1d\xd8\x83\xb5\xce\x88&gt;\xc6\xa7\xa6\xaa\x8a\t\xed~\xfa\x9a\xf2\xa8"0\x02NG\xdaa\x94\x07\x87\xf9w\x85\xe4\x1cF\xedj\xb1+,\x03T\x93&amp;\x17(\xb9\x04\xe1=\xb5A\xd4\xb2\x9a;\xea$}:\x89\t\xd5\x8a\xb6Xx\xa6\x17{\xed\x88\xe2\xab\x9a\xe1\xbd\xf1\xf8\x8f\xe5\x1a(\x1f\x02j\xbe\x8abQ#Y\x8b\x1a$x]\x83\x07,\xae\xadp9+5&lt;&gt;\xf1\x94\xbfy\xea\x89\xa7c\xda\xaa\xb7XiJ\xd9\xde\xc0\xb8\xc3\xc0S\xcb\xa0\x88\xf5\x13V&gt;\xee\xa2\xdd\x03\xff\x84\xc8\xfaf \xc9\x87W\x9b\xca\xc8\x04\x06u\xed\xfe@\x11\xb00\x92p\x11\xe5\x8c*K\xec\x02O\xff\xbfx\x06:\xeb\x07\t4\xc17\x17\xef~u\xcd\xd5/\x19\x8b+k\xc8tG\x82&gt;a\xbf\x02\xefvY\x1d)\xdd3\xd5\xb9\xb5\xf6\xc2G"\xb6/\x16B*q@BY\xa9\x9ea?\x87-\x1cq\xda \xaaHd\xb8\xc4Oe\xdd-+\xe7\xe0-a\xe6g\xfc\x867\xfa\xcf\x11Z\xe7\x7f\xef\xf4G0\x7f\xa3FT!-\x1d\x03\xde2\x1c\xd7\xd4\x9d\x8a&lt;\x1f\xf3\x9c(\x07\x9fh\xaeb\xf5\xce)\xb8hE\xda\xd86\xb3\xf1\xed\xa4\xdb\xbe\x14\x00z\x16\xa8%_\xa6\x86\x9b\xcd\xe6 \xd4\x0e\x85BE\xa2\x1cj!D\xbf\xb3\x99X\x18\xeb9rpC\xf4\xdb\x8aS\xe0\xado 8L\x99:h"\x10\x00\xd3~\xa6;\xd8\x0f\t\x83\xab\x87jE\xda\x05\xfa\xb1\xa8\xb7/!_dm\xa45\xa6;\xe3o\t\x91\xa9\xa7\x80\xf3\x04\xae\xfb\xb6\x1c\x1d;^\x19\xb7w\xa8}I\xe6yi\x13z\xc9\x1b*^"A\xb4r\xf5F\x9e\xfd\x11~\t\xd2\x88\xf6@@\xe5*\x8c\x84\x99\xd9B\xa2\x0c\xc1\xc6\xc1(Td\xb2\xf3\xe9\xe9\xb2\xa1)\x8c&gt;\xbf\x8c\xf5\xe0\xac}\xf8e\x91\xbdH\x81\xff\xd1\x05\xbb\xd8\xd5\xb6!0\x90\xf7^q\xff\x15\xdfE\xf2\xd3\xdb\x87I\xe4\x9c\xad\x90b\x0bV\x80\xd8\xdeT\xdd\x99\xc7&amp;\xeb\xefY\xa9\xda\\\x01\xbfMx\xfc,\x84\xbd \xf8\xa6\xa5\x04rd\xc8\x12Q\xdf,\xdb\x99\x12\xfcg\x9c\xd1\xe7\x9e\xc6.\x95\x97Q\x9e\x0c\x15c\xd4|\x9c_\xc7\xd65\x96\xcb\x13\xac\xd2\x8b\xe8+\x1d\x10-\x92t"\xdf\xc4\xf9\xf1W1c\x0bz\xe8\x17\xfa\xaa\xed\x17\x15]\xe3O\xf3\nw.\rB\xaf\x87m\n\xc2K\xff\x19&gt;}\x8apY\xfb\x1b\x08\xbaRI\xb0\xcd@\xaf\xc7\xd5\xe4\x16\x92\x10F\xe4x\x1fi\xc9|\x1cn+0\xb2X\xa4\xec\xe7\x88#\x82P*7go$\x0b\xb2\x12;:fz;\x9e\x9a\x07\xb4K\x0c\x0bC\x96\x1b\xbd="A@5\x9b\x8c\xfa\xdb\x03\xadI\xed\x18\xa6%\x9aK\xed\xf6\xe7\x83\x02\xc9\xbfGF\x9c\xca\x17\xd6\xad\xc0\xe6\x8cJ\x02\xc3\xf1\x8ef\x16\xafy\xa0\x16\xce\xf9`y\x19j=&lt;\x97\xd3H\x16ov\x88\xa8\x86\xcf\xf7b\xff\x8bv$~-7Y\xef\xfc\x9e\xea\xdb\xa3\x82\x15G\x83\xfa\xac\x9d\xa3\xaea+\xb7\xa7\xb1;}\x0b$\x91\xc9\x1b\x19\xce\x82\x01\xef\xb8\xa5\x12\x90\xcf\x12\x80\x0e\x8aquS\xd7\x0eE\xbd\x01\x18a\tO\xc19\xfe\x8c\xba\xe7\x07\x84#\x88\xf3\x14\x15\rW\x7fH\x9e\xb7xMz\x9b&amp;\xf9\\\x84\x85\x93\xd6\x87\xd0\xae\x10\x89\xc1z\xda;t\xbc\xe9\xd2\xaa\xe6\x08\x18\xdb\x80\xe1-\\E#\xfb\x18f\x982\xe1q2@\xef&amp;\x98\xb1\x17w\xd7L|rm\xba\xc4d\x80R\x00t\x91\x18w\xf3\xc0\\=k\n\xb5Cb?\x9c\x8cD^fS\x83\xfe9\xfa\x0e\xc6h\x03Yp]qN\xcc\xd0_\xe65\xc6\xf1L\xe4U\x18\xe5J\xbb\x05\xd7\xa5[B\xb7\xe9\x014G\x9fQ&lt;\xe04\xd9{Oy@\xfb\xd9\xeesG&gt;\x9a(\x853\xa5\x93\x8f\xc4\x04*\x03\xde\xf0%\xe9%\xa5\xca\x99\x8a\xdcT\xa7\xd9\xd5D\xac\xd8\x96\xd0\x1c\x147\x90\xf0\x80\xfbL2\x89\x88\x93\x9d\xb7\xc4\x0b\x83v\xb9\xc8pX\xcc\x06\x06T\x07S\xb6\x1d;\x01&amp;Ev\xa0Z\xfcT\xae\xdb\x8f\x9f\xd8\xae\xc4\xa3\xa8\x018\x82p:\xef\x0b\x8e\xca\t\x981\xd3`\xc8\xa7\xb6\xf6\xa8p\x90\x00\xbe\xeb\xa2\xbd\xcf#n\x84\tw-\xa8\xe5K^Eq\xfbq\x8d\xeat\x12\xeb\xcf\x06_\xeezQ\xbdrN\xdc!9\xd4Hq,\xbb.\x01\x0c$ks\x95\x9c\x95\xcd\x8d\xfb%\xfc\xb5\x1e\xa8\x9a\xa2h\xd0\xdf\x96\xda)\x9b\xf7&amp;-\xd1`\xe6\x86\xf6\x81\xe9\xd7\'\xba\xd0\x922\x7fH\xf3R\x10\xfc\xe4\x90_\tI\xd9a\xd5:o\xc3&lt;\xabl\xe5i\xd7\xaf\x7f\xd8\x05\xc8\xa4\xbc\xfc\'\xef9J\x82\xcb$\x82\xe1\xd3.*j\xad\x12\xb3\x960\x8a\xaf\x8d\x02\xcf\x1df\x8fx\xe7\x8e\x07L\xdaJ=\x9d\x92\x1c}\xe7\x86yi\x883\xb7):\xe8\xcc\xe0Zd\nu\xfaG\xbaq5F\xd6\x14`\x9e\xbd3e\x18o\xd7\xfc*\xb1\x1b\x8a\x9cg\x7f\x0c\xf2\xd6\xf2X\xc9\xbc\x0e"o\xec\xc4%\xc6yq\xce \x0cF%\xae6Q\xe4?@q\x98\xc1\xd7\x04\r\xb2\xa8\xaf\xac\x01\xc2\x06\xba\n\xc3\xd3r\xc5v\x996.1R,z\x87\x03\xc8\x00e\x96/r\xbc\x0f)k\xbe|\xcb\x8f^s#\x86\xe7\x1d\x9bs\x18\xbe\xafs;\xb6 \x9cU\x86^\xf0\xd4\xdaL\x14L\x7f\x8bx\x85(S\xf8\x10P\xe3Hq\x8e\xf1\xbf\x0e?\x1b\x0e^\x8b\x0eb\xd5y\xc8y/&amp;\x92V\x9eC\xb1\x1a4\x1d\t~\x18I\xed\xaf\x0ep\x1a\xc4\x9d\x87\\i\xbf\xce~C\xdbg%Q\x00\xf8)\'\xb4\xa9Z\xdb#k\xec3\xe7\xd8V\xdd:)\xceWf\'\xf4\xe6k+K\xf8\xa2\xcf\x9b=i\xce2n\xc0\xb9U\x17\xcd\xf4\xca\xf1y\x82w\xb7 \xb2\xb9\x13l\x94JeIW\xfb\xa0\x91\xafP\\M\x9c\\\xc0\xc1\x94&gt;\x8b\x00\x97\xc6\xba\xe1\xfa\\\xbc7\xef\xa5G\xef\x10\xceX\xbe\x05I\x08\x84e\xb9Q\xf1\x8cM\x95\xdc\xcf\x97,\x94\x1c\xecO7U\xfa\xd7\x1a\x95l\xbe\xd2\xe5\x1fm\xbd\xc7V\x90S\x9e[m\x03\x8e_ \x11Oy\xc3\xfb\xc5w\x99\xe9\x19@fs\xb1\xd5\x04\x98^|_\x00\xfb\xe8\xa9I*\xff\xb2\xe7\x83\x0br\xc7\x13\x02\xcd7\x9d\xecZ:\xfa2\x96O\x02\xcc\x97\xeb\xe8\xee\xd1b{#.p\x82\xfb\xa4\xa3eX\xcc6Y\x010\x19&lt;1P&gt;]2\x10\x8c\x08\x13\xea\xba\xb2l\x01\xa0\x8dj\x0cSb\x9c\x13\xf2[X^i\xa5x\xc7\x87q.v\xc2\xb1?\xa3h\xb7m \x82\x84\x8c\xb5\x1c\x96\xbdz\x97e\x18\x10\xf9r\xeeuy\xd2\xf3\x87\xbf\x10k\x8c\xa0;\xc0\x1fP[bh\xcc\x1a\xe7\xa0W\x16\xe8\xaa\xb7\xdd\x00\x92"\xc5\x17\xee\x15\xe8V\xa1ea\xe9TR\xc4W\xdeF\xaf(\xbd\xbcN\x95,\n\xfb\x140\x04\x88yO&amp;`?\xdfO@\x12\x94i\xdf\xf2\x8d\xf7T\xca\xce\rL\xc3\xb0\x12\x03\x1a[\x1a\xe1\x8c\xd9\xbaV\x1dmh\xac\xad\xf6\xc4\x1a\xe8\xe8\xee[0\xaf\xf2\x04=\x83y6\x01\x9aF\xd1\xa434\x92\x10\x10c\x80\x07\xdf{d\xb3\xa3=\xf2MQ\xc3\xd671\x854\xa8B\xda{&amp;\xdd\x9f\xdf_\xe5m\x89\xb1\xc2s\x81\x05A\x10^\x15gx\x99\x85j|\xf6&amp;E\xc8&gt;\xacN\x97(7!7\xc7\xfbf\xc6G\xbe\x0b3\x1b\xfe\xd7Q\xd5\x9b\t\x106N,\xea\x85l\xc9\xc4T\xc2\xd0tL\x17[\x1e\r LY\xfa\x82\x91\x12\xba\x80;a\x8d\xd7\xd9\xe25U\x91\x052\x8b\xc1q\x0bv\x16\xb3;tb\xa0DxxQp\xc9\x97`\xae\xfbw\xcfK@\xb0_\xb6\xcfR\xf4\x031\x02\tR?\xfb}\xd4\xec\\\x8e\xd1\xb9\x01\xfa\xa0\xe84\xe7U\r\xa3\xdd\x81y\xad\xeb&lt;B\x1aOJ\'\x82J\xbc\xb7\xc9"\xc8z\xb2\xcd\x9f\xa4 X\xd5\x1f\x18b\x8d\x831\x95WpWK8\xc4\xef\xda\xbd\xbcKl\xd5\xb1\xe7\xe1O\t`;6\x0c\x04\x94\'\xdb\x91\xf1\xd7&gt;8Xg*\x9c\xb0&amp;\x07\x05\xbc#X\xe3\xee\x00\xb8\xd8&lt;\x89\xfe\xbeo\x01\xad1\x7f\r^\xef\xa1\xf8-\xa1\x8e\x99\x17s\xfd\xcb\xb4\xb5\x91ycH\xc1\x03\xfbA\xff\xd3PM\x02 \x92\xbf\x1c\x96\xc2B*\x9c\x8f\xdao\xbf\xba;\x10\xef\x96`4=\xe6r3^\xc6\x9d\x19!d-\xfc\xd0\xb2\xe0|H\x0e\xb9OtOQAb)\xea\x01\x83\x16\xed\xf3jdosS!\xc5\x8d{\xfd\xb1\x13\xb4\xe3\xcf\xf5\x8d\x1d\xec\xc5\x93\x87\xfc-\xd9\xf0\x0b\x08_\xa8?I{D@{\x05\xa0W\xc0\x0b0\x88\x94:&gt;M\xf1\x16\xcfA\xa2\xe2\xf1\xc8\xd2\x9e\x9b\xd3\x86d\\\x93@\xbe\x10\xac\x03\xbf\x90\x9erG\x0fgbj\xb4Q\nH:\xfa\xb9e}\r\xa4\xc4\xcaN\xa3\xf1\xbd\xdf\xdb\r7\x86lX*\xa6\xd2\xa0\xdd\x86x\x14P\x80.\xf8R\xc6\xa78\xb1rb\xea\xa8\x96C\xa1n\xd4=/\xe3\x8fE,\xf4\x19\xa1L\x94\xf7\x1f\xb4\xb3|K!\xd9\x88\x9b\xab\x18"\xca%\x07x~\xbf=\xea\xeb\x17\xfe\x8b\xd3g0V\xe1\xa3(g\x90\xbb\x0c@\x17\xf9t\xfc1L\x80\xf6\xf9j.L\x10\xabUX\x1cK*\x8a%\x89!\\\xb0\xadZ\x89\xb7\xc3\xc8\xbei\xc1\xec\xb0\xf5M\x1a\xc8b\x16\x14M5\xcf\r\x11#\x18\xa0\xdeu#A\xe0\x7ft\x1c\x80V\xe9E\xb4\xd6\xb2\x16\xbd\x1aC\xaa\n\xf7\xab\xf5(b\x0b\x05:\xc7\xbc $Q\xdeI\xff\x15s\xe3l,\xd9X\xc8K\xeeY\xd6\xcb\xa4\xfb\xdf\x03\xbeJ:&amp;\xca]c\x8aiN4t\xaax\xd2\x15\x96\x07T\x163r\x8e\xc7\x95\xc4\xd7Q\x08\x8d\x96\x98\x89\xbc*\xe3H\x8eb)i\x08\x84\x15\x0f\xdc\x142\xb7\x9f\xca%9D&lt;\x01\xdaYT\xcb\x8d\xe01\xef\xa9\x08V\x82\'.\xe4\x1c\x87\xc5\xa5)o\x96\x8d\x99\x9a\x9b\xc1\x828\x7f\x7f\\lv\x81\xcc\xf7\xd3#wZ\xb0\xd4#\xfb\xcc\x8b|\xb5\xd1\xf9Tf\x1d\xeaO\xaa\xf7\x08\'\xc4\xbc\x10\xf4\x08\xe9t\xd9\xd8,\xa9\x0b\x9f\x8e\xd9?\x94\xc1(\x1c\x95\xc5\x8b\x9e\x85\x84\\\xf4\xc5\xfa\x03\xe0\xdaD_\x9b02\xa6s\xb0\xdf\x83\xae\xbe\x08\xb2\x1f1\x00\xa6D\xd5\x08\xaa\x82\x8a\x8b\xf9_dS\x81\xbb&lt;\xc6\x8a\xd4\xae\x8aY\xf7\xe3!N\xf9v\xd5\xf3&gt;\xa2a\x11\xb6\x84&gt;\xe7S\xfc\xb8P\x83\xf5\x98\x16\xfc\xdc\x9a[\xf0\x81\xcd\x90c\xc9}GK\x85\x184\x8e\x8ci\x95\xda6\xfem\x82\xf18\xc6\xb0\xe6\x11\x97\xd0\x00P\x15\xbcq\x05\xddHb!\xf4\x075&gt;P\xf7\x97\x9d\xdb\xa4\x12\xcbT\x82\xb0\x85\x08\x12;Z@:\xa9\xfc6V:\xd9=\xfe\x1a\x0e\xd4\xaa\x04Z\xbf\xf3oS\xd3\x82\x04e\xa2\xfc\xfe\xeaw^A\x00\xaa\xd3\x90+g\xfaj\xbdS\xe8h\x0eG\nI6\x82*R\xf3\x8d\xaf\x82\xa3S\x1b\xf25\xbe\xcd\xf1\xb6\t&amp;\xb7\x07!\xe6\x16\xe9\xc7x\x06\x1f$C\xfe\x01\xe0\x96\xc3\xe1\x9b\xf7\xb2J-\xdb\x9a\xfa\n\xa5*(P\x98C\x1e\xc8\x9b]y\x94\xa4\xe0\xaezO!\x9a\x1d\xea\x10\x11\x033\xca\xbe\xe3\xacg\x8c\xabq\xb8\x01\xf4Q\xbe\x90\xf8\xce\xea\x80\xd5\x14\xdb\xdc\xd0\x8b\xf5\x1c\xa3\xd7\x90\xaf\xe9\xc1~t\xbb\xd0\xe6\xdc(\xc7]\xe4\x1aZ\xd1\x1e=\x96\x13\xec\x18\xb5\xe3\x8e\xcf\x9e\xedtGw|j\xb6D\xd0\x12/\xf6`\xa9\x94\xd9&gt;\x87\xc2\'\xc5\xe5\x89\xd3\xe4\xe9\xbc`\xb2\xbc\xbb\x0b\xe0h\x8d\xdb\x1e\xc4\xa3\x83*\xedb6\x1c1\xe5\xcc\x8c\x93\xd8\x8elE\xe3\x1d\xaao\xc52\xdd\xde\xddluz\xe7J\xdc\xab\xb6/"+\x9c\xf0\xa7d#\x83\x84&lt;\xe8\xc0\xdf\x98\x02\xf64F2&amp;\xe9\xfc\xba&lt;\r\x04_\xa7b\x9f\nz&gt;5\\\r\xd0\x15\x9bd\xb2V#XU\xa0\xbb!y\xcc\x8ak\x8d\xb9\x17{\xbaN[\x17\xf9\xce\x8e\x95A\xc7\xd7\xc8\x8a\x04\x12a\xc9\xa9\xd9\x9c\x1bM\xb5\xbb\xe7\xb3\xe3u\xc1"L\x9c\x03@\x93\x80\xca\x07\x94\x8d%pa\xdf062\xfe\xdd\x9f3\x9f|\xae+c\xaa\x81\xb4^\x90\xfa\xab\xd8\x8dB\xbd\xeb\xf9\x16?+\x10\x91I\xb6\xd7\x15Yn\xb1\xf5s\xe3~.\xd1\xe2\xa5((ae\xdb\xf0\x97\xfc&lt;W\x8dN0\x1d.\x87\xb8\x98fz\x98\xee\xe6\x87\xe4\xaf\xfe\xfd;\x16\xb0\x08\x87\xdaF\xd9\x99\xf0\xeb\xde\x91\x16\xb1n\xeexv\xf1\xc3\x07\xdd\xe2\x8a\xd0\xcdB\xa7\xf0$\xb8\x16B\xa6+\xf5\xea\xb8L+\xbc\x04\xead\x19~\xec\xad\x81_\xf0\x9b\x05\x83\x90*\xe50\xb5\xb1C\x11\x9e\x0f\x1d\xcb\xe00\xc9\xde\xe1\x8b\xa2`\xe5\xab1\x0cs\xe2\xb5\xfe\x02M\x12\xd0\x1b\xefV}\x08^Z-U_\xa8\x08\xafl\xb9\xff\xd5Z\xf3\x9a\x8aY\x84Dr4R\x96\xb3k\xf3\xc5\xa8\xffNu6$\xbc\xa8\xe1\xc8\xbaNrs\xccD\x93x#\x1f0P\x18h3-\\&amp;\xabsH\xd9\xdb\x17\xc1\xb2\xb48\x10\xfc\x07\x9bQ\xab\x08\x06\xb38\xa1I\xef\xbd\x18\x18o\x02f\xb2\xc6e\xd1ii\xfe\xdd\x15\xc9\x85\xed$\xa9\xf2 X\xa9\xea\xd77\xbaI\x00_4\x8dn\x98_\xa4\x99\xf1\x89"~6\x1e\xdd\xa2}\x03\xd1\x86\x8b\x8b\xe2V~\xc6Rg\xd6\x15|%`\x12\x1fZaH\xdc*\xfeZ\xe87I\xb3\xd0f\n\xf8\xc4\xfb\xa2\x14\xb2;\xb1\x1b\xf4\xd4\xd10\xc9.\xe7\xc74\x82\xd6\xd8~\x88\xb5\xd3\x9aA\xd2\xa8\x7f\xa8\xc3}\x8aE\xb1\x14\xfc"\xd8\xe6\xe2.\xbc\xe7\xfd1B\xb1\xd7\\\xb6\xdf\x0c\x155s\xa2\xd1&lt;\x07\xa6Tk7z6D\xcd\x1d\xec\xa9\x12\x06\x15J\x85\xde\x81\xea\x1fM+q\xba\xb9\xa0\r\xf0\xd0j\x03Y\xc3\x0fI\xe7zd\xb2\x1a\x06\xbeb\xca-\xa2\xd9&lt;\xf6o:~\xc5a\xc5\x00\xe5\xcaD\xb8\x86\xc3\x7f!fT\xbf\xfe9;S\xcc&gt;R\xe1S\x05$\xce\x10!SU\xa3\xf0T\xa6hN\xd1\xf0\x8c\x98"\xa9\xb5\x8b6\x9eK\xafB\xb6\x7f\x04\x0c3\xc5#Zg\x1e|=\xbb\xcc\xdc\x83Y\x9e\xb3l\xa0\x13\x1d\xc7\'\xcc\xb6\xdd5&lt;*\xa7\xfd\xbaH :\xa3\x94\x9e[!\xca\x96\xec\xf2f\xf3\x14\\\xb5\xdfm\xfc\xe5\xaa\xf2*K\x8d\x9f\x9c\xafu\xcdm\x92\x991\x8d@\x93\xc6R\xe0#\x0b\xe3Vn\xfbZL\x1c\xf8b/\x97\xber \x85\x1c\xa0\x88I\x98\xbcvu\xf6\xbf\xd5CQ\xce#\x1f\xad\xe7c)\xdd\xcc\xb0\xca\xa33;\xbeJ\x03^@&lt;\xfe\xf3\xbfs_KH\x88V\xd0\xb7\x8f\xe8T\xc7\x99\x7f\xefg\xde\xca\xfe\xed\x99\xf3\x0b\x80\xc8w\xc5\xe0N9\x7f\x9au\x92]E\x8f+\xf1V\xe6\x94H!\x9eq]\xab\x06\x18\x8e\x1c\xfe[\xc1H\x87baH\xba\xaf+TS\xce\x06&amp;Qu\x95G\x13\x01\xcf\xe6W(\'\xbf\xc0\x99h\xe7M\xd5v\xe26t\xb8AE\x89)v\xfb\x0fH0\xbf\xe80\xb1\xeb}\xf7I4\xce\xa8&lt;\xb0\x1d\x92&lt;ipS\xdb\xea9\xfb[\x88\'c*\x07\xdd\x83y\xa4]\xbd?\x0e\xf8\xbb\xc3Bpo\xad\x1a}\xbdy\x1e\xadw\x0f#\x8c\x87\x9bJp\xbd\x88Xuz\xd3\xb9\x8d\xa9f\xfd\x87\x14p\xac\x00\xbd(\xa3\xe6\xd3\xe7t\xbd\xeb\xa0N\xe4;\xbc\x11\'\x1bL\n5\x19\xccP\x82\xcb\x83\x87\xcd|\x9e\x98\xfc:G\xf3`q\xa1\x18\xdc\xeaz\x18X\xadha\t\x93\xe6\x17)\x8dw8\x99\xcc\xe4\xf9\xf8&lt;[\x81Y\xe6\xdb\xfc\x99\xe5\xe9\x10\xb1\x7fT\xbc\xc2\xac\x9d\xd6`\x887\x85\xc1k\x88)f\x80\xd5\x80\xeb@\x07w\x1a\xba"\xa9\x8a\xfazPv\xab\xd4-\x90\xe8\xb6Y^;U\x99\xad\xa4\xb7\xbe\x8a\xca\x88\x932U\x97%\n\x1a\x12F\xb3d\xd2\x8d\xbe\xc9zh\x14\xe9\x0c#\xdb\x12\x9a\xd6\x84J\xaf\x853\xa3.U);\x13/\xaa\x97:\x94!o\x19\x18\xd8\xce\xccL\xf1@\xb7\xa2\xf6\xae\xa8\xd4V\x12\xa4\x83\xe7Y|\x8dLQw\xfa\xc7\x8d\xb6\xe8Q,\xe6\x8e\x1d\x9e#z~\xed\xed\x85\xccU/\xfe\x929\x03\x80J\x12\xd8\xdb\xfdb\xa5\xaa\x1e\xf4j\xe5\xfe\x94\xaf\xad\x04\x08\xcdV\x89\xce\x98\x90\xd6\xb9\x1f\x97\x05\x96\xee\x01\xca,\x95\x7f\xba\xf9VDZ\x9e\x03\x8f\x95\xe9\xf4\x9e\xabRX\xe4\x7f|N\xb9rIx\xccM\xf3aD\xe7\xf9\xd1\xa2\xe85R\xdf\t\xf7\x02"\x90\xafiN\xa2\xd0\xe8\xc3\xa3\x882D);\x9c\xael5=\x07Y\xe4F\x8b\xa0\x83\xe7,\x98\xfe{\x15\xe4\x04\xdd4al\xfd\xe7\'\xeb\xb9!\xc5\xd6\xf3\x04\x1b\xd2\xe4\x81\xa2\xe4"*\xbc}|:#f\xe4\xd0\x1a9\x8e\x8d7\xd4\xeaX\xd4\x01\xfb%\x16\x98\x1c\xbcq\xf4w\xbc\xbf&gt;T\x02L\xb1F\x1b\x80=\x10*\xc1\xf0oi\xce\xd3\xa5O\xc7\x86.\xf2=\x87\x944\xc3\x19\xca\xc9.\xf7K\xd6\xa7\xe2x\x7fM\xcd\xcd]\xd0\xe4\xbdq\xef\x1a,\xb6\xaf\x89\x7f\xd1\xa8\x1fH`\xe0c\xcd\xdfB\xdc\x1a\x9e\x80\x9d\xef=r\x0c\x8dp\x14\xcb\xf1*\xb6\x00\t\x0f\xe8^\x80\xf9\x91\xee\r\xc2\x85\x174W{\xfb)\xb6\xbd\xb4\xbf\xdfZ\xbc\xb0d\xc0\xf1\xa1,aH\x11\x8f\xe7\x97\xa0\xea*\xd3\xdbR\x81#\xa3\x98\xef\xccU@\x1bMY\xa9\xaa\xa9gy\x1aZ+`\x97{\x87\xbd\xda\xde\xaf\xc1h8{\x9d\xc5z\x88\xe56\xd3\x85\x92O\x04\t_d\x13\xcc\xb3\xa4!\x0f\xe91_Z\x8e\xcdbs\x83m\x10\xfb\xf3\x8dh"\xd6\x16\xeb\x7f\xf2\x7f\xe6\xdb\xf2\xbf\xcb-Di\xd0\x86\x15\x15c\x9f\r\xc8\xeaL\x9a:4\xfe\xa0\xfe\xb5e\xaf\xbe\x84\x07F\x99bK\xaf1\x0c\xed\xe0?-\xea\xb0\x1d\x92\x0c\x0c\xdbX\xfb\x9f\xbb\xd6\xea;\xe5\xb3\xde\xaf|g\xee\xad\xb1l\x9ehA{G\xa7\x93[\xac\xc4\xc6\tCO\xfd\x1d\xae3\xb7v\xf0\xe1\xc7\xb2F&lt;\xa57\xdcHf\x04\xa6\xa0\xa6\x99W1")Z\xbc_x\x82=\x84\x80\x9a\x9d\x92\xc5\xb4Q}\x92\xa2\x9b\x9d\xa9y\xd8\x87\x08\x92\xe8\xee\x0c\xec\xfc^\x9c\x81\x9d\x18\x83\xa5\xee\x17\x95\xa4\x89\xc4\x8fnPzx\xb4\xf3(Q\xb2\x9d~:\x9auC\xf1x\xa4&gt;\xaaa)\x99.\x87\x9a\x9e\xd8(W\xf5\xaa7\xb3Q\xf3\xa8\x04\x9fA r\x84\xa7\x12\x8d@\xdb\x0e\xd3\x93\xdb\xe0\x05\x1bXq\xfc\x13NW\x00xL\xbe\xd8\x1f?\xf1\x14\x8b\xef\xac\xe8\xa9\xdaF0vlS\xebn\x99\xaa\x05F\xb9"\x9c\xda\xcc\xbe5c\xcdf\t\xd3\xbd\xd2\x9e\x8cJ\x11E]\xdc(\x92\x8f\x83\x94\x90\x9c\x84J\x88 \x84\xd4\xa2@-ao\xdd\xbf\xea\xfe(\x0f\xbf\x02\x17\x7f@\xdb\x7f\x08\x02\x04}t|\xa8\r&lt;\xb6\xbe\x81\xaf\x856\rk\xba}\xcf:\xfe\x17x\xdc-ot\xe2Y\x90\x97\xec\x18\x9eU\xac\xf8\xa6\xea\xc9\xe4\xc2\x10\xb2\xd9u\xc4\x82xA\xf0A\x8d\xb0V\xa5\xe4\x8b\xb0\xd3\xfd\xd6\x94\x00\x13\xa6\xfd\xfbh\xf1TM\x89.\xa8\xd5\xd2[\xaa\xf8r\xde\xa6\n\xf3\xf0\x97\x1f\t\xd8\xf2j\xd2\x8bH\x0c\x9b&lt;\x9eN\xa1\xcb\xbfeZ3ui\xeek\xfc\xa9\xe9\x039\xab\xba"#\xd6\xb0\xe6\xdfH\xad\xb9\xc10\xb6!\xec\xe6O]\\\xa4\x91\x14!\xaa\x8f\xf8\x8be\xf0\n\xa9\xd2\xd4(+\xd8\xab\x99&gt;\xbf\xb8\xde\xf2&amp;\x15\xcdb1\x1f5\x9d\xdc\xea\xb5\x1d\xc4\xbf:\xa7\xb6\x00G\x96\xbb\xd6Q\xc5\xfa\xbcC\xb2E\xcc\x17~Q\xff.0{}\xd5J\x11Nl\xf2\x02\x84p\x11\xdc\xd7i\xbb\xd0NY\xe1\x81"\xd8C\x849\xe8\xf5\xa5GI\xcb\x83P"[:\xaa\x93C\xb5s\x1f\xdf;\x04\xa42, \x8e\x11S\xfbHj\xe9\xd1\x8f\x8cm\xcb\x9f\xd4STsS\x17\x1b!\x7fj\xbf\xdc\x0f\xfe5T\x9d\xdfcP\x19"\xe1\xdd\xeft\xd1z`v\xba\xfc\x80m"\x12=\x7f[h\xc0\xfdc+L\xba\xadF\x06\xd7\xc2\xf0\x99\xdb!\r\x94A\xf4\x82\x05\x03\xe6F\xdd%A`\x92\xa4\x9f\x8b\xcf2W\xd2`\xa2\xd0\xf0\xb0"jO^F\xbd\x0f(\xff\xc5\n\xe3\xc3{qe\xa02W\xc0\xfa\xdc\xe1\x1fO\x0c\x92\x02\xe5LQU\xed\x885\xbe76\xb7(\xc2\x19\xdf\xec\xc3\xf6CmZ\xee\xaap\x1dx\x1f\xffQ\xc8\xe8\xfd/\x8el\x91\x0f\x9a\xc3+G\xc0\x97[\xb64\xbf\x83\xb5\x99\xc8\xe0\xbb\xfc\x8d\x0ew\xf3W\x02\xfe\xb3\x82W\x9f\xde\xdeO\x7f\x17!z;\x1b\x16=\x81\x05\xfd\xcb~\xaf\xa4\xa62\'\x84\xc1\'P\xfa\x98\x03\xfd]\xee\\rKM\x06\x98E\x8da\xbf\x9dU\x1d%\xa5\xb9\xd8#\xba\xa8F\xa6mQ\xc3\x9f,\x0b^\xea\x036!\x08\xb2,\xdc\x10\x06w=\xdb6\\@\x0e*\xab\x88\xcd\x88\x19\xc2%\xc7\xb0\xb6\xe7\x9d\xef\xc7\xe2\xc4\x13\x07\xe86u\x81M\x1b\xd4d\xae\xb5c\x1a\x10\x82\x1c\xca%\xcc\xda\nZ\xdc\xe0\xd4%%\xaf+\xfc\'\x17\xe7$\xd0a\xea|\xc9\xc1\x1d\xbdL\x9be(\xbc\x1f&gt;t\xfe/\xf2fw\xc00\xb79\xab$;l\xf6\xad\xbeP8\x0ew\x0e1V\xc1\xcb\xfa\xc73j\xd8\xbd\x81\xab\xee\xcc\x89`\x837XcP\x8181&gt;t\xd6\x19\xcf\xbb\x886\x14\x11\xfa\x8e\xa4\xc7\x97\xd2\xa2\xf8U\x96\xbc\x1f\x17\xce\x0e z\xfb\x89\xfc\x82\xa5I\x1d!\xf2\x81D\x15[\xd0\xa7\xcdy\xb0D\xf7\xfd\x8b\x96\xce\x15\xfd\xfc\xb4\xa7+\xbd\x03\xc6\x01B\xb9\x0e~X\xcc\xe6\x06\x14\x98L\xdd1\x1e\xd9\xac\x95\xa3z\xa1\n\x0e\xcc\x99a\xf4BU\xb6\x87\xba\xdfl\xc0|\x01&gt;l\xfa\xdb\x1a\xacPMS\x17\xfd\x84\xc5A\x88\x112T\xf2\xedq\xb7\x11q{=\xe7\xa3\xce\xb1\xbb\x80\x90\xbc\xfd\x051\x81\xe1(\xef\xbe\xe7z\x04\x88\xa1Ij_\x7f\xb9&gt;\x0b\xb4\xad\xe4?y\xd9\xcd\x94&gt;2\xefy\xeaiX\x13\x96\xa8l\xd1s\'\xe6\x97)\x08\xaf\xc8\xf6\x0c?\xec\xc6M\xb1\xaak\x94\x80\xe8\xaf\xbe\xb7\xe3u\x1f\x90\'\xc3\x83\x0e\x9bj\xd1a\x98\xf4\x1f\xa1\xb5&lt;Z\x0b\xfd^_\xef\xd1d\x16O\x83\x05\x90\xa8\xef(\x01#&gt;\xa3s\x0b*+\xb7%\xf3\tJ\t\x97\xae\x9a \x8e\x9fs9\x9c?W\xb1\xa8)\xe2\x82\xac\xf7\x15\xf7\xa4a\xa0\xf9\xb0,9\xff`\xd9\xb4\xf5F\x14\x08+\x8b\xcc\x9eT\x10\x1f\xea\x01\x86\x08\x96g$\xa0v\xf19\xe1\xb8\x98\\B\x8aJ\xcbg\xb4\x0bT\xf29\xd9\x90\xa7\x04"\x83\x84M\xbeoX\xecx\xb8\xfc\x85\xcfB\x0b&amp;\xba\xe0\rd\xdc\xd5X\xab,#\x8f\x1a\x7f\x9f\xebV;\x88\xe1-&gt;\xd76y\xdfg\x19N\xceT\xddCnl\x98\x88\xa5\xce\xb4\'\xben\xb7\xfd7HJ\xe4\xa7WA}\x89\xe5om\xfcv"^\x90\x17\xb1\xce\xa7\x9d\xf6\xbb\xc4\x10\xdd\x87q\x96N\x14+V~\xab\xc4\x1c\xfd\xc3\xcdv\xe7c&gt;\xa1}~\xc2\xad\xb4\x08\xd9\x11\x8d\x87\xe2\xbeS\x9f\x80\x16\xc7\x84*0\xcc\xf2\x89\xf0\xa1l\x0f\xfe\xefK#\x80\xfd\xd8\x13\xfe\xb1\xe7V\xd0\x05\x16\\F\x85\xd6\xc9ha-9\x9bNb^\x1c"\xa5\x1ce\xf2\xae\x0f\xf8\x91\xf3\xbd\xf3R\xefb\x93t\xcc\x82\x96\xd5\xfeYj\xf0X3:\xee|\x96\xe0\x9alP?\xc2\x04\xbe\xc9\xc7\xef\x83\xdeme/ xJ\x9f\xe8\xc0f\x98@}\xa7\x86\xa5"\xdeZ4\xdd\xdf\xf6C\xc3\x07\xd5H\x8e\x16\xf8\x94#9\n\x9bN\x8a)\xb2\x8dD\xc8\xc7\x000\xcc\xba\xf9I\x92\x0c/\xf4\xc9\x8b\x1a\xdfk\xc2&lt;\xee\x14=\xc3\xa1\xea*\xa6L,BN?\x06\x8a\x9e\x9cPp\xe9U;\xdfN`\xa8\x9e\xb6\xe8\xa2\x1bRh\xe5\x14\xe0\xc2\x15\xb36f\xd0\xa6\x18!\x7f(\x82\x03\xce\xda\xfe\x11]\xd1\x1a.\x01\xd2\xbf\x07k8Y5\r\xa0\xc3\x99|_\xd0\x80\xa8&amp;\xd1cE\x89\xa3\x80\xcb~\xf6\xb0\xc6\xfb9`\xe9\xb0I-n\x1d\xda\xfa_\xf5\xe2B\xc75Y\xb8\xed\xccz\xddg.\x1a/\xa4v\x83V,!\x81\x01\xe1\t\x0e\x01\xd3\xa8\xa1W\xeal&lt;\xe8@\x92\x90\x80n9\xd7\x1f4T\x16\xe8M\x91\x80\xf3\x13SO\n\x0b~\x15=\xb3\xc2v\xec\x1e\xb8\n\xa6w\xd2\xe7n\x9c\\\x03\x9by\x93\x8e\xa0\xe1&amp;\xf8&amp;e\x86\xe9\x18h\x04zm\xf0\xc5\x1e\xfe\xcc\xe8U\xa9\xc1\xa2@\xae\xef\xb7\x8e\xc9$D"\xe2\xba C\xf7\x1a\xf3\xae\x13\xc5|\xbd\xb7\x0e\x0b\xa9e\xab\x13VW\xe6\xaa\x93\x16\xc7\xb8s\x8b\xbd\xcb\xc1+\xb1_xC\x12\xc346\x08u\xd7w\x07\x9a!%\xfe\xb4\x01\xbc\x9c\xaa\x95\xfa,\x82\xd8\xc5G\x1d\xb3\xf8\x90g\xd8\x06\x12qs\xbcM\xac\xd6\xe7\xad\x90\xdac\x1dN\xc1\x12\xcb\xee\x07}\xe4ui-\x86\x92\x1a\xfe\x0fHPl\x9f\xf4\xea\xbf\xf7\xd7\x98b\xb0\x0c\xc17g.4\x97.\xb1`\xcfV1\xd2\x88\xa3F\xec\xaa\xa8\xfe\x8a\x1a\xec\x87\x9exB\xcf\xf1\xd9a\xc6i\x11\x11\xbc\x03B\xae\xea\x84WF\xab\x80m&amp;s&gt;P\x85\xa6\xf0\xbeC:f\x90`\x07\xd9-\xcdY\x16\x13\xde\xd9RO\xf6\xc4\x7f\xe5\xcfG2}\xaf\n\x05K\xe5[.\x04\xd9\x90@\x00\x18Z\xd0O\xf2\xe96\x8d\x95W\x8c\xea7\x8f \xe5\x9f\xf3d7\xd6}\xd1\xef\xfd\xf3\xf3\x1b\xc1o\xfdw\xd4\xcd\x13\xb5\xe7\x8f`\x99\xee\xb1\x90Tt\x90\xa2\xff\x80\xc9k\x96Q\x9a[\x04\x14l\x9d\xf0C\x90\'\xc2\xac\x15\xa3\xab,\xee\xf0\x8b \r\xd9\x11\xfcBs\xf6\xb9\xf0s|\xb2\xa1K\x19\x97Oid\xfa\xf4\x97P\x13&gt;\x8d\x96\xe5I\x91@\x9c&amp;\xa49\x8c\xeaY\xfc(\xa7\xccr\xec;B!\\w\x9d\x13\xe4A7\xd8C\xe0\xfe"!\xaf@\x11V!c\xfe\x8f\xaeC\xbf?\xb0\x99.5\xe4\xd29\x00\xae\xf1"\xf8\xd5\xba\xd1!]1fA\x83\x14_\x7f\x9el\xcb\x98*M\x97,I\xa3\x14f\x1a\'\x9d\x02\x18\x1bZ\x12\x1dv\x1e\xad\xe29\x80_Y7\x0e!\xb8;\xd4\xfeI\xf3\xfe\x0b\xb1\x1e\xdf\xad\x1d^B\x8cM\xd0\xcf\x08}\x85f=S\xaf\x83\x9b\xdc\x08\xbef\xads\xf7\x99D\xc3Y\xe5V_\xfc\x9a\xd1\xad\xdd\xbfK\xbb{\xa8\xadA\xbc\xe3\r\xb3k\x10\xec=*~ (\xfcgs\xfc{\xa4P\xeaA|\xe5*\xc0\x04x/6\xeb\x8d\xeao\xa4\xb9\xd1\x17\xf3\x11\x1a\xdfV\xeb\xb9E\xb1\x90V\xed\xc3mb\xb3\xcd&lt;\x1b0\x1e\x08\x1e.:\xf1t(3\xc0\x90\xf96/\xdf\xd8%X5A\xbc\xfa\x13\x93x\xa2\xc4\xab\x8e\xda\xb4\'\xbeS\x9e\x9d\xa9\t\xbc\xa7\x9fr\xfd3M\xc2g8*!\xe0\xc7&gt;%\x80\xac\xc73\x13\x18\xdc\xa5@\xc2\x8e\xe7\xaa@\xa0`\xabUST\xbd\xaft#\xdd\x01\xf6\xef#/\xf1TXU\x08O\xdas\xf3X1j\xb8\x8a\xc4\xa5\xd24\xc3]\xe2\x1e-\x0e\x9a\x94?\x8b\xe0[\x13\xfb\x00+u \xd1\xe4\xcc\xd9\xa7*\xe2KN\x8e\x1b\xa3\xa1\xdc1[\xbbp^\x89\x96\xdc\xf8d\xd0\x90\x181L\xd3\xb0\x15\xa9*\x15\xb6\xaa\x95\xa9\xdd\xdc"^\x01\x95\xe6\x15mB\xda\x89#\xc9\xf4\x86\xd9\xa7\x865t`\x0f\xfa\xd4\x9d\xb0\xc5\nZ\xa4\\\xd3\xc6\xf4\x9c\x88\x83\x1d\nk3o\x88\xa7\xe2i!.JOy\x86b\xb2\x01cJ\xd1U\xf0E\x04P.\x00\xbb\xb2\x15\x14\xd8\x1c|\xd1\xf1v\x8f\t\x96\x8d\xe4\x18&gt;gl\x00\x1e\x82\x89X\xe9R\xc4T\x86\xf2\t\xddw7NQ\xa6#\x8d\xd0Ai\xe4\x89o\x84\xad-\xa7s\x17\xdbh\x02\xcf\n7\x1f\x85\xc6\xafp\x9e\x98\x81~\xcfc\x12\x99C\x02\x0e\xfe\xc7\x92&gt;\xd8\xeca\xb2\xc50\xa8\x02\xbe\xe5\x96\xda\x01\x00\xe3O\xf2\xe04\xdex\xcb\xea\x88\xd5x\xd1\xef\x1anY\x1c\x9fA\x15\x08\xb7\xca\xc9F\x1b\xc8:\x85\xdc\x0e\xf0\xad\x07yR8?\xa7\xb0\xf5\x9b\xf3\xa6\x85\xcf4\xbd\x85z\x939\xaf\x93\x80\xf3_Q\x05\xf5\xe4\x07m\xdb\x01(\xb9\xb5I\xdc\xe9\xbb~\x00e(G*6\xd8\xaf\xeb\x16\x86\xfd^\xdf\x99Mk\xa2!\xadY\xc9\x0cp{\x0ed\xb9"\xa3\x8bR\\#\x87\xaf\xfd]\x85\xb7\xa6\x0b\xb0\x1f\xfa|\x8a\xba:\xe9\x13t\x10\xd6]\xe2\x06\xa0`]\xb9\xd9Y"\x00\xd2\x06\x9f\xd3\'6\x9c\x02Oz=E\x08\xd4x\x16\x93\xf9z\x19\xd8\x16&lt;K!\xf9\xaaww\x8c\xb69&amp;\n?\xe1-\xab\x10\x0c\x03\xaf\x19b\xde\xfd\xc64\xe7\x84 \x85_IboL\xb0#\xd4\x00\xfe\xea\xf9\xa8\x82\xda\xc0bY\x1b\x16.\xc1+\x92\xf5\x12a4=\xb2i\x96i\xd9\xdb\x8e@\xb5\x8fU\x18\x8b\xe5\xb3\xa4vt\x07\x92\xc1\x00jW\xc2\xe8z\xa1\xd6\xeb\x16\xdd\xab\xf7\xfb\x14i\xd5\x17.o\x8bX\xa3b\xc6,\xa6\x81\xd7\x13[\x07u*\xf8\xfb\xdbt.0\xfd|\xaa\x1d\xa1\xcb\xd0\x03\xe9\xeco2\xd7Ykq\xd7\xd8\x95\xeb0\xd4\x1cGg\x95\xc4+CA\xef\xd9\x7f\xfc\x93\x04\xa7\xa8\x82F\xc5\xa7\xe8\xe6g\xc2K\\@\xaa\xc3\xc30w\xd2&amp;\xf8\n\xbf\x08\x11)\xbcn\x91\xe2E\x85V\r\xaf\x05+3\xcdf\xfc\xf2\xbd\x1d\xc2\xb4\xa1\xa6\xed\x08\xefecc1\xf1$\x01\x12\xea\x87\xbe\xfb&gt;H\xc0\x85\x85\xd5\x99\x1a\x06\x8f\xf0L\x8d\xea\xf6\x07\xf2\x7f \x0ez\x1f8\xf0\xbd8\xfea\x01\x87\xb03\xba\xdd\x88\xe4Ii\xcc\xc5$5\xc8\xda\x0c\xc2\xaa\xf2\x05\x8dp^\xad\xd3 \xabp]\xb1\xb4J\xab\xe2\x115O*\xf1\xb4\x9dymR\xd2\x80(\xa3\x91_\xde\x84nK\x91\xd0\x0e\xb6\x1a$(\xe5\x02r,RR\x0fy\xe7"$&gt;K[\xec0\xe1&amp;T\xf9+\xc6\xdb\x07B,\xd3gk\x12W\x85\x90N\xe1\x06\xa2\xfa\x13\xaa\x0f)\x80S\xb3\xe7y\xc3(\xb8Fo\xecK,\xc5\xd0\xeb/iFD\xe7\xf7\xa1[G\xe0\xdf{\xcdJ\xe3\x1f\xee\xf9*\xd5\x97\xf6\xcfZ\xee\xa6n\x85\xe4\xffVf\x07\x90\x9a\x95\xc1V!\xdb&gt;\xc4\xb9W\xe2\xed\xbbo\xed\x12V\x18`\x80\x05|s\x9d\x8c\xd9uS \xfc\xfd\x88?\xdc\x9aT\xf9\xe2\xbb\xf5\x15\xf2%&lt;\xdc\x16\x99}\xe5\xd0qL\x80u/\x91\xc6\xf3\xa0\x8a\x98\x1d\x98q\x02\xe2\\\xe3\xd8\xbf\t\x11jd\x03S\xe5\xa3\xbdC\x91g\x8fmn\x08\x00?5\xefe \xda\xd9\x05\xd2\x18\x9b\xa2\x92\xc3.;\x15\xaa\xb8F\x89p\x1b\xe4]\xb2\xce%]9\x11[\xd6\xa2\xd0\x81\x15\xb5\xf0\xd2\x80L\x88\x0</t>
         </is>
       </c>
     </row>
